--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, o custo-hora (da planilha 05), impostos, as margens mínima e alvo e a folga para horas não previstas. Isso vira hora mínima e hora alvo.</t>
+          <t>Em Config, o custo-hora (da planilha 05), impostos, as margens mínima e alvo e a folga para horas não previstas. Isso vira a hora mínima com folga e a hora alvo com folga: a hora mínima da 05 (R$ 110 no exemplo) acrescida de 20 % de horas não previstas (R$ 127,88).</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie "O que cobramos hoje, por área" e peça à IA para apontar onde o escritório está cobrando abaixo do custo e sugerir uma conversa de reajuste. Os valores da tabela são do seu escritório, não uma tabela oficial.</t>
+          <t>Copie "O que cobramos hoje, por área" e use o prompt "Honorários 06 · Montar a tabela de referência interna" da biblioteca do kit para apontar onde o escritório está cobrando abaixo do custo e sugerir uma conversa de reajuste. Os valores da tabela são do seu escritório, não uma tabela oficial.</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -1020,9 +1020,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Tabela de referência de honorários · "&amp;Config!$B$5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Tabela de referência de honorários · Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -1035,13 +1035,13 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Hora mínima</t>
+          <t>Hora mínima com folga</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Hora alvo</t>
+          <t>Hora alvo com folga</t>
         </is>
       </c>
       <c r="D4" s="10" t="n"/>
@@ -1067,27 +1067,27 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>Config!$B$12</f>
-        <v/>
+        <v>127.880129032258</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>Config!$B$13</f>
-        <v/>
+        <v>168.692936170213</v>
       </c>
       <c r="D5" s="10" t="n"/>
-      <c r="E5" s="17">
+      <c r="E5" s="17" t="str">
         <f>COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo"))</f>
-        <v/>
+        <v>10 de 38</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>SUM('Nossos casos'!$K$5:$K$204)</f>
-        <v/>
+        <v>11876.6896774193</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="19">
         <f>IFERROR(SUM('Nossos casos'!$F$5:$F$204)/SUM('Nossos casos'!$G$5:$G$204),0)</f>
-        <v/>
+        <v>153.314696485623</v>
       </c>
       <c r="J5" s="14" t="n"/>
     </row>
@@ -1169,19 +1169,19 @@
       </c>
       <c r="F9" s="25">
         <f>IF(OR(A9="",C9=""),"",C9*Config!$B$12)</f>
-        <v/>
+        <v>383.640387096774</v>
       </c>
       <c r="G9" s="25">
         <f>IF(OR(A9="",D9=""),"",D9*Config!$B$13)</f>
-        <v/>
+        <v>1349.5434893617</v>
       </c>
       <c r="H9" s="25">
         <f>IF(OR(F9="",G9=""),"",(F9+G9)/2)</f>
-        <v/>
-      </c>
-      <c r="I9" s="26">
+        <v>866.591938229238</v>
+      </c>
+      <c r="I9" s="26" t="str">
         <f>IF(A9="","",IF(E9="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E9="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E9="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="10">
@@ -1208,19 +1208,19 @@
       </c>
       <c r="F10" s="25">
         <f>IF(OR(A10="",C10=""),"",C10*Config!$B$12)</f>
-        <v/>
+        <v>767.280774193548</v>
       </c>
       <c r="G10" s="25">
         <f>IF(OR(A10="",D10=""),"",D10*Config!$B$13)</f>
-        <v/>
+        <v>2530.39404255319</v>
       </c>
       <c r="H10" s="25">
         <f>IF(OR(F10="",G10=""),"",(F10+G10)/2)</f>
-        <v/>
-      </c>
-      <c r="I10" s="26">
+        <v>1648.83740837337</v>
+      </c>
+      <c r="I10" s="26" t="str">
         <f>IF(A10="","",IF(E10="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E10="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E10="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="11">
@@ -1247,19 +1247,19 @@
       </c>
       <c r="F11" s="25">
         <f>IF(OR(A11="",C11=""),"",C11*Config!$B$12)</f>
-        <v/>
+        <v>6394.0064516129</v>
       </c>
       <c r="G11" s="25">
         <f>IF(OR(A11="",D11=""),"",D11*Config!$B$13)</f>
-        <v/>
+        <v>16869.2936170213</v>
       </c>
       <c r="H11" s="25">
         <f>IF(OR(F11="",G11=""),"",(F11+G11)/2)</f>
-        <v/>
-      </c>
-      <c r="I11" s="26">
+        <v>11631.6500343171</v>
+      </c>
+      <c r="I11" s="26" t="str">
         <f>IF(A11="","",IF(E11="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E11="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E11="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
     <row r="12">
@@ -1286,19 +1286,19 @@
       </c>
       <c r="F12" s="25">
         <f>IF(OR(A12="",C12=""),"",C12*Config!$B$12)</f>
-        <v/>
+        <v>1918.20193548387</v>
       </c>
       <c r="G12" s="25">
         <f>IF(OR(A12="",D12=""),"",D12*Config!$B$13)</f>
-        <v/>
+        <v>5904.25276595745</v>
       </c>
       <c r="H12" s="25">
         <f>IF(OR(F12="",G12=""),"",(F12+G12)/2)</f>
-        <v/>
-      </c>
-      <c r="I12" s="26">
+        <v>3911.22735072066</v>
+      </c>
+      <c r="I12" s="26" t="str">
         <f>IF(A12="","",IF(E12="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E12="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E12="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="13">
@@ -1325,19 +1325,19 @@
       </c>
       <c r="F13" s="25">
         <f>IF(OR(A13="",C13=""),"",C13*Config!$B$12)</f>
-        <v/>
+        <v>1023.04103225806</v>
       </c>
       <c r="G13" s="25">
         <f>IF(OR(A13="",D13=""),"",D13*Config!$B$13)</f>
-        <v/>
+        <v>4217.32340425532</v>
       </c>
       <c r="H13" s="25">
         <f>IF(OR(F13="",G13=""),"",(F13+G13)/2)</f>
-        <v/>
-      </c>
-      <c r="I13" s="26">
+        <v>2620.18221825669</v>
+      </c>
+      <c r="I13" s="26" t="str">
         <f>IF(A13="","",IF(E13="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E13="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E13="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
     <row r="14">
@@ -1364,19 +1364,19 @@
       </c>
       <c r="F14" s="25">
         <f>IF(OR(A14="",C14=""),"",C14*Config!$B$12)</f>
-        <v/>
+        <v>383.640387096774</v>
       </c>
       <c r="G14" s="25">
         <f>IF(OR(A14="",D14=""),"",D14*Config!$B$13)</f>
-        <v/>
+        <v>1349.5434893617</v>
       </c>
       <c r="H14" s="25">
         <f>IF(OR(F14="",G14=""),"",(F14+G14)/2)</f>
-        <v/>
-      </c>
-      <c r="I14" s="26">
+        <v>866.591938229238</v>
+      </c>
+      <c r="I14" s="26" t="str">
         <f>IF(A14="","",IF(E14="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E14="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E14="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="15">
@@ -1403,19 +1403,19 @@
       </c>
       <c r="F15" s="25">
         <f>IF(OR(A15="",C15=""),"",C15*Config!$B$12)</f>
-        <v/>
+        <v>767.280774193548</v>
       </c>
       <c r="G15" s="25">
         <f>IF(OR(A15="",D15=""),"",D15*Config!$B$13)</f>
-        <v/>
+        <v>2530.39404255319</v>
       </c>
       <c r="H15" s="25">
         <f>IF(OR(F15="",G15=""),"",(F15+G15)/2)</f>
-        <v/>
-      </c>
-      <c r="I15" s="26">
+        <v>1648.83740837337</v>
+      </c>
+      <c r="I15" s="26" t="str">
         <f>IF(A15="","",IF(E15="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E15="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E15="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="16">
@@ -1442,19 +1442,19 @@
       </c>
       <c r="F16" s="25">
         <f>IF(OR(A16="",C16=""),"",C16*Config!$B$12)</f>
-        <v/>
+        <v>4475.80451612903</v>
       </c>
       <c r="G16" s="25">
         <f>IF(OR(A16="",D16=""),"",D16*Config!$B$13)</f>
-        <v/>
+        <v>11808.5055319149</v>
       </c>
       <c r="H16" s="25">
         <f>IF(OR(F16="",G16=""),"",(F16+G16)/2)</f>
-        <v/>
-      </c>
-      <c r="I16" s="26">
+        <v>8142.15502402196</v>
+      </c>
+      <c r="I16" s="26" t="str">
         <f>IF(A16="","",IF(E16="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E16="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E16="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Percentual que, na chance esperada, fique dentro da faixa</v>
       </c>
     </row>
     <row r="17">
@@ -1481,19 +1481,19 @@
       </c>
       <c r="F17" s="25">
         <f>IF(OR(A17="",C17=""),"",C17*Config!$B$12)</f>
-        <v/>
+        <v>1918.20193548387</v>
       </c>
       <c r="G17" s="25">
         <f>IF(OR(A17="",D17=""),"",D17*Config!$B$13)</f>
-        <v/>
+        <v>5904.25276595745</v>
       </c>
       <c r="H17" s="25">
         <f>IF(OR(F17="",G17=""),"",(F17+G17)/2)</f>
-        <v/>
-      </c>
-      <c r="I17" s="26">
+        <v>3911.22735072066</v>
+      </c>
+      <c r="I17" s="26" t="str">
         <f>IF(A17="","",IF(E17="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E17="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E17="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="18">
@@ -1520,19 +1520,19 @@
       </c>
       <c r="F18" s="25">
         <f>IF(OR(A18="",C18=""),"",C18*Config!$B$12)</f>
-        <v/>
+        <v>1023.04103225806</v>
       </c>
       <c r="G18" s="25">
         <f>IF(OR(A18="",D18=""),"",D18*Config!$B$13)</f>
-        <v/>
+        <v>4217.32340425532</v>
       </c>
       <c r="H18" s="25">
         <f>IF(OR(F18="",G18=""),"",(F18+G18)/2)</f>
-        <v/>
-      </c>
-      <c r="I18" s="26">
+        <v>2620.18221825669</v>
+      </c>
+      <c r="I18" s="26" t="str">
         <f>IF(A18="","",IF(E18="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E18="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E18="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
     <row r="19">
@@ -1559,19 +1559,19 @@
       </c>
       <c r="F19" s="25">
         <f>IF(OR(A19="",C19=""),"",C19*Config!$B$12)</f>
-        <v/>
+        <v>383.640387096774</v>
       </c>
       <c r="G19" s="25">
         <f>IF(OR(A19="",D19=""),"",D19*Config!$B$13)</f>
-        <v/>
+        <v>1349.5434893617</v>
       </c>
       <c r="H19" s="25">
         <f>IF(OR(F19="",G19=""),"",(F19+G19)/2)</f>
-        <v/>
-      </c>
-      <c r="I19" s="26">
+        <v>866.591938229238</v>
+      </c>
+      <c r="I19" s="26" t="str">
         <f>IF(A19="","",IF(E19="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E19="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E19="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="20">
@@ -1598,19 +1598,19 @@
       </c>
       <c r="F20" s="25">
         <f>IF(OR(A20="",C20=""),"",C20*Config!$B$12)</f>
-        <v/>
+        <v>767.280774193548</v>
       </c>
       <c r="G20" s="25">
         <f>IF(OR(A20="",D20=""),"",D20*Config!$B$13)</f>
-        <v/>
+        <v>2530.39404255319</v>
       </c>
       <c r="H20" s="25">
         <f>IF(OR(F20="",G20=""),"",(F20+G20)/2)</f>
-        <v/>
-      </c>
-      <c r="I20" s="26">
+        <v>1648.83740837337</v>
+      </c>
+      <c r="I20" s="26" t="str">
         <f>IF(A20="","",IF(E20="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E20="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E20="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="21">
@@ -1637,19 +1637,19 @@
       </c>
       <c r="F21" s="25">
         <f>IF(OR(A21="",C21=""),"",C21*Config!$B$12)</f>
-        <v/>
+        <v>3836.40387096774</v>
       </c>
       <c r="G21" s="25">
         <f>IF(OR(A21="",D21=""),"",D21*Config!$B$13)</f>
-        <v/>
+        <v>10121.5761702128</v>
       </c>
       <c r="H21" s="25">
         <f>IF(OR(F21="",G21=""),"",(F21+G21)/2)</f>
-        <v/>
-      </c>
-      <c r="I21" s="26">
+        <v>6978.99002059025</v>
+      </c>
+      <c r="I21" s="26" t="str">
         <f>IF(A21="","",IF(E21="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E21="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E21="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Percentual que, na chance esperada, fique dentro da faixa</v>
       </c>
     </row>
     <row r="22">
@@ -1676,19 +1676,19 @@
       </c>
       <c r="F22" s="25">
         <f>IF(OR(A22="",C22=""),"",C22*Config!$B$12)</f>
-        <v/>
+        <v>1918.20193548387</v>
       </c>
       <c r="G22" s="25">
         <f>IF(OR(A22="",D22=""),"",D22*Config!$B$13)</f>
-        <v/>
+        <v>5904.25276595745</v>
       </c>
       <c r="H22" s="25">
         <f>IF(OR(F22="",G22=""),"",(F22+G22)/2)</f>
-        <v/>
-      </c>
-      <c r="I22" s="26">
+        <v>3911.22735072066</v>
+      </c>
+      <c r="I22" s="26" t="str">
         <f>IF(A22="","",IF(E22="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E22="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E22="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="23">
@@ -1715,19 +1715,19 @@
       </c>
       <c r="F23" s="25">
         <f>IF(OR(A23="",C23=""),"",C23*Config!$B$12)</f>
-        <v/>
+        <v>1023.04103225806</v>
       </c>
       <c r="G23" s="25">
         <f>IF(OR(A23="",D23=""),"",D23*Config!$B$13)</f>
-        <v/>
+        <v>4217.32340425532</v>
       </c>
       <c r="H23" s="25">
         <f>IF(OR(F23="",G23=""),"",(F23+G23)/2)</f>
-        <v/>
-      </c>
-      <c r="I23" s="26">
+        <v>2620.18221825669</v>
+      </c>
+      <c r="I23" s="26" t="str">
         <f>IF(A23="","",IF(E23="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E23="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E23="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
     <row r="24">
@@ -1754,19 +1754,19 @@
       </c>
       <c r="F24" s="25">
         <f>IF(OR(A24="",C24=""),"",C24*Config!$B$12)</f>
-        <v/>
+        <v>511.520516129032</v>
       </c>
       <c r="G24" s="25">
         <f>IF(OR(A24="",D24=""),"",D24*Config!$B$13)</f>
-        <v/>
+        <v>2024.31523404255</v>
       </c>
       <c r="H24" s="25">
         <f>IF(OR(F24="",G24=""),"",(F24+G24)/2)</f>
-        <v/>
-      </c>
-      <c r="I24" s="26">
+        <v>1267.91787508579</v>
+      </c>
+      <c r="I24" s="26" t="str">
         <f>IF(A24="","",IF(E24="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E24="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E24="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Cobre a hora entre a mínima e a alvo; a faixa é o total esperado</v>
       </c>
     </row>
     <row r="25">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="F25" s="25">
         <f>IF(OR(A25="",C25=""),"",C25*Config!$B$12)</f>
-        <v/>
+        <v>767.280774193548</v>
       </c>
       <c r="G25" s="25">
         <f>IF(OR(A25="",D25=""),"",D25*Config!$B$13)</f>
-        <v/>
+        <v>2530.39404255319</v>
       </c>
       <c r="H25" s="25">
         <f>IF(OR(F25="",G25=""),"",(F25+G25)/2)</f>
-        <v/>
-      </c>
-      <c r="I25" s="26">
+        <v>1648.83740837337</v>
+      </c>
+      <c r="I25" s="26" t="str">
         <f>IF(A25="","",IF(E25="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E25="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E25="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="26">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="F26" s="25">
         <f>IF(OR(A26="",C26=""),"",C26*Config!$B$12)</f>
-        <v/>
+        <v>7672.80774193548</v>
       </c>
       <c r="G26" s="25">
         <f>IF(OR(A26="",D26=""),"",D26*Config!$B$13)</f>
-        <v/>
+        <v>20243.1523404255</v>
       </c>
       <c r="H26" s="25">
         <f>IF(OR(F26="",G26=""),"",(F26+G26)/2)</f>
-        <v/>
-      </c>
-      <c r="I26" s="26">
+        <v>13957.9800411805</v>
+      </c>
+      <c r="I26" s="26" t="str">
         <f>IF(A26="","",IF(E26="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E26="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E26="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Cobre a hora entre a mínima e a alvo; a faixa é o total esperado</v>
       </c>
     </row>
     <row r="27">
@@ -1871,19 +1871,19 @@
       </c>
       <c r="F27" s="25">
         <f>IF(OR(A27="",C27=""),"",C27*Config!$B$12)</f>
-        <v/>
+        <v>1918.20193548387</v>
       </c>
       <c r="G27" s="25">
         <f>IF(OR(A27="",D27=""),"",D27*Config!$B$13)</f>
-        <v/>
+        <v>5904.25276595745</v>
       </c>
       <c r="H27" s="25">
         <f>IF(OR(F27="",G27=""),"",(F27+G27)/2)</f>
-        <v/>
-      </c>
-      <c r="I27" s="26">
+        <v>3911.22735072066</v>
+      </c>
+      <c r="I27" s="26" t="str">
         <f>IF(A27="","",IF(E27="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E27="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E27="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="28">
@@ -1910,19 +1910,19 @@
       </c>
       <c r="F28" s="25">
         <f>IF(OR(A28="",C28=""),"",C28*Config!$B$12)</f>
-        <v/>
+        <v>1023.04103225806</v>
       </c>
       <c r="G28" s="25">
         <f>IF(OR(A28="",D28=""),"",D28*Config!$B$13)</f>
-        <v/>
+        <v>4217.32340425532</v>
       </c>
       <c r="H28" s="25">
         <f>IF(OR(F28="",G28=""),"",(F28+G28)/2)</f>
-        <v/>
-      </c>
-      <c r="I28" s="26">
+        <v>2620.18221825669</v>
+      </c>
+      <c r="I28" s="26" t="str">
         <f>IF(A28="","",IF(E28="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E28="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E28="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
     <row r="29">
@@ -1949,19 +1949,19 @@
       </c>
       <c r="F29" s="25">
         <f>IF(OR(A29="",C29=""),"",C29*Config!$B$12)</f>
-        <v/>
+        <v>383.640387096774</v>
       </c>
       <c r="G29" s="25">
         <f>IF(OR(A29="",D29=""),"",D29*Config!$B$13)</f>
-        <v/>
+        <v>1349.5434893617</v>
       </c>
       <c r="H29" s="25">
         <f>IF(OR(F29="",G29=""),"",(F29+G29)/2)</f>
-        <v/>
-      </c>
-      <c r="I29" s="26">
+        <v>866.591938229238</v>
+      </c>
+      <c r="I29" s="26" t="str">
         <f>IF(A29="","",IF(E29="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E29="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E29="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="30">
@@ -1988,19 +1988,19 @@
       </c>
       <c r="F30" s="25">
         <f>IF(OR(A30="",C30=""),"",C30*Config!$B$12)</f>
-        <v/>
+        <v>767.280774193548</v>
       </c>
       <c r="G30" s="25">
         <f>IF(OR(A30="",D30=""),"",D30*Config!$B$13)</f>
-        <v/>
+        <v>2530.39404255319</v>
       </c>
       <c r="H30" s="25">
         <f>IF(OR(F30="",G30=""),"",(F30+G30)/2)</f>
-        <v/>
-      </c>
-      <c r="I30" s="26">
+        <v>1648.83740837337</v>
+      </c>
+      <c r="I30" s="26" t="str">
         <f>IF(A30="","",IF(E30="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E30="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E30="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="31">
@@ -2027,19 +2027,19 @@
       </c>
       <c r="F31" s="25">
         <f>IF(OR(A31="",C31=""),"",C31*Config!$B$12)</f>
-        <v/>
+        <v>3836.40387096774</v>
       </c>
       <c r="G31" s="25">
         <f>IF(OR(A31="",D31=""),"",D31*Config!$B$13)</f>
-        <v/>
+        <v>11808.5055319149</v>
       </c>
       <c r="H31" s="25">
         <f>IF(OR(F31="",G31=""),"",(F31+G31)/2)</f>
-        <v/>
-      </c>
-      <c r="I31" s="26">
+        <v>7822.45470144132</v>
+      </c>
+      <c r="I31" s="26" t="str">
         <f>IF(A31="","",IF(E31="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E31="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E31="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="32">
@@ -2066,19 +2066,19 @@
       </c>
       <c r="F32" s="25">
         <f>IF(OR(A32="",C32=""),"",C32*Config!$B$12)</f>
-        <v/>
+        <v>1918.20193548387</v>
       </c>
       <c r="G32" s="25">
         <f>IF(OR(A32="",D32=""),"",D32*Config!$B$13)</f>
-        <v/>
+        <v>5904.25276595745</v>
       </c>
       <c r="H32" s="25">
         <f>IF(OR(F32="",G32=""),"",(F32+G32)/2)</f>
-        <v/>
-      </c>
-      <c r="I32" s="26">
+        <v>3911.22735072066</v>
+      </c>
+      <c r="I32" s="26" t="str">
         <f>IF(A32="","",IF(E32="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E32="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E32="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
     <row r="33">
@@ -2105,19 +2105,19 @@
       </c>
       <c r="F33" s="25">
         <f>IF(OR(A33="",C33=""),"",C33*Config!$B$12)</f>
-        <v/>
+        <v>1023.04103225806</v>
       </c>
       <c r="G33" s="25">
         <f>IF(OR(A33="",D33=""),"",D33*Config!$B$13)</f>
-        <v/>
+        <v>4217.32340425532</v>
       </c>
       <c r="H33" s="25">
         <f>IF(OR(F33="",G33=""),"",(F33+G33)/2)</f>
-        <v/>
-      </c>
-      <c r="I33" s="26">
+        <v>2620.18221825669</v>
+      </c>
+      <c r="I33" s="26" t="str">
         <f>IF(A33="","",IF(E33="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E33="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E33="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
-        <v/>
+        <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
     <row r="34">
@@ -2468,7 +2468,7 @@
     <row r="49">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>Mínimo = horas de × hora mínima. Máximo = horas até × hora alvo (as duas já incluem a folga de horas de Config). Abaixo do mínimo, o caso paga o custo mas não a margem que o escritório precisa.</t>
+          <t>Mínimo = horas de × hora mínima com folga. Máximo = horas até × hora alvo com folga (as duas incluem os 20 % de horas não previstas de Config; por isso a hora mínima daqui é maior que a da planilha 05). Abaixo do mínimo, o caso paga o custo mas não a margem que o escritório precisa.</t>
         </is>
       </c>
     </row>
@@ -2522,173 +2522,173 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28">
+      <c r="A54" s="28" t="str">
         <f>IF(Config!$E$16="","",Config!$E$16)</f>
-        <v/>
+        <v>Cível</v>
       </c>
       <c r="B54" s="29">
         <f>IF(Config!$E$16="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$16,'Nossos casos'!$J$5:$J$204,"&lt;&gt;"))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C54" s="25">
         <f>IF(Config!$E$16="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
-        <v/>
+        <v>101500</v>
       </c>
       <c r="D54" s="29">
         <f>IF(Config!$E$16="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
-        <v/>
+        <v>632</v>
       </c>
       <c r="E54" s="30">
         <f>IF(OR(Config!$E$16="",D54=0),"",C54/D54)</f>
-        <v/>
+        <v>160.601265822785</v>
       </c>
       <c r="F54" s="31">
         <f>IF(E54="","",E54/Config!$B$12-1)</f>
-        <v/>
+        <v>0.255873504649599</v>
       </c>
       <c r="G54" s="29">
         <f>IF(Config!$E$16="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$16,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H54" s="25">
         <f>IF(Config!$E$16="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
-        <v/>
+        <v>1509.21161290322</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28">
+      <c r="A55" s="28" t="str">
         <f>IF(Config!$E$17="","",Config!$E$17)</f>
-        <v/>
+        <v>Trabalhista</v>
       </c>
       <c r="B55" s="29">
         <f>IF(Config!$E$17="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$17,'Nossos casos'!$J$5:$J$204,"&lt;&gt;"))</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C55" s="25">
         <f>IF(Config!$E$17="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
-        <v/>
+        <v>105400</v>
       </c>
       <c r="D55" s="29">
         <f>IF(Config!$E$17="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
-        <v/>
+        <v>838</v>
       </c>
       <c r="E55" s="30">
         <f>IF(OR(Config!$E$17="",D55=0),"",C55/D55)</f>
-        <v/>
+        <v>125.775656324582</v>
       </c>
       <c r="F55" s="31">
         <f>IF(E55="","",E55/Config!$B$12-1)</f>
-        <v/>
+        <v>-0.0164566045061219</v>
       </c>
       <c r="G55" s="29">
         <f>IF(Config!$E$17="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$17,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H55" s="25">
         <f>IF(Config!$E$17="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
-        <v/>
+        <v>9218.8658064516</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="28">
+      <c r="A56" s="28" t="str">
         <f>IF(Config!$E$18="","",Config!$E$18)</f>
-        <v/>
+        <v>Previdenciário</v>
       </c>
       <c r="B56" s="29">
         <f>IF(Config!$E$18="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$18,'Nossos casos'!$J$5:$J$204,"&lt;&gt;"))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C56" s="25">
         <f>IF(Config!$E$18="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
-        <v/>
+        <v>39400</v>
       </c>
       <c r="D56" s="29">
         <f>IF(Config!$E$18="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
-        <v/>
+        <v>264</v>
       </c>
       <c r="E56" s="30">
         <f>IF(OR(Config!$E$18="",D56=0),"",C56/D56)</f>
-        <v/>
+        <v>149.242424242424</v>
       </c>
       <c r="F56" s="31">
         <f>IF(E56="","",E56/Config!$B$12-1)</f>
-        <v/>
+        <v>0.167049371718866</v>
       </c>
       <c r="G56" s="29">
         <f>IF(Config!$E$18="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$18,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H56" s="25">
         <f>IF(Config!$E$18="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
-        <v/>
+        <v>1115.20516129032</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="28">
+      <c r="A57" s="28" t="str">
         <f>IF(Config!$E$19="","",Config!$E$19)</f>
-        <v/>
+        <v>Empresarial</v>
       </c>
       <c r="B57" s="29">
         <f>IF(Config!$E$19="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$19,'Nossos casos'!$J$5:$J$204,"&lt;&gt;"))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C57" s="25">
         <f>IF(Config!$E$19="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
-        <v/>
+        <v>115000</v>
       </c>
       <c r="D57" s="29">
         <f>IF(Config!$E$19="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
-        <v/>
+        <v>615</v>
       </c>
       <c r="E57" s="30">
         <f>IF(OR(Config!$E$19="",D57=0),"",C57/D57)</f>
-        <v/>
+        <v>186.991869918699</v>
       </c>
       <c r="F57" s="31">
         <f>IF(E57="","",E57/Config!$B$12-1)</f>
-        <v/>
+        <v>0.462243362856868</v>
       </c>
       <c r="G57" s="29">
         <f>IF(Config!$E$19="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$19,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H57" s="25">
         <f>IF(Config!$E$19="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="28">
+      <c r="A58" s="28" t="str">
         <f>IF(Config!$E$20="","",Config!$E$20)</f>
-        <v/>
+        <v>Família</v>
       </c>
       <c r="B58" s="29">
         <f>IF(Config!$E$20="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$20,'Nossos casos'!$J$5:$J$204,"&lt;&gt;"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C58" s="25">
         <f>IF(Config!$E$20="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
-        <v/>
+        <v>22600</v>
       </c>
       <c r="D58" s="29">
         <f>IF(Config!$E$20="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
-        <v/>
+        <v>155</v>
       </c>
       <c r="E58" s="30">
         <f>IF(OR(Config!$E$20="",D58=0),"",C58/D58)</f>
-        <v/>
+        <v>145.806451612903</v>
       </c>
       <c r="F58" s="31">
         <f>IF(E58="","",E58/Config!$B$12-1)</f>
-        <v/>
+        <v>0.140180673231282</v>
       </c>
       <c r="G58" s="29">
         <f>IF(Config!$E$20="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$20,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H58" s="25">
         <f>IF(Config!$E$20="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
-        <v/>
+        <v>33.4070967741918</v>
       </c>
     </row>
     <row r="59">
@@ -3256,307 +3256,307 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="28">
+      <c r="A78" s="28" t="str">
         <f>IF($I78="","",INDEX('Nossos casos'!$A$5:$A$204,$I78))</f>
-        <v/>
-      </c>
-      <c r="B78" s="28">
+        <v>2998500-50.2026.8.26.0515</v>
+      </c>
+      <c r="B78" s="28" t="str">
         <f>IF($I78="","",INDEX('Nossos casos'!$B$5:$B$204,$I78))</f>
-        <v/>
-      </c>
-      <c r="C78" s="33">
+        <v>Ana Beatriz Moreira</v>
+      </c>
+      <c r="C78" s="33" t="str">
         <f>IF($I78="","",INDEX('Nossos casos'!$C$5:$C$204,$I78))</f>
-        <v/>
-      </c>
-      <c r="D78" s="33">
+        <v>Trabalhista</v>
+      </c>
+      <c r="D78" s="33" t="str">
         <f>IF($I78="","",INDEX('Nossos casos'!$D$5:$D$204,$I78))</f>
-        <v/>
+        <v>Êxito</v>
       </c>
       <c r="E78" s="25">
         <f>IF($I78="","",INDEX('Nossos casos'!$F$5:$F$204,$I78))</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="F78" s="29">
         <f>IF($I78="","",INDEX('Nossos casos'!$G$5:$G$204,$I78))</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="G78" s="30">
         <f>IF($I78="","",INDEX('Nossos casos'!$H$5:$H$204,$I78))</f>
-        <v/>
+        <v>85.7142857142857</v>
       </c>
       <c r="H78" s="25">
         <f>IF($I78="","",INDEX('Nossos casos'!$K$5:$K$204,$I78))</f>
-        <v/>
+        <v>2951.60903225806</v>
       </c>
       <c r="I78" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,1)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,1),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="28">
+      <c r="A79" s="28" t="str">
         <f>IF($I79="","",INDEX('Nossos casos'!$A$5:$A$204,$I79))</f>
-        <v/>
-      </c>
-      <c r="B79" s="28">
+        <v>9495290-86.2025.8.26.0503</v>
+      </c>
+      <c r="B79" s="28" t="str">
         <f>IF($I79="","",INDEX('Nossos casos'!$B$5:$B$204,$I79))</f>
-        <v/>
-      </c>
-      <c r="C79" s="33">
+        <v>Helena Duarte</v>
+      </c>
+      <c r="C79" s="33" t="str">
         <f>IF($I79="","",INDEX('Nossos casos'!$C$5:$C$204,$I79))</f>
-        <v/>
-      </c>
-      <c r="D79" s="33">
+        <v>Trabalhista</v>
+      </c>
+      <c r="D79" s="33" t="str">
         <f>IF($I79="","",INDEX('Nossos casos'!$D$5:$D$204,$I79))</f>
-        <v/>
+        <v>Êxito</v>
       </c>
       <c r="E79" s="25">
         <f>IF($I79="","",INDEX('Nossos casos'!$F$5:$F$204,$I79))</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="F79" s="29">
         <f>IF($I79="","",INDEX('Nossos casos'!$G$5:$G$204,$I79))</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="G79" s="30">
         <f>IF($I79="","",INDEX('Nossos casos'!$H$5:$H$204,$I79))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="H79" s="25">
         <f>IF($I79="","",INDEX('Nossos casos'!$K$5:$K$204,$I79))</f>
-        <v/>
+        <v>1951.60903225806</v>
       </c>
       <c r="I79" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,2)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,2),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="28">
+      <c r="A80" s="28" t="str">
         <f>IF($I80="","",INDEX('Nossos casos'!$A$5:$A$204,$I80))</f>
-        <v/>
-      </c>
-      <c r="B80" s="28">
+        <v>9236009-85.2025.8.26.0452</v>
+      </c>
+      <c r="B80" s="28" t="str">
         <f>IF($I80="","",INDEX('Nossos casos'!$B$5:$B$204,$I80))</f>
-        <v/>
-      </c>
-      <c r="C80" s="33">
+        <v>Bistrô 42</v>
+      </c>
+      <c r="C80" s="33" t="str">
         <f>IF($I80="","",INDEX('Nossos casos'!$C$5:$C$204,$I80))</f>
-        <v/>
-      </c>
-      <c r="D80" s="33">
+        <v>Trabalhista</v>
+      </c>
+      <c r="D80" s="33" t="str">
         <f>IF($I80="","",INDEX('Nossos casos'!$D$5:$D$204,$I80))</f>
-        <v/>
+        <v>Êxito</v>
       </c>
       <c r="E80" s="25">
         <f>IF($I80="","",INDEX('Nossos casos'!$F$5:$F$204,$I80))</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="F80" s="29">
         <f>IF($I80="","",INDEX('Nossos casos'!$G$5:$G$204,$I80))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="G80" s="30">
         <f>IF($I80="","",INDEX('Nossos casos'!$H$5:$H$204,$I80))</f>
-        <v/>
+        <v>88.8888888888889</v>
       </c>
       <c r="H80" s="25">
         <f>IF($I80="","",INDEX('Nossos casos'!$K$5:$K$204,$I80))</f>
-        <v/>
+        <v>1754.60580645161</v>
       </c>
       <c r="I80" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,3)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,3),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="28">
+      <c r="A81" s="28" t="str">
         <f>IF($I81="","",INDEX('Nossos casos'!$A$5:$A$204,$I81))</f>
-        <v/>
-      </c>
-      <c r="B81" s="28">
+        <v>6710873-21.2025.8.26.0571</v>
+      </c>
+      <c r="B81" s="28" t="str">
         <f>IF($I81="","",INDEX('Nossos casos'!$B$5:$B$204,$I81))</f>
-        <v/>
-      </c>
-      <c r="C81" s="33">
+        <v>Escola Aurora</v>
+      </c>
+      <c r="C81" s="33" t="str">
         <f>IF($I81="","",INDEX('Nossos casos'!$C$5:$C$204,$I81))</f>
-        <v/>
-      </c>
-      <c r="D81" s="33">
+        <v>Cível</v>
+      </c>
+      <c r="D81" s="33" t="str">
         <f>IF($I81="","",INDEX('Nossos casos'!$D$5:$D$204,$I81))</f>
-        <v/>
+        <v>Misto</v>
       </c>
       <c r="E81" s="25">
         <f>IF($I81="","",INDEX('Nossos casos'!$F$5:$F$204,$I81))</f>
-        <v/>
+        <v>10000</v>
       </c>
       <c r="F81" s="29">
         <f>IF($I81="","",INDEX('Nossos casos'!$G$5:$G$204,$I81))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="G81" s="30">
         <f>IF($I81="","",INDEX('Nossos casos'!$H$5:$H$204,$I81))</f>
-        <v/>
+        <v>111.111111111111</v>
       </c>
       <c r="H81" s="25">
         <f>IF($I81="","",INDEX('Nossos casos'!$K$5:$K$204,$I81))</f>
-        <v/>
+        <v>1509.21161290322</v>
       </c>
       <c r="I81" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,4)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,4),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="28">
+      <c r="A82" s="28" t="str">
         <f>IF($I82="","",INDEX('Nossos casos'!$A$5:$A$204,$I82))</f>
-        <v/>
-      </c>
-      <c r="B82" s="28">
+        <v>4526984-60.2026.8.26.0258</v>
+      </c>
+      <c r="B82" s="28" t="str">
         <f>IF($I82="","",INDEX('Nossos casos'!$B$5:$B$204,$I82))</f>
-        <v/>
-      </c>
-      <c r="C82" s="33">
+        <v>Transportadora Rota Sul</v>
+      </c>
+      <c r="C82" s="33" t="str">
         <f>IF($I82="","",INDEX('Nossos casos'!$C$5:$C$204,$I82))</f>
-        <v/>
-      </c>
-      <c r="D82" s="33">
+        <v>Trabalhista</v>
+      </c>
+      <c r="D82" s="33" t="str">
         <f>IF($I82="","",INDEX('Nossos casos'!$D$5:$D$204,$I82))</f>
-        <v/>
+        <v>Êxito</v>
       </c>
       <c r="E82" s="25">
         <f>IF($I82="","",INDEX('Nossos casos'!$F$5:$F$204,$I82))</f>
-        <v/>
+        <v>9000</v>
       </c>
       <c r="F82" s="29">
         <f>IF($I82="","",INDEX('Nossos casos'!$G$5:$G$204,$I82))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="G82" s="30">
         <f>IF($I82="","",INDEX('Nossos casos'!$H$5:$H$204,$I82))</f>
-        <v/>
+        <v>112.5</v>
       </c>
       <c r="H82" s="25">
         <f>IF($I82="","",INDEX('Nossos casos'!$K$5:$K$204,$I82))</f>
-        <v/>
+        <v>1230.41032258064</v>
       </c>
       <c r="I82" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,5)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,5),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="28">
+      <c r="A83" s="28" t="str">
         <f>IF($I83="","",INDEX('Nossos casos'!$A$5:$A$204,$I83))</f>
-        <v/>
-      </c>
-      <c r="B83" s="28">
+        <v>5900991-46.2026.8.26.0469</v>
+      </c>
+      <c r="B83" s="28" t="str">
         <f>IF($I83="","",INDEX('Nossos casos'!$B$5:$B$204,$I83))</f>
-        <v/>
-      </c>
-      <c r="C83" s="33">
+        <v>José Antônio Ribeiro</v>
+      </c>
+      <c r="C83" s="33" t="str">
         <f>IF($I83="","",INDEX('Nossos casos'!$C$5:$C$204,$I83))</f>
-        <v/>
-      </c>
-      <c r="D83" s="33">
+        <v>Previdenciário</v>
+      </c>
+      <c r="D83" s="33" t="str">
         <f>IF($I83="","",INDEX('Nossos casos'!$D$5:$D$204,$I83))</f>
-        <v/>
+        <v>Êxito</v>
       </c>
       <c r="E83" s="25">
         <f>IF($I83="","",INDEX('Nossos casos'!$F$5:$F$204,$I83))</f>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="F83" s="29">
         <f>IF($I83="","",INDEX('Nossos casos'!$G$5:$G$204,$I83))</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="G83" s="30">
         <f>IF($I83="","",INDEX('Nossos casos'!$H$5:$H$204,$I83))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="H83" s="25">
         <f>IF($I83="","",INDEX('Nossos casos'!$K$5:$K$204,$I83))</f>
-        <v/>
+        <v>1115.20516129032</v>
       </c>
       <c r="I83" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,6)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,6),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="28">
+      <c r="A84" s="28" t="str">
         <f>IF($I84="","",INDEX('Nossos casos'!$A$5:$A$204,$I84))</f>
-        <v/>
-      </c>
-      <c r="B84" s="28">
+        <v>8056747-83.2026.8.26.0561</v>
+      </c>
+      <c r="B84" s="28" t="str">
         <f>IF($I84="","",INDEX('Nossos casos'!$B$5:$B$204,$I84))</f>
-        <v/>
-      </c>
-      <c r="C84" s="33">
+        <v>Bistrô 42</v>
+      </c>
+      <c r="C84" s="33" t="str">
         <f>IF($I84="","",INDEX('Nossos casos'!$C$5:$C$204,$I84))</f>
-        <v/>
-      </c>
-      <c r="D84" s="33">
+        <v>Trabalhista</v>
+      </c>
+      <c r="D84" s="33" t="str">
         <f>IF($I84="","",INDEX('Nossos casos'!$D$5:$D$204,$I84))</f>
-        <v/>
+        <v>Fixo</v>
       </c>
       <c r="E84" s="25">
         <f>IF($I84="","",INDEX('Nossos casos'!$F$5:$F$204,$I84))</f>
-        <v/>
+        <v>9500</v>
       </c>
       <c r="F84" s="29">
         <f>IF($I84="","",INDEX('Nossos casos'!$G$5:$G$204,$I84))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="G84" s="30">
         <f>IF($I84="","",INDEX('Nossos casos'!$H$5:$H$204,$I84))</f>
-        <v/>
+        <v>118.75</v>
       </c>
       <c r="H84" s="25">
         <f>IF($I84="","",INDEX('Nossos casos'!$K$5:$K$204,$I84))</f>
-        <v/>
+        <v>730.410322580643</v>
       </c>
       <c r="I84" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,7)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,7),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="28">
+      <c r="A85" s="28" t="str">
         <f>IF($I85="","",INDEX('Nossos casos'!$A$5:$A$204,$I85))</f>
-        <v/>
-      </c>
-      <c r="B85" s="28">
+        <v>9420478-99.2025.8.26.0491</v>
+      </c>
+      <c r="B85" s="28" t="str">
         <f>IF($I85="","",INDEX('Nossos casos'!$B$5:$B$204,$I85))</f>
-        <v/>
-      </c>
-      <c r="C85" s="33">
+        <v>Ana Beatriz Moreira</v>
+      </c>
+      <c r="C85" s="33" t="str">
         <f>IF($I85="","",INDEX('Nossos casos'!$C$5:$C$204,$I85))</f>
-        <v/>
-      </c>
-      <c r="D85" s="33">
+        <v>Trabalhista</v>
+      </c>
+      <c r="D85" s="33" t="str">
         <f>IF($I85="","",INDEX('Nossos casos'!$D$5:$D$204,$I85))</f>
-        <v/>
+        <v>Misto</v>
       </c>
       <c r="E85" s="25">
         <f>IF($I85="","",INDEX('Nossos casos'!$F$5:$F$204,$I85))</f>
-        <v/>
+        <v>8500</v>
       </c>
       <c r="F85" s="29">
         <f>IF($I85="","",INDEX('Nossos casos'!$G$5:$G$204,$I85))</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="G85" s="30">
         <f>IF($I85="","",INDEX('Nossos casos'!$H$5:$H$204,$I85))</f>
-        <v/>
+        <v>121.428571428571</v>
       </c>
       <c r="H85" s="25">
         <f>IF($I85="","",INDEX('Nossos casos'!$K$5:$K$204,$I85))</f>
-        <v/>
+        <v>451.609032258062</v>
       </c>
       <c r="I85" s="34">
         <f>IFERROR(IF(LARGE('Nossos casos'!$L$5:$L$204,8)&lt;1,"",MATCH(LARGE('Nossos casos'!$L$5:$L$204,8),'Nossos casos'!$L$5:$L$204,0)),"")</f>
-        <v/>
+        <v>38</v>
       </c>
     </row>
     <row r="86">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B6" s="36">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="7">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="B7" s="37" t="n">
-        <v>66.06999999999999</v>
+        <v>66.0714</v>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
@@ -3755,28 +3755,28 @@
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>Hora mínima (R$)</t>
+          <t>Hora mínima com folga (20 % de horas não previstas) (R$)</t>
         </is>
       </c>
       <c r="B12" s="39">
         <f>IFERROR(B7*(1+B11)/(1-B8-B9),"")</f>
-        <v/>
+        <v>127.880129032258</v>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>Custo-hora × (1 + folga) ÷ (1 − impostos − margem mínima).</t>
+          <t>Custo-hora × (1 + folga) ÷ (1 − impostos − margem mínima). É a hora mínima da planilha 05 (R$ 106,57 → R$ 110) com 20 % de folga para horas não previstas: por isso é maior. A tabela usa esta, mais protegida, porque a faixa é fixada antes de conhecer o caso.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Hora alvo (R$)</t>
+          <t>Hora alvo com folga (R$)</t>
         </is>
       </c>
       <c r="B13" s="39">
         <f>IFERROR(B7*(1+B11)/(1-B8-B10),"")</f>
-        <v/>
+        <v>168.692936170213</v>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4007,7 +4007,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Uma linha por caso: valor contratado e horas estimadas. O valor por hora é comparado com a hora mínima e a hora alvo de Config.</t>
+          <t>Uma linha por caso (copie da planilha 13 · Carteira, aba Casos: a 13 é a fonte; horas estimadas da 16). O valor por hora é comparado com a hora mínima com folga e a hora alvo de Config.</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>Contra a hora mínima</t>
+          <t>Contra a hora mínima com folga</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
@@ -4076,7 +4076,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>9236009-85.2026.8.26.0452</t>
+          <t>CONS-2026-01</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -4091,45 +4091,45 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F5" s="40" t="n">
-        <v>14400</v>
+        <v>18000</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H5" s="30">
         <f>IF(OR(A5="",G5="",G5=0,F5=""),"",F5/G5)</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="I5" s="31">
         <f>IF(H5="","",H5/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J5" s="33">
+        <v>0.954955800341247</v>
+      </c>
+      <c r="J5" s="33" t="str">
         <f>IF(H5="","",IF(H5&lt;Config!$B$12,"Abaixo do mínimo",IF(H5&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K5" s="25">
         <f>IF(H5="","",MAX(0,Config!$B$12*G5-F5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L5" s="41">
         <f>IF(K5="","",K5+ROW()/1000000)</f>
-        <v/>
+        <v>5e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>9225646-96.2026.8.26.0322</t>
+          <t>2998500-50.2026.8.26.0515</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
@@ -4144,45 +4144,45 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F6" s="40" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H6" s="30">
         <f>IF(OR(A6="",G6="",G6=0,F6=""),"",F6/G6)</f>
-        <v/>
+        <v>85.7142857142857</v>
       </c>
       <c r="I6" s="31">
         <f>IF(H6="","",H6/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J6" s="33">
+        <v>-0.329729439883001</v>
+      </c>
+      <c r="J6" s="33" t="str">
         <f>IF(H6="","",IF(H6&lt;Config!$B$12,"Abaixo do mínimo",IF(H6&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K6" s="25">
         <f>IF(H6="","",MAX(0,Config!$B$12*G6-F6))</f>
-        <v/>
+        <v>2951.60903225806</v>
       </c>
       <c r="L6" s="41">
         <f>IF(K6="","",K6+ROW()/1000000)</f>
-        <v/>
+        <v>2951.60903825806</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>6710873-21.2025.8.26.0571</t>
+          <t>9586960-92.2026.8.26.0106</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -4202,40 +4202,40 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F7" s="40" t="n">
-        <v>8100</v>
+        <v>15500</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H7" s="30">
         <f>IF(OR(A7="",G7="",G7=0,F7=""),"",F7/G7)</f>
-        <v/>
+        <v>172.222222222222</v>
       </c>
       <c r="I7" s="31">
         <f>IF(H7="","",H7/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J7" s="33">
+        <v>0.34674732912397</v>
+      </c>
+      <c r="J7" s="33" t="str">
         <f>IF(H7="","",IF(H7&lt;Config!$B$12,"Abaixo do mínimo",IF(H7&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K7" s="25">
         <f>IF(H7="","",MAX(0,Config!$B$12*G7-F7))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L7" s="41">
         <f>IF(K7="","",K7+ROW()/1000000)</f>
-        <v/>
+        <v>7e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>8735513-64.2025.8.26.0093</t>
+          <t>4746093-86.2026.8.26.0637</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
@@ -4250,45 +4250,45 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F8" s="40" t="n">
-        <v>5700</v>
+        <v>5400</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H8" s="30">
         <f>IF(OR(A8="",G8="",G8=0,F8=""),"",F8/G8)</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="I8" s="31">
         <f>IF(H8="","",H8/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J8" s="33">
+        <v>0.0556761321842736</v>
+      </c>
+      <c r="J8" s="33" t="str">
         <f>IF(H8="","",IF(H8&lt;Config!$B$12,"Abaixo do mínimo",IF(H8&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K8" s="25">
         <f>IF(H8="","",MAX(0,Config!$B$12*G8-F8))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L8" s="41">
         <f>IF(K8="","",K8+ROW()/1000000)</f>
-        <v/>
+        <v>8e-06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>9802211-43.2025.8.26.0431</t>
+          <t>CONS-2026-02</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -4303,55 +4303,55 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F9" s="40" t="n">
-        <v>19600</v>
+        <v>8400</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="H9" s="30">
         <f>IF(OR(A9="",G9="",G9=0,F9=""),"",F9/G9)</f>
-        <v/>
+        <v>186.666666666667</v>
       </c>
       <c r="I9" s="31">
         <f>IF(H9="","",H9/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J9" s="33">
+        <v>0.459700330921465</v>
+      </c>
+      <c r="J9" s="33" t="str">
         <f>IF(H9="","",IF(H9&lt;Config!$B$12,"Abaixo do mínimo",IF(H9&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K9" s="25">
         <f>IF(H9="","",MAX(0,Config!$B$12*G9-F9))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L9" s="41">
         <f>IF(K9="","",K9+ROW()/1000000)</f>
-        <v/>
+        <v>9e-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>9778116-95.2026.8.26.0106</t>
+          <t>CONS-2026-03</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -4361,262 +4361,262 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F10" s="40" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H10" s="30">
         <f>IF(OR(A10="",G10="",G10=0,F10=""),"",F10/G10)</f>
-        <v/>
+        <v>187.5</v>
       </c>
       <c r="I10" s="31">
         <f>IF(H10="","",H10/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J10" s="33">
+        <v>0.466216850255936</v>
+      </c>
+      <c r="J10" s="33" t="str">
         <f>IF(H10="","",IF(H10&lt;Config!$B$12,"Abaixo do mínimo",IF(H10&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K10" s="25">
         <f>IF(H10="","",MAX(0,Config!$B$12*G10-F10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L10" s="41">
         <f>IF(K10="","",K10+ROW()/1000000)</f>
-        <v/>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>8875326-79.2026.8.26.0258</t>
+          <t>CONS-2026-04</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F11" s="40" t="n">
-        <v>4600</v>
+        <v>13200</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="H11" s="30">
         <f>IF(OR(A11="",G11="",G11=0,F11=""),"",F11/G11)</f>
-        <v/>
+        <v>183.333333333333</v>
       </c>
       <c r="I11" s="31">
         <f>IF(H11="","",H11/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J11" s="33">
+        <v>0.433634253583582</v>
+      </c>
+      <c r="J11" s="33" t="str">
         <f>IF(H11="","",IF(H11&lt;Config!$B$12,"Abaixo do mínimo",IF(H11&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K11" s="25">
         <f>IF(H11="","",MAX(0,Config!$B$12*G11-F11))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L11" s="41">
         <f>IF(K11="","",K11+ROW()/1000000)</f>
-        <v/>
+        <v>1.1e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>4397912-47.2025.8.26.0276</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F12" s="40" t="n">
-        <v>11300</v>
+        <v>9500</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H12" s="30">
         <f>IF(OR(A12="",G12="",G12=0,F12=""),"",F12/G12)</f>
-        <v/>
+        <v>118.75</v>
       </c>
       <c r="I12" s="31">
         <f>IF(H12="","",H12/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J12" s="33">
+        <v>-0.0713959948379075</v>
+      </c>
+      <c r="J12" s="33" t="str">
         <f>IF(H12="","",IF(H12&lt;Config!$B$12,"Abaixo do mínimo",IF(H12&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K12" s="25">
         <f>IF(H12="","",MAX(0,Config!$B$12*G12-F12))</f>
-        <v/>
+        <v>730.410322580643</v>
       </c>
       <c r="L12" s="41">
         <f>IF(K12="","",K12+ROW()/1000000)</f>
-        <v/>
+        <v>730.410334580643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>4352718-43.2025.8.26.0498</t>
+          <t>9236009-85.2025.8.26.0452</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="F13" s="40" t="n">
-        <v>9300</v>
+        <v>4000</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H13" s="30">
         <f>IF(OR(A13="",G13="",G13=0,F13=""),"",F13/G13)</f>
-        <v/>
+        <v>88.8888888888889</v>
       </c>
       <c r="I13" s="31">
         <f>IF(H13="","",H13/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J13" s="33">
+        <v>-0.304904604323112</v>
+      </c>
+      <c r="J13" s="33" t="str">
         <f>IF(H13="","",IF(H13&lt;Config!$B$12,"Abaixo do mínimo",IF(H13&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K13" s="25">
         <f>IF(H13="","",MAX(0,Config!$B$12*G13-F13))</f>
-        <v/>
+        <v>1754.60580645161</v>
       </c>
       <c r="L13" s="41">
         <f>IF(K13="","",K13+ROW()/1000000)</f>
-        <v/>
+        <v>1754.60581945161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>2650441-66.2026.8.26.0528</t>
+          <t>5025425-10.2025.8.26.0629</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="F14" s="40" t="n">
-        <v>7800</v>
+        <v>15000</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="H14" s="30">
         <f>IF(OR(A14="",G14="",G14=0,F14=""),"",F14/G14)</f>
-        <v/>
+        <v>157.894736842105</v>
       </c>
       <c r="I14" s="31">
         <f>IF(H14="","",H14/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J14" s="33">
+        <v>0.234708926531314</v>
+      </c>
+      <c r="J14" s="33" t="str">
         <f>IF(H14="","",IF(H14&lt;Config!$B$12,"Abaixo do mínimo",IF(H14&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K14" s="25">
         <f>IF(H14="","",MAX(0,Config!$B$12*G14-F14))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L14" s="41">
         <f>IF(K14="","",K14+ROW()/1000000)</f>
-        <v/>
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>5470559-73.2026.8.26.0380</t>
+          <t>2354318-24.2026.8.26.0295</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
@@ -4633,43 +4633,43 @@
         <v>10200</v>
       </c>
       <c r="G15" s="23" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H15" s="30">
         <f>IF(OR(A15="",G15="",G15=0,F15=""),"",F15/G15)</f>
-        <v/>
+        <v>170</v>
       </c>
       <c r="I15" s="31">
         <f>IF(H15="","",H15/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J15" s="33">
+        <v>0.329369944232048</v>
+      </c>
+      <c r="J15" s="33" t="str">
         <f>IF(H15="","",IF(H15&lt;Config!$B$12,"Abaixo do mínimo",IF(H15&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K15" s="25">
         <f>IF(H15="","",MAX(0,Config!$B$12*G15-F15))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L15" s="41">
         <f>IF(K15="","",K15+ROW()/1000000)</f>
-        <v/>
+        <v>1.5e-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>8570388-84.2025.8.26.0560</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -4679,55 +4679,55 @@
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10400</v>
+        <v>21600</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="H16" s="30">
         <f>IF(OR(A16="",G16="",G16=0,F16=""),"",F16/G16)</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="I16" s="31">
         <f>IF(H16="","",H16/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J16" s="33">
+        <v>0.407568176245698</v>
+      </c>
+      <c r="J16" s="33" t="str">
         <f>IF(H16="","",IF(H16&lt;Config!$B$12,"Abaixo do mínimo",IF(H16&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K16" s="25">
         <f>IF(H16="","",MAX(0,Config!$B$12*G16-F16))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L16" s="41">
         <f>IF(K16="","",K16+ROW()/1000000)</f>
-        <v/>
+        <v>1.6e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>6258696-95.2026.8.26.0598</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -4736,94 +4736,94 @@
         </is>
       </c>
       <c r="F17" s="40" t="n">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H17" s="30">
         <f>IF(OR(A17="",G17="",G17=0,F17=""),"",F17/G17)</f>
-        <v/>
+        <v>163.636363636364</v>
       </c>
       <c r="I17" s="31">
         <f>IF(H17="","",H17/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J17" s="33">
+        <v>0.279607432950635</v>
+      </c>
+      <c r="J17" s="33" t="str">
         <f>IF(H17="","",IF(H17&lt;Config!$B$12,"Abaixo do mínimo",IF(H17&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K17" s="25">
         <f>IF(H17="","",MAX(0,Config!$B$12*G17-F17))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L17" s="41">
         <f>IF(K17="","",K17+ROW()/1000000)</f>
-        <v/>
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>9467819-47.2025.8.26.0087</t>
+          <t>9225646-96.2025.8.26.0322</t>
         </is>
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F18" s="40" t="n">
-        <v>6200</v>
+        <v>13500</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H18" s="30">
         <f>IF(OR(A18="",G18="",G18=0,F18=""),"",F18/G18)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="I18" s="31">
         <f>IF(H18="","",H18/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J18" s="33">
+        <v>0.172973480204748</v>
+      </c>
+      <c r="J18" s="33" t="str">
         <f>IF(H18="","",IF(H18&lt;Config!$B$12,"Abaixo do mínimo",IF(H18&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K18" s="25">
         <f>IF(H18="","",MAX(0,Config!$B$12*G18-F18))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L18" s="41">
         <f>IF(K18="","",K18+ROW()/1000000)</f>
-        <v/>
+        <v>1.8e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>4300029-58.2025.8.26.0015</t>
+          <t>4526984-60.2026.8.26.0258</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -4833,166 +4833,166 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F19" s="40" t="n">
-        <v>10300</v>
+        <v>9000</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="H19" s="30">
         <f>IF(OR(A19="",G19="",G19=0,F19=""),"",F19/G19)</f>
-        <v/>
+        <v>112.5</v>
       </c>
       <c r="I19" s="31">
         <f>IF(H19="","",H19/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J19" s="33">
+        <v>-0.120269889846439</v>
+      </c>
+      <c r="J19" s="33" t="str">
         <f>IF(H19="","",IF(H19&lt;Config!$B$12,"Abaixo do mínimo",IF(H19&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K19" s="25">
         <f>IF(H19="","",MAX(0,Config!$B$12*G19-F19))</f>
-        <v/>
+        <v>1230.41032258064</v>
       </c>
       <c r="L19" s="41">
         <f>IF(K19="","",K19+ROW()/1000000)</f>
-        <v/>
+        <v>1230.41034158064</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>8986364-51.2026.8.26.0700</t>
+          <t>CONS-2026-06</t>
         </is>
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F20" s="40" t="n">
-        <v>14900</v>
+        <v>4400</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="H20" s="30">
         <f>IF(OR(A20="",G20="",G20=0,F20=""),"",F20/G20)</f>
-        <v/>
+        <v>157.142857142857</v>
       </c>
       <c r="I20" s="31">
         <f>IF(H20="","",H20/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J20" s="33">
+        <v>0.228829360214498</v>
+      </c>
+      <c r="J20" s="33" t="str">
         <f>IF(H20="","",IF(H20&lt;Config!$B$12,"Abaixo do mínimo",IF(H20&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K20" s="25">
         <f>IF(H20="","",MAX(0,Config!$B$12*G20-F20))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L20" s="41">
         <f>IF(K20="","",K20+ROW()/1000000)</f>
-        <v/>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="22" t="inlineStr">
         <is>
-          <t>9717671-36.2026.8.26.0445</t>
+          <t>6832730-55.2026.8.26.0386</t>
         </is>
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Acordo</t>
         </is>
       </c>
       <c r="F21" s="40" t="n">
-        <v>11800</v>
+        <v>9000</v>
       </c>
       <c r="G21" s="23" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H21" s="30">
         <f>IF(OR(A21="",G21="",G21=0,F21=""),"",F21/G21)</f>
-        <v/>
+        <v>163.636363636364</v>
       </c>
       <c r="I21" s="31">
         <f>IF(H21="","",H21/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J21" s="33">
+        <v>0.279607432950635</v>
+      </c>
+      <c r="J21" s="33" t="str">
         <f>IF(H21="","",IF(H21&lt;Config!$B$12,"Abaixo do mínimo",IF(H21&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K21" s="25">
         <f>IF(H21="","",MAX(0,Config!$B$12*G21-F21))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L21" s="41">
         <f>IF(K21="","",K21+ROW()/1000000)</f>
-        <v/>
+        <v>2.1e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>1808451-67.2026.8.26.0657</t>
+          <t>9616569-91.2026.8.26.0079</t>
         </is>
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -5001,99 +5001,99 @@
         </is>
       </c>
       <c r="F22" s="40" t="n">
-        <v>7900</v>
+        <v>6600</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H22" s="30">
         <f>IF(OR(A22="",G22="",G22=0,F22=""),"",F22/G22)</f>
-        <v/>
+        <v>146.666666666667</v>
       </c>
       <c r="I22" s="31">
         <f>IF(H22="","",H22/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J22" s="33">
+        <v>0.146907402866865</v>
+      </c>
+      <c r="J22" s="33" t="str">
         <f>IF(H22="","",IF(H22&lt;Config!$B$12,"Abaixo do mínimo",IF(H22&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K22" s="25">
         <f>IF(H22="","",MAX(0,Config!$B$12*G22-F22))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L22" s="41">
         <f>IF(K22="","",K22+ROW()/1000000)</f>
-        <v/>
+        <v>2.2e-05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>3310587-30.2026.8.26.0678</t>
+          <t>6710873-21.2025.8.26.0571</t>
         </is>
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="F23" s="40" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="H23" s="30">
         <f>IF(OR(A23="",G23="",G23=0,F23=""),"",F23/G23)</f>
-        <v/>
+        <v>111.111111111111</v>
       </c>
       <c r="I23" s="31">
         <f>IF(H23="","",H23/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J23" s="33">
+        <v>-0.13113075540389</v>
+      </c>
+      <c r="J23" s="33" t="str">
         <f>IF(H23="","",IF(H23&lt;Config!$B$12,"Abaixo do mínimo",IF(H23&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K23" s="25">
         <f>IF(H23="","",MAX(0,Config!$B$12*G23-F23))</f>
-        <v/>
+        <v>1509.21161290322</v>
       </c>
       <c r="L23" s="41">
         <f>IF(K23="","",K23+ROW()/1000000)</f>
-        <v/>
+        <v>1509.21163590322</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>3930894-43.2025.8.26.0476</t>
+          <t>5900991-46.2026.8.26.0469</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Ana Beatriz Moreira</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -5103,98 +5103,98 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F24" s="40" t="n">
-        <v>6600</v>
+        <v>4000</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H24" s="30">
         <f>IF(OR(A24="",G24="",G24=0,F24=""),"",F24/G24)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="I24" s="31">
         <f>IF(H24="","",H24/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J24" s="33">
+        <v>-0.218017679863501</v>
+      </c>
+      <c r="J24" s="33" t="str">
         <f>IF(H24="","",IF(H24&lt;Config!$B$12,"Abaixo do mínimo",IF(H24&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K24" s="25">
         <f>IF(H24="","",MAX(0,Config!$B$12*G24-F24))</f>
-        <v/>
+        <v>1115.20516129032</v>
       </c>
       <c r="L24" s="41">
         <f>IF(K24="","",K24+ROW()/1000000)</f>
-        <v/>
+        <v>1115.20518529032</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>9802987-45.2025.8.26.0097</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Instrução</t>
         </is>
       </c>
       <c r="F25" s="40" t="n">
-        <v>13900</v>
+        <v>15000</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H25" s="30">
         <f>IF(OR(A25="",G25="",G25=0,F25=""),"",F25/G25)</f>
-        <v/>
+        <v>157.894736842105</v>
       </c>
       <c r="I25" s="31">
         <f>IF(H25="","",H25/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J25" s="33">
+        <v>0.234708926531314</v>
+      </c>
+      <c r="J25" s="33" t="str">
         <f>IF(H25="","",IF(H25&lt;Config!$B$12,"Abaixo do mínimo",IF(H25&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K25" s="25">
         <f>IF(H25="","",MAX(0,Config!$B$12*G25-F25))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L25" s="41">
         <f>IF(K25="","",K25+ROW()/1000000)</f>
-        <v/>
+        <v>2.5e-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>6904743-30.2025.8.26.0361</t>
+          <t>6184138-13.2026.8.26.0378</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -5204,55 +5204,55 @@
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F26" s="40" t="n">
-        <v>10400</v>
+        <v>9000</v>
       </c>
       <c r="G26" s="23" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H26" s="30">
         <f>IF(OR(A26="",G26="",G26=0,F26=""),"",F26/G26)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="I26" s="31">
         <f>IF(H26="","",H26/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J26" s="33">
+        <v>0.172973480204748</v>
+      </c>
+      <c r="J26" s="33" t="str">
         <f>IF(H26="","",IF(H26&lt;Config!$B$12,"Abaixo do mínimo",IF(H26&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K26" s="25">
         <f>IF(H26="","",MAX(0,Config!$B$12*G26-F26))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L26" s="41">
         <f>IF(K26="","",K26+ROW()/1000000)</f>
-        <v/>
+        <v>2.6e-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>5497983-95.2025.8.26.0570</t>
+          <t>7099226-69.2026.8.26.0433</t>
         </is>
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -5262,151 +5262,151 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>Sentença</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F27" s="40" t="n">
-        <v>9400</v>
+        <v>12000</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H27" s="30">
         <f>IF(OR(A27="",G27="",G27=0,F27=""),"",F27/G27)</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="I27" s="31">
         <f>IF(H27="","",H27/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J27" s="33">
+        <v>0.251171712218398</v>
+      </c>
+      <c r="J27" s="33" t="str">
         <f>IF(H27="","",IF(H27&lt;Config!$B$12,"Abaixo do mínimo",IF(H27&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K27" s="25">
         <f>IF(H27="","",MAX(0,Config!$B$12*G27-F27))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L27" s="41">
         <f>IF(K27="","",K27+ROW()/1000000)</f>
-        <v/>
+        <v>2.7e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>4112092-92.2025.8.26.0646</t>
+          <t>2521428-61.2026.8.26.0600</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Acordo</t>
         </is>
       </c>
       <c r="F28" s="40" t="n">
-        <v>4200</v>
+        <v>7600</v>
       </c>
       <c r="G28" s="23" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H28" s="30">
         <f>IF(OR(A28="",G28="",G28=0,F28=""),"",F28/G28)</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="I28" s="31">
         <f>IF(H28="","",H28/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J28" s="33">
+        <v>0.485766408259348</v>
+      </c>
+      <c r="J28" s="33" t="str">
         <f>IF(H28="","",IF(H28&lt;Config!$B$12,"Abaixo do mínimo",IF(H28&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K28" s="25">
         <f>IF(H28="","",MAX(0,Config!$B$12*G28-F28))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L28" s="41">
         <f>IF(K28="","",K28+ROW()/1000000)</f>
-        <v/>
+        <v>2.8e-05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>5297049-18.2026.8.26.0015</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Hora</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Execução</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="F29" s="40" t="n">
-        <v>11700</v>
+        <v>24000</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="H29" s="30">
         <f>IF(OR(A29="",G29="",G29=0,F29=""),"",F29/G29)</f>
-        <v/>
+        <v>180.451127819549</v>
       </c>
       <c r="I29" s="31">
         <f>IF(H29="","",H29/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J29" s="33">
+        <v>0.411095916035788</v>
+      </c>
+      <c r="J29" s="33" t="str">
         <f>IF(H29="","",IF(H29&lt;Config!$B$12,"Abaixo do mínimo",IF(H29&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K29" s="25">
         <f>IF(H29="","",MAX(0,Config!$B$12*G29-F29))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L29" s="41">
         <f>IF(K29="","",K29+ROW()/1000000)</f>
-        <v/>
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>6877173-50.2026.8.26.0467</t>
+          <t>CONS-2026-07</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -5416,156 +5416,156 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Consultivo</t>
         </is>
       </c>
       <c r="F30" s="40" t="n">
-        <v>21100</v>
+        <v>7000</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="H30" s="30">
         <f>IF(OR(A30="",G30="",G30=0,F30=""),"",F30/G30)</f>
-        <v/>
+        <v>233.333333333333</v>
       </c>
       <c r="I30" s="31">
         <f>IF(H30="","",H30/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J30" s="33">
+        <v>0.824625413651831</v>
+      </c>
+      <c r="J30" s="33" t="str">
         <f>IF(H30="","",IF(H30&lt;Config!$B$12,"Abaixo do mínimo",IF(H30&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K30" s="25">
         <f>IF(H30="","",MAX(0,Config!$B$12*G30-F30))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L30" s="41">
         <f>IF(K30="","",K30+ROW()/1000000)</f>
-        <v/>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>3003874-97.2026.8.26.0384</t>
+          <t>9495290-86.2025.8.26.0503</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Execução</t>
         </is>
       </c>
       <c r="F31" s="40" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H31" s="30">
         <f>IF(OR(A31="",G31="",G31=0,F31=""),"",F31/G31)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="I31" s="31">
         <f>IF(H31="","",H31/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J31" s="33">
+        <v>-0.218017679863501</v>
+      </c>
+      <c r="J31" s="33" t="str">
         <f>IF(H31="","",IF(H31&lt;Config!$B$12,"Abaixo do mínimo",IF(H31&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K31" s="25">
         <f>IF(H31="","",MAX(0,Config!$B$12*G31-F31))</f>
-        <v/>
+        <v>1951.60903225806</v>
       </c>
       <c r="L31" s="41">
         <f>IF(K31="","",K31+ROW()/1000000)</f>
-        <v/>
+        <v>1951.60906325806</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>6545676-47.2025.8.26.0126</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>Recurso</t>
+          <t>Inicial</t>
         </is>
       </c>
       <c r="F32" s="40" t="n">
-        <v>6600</v>
+        <v>7500</v>
       </c>
       <c r="G32" s="23" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H32" s="30">
         <f>IF(OR(A32="",G32="",G32=0,F32=""),"",F32/G32)</f>
-        <v/>
+        <v>136.363636363636</v>
       </c>
       <c r="I32" s="31">
         <f>IF(H32="","",H32/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J32" s="33">
+        <v>0.0663395274588623</v>
+      </c>
+      <c r="J32" s="33" t="str">
         <f>IF(H32="","",IF(H32&lt;Config!$B$12,"Abaixo do mínimo",IF(H32&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K32" s="25">
         <f>IF(H32="","",MAX(0,Config!$B$12*G32-F32))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L32" s="41">
         <f>IF(K32="","",K32+ROW()/1000000)</f>
-        <v/>
+        <v>3.2e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>1941959-24.2026.8.26.0167</t>
+          <t>8045862-82.2026.8.26.0491</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Carlos Eduardo Nunes</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -5575,55 +5575,55 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Sentença</t>
         </is>
       </c>
       <c r="F33" s="40" t="n">
-        <v>6500</v>
+        <v>7600</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H33" s="30">
         <f>IF(OR(A33="",G33="",G33=0,F33=""),"",F33/G33)</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="I33" s="31">
         <f>IF(H33="","",H33/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J33" s="33">
+        <v>0.485766408259348</v>
+      </c>
+      <c r="J33" s="33" t="str">
         <f>IF(H33="","",IF(H33&lt;Config!$B$12,"Abaixo do mínimo",IF(H33&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K33" s="25">
         <f>IF(H33="","",MAX(0,Config!$B$12*G33-F33))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L33" s="41">
         <f>IF(K33="","",K33+ROW()/1000000)</f>
-        <v/>
+        <v>3.3e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>3118925-55.2025.8.26.0426</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
@@ -5633,45 +5633,45 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>Inicial</t>
+          <t>Recurso</t>
         </is>
       </c>
       <c r="F34" s="40" t="n">
-        <v>4500</v>
+        <v>5400</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H34" s="30">
         <f>IF(OR(A34="",G34="",G34=0,F34=""),"",F34/G34)</f>
-        <v/>
+        <v>154.285714285714</v>
       </c>
       <c r="I34" s="31">
         <f>IF(H34="","",H34/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J34" s="33">
+        <v>0.206487008210598</v>
+      </c>
+      <c r="J34" s="33" t="str">
         <f>IF(H34="","",IF(H34&lt;Config!$B$12,"Abaixo do mínimo",IF(H34&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K34" s="25">
         <f>IF(H34="","",MAX(0,Config!$B$12*G34-F34))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L34" s="41">
         <f>IF(K34="","",K34+ROW()/1000000)</f>
-        <v/>
+        <v>3.4e-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>7658179-42.2026.8.26.0152</t>
+          <t>4766902-26.2025.8.26.0051</t>
         </is>
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Padaria do Sol Ltda</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -5681,156 +5681,156 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>Acordo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F35" s="40" t="n">
-        <v>18300</v>
+        <v>12000</v>
       </c>
       <c r="G35" s="23" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H35" s="30">
         <f>IF(OR(A35="",G35="",G35=0,F35=""),"",F35/G35)</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="I35" s="31">
         <f>IF(H35="","",H35/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J35" s="33">
+        <v>0.563964640272998</v>
+      </c>
+      <c r="J35" s="33" t="str">
         <f>IF(H35="","",IF(H35&lt;Config!$B$12,"Abaixo do mínimo",IF(H35&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Acima do alvo</v>
       </c>
       <c r="K35" s="25">
         <f>IF(H35="","",MAX(0,Config!$B$12*G35-F35))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L35" s="41">
         <f>IF(K35="","",K35+ROW()/1000000)</f>
-        <v/>
+        <v>3.5e-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>3326285-90.2025.8.26.0608</t>
+          <t>9778116-95.2025.8.26.0106</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
+          <t>Construtora Horizonte</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F36" s="40" t="n">
-        <v>5500</v>
+        <v>18000</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="H36" s="30">
         <f>IF(OR(A36="",G36="",G36=0,F36=""),"",F36/G36)</f>
-        <v/>
+        <v>163.636363636364</v>
       </c>
       <c r="I36" s="31">
         <f>IF(H36="","",H36/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J36" s="33">
+        <v>0.279607432950635</v>
+      </c>
+      <c r="J36" s="33" t="str">
         <f>IF(H36="","",IF(H36&lt;Config!$B$12,"Abaixo do mínimo",IF(H36&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K36" s="25">
         <f>IF(H36="","",MAX(0,Config!$B$12*G36-F36))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L36" s="41">
         <f>IF(K36="","",K36+ROW()/1000000)</f>
-        <v/>
+        <v>3.6e-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>1191416-90.2025.8.26.0249</t>
+          <t>8204296-70.2025.8.26.0146</t>
         </is>
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>Instrução</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F37" s="40" t="n">
-        <v>12400</v>
+        <v>6500</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H37" s="30">
         <f>IF(OR(A37="",G37="",G37=0,F37=""),"",F37/G37)</f>
-        <v/>
+        <v>144.444444444444</v>
       </c>
       <c r="I37" s="31">
         <f>IF(H37="","",H37/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J37" s="33">
+        <v>0.129530017974943</v>
+      </c>
+      <c r="J37" s="33" t="str">
         <f>IF(H37="","",IF(H37&lt;Config!$B$12,"Abaixo do mínimo",IF(H37&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K37" s="25">
         <f>IF(H37="","",MAX(0,Config!$B$12*G37-F37))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L37" s="41">
         <f>IF(K37="","",K37+ROW()/1000000)</f>
-        <v/>
+        <v>3.7e-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>5626517-53.2026.8.26.0206</t>
+          <t>9088515-39.2025.8.26.0125</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Loja Verde Comércio</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -5840,60 +5840,60 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>Consultivo</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="F38" s="40" t="n">
-        <v>16900</v>
+        <v>6000</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="H38" s="30">
         <f>IF(OR(A38="",G38="",G38=0,F38=""),"",F38/G38)</f>
-        <v/>
+        <v>133.333333333333</v>
       </c>
       <c r="I38" s="31">
         <f>IF(H38="","",H38/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J38" s="33">
+        <v>0.0426430935153319</v>
+      </c>
+      <c r="J38" s="33" t="str">
         <f>IF(H38="","",IF(H38&lt;Config!$B$12,"Abaixo do mínimo",IF(H38&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K38" s="25">
         <f>IF(H38="","",MAX(0,Config!$B$12*G38-F38))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L38" s="41">
         <f>IF(K38="","",K38+ROW()/1000000)</f>
-        <v/>
+        <v>3.8e-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>6237740-34.2025.8.26.0163</t>
+          <t>8663770-96.2025.8.26.0481</t>
         </is>
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -5902,51 +5902,51 @@
         </is>
       </c>
       <c r="F39" s="40" t="n">
-        <v>5700</v>
+        <v>12000</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="H39" s="30">
         <f>IF(OR(A39="",G39="",G39=0,F39=""),"",F39/G39)</f>
-        <v/>
+        <v>126.315789473684</v>
       </c>
       <c r="I39" s="31">
         <f>IF(H39="","",H39/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J39" s="33">
+        <v>-0.0122328587749487</v>
+      </c>
+      <c r="J39" s="33" t="str">
         <f>IF(H39="","",IF(H39&lt;Config!$B$12,"Abaixo do mínimo",IF(H39&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K39" s="25">
         <f>IF(H39="","",MAX(0,Config!$B$12*G39-F39))</f>
-        <v/>
+        <v>148.612258064513</v>
       </c>
       <c r="L39" s="41">
         <f>IF(K39="","",K39+ROW()/1000000)</f>
-        <v/>
+        <v>148.612297064513</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>9778303-99.2026.8.26.0419</t>
+          <t>5211189-81.2025.8.26.0412</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Fernanda Castro</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -5955,51 +5955,51 @@
         </is>
       </c>
       <c r="F40" s="40" t="n">
-        <v>14100</v>
+        <v>7000</v>
       </c>
       <c r="G40" s="23" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H40" s="30">
         <f>IF(OR(A40="",G40="",G40=0,F40=""),"",F40/G40)</f>
-        <v/>
+        <v>127.272727272727</v>
       </c>
       <c r="I40" s="31">
         <f>IF(H40="","",H40/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J40" s="33">
+        <v>-0.00474977437172863</v>
+      </c>
+      <c r="J40" s="33" t="str">
         <f>IF(H40="","",IF(H40&lt;Config!$B$12,"Abaixo do mínimo",IF(H40&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K40" s="25">
         <f>IF(H40="","",MAX(0,Config!$B$12*G40-F40))</f>
-        <v/>
+        <v>33.4070967741918</v>
       </c>
       <c r="L40" s="41">
         <f>IF(K40="","",K40+ROW()/1000000)</f>
-        <v/>
+        <v>33.4071367741918</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>3314594-22.2025.8.26.0019</t>
+          <t>6161129-80.2025.8.26.0663</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -6008,36 +6008,36 @@
         </is>
       </c>
       <c r="F41" s="40" t="n">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="G41" s="23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H41" s="30">
         <f>IF(OR(A41="",G41="",G41=0,F41=""),"",F41/G41)</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="I41" s="31">
         <f>IF(H41="","",H41/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J41" s="33">
+        <v>0.172973480204748</v>
+      </c>
+      <c r="J41" s="33" t="str">
         <f>IF(H41="","",IF(H41&lt;Config!$B$12,"Abaixo do mínimo",IF(H41&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Na faixa</v>
       </c>
       <c r="K41" s="25">
         <f>IF(H41="","",MAX(0,Config!$B$12*G41-F41))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L41" s="41">
         <f>IF(K41="","",K41+ROW()/1000000)</f>
-        <v/>
+        <v>4.1e-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>7598076-58.2025.8.26.0552</t>
+          <t>9420478-99.2025.8.26.0491</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -6061,30 +6061,30 @@
         </is>
       </c>
       <c r="F42" s="40" t="n">
-        <v>11300</v>
+        <v>8500</v>
       </c>
       <c r="G42" s="23" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H42" s="30">
         <f>IF(OR(A42="",G42="",G42=0,F42=""),"",F42/G42)</f>
-        <v/>
+        <v>121.428571428571</v>
       </c>
       <c r="I42" s="31">
         <f>IF(H42="","",H42/Config!$B$12-1)</f>
-        <v/>
-      </c>
-      <c r="J42" s="33">
+        <v>-0.0504500398342512</v>
+      </c>
+      <c r="J42" s="33" t="str">
         <f>IF(H42="","",IF(H42&lt;Config!$B$12,"Abaixo do mínimo",IF(H42&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
-        <v/>
+        <v>Abaixo do mínimo</v>
       </c>
       <c r="K42" s="25">
         <f>IF(H42="","",MAX(0,Config!$B$12*G42-F42))</f>
-        <v/>
+        <v>451.609032258062</v>
       </c>
       <c r="L42" s="41">
         <f>IF(K42="","",K42+ROW()/1000000)</f>
-        <v/>
+        <v>451.609074258062</v>
       </c>
     </row>
     <row r="43">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -21,11 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="167" formatCode="+0%;-0%;0%"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="+0%;-0%;0%"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -225,19 +226,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -255,7 +256,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,10 +265,10 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -278,10 +279,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -289,10 +290,10 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -814,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -975,17 +976,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -3672,9 +3685,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="36">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B6" s="36" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="7">
@@ -10811,7 +10823,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$E$16,0,0,MAX(1,COUNTA(Config!$E$16:$E$35)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -1089,12 +1089,12 @@
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17" t="str">
-        <f>COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo"))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo")))</f>
         <v>10 de 38</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>SUM('Nossos casos'!$K$5:$K$204)</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,SUM('Nossos casos'!$K$5:$K$204))</f>
         <v>11876.6896774193</v>
       </c>
       <c r="H5" s="12" t="n"/>
@@ -1181,15 +1181,15 @@
         </is>
       </c>
       <c r="F9" s="25">
-        <f>IF(OR(A9="",C9=""),"",C9*Config!$B$12)</f>
+        <f>IF(OR(A9="",C9=""),"",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G9" s="25">
-        <f>IF(OR(A9="",D9=""),"",D9*Config!$B$13)</f>
+        <f>IF(OR(A9="",D9=""),"",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H9" s="25">
-        <f>IF(OR(F9="",G9=""),"",(F9+G9)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"",(F9+G9)/2)</f>
         <v>866.591938229238</v>
       </c>
       <c r="I9" s="26" t="str">
@@ -1220,15 +1220,15 @@
         </is>
       </c>
       <c r="F10" s="25">
-        <f>IF(OR(A10="",C10=""),"",C10*Config!$B$12)</f>
+        <f>IF(OR(A10="",C10=""),"",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G10" s="25">
-        <f>IF(OR(A10="",D10=""),"",D10*Config!$B$13)</f>
+        <f>IF(OR(A10="",D10=""),"",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H10" s="25">
-        <f>IF(OR(F10="",G10=""),"",(F10+G10)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"",(F10+G10)/2)</f>
         <v>1648.83740837337</v>
       </c>
       <c r="I10" s="26" t="str">
@@ -1259,15 +1259,15 @@
         </is>
       </c>
       <c r="F11" s="25">
-        <f>IF(OR(A11="",C11=""),"",C11*Config!$B$12)</f>
+        <f>IF(OR(A11="",C11=""),"",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12))</f>
         <v>6394.0064516129</v>
       </c>
       <c r="G11" s="25">
-        <f>IF(OR(A11="",D11=""),"",D11*Config!$B$13)</f>
+        <f>IF(OR(A11="",D11=""),"",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13))</f>
         <v>16869.2936170213</v>
       </c>
       <c r="H11" s="25">
-        <f>IF(OR(F11="",G11=""),"",(F11+G11)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"",(F11+G11)/2)</f>
         <v>11631.6500343171</v>
       </c>
       <c r="I11" s="26" t="str">
@@ -1298,15 +1298,15 @@
         </is>
       </c>
       <c r="F12" s="25">
-        <f>IF(OR(A12="",C12=""),"",C12*Config!$B$12)</f>
+        <f>IF(OR(A12="",C12=""),"",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G12" s="25">
-        <f>IF(OR(A12="",D12=""),"",D12*Config!$B$13)</f>
+        <f>IF(OR(A12="",D12=""),"",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H12" s="25">
-        <f>IF(OR(F12="",G12=""),"",(F12+G12)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"",(F12+G12)/2)</f>
         <v>3911.22735072066</v>
       </c>
       <c r="I12" s="26" t="str">
@@ -1337,15 +1337,15 @@
         </is>
       </c>
       <c r="F13" s="25">
-        <f>IF(OR(A13="",C13=""),"",C13*Config!$B$12)</f>
+        <f>IF(OR(A13="",C13=""),"",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G13" s="25">
-        <f>IF(OR(A13="",D13=""),"",D13*Config!$B$13)</f>
+        <f>IF(OR(A13="",D13=""),"",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H13" s="25">
-        <f>IF(OR(F13="",G13=""),"",(F13+G13)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"",(F13+G13)/2)</f>
         <v>2620.18221825669</v>
       </c>
       <c r="I13" s="26" t="str">
@@ -1376,15 +1376,15 @@
         </is>
       </c>
       <c r="F14" s="25">
-        <f>IF(OR(A14="",C14=""),"",C14*Config!$B$12)</f>
+        <f>IF(OR(A14="",C14=""),"",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G14" s="25">
-        <f>IF(OR(A14="",D14=""),"",D14*Config!$B$13)</f>
+        <f>IF(OR(A14="",D14=""),"",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H14" s="25">
-        <f>IF(OR(F14="",G14=""),"",(F14+G14)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"",(F14+G14)/2)</f>
         <v>866.591938229238</v>
       </c>
       <c r="I14" s="26" t="str">
@@ -1415,15 +1415,15 @@
         </is>
       </c>
       <c r="F15" s="25">
-        <f>IF(OR(A15="",C15=""),"",C15*Config!$B$12)</f>
+        <f>IF(OR(A15="",C15=""),"",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G15" s="25">
-        <f>IF(OR(A15="",D15=""),"",D15*Config!$B$13)</f>
+        <f>IF(OR(A15="",D15=""),"",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H15" s="25">
-        <f>IF(OR(F15="",G15=""),"",(F15+G15)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"",(F15+G15)/2)</f>
         <v>1648.83740837337</v>
       </c>
       <c r="I15" s="26" t="str">
@@ -1454,15 +1454,15 @@
         </is>
       </c>
       <c r="F16" s="25">
-        <f>IF(OR(A16="",C16=""),"",C16*Config!$B$12)</f>
+        <f>IF(OR(A16="",C16=""),"",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12))</f>
         <v>4475.80451612903</v>
       </c>
       <c r="G16" s="25">
-        <f>IF(OR(A16="",D16=""),"",D16*Config!$B$13)</f>
+        <f>IF(OR(A16="",D16=""),"",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H16" s="25">
-        <f>IF(OR(F16="",G16=""),"",(F16+G16)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"",(F16+G16)/2)</f>
         <v>8142.15502402196</v>
       </c>
       <c r="I16" s="26" t="str">
@@ -1493,15 +1493,15 @@
         </is>
       </c>
       <c r="F17" s="25">
-        <f>IF(OR(A17="",C17=""),"",C17*Config!$B$12)</f>
+        <f>IF(OR(A17="",C17=""),"",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G17" s="25">
-        <f>IF(OR(A17="",D17=""),"",D17*Config!$B$13)</f>
+        <f>IF(OR(A17="",D17=""),"",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H17" s="25">
-        <f>IF(OR(F17="",G17=""),"",(F17+G17)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"",(F17+G17)/2)</f>
         <v>3911.22735072066</v>
       </c>
       <c r="I17" s="26" t="str">
@@ -1532,15 +1532,15 @@
         </is>
       </c>
       <c r="F18" s="25">
-        <f>IF(OR(A18="",C18=""),"",C18*Config!$B$12)</f>
+        <f>IF(OR(A18="",C18=""),"",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G18" s="25">
-        <f>IF(OR(A18="",D18=""),"",D18*Config!$B$13)</f>
+        <f>IF(OR(A18="",D18=""),"",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H18" s="25">
-        <f>IF(OR(F18="",G18=""),"",(F18+G18)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"",(F18+G18)/2)</f>
         <v>2620.18221825669</v>
       </c>
       <c r="I18" s="26" t="str">
@@ -1571,15 +1571,15 @@
         </is>
       </c>
       <c r="F19" s="25">
-        <f>IF(OR(A19="",C19=""),"",C19*Config!$B$12)</f>
+        <f>IF(OR(A19="",C19=""),"",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G19" s="25">
-        <f>IF(OR(A19="",D19=""),"",D19*Config!$B$13)</f>
+        <f>IF(OR(A19="",D19=""),"",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H19" s="25">
-        <f>IF(OR(F19="",G19=""),"",(F19+G19)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"",(F19+G19)/2)</f>
         <v>866.591938229238</v>
       </c>
       <c r="I19" s="26" t="str">
@@ -1610,15 +1610,15 @@
         </is>
       </c>
       <c r="F20" s="25">
-        <f>IF(OR(A20="",C20=""),"",C20*Config!$B$12)</f>
+        <f>IF(OR(A20="",C20=""),"",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G20" s="25">
-        <f>IF(OR(A20="",D20=""),"",D20*Config!$B$13)</f>
+        <f>IF(OR(A20="",D20=""),"",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H20" s="25">
-        <f>IF(OR(F20="",G20=""),"",(F20+G20)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20))),"",(F20+G20)/2)</f>
         <v>1648.83740837337</v>
       </c>
       <c r="I20" s="26" t="str">
@@ -1649,15 +1649,15 @@
         </is>
       </c>
       <c r="F21" s="25">
-        <f>IF(OR(A21="",C21=""),"",C21*Config!$B$12)</f>
+        <f>IF(OR(A21="",C21=""),"",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G21" s="25">
-        <f>IF(OR(A21="",D21=""),"",D21*Config!$B$13)</f>
+        <f>IF(OR(A21="",D21=""),"",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13))</f>
         <v>10121.5761702128</v>
       </c>
       <c r="H21" s="25">
-        <f>IF(OR(F21="",G21=""),"",(F21+G21)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21))),"",(F21+G21)/2)</f>
         <v>6978.99002059025</v>
       </c>
       <c r="I21" s="26" t="str">
@@ -1688,15 +1688,15 @@
         </is>
       </c>
       <c r="F22" s="25">
-        <f>IF(OR(A22="",C22=""),"",C22*Config!$B$12)</f>
+        <f>IF(OR(A22="",C22=""),"",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G22" s="25">
-        <f>IF(OR(A22="",D22=""),"",D22*Config!$B$13)</f>
+        <f>IF(OR(A22="",D22=""),"",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H22" s="25">
-        <f>IF(OR(F22="",G22=""),"",(F22+G22)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22))),"",(F22+G22)/2)</f>
         <v>3911.22735072066</v>
       </c>
       <c r="I22" s="26" t="str">
@@ -1727,15 +1727,15 @@
         </is>
       </c>
       <c r="F23" s="25">
-        <f>IF(OR(A23="",C23=""),"",C23*Config!$B$12)</f>
+        <f>IF(OR(A23="",C23=""),"",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G23" s="25">
-        <f>IF(OR(A23="",D23=""),"",D23*Config!$B$13)</f>
+        <f>IF(OR(A23="",D23=""),"",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H23" s="25">
-        <f>IF(OR(F23="",G23=""),"",(F23+G23)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23))),"",(F23+G23)/2)</f>
         <v>2620.18221825669</v>
       </c>
       <c r="I23" s="26" t="str">
@@ -1766,15 +1766,15 @@
         </is>
       </c>
       <c r="F24" s="25">
-        <f>IF(OR(A24="",C24=""),"",C24*Config!$B$12)</f>
+        <f>IF(OR(A24="",C24=""),"",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12))</f>
         <v>511.520516129032</v>
       </c>
       <c r="G24" s="25">
-        <f>IF(OR(A24="",D24=""),"",D24*Config!$B$13)</f>
+        <f>IF(OR(A24="",D24=""),"",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13))</f>
         <v>2024.31523404255</v>
       </c>
       <c r="H24" s="25">
-        <f>IF(OR(F24="",G24=""),"",(F24+G24)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24))),"",(F24+G24)/2)</f>
         <v>1267.91787508579</v>
       </c>
       <c r="I24" s="26" t="str">
@@ -1805,15 +1805,15 @@
         </is>
       </c>
       <c r="F25" s="25">
-        <f>IF(OR(A25="",C25=""),"",C25*Config!$B$12)</f>
+        <f>IF(OR(A25="",C25=""),"",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G25" s="25">
-        <f>IF(OR(A25="",D25=""),"",D25*Config!$B$13)</f>
+        <f>IF(OR(A25="",D25=""),"",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H25" s="25">
-        <f>IF(OR(F25="",G25=""),"",(F25+G25)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F25)),NOT(ISNUMBER(G25))),"",(F25+G25)/2)</f>
         <v>1648.83740837337</v>
       </c>
       <c r="I25" s="26" t="str">
@@ -1844,15 +1844,15 @@
         </is>
       </c>
       <c r="F26" s="25">
-        <f>IF(OR(A26="",C26=""),"",C26*Config!$B$12)</f>
+        <f>IF(OR(A26="",C26=""),"",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12))</f>
         <v>7672.80774193548</v>
       </c>
       <c r="G26" s="25">
-        <f>IF(OR(A26="",D26=""),"",D26*Config!$B$13)</f>
+        <f>IF(OR(A26="",D26=""),"",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13))</f>
         <v>20243.1523404255</v>
       </c>
       <c r="H26" s="25">
-        <f>IF(OR(F26="",G26=""),"",(F26+G26)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F26)),NOT(ISNUMBER(G26))),"",(F26+G26)/2)</f>
         <v>13957.9800411805</v>
       </c>
       <c r="I26" s="26" t="str">
@@ -1883,15 +1883,15 @@
         </is>
       </c>
       <c r="F27" s="25">
-        <f>IF(OR(A27="",C27=""),"",C27*Config!$B$12)</f>
+        <f>IF(OR(A27="",C27=""),"",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G27" s="25">
-        <f>IF(OR(A27="",D27=""),"",D27*Config!$B$13)</f>
+        <f>IF(OR(A27="",D27=""),"",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H27" s="25">
-        <f>IF(OR(F27="",G27=""),"",(F27+G27)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F27)),NOT(ISNUMBER(G27))),"",(F27+G27)/2)</f>
         <v>3911.22735072066</v>
       </c>
       <c r="I27" s="26" t="str">
@@ -1922,15 +1922,15 @@
         </is>
       </c>
       <c r="F28" s="25">
-        <f>IF(OR(A28="",C28=""),"",C28*Config!$B$12)</f>
+        <f>IF(OR(A28="",C28=""),"",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G28" s="25">
-        <f>IF(OR(A28="",D28=""),"",D28*Config!$B$13)</f>
+        <f>IF(OR(A28="",D28=""),"",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H28" s="25">
-        <f>IF(OR(F28="",G28=""),"",(F28+G28)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F28)),NOT(ISNUMBER(G28))),"",(F28+G28)/2)</f>
         <v>2620.18221825669</v>
       </c>
       <c r="I28" s="26" t="str">
@@ -1961,15 +1961,15 @@
         </is>
       </c>
       <c r="F29" s="25">
-        <f>IF(OR(A29="",C29=""),"",C29*Config!$B$12)</f>
+        <f>IF(OR(A29="",C29=""),"",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G29" s="25">
-        <f>IF(OR(A29="",D29=""),"",D29*Config!$B$13)</f>
+        <f>IF(OR(A29="",D29=""),"",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H29" s="25">
-        <f>IF(OR(F29="",G29=""),"",(F29+G29)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F29)),NOT(ISNUMBER(G29))),"",(F29+G29)/2)</f>
         <v>866.591938229238</v>
       </c>
       <c r="I29" s="26" t="str">
@@ -2000,15 +2000,15 @@
         </is>
       </c>
       <c r="F30" s="25">
-        <f>IF(OR(A30="",C30=""),"",C30*Config!$B$12)</f>
+        <f>IF(OR(A30="",C30=""),"",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G30" s="25">
-        <f>IF(OR(A30="",D30=""),"",D30*Config!$B$13)</f>
+        <f>IF(OR(A30="",D30=""),"",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H30" s="25">
-        <f>IF(OR(F30="",G30=""),"",(F30+G30)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F30)),NOT(ISNUMBER(G30))),"",(F30+G30)/2)</f>
         <v>1648.83740837337</v>
       </c>
       <c r="I30" s="26" t="str">
@@ -2039,15 +2039,15 @@
         </is>
       </c>
       <c r="F31" s="25">
-        <f>IF(OR(A31="",C31=""),"",C31*Config!$B$12)</f>
+        <f>IF(OR(A31="",C31=""),"",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G31" s="25">
-        <f>IF(OR(A31="",D31=""),"",D31*Config!$B$13)</f>
+        <f>IF(OR(A31="",D31=""),"",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H31" s="25">
-        <f>IF(OR(F31="",G31=""),"",(F31+G31)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F31)),NOT(ISNUMBER(G31))),"",(F31+G31)/2)</f>
         <v>7822.45470144132</v>
       </c>
       <c r="I31" s="26" t="str">
@@ -2078,15 +2078,15 @@
         </is>
       </c>
       <c r="F32" s="25">
-        <f>IF(OR(A32="",C32=""),"",C32*Config!$B$12)</f>
+        <f>IF(OR(A32="",C32=""),"",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G32" s="25">
-        <f>IF(OR(A32="",D32=""),"",D32*Config!$B$13)</f>
+        <f>IF(OR(A32="",D32=""),"",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H32" s="25">
-        <f>IF(OR(F32="",G32=""),"",(F32+G32)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F32)),NOT(ISNUMBER(G32))),"",(F32+G32)/2)</f>
         <v>3911.22735072066</v>
       </c>
       <c r="I32" s="26" t="str">
@@ -2117,15 +2117,15 @@
         </is>
       </c>
       <c r="F33" s="25">
-        <f>IF(OR(A33="",C33=""),"",C33*Config!$B$12)</f>
+        <f>IF(OR(A33="",C33=""),"",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G33" s="25">
-        <f>IF(OR(A33="",D33=""),"",D33*Config!$B$13)</f>
+        <f>IF(OR(A33="",D33=""),"",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H33" s="25">
-        <f>IF(OR(F33="",G33=""),"",(F33+G33)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F33)),NOT(ISNUMBER(G33))),"",(F33+G33)/2)</f>
         <v>2620.18221825669</v>
       </c>
       <c r="I33" s="26" t="str">
@@ -2140,15 +2140,15 @@
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="24" t="n"/>
       <c r="F34" s="25">
-        <f>IF(OR(A34="",C34=""),"",C34*Config!$B$12)</f>
+        <f>IF(OR(A34="",C34=""),"",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G34" s="25">
-        <f>IF(OR(A34="",D34=""),"",D34*Config!$B$13)</f>
+        <f>IF(OR(A34="",D34=""),"",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H34" s="25">
-        <f>IF(OR(F34="",G34=""),"",(F34+G34)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F34)),NOT(ISNUMBER(G34))),"",(F34+G34)/2)</f>
         <v/>
       </c>
       <c r="I34" s="26">
@@ -2163,15 +2163,15 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="24" t="n"/>
       <c r="F35" s="25">
-        <f>IF(OR(A35="",C35=""),"",C35*Config!$B$12)</f>
+        <f>IF(OR(A35="",C35=""),"",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G35" s="25">
-        <f>IF(OR(A35="",D35=""),"",D35*Config!$B$13)</f>
+        <f>IF(OR(A35="",D35=""),"",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H35" s="25">
-        <f>IF(OR(F35="",G35=""),"",(F35+G35)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F35)),NOT(ISNUMBER(G35))),"",(F35+G35)/2)</f>
         <v/>
       </c>
       <c r="I35" s="26">
@@ -2186,15 +2186,15 @@
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="24" t="n"/>
       <c r="F36" s="25">
-        <f>IF(OR(A36="",C36=""),"",C36*Config!$B$12)</f>
+        <f>IF(OR(A36="",C36=""),"",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G36" s="25">
-        <f>IF(OR(A36="",D36=""),"",D36*Config!$B$13)</f>
+        <f>IF(OR(A36="",D36=""),"",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H36" s="25">
-        <f>IF(OR(F36="",G36=""),"",(F36+G36)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F36)),NOT(ISNUMBER(G36))),"",(F36+G36)/2)</f>
         <v/>
       </c>
       <c r="I36" s="26">
@@ -2209,15 +2209,15 @@
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="24" t="n"/>
       <c r="F37" s="25">
-        <f>IF(OR(A37="",C37=""),"",C37*Config!$B$12)</f>
+        <f>IF(OR(A37="",C37=""),"",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G37" s="25">
-        <f>IF(OR(A37="",D37=""),"",D37*Config!$B$13)</f>
+        <f>IF(OR(A37="",D37=""),"",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H37" s="25">
-        <f>IF(OR(F37="",G37=""),"",(F37+G37)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F37)),NOT(ISNUMBER(G37))),"",(F37+G37)/2)</f>
         <v/>
       </c>
       <c r="I37" s="26">
@@ -2232,15 +2232,15 @@
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="24" t="n"/>
       <c r="F38" s="25">
-        <f>IF(OR(A38="",C38=""),"",C38*Config!$B$12)</f>
+        <f>IF(OR(A38="",C38=""),"",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G38" s="25">
-        <f>IF(OR(A38="",D38=""),"",D38*Config!$B$13)</f>
+        <f>IF(OR(A38="",D38=""),"",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H38" s="25">
-        <f>IF(OR(F38="",G38=""),"",(F38+G38)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F38)),NOT(ISNUMBER(G38))),"",(F38+G38)/2)</f>
         <v/>
       </c>
       <c r="I38" s="26">
@@ -2255,15 +2255,15 @@
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="25">
-        <f>IF(OR(A39="",C39=""),"",C39*Config!$B$12)</f>
+        <f>IF(OR(A39="",C39=""),"",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G39" s="25">
-        <f>IF(OR(A39="",D39=""),"",D39*Config!$B$13)</f>
+        <f>IF(OR(A39="",D39=""),"",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H39" s="25">
-        <f>IF(OR(F39="",G39=""),"",(F39+G39)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F39)),NOT(ISNUMBER(G39))),"",(F39+G39)/2)</f>
         <v/>
       </c>
       <c r="I39" s="26">
@@ -2278,15 +2278,15 @@
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="24" t="n"/>
       <c r="F40" s="25">
-        <f>IF(OR(A40="",C40=""),"",C40*Config!$B$12)</f>
+        <f>IF(OR(A40="",C40=""),"",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G40" s="25">
-        <f>IF(OR(A40="",D40=""),"",D40*Config!$B$13)</f>
+        <f>IF(OR(A40="",D40=""),"",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H40" s="25">
-        <f>IF(OR(F40="",G40=""),"",(F40+G40)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F40)),NOT(ISNUMBER(G40))),"",(F40+G40)/2)</f>
         <v/>
       </c>
       <c r="I40" s="26">
@@ -2301,15 +2301,15 @@
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="24" t="n"/>
       <c r="F41" s="25">
-        <f>IF(OR(A41="",C41=""),"",C41*Config!$B$12)</f>
+        <f>IF(OR(A41="",C41=""),"",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G41" s="25">
-        <f>IF(OR(A41="",D41=""),"",D41*Config!$B$13)</f>
+        <f>IF(OR(A41="",D41=""),"",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H41" s="25">
-        <f>IF(OR(F41="",G41=""),"",(F41+G41)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F41)),NOT(ISNUMBER(G41))),"",(F41+G41)/2)</f>
         <v/>
       </c>
       <c r="I41" s="26">
@@ -2324,15 +2324,15 @@
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="25">
-        <f>IF(OR(A42="",C42=""),"",C42*Config!$B$12)</f>
+        <f>IF(OR(A42="",C42=""),"",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G42" s="25">
-        <f>IF(OR(A42="",D42=""),"",D42*Config!$B$13)</f>
+        <f>IF(OR(A42="",D42=""),"",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H42" s="25">
-        <f>IF(OR(F42="",G42=""),"",(F42+G42)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F42)),NOT(ISNUMBER(G42))),"",(F42+G42)/2)</f>
         <v/>
       </c>
       <c r="I42" s="26">
@@ -2347,15 +2347,15 @@
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="24" t="n"/>
       <c r="F43" s="25">
-        <f>IF(OR(A43="",C43=""),"",C43*Config!$B$12)</f>
+        <f>IF(OR(A43="",C43=""),"",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G43" s="25">
-        <f>IF(OR(A43="",D43=""),"",D43*Config!$B$13)</f>
+        <f>IF(OR(A43="",D43=""),"",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H43" s="25">
-        <f>IF(OR(F43="",G43=""),"",(F43+G43)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F43)),NOT(ISNUMBER(G43))),"",(F43+G43)/2)</f>
         <v/>
       </c>
       <c r="I43" s="26">
@@ -2370,15 +2370,15 @@
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="24" t="n"/>
       <c r="F44" s="25">
-        <f>IF(OR(A44="",C44=""),"",C44*Config!$B$12)</f>
+        <f>IF(OR(A44="",C44=""),"",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G44" s="25">
-        <f>IF(OR(A44="",D44=""),"",D44*Config!$B$13)</f>
+        <f>IF(OR(A44="",D44=""),"",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H44" s="25">
-        <f>IF(OR(F44="",G44=""),"",(F44+G44)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F44)),NOT(ISNUMBER(G44))),"",(F44+G44)/2)</f>
         <v/>
       </c>
       <c r="I44" s="26">
@@ -2393,15 +2393,15 @@
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="24" t="n"/>
       <c r="F45" s="25">
-        <f>IF(OR(A45="",C45=""),"",C45*Config!$B$12)</f>
+        <f>IF(OR(A45="",C45=""),"",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G45" s="25">
-        <f>IF(OR(A45="",D45=""),"",D45*Config!$B$13)</f>
+        <f>IF(OR(A45="",D45=""),"",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H45" s="25">
-        <f>IF(OR(F45="",G45=""),"",(F45+G45)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F45)),NOT(ISNUMBER(G45))),"",(F45+G45)/2)</f>
         <v/>
       </c>
       <c r="I45" s="26">
@@ -2416,15 +2416,15 @@
       <c r="D46" s="23" t="n"/>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="25">
-        <f>IF(OR(A46="",C46=""),"",C46*Config!$B$12)</f>
+        <f>IF(OR(A46="",C46=""),"",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G46" s="25">
-        <f>IF(OR(A46="",D46=""),"",D46*Config!$B$13)</f>
+        <f>IF(OR(A46="",D46=""),"",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H46" s="25">
-        <f>IF(OR(F46="",G46=""),"",(F46+G46)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F46)),NOT(ISNUMBER(G46))),"",(F46+G46)/2)</f>
         <v/>
       </c>
       <c r="I46" s="26">
@@ -2439,15 +2439,15 @@
       <c r="D47" s="23" t="n"/>
       <c r="E47" s="24" t="n"/>
       <c r="F47" s="25">
-        <f>IF(OR(A47="",C47=""),"",C47*Config!$B$12)</f>
+        <f>IF(OR(A47="",C47=""),"",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G47" s="25">
-        <f>IF(OR(A47="",D47=""),"",D47*Config!$B$13)</f>
+        <f>IF(OR(A47="",D47=""),"",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H47" s="25">
-        <f>IF(OR(F47="",G47=""),"",(F47+G47)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F47)),NOT(ISNUMBER(G47))),"",(F47+G47)/2)</f>
         <v/>
       </c>
       <c r="I47" s="26">
@@ -2462,15 +2462,15 @@
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="24" t="n"/>
       <c r="F48" s="25">
-        <f>IF(OR(A48="",C48=""),"",C48*Config!$B$12)</f>
+        <f>IF(OR(A48="",C48=""),"",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12))</f>
         <v/>
       </c>
       <c r="G48" s="25">
-        <f>IF(OR(A48="",D48=""),"",D48*Config!$B$13)</f>
+        <f>IF(OR(A48="",D48=""),"",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13))</f>
         <v/>
       </c>
       <c r="H48" s="25">
-        <f>IF(OR(F48="",G48=""),"",(F48+G48)/2)</f>
+        <f>IF(OR(NOT(ISNUMBER(F48)),NOT(ISNUMBER(G48))),"",(F48+G48)/2)</f>
         <v/>
       </c>
       <c r="I48" s="26">
@@ -2556,15 +2556,15 @@
         <v>160.601265822785</v>
       </c>
       <c r="F54" s="31">
-        <f>IF(E54="","",E54/Config!$B$12-1)</f>
+        <f>IF(OR(E54="",NOT(ISNUMBER(Config!$B$12))),"",E54/Config!$B$12-1)</f>
         <v>0.255873504649599</v>
       </c>
       <c r="G54" s="29">
-        <f>IF(Config!$E$16="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$16,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$16,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>1</v>
       </c>
       <c r="H54" s="25">
-        <f>IF(Config!$E$16="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
+        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
         <v>1509.21161290322</v>
       </c>
     </row>
@@ -2590,15 +2590,15 @@
         <v>125.775656324582</v>
       </c>
       <c r="F55" s="31">
-        <f>IF(E55="","",E55/Config!$B$12-1)</f>
+        <f>IF(OR(E55="",NOT(ISNUMBER(Config!$B$12))),"",E55/Config!$B$12-1)</f>
         <v>-0.0164566045061219</v>
       </c>
       <c r="G55" s="29">
-        <f>IF(Config!$E$17="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$17,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$17,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>7</v>
       </c>
       <c r="H55" s="25">
-        <f>IF(Config!$E$17="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
+        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
         <v>9218.8658064516</v>
       </c>
     </row>
@@ -2624,15 +2624,15 @@
         <v>149.242424242424</v>
       </c>
       <c r="F56" s="31">
-        <f>IF(E56="","",E56/Config!$B$12-1)</f>
+        <f>IF(OR(E56="",NOT(ISNUMBER(Config!$B$12))),"",E56/Config!$B$12-1)</f>
         <v>0.167049371718866</v>
       </c>
       <c r="G56" s="29">
-        <f>IF(Config!$E$18="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$18,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$18,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>1</v>
       </c>
       <c r="H56" s="25">
-        <f>IF(Config!$E$18="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
+        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
         <v>1115.20516129032</v>
       </c>
     </row>
@@ -2658,15 +2658,15 @@
         <v>186.991869918699</v>
       </c>
       <c r="F57" s="31">
-        <f>IF(E57="","",E57/Config!$B$12-1)</f>
+        <f>IF(OR(E57="",NOT(ISNUMBER(Config!$B$12))),"",E57/Config!$B$12-1)</f>
         <v>0.462243362856868</v>
       </c>
       <c r="G57" s="29">
-        <f>IF(Config!$E$19="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$19,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$19,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>0</v>
       </c>
       <c r="H57" s="25">
-        <f>IF(Config!$E$19="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
+        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
         <v>0</v>
       </c>
     </row>
@@ -2692,15 +2692,15 @@
         <v>145.806451612903</v>
       </c>
       <c r="F58" s="31">
-        <f>IF(E58="","",E58/Config!$B$12-1)</f>
+        <f>IF(OR(E58="",NOT(ISNUMBER(Config!$B$12))),"",E58/Config!$B$12-1)</f>
         <v>0.140180673231282</v>
       </c>
       <c r="G58" s="29">
-        <f>IF(Config!$E$20="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$20,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$20,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>1</v>
       </c>
       <c r="H58" s="25">
-        <f>IF(Config!$E$20="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
+        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
         <v>33.4070967741918</v>
       </c>
     </row>
@@ -2726,15 +2726,15 @@
         <v/>
       </c>
       <c r="F59" s="31">
-        <f>IF(E59="","",E59/Config!$B$12-1)</f>
+        <f>IF(OR(E59="",NOT(ISNUMBER(Config!$B$12))),"",E59/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G59" s="29">
-        <f>IF(Config!$E$21="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$21,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$21,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H59" s="25">
-        <f>IF(Config!$E$21="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
+        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
         <v/>
       </c>
     </row>
@@ -2760,15 +2760,15 @@
         <v/>
       </c>
       <c r="F60" s="31">
-        <f>IF(E60="","",E60/Config!$B$12-1)</f>
+        <f>IF(OR(E60="",NOT(ISNUMBER(Config!$B$12))),"",E60/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G60" s="29">
-        <f>IF(Config!$E$22="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$22,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$22,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H60" s="25">
-        <f>IF(Config!$E$22="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
+        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
         <v/>
       </c>
     </row>
@@ -2794,15 +2794,15 @@
         <v/>
       </c>
       <c r="F61" s="31">
-        <f>IF(E61="","",E61/Config!$B$12-1)</f>
+        <f>IF(OR(E61="",NOT(ISNUMBER(Config!$B$12))),"",E61/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G61" s="29">
-        <f>IF(Config!$E$23="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$23,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$23,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H61" s="25">
-        <f>IF(Config!$E$23="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
+        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
         <v/>
       </c>
     </row>
@@ -2828,15 +2828,15 @@
         <v/>
       </c>
       <c r="F62" s="31">
-        <f>IF(E62="","",E62/Config!$B$12-1)</f>
+        <f>IF(OR(E62="",NOT(ISNUMBER(Config!$B$12))),"",E62/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G62" s="29">
-        <f>IF(Config!$E$24="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$24,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$24,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H62" s="25">
-        <f>IF(Config!$E$24="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
+        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
         <v/>
       </c>
     </row>
@@ -2862,15 +2862,15 @@
         <v/>
       </c>
       <c r="F63" s="31">
-        <f>IF(E63="","",E63/Config!$B$12-1)</f>
+        <f>IF(OR(E63="",NOT(ISNUMBER(Config!$B$12))),"",E63/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G63" s="29">
-        <f>IF(Config!$E$25="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$25,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$25,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H63" s="25">
-        <f>IF(Config!$E$25="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
+        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
         <v/>
       </c>
     </row>
@@ -2896,15 +2896,15 @@
         <v/>
       </c>
       <c r="F64" s="31">
-        <f>IF(E64="","",E64/Config!$B$12-1)</f>
+        <f>IF(OR(E64="",NOT(ISNUMBER(Config!$B$12))),"",E64/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G64" s="29">
-        <f>IF(Config!$E$26="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$26,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$26,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H64" s="25">
-        <f>IF(Config!$E$26="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
+        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
         <v/>
       </c>
     </row>
@@ -2930,15 +2930,15 @@
         <v/>
       </c>
       <c r="F65" s="31">
-        <f>IF(E65="","",E65/Config!$B$12-1)</f>
+        <f>IF(OR(E65="",NOT(ISNUMBER(Config!$B$12))),"",E65/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G65" s="29">
-        <f>IF(Config!$E$27="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$27,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$27,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H65" s="25">
-        <f>IF(Config!$E$27="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
+        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
         <v/>
       </c>
     </row>
@@ -2964,15 +2964,15 @@
         <v/>
       </c>
       <c r="F66" s="31">
-        <f>IF(E66="","",E66/Config!$B$12-1)</f>
+        <f>IF(OR(E66="",NOT(ISNUMBER(Config!$B$12))),"",E66/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G66" s="29">
-        <f>IF(Config!$E$28="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$28,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$28,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H66" s="25">
-        <f>IF(Config!$E$28="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
+        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
         <v/>
       </c>
     </row>
@@ -2998,15 +2998,15 @@
         <v/>
       </c>
       <c r="F67" s="31">
-        <f>IF(E67="","",E67/Config!$B$12-1)</f>
+        <f>IF(OR(E67="",NOT(ISNUMBER(Config!$B$12))),"",E67/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G67" s="29">
-        <f>IF(Config!$E$29="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$29,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$29,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H67" s="25">
-        <f>IF(Config!$E$29="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
+        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
         <v/>
       </c>
     </row>
@@ -3032,15 +3032,15 @@
         <v/>
       </c>
       <c r="F68" s="31">
-        <f>IF(E68="","",E68/Config!$B$12-1)</f>
+        <f>IF(OR(E68="",NOT(ISNUMBER(Config!$B$12))),"",E68/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G68" s="29">
-        <f>IF(Config!$E$30="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$30,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$30,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H68" s="25">
-        <f>IF(Config!$E$30="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
+        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
         <v/>
       </c>
     </row>
@@ -3066,15 +3066,15 @@
         <v/>
       </c>
       <c r="F69" s="31">
-        <f>IF(E69="","",E69/Config!$B$12-1)</f>
+        <f>IF(OR(E69="",NOT(ISNUMBER(Config!$B$12))),"",E69/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G69" s="29">
-        <f>IF(Config!$E$31="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$31,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$31,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H69" s="25">
-        <f>IF(Config!$E$31="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
+        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
         <v/>
       </c>
     </row>
@@ -3100,15 +3100,15 @@
         <v/>
       </c>
       <c r="F70" s="31">
-        <f>IF(E70="","",E70/Config!$B$12-1)</f>
+        <f>IF(OR(E70="",NOT(ISNUMBER(Config!$B$12))),"",E70/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G70" s="29">
-        <f>IF(Config!$E$32="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$32,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$32,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H70" s="25">
-        <f>IF(Config!$E$32="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
+        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
         <v/>
       </c>
     </row>
@@ -3134,15 +3134,15 @@
         <v/>
       </c>
       <c r="F71" s="31">
-        <f>IF(E71="","",E71/Config!$B$12-1)</f>
+        <f>IF(OR(E71="",NOT(ISNUMBER(Config!$B$12))),"",E71/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G71" s="29">
-        <f>IF(Config!$E$33="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$33,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$33,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H71" s="25">
-        <f>IF(Config!$E$33="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
+        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
         <v/>
       </c>
     </row>
@@ -3168,15 +3168,15 @@
         <v/>
       </c>
       <c r="F72" s="31">
-        <f>IF(E72="","",E72/Config!$B$12-1)</f>
+        <f>IF(OR(E72="",NOT(ISNUMBER(Config!$B$12))),"",E72/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G72" s="29">
-        <f>IF(Config!$E$34="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$34,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$34,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H72" s="25">
-        <f>IF(Config!$E$34="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
+        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
         <v/>
       </c>
     </row>
@@ -3202,15 +3202,15 @@
         <v/>
       </c>
       <c r="F73" s="31">
-        <f>IF(E73="","",E73/Config!$B$12-1)</f>
+        <f>IF(OR(E73="",NOT(ISNUMBER(Config!$B$12))),"",E73/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="G73" s="29">
-        <f>IF(Config!$E$35="","",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$35,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$35,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H73" s="25">
-        <f>IF(Config!$E$35="","",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
+        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
         <v/>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="B12" s="39">
-        <f>IFERROR(B7*(1+B11)/(1-B8-B9),"")</f>
+        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1,B11&gt;=0),FALSE),B7*(1+B11)/(1-B8-B9),"margens inválidas (Config)"))</f>
         <v>127.880129032258</v>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="B13" s="39">
-        <f>IFERROR(B7*(1+B11)/(1-B8-B10),"")</f>
+        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1,B11&gt;=0),FALSE),B7*(1+B11)/(1-B8-B10),"margens inválidas (Config)"))</f>
         <v>168.692936170213</v>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -3982,6 +3982,20 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem mínima entre 0 % e a margem alvo, e impostos + margem abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B10),B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Folga de 0 % para cima." type="custom">
+      <formula1>=AND(ISNUMBER(B11),B11&gt;=0)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4122,15 +4136,15 @@
         <v>250</v>
       </c>
       <c r="I5" s="31">
-        <f>IF(H5="","",H5/Config!$B$12-1)</f>
+        <f>IF(OR(H5="",NOT(ISNUMBER(Config!$B$12))),"",H5/Config!$B$12-1)</f>
         <v>0.954955800341247</v>
       </c>
       <c r="J5" s="33" t="str">
-        <f>IF(H5="","",IF(H5&lt;Config!$B$12,"Abaixo do mínimo",IF(H5&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H5="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H5&lt;Config!$B$12,"Abaixo do mínimo",IF(H5&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K5" s="25">
-        <f>IF(H5="","",MAX(0,Config!$B$12*G5-F5))</f>
+        <f>IF(OR(H5="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G5-F5))</f>
         <v>0</v>
       </c>
       <c r="L5" s="41">
@@ -4175,15 +4189,15 @@
         <v>85.7142857142857</v>
       </c>
       <c r="I6" s="31">
-        <f>IF(H6="","",H6/Config!$B$12-1)</f>
+        <f>IF(OR(H6="",NOT(ISNUMBER(Config!$B$12))),"",H6/Config!$B$12-1)</f>
         <v>-0.329729439883001</v>
       </c>
       <c r="J6" s="33" t="str">
-        <f>IF(H6="","",IF(H6&lt;Config!$B$12,"Abaixo do mínimo",IF(H6&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H6="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H6&lt;Config!$B$12,"Abaixo do mínimo",IF(H6&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K6" s="25">
-        <f>IF(H6="","",MAX(0,Config!$B$12*G6-F6))</f>
+        <f>IF(OR(H6="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G6-F6))</f>
         <v>2951.60903225806</v>
       </c>
       <c r="L6" s="41">
@@ -4228,15 +4242,15 @@
         <v>172.222222222222</v>
       </c>
       <c r="I7" s="31">
-        <f>IF(H7="","",H7/Config!$B$12-1)</f>
+        <f>IF(OR(H7="",NOT(ISNUMBER(Config!$B$12))),"",H7/Config!$B$12-1)</f>
         <v>0.34674732912397</v>
       </c>
       <c r="J7" s="33" t="str">
-        <f>IF(H7="","",IF(H7&lt;Config!$B$12,"Abaixo do mínimo",IF(H7&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H7="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H7&lt;Config!$B$12,"Abaixo do mínimo",IF(H7&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K7" s="25">
-        <f>IF(H7="","",MAX(0,Config!$B$12*G7-F7))</f>
+        <f>IF(OR(H7="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G7-F7))</f>
         <v>0</v>
       </c>
       <c r="L7" s="41">
@@ -4281,15 +4295,15 @@
         <v>135</v>
       </c>
       <c r="I8" s="31">
-        <f>IF(H8="","",H8/Config!$B$12-1)</f>
+        <f>IF(OR(H8="",NOT(ISNUMBER(Config!$B$12))),"",H8/Config!$B$12-1)</f>
         <v>0.0556761321842736</v>
       </c>
       <c r="J8" s="33" t="str">
-        <f>IF(H8="","",IF(H8&lt;Config!$B$12,"Abaixo do mínimo",IF(H8&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H8="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H8&lt;Config!$B$12,"Abaixo do mínimo",IF(H8&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K8" s="25">
-        <f>IF(H8="","",MAX(0,Config!$B$12*G8-F8))</f>
+        <f>IF(OR(H8="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G8-F8))</f>
         <v>0</v>
       </c>
       <c r="L8" s="41">
@@ -4334,15 +4348,15 @@
         <v>186.666666666667</v>
       </c>
       <c r="I9" s="31">
-        <f>IF(H9="","",H9/Config!$B$12-1)</f>
+        <f>IF(OR(H9="",NOT(ISNUMBER(Config!$B$12))),"",H9/Config!$B$12-1)</f>
         <v>0.459700330921465</v>
       </c>
       <c r="J9" s="33" t="str">
-        <f>IF(H9="","",IF(H9&lt;Config!$B$12,"Abaixo do mínimo",IF(H9&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H9="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H9&lt;Config!$B$12,"Abaixo do mínimo",IF(H9&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K9" s="25">
-        <f>IF(H9="","",MAX(0,Config!$B$12*G9-F9))</f>
+        <f>IF(OR(H9="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G9-F9))</f>
         <v>0</v>
       </c>
       <c r="L9" s="41">
@@ -4387,15 +4401,15 @@
         <v>187.5</v>
       </c>
       <c r="I10" s="31">
-        <f>IF(H10="","",H10/Config!$B$12-1)</f>
+        <f>IF(OR(H10="",NOT(ISNUMBER(Config!$B$12))),"",H10/Config!$B$12-1)</f>
         <v>0.466216850255936</v>
       </c>
       <c r="J10" s="33" t="str">
-        <f>IF(H10="","",IF(H10&lt;Config!$B$12,"Abaixo do mínimo",IF(H10&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H10="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H10&lt;Config!$B$12,"Abaixo do mínimo",IF(H10&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K10" s="25">
-        <f>IF(H10="","",MAX(0,Config!$B$12*G10-F10))</f>
+        <f>IF(OR(H10="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G10-F10))</f>
         <v>0</v>
       </c>
       <c r="L10" s="41">
@@ -4440,15 +4454,15 @@
         <v>183.333333333333</v>
       </c>
       <c r="I11" s="31">
-        <f>IF(H11="","",H11/Config!$B$12-1)</f>
+        <f>IF(OR(H11="",NOT(ISNUMBER(Config!$B$12))),"",H11/Config!$B$12-1)</f>
         <v>0.433634253583582</v>
       </c>
       <c r="J11" s="33" t="str">
-        <f>IF(H11="","",IF(H11&lt;Config!$B$12,"Abaixo do mínimo",IF(H11&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H11="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H11&lt;Config!$B$12,"Abaixo do mínimo",IF(H11&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K11" s="25">
-        <f>IF(H11="","",MAX(0,Config!$B$12*G11-F11))</f>
+        <f>IF(OR(H11="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G11-F11))</f>
         <v>0</v>
       </c>
       <c r="L11" s="41">
@@ -4493,15 +4507,15 @@
         <v>118.75</v>
       </c>
       <c r="I12" s="31">
-        <f>IF(H12="","",H12/Config!$B$12-1)</f>
+        <f>IF(OR(H12="",NOT(ISNUMBER(Config!$B$12))),"",H12/Config!$B$12-1)</f>
         <v>-0.0713959948379075</v>
       </c>
       <c r="J12" s="33" t="str">
-        <f>IF(H12="","",IF(H12&lt;Config!$B$12,"Abaixo do mínimo",IF(H12&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H12="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H12&lt;Config!$B$12,"Abaixo do mínimo",IF(H12&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K12" s="25">
-        <f>IF(H12="","",MAX(0,Config!$B$12*G12-F12))</f>
+        <f>IF(OR(H12="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G12-F12))</f>
         <v>730.410322580643</v>
       </c>
       <c r="L12" s="41">
@@ -4546,15 +4560,15 @@
         <v>88.8888888888889</v>
       </c>
       <c r="I13" s="31">
-        <f>IF(H13="","",H13/Config!$B$12-1)</f>
+        <f>IF(OR(H13="",NOT(ISNUMBER(Config!$B$12))),"",H13/Config!$B$12-1)</f>
         <v>-0.304904604323112</v>
       </c>
       <c r="J13" s="33" t="str">
-        <f>IF(H13="","",IF(H13&lt;Config!$B$12,"Abaixo do mínimo",IF(H13&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H13="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H13&lt;Config!$B$12,"Abaixo do mínimo",IF(H13&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K13" s="25">
-        <f>IF(H13="","",MAX(0,Config!$B$12*G13-F13))</f>
+        <f>IF(OR(H13="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G13-F13))</f>
         <v>1754.60580645161</v>
       </c>
       <c r="L13" s="41">
@@ -4599,15 +4613,15 @@
         <v>157.894736842105</v>
       </c>
       <c r="I14" s="31">
-        <f>IF(H14="","",H14/Config!$B$12-1)</f>
+        <f>IF(OR(H14="",NOT(ISNUMBER(Config!$B$12))),"",H14/Config!$B$12-1)</f>
         <v>0.234708926531314</v>
       </c>
       <c r="J14" s="33" t="str">
-        <f>IF(H14="","",IF(H14&lt;Config!$B$12,"Abaixo do mínimo",IF(H14&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H14="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H14&lt;Config!$B$12,"Abaixo do mínimo",IF(H14&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K14" s="25">
-        <f>IF(H14="","",MAX(0,Config!$B$12*G14-F14))</f>
+        <f>IF(OR(H14="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G14-F14))</f>
         <v>0</v>
       </c>
       <c r="L14" s="41">
@@ -4652,15 +4666,15 @@
         <v>170</v>
       </c>
       <c r="I15" s="31">
-        <f>IF(H15="","",H15/Config!$B$12-1)</f>
+        <f>IF(OR(H15="",NOT(ISNUMBER(Config!$B$12))),"",H15/Config!$B$12-1)</f>
         <v>0.329369944232048</v>
       </c>
       <c r="J15" s="33" t="str">
-        <f>IF(H15="","",IF(H15&lt;Config!$B$12,"Abaixo do mínimo",IF(H15&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H15="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H15&lt;Config!$B$12,"Abaixo do mínimo",IF(H15&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K15" s="25">
-        <f>IF(H15="","",MAX(0,Config!$B$12*G15-F15))</f>
+        <f>IF(OR(H15="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G15-F15))</f>
         <v>0</v>
       </c>
       <c r="L15" s="41">
@@ -4705,15 +4719,15 @@
         <v>180</v>
       </c>
       <c r="I16" s="31">
-        <f>IF(H16="","",H16/Config!$B$12-1)</f>
+        <f>IF(OR(H16="",NOT(ISNUMBER(Config!$B$12))),"",H16/Config!$B$12-1)</f>
         <v>0.407568176245698</v>
       </c>
       <c r="J16" s="33" t="str">
-        <f>IF(H16="","",IF(H16&lt;Config!$B$12,"Abaixo do mínimo",IF(H16&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H16="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H16&lt;Config!$B$12,"Abaixo do mínimo",IF(H16&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K16" s="25">
-        <f>IF(H16="","",MAX(0,Config!$B$12*G16-F16))</f>
+        <f>IF(OR(H16="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G16-F16))</f>
         <v>0</v>
       </c>
       <c r="L16" s="41">
@@ -4758,15 +4772,15 @@
         <v>163.636363636364</v>
       </c>
       <c r="I17" s="31">
-        <f>IF(H17="","",H17/Config!$B$12-1)</f>
+        <f>IF(OR(H17="",NOT(ISNUMBER(Config!$B$12))),"",H17/Config!$B$12-1)</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J17" s="33" t="str">
-        <f>IF(H17="","",IF(H17&lt;Config!$B$12,"Abaixo do mínimo",IF(H17&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H17="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H17&lt;Config!$B$12,"Abaixo do mínimo",IF(H17&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K17" s="25">
-        <f>IF(H17="","",MAX(0,Config!$B$12*G17-F17))</f>
+        <f>IF(OR(H17="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G17-F17))</f>
         <v>0</v>
       </c>
       <c r="L17" s="41">
@@ -4811,15 +4825,15 @@
         <v>150</v>
       </c>
       <c r="I18" s="31">
-        <f>IF(H18="","",H18/Config!$B$12-1)</f>
+        <f>IF(OR(H18="",NOT(ISNUMBER(Config!$B$12))),"",H18/Config!$B$12-1)</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J18" s="33" t="str">
-        <f>IF(H18="","",IF(H18&lt;Config!$B$12,"Abaixo do mínimo",IF(H18&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H18="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H18&lt;Config!$B$12,"Abaixo do mínimo",IF(H18&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K18" s="25">
-        <f>IF(H18="","",MAX(0,Config!$B$12*G18-F18))</f>
+        <f>IF(OR(H18="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G18-F18))</f>
         <v>0</v>
       </c>
       <c r="L18" s="41">
@@ -4864,15 +4878,15 @@
         <v>112.5</v>
       </c>
       <c r="I19" s="31">
-        <f>IF(H19="","",H19/Config!$B$12-1)</f>
+        <f>IF(OR(H19="",NOT(ISNUMBER(Config!$B$12))),"",H19/Config!$B$12-1)</f>
         <v>-0.120269889846439</v>
       </c>
       <c r="J19" s="33" t="str">
-        <f>IF(H19="","",IF(H19&lt;Config!$B$12,"Abaixo do mínimo",IF(H19&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H19="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H19&lt;Config!$B$12,"Abaixo do mínimo",IF(H19&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K19" s="25">
-        <f>IF(H19="","",MAX(0,Config!$B$12*G19-F19))</f>
+        <f>IF(OR(H19="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G19-F19))</f>
         <v>1230.41032258064</v>
       </c>
       <c r="L19" s="41">
@@ -4917,15 +4931,15 @@
         <v>157.142857142857</v>
       </c>
       <c r="I20" s="31">
-        <f>IF(H20="","",H20/Config!$B$12-1)</f>
+        <f>IF(OR(H20="",NOT(ISNUMBER(Config!$B$12))),"",H20/Config!$B$12-1)</f>
         <v>0.228829360214498</v>
       </c>
       <c r="J20" s="33" t="str">
-        <f>IF(H20="","",IF(H20&lt;Config!$B$12,"Abaixo do mínimo",IF(H20&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H20="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H20&lt;Config!$B$12,"Abaixo do mínimo",IF(H20&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K20" s="25">
-        <f>IF(H20="","",MAX(0,Config!$B$12*G20-F20))</f>
+        <f>IF(OR(H20="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G20-F20))</f>
         <v>0</v>
       </c>
       <c r="L20" s="41">
@@ -4970,15 +4984,15 @@
         <v>163.636363636364</v>
       </c>
       <c r="I21" s="31">
-        <f>IF(H21="","",H21/Config!$B$12-1)</f>
+        <f>IF(OR(H21="",NOT(ISNUMBER(Config!$B$12))),"",H21/Config!$B$12-1)</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J21" s="33" t="str">
-        <f>IF(H21="","",IF(H21&lt;Config!$B$12,"Abaixo do mínimo",IF(H21&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H21="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H21&lt;Config!$B$12,"Abaixo do mínimo",IF(H21&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K21" s="25">
-        <f>IF(H21="","",MAX(0,Config!$B$12*G21-F21))</f>
+        <f>IF(OR(H21="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G21-F21))</f>
         <v>0</v>
       </c>
       <c r="L21" s="41">
@@ -5023,15 +5037,15 @@
         <v>146.666666666667</v>
       </c>
       <c r="I22" s="31">
-        <f>IF(H22="","",H22/Config!$B$12-1)</f>
+        <f>IF(OR(H22="",NOT(ISNUMBER(Config!$B$12))),"",H22/Config!$B$12-1)</f>
         <v>0.146907402866865</v>
       </c>
       <c r="J22" s="33" t="str">
-        <f>IF(H22="","",IF(H22&lt;Config!$B$12,"Abaixo do mínimo",IF(H22&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H22="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H22&lt;Config!$B$12,"Abaixo do mínimo",IF(H22&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K22" s="25">
-        <f>IF(H22="","",MAX(0,Config!$B$12*G22-F22))</f>
+        <f>IF(OR(H22="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G22-F22))</f>
         <v>0</v>
       </c>
       <c r="L22" s="41">
@@ -5076,15 +5090,15 @@
         <v>111.111111111111</v>
       </c>
       <c r="I23" s="31">
-        <f>IF(H23="","",H23/Config!$B$12-1)</f>
+        <f>IF(OR(H23="",NOT(ISNUMBER(Config!$B$12))),"",H23/Config!$B$12-1)</f>
         <v>-0.13113075540389</v>
       </c>
       <c r="J23" s="33" t="str">
-        <f>IF(H23="","",IF(H23&lt;Config!$B$12,"Abaixo do mínimo",IF(H23&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H23="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H23&lt;Config!$B$12,"Abaixo do mínimo",IF(H23&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K23" s="25">
-        <f>IF(H23="","",MAX(0,Config!$B$12*G23-F23))</f>
+        <f>IF(OR(H23="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G23-F23))</f>
         <v>1509.21161290322</v>
       </c>
       <c r="L23" s="41">
@@ -5129,15 +5143,15 @@
         <v>100</v>
       </c>
       <c r="I24" s="31">
-        <f>IF(H24="","",H24/Config!$B$12-1)</f>
+        <f>IF(OR(H24="",NOT(ISNUMBER(Config!$B$12))),"",H24/Config!$B$12-1)</f>
         <v>-0.218017679863501</v>
       </c>
       <c r="J24" s="33" t="str">
-        <f>IF(H24="","",IF(H24&lt;Config!$B$12,"Abaixo do mínimo",IF(H24&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H24="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H24&lt;Config!$B$12,"Abaixo do mínimo",IF(H24&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K24" s="25">
-        <f>IF(H24="","",MAX(0,Config!$B$12*G24-F24))</f>
+        <f>IF(OR(H24="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G24-F24))</f>
         <v>1115.20516129032</v>
       </c>
       <c r="L24" s="41">
@@ -5182,15 +5196,15 @@
         <v>157.894736842105</v>
       </c>
       <c r="I25" s="31">
-        <f>IF(H25="","",H25/Config!$B$12-1)</f>
+        <f>IF(OR(H25="",NOT(ISNUMBER(Config!$B$12))),"",H25/Config!$B$12-1)</f>
         <v>0.234708926531314</v>
       </c>
       <c r="J25" s="33" t="str">
-        <f>IF(H25="","",IF(H25&lt;Config!$B$12,"Abaixo do mínimo",IF(H25&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H25="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H25&lt;Config!$B$12,"Abaixo do mínimo",IF(H25&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K25" s="25">
-        <f>IF(H25="","",MAX(0,Config!$B$12*G25-F25))</f>
+        <f>IF(OR(H25="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G25-F25))</f>
         <v>0</v>
       </c>
       <c r="L25" s="41">
@@ -5235,15 +5249,15 @@
         <v>150</v>
       </c>
       <c r="I26" s="31">
-        <f>IF(H26="","",H26/Config!$B$12-1)</f>
+        <f>IF(OR(H26="",NOT(ISNUMBER(Config!$B$12))),"",H26/Config!$B$12-1)</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J26" s="33" t="str">
-        <f>IF(H26="","",IF(H26&lt;Config!$B$12,"Abaixo do mínimo",IF(H26&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H26="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H26&lt;Config!$B$12,"Abaixo do mínimo",IF(H26&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K26" s="25">
-        <f>IF(H26="","",MAX(0,Config!$B$12*G26-F26))</f>
+        <f>IF(OR(H26="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G26-F26))</f>
         <v>0</v>
       </c>
       <c r="L26" s="41">
@@ -5288,15 +5302,15 @@
         <v>160</v>
       </c>
       <c r="I27" s="31">
-        <f>IF(H27="","",H27/Config!$B$12-1)</f>
+        <f>IF(OR(H27="",NOT(ISNUMBER(Config!$B$12))),"",H27/Config!$B$12-1)</f>
         <v>0.251171712218398</v>
       </c>
       <c r="J27" s="33" t="str">
-        <f>IF(H27="","",IF(H27&lt;Config!$B$12,"Abaixo do mínimo",IF(H27&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H27="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H27&lt;Config!$B$12,"Abaixo do mínimo",IF(H27&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K27" s="25">
-        <f>IF(H27="","",MAX(0,Config!$B$12*G27-F27))</f>
+        <f>IF(OR(H27="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G27-F27))</f>
         <v>0</v>
       </c>
       <c r="L27" s="41">
@@ -5341,15 +5355,15 @@
         <v>190</v>
       </c>
       <c r="I28" s="31">
-        <f>IF(H28="","",H28/Config!$B$12-1)</f>
+        <f>IF(OR(H28="",NOT(ISNUMBER(Config!$B$12))),"",H28/Config!$B$12-1)</f>
         <v>0.485766408259348</v>
       </c>
       <c r="J28" s="33" t="str">
-        <f>IF(H28="","",IF(H28&lt;Config!$B$12,"Abaixo do mínimo",IF(H28&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H28="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H28&lt;Config!$B$12,"Abaixo do mínimo",IF(H28&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K28" s="25">
-        <f>IF(H28="","",MAX(0,Config!$B$12*G28-F28))</f>
+        <f>IF(OR(H28="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G28-F28))</f>
         <v>0</v>
       </c>
       <c r="L28" s="41">
@@ -5394,15 +5408,15 @@
         <v>180.451127819549</v>
       </c>
       <c r="I29" s="31">
-        <f>IF(H29="","",H29/Config!$B$12-1)</f>
+        <f>IF(OR(H29="",NOT(ISNUMBER(Config!$B$12))),"",H29/Config!$B$12-1)</f>
         <v>0.411095916035788</v>
       </c>
       <c r="J29" s="33" t="str">
-        <f>IF(H29="","",IF(H29&lt;Config!$B$12,"Abaixo do mínimo",IF(H29&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H29="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H29&lt;Config!$B$12,"Abaixo do mínimo",IF(H29&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K29" s="25">
-        <f>IF(H29="","",MAX(0,Config!$B$12*G29-F29))</f>
+        <f>IF(OR(H29="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G29-F29))</f>
         <v>0</v>
       </c>
       <c r="L29" s="41">
@@ -5447,15 +5461,15 @@
         <v>233.333333333333</v>
       </c>
       <c r="I30" s="31">
-        <f>IF(H30="","",H30/Config!$B$12-1)</f>
+        <f>IF(OR(H30="",NOT(ISNUMBER(Config!$B$12))),"",H30/Config!$B$12-1)</f>
         <v>0.824625413651831</v>
       </c>
       <c r="J30" s="33" t="str">
-        <f>IF(H30="","",IF(H30&lt;Config!$B$12,"Abaixo do mínimo",IF(H30&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H30="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H30&lt;Config!$B$12,"Abaixo do mínimo",IF(H30&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K30" s="25">
-        <f>IF(H30="","",MAX(0,Config!$B$12*G30-F30))</f>
+        <f>IF(OR(H30="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G30-F30))</f>
         <v>0</v>
       </c>
       <c r="L30" s="41">
@@ -5500,15 +5514,15 @@
         <v>100</v>
       </c>
       <c r="I31" s="31">
-        <f>IF(H31="","",H31/Config!$B$12-1)</f>
+        <f>IF(OR(H31="",NOT(ISNUMBER(Config!$B$12))),"",H31/Config!$B$12-1)</f>
         <v>-0.218017679863501</v>
       </c>
       <c r="J31" s="33" t="str">
-        <f>IF(H31="","",IF(H31&lt;Config!$B$12,"Abaixo do mínimo",IF(H31&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H31="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H31&lt;Config!$B$12,"Abaixo do mínimo",IF(H31&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K31" s="25">
-        <f>IF(H31="","",MAX(0,Config!$B$12*G31-F31))</f>
+        <f>IF(OR(H31="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G31-F31))</f>
         <v>1951.60903225806</v>
       </c>
       <c r="L31" s="41">
@@ -5553,15 +5567,15 @@
         <v>136.363636363636</v>
       </c>
       <c r="I32" s="31">
-        <f>IF(H32="","",H32/Config!$B$12-1)</f>
+        <f>IF(OR(H32="",NOT(ISNUMBER(Config!$B$12))),"",H32/Config!$B$12-1)</f>
         <v>0.0663395274588623</v>
       </c>
       <c r="J32" s="33" t="str">
-        <f>IF(H32="","",IF(H32&lt;Config!$B$12,"Abaixo do mínimo",IF(H32&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H32="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H32&lt;Config!$B$12,"Abaixo do mínimo",IF(H32&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K32" s="25">
-        <f>IF(H32="","",MAX(0,Config!$B$12*G32-F32))</f>
+        <f>IF(OR(H32="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G32-F32))</f>
         <v>0</v>
       </c>
       <c r="L32" s="41">
@@ -5606,15 +5620,15 @@
         <v>190</v>
       </c>
       <c r="I33" s="31">
-        <f>IF(H33="","",H33/Config!$B$12-1)</f>
+        <f>IF(OR(H33="",NOT(ISNUMBER(Config!$B$12))),"",H33/Config!$B$12-1)</f>
         <v>0.485766408259348</v>
       </c>
       <c r="J33" s="33" t="str">
-        <f>IF(H33="","",IF(H33&lt;Config!$B$12,"Abaixo do mínimo",IF(H33&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H33="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H33&lt;Config!$B$12,"Abaixo do mínimo",IF(H33&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K33" s="25">
-        <f>IF(H33="","",MAX(0,Config!$B$12*G33-F33))</f>
+        <f>IF(OR(H33="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G33-F33))</f>
         <v>0</v>
       </c>
       <c r="L33" s="41">
@@ -5659,15 +5673,15 @@
         <v>154.285714285714</v>
       </c>
       <c r="I34" s="31">
-        <f>IF(H34="","",H34/Config!$B$12-1)</f>
+        <f>IF(OR(H34="",NOT(ISNUMBER(Config!$B$12))),"",H34/Config!$B$12-1)</f>
         <v>0.206487008210598</v>
       </c>
       <c r="J34" s="33" t="str">
-        <f>IF(H34="","",IF(H34&lt;Config!$B$12,"Abaixo do mínimo",IF(H34&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H34="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H34&lt;Config!$B$12,"Abaixo do mínimo",IF(H34&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K34" s="25">
-        <f>IF(H34="","",MAX(0,Config!$B$12*G34-F34))</f>
+        <f>IF(OR(H34="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G34-F34))</f>
         <v>0</v>
       </c>
       <c r="L34" s="41">
@@ -5712,15 +5726,15 @@
         <v>200</v>
       </c>
       <c r="I35" s="31">
-        <f>IF(H35="","",H35/Config!$B$12-1)</f>
+        <f>IF(OR(H35="",NOT(ISNUMBER(Config!$B$12))),"",H35/Config!$B$12-1)</f>
         <v>0.563964640272998</v>
       </c>
       <c r="J35" s="33" t="str">
-        <f>IF(H35="","",IF(H35&lt;Config!$B$12,"Abaixo do mínimo",IF(H35&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H35="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H35&lt;Config!$B$12,"Abaixo do mínimo",IF(H35&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K35" s="25">
-        <f>IF(H35="","",MAX(0,Config!$B$12*G35-F35))</f>
+        <f>IF(OR(H35="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G35-F35))</f>
         <v>0</v>
       </c>
       <c r="L35" s="41">
@@ -5765,15 +5779,15 @@
         <v>163.636363636364</v>
       </c>
       <c r="I36" s="31">
-        <f>IF(H36="","",H36/Config!$B$12-1)</f>
+        <f>IF(OR(H36="",NOT(ISNUMBER(Config!$B$12))),"",H36/Config!$B$12-1)</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J36" s="33" t="str">
-        <f>IF(H36="","",IF(H36&lt;Config!$B$12,"Abaixo do mínimo",IF(H36&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H36="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H36&lt;Config!$B$12,"Abaixo do mínimo",IF(H36&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K36" s="25">
-        <f>IF(H36="","",MAX(0,Config!$B$12*G36-F36))</f>
+        <f>IF(OR(H36="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G36-F36))</f>
         <v>0</v>
       </c>
       <c r="L36" s="41">
@@ -5818,15 +5832,15 @@
         <v>144.444444444444</v>
       </c>
       <c r="I37" s="31">
-        <f>IF(H37="","",H37/Config!$B$12-1)</f>
+        <f>IF(OR(H37="",NOT(ISNUMBER(Config!$B$12))),"",H37/Config!$B$12-1)</f>
         <v>0.129530017974943</v>
       </c>
       <c r="J37" s="33" t="str">
-        <f>IF(H37="","",IF(H37&lt;Config!$B$12,"Abaixo do mínimo",IF(H37&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H37="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H37&lt;Config!$B$12,"Abaixo do mínimo",IF(H37&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K37" s="25">
-        <f>IF(H37="","",MAX(0,Config!$B$12*G37-F37))</f>
+        <f>IF(OR(H37="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G37-F37))</f>
         <v>0</v>
       </c>
       <c r="L37" s="41">
@@ -5871,15 +5885,15 @@
         <v>133.333333333333</v>
       </c>
       <c r="I38" s="31">
-        <f>IF(H38="","",H38/Config!$B$12-1)</f>
+        <f>IF(OR(H38="",NOT(ISNUMBER(Config!$B$12))),"",H38/Config!$B$12-1)</f>
         <v>0.0426430935153319</v>
       </c>
       <c r="J38" s="33" t="str">
-        <f>IF(H38="","",IF(H38&lt;Config!$B$12,"Abaixo do mínimo",IF(H38&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H38="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H38&lt;Config!$B$12,"Abaixo do mínimo",IF(H38&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K38" s="25">
-        <f>IF(H38="","",MAX(0,Config!$B$12*G38-F38))</f>
+        <f>IF(OR(H38="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G38-F38))</f>
         <v>0</v>
       </c>
       <c r="L38" s="41">
@@ -5924,15 +5938,15 @@
         <v>126.315789473684</v>
       </c>
       <c r="I39" s="31">
-        <f>IF(H39="","",H39/Config!$B$12-1)</f>
+        <f>IF(OR(H39="",NOT(ISNUMBER(Config!$B$12))),"",H39/Config!$B$12-1)</f>
         <v>-0.0122328587749487</v>
       </c>
       <c r="J39" s="33" t="str">
-        <f>IF(H39="","",IF(H39&lt;Config!$B$12,"Abaixo do mínimo",IF(H39&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H39="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H39&lt;Config!$B$12,"Abaixo do mínimo",IF(H39&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K39" s="25">
-        <f>IF(H39="","",MAX(0,Config!$B$12*G39-F39))</f>
+        <f>IF(OR(H39="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G39-F39))</f>
         <v>148.612258064513</v>
       </c>
       <c r="L39" s="41">
@@ -5977,15 +5991,15 @@
         <v>127.272727272727</v>
       </c>
       <c r="I40" s="31">
-        <f>IF(H40="","",H40/Config!$B$12-1)</f>
+        <f>IF(OR(H40="",NOT(ISNUMBER(Config!$B$12))),"",H40/Config!$B$12-1)</f>
         <v>-0.00474977437172863</v>
       </c>
       <c r="J40" s="33" t="str">
-        <f>IF(H40="","",IF(H40&lt;Config!$B$12,"Abaixo do mínimo",IF(H40&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H40="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H40&lt;Config!$B$12,"Abaixo do mínimo",IF(H40&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K40" s="25">
-        <f>IF(H40="","",MAX(0,Config!$B$12*G40-F40))</f>
+        <f>IF(OR(H40="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G40-F40))</f>
         <v>33.4070967741918</v>
       </c>
       <c r="L40" s="41">
@@ -6030,15 +6044,15 @@
         <v>150</v>
       </c>
       <c r="I41" s="31">
-        <f>IF(H41="","",H41/Config!$B$12-1)</f>
+        <f>IF(OR(H41="",NOT(ISNUMBER(Config!$B$12))),"",H41/Config!$B$12-1)</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J41" s="33" t="str">
-        <f>IF(H41="","",IF(H41&lt;Config!$B$12,"Abaixo do mínimo",IF(H41&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H41="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H41&lt;Config!$B$12,"Abaixo do mínimo",IF(H41&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K41" s="25">
-        <f>IF(H41="","",MAX(0,Config!$B$12*G41-F41))</f>
+        <f>IF(OR(H41="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G41-F41))</f>
         <v>0</v>
       </c>
       <c r="L41" s="41">
@@ -6083,15 +6097,15 @@
         <v>121.428571428571</v>
       </c>
       <c r="I42" s="31">
-        <f>IF(H42="","",H42/Config!$B$12-1)</f>
+        <f>IF(OR(H42="",NOT(ISNUMBER(Config!$B$12))),"",H42/Config!$B$12-1)</f>
         <v>-0.0504500398342512</v>
       </c>
       <c r="J42" s="33" t="str">
-        <f>IF(H42="","",IF(H42&lt;Config!$B$12,"Abaixo do mínimo",IF(H42&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H42="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H42&lt;Config!$B$12,"Abaixo do mínimo",IF(H42&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K42" s="25">
-        <f>IF(H42="","",MAX(0,Config!$B$12*G42-F42))</f>
+        <f>IF(OR(H42="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G42-F42))</f>
         <v>451.609032258062</v>
       </c>
       <c r="L42" s="41">
@@ -6112,15 +6126,15 @@
         <v/>
       </c>
       <c r="I43" s="31">
-        <f>IF(H43="","",H43/Config!$B$12-1)</f>
+        <f>IF(OR(H43="",NOT(ISNUMBER(Config!$B$12))),"",H43/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J43" s="33">
-        <f>IF(H43="","",IF(H43&lt;Config!$B$12,"Abaixo do mínimo",IF(H43&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H43="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H43&lt;Config!$B$12,"Abaixo do mínimo",IF(H43&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K43" s="25">
-        <f>IF(H43="","",MAX(0,Config!$B$12*G43-F43))</f>
+        <f>IF(OR(H43="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G43-F43))</f>
         <v/>
       </c>
       <c r="L43" s="41">
@@ -6141,15 +6155,15 @@
         <v/>
       </c>
       <c r="I44" s="31">
-        <f>IF(H44="","",H44/Config!$B$12-1)</f>
+        <f>IF(OR(H44="",NOT(ISNUMBER(Config!$B$12))),"",H44/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J44" s="33">
-        <f>IF(H44="","",IF(H44&lt;Config!$B$12,"Abaixo do mínimo",IF(H44&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H44="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H44&lt;Config!$B$12,"Abaixo do mínimo",IF(H44&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K44" s="25">
-        <f>IF(H44="","",MAX(0,Config!$B$12*G44-F44))</f>
+        <f>IF(OR(H44="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G44-F44))</f>
         <v/>
       </c>
       <c r="L44" s="41">
@@ -6170,15 +6184,15 @@
         <v/>
       </c>
       <c r="I45" s="31">
-        <f>IF(H45="","",H45/Config!$B$12-1)</f>
+        <f>IF(OR(H45="",NOT(ISNUMBER(Config!$B$12))),"",H45/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J45" s="33">
-        <f>IF(H45="","",IF(H45&lt;Config!$B$12,"Abaixo do mínimo",IF(H45&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H45="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H45&lt;Config!$B$12,"Abaixo do mínimo",IF(H45&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K45" s="25">
-        <f>IF(H45="","",MAX(0,Config!$B$12*G45-F45))</f>
+        <f>IF(OR(H45="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G45-F45))</f>
         <v/>
       </c>
       <c r="L45" s="41">
@@ -6199,15 +6213,15 @@
         <v/>
       </c>
       <c r="I46" s="31">
-        <f>IF(H46="","",H46/Config!$B$12-1)</f>
+        <f>IF(OR(H46="",NOT(ISNUMBER(Config!$B$12))),"",H46/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J46" s="33">
-        <f>IF(H46="","",IF(H46&lt;Config!$B$12,"Abaixo do mínimo",IF(H46&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H46="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H46&lt;Config!$B$12,"Abaixo do mínimo",IF(H46&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K46" s="25">
-        <f>IF(H46="","",MAX(0,Config!$B$12*G46-F46))</f>
+        <f>IF(OR(H46="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G46-F46))</f>
         <v/>
       </c>
       <c r="L46" s="41">
@@ -6228,15 +6242,15 @@
         <v/>
       </c>
       <c r="I47" s="31">
-        <f>IF(H47="","",H47/Config!$B$12-1)</f>
+        <f>IF(OR(H47="",NOT(ISNUMBER(Config!$B$12))),"",H47/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J47" s="33">
-        <f>IF(H47="","",IF(H47&lt;Config!$B$12,"Abaixo do mínimo",IF(H47&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H47="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H47&lt;Config!$B$12,"Abaixo do mínimo",IF(H47&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K47" s="25">
-        <f>IF(H47="","",MAX(0,Config!$B$12*G47-F47))</f>
+        <f>IF(OR(H47="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G47-F47))</f>
         <v/>
       </c>
       <c r="L47" s="41">
@@ -6257,15 +6271,15 @@
         <v/>
       </c>
       <c r="I48" s="31">
-        <f>IF(H48="","",H48/Config!$B$12-1)</f>
+        <f>IF(OR(H48="",NOT(ISNUMBER(Config!$B$12))),"",H48/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J48" s="33">
-        <f>IF(H48="","",IF(H48&lt;Config!$B$12,"Abaixo do mínimo",IF(H48&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H48="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H48&lt;Config!$B$12,"Abaixo do mínimo",IF(H48&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K48" s="25">
-        <f>IF(H48="","",MAX(0,Config!$B$12*G48-F48))</f>
+        <f>IF(OR(H48="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G48-F48))</f>
         <v/>
       </c>
       <c r="L48" s="41">
@@ -6286,15 +6300,15 @@
         <v/>
       </c>
       <c r="I49" s="31">
-        <f>IF(H49="","",H49/Config!$B$12-1)</f>
+        <f>IF(OR(H49="",NOT(ISNUMBER(Config!$B$12))),"",H49/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J49" s="33">
-        <f>IF(H49="","",IF(H49&lt;Config!$B$12,"Abaixo do mínimo",IF(H49&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H49="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H49&lt;Config!$B$12,"Abaixo do mínimo",IF(H49&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K49" s="25">
-        <f>IF(H49="","",MAX(0,Config!$B$12*G49-F49))</f>
+        <f>IF(OR(H49="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G49-F49))</f>
         <v/>
       </c>
       <c r="L49" s="41">
@@ -6315,15 +6329,15 @@
         <v/>
       </c>
       <c r="I50" s="31">
-        <f>IF(H50="","",H50/Config!$B$12-1)</f>
+        <f>IF(OR(H50="",NOT(ISNUMBER(Config!$B$12))),"",H50/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J50" s="33">
-        <f>IF(H50="","",IF(H50&lt;Config!$B$12,"Abaixo do mínimo",IF(H50&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H50="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H50&lt;Config!$B$12,"Abaixo do mínimo",IF(H50&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K50" s="25">
-        <f>IF(H50="","",MAX(0,Config!$B$12*G50-F50))</f>
+        <f>IF(OR(H50="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G50-F50))</f>
         <v/>
       </c>
       <c r="L50" s="41">
@@ -6344,15 +6358,15 @@
         <v/>
       </c>
       <c r="I51" s="31">
-        <f>IF(H51="","",H51/Config!$B$12-1)</f>
+        <f>IF(OR(H51="",NOT(ISNUMBER(Config!$B$12))),"",H51/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J51" s="33">
-        <f>IF(H51="","",IF(H51&lt;Config!$B$12,"Abaixo do mínimo",IF(H51&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H51="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H51&lt;Config!$B$12,"Abaixo do mínimo",IF(H51&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K51" s="25">
-        <f>IF(H51="","",MAX(0,Config!$B$12*G51-F51))</f>
+        <f>IF(OR(H51="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G51-F51))</f>
         <v/>
       </c>
       <c r="L51" s="41">
@@ -6373,15 +6387,15 @@
         <v/>
       </c>
       <c r="I52" s="31">
-        <f>IF(H52="","",H52/Config!$B$12-1)</f>
+        <f>IF(OR(H52="",NOT(ISNUMBER(Config!$B$12))),"",H52/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J52" s="33">
-        <f>IF(H52="","",IF(H52&lt;Config!$B$12,"Abaixo do mínimo",IF(H52&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H52="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H52&lt;Config!$B$12,"Abaixo do mínimo",IF(H52&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K52" s="25">
-        <f>IF(H52="","",MAX(0,Config!$B$12*G52-F52))</f>
+        <f>IF(OR(H52="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G52-F52))</f>
         <v/>
       </c>
       <c r="L52" s="41">
@@ -6402,15 +6416,15 @@
         <v/>
       </c>
       <c r="I53" s="31">
-        <f>IF(H53="","",H53/Config!$B$12-1)</f>
+        <f>IF(OR(H53="",NOT(ISNUMBER(Config!$B$12))),"",H53/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J53" s="33">
-        <f>IF(H53="","",IF(H53&lt;Config!$B$12,"Abaixo do mínimo",IF(H53&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H53="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H53&lt;Config!$B$12,"Abaixo do mínimo",IF(H53&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K53" s="25">
-        <f>IF(H53="","",MAX(0,Config!$B$12*G53-F53))</f>
+        <f>IF(OR(H53="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G53-F53))</f>
         <v/>
       </c>
       <c r="L53" s="41">
@@ -6431,15 +6445,15 @@
         <v/>
       </c>
       <c r="I54" s="31">
-        <f>IF(H54="","",H54/Config!$B$12-1)</f>
+        <f>IF(OR(H54="",NOT(ISNUMBER(Config!$B$12))),"",H54/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J54" s="33">
-        <f>IF(H54="","",IF(H54&lt;Config!$B$12,"Abaixo do mínimo",IF(H54&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H54="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H54&lt;Config!$B$12,"Abaixo do mínimo",IF(H54&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K54" s="25">
-        <f>IF(H54="","",MAX(0,Config!$B$12*G54-F54))</f>
+        <f>IF(OR(H54="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G54-F54))</f>
         <v/>
       </c>
       <c r="L54" s="41">
@@ -6460,15 +6474,15 @@
         <v/>
       </c>
       <c r="I55" s="31">
-        <f>IF(H55="","",H55/Config!$B$12-1)</f>
+        <f>IF(OR(H55="",NOT(ISNUMBER(Config!$B$12))),"",H55/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J55" s="33">
-        <f>IF(H55="","",IF(H55&lt;Config!$B$12,"Abaixo do mínimo",IF(H55&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H55="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H55&lt;Config!$B$12,"Abaixo do mínimo",IF(H55&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K55" s="25">
-        <f>IF(H55="","",MAX(0,Config!$B$12*G55-F55))</f>
+        <f>IF(OR(H55="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G55-F55))</f>
         <v/>
       </c>
       <c r="L55" s="41">
@@ -6489,15 +6503,15 @@
         <v/>
       </c>
       <c r="I56" s="31">
-        <f>IF(H56="","",H56/Config!$B$12-1)</f>
+        <f>IF(OR(H56="",NOT(ISNUMBER(Config!$B$12))),"",H56/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J56" s="33">
-        <f>IF(H56="","",IF(H56&lt;Config!$B$12,"Abaixo do mínimo",IF(H56&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H56="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H56&lt;Config!$B$12,"Abaixo do mínimo",IF(H56&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K56" s="25">
-        <f>IF(H56="","",MAX(0,Config!$B$12*G56-F56))</f>
+        <f>IF(OR(H56="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G56-F56))</f>
         <v/>
       </c>
       <c r="L56" s="41">
@@ -6518,15 +6532,15 @@
         <v/>
       </c>
       <c r="I57" s="31">
-        <f>IF(H57="","",H57/Config!$B$12-1)</f>
+        <f>IF(OR(H57="",NOT(ISNUMBER(Config!$B$12))),"",H57/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J57" s="33">
-        <f>IF(H57="","",IF(H57&lt;Config!$B$12,"Abaixo do mínimo",IF(H57&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H57="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H57&lt;Config!$B$12,"Abaixo do mínimo",IF(H57&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K57" s="25">
-        <f>IF(H57="","",MAX(0,Config!$B$12*G57-F57))</f>
+        <f>IF(OR(H57="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G57-F57))</f>
         <v/>
       </c>
       <c r="L57" s="41">
@@ -6547,15 +6561,15 @@
         <v/>
       </c>
       <c r="I58" s="31">
-        <f>IF(H58="","",H58/Config!$B$12-1)</f>
+        <f>IF(OR(H58="",NOT(ISNUMBER(Config!$B$12))),"",H58/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J58" s="33">
-        <f>IF(H58="","",IF(H58&lt;Config!$B$12,"Abaixo do mínimo",IF(H58&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H58="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H58&lt;Config!$B$12,"Abaixo do mínimo",IF(H58&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K58" s="25">
-        <f>IF(H58="","",MAX(0,Config!$B$12*G58-F58))</f>
+        <f>IF(OR(H58="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G58-F58))</f>
         <v/>
       </c>
       <c r="L58" s="41">
@@ -6576,15 +6590,15 @@
         <v/>
       </c>
       <c r="I59" s="31">
-        <f>IF(H59="","",H59/Config!$B$12-1)</f>
+        <f>IF(OR(H59="",NOT(ISNUMBER(Config!$B$12))),"",H59/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J59" s="33">
-        <f>IF(H59="","",IF(H59&lt;Config!$B$12,"Abaixo do mínimo",IF(H59&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H59="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H59&lt;Config!$B$12,"Abaixo do mínimo",IF(H59&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K59" s="25">
-        <f>IF(H59="","",MAX(0,Config!$B$12*G59-F59))</f>
+        <f>IF(OR(H59="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G59-F59))</f>
         <v/>
       </c>
       <c r="L59" s="41">
@@ -6605,15 +6619,15 @@
         <v/>
       </c>
       <c r="I60" s="31">
-        <f>IF(H60="","",H60/Config!$B$12-1)</f>
+        <f>IF(OR(H60="",NOT(ISNUMBER(Config!$B$12))),"",H60/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J60" s="33">
-        <f>IF(H60="","",IF(H60&lt;Config!$B$12,"Abaixo do mínimo",IF(H60&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H60="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H60&lt;Config!$B$12,"Abaixo do mínimo",IF(H60&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K60" s="25">
-        <f>IF(H60="","",MAX(0,Config!$B$12*G60-F60))</f>
+        <f>IF(OR(H60="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G60-F60))</f>
         <v/>
       </c>
       <c r="L60" s="41">
@@ -6634,15 +6648,15 @@
         <v/>
       </c>
       <c r="I61" s="31">
-        <f>IF(H61="","",H61/Config!$B$12-1)</f>
+        <f>IF(OR(H61="",NOT(ISNUMBER(Config!$B$12))),"",H61/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J61" s="33">
-        <f>IF(H61="","",IF(H61&lt;Config!$B$12,"Abaixo do mínimo",IF(H61&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H61="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H61&lt;Config!$B$12,"Abaixo do mínimo",IF(H61&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K61" s="25">
-        <f>IF(H61="","",MAX(0,Config!$B$12*G61-F61))</f>
+        <f>IF(OR(H61="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G61-F61))</f>
         <v/>
       </c>
       <c r="L61" s="41">
@@ -6663,15 +6677,15 @@
         <v/>
       </c>
       <c r="I62" s="31">
-        <f>IF(H62="","",H62/Config!$B$12-1)</f>
+        <f>IF(OR(H62="",NOT(ISNUMBER(Config!$B$12))),"",H62/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J62" s="33">
-        <f>IF(H62="","",IF(H62&lt;Config!$B$12,"Abaixo do mínimo",IF(H62&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H62="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H62&lt;Config!$B$12,"Abaixo do mínimo",IF(H62&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K62" s="25">
-        <f>IF(H62="","",MAX(0,Config!$B$12*G62-F62))</f>
+        <f>IF(OR(H62="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G62-F62))</f>
         <v/>
       </c>
       <c r="L62" s="41">
@@ -6692,15 +6706,15 @@
         <v/>
       </c>
       <c r="I63" s="31">
-        <f>IF(H63="","",H63/Config!$B$12-1)</f>
+        <f>IF(OR(H63="",NOT(ISNUMBER(Config!$B$12))),"",H63/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J63" s="33">
-        <f>IF(H63="","",IF(H63&lt;Config!$B$12,"Abaixo do mínimo",IF(H63&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H63="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H63&lt;Config!$B$12,"Abaixo do mínimo",IF(H63&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K63" s="25">
-        <f>IF(H63="","",MAX(0,Config!$B$12*G63-F63))</f>
+        <f>IF(OR(H63="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G63-F63))</f>
         <v/>
       </c>
       <c r="L63" s="41">
@@ -6721,15 +6735,15 @@
         <v/>
       </c>
       <c r="I64" s="31">
-        <f>IF(H64="","",H64/Config!$B$12-1)</f>
+        <f>IF(OR(H64="",NOT(ISNUMBER(Config!$B$12))),"",H64/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J64" s="33">
-        <f>IF(H64="","",IF(H64&lt;Config!$B$12,"Abaixo do mínimo",IF(H64&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H64="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H64&lt;Config!$B$12,"Abaixo do mínimo",IF(H64&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K64" s="25">
-        <f>IF(H64="","",MAX(0,Config!$B$12*G64-F64))</f>
+        <f>IF(OR(H64="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G64-F64))</f>
         <v/>
       </c>
       <c r="L64" s="41">
@@ -6750,15 +6764,15 @@
         <v/>
       </c>
       <c r="I65" s="31">
-        <f>IF(H65="","",H65/Config!$B$12-1)</f>
+        <f>IF(OR(H65="",NOT(ISNUMBER(Config!$B$12))),"",H65/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J65" s="33">
-        <f>IF(H65="","",IF(H65&lt;Config!$B$12,"Abaixo do mínimo",IF(H65&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H65="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H65&lt;Config!$B$12,"Abaixo do mínimo",IF(H65&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K65" s="25">
-        <f>IF(H65="","",MAX(0,Config!$B$12*G65-F65))</f>
+        <f>IF(OR(H65="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G65-F65))</f>
         <v/>
       </c>
       <c r="L65" s="41">
@@ -6779,15 +6793,15 @@
         <v/>
       </c>
       <c r="I66" s="31">
-        <f>IF(H66="","",H66/Config!$B$12-1)</f>
+        <f>IF(OR(H66="",NOT(ISNUMBER(Config!$B$12))),"",H66/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J66" s="33">
-        <f>IF(H66="","",IF(H66&lt;Config!$B$12,"Abaixo do mínimo",IF(H66&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H66="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H66&lt;Config!$B$12,"Abaixo do mínimo",IF(H66&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K66" s="25">
-        <f>IF(H66="","",MAX(0,Config!$B$12*G66-F66))</f>
+        <f>IF(OR(H66="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G66-F66))</f>
         <v/>
       </c>
       <c r="L66" s="41">
@@ -6808,15 +6822,15 @@
         <v/>
       </c>
       <c r="I67" s="31">
-        <f>IF(H67="","",H67/Config!$B$12-1)</f>
+        <f>IF(OR(H67="",NOT(ISNUMBER(Config!$B$12))),"",H67/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J67" s="33">
-        <f>IF(H67="","",IF(H67&lt;Config!$B$12,"Abaixo do mínimo",IF(H67&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H67="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H67&lt;Config!$B$12,"Abaixo do mínimo",IF(H67&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K67" s="25">
-        <f>IF(H67="","",MAX(0,Config!$B$12*G67-F67))</f>
+        <f>IF(OR(H67="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G67-F67))</f>
         <v/>
       </c>
       <c r="L67" s="41">
@@ -6837,15 +6851,15 @@
         <v/>
       </c>
       <c r="I68" s="31">
-        <f>IF(H68="","",H68/Config!$B$12-1)</f>
+        <f>IF(OR(H68="",NOT(ISNUMBER(Config!$B$12))),"",H68/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J68" s="33">
-        <f>IF(H68="","",IF(H68&lt;Config!$B$12,"Abaixo do mínimo",IF(H68&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H68="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H68&lt;Config!$B$12,"Abaixo do mínimo",IF(H68&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K68" s="25">
-        <f>IF(H68="","",MAX(0,Config!$B$12*G68-F68))</f>
+        <f>IF(OR(H68="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G68-F68))</f>
         <v/>
       </c>
       <c r="L68" s="41">
@@ -6866,15 +6880,15 @@
         <v/>
       </c>
       <c r="I69" s="31">
-        <f>IF(H69="","",H69/Config!$B$12-1)</f>
+        <f>IF(OR(H69="",NOT(ISNUMBER(Config!$B$12))),"",H69/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J69" s="33">
-        <f>IF(H69="","",IF(H69&lt;Config!$B$12,"Abaixo do mínimo",IF(H69&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H69="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H69&lt;Config!$B$12,"Abaixo do mínimo",IF(H69&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K69" s="25">
-        <f>IF(H69="","",MAX(0,Config!$B$12*G69-F69))</f>
+        <f>IF(OR(H69="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G69-F69))</f>
         <v/>
       </c>
       <c r="L69" s="41">
@@ -6895,15 +6909,15 @@
         <v/>
       </c>
       <c r="I70" s="31">
-        <f>IF(H70="","",H70/Config!$B$12-1)</f>
+        <f>IF(OR(H70="",NOT(ISNUMBER(Config!$B$12))),"",H70/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J70" s="33">
-        <f>IF(H70="","",IF(H70&lt;Config!$B$12,"Abaixo do mínimo",IF(H70&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H70="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H70&lt;Config!$B$12,"Abaixo do mínimo",IF(H70&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K70" s="25">
-        <f>IF(H70="","",MAX(0,Config!$B$12*G70-F70))</f>
+        <f>IF(OR(H70="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G70-F70))</f>
         <v/>
       </c>
       <c r="L70" s="41">
@@ -6924,15 +6938,15 @@
         <v/>
       </c>
       <c r="I71" s="31">
-        <f>IF(H71="","",H71/Config!$B$12-1)</f>
+        <f>IF(OR(H71="",NOT(ISNUMBER(Config!$B$12))),"",H71/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J71" s="33">
-        <f>IF(H71="","",IF(H71&lt;Config!$B$12,"Abaixo do mínimo",IF(H71&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H71="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H71&lt;Config!$B$12,"Abaixo do mínimo",IF(H71&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K71" s="25">
-        <f>IF(H71="","",MAX(0,Config!$B$12*G71-F71))</f>
+        <f>IF(OR(H71="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G71-F71))</f>
         <v/>
       </c>
       <c r="L71" s="41">
@@ -6953,15 +6967,15 @@
         <v/>
       </c>
       <c r="I72" s="31">
-        <f>IF(H72="","",H72/Config!$B$12-1)</f>
+        <f>IF(OR(H72="",NOT(ISNUMBER(Config!$B$12))),"",H72/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J72" s="33">
-        <f>IF(H72="","",IF(H72&lt;Config!$B$12,"Abaixo do mínimo",IF(H72&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H72="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H72&lt;Config!$B$12,"Abaixo do mínimo",IF(H72&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K72" s="25">
-        <f>IF(H72="","",MAX(0,Config!$B$12*G72-F72))</f>
+        <f>IF(OR(H72="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G72-F72))</f>
         <v/>
       </c>
       <c r="L72" s="41">
@@ -6982,15 +6996,15 @@
         <v/>
       </c>
       <c r="I73" s="31">
-        <f>IF(H73="","",H73/Config!$B$12-1)</f>
+        <f>IF(OR(H73="",NOT(ISNUMBER(Config!$B$12))),"",H73/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J73" s="33">
-        <f>IF(H73="","",IF(H73&lt;Config!$B$12,"Abaixo do mínimo",IF(H73&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H73="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H73&lt;Config!$B$12,"Abaixo do mínimo",IF(H73&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K73" s="25">
-        <f>IF(H73="","",MAX(0,Config!$B$12*G73-F73))</f>
+        <f>IF(OR(H73="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G73-F73))</f>
         <v/>
       </c>
       <c r="L73" s="41">
@@ -7011,15 +7025,15 @@
         <v/>
       </c>
       <c r="I74" s="31">
-        <f>IF(H74="","",H74/Config!$B$12-1)</f>
+        <f>IF(OR(H74="",NOT(ISNUMBER(Config!$B$12))),"",H74/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J74" s="33">
-        <f>IF(H74="","",IF(H74&lt;Config!$B$12,"Abaixo do mínimo",IF(H74&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H74="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H74&lt;Config!$B$12,"Abaixo do mínimo",IF(H74&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K74" s="25">
-        <f>IF(H74="","",MAX(0,Config!$B$12*G74-F74))</f>
+        <f>IF(OR(H74="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G74-F74))</f>
         <v/>
       </c>
       <c r="L74" s="41">
@@ -7040,15 +7054,15 @@
         <v/>
       </c>
       <c r="I75" s="31">
-        <f>IF(H75="","",H75/Config!$B$12-1)</f>
+        <f>IF(OR(H75="",NOT(ISNUMBER(Config!$B$12))),"",H75/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J75" s="33">
-        <f>IF(H75="","",IF(H75&lt;Config!$B$12,"Abaixo do mínimo",IF(H75&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H75="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H75&lt;Config!$B$12,"Abaixo do mínimo",IF(H75&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K75" s="25">
-        <f>IF(H75="","",MAX(0,Config!$B$12*G75-F75))</f>
+        <f>IF(OR(H75="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G75-F75))</f>
         <v/>
       </c>
       <c r="L75" s="41">
@@ -7069,15 +7083,15 @@
         <v/>
       </c>
       <c r="I76" s="31">
-        <f>IF(H76="","",H76/Config!$B$12-1)</f>
+        <f>IF(OR(H76="",NOT(ISNUMBER(Config!$B$12))),"",H76/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J76" s="33">
-        <f>IF(H76="","",IF(H76&lt;Config!$B$12,"Abaixo do mínimo",IF(H76&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H76="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H76&lt;Config!$B$12,"Abaixo do mínimo",IF(H76&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K76" s="25">
-        <f>IF(H76="","",MAX(0,Config!$B$12*G76-F76))</f>
+        <f>IF(OR(H76="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G76-F76))</f>
         <v/>
       </c>
       <c r="L76" s="41">
@@ -7098,15 +7112,15 @@
         <v/>
       </c>
       <c r="I77" s="31">
-        <f>IF(H77="","",H77/Config!$B$12-1)</f>
+        <f>IF(OR(H77="",NOT(ISNUMBER(Config!$B$12))),"",H77/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J77" s="33">
-        <f>IF(H77="","",IF(H77&lt;Config!$B$12,"Abaixo do mínimo",IF(H77&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H77="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H77&lt;Config!$B$12,"Abaixo do mínimo",IF(H77&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K77" s="25">
-        <f>IF(H77="","",MAX(0,Config!$B$12*G77-F77))</f>
+        <f>IF(OR(H77="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G77-F77))</f>
         <v/>
       </c>
       <c r="L77" s="41">
@@ -7127,15 +7141,15 @@
         <v/>
       </c>
       <c r="I78" s="31">
-        <f>IF(H78="","",H78/Config!$B$12-1)</f>
+        <f>IF(OR(H78="",NOT(ISNUMBER(Config!$B$12))),"",H78/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J78" s="33">
-        <f>IF(H78="","",IF(H78&lt;Config!$B$12,"Abaixo do mínimo",IF(H78&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H78="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H78&lt;Config!$B$12,"Abaixo do mínimo",IF(H78&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K78" s="25">
-        <f>IF(H78="","",MAX(0,Config!$B$12*G78-F78))</f>
+        <f>IF(OR(H78="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G78-F78))</f>
         <v/>
       </c>
       <c r="L78" s="41">
@@ -7156,15 +7170,15 @@
         <v/>
       </c>
       <c r="I79" s="31">
-        <f>IF(H79="","",H79/Config!$B$12-1)</f>
+        <f>IF(OR(H79="",NOT(ISNUMBER(Config!$B$12))),"",H79/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J79" s="33">
-        <f>IF(H79="","",IF(H79&lt;Config!$B$12,"Abaixo do mínimo",IF(H79&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H79="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H79&lt;Config!$B$12,"Abaixo do mínimo",IF(H79&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K79" s="25">
-        <f>IF(H79="","",MAX(0,Config!$B$12*G79-F79))</f>
+        <f>IF(OR(H79="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G79-F79))</f>
         <v/>
       </c>
       <c r="L79" s="41">
@@ -7185,15 +7199,15 @@
         <v/>
       </c>
       <c r="I80" s="31">
-        <f>IF(H80="","",H80/Config!$B$12-1)</f>
+        <f>IF(OR(H80="",NOT(ISNUMBER(Config!$B$12))),"",H80/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J80" s="33">
-        <f>IF(H80="","",IF(H80&lt;Config!$B$12,"Abaixo do mínimo",IF(H80&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H80="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H80&lt;Config!$B$12,"Abaixo do mínimo",IF(H80&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K80" s="25">
-        <f>IF(H80="","",MAX(0,Config!$B$12*G80-F80))</f>
+        <f>IF(OR(H80="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G80-F80))</f>
         <v/>
       </c>
       <c r="L80" s="41">
@@ -7214,15 +7228,15 @@
         <v/>
       </c>
       <c r="I81" s="31">
-        <f>IF(H81="","",H81/Config!$B$12-1)</f>
+        <f>IF(OR(H81="",NOT(ISNUMBER(Config!$B$12))),"",H81/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J81" s="33">
-        <f>IF(H81="","",IF(H81&lt;Config!$B$12,"Abaixo do mínimo",IF(H81&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H81="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H81&lt;Config!$B$12,"Abaixo do mínimo",IF(H81&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K81" s="25">
-        <f>IF(H81="","",MAX(0,Config!$B$12*G81-F81))</f>
+        <f>IF(OR(H81="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G81-F81))</f>
         <v/>
       </c>
       <c r="L81" s="41">
@@ -7243,15 +7257,15 @@
         <v/>
       </c>
       <c r="I82" s="31">
-        <f>IF(H82="","",H82/Config!$B$12-1)</f>
+        <f>IF(OR(H82="",NOT(ISNUMBER(Config!$B$12))),"",H82/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J82" s="33">
-        <f>IF(H82="","",IF(H82&lt;Config!$B$12,"Abaixo do mínimo",IF(H82&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H82="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H82&lt;Config!$B$12,"Abaixo do mínimo",IF(H82&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K82" s="25">
-        <f>IF(H82="","",MAX(0,Config!$B$12*G82-F82))</f>
+        <f>IF(OR(H82="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G82-F82))</f>
         <v/>
       </c>
       <c r="L82" s="41">
@@ -7272,15 +7286,15 @@
         <v/>
       </c>
       <c r="I83" s="31">
-        <f>IF(H83="","",H83/Config!$B$12-1)</f>
+        <f>IF(OR(H83="",NOT(ISNUMBER(Config!$B$12))),"",H83/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J83" s="33">
-        <f>IF(H83="","",IF(H83&lt;Config!$B$12,"Abaixo do mínimo",IF(H83&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H83="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H83&lt;Config!$B$12,"Abaixo do mínimo",IF(H83&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K83" s="25">
-        <f>IF(H83="","",MAX(0,Config!$B$12*G83-F83))</f>
+        <f>IF(OR(H83="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G83-F83))</f>
         <v/>
       </c>
       <c r="L83" s="41">
@@ -7301,15 +7315,15 @@
         <v/>
       </c>
       <c r="I84" s="31">
-        <f>IF(H84="","",H84/Config!$B$12-1)</f>
+        <f>IF(OR(H84="",NOT(ISNUMBER(Config!$B$12))),"",H84/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J84" s="33">
-        <f>IF(H84="","",IF(H84&lt;Config!$B$12,"Abaixo do mínimo",IF(H84&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H84="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H84&lt;Config!$B$12,"Abaixo do mínimo",IF(H84&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K84" s="25">
-        <f>IF(H84="","",MAX(0,Config!$B$12*G84-F84))</f>
+        <f>IF(OR(H84="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G84-F84))</f>
         <v/>
       </c>
       <c r="L84" s="41">
@@ -7330,15 +7344,15 @@
         <v/>
       </c>
       <c r="I85" s="31">
-        <f>IF(H85="","",H85/Config!$B$12-1)</f>
+        <f>IF(OR(H85="",NOT(ISNUMBER(Config!$B$12))),"",H85/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J85" s="33">
-        <f>IF(H85="","",IF(H85&lt;Config!$B$12,"Abaixo do mínimo",IF(H85&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H85="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H85&lt;Config!$B$12,"Abaixo do mínimo",IF(H85&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K85" s="25">
-        <f>IF(H85="","",MAX(0,Config!$B$12*G85-F85))</f>
+        <f>IF(OR(H85="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G85-F85))</f>
         <v/>
       </c>
       <c r="L85" s="41">
@@ -7359,15 +7373,15 @@
         <v/>
       </c>
       <c r="I86" s="31">
-        <f>IF(H86="","",H86/Config!$B$12-1)</f>
+        <f>IF(OR(H86="",NOT(ISNUMBER(Config!$B$12))),"",H86/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J86" s="33">
-        <f>IF(H86="","",IF(H86&lt;Config!$B$12,"Abaixo do mínimo",IF(H86&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H86="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H86&lt;Config!$B$12,"Abaixo do mínimo",IF(H86&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K86" s="25">
-        <f>IF(H86="","",MAX(0,Config!$B$12*G86-F86))</f>
+        <f>IF(OR(H86="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G86-F86))</f>
         <v/>
       </c>
       <c r="L86" s="41">
@@ -7388,15 +7402,15 @@
         <v/>
       </c>
       <c r="I87" s="31">
-        <f>IF(H87="","",H87/Config!$B$12-1)</f>
+        <f>IF(OR(H87="",NOT(ISNUMBER(Config!$B$12))),"",H87/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J87" s="33">
-        <f>IF(H87="","",IF(H87&lt;Config!$B$12,"Abaixo do mínimo",IF(H87&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H87="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H87&lt;Config!$B$12,"Abaixo do mínimo",IF(H87&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K87" s="25">
-        <f>IF(H87="","",MAX(0,Config!$B$12*G87-F87))</f>
+        <f>IF(OR(H87="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G87-F87))</f>
         <v/>
       </c>
       <c r="L87" s="41">
@@ -7417,15 +7431,15 @@
         <v/>
       </c>
       <c r="I88" s="31">
-        <f>IF(H88="","",H88/Config!$B$12-1)</f>
+        <f>IF(OR(H88="",NOT(ISNUMBER(Config!$B$12))),"",H88/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J88" s="33">
-        <f>IF(H88="","",IF(H88&lt;Config!$B$12,"Abaixo do mínimo",IF(H88&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H88="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H88&lt;Config!$B$12,"Abaixo do mínimo",IF(H88&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K88" s="25">
-        <f>IF(H88="","",MAX(0,Config!$B$12*G88-F88))</f>
+        <f>IF(OR(H88="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G88-F88))</f>
         <v/>
       </c>
       <c r="L88" s="41">
@@ -7446,15 +7460,15 @@
         <v/>
       </c>
       <c r="I89" s="31">
-        <f>IF(H89="","",H89/Config!$B$12-1)</f>
+        <f>IF(OR(H89="",NOT(ISNUMBER(Config!$B$12))),"",H89/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J89" s="33">
-        <f>IF(H89="","",IF(H89&lt;Config!$B$12,"Abaixo do mínimo",IF(H89&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H89="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H89&lt;Config!$B$12,"Abaixo do mínimo",IF(H89&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K89" s="25">
-        <f>IF(H89="","",MAX(0,Config!$B$12*G89-F89))</f>
+        <f>IF(OR(H89="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G89-F89))</f>
         <v/>
       </c>
       <c r="L89" s="41">
@@ -7475,15 +7489,15 @@
         <v/>
       </c>
       <c r="I90" s="31">
-        <f>IF(H90="","",H90/Config!$B$12-1)</f>
+        <f>IF(OR(H90="",NOT(ISNUMBER(Config!$B$12))),"",H90/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J90" s="33">
-        <f>IF(H90="","",IF(H90&lt;Config!$B$12,"Abaixo do mínimo",IF(H90&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H90="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H90&lt;Config!$B$12,"Abaixo do mínimo",IF(H90&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K90" s="25">
-        <f>IF(H90="","",MAX(0,Config!$B$12*G90-F90))</f>
+        <f>IF(OR(H90="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G90-F90))</f>
         <v/>
       </c>
       <c r="L90" s="41">
@@ -7504,15 +7518,15 @@
         <v/>
       </c>
       <c r="I91" s="31">
-        <f>IF(H91="","",H91/Config!$B$12-1)</f>
+        <f>IF(OR(H91="",NOT(ISNUMBER(Config!$B$12))),"",H91/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J91" s="33">
-        <f>IF(H91="","",IF(H91&lt;Config!$B$12,"Abaixo do mínimo",IF(H91&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H91="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H91&lt;Config!$B$12,"Abaixo do mínimo",IF(H91&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K91" s="25">
-        <f>IF(H91="","",MAX(0,Config!$B$12*G91-F91))</f>
+        <f>IF(OR(H91="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G91-F91))</f>
         <v/>
       </c>
       <c r="L91" s="41">
@@ -7533,15 +7547,15 @@
         <v/>
       </c>
       <c r="I92" s="31">
-        <f>IF(H92="","",H92/Config!$B$12-1)</f>
+        <f>IF(OR(H92="",NOT(ISNUMBER(Config!$B$12))),"",H92/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J92" s="33">
-        <f>IF(H92="","",IF(H92&lt;Config!$B$12,"Abaixo do mínimo",IF(H92&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H92="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H92&lt;Config!$B$12,"Abaixo do mínimo",IF(H92&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K92" s="25">
-        <f>IF(H92="","",MAX(0,Config!$B$12*G92-F92))</f>
+        <f>IF(OR(H92="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G92-F92))</f>
         <v/>
       </c>
       <c r="L92" s="41">
@@ -7562,15 +7576,15 @@
         <v/>
       </c>
       <c r="I93" s="31">
-        <f>IF(H93="","",H93/Config!$B$12-1)</f>
+        <f>IF(OR(H93="",NOT(ISNUMBER(Config!$B$12))),"",H93/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J93" s="33">
-        <f>IF(H93="","",IF(H93&lt;Config!$B$12,"Abaixo do mínimo",IF(H93&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H93="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H93&lt;Config!$B$12,"Abaixo do mínimo",IF(H93&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K93" s="25">
-        <f>IF(H93="","",MAX(0,Config!$B$12*G93-F93))</f>
+        <f>IF(OR(H93="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G93-F93))</f>
         <v/>
       </c>
       <c r="L93" s="41">
@@ -7591,15 +7605,15 @@
         <v/>
       </c>
       <c r="I94" s="31">
-        <f>IF(H94="","",H94/Config!$B$12-1)</f>
+        <f>IF(OR(H94="",NOT(ISNUMBER(Config!$B$12))),"",H94/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J94" s="33">
-        <f>IF(H94="","",IF(H94&lt;Config!$B$12,"Abaixo do mínimo",IF(H94&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H94="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H94&lt;Config!$B$12,"Abaixo do mínimo",IF(H94&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K94" s="25">
-        <f>IF(H94="","",MAX(0,Config!$B$12*G94-F94))</f>
+        <f>IF(OR(H94="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G94-F94))</f>
         <v/>
       </c>
       <c r="L94" s="41">
@@ -7620,15 +7634,15 @@
         <v/>
       </c>
       <c r="I95" s="31">
-        <f>IF(H95="","",H95/Config!$B$12-1)</f>
+        <f>IF(OR(H95="",NOT(ISNUMBER(Config!$B$12))),"",H95/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J95" s="33">
-        <f>IF(H95="","",IF(H95&lt;Config!$B$12,"Abaixo do mínimo",IF(H95&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H95="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H95&lt;Config!$B$12,"Abaixo do mínimo",IF(H95&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K95" s="25">
-        <f>IF(H95="","",MAX(0,Config!$B$12*G95-F95))</f>
+        <f>IF(OR(H95="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G95-F95))</f>
         <v/>
       </c>
       <c r="L95" s="41">
@@ -7649,15 +7663,15 @@
         <v/>
       </c>
       <c r="I96" s="31">
-        <f>IF(H96="","",H96/Config!$B$12-1)</f>
+        <f>IF(OR(H96="",NOT(ISNUMBER(Config!$B$12))),"",H96/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J96" s="33">
-        <f>IF(H96="","",IF(H96&lt;Config!$B$12,"Abaixo do mínimo",IF(H96&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H96="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H96&lt;Config!$B$12,"Abaixo do mínimo",IF(H96&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K96" s="25">
-        <f>IF(H96="","",MAX(0,Config!$B$12*G96-F96))</f>
+        <f>IF(OR(H96="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G96-F96))</f>
         <v/>
       </c>
       <c r="L96" s="41">
@@ -7678,15 +7692,15 @@
         <v/>
       </c>
       <c r="I97" s="31">
-        <f>IF(H97="","",H97/Config!$B$12-1)</f>
+        <f>IF(OR(H97="",NOT(ISNUMBER(Config!$B$12))),"",H97/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J97" s="33">
-        <f>IF(H97="","",IF(H97&lt;Config!$B$12,"Abaixo do mínimo",IF(H97&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H97="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H97&lt;Config!$B$12,"Abaixo do mínimo",IF(H97&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K97" s="25">
-        <f>IF(H97="","",MAX(0,Config!$B$12*G97-F97))</f>
+        <f>IF(OR(H97="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G97-F97))</f>
         <v/>
       </c>
       <c r="L97" s="41">
@@ -7707,15 +7721,15 @@
         <v/>
       </c>
       <c r="I98" s="31">
-        <f>IF(H98="","",H98/Config!$B$12-1)</f>
+        <f>IF(OR(H98="",NOT(ISNUMBER(Config!$B$12))),"",H98/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J98" s="33">
-        <f>IF(H98="","",IF(H98&lt;Config!$B$12,"Abaixo do mínimo",IF(H98&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H98="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H98&lt;Config!$B$12,"Abaixo do mínimo",IF(H98&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K98" s="25">
-        <f>IF(H98="","",MAX(0,Config!$B$12*G98-F98))</f>
+        <f>IF(OR(H98="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G98-F98))</f>
         <v/>
       </c>
       <c r="L98" s="41">
@@ -7736,15 +7750,15 @@
         <v/>
       </c>
       <c r="I99" s="31">
-        <f>IF(H99="","",H99/Config!$B$12-1)</f>
+        <f>IF(OR(H99="",NOT(ISNUMBER(Config!$B$12))),"",H99/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J99" s="33">
-        <f>IF(H99="","",IF(H99&lt;Config!$B$12,"Abaixo do mínimo",IF(H99&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H99="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H99&lt;Config!$B$12,"Abaixo do mínimo",IF(H99&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K99" s="25">
-        <f>IF(H99="","",MAX(0,Config!$B$12*G99-F99))</f>
+        <f>IF(OR(H99="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G99-F99))</f>
         <v/>
       </c>
       <c r="L99" s="41">
@@ -7765,15 +7779,15 @@
         <v/>
       </c>
       <c r="I100" s="31">
-        <f>IF(H100="","",H100/Config!$B$12-1)</f>
+        <f>IF(OR(H100="",NOT(ISNUMBER(Config!$B$12))),"",H100/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J100" s="33">
-        <f>IF(H100="","",IF(H100&lt;Config!$B$12,"Abaixo do mínimo",IF(H100&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H100="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H100&lt;Config!$B$12,"Abaixo do mínimo",IF(H100&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K100" s="25">
-        <f>IF(H100="","",MAX(0,Config!$B$12*G100-F100))</f>
+        <f>IF(OR(H100="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G100-F100))</f>
         <v/>
       </c>
       <c r="L100" s="41">
@@ -7794,15 +7808,15 @@
         <v/>
       </c>
       <c r="I101" s="31">
-        <f>IF(H101="","",H101/Config!$B$12-1)</f>
+        <f>IF(OR(H101="",NOT(ISNUMBER(Config!$B$12))),"",H101/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J101" s="33">
-        <f>IF(H101="","",IF(H101&lt;Config!$B$12,"Abaixo do mínimo",IF(H101&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H101="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H101&lt;Config!$B$12,"Abaixo do mínimo",IF(H101&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K101" s="25">
-        <f>IF(H101="","",MAX(0,Config!$B$12*G101-F101))</f>
+        <f>IF(OR(H101="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G101-F101))</f>
         <v/>
       </c>
       <c r="L101" s="41">
@@ -7823,15 +7837,15 @@
         <v/>
       </c>
       <c r="I102" s="31">
-        <f>IF(H102="","",H102/Config!$B$12-1)</f>
+        <f>IF(OR(H102="",NOT(ISNUMBER(Config!$B$12))),"",H102/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J102" s="33">
-        <f>IF(H102="","",IF(H102&lt;Config!$B$12,"Abaixo do mínimo",IF(H102&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H102="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H102&lt;Config!$B$12,"Abaixo do mínimo",IF(H102&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K102" s="25">
-        <f>IF(H102="","",MAX(0,Config!$B$12*G102-F102))</f>
+        <f>IF(OR(H102="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G102-F102))</f>
         <v/>
       </c>
       <c r="L102" s="41">
@@ -7852,15 +7866,15 @@
         <v/>
       </c>
       <c r="I103" s="31">
-        <f>IF(H103="","",H103/Config!$B$12-1)</f>
+        <f>IF(OR(H103="",NOT(ISNUMBER(Config!$B$12))),"",H103/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J103" s="33">
-        <f>IF(H103="","",IF(H103&lt;Config!$B$12,"Abaixo do mínimo",IF(H103&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H103="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H103&lt;Config!$B$12,"Abaixo do mínimo",IF(H103&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K103" s="25">
-        <f>IF(H103="","",MAX(0,Config!$B$12*G103-F103))</f>
+        <f>IF(OR(H103="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G103-F103))</f>
         <v/>
       </c>
       <c r="L103" s="41">
@@ -7881,15 +7895,15 @@
         <v/>
       </c>
       <c r="I104" s="31">
-        <f>IF(H104="","",H104/Config!$B$12-1)</f>
+        <f>IF(OR(H104="",NOT(ISNUMBER(Config!$B$12))),"",H104/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J104" s="33">
-        <f>IF(H104="","",IF(H104&lt;Config!$B$12,"Abaixo do mínimo",IF(H104&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H104="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H104&lt;Config!$B$12,"Abaixo do mínimo",IF(H104&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K104" s="25">
-        <f>IF(H104="","",MAX(0,Config!$B$12*G104-F104))</f>
+        <f>IF(OR(H104="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G104-F104))</f>
         <v/>
       </c>
       <c r="L104" s="41">
@@ -7910,15 +7924,15 @@
         <v/>
       </c>
       <c r="I105" s="31">
-        <f>IF(H105="","",H105/Config!$B$12-1)</f>
+        <f>IF(OR(H105="",NOT(ISNUMBER(Config!$B$12))),"",H105/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J105" s="33">
-        <f>IF(H105="","",IF(H105&lt;Config!$B$12,"Abaixo do mínimo",IF(H105&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H105="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H105&lt;Config!$B$12,"Abaixo do mínimo",IF(H105&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K105" s="25">
-        <f>IF(H105="","",MAX(0,Config!$B$12*G105-F105))</f>
+        <f>IF(OR(H105="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G105-F105))</f>
         <v/>
       </c>
       <c r="L105" s="41">
@@ -7939,15 +7953,15 @@
         <v/>
       </c>
       <c r="I106" s="31">
-        <f>IF(H106="","",H106/Config!$B$12-1)</f>
+        <f>IF(OR(H106="",NOT(ISNUMBER(Config!$B$12))),"",H106/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J106" s="33">
-        <f>IF(H106="","",IF(H106&lt;Config!$B$12,"Abaixo do mínimo",IF(H106&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H106="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H106&lt;Config!$B$12,"Abaixo do mínimo",IF(H106&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K106" s="25">
-        <f>IF(H106="","",MAX(0,Config!$B$12*G106-F106))</f>
+        <f>IF(OR(H106="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G106-F106))</f>
         <v/>
       </c>
       <c r="L106" s="41">
@@ -7968,15 +7982,15 @@
         <v/>
       </c>
       <c r="I107" s="31">
-        <f>IF(H107="","",H107/Config!$B$12-1)</f>
+        <f>IF(OR(H107="",NOT(ISNUMBER(Config!$B$12))),"",H107/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J107" s="33">
-        <f>IF(H107="","",IF(H107&lt;Config!$B$12,"Abaixo do mínimo",IF(H107&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H107="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H107&lt;Config!$B$12,"Abaixo do mínimo",IF(H107&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K107" s="25">
-        <f>IF(H107="","",MAX(0,Config!$B$12*G107-F107))</f>
+        <f>IF(OR(H107="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G107-F107))</f>
         <v/>
       </c>
       <c r="L107" s="41">
@@ -7997,15 +8011,15 @@
         <v/>
       </c>
       <c r="I108" s="31">
-        <f>IF(H108="","",H108/Config!$B$12-1)</f>
+        <f>IF(OR(H108="",NOT(ISNUMBER(Config!$B$12))),"",H108/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J108" s="33">
-        <f>IF(H108="","",IF(H108&lt;Config!$B$12,"Abaixo do mínimo",IF(H108&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H108="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H108&lt;Config!$B$12,"Abaixo do mínimo",IF(H108&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K108" s="25">
-        <f>IF(H108="","",MAX(0,Config!$B$12*G108-F108))</f>
+        <f>IF(OR(H108="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G108-F108))</f>
         <v/>
       </c>
       <c r="L108" s="41">
@@ -8026,15 +8040,15 @@
         <v/>
       </c>
       <c r="I109" s="31">
-        <f>IF(H109="","",H109/Config!$B$12-1)</f>
+        <f>IF(OR(H109="",NOT(ISNUMBER(Config!$B$12))),"",H109/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J109" s="33">
-        <f>IF(H109="","",IF(H109&lt;Config!$B$12,"Abaixo do mínimo",IF(H109&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H109="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H109&lt;Config!$B$12,"Abaixo do mínimo",IF(H109&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K109" s="25">
-        <f>IF(H109="","",MAX(0,Config!$B$12*G109-F109))</f>
+        <f>IF(OR(H109="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G109-F109))</f>
         <v/>
       </c>
       <c r="L109" s="41">
@@ -8055,15 +8069,15 @@
         <v/>
       </c>
       <c r="I110" s="31">
-        <f>IF(H110="","",H110/Config!$B$12-1)</f>
+        <f>IF(OR(H110="",NOT(ISNUMBER(Config!$B$12))),"",H110/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J110" s="33">
-        <f>IF(H110="","",IF(H110&lt;Config!$B$12,"Abaixo do mínimo",IF(H110&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H110="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H110&lt;Config!$B$12,"Abaixo do mínimo",IF(H110&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K110" s="25">
-        <f>IF(H110="","",MAX(0,Config!$B$12*G110-F110))</f>
+        <f>IF(OR(H110="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G110-F110))</f>
         <v/>
       </c>
       <c r="L110" s="41">
@@ -8084,15 +8098,15 @@
         <v/>
       </c>
       <c r="I111" s="31">
-        <f>IF(H111="","",H111/Config!$B$12-1)</f>
+        <f>IF(OR(H111="",NOT(ISNUMBER(Config!$B$12))),"",H111/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J111" s="33">
-        <f>IF(H111="","",IF(H111&lt;Config!$B$12,"Abaixo do mínimo",IF(H111&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H111="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H111&lt;Config!$B$12,"Abaixo do mínimo",IF(H111&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K111" s="25">
-        <f>IF(H111="","",MAX(0,Config!$B$12*G111-F111))</f>
+        <f>IF(OR(H111="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G111-F111))</f>
         <v/>
       </c>
       <c r="L111" s="41">
@@ -8113,15 +8127,15 @@
         <v/>
       </c>
       <c r="I112" s="31">
-        <f>IF(H112="","",H112/Config!$B$12-1)</f>
+        <f>IF(OR(H112="",NOT(ISNUMBER(Config!$B$12))),"",H112/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J112" s="33">
-        <f>IF(H112="","",IF(H112&lt;Config!$B$12,"Abaixo do mínimo",IF(H112&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H112="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H112&lt;Config!$B$12,"Abaixo do mínimo",IF(H112&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K112" s="25">
-        <f>IF(H112="","",MAX(0,Config!$B$12*G112-F112))</f>
+        <f>IF(OR(H112="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G112-F112))</f>
         <v/>
       </c>
       <c r="L112" s="41">
@@ -8142,15 +8156,15 @@
         <v/>
       </c>
       <c r="I113" s="31">
-        <f>IF(H113="","",H113/Config!$B$12-1)</f>
+        <f>IF(OR(H113="",NOT(ISNUMBER(Config!$B$12))),"",H113/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J113" s="33">
-        <f>IF(H113="","",IF(H113&lt;Config!$B$12,"Abaixo do mínimo",IF(H113&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H113="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H113&lt;Config!$B$12,"Abaixo do mínimo",IF(H113&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K113" s="25">
-        <f>IF(H113="","",MAX(0,Config!$B$12*G113-F113))</f>
+        <f>IF(OR(H113="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G113-F113))</f>
         <v/>
       </c>
       <c r="L113" s="41">
@@ -8171,15 +8185,15 @@
         <v/>
       </c>
       <c r="I114" s="31">
-        <f>IF(H114="","",H114/Config!$B$12-1)</f>
+        <f>IF(OR(H114="",NOT(ISNUMBER(Config!$B$12))),"",H114/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J114" s="33">
-        <f>IF(H114="","",IF(H114&lt;Config!$B$12,"Abaixo do mínimo",IF(H114&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H114="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H114&lt;Config!$B$12,"Abaixo do mínimo",IF(H114&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K114" s="25">
-        <f>IF(H114="","",MAX(0,Config!$B$12*G114-F114))</f>
+        <f>IF(OR(H114="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G114-F114))</f>
         <v/>
       </c>
       <c r="L114" s="41">
@@ -8200,15 +8214,15 @@
         <v/>
       </c>
       <c r="I115" s="31">
-        <f>IF(H115="","",H115/Config!$B$12-1)</f>
+        <f>IF(OR(H115="",NOT(ISNUMBER(Config!$B$12))),"",H115/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J115" s="33">
-        <f>IF(H115="","",IF(H115&lt;Config!$B$12,"Abaixo do mínimo",IF(H115&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H115="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H115&lt;Config!$B$12,"Abaixo do mínimo",IF(H115&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K115" s="25">
-        <f>IF(H115="","",MAX(0,Config!$B$12*G115-F115))</f>
+        <f>IF(OR(H115="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G115-F115))</f>
         <v/>
       </c>
       <c r="L115" s="41">
@@ -8229,15 +8243,15 @@
         <v/>
       </c>
       <c r="I116" s="31">
-        <f>IF(H116="","",H116/Config!$B$12-1)</f>
+        <f>IF(OR(H116="",NOT(ISNUMBER(Config!$B$12))),"",H116/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J116" s="33">
-        <f>IF(H116="","",IF(H116&lt;Config!$B$12,"Abaixo do mínimo",IF(H116&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H116="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H116&lt;Config!$B$12,"Abaixo do mínimo",IF(H116&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K116" s="25">
-        <f>IF(H116="","",MAX(0,Config!$B$12*G116-F116))</f>
+        <f>IF(OR(H116="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G116-F116))</f>
         <v/>
       </c>
       <c r="L116" s="41">
@@ -8258,15 +8272,15 @@
         <v/>
       </c>
       <c r="I117" s="31">
-        <f>IF(H117="","",H117/Config!$B$12-1)</f>
+        <f>IF(OR(H117="",NOT(ISNUMBER(Config!$B$12))),"",H117/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J117" s="33">
-        <f>IF(H117="","",IF(H117&lt;Config!$B$12,"Abaixo do mínimo",IF(H117&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H117="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H117&lt;Config!$B$12,"Abaixo do mínimo",IF(H117&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K117" s="25">
-        <f>IF(H117="","",MAX(0,Config!$B$12*G117-F117))</f>
+        <f>IF(OR(H117="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G117-F117))</f>
         <v/>
       </c>
       <c r="L117" s="41">
@@ -8287,15 +8301,15 @@
         <v/>
       </c>
       <c r="I118" s="31">
-        <f>IF(H118="","",H118/Config!$B$12-1)</f>
+        <f>IF(OR(H118="",NOT(ISNUMBER(Config!$B$12))),"",H118/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J118" s="33">
-        <f>IF(H118="","",IF(H118&lt;Config!$B$12,"Abaixo do mínimo",IF(H118&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H118="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H118&lt;Config!$B$12,"Abaixo do mínimo",IF(H118&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K118" s="25">
-        <f>IF(H118="","",MAX(0,Config!$B$12*G118-F118))</f>
+        <f>IF(OR(H118="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G118-F118))</f>
         <v/>
       </c>
       <c r="L118" s="41">
@@ -8316,15 +8330,15 @@
         <v/>
       </c>
       <c r="I119" s="31">
-        <f>IF(H119="","",H119/Config!$B$12-1)</f>
+        <f>IF(OR(H119="",NOT(ISNUMBER(Config!$B$12))),"",H119/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J119" s="33">
-        <f>IF(H119="","",IF(H119&lt;Config!$B$12,"Abaixo do mínimo",IF(H119&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H119="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H119&lt;Config!$B$12,"Abaixo do mínimo",IF(H119&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K119" s="25">
-        <f>IF(H119="","",MAX(0,Config!$B$12*G119-F119))</f>
+        <f>IF(OR(H119="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G119-F119))</f>
         <v/>
       </c>
       <c r="L119" s="41">
@@ -8345,15 +8359,15 @@
         <v/>
       </c>
       <c r="I120" s="31">
-        <f>IF(H120="","",H120/Config!$B$12-1)</f>
+        <f>IF(OR(H120="",NOT(ISNUMBER(Config!$B$12))),"",H120/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J120" s="33">
-        <f>IF(H120="","",IF(H120&lt;Config!$B$12,"Abaixo do mínimo",IF(H120&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H120="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H120&lt;Config!$B$12,"Abaixo do mínimo",IF(H120&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K120" s="25">
-        <f>IF(H120="","",MAX(0,Config!$B$12*G120-F120))</f>
+        <f>IF(OR(H120="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G120-F120))</f>
         <v/>
       </c>
       <c r="L120" s="41">
@@ -8374,15 +8388,15 @@
         <v/>
       </c>
       <c r="I121" s="31">
-        <f>IF(H121="","",H121/Config!$B$12-1)</f>
+        <f>IF(OR(H121="",NOT(ISNUMBER(Config!$B$12))),"",H121/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J121" s="33">
-        <f>IF(H121="","",IF(H121&lt;Config!$B$12,"Abaixo do mínimo",IF(H121&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H121="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H121&lt;Config!$B$12,"Abaixo do mínimo",IF(H121&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K121" s="25">
-        <f>IF(H121="","",MAX(0,Config!$B$12*G121-F121))</f>
+        <f>IF(OR(H121="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G121-F121))</f>
         <v/>
       </c>
       <c r="L121" s="41">
@@ -8403,15 +8417,15 @@
         <v/>
       </c>
       <c r="I122" s="31">
-        <f>IF(H122="","",H122/Config!$B$12-1)</f>
+        <f>IF(OR(H122="",NOT(ISNUMBER(Config!$B$12))),"",H122/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J122" s="33">
-        <f>IF(H122="","",IF(H122&lt;Config!$B$12,"Abaixo do mínimo",IF(H122&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H122="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H122&lt;Config!$B$12,"Abaixo do mínimo",IF(H122&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K122" s="25">
-        <f>IF(H122="","",MAX(0,Config!$B$12*G122-F122))</f>
+        <f>IF(OR(H122="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G122-F122))</f>
         <v/>
       </c>
       <c r="L122" s="41">
@@ -8432,15 +8446,15 @@
         <v/>
       </c>
       <c r="I123" s="31">
-        <f>IF(H123="","",H123/Config!$B$12-1)</f>
+        <f>IF(OR(H123="",NOT(ISNUMBER(Config!$B$12))),"",H123/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J123" s="33">
-        <f>IF(H123="","",IF(H123&lt;Config!$B$12,"Abaixo do mínimo",IF(H123&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H123="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H123&lt;Config!$B$12,"Abaixo do mínimo",IF(H123&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K123" s="25">
-        <f>IF(H123="","",MAX(0,Config!$B$12*G123-F123))</f>
+        <f>IF(OR(H123="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G123-F123))</f>
         <v/>
       </c>
       <c r="L123" s="41">
@@ -8461,15 +8475,15 @@
         <v/>
       </c>
       <c r="I124" s="31">
-        <f>IF(H124="","",H124/Config!$B$12-1)</f>
+        <f>IF(OR(H124="",NOT(ISNUMBER(Config!$B$12))),"",H124/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J124" s="33">
-        <f>IF(H124="","",IF(H124&lt;Config!$B$12,"Abaixo do mínimo",IF(H124&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H124="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H124&lt;Config!$B$12,"Abaixo do mínimo",IF(H124&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K124" s="25">
-        <f>IF(H124="","",MAX(0,Config!$B$12*G124-F124))</f>
+        <f>IF(OR(H124="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G124-F124))</f>
         <v/>
       </c>
       <c r="L124" s="41">
@@ -8490,15 +8504,15 @@
         <v/>
       </c>
       <c r="I125" s="31">
-        <f>IF(H125="","",H125/Config!$B$12-1)</f>
+        <f>IF(OR(H125="",NOT(ISNUMBER(Config!$B$12))),"",H125/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J125" s="33">
-        <f>IF(H125="","",IF(H125&lt;Config!$B$12,"Abaixo do mínimo",IF(H125&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H125="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H125&lt;Config!$B$12,"Abaixo do mínimo",IF(H125&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K125" s="25">
-        <f>IF(H125="","",MAX(0,Config!$B$12*G125-F125))</f>
+        <f>IF(OR(H125="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G125-F125))</f>
         <v/>
       </c>
       <c r="L125" s="41">
@@ -8519,15 +8533,15 @@
         <v/>
       </c>
       <c r="I126" s="31">
-        <f>IF(H126="","",H126/Config!$B$12-1)</f>
+        <f>IF(OR(H126="",NOT(ISNUMBER(Config!$B$12))),"",H126/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J126" s="33">
-        <f>IF(H126="","",IF(H126&lt;Config!$B$12,"Abaixo do mínimo",IF(H126&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H126="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H126&lt;Config!$B$12,"Abaixo do mínimo",IF(H126&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K126" s="25">
-        <f>IF(H126="","",MAX(0,Config!$B$12*G126-F126))</f>
+        <f>IF(OR(H126="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G126-F126))</f>
         <v/>
       </c>
       <c r="L126" s="41">
@@ -8548,15 +8562,15 @@
         <v/>
       </c>
       <c r="I127" s="31">
-        <f>IF(H127="","",H127/Config!$B$12-1)</f>
+        <f>IF(OR(H127="",NOT(ISNUMBER(Config!$B$12))),"",H127/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J127" s="33">
-        <f>IF(H127="","",IF(H127&lt;Config!$B$12,"Abaixo do mínimo",IF(H127&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H127="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H127&lt;Config!$B$12,"Abaixo do mínimo",IF(H127&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K127" s="25">
-        <f>IF(H127="","",MAX(0,Config!$B$12*G127-F127))</f>
+        <f>IF(OR(H127="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G127-F127))</f>
         <v/>
       </c>
       <c r="L127" s="41">
@@ -8577,15 +8591,15 @@
         <v/>
       </c>
       <c r="I128" s="31">
-        <f>IF(H128="","",H128/Config!$B$12-1)</f>
+        <f>IF(OR(H128="",NOT(ISNUMBER(Config!$B$12))),"",H128/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J128" s="33">
-        <f>IF(H128="","",IF(H128&lt;Config!$B$12,"Abaixo do mínimo",IF(H128&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H128="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H128&lt;Config!$B$12,"Abaixo do mínimo",IF(H128&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K128" s="25">
-        <f>IF(H128="","",MAX(0,Config!$B$12*G128-F128))</f>
+        <f>IF(OR(H128="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G128-F128))</f>
         <v/>
       </c>
       <c r="L128" s="41">
@@ -8606,15 +8620,15 @@
         <v/>
       </c>
       <c r="I129" s="31">
-        <f>IF(H129="","",H129/Config!$B$12-1)</f>
+        <f>IF(OR(H129="",NOT(ISNUMBER(Config!$B$12))),"",H129/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J129" s="33">
-        <f>IF(H129="","",IF(H129&lt;Config!$B$12,"Abaixo do mínimo",IF(H129&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H129="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H129&lt;Config!$B$12,"Abaixo do mínimo",IF(H129&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K129" s="25">
-        <f>IF(H129="","",MAX(0,Config!$B$12*G129-F129))</f>
+        <f>IF(OR(H129="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G129-F129))</f>
         <v/>
       </c>
       <c r="L129" s="41">
@@ -8635,15 +8649,15 @@
         <v/>
       </c>
       <c r="I130" s="31">
-        <f>IF(H130="","",H130/Config!$B$12-1)</f>
+        <f>IF(OR(H130="",NOT(ISNUMBER(Config!$B$12))),"",H130/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J130" s="33">
-        <f>IF(H130="","",IF(H130&lt;Config!$B$12,"Abaixo do mínimo",IF(H130&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H130="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H130&lt;Config!$B$12,"Abaixo do mínimo",IF(H130&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K130" s="25">
-        <f>IF(H130="","",MAX(0,Config!$B$12*G130-F130))</f>
+        <f>IF(OR(H130="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G130-F130))</f>
         <v/>
       </c>
       <c r="L130" s="41">
@@ -8664,15 +8678,15 @@
         <v/>
       </c>
       <c r="I131" s="31">
-        <f>IF(H131="","",H131/Config!$B$12-1)</f>
+        <f>IF(OR(H131="",NOT(ISNUMBER(Config!$B$12))),"",H131/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J131" s="33">
-        <f>IF(H131="","",IF(H131&lt;Config!$B$12,"Abaixo do mínimo",IF(H131&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H131="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H131&lt;Config!$B$12,"Abaixo do mínimo",IF(H131&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K131" s="25">
-        <f>IF(H131="","",MAX(0,Config!$B$12*G131-F131))</f>
+        <f>IF(OR(H131="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G131-F131))</f>
         <v/>
       </c>
       <c r="L131" s="41">
@@ -8693,15 +8707,15 @@
         <v/>
       </c>
       <c r="I132" s="31">
-        <f>IF(H132="","",H132/Config!$B$12-1)</f>
+        <f>IF(OR(H132="",NOT(ISNUMBER(Config!$B$12))),"",H132/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J132" s="33">
-        <f>IF(H132="","",IF(H132&lt;Config!$B$12,"Abaixo do mínimo",IF(H132&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H132="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H132&lt;Config!$B$12,"Abaixo do mínimo",IF(H132&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K132" s="25">
-        <f>IF(H132="","",MAX(0,Config!$B$12*G132-F132))</f>
+        <f>IF(OR(H132="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G132-F132))</f>
         <v/>
       </c>
       <c r="L132" s="41">
@@ -8722,15 +8736,15 @@
         <v/>
       </c>
       <c r="I133" s="31">
-        <f>IF(H133="","",H133/Config!$B$12-1)</f>
+        <f>IF(OR(H133="",NOT(ISNUMBER(Config!$B$12))),"",H133/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J133" s="33">
-        <f>IF(H133="","",IF(H133&lt;Config!$B$12,"Abaixo do mínimo",IF(H133&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H133="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H133&lt;Config!$B$12,"Abaixo do mínimo",IF(H133&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K133" s="25">
-        <f>IF(H133="","",MAX(0,Config!$B$12*G133-F133))</f>
+        <f>IF(OR(H133="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G133-F133))</f>
         <v/>
       </c>
       <c r="L133" s="41">
@@ -8751,15 +8765,15 @@
         <v/>
       </c>
       <c r="I134" s="31">
-        <f>IF(H134="","",H134/Config!$B$12-1)</f>
+        <f>IF(OR(H134="",NOT(ISNUMBER(Config!$B$12))),"",H134/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J134" s="33">
-        <f>IF(H134="","",IF(H134&lt;Config!$B$12,"Abaixo do mínimo",IF(H134&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H134="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H134&lt;Config!$B$12,"Abaixo do mínimo",IF(H134&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K134" s="25">
-        <f>IF(H134="","",MAX(0,Config!$B$12*G134-F134))</f>
+        <f>IF(OR(H134="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G134-F134))</f>
         <v/>
       </c>
       <c r="L134" s="41">
@@ -8780,15 +8794,15 @@
         <v/>
       </c>
       <c r="I135" s="31">
-        <f>IF(H135="","",H135/Config!$B$12-1)</f>
+        <f>IF(OR(H135="",NOT(ISNUMBER(Config!$B$12))),"",H135/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J135" s="33">
-        <f>IF(H135="","",IF(H135&lt;Config!$B$12,"Abaixo do mínimo",IF(H135&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H135="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H135&lt;Config!$B$12,"Abaixo do mínimo",IF(H135&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K135" s="25">
-        <f>IF(H135="","",MAX(0,Config!$B$12*G135-F135))</f>
+        <f>IF(OR(H135="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G135-F135))</f>
         <v/>
       </c>
       <c r="L135" s="41">
@@ -8809,15 +8823,15 @@
         <v/>
       </c>
       <c r="I136" s="31">
-        <f>IF(H136="","",H136/Config!$B$12-1)</f>
+        <f>IF(OR(H136="",NOT(ISNUMBER(Config!$B$12))),"",H136/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J136" s="33">
-        <f>IF(H136="","",IF(H136&lt;Config!$B$12,"Abaixo do mínimo",IF(H136&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H136="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H136&lt;Config!$B$12,"Abaixo do mínimo",IF(H136&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K136" s="25">
-        <f>IF(H136="","",MAX(0,Config!$B$12*G136-F136))</f>
+        <f>IF(OR(H136="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G136-F136))</f>
         <v/>
       </c>
       <c r="L136" s="41">
@@ -8838,15 +8852,15 @@
         <v/>
       </c>
       <c r="I137" s="31">
-        <f>IF(H137="","",H137/Config!$B$12-1)</f>
+        <f>IF(OR(H137="",NOT(ISNUMBER(Config!$B$12))),"",H137/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J137" s="33">
-        <f>IF(H137="","",IF(H137&lt;Config!$B$12,"Abaixo do mínimo",IF(H137&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H137="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H137&lt;Config!$B$12,"Abaixo do mínimo",IF(H137&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K137" s="25">
-        <f>IF(H137="","",MAX(0,Config!$B$12*G137-F137))</f>
+        <f>IF(OR(H137="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G137-F137))</f>
         <v/>
       </c>
       <c r="L137" s="41">
@@ -8867,15 +8881,15 @@
         <v/>
       </c>
       <c r="I138" s="31">
-        <f>IF(H138="","",H138/Config!$B$12-1)</f>
+        <f>IF(OR(H138="",NOT(ISNUMBER(Config!$B$12))),"",H138/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J138" s="33">
-        <f>IF(H138="","",IF(H138&lt;Config!$B$12,"Abaixo do mínimo",IF(H138&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H138="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H138&lt;Config!$B$12,"Abaixo do mínimo",IF(H138&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K138" s="25">
-        <f>IF(H138="","",MAX(0,Config!$B$12*G138-F138))</f>
+        <f>IF(OR(H138="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G138-F138))</f>
         <v/>
       </c>
       <c r="L138" s="41">
@@ -8896,15 +8910,15 @@
         <v/>
       </c>
       <c r="I139" s="31">
-        <f>IF(H139="","",H139/Config!$B$12-1)</f>
+        <f>IF(OR(H139="",NOT(ISNUMBER(Config!$B$12))),"",H139/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J139" s="33">
-        <f>IF(H139="","",IF(H139&lt;Config!$B$12,"Abaixo do mínimo",IF(H139&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H139="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H139&lt;Config!$B$12,"Abaixo do mínimo",IF(H139&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K139" s="25">
-        <f>IF(H139="","",MAX(0,Config!$B$12*G139-F139))</f>
+        <f>IF(OR(H139="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G139-F139))</f>
         <v/>
       </c>
       <c r="L139" s="41">
@@ -8925,15 +8939,15 @@
         <v/>
       </c>
       <c r="I140" s="31">
-        <f>IF(H140="","",H140/Config!$B$12-1)</f>
+        <f>IF(OR(H140="",NOT(ISNUMBER(Config!$B$12))),"",H140/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J140" s="33">
-        <f>IF(H140="","",IF(H140&lt;Config!$B$12,"Abaixo do mínimo",IF(H140&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H140="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H140&lt;Config!$B$12,"Abaixo do mínimo",IF(H140&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K140" s="25">
-        <f>IF(H140="","",MAX(0,Config!$B$12*G140-F140))</f>
+        <f>IF(OR(H140="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G140-F140))</f>
         <v/>
       </c>
       <c r="L140" s="41">
@@ -8954,15 +8968,15 @@
         <v/>
       </c>
       <c r="I141" s="31">
-        <f>IF(H141="","",H141/Config!$B$12-1)</f>
+        <f>IF(OR(H141="",NOT(ISNUMBER(Config!$B$12))),"",H141/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J141" s="33">
-        <f>IF(H141="","",IF(H141&lt;Config!$B$12,"Abaixo do mínimo",IF(H141&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H141="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H141&lt;Config!$B$12,"Abaixo do mínimo",IF(H141&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K141" s="25">
-        <f>IF(H141="","",MAX(0,Config!$B$12*G141-F141))</f>
+        <f>IF(OR(H141="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G141-F141))</f>
         <v/>
       </c>
       <c r="L141" s="41">
@@ -8983,15 +8997,15 @@
         <v/>
       </c>
       <c r="I142" s="31">
-        <f>IF(H142="","",H142/Config!$B$12-1)</f>
+        <f>IF(OR(H142="",NOT(ISNUMBER(Config!$B$12))),"",H142/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J142" s="33">
-        <f>IF(H142="","",IF(H142&lt;Config!$B$12,"Abaixo do mínimo",IF(H142&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H142="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H142&lt;Config!$B$12,"Abaixo do mínimo",IF(H142&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K142" s="25">
-        <f>IF(H142="","",MAX(0,Config!$B$12*G142-F142))</f>
+        <f>IF(OR(H142="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G142-F142))</f>
         <v/>
       </c>
       <c r="L142" s="41">
@@ -9012,15 +9026,15 @@
         <v/>
       </c>
       <c r="I143" s="31">
-        <f>IF(H143="","",H143/Config!$B$12-1)</f>
+        <f>IF(OR(H143="",NOT(ISNUMBER(Config!$B$12))),"",H143/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J143" s="33">
-        <f>IF(H143="","",IF(H143&lt;Config!$B$12,"Abaixo do mínimo",IF(H143&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H143="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H143&lt;Config!$B$12,"Abaixo do mínimo",IF(H143&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K143" s="25">
-        <f>IF(H143="","",MAX(0,Config!$B$12*G143-F143))</f>
+        <f>IF(OR(H143="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G143-F143))</f>
         <v/>
       </c>
       <c r="L143" s="41">
@@ -9041,15 +9055,15 @@
         <v/>
       </c>
       <c r="I144" s="31">
-        <f>IF(H144="","",H144/Config!$B$12-1)</f>
+        <f>IF(OR(H144="",NOT(ISNUMBER(Config!$B$12))),"",H144/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J144" s="33">
-        <f>IF(H144="","",IF(H144&lt;Config!$B$12,"Abaixo do mínimo",IF(H144&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H144="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H144&lt;Config!$B$12,"Abaixo do mínimo",IF(H144&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K144" s="25">
-        <f>IF(H144="","",MAX(0,Config!$B$12*G144-F144))</f>
+        <f>IF(OR(H144="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G144-F144))</f>
         <v/>
       </c>
       <c r="L144" s="41">
@@ -9070,15 +9084,15 @@
         <v/>
       </c>
       <c r="I145" s="31">
-        <f>IF(H145="","",H145/Config!$B$12-1)</f>
+        <f>IF(OR(H145="",NOT(ISNUMBER(Config!$B$12))),"",H145/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J145" s="33">
-        <f>IF(H145="","",IF(H145&lt;Config!$B$12,"Abaixo do mínimo",IF(H145&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H145="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H145&lt;Config!$B$12,"Abaixo do mínimo",IF(H145&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K145" s="25">
-        <f>IF(H145="","",MAX(0,Config!$B$12*G145-F145))</f>
+        <f>IF(OR(H145="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G145-F145))</f>
         <v/>
       </c>
       <c r="L145" s="41">
@@ -9099,15 +9113,15 @@
         <v/>
       </c>
       <c r="I146" s="31">
-        <f>IF(H146="","",H146/Config!$B$12-1)</f>
+        <f>IF(OR(H146="",NOT(ISNUMBER(Config!$B$12))),"",H146/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J146" s="33">
-        <f>IF(H146="","",IF(H146&lt;Config!$B$12,"Abaixo do mínimo",IF(H146&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H146="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H146&lt;Config!$B$12,"Abaixo do mínimo",IF(H146&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K146" s="25">
-        <f>IF(H146="","",MAX(0,Config!$B$12*G146-F146))</f>
+        <f>IF(OR(H146="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G146-F146))</f>
         <v/>
       </c>
       <c r="L146" s="41">
@@ -9128,15 +9142,15 @@
         <v/>
       </c>
       <c r="I147" s="31">
-        <f>IF(H147="","",H147/Config!$B$12-1)</f>
+        <f>IF(OR(H147="",NOT(ISNUMBER(Config!$B$12))),"",H147/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J147" s="33">
-        <f>IF(H147="","",IF(H147&lt;Config!$B$12,"Abaixo do mínimo",IF(H147&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H147="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H147&lt;Config!$B$12,"Abaixo do mínimo",IF(H147&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K147" s="25">
-        <f>IF(H147="","",MAX(0,Config!$B$12*G147-F147))</f>
+        <f>IF(OR(H147="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G147-F147))</f>
         <v/>
       </c>
       <c r="L147" s="41">
@@ -9157,15 +9171,15 @@
         <v/>
       </c>
       <c r="I148" s="31">
-        <f>IF(H148="","",H148/Config!$B$12-1)</f>
+        <f>IF(OR(H148="",NOT(ISNUMBER(Config!$B$12))),"",H148/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J148" s="33">
-        <f>IF(H148="","",IF(H148&lt;Config!$B$12,"Abaixo do mínimo",IF(H148&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H148="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H148&lt;Config!$B$12,"Abaixo do mínimo",IF(H148&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K148" s="25">
-        <f>IF(H148="","",MAX(0,Config!$B$12*G148-F148))</f>
+        <f>IF(OR(H148="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G148-F148))</f>
         <v/>
       </c>
       <c r="L148" s="41">
@@ -9186,15 +9200,15 @@
         <v/>
       </c>
       <c r="I149" s="31">
-        <f>IF(H149="","",H149/Config!$B$12-1)</f>
+        <f>IF(OR(H149="",NOT(ISNUMBER(Config!$B$12))),"",H149/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J149" s="33">
-        <f>IF(H149="","",IF(H149&lt;Config!$B$12,"Abaixo do mínimo",IF(H149&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H149="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H149&lt;Config!$B$12,"Abaixo do mínimo",IF(H149&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K149" s="25">
-        <f>IF(H149="","",MAX(0,Config!$B$12*G149-F149))</f>
+        <f>IF(OR(H149="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G149-F149))</f>
         <v/>
       </c>
       <c r="L149" s="41">
@@ -9215,15 +9229,15 @@
         <v/>
       </c>
       <c r="I150" s="31">
-        <f>IF(H150="","",H150/Config!$B$12-1)</f>
+        <f>IF(OR(H150="",NOT(ISNUMBER(Config!$B$12))),"",H150/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J150" s="33">
-        <f>IF(H150="","",IF(H150&lt;Config!$B$12,"Abaixo do mínimo",IF(H150&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H150="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H150&lt;Config!$B$12,"Abaixo do mínimo",IF(H150&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K150" s="25">
-        <f>IF(H150="","",MAX(0,Config!$B$12*G150-F150))</f>
+        <f>IF(OR(H150="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G150-F150))</f>
         <v/>
       </c>
       <c r="L150" s="41">
@@ -9244,15 +9258,15 @@
         <v/>
       </c>
       <c r="I151" s="31">
-        <f>IF(H151="","",H151/Config!$B$12-1)</f>
+        <f>IF(OR(H151="",NOT(ISNUMBER(Config!$B$12))),"",H151/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J151" s="33">
-        <f>IF(H151="","",IF(H151&lt;Config!$B$12,"Abaixo do mínimo",IF(H151&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H151="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H151&lt;Config!$B$12,"Abaixo do mínimo",IF(H151&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K151" s="25">
-        <f>IF(H151="","",MAX(0,Config!$B$12*G151-F151))</f>
+        <f>IF(OR(H151="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G151-F151))</f>
         <v/>
       </c>
       <c r="L151" s="41">
@@ -9273,15 +9287,15 @@
         <v/>
       </c>
       <c r="I152" s="31">
-        <f>IF(H152="","",H152/Config!$B$12-1)</f>
+        <f>IF(OR(H152="",NOT(ISNUMBER(Config!$B$12))),"",H152/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J152" s="33">
-        <f>IF(H152="","",IF(H152&lt;Config!$B$12,"Abaixo do mínimo",IF(H152&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H152="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H152&lt;Config!$B$12,"Abaixo do mínimo",IF(H152&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K152" s="25">
-        <f>IF(H152="","",MAX(0,Config!$B$12*G152-F152))</f>
+        <f>IF(OR(H152="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G152-F152))</f>
         <v/>
       </c>
       <c r="L152" s="41">
@@ -9302,15 +9316,15 @@
         <v/>
       </c>
       <c r="I153" s="31">
-        <f>IF(H153="","",H153/Config!$B$12-1)</f>
+        <f>IF(OR(H153="",NOT(ISNUMBER(Config!$B$12))),"",H153/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J153" s="33">
-        <f>IF(H153="","",IF(H153&lt;Config!$B$12,"Abaixo do mínimo",IF(H153&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H153="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H153&lt;Config!$B$12,"Abaixo do mínimo",IF(H153&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K153" s="25">
-        <f>IF(H153="","",MAX(0,Config!$B$12*G153-F153))</f>
+        <f>IF(OR(H153="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G153-F153))</f>
         <v/>
       </c>
       <c r="L153" s="41">
@@ -9331,15 +9345,15 @@
         <v/>
       </c>
       <c r="I154" s="31">
-        <f>IF(H154="","",H154/Config!$B$12-1)</f>
+        <f>IF(OR(H154="",NOT(ISNUMBER(Config!$B$12))),"",H154/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J154" s="33">
-        <f>IF(H154="","",IF(H154&lt;Config!$B$12,"Abaixo do mínimo",IF(H154&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H154="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H154&lt;Config!$B$12,"Abaixo do mínimo",IF(H154&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K154" s="25">
-        <f>IF(H154="","",MAX(0,Config!$B$12*G154-F154))</f>
+        <f>IF(OR(H154="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G154-F154))</f>
         <v/>
       </c>
       <c r="L154" s="41">
@@ -9360,15 +9374,15 @@
         <v/>
       </c>
       <c r="I155" s="31">
-        <f>IF(H155="","",H155/Config!$B$12-1)</f>
+        <f>IF(OR(H155="",NOT(ISNUMBER(Config!$B$12))),"",H155/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J155" s="33">
-        <f>IF(H155="","",IF(H155&lt;Config!$B$12,"Abaixo do mínimo",IF(H155&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H155="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H155&lt;Config!$B$12,"Abaixo do mínimo",IF(H155&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K155" s="25">
-        <f>IF(H155="","",MAX(0,Config!$B$12*G155-F155))</f>
+        <f>IF(OR(H155="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G155-F155))</f>
         <v/>
       </c>
       <c r="L155" s="41">
@@ -9389,15 +9403,15 @@
         <v/>
       </c>
       <c r="I156" s="31">
-        <f>IF(H156="","",H156/Config!$B$12-1)</f>
+        <f>IF(OR(H156="",NOT(ISNUMBER(Config!$B$12))),"",H156/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J156" s="33">
-        <f>IF(H156="","",IF(H156&lt;Config!$B$12,"Abaixo do mínimo",IF(H156&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H156="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H156&lt;Config!$B$12,"Abaixo do mínimo",IF(H156&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K156" s="25">
-        <f>IF(H156="","",MAX(0,Config!$B$12*G156-F156))</f>
+        <f>IF(OR(H156="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G156-F156))</f>
         <v/>
       </c>
       <c r="L156" s="41">
@@ -9418,15 +9432,15 @@
         <v/>
       </c>
       <c r="I157" s="31">
-        <f>IF(H157="","",H157/Config!$B$12-1)</f>
+        <f>IF(OR(H157="",NOT(ISNUMBER(Config!$B$12))),"",H157/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J157" s="33">
-        <f>IF(H157="","",IF(H157&lt;Config!$B$12,"Abaixo do mínimo",IF(H157&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H157="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H157&lt;Config!$B$12,"Abaixo do mínimo",IF(H157&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K157" s="25">
-        <f>IF(H157="","",MAX(0,Config!$B$12*G157-F157))</f>
+        <f>IF(OR(H157="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G157-F157))</f>
         <v/>
       </c>
       <c r="L157" s="41">
@@ -9447,15 +9461,15 @@
         <v/>
       </c>
       <c r="I158" s="31">
-        <f>IF(H158="","",H158/Config!$B$12-1)</f>
+        <f>IF(OR(H158="",NOT(ISNUMBER(Config!$B$12))),"",H158/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J158" s="33">
-        <f>IF(H158="","",IF(H158&lt;Config!$B$12,"Abaixo do mínimo",IF(H158&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H158="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H158&lt;Config!$B$12,"Abaixo do mínimo",IF(H158&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K158" s="25">
-        <f>IF(H158="","",MAX(0,Config!$B$12*G158-F158))</f>
+        <f>IF(OR(H158="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G158-F158))</f>
         <v/>
       </c>
       <c r="L158" s="41">
@@ -9476,15 +9490,15 @@
         <v/>
       </c>
       <c r="I159" s="31">
-        <f>IF(H159="","",H159/Config!$B$12-1)</f>
+        <f>IF(OR(H159="",NOT(ISNUMBER(Config!$B$12))),"",H159/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J159" s="33">
-        <f>IF(H159="","",IF(H159&lt;Config!$B$12,"Abaixo do mínimo",IF(H159&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H159="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H159&lt;Config!$B$12,"Abaixo do mínimo",IF(H159&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K159" s="25">
-        <f>IF(H159="","",MAX(0,Config!$B$12*G159-F159))</f>
+        <f>IF(OR(H159="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G159-F159))</f>
         <v/>
       </c>
       <c r="L159" s="41">
@@ -9505,15 +9519,15 @@
         <v/>
       </c>
       <c r="I160" s="31">
-        <f>IF(H160="","",H160/Config!$B$12-1)</f>
+        <f>IF(OR(H160="",NOT(ISNUMBER(Config!$B$12))),"",H160/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J160" s="33">
-        <f>IF(H160="","",IF(H160&lt;Config!$B$12,"Abaixo do mínimo",IF(H160&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H160="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H160&lt;Config!$B$12,"Abaixo do mínimo",IF(H160&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K160" s="25">
-        <f>IF(H160="","",MAX(0,Config!$B$12*G160-F160))</f>
+        <f>IF(OR(H160="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G160-F160))</f>
         <v/>
       </c>
       <c r="L160" s="41">
@@ -9534,15 +9548,15 @@
         <v/>
       </c>
       <c r="I161" s="31">
-        <f>IF(H161="","",H161/Config!$B$12-1)</f>
+        <f>IF(OR(H161="",NOT(ISNUMBER(Config!$B$12))),"",H161/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J161" s="33">
-        <f>IF(H161="","",IF(H161&lt;Config!$B$12,"Abaixo do mínimo",IF(H161&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H161="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H161&lt;Config!$B$12,"Abaixo do mínimo",IF(H161&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K161" s="25">
-        <f>IF(H161="","",MAX(0,Config!$B$12*G161-F161))</f>
+        <f>IF(OR(H161="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G161-F161))</f>
         <v/>
       </c>
       <c r="L161" s="41">
@@ -9563,15 +9577,15 @@
         <v/>
       </c>
       <c r="I162" s="31">
-        <f>IF(H162="","",H162/Config!$B$12-1)</f>
+        <f>IF(OR(H162="",NOT(ISNUMBER(Config!$B$12))),"",H162/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J162" s="33">
-        <f>IF(H162="","",IF(H162&lt;Config!$B$12,"Abaixo do mínimo",IF(H162&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H162="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H162&lt;Config!$B$12,"Abaixo do mínimo",IF(H162&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K162" s="25">
-        <f>IF(H162="","",MAX(0,Config!$B$12*G162-F162))</f>
+        <f>IF(OR(H162="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G162-F162))</f>
         <v/>
       </c>
       <c r="L162" s="41">
@@ -9592,15 +9606,15 @@
         <v/>
       </c>
       <c r="I163" s="31">
-        <f>IF(H163="","",H163/Config!$B$12-1)</f>
+        <f>IF(OR(H163="",NOT(ISNUMBER(Config!$B$12))),"",H163/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J163" s="33">
-        <f>IF(H163="","",IF(H163&lt;Config!$B$12,"Abaixo do mínimo",IF(H163&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H163="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H163&lt;Config!$B$12,"Abaixo do mínimo",IF(H163&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K163" s="25">
-        <f>IF(H163="","",MAX(0,Config!$B$12*G163-F163))</f>
+        <f>IF(OR(H163="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G163-F163))</f>
         <v/>
       </c>
       <c r="L163" s="41">
@@ -9621,15 +9635,15 @@
         <v/>
       </c>
       <c r="I164" s="31">
-        <f>IF(H164="","",H164/Config!$B$12-1)</f>
+        <f>IF(OR(H164="",NOT(ISNUMBER(Config!$B$12))),"",H164/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J164" s="33">
-        <f>IF(H164="","",IF(H164&lt;Config!$B$12,"Abaixo do mínimo",IF(H164&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H164="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H164&lt;Config!$B$12,"Abaixo do mínimo",IF(H164&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K164" s="25">
-        <f>IF(H164="","",MAX(0,Config!$B$12*G164-F164))</f>
+        <f>IF(OR(H164="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G164-F164))</f>
         <v/>
       </c>
       <c r="L164" s="41">
@@ -9650,15 +9664,15 @@
         <v/>
       </c>
       <c r="I165" s="31">
-        <f>IF(H165="","",H165/Config!$B$12-1)</f>
+        <f>IF(OR(H165="",NOT(ISNUMBER(Config!$B$12))),"",H165/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J165" s="33">
-        <f>IF(H165="","",IF(H165&lt;Config!$B$12,"Abaixo do mínimo",IF(H165&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H165="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H165&lt;Config!$B$12,"Abaixo do mínimo",IF(H165&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K165" s="25">
-        <f>IF(H165="","",MAX(0,Config!$B$12*G165-F165))</f>
+        <f>IF(OR(H165="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G165-F165))</f>
         <v/>
       </c>
       <c r="L165" s="41">
@@ -9679,15 +9693,15 @@
         <v/>
       </c>
       <c r="I166" s="31">
-        <f>IF(H166="","",H166/Config!$B$12-1)</f>
+        <f>IF(OR(H166="",NOT(ISNUMBER(Config!$B$12))),"",H166/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J166" s="33">
-        <f>IF(H166="","",IF(H166&lt;Config!$B$12,"Abaixo do mínimo",IF(H166&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H166="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H166&lt;Config!$B$12,"Abaixo do mínimo",IF(H166&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K166" s="25">
-        <f>IF(H166="","",MAX(0,Config!$B$12*G166-F166))</f>
+        <f>IF(OR(H166="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G166-F166))</f>
         <v/>
       </c>
       <c r="L166" s="41">
@@ -9708,15 +9722,15 @@
         <v/>
       </c>
       <c r="I167" s="31">
-        <f>IF(H167="","",H167/Config!$B$12-1)</f>
+        <f>IF(OR(H167="",NOT(ISNUMBER(Config!$B$12))),"",H167/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J167" s="33">
-        <f>IF(H167="","",IF(H167&lt;Config!$B$12,"Abaixo do mínimo",IF(H167&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H167="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H167&lt;Config!$B$12,"Abaixo do mínimo",IF(H167&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K167" s="25">
-        <f>IF(H167="","",MAX(0,Config!$B$12*G167-F167))</f>
+        <f>IF(OR(H167="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G167-F167))</f>
         <v/>
       </c>
       <c r="L167" s="41">
@@ -9737,15 +9751,15 @@
         <v/>
       </c>
       <c r="I168" s="31">
-        <f>IF(H168="","",H168/Config!$B$12-1)</f>
+        <f>IF(OR(H168="",NOT(ISNUMBER(Config!$B$12))),"",H168/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J168" s="33">
-        <f>IF(H168="","",IF(H168&lt;Config!$B$12,"Abaixo do mínimo",IF(H168&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H168="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H168&lt;Config!$B$12,"Abaixo do mínimo",IF(H168&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K168" s="25">
-        <f>IF(H168="","",MAX(0,Config!$B$12*G168-F168))</f>
+        <f>IF(OR(H168="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G168-F168))</f>
         <v/>
       </c>
       <c r="L168" s="41">
@@ -9766,15 +9780,15 @@
         <v/>
       </c>
       <c r="I169" s="31">
-        <f>IF(H169="","",H169/Config!$B$12-1)</f>
+        <f>IF(OR(H169="",NOT(ISNUMBER(Config!$B$12))),"",H169/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J169" s="33">
-        <f>IF(H169="","",IF(H169&lt;Config!$B$12,"Abaixo do mínimo",IF(H169&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H169="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H169&lt;Config!$B$12,"Abaixo do mínimo",IF(H169&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K169" s="25">
-        <f>IF(H169="","",MAX(0,Config!$B$12*G169-F169))</f>
+        <f>IF(OR(H169="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G169-F169))</f>
         <v/>
       </c>
       <c r="L169" s="41">
@@ -9795,15 +9809,15 @@
         <v/>
       </c>
       <c r="I170" s="31">
-        <f>IF(H170="","",H170/Config!$B$12-1)</f>
+        <f>IF(OR(H170="",NOT(ISNUMBER(Config!$B$12))),"",H170/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J170" s="33">
-        <f>IF(H170="","",IF(H170&lt;Config!$B$12,"Abaixo do mínimo",IF(H170&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H170="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H170&lt;Config!$B$12,"Abaixo do mínimo",IF(H170&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K170" s="25">
-        <f>IF(H170="","",MAX(0,Config!$B$12*G170-F170))</f>
+        <f>IF(OR(H170="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G170-F170))</f>
         <v/>
       </c>
       <c r="L170" s="41">
@@ -9824,15 +9838,15 @@
         <v/>
       </c>
       <c r="I171" s="31">
-        <f>IF(H171="","",H171/Config!$B$12-1)</f>
+        <f>IF(OR(H171="",NOT(ISNUMBER(Config!$B$12))),"",H171/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J171" s="33">
-        <f>IF(H171="","",IF(H171&lt;Config!$B$12,"Abaixo do mínimo",IF(H171&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H171="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H171&lt;Config!$B$12,"Abaixo do mínimo",IF(H171&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K171" s="25">
-        <f>IF(H171="","",MAX(0,Config!$B$12*G171-F171))</f>
+        <f>IF(OR(H171="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G171-F171))</f>
         <v/>
       </c>
       <c r="L171" s="41">
@@ -9853,15 +9867,15 @@
         <v/>
       </c>
       <c r="I172" s="31">
-        <f>IF(H172="","",H172/Config!$B$12-1)</f>
+        <f>IF(OR(H172="",NOT(ISNUMBER(Config!$B$12))),"",H172/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J172" s="33">
-        <f>IF(H172="","",IF(H172&lt;Config!$B$12,"Abaixo do mínimo",IF(H172&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H172="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H172&lt;Config!$B$12,"Abaixo do mínimo",IF(H172&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K172" s="25">
-        <f>IF(H172="","",MAX(0,Config!$B$12*G172-F172))</f>
+        <f>IF(OR(H172="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G172-F172))</f>
         <v/>
       </c>
       <c r="L172" s="41">
@@ -9882,15 +9896,15 @@
         <v/>
       </c>
       <c r="I173" s="31">
-        <f>IF(H173="","",H173/Config!$B$12-1)</f>
+        <f>IF(OR(H173="",NOT(ISNUMBER(Config!$B$12))),"",H173/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J173" s="33">
-        <f>IF(H173="","",IF(H173&lt;Config!$B$12,"Abaixo do mínimo",IF(H173&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H173="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H173&lt;Config!$B$12,"Abaixo do mínimo",IF(H173&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K173" s="25">
-        <f>IF(H173="","",MAX(0,Config!$B$12*G173-F173))</f>
+        <f>IF(OR(H173="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G173-F173))</f>
         <v/>
       </c>
       <c r="L173" s="41">
@@ -9911,15 +9925,15 @@
         <v/>
       </c>
       <c r="I174" s="31">
-        <f>IF(H174="","",H174/Config!$B$12-1)</f>
+        <f>IF(OR(H174="",NOT(ISNUMBER(Config!$B$12))),"",H174/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J174" s="33">
-        <f>IF(H174="","",IF(H174&lt;Config!$B$12,"Abaixo do mínimo",IF(H174&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H174="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H174&lt;Config!$B$12,"Abaixo do mínimo",IF(H174&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K174" s="25">
-        <f>IF(H174="","",MAX(0,Config!$B$12*G174-F174))</f>
+        <f>IF(OR(H174="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G174-F174))</f>
         <v/>
       </c>
       <c r="L174" s="41">
@@ -9940,15 +9954,15 @@
         <v/>
       </c>
       <c r="I175" s="31">
-        <f>IF(H175="","",H175/Config!$B$12-1)</f>
+        <f>IF(OR(H175="",NOT(ISNUMBER(Config!$B$12))),"",H175/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J175" s="33">
-        <f>IF(H175="","",IF(H175&lt;Config!$B$12,"Abaixo do mínimo",IF(H175&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H175="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H175&lt;Config!$B$12,"Abaixo do mínimo",IF(H175&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K175" s="25">
-        <f>IF(H175="","",MAX(0,Config!$B$12*G175-F175))</f>
+        <f>IF(OR(H175="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G175-F175))</f>
         <v/>
       </c>
       <c r="L175" s="41">
@@ -9969,15 +9983,15 @@
         <v/>
       </c>
       <c r="I176" s="31">
-        <f>IF(H176="","",H176/Config!$B$12-1)</f>
+        <f>IF(OR(H176="",NOT(ISNUMBER(Config!$B$12))),"",H176/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J176" s="33">
-        <f>IF(H176="","",IF(H176&lt;Config!$B$12,"Abaixo do mínimo",IF(H176&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H176="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H176&lt;Config!$B$12,"Abaixo do mínimo",IF(H176&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K176" s="25">
-        <f>IF(H176="","",MAX(0,Config!$B$12*G176-F176))</f>
+        <f>IF(OR(H176="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G176-F176))</f>
         <v/>
       </c>
       <c r="L176" s="41">
@@ -9998,15 +10012,15 @@
         <v/>
       </c>
       <c r="I177" s="31">
-        <f>IF(H177="","",H177/Config!$B$12-1)</f>
+        <f>IF(OR(H177="",NOT(ISNUMBER(Config!$B$12))),"",H177/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J177" s="33">
-        <f>IF(H177="","",IF(H177&lt;Config!$B$12,"Abaixo do mínimo",IF(H177&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H177="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H177&lt;Config!$B$12,"Abaixo do mínimo",IF(H177&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K177" s="25">
-        <f>IF(H177="","",MAX(0,Config!$B$12*G177-F177))</f>
+        <f>IF(OR(H177="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G177-F177))</f>
         <v/>
       </c>
       <c r="L177" s="41">
@@ -10027,15 +10041,15 @@
         <v/>
       </c>
       <c r="I178" s="31">
-        <f>IF(H178="","",H178/Config!$B$12-1)</f>
+        <f>IF(OR(H178="",NOT(ISNUMBER(Config!$B$12))),"",H178/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J178" s="33">
-        <f>IF(H178="","",IF(H178&lt;Config!$B$12,"Abaixo do mínimo",IF(H178&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H178="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H178&lt;Config!$B$12,"Abaixo do mínimo",IF(H178&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K178" s="25">
-        <f>IF(H178="","",MAX(0,Config!$B$12*G178-F178))</f>
+        <f>IF(OR(H178="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G178-F178))</f>
         <v/>
       </c>
       <c r="L178" s="41">
@@ -10056,15 +10070,15 @@
         <v/>
       </c>
       <c r="I179" s="31">
-        <f>IF(H179="","",H179/Config!$B$12-1)</f>
+        <f>IF(OR(H179="",NOT(ISNUMBER(Config!$B$12))),"",H179/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J179" s="33">
-        <f>IF(H179="","",IF(H179&lt;Config!$B$12,"Abaixo do mínimo",IF(H179&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H179="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H179&lt;Config!$B$12,"Abaixo do mínimo",IF(H179&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K179" s="25">
-        <f>IF(H179="","",MAX(0,Config!$B$12*G179-F179))</f>
+        <f>IF(OR(H179="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G179-F179))</f>
         <v/>
       </c>
       <c r="L179" s="41">
@@ -10085,15 +10099,15 @@
         <v/>
       </c>
       <c r="I180" s="31">
-        <f>IF(H180="","",H180/Config!$B$12-1)</f>
+        <f>IF(OR(H180="",NOT(ISNUMBER(Config!$B$12))),"",H180/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J180" s="33">
-        <f>IF(H180="","",IF(H180&lt;Config!$B$12,"Abaixo do mínimo",IF(H180&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H180="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H180&lt;Config!$B$12,"Abaixo do mínimo",IF(H180&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K180" s="25">
-        <f>IF(H180="","",MAX(0,Config!$B$12*G180-F180))</f>
+        <f>IF(OR(H180="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G180-F180))</f>
         <v/>
       </c>
       <c r="L180" s="41">
@@ -10114,15 +10128,15 @@
         <v/>
       </c>
       <c r="I181" s="31">
-        <f>IF(H181="","",H181/Config!$B$12-1)</f>
+        <f>IF(OR(H181="",NOT(ISNUMBER(Config!$B$12))),"",H181/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J181" s="33">
-        <f>IF(H181="","",IF(H181&lt;Config!$B$12,"Abaixo do mínimo",IF(H181&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H181="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H181&lt;Config!$B$12,"Abaixo do mínimo",IF(H181&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K181" s="25">
-        <f>IF(H181="","",MAX(0,Config!$B$12*G181-F181))</f>
+        <f>IF(OR(H181="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G181-F181))</f>
         <v/>
       </c>
       <c r="L181" s="41">
@@ -10143,15 +10157,15 @@
         <v/>
       </c>
       <c r="I182" s="31">
-        <f>IF(H182="","",H182/Config!$B$12-1)</f>
+        <f>IF(OR(H182="",NOT(ISNUMBER(Config!$B$12))),"",H182/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J182" s="33">
-        <f>IF(H182="","",IF(H182&lt;Config!$B$12,"Abaixo do mínimo",IF(H182&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H182="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H182&lt;Config!$B$12,"Abaixo do mínimo",IF(H182&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K182" s="25">
-        <f>IF(H182="","",MAX(0,Config!$B$12*G182-F182))</f>
+        <f>IF(OR(H182="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G182-F182))</f>
         <v/>
       </c>
       <c r="L182" s="41">
@@ -10172,15 +10186,15 @@
         <v/>
       </c>
       <c r="I183" s="31">
-        <f>IF(H183="","",H183/Config!$B$12-1)</f>
+        <f>IF(OR(H183="",NOT(ISNUMBER(Config!$B$12))),"",H183/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J183" s="33">
-        <f>IF(H183="","",IF(H183&lt;Config!$B$12,"Abaixo do mínimo",IF(H183&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H183="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H183&lt;Config!$B$12,"Abaixo do mínimo",IF(H183&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K183" s="25">
-        <f>IF(H183="","",MAX(0,Config!$B$12*G183-F183))</f>
+        <f>IF(OR(H183="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G183-F183))</f>
         <v/>
       </c>
       <c r="L183" s="41">
@@ -10201,15 +10215,15 @@
         <v/>
       </c>
       <c r="I184" s="31">
-        <f>IF(H184="","",H184/Config!$B$12-1)</f>
+        <f>IF(OR(H184="",NOT(ISNUMBER(Config!$B$12))),"",H184/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J184" s="33">
-        <f>IF(H184="","",IF(H184&lt;Config!$B$12,"Abaixo do mínimo",IF(H184&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H184="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H184&lt;Config!$B$12,"Abaixo do mínimo",IF(H184&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K184" s="25">
-        <f>IF(H184="","",MAX(0,Config!$B$12*G184-F184))</f>
+        <f>IF(OR(H184="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G184-F184))</f>
         <v/>
       </c>
       <c r="L184" s="41">
@@ -10230,15 +10244,15 @@
         <v/>
       </c>
       <c r="I185" s="31">
-        <f>IF(H185="","",H185/Config!$B$12-1)</f>
+        <f>IF(OR(H185="",NOT(ISNUMBER(Config!$B$12))),"",H185/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J185" s="33">
-        <f>IF(H185="","",IF(H185&lt;Config!$B$12,"Abaixo do mínimo",IF(H185&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H185="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H185&lt;Config!$B$12,"Abaixo do mínimo",IF(H185&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K185" s="25">
-        <f>IF(H185="","",MAX(0,Config!$B$12*G185-F185))</f>
+        <f>IF(OR(H185="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G185-F185))</f>
         <v/>
       </c>
       <c r="L185" s="41">
@@ -10259,15 +10273,15 @@
         <v/>
       </c>
       <c r="I186" s="31">
-        <f>IF(H186="","",H186/Config!$B$12-1)</f>
+        <f>IF(OR(H186="",NOT(ISNUMBER(Config!$B$12))),"",H186/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J186" s="33">
-        <f>IF(H186="","",IF(H186&lt;Config!$B$12,"Abaixo do mínimo",IF(H186&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H186="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H186&lt;Config!$B$12,"Abaixo do mínimo",IF(H186&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K186" s="25">
-        <f>IF(H186="","",MAX(0,Config!$B$12*G186-F186))</f>
+        <f>IF(OR(H186="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G186-F186))</f>
         <v/>
       </c>
       <c r="L186" s="41">
@@ -10288,15 +10302,15 @@
         <v/>
       </c>
       <c r="I187" s="31">
-        <f>IF(H187="","",H187/Config!$B$12-1)</f>
+        <f>IF(OR(H187="",NOT(ISNUMBER(Config!$B$12))),"",H187/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J187" s="33">
-        <f>IF(H187="","",IF(H187&lt;Config!$B$12,"Abaixo do mínimo",IF(H187&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H187="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H187&lt;Config!$B$12,"Abaixo do mínimo",IF(H187&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K187" s="25">
-        <f>IF(H187="","",MAX(0,Config!$B$12*G187-F187))</f>
+        <f>IF(OR(H187="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G187-F187))</f>
         <v/>
       </c>
       <c r="L187" s="41">
@@ -10317,15 +10331,15 @@
         <v/>
       </c>
       <c r="I188" s="31">
-        <f>IF(H188="","",H188/Config!$B$12-1)</f>
+        <f>IF(OR(H188="",NOT(ISNUMBER(Config!$B$12))),"",H188/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J188" s="33">
-        <f>IF(H188="","",IF(H188&lt;Config!$B$12,"Abaixo do mínimo",IF(H188&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H188="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H188&lt;Config!$B$12,"Abaixo do mínimo",IF(H188&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K188" s="25">
-        <f>IF(H188="","",MAX(0,Config!$B$12*G188-F188))</f>
+        <f>IF(OR(H188="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G188-F188))</f>
         <v/>
       </c>
       <c r="L188" s="41">
@@ -10346,15 +10360,15 @@
         <v/>
       </c>
       <c r="I189" s="31">
-        <f>IF(H189="","",H189/Config!$B$12-1)</f>
+        <f>IF(OR(H189="",NOT(ISNUMBER(Config!$B$12))),"",H189/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J189" s="33">
-        <f>IF(H189="","",IF(H189&lt;Config!$B$12,"Abaixo do mínimo",IF(H189&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H189="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H189&lt;Config!$B$12,"Abaixo do mínimo",IF(H189&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K189" s="25">
-        <f>IF(H189="","",MAX(0,Config!$B$12*G189-F189))</f>
+        <f>IF(OR(H189="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G189-F189))</f>
         <v/>
       </c>
       <c r="L189" s="41">
@@ -10375,15 +10389,15 @@
         <v/>
       </c>
       <c r="I190" s="31">
-        <f>IF(H190="","",H190/Config!$B$12-1)</f>
+        <f>IF(OR(H190="",NOT(ISNUMBER(Config!$B$12))),"",H190/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J190" s="33">
-        <f>IF(H190="","",IF(H190&lt;Config!$B$12,"Abaixo do mínimo",IF(H190&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H190="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H190&lt;Config!$B$12,"Abaixo do mínimo",IF(H190&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K190" s="25">
-        <f>IF(H190="","",MAX(0,Config!$B$12*G190-F190))</f>
+        <f>IF(OR(H190="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G190-F190))</f>
         <v/>
       </c>
       <c r="L190" s="41">
@@ -10404,15 +10418,15 @@
         <v/>
       </c>
       <c r="I191" s="31">
-        <f>IF(H191="","",H191/Config!$B$12-1)</f>
+        <f>IF(OR(H191="",NOT(ISNUMBER(Config!$B$12))),"",H191/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J191" s="33">
-        <f>IF(H191="","",IF(H191&lt;Config!$B$12,"Abaixo do mínimo",IF(H191&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H191="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H191&lt;Config!$B$12,"Abaixo do mínimo",IF(H191&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K191" s="25">
-        <f>IF(H191="","",MAX(0,Config!$B$12*G191-F191))</f>
+        <f>IF(OR(H191="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G191-F191))</f>
         <v/>
       </c>
       <c r="L191" s="41">
@@ -10433,15 +10447,15 @@
         <v/>
       </c>
       <c r="I192" s="31">
-        <f>IF(H192="","",H192/Config!$B$12-1)</f>
+        <f>IF(OR(H192="",NOT(ISNUMBER(Config!$B$12))),"",H192/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J192" s="33">
-        <f>IF(H192="","",IF(H192&lt;Config!$B$12,"Abaixo do mínimo",IF(H192&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H192="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H192&lt;Config!$B$12,"Abaixo do mínimo",IF(H192&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K192" s="25">
-        <f>IF(H192="","",MAX(0,Config!$B$12*G192-F192))</f>
+        <f>IF(OR(H192="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G192-F192))</f>
         <v/>
       </c>
       <c r="L192" s="41">
@@ -10462,15 +10476,15 @@
         <v/>
       </c>
       <c r="I193" s="31">
-        <f>IF(H193="","",H193/Config!$B$12-1)</f>
+        <f>IF(OR(H193="",NOT(ISNUMBER(Config!$B$12))),"",H193/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J193" s="33">
-        <f>IF(H193="","",IF(H193&lt;Config!$B$12,"Abaixo do mínimo",IF(H193&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H193="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H193&lt;Config!$B$12,"Abaixo do mínimo",IF(H193&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K193" s="25">
-        <f>IF(H193="","",MAX(0,Config!$B$12*G193-F193))</f>
+        <f>IF(OR(H193="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G193-F193))</f>
         <v/>
       </c>
       <c r="L193" s="41">
@@ -10491,15 +10505,15 @@
         <v/>
       </c>
       <c r="I194" s="31">
-        <f>IF(H194="","",H194/Config!$B$12-1)</f>
+        <f>IF(OR(H194="",NOT(ISNUMBER(Config!$B$12))),"",H194/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J194" s="33">
-        <f>IF(H194="","",IF(H194&lt;Config!$B$12,"Abaixo do mínimo",IF(H194&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H194="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H194&lt;Config!$B$12,"Abaixo do mínimo",IF(H194&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K194" s="25">
-        <f>IF(H194="","",MAX(0,Config!$B$12*G194-F194))</f>
+        <f>IF(OR(H194="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G194-F194))</f>
         <v/>
       </c>
       <c r="L194" s="41">
@@ -10520,15 +10534,15 @@
         <v/>
       </c>
       <c r="I195" s="31">
-        <f>IF(H195="","",H195/Config!$B$12-1)</f>
+        <f>IF(OR(H195="",NOT(ISNUMBER(Config!$B$12))),"",H195/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J195" s="33">
-        <f>IF(H195="","",IF(H195&lt;Config!$B$12,"Abaixo do mínimo",IF(H195&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H195="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H195&lt;Config!$B$12,"Abaixo do mínimo",IF(H195&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K195" s="25">
-        <f>IF(H195="","",MAX(0,Config!$B$12*G195-F195))</f>
+        <f>IF(OR(H195="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G195-F195))</f>
         <v/>
       </c>
       <c r="L195" s="41">
@@ -10549,15 +10563,15 @@
         <v/>
       </c>
       <c r="I196" s="31">
-        <f>IF(H196="","",H196/Config!$B$12-1)</f>
+        <f>IF(OR(H196="",NOT(ISNUMBER(Config!$B$12))),"",H196/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J196" s="33">
-        <f>IF(H196="","",IF(H196&lt;Config!$B$12,"Abaixo do mínimo",IF(H196&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H196="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H196&lt;Config!$B$12,"Abaixo do mínimo",IF(H196&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K196" s="25">
-        <f>IF(H196="","",MAX(0,Config!$B$12*G196-F196))</f>
+        <f>IF(OR(H196="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G196-F196))</f>
         <v/>
       </c>
       <c r="L196" s="41">
@@ -10578,15 +10592,15 @@
         <v/>
       </c>
       <c r="I197" s="31">
-        <f>IF(H197="","",H197/Config!$B$12-1)</f>
+        <f>IF(OR(H197="",NOT(ISNUMBER(Config!$B$12))),"",H197/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J197" s="33">
-        <f>IF(H197="","",IF(H197&lt;Config!$B$12,"Abaixo do mínimo",IF(H197&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H197="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H197&lt;Config!$B$12,"Abaixo do mínimo",IF(H197&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K197" s="25">
-        <f>IF(H197="","",MAX(0,Config!$B$12*G197-F197))</f>
+        <f>IF(OR(H197="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G197-F197))</f>
         <v/>
       </c>
       <c r="L197" s="41">
@@ -10607,15 +10621,15 @@
         <v/>
       </c>
       <c r="I198" s="31">
-        <f>IF(H198="","",H198/Config!$B$12-1)</f>
+        <f>IF(OR(H198="",NOT(ISNUMBER(Config!$B$12))),"",H198/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J198" s="33">
-        <f>IF(H198="","",IF(H198&lt;Config!$B$12,"Abaixo do mínimo",IF(H198&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H198="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H198&lt;Config!$B$12,"Abaixo do mínimo",IF(H198&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K198" s="25">
-        <f>IF(H198="","",MAX(0,Config!$B$12*G198-F198))</f>
+        <f>IF(OR(H198="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G198-F198))</f>
         <v/>
       </c>
       <c r="L198" s="41">
@@ -10636,15 +10650,15 @@
         <v/>
       </c>
       <c r="I199" s="31">
-        <f>IF(H199="","",H199/Config!$B$12-1)</f>
+        <f>IF(OR(H199="",NOT(ISNUMBER(Config!$B$12))),"",H199/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J199" s="33">
-        <f>IF(H199="","",IF(H199&lt;Config!$B$12,"Abaixo do mínimo",IF(H199&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H199="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H199&lt;Config!$B$12,"Abaixo do mínimo",IF(H199&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K199" s="25">
-        <f>IF(H199="","",MAX(0,Config!$B$12*G199-F199))</f>
+        <f>IF(OR(H199="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G199-F199))</f>
         <v/>
       </c>
       <c r="L199" s="41">
@@ -10665,15 +10679,15 @@
         <v/>
       </c>
       <c r="I200" s="31">
-        <f>IF(H200="","",H200/Config!$B$12-1)</f>
+        <f>IF(OR(H200="",NOT(ISNUMBER(Config!$B$12))),"",H200/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J200" s="33">
-        <f>IF(H200="","",IF(H200&lt;Config!$B$12,"Abaixo do mínimo",IF(H200&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H200="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H200&lt;Config!$B$12,"Abaixo do mínimo",IF(H200&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K200" s="25">
-        <f>IF(H200="","",MAX(0,Config!$B$12*G200-F200))</f>
+        <f>IF(OR(H200="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G200-F200))</f>
         <v/>
       </c>
       <c r="L200" s="41">
@@ -10694,15 +10708,15 @@
         <v/>
       </c>
       <c r="I201" s="31">
-        <f>IF(H201="","",H201/Config!$B$12-1)</f>
+        <f>IF(OR(H201="",NOT(ISNUMBER(Config!$B$12))),"",H201/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J201" s="33">
-        <f>IF(H201="","",IF(H201&lt;Config!$B$12,"Abaixo do mínimo",IF(H201&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H201="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H201&lt;Config!$B$12,"Abaixo do mínimo",IF(H201&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K201" s="25">
-        <f>IF(H201="","",MAX(0,Config!$B$12*G201-F201))</f>
+        <f>IF(OR(H201="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G201-F201))</f>
         <v/>
       </c>
       <c r="L201" s="41">
@@ -10723,15 +10737,15 @@
         <v/>
       </c>
       <c r="I202" s="31">
-        <f>IF(H202="","",H202/Config!$B$12-1)</f>
+        <f>IF(OR(H202="",NOT(ISNUMBER(Config!$B$12))),"",H202/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J202" s="33">
-        <f>IF(H202="","",IF(H202&lt;Config!$B$12,"Abaixo do mínimo",IF(H202&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H202="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H202&lt;Config!$B$12,"Abaixo do mínimo",IF(H202&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K202" s="25">
-        <f>IF(H202="","",MAX(0,Config!$B$12*G202-F202))</f>
+        <f>IF(OR(H202="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G202-F202))</f>
         <v/>
       </c>
       <c r="L202" s="41">
@@ -10752,15 +10766,15 @@
         <v/>
       </c>
       <c r="I203" s="31">
-        <f>IF(H203="","",H203/Config!$B$12-1)</f>
+        <f>IF(OR(H203="",NOT(ISNUMBER(Config!$B$12))),"",H203/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J203" s="33">
-        <f>IF(H203="","",IF(H203&lt;Config!$B$12,"Abaixo do mínimo",IF(H203&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H203="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H203&lt;Config!$B$12,"Abaixo do mínimo",IF(H203&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K203" s="25">
-        <f>IF(H203="","",MAX(0,Config!$B$12*G203-F203))</f>
+        <f>IF(OR(H203="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G203-F203))</f>
         <v/>
       </c>
       <c r="L203" s="41">
@@ -10781,15 +10795,15 @@
         <v/>
       </c>
       <c r="I204" s="31">
-        <f>IF(H204="","",H204/Config!$B$12-1)</f>
+        <f>IF(OR(H204="",NOT(ISNUMBER(Config!$B$12))),"",H204/Config!$B$12-1)</f>
         <v/>
       </c>
       <c r="J204" s="33">
-        <f>IF(H204="","",IF(H204&lt;Config!$B$12,"Abaixo do mínimo",IF(H204&lt;Config!$B$13,"Na faixa","Acima do alvo")))</f>
+        <f>IF(H204="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H204&lt;Config!$B$12,"Abaixo do mínimo",IF(H204&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
         <v/>
       </c>
       <c r="K204" s="25">
-        <f>IF(H204="","",MAX(0,Config!$B$12*G204-F204))</f>
+        <f>IF(OR(H204="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G204-F204))</f>
         <v/>
       </c>
       <c r="L204" s="41">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -2556,7 +2556,7 @@
         <v>160.601265822785</v>
       </c>
       <c r="F54" s="31">
-        <f>IF(OR(E54="",NOT(ISNUMBER(Config!$B$12))),"",E54/Config!$B$12-1)</f>
+        <f>IF(OR(E54="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E54/Config!$B$12-1))</f>
         <v>0.255873504649599</v>
       </c>
       <c r="G54" s="29">
@@ -2590,7 +2590,7 @@
         <v>125.775656324582</v>
       </c>
       <c r="F55" s="31">
-        <f>IF(OR(E55="",NOT(ISNUMBER(Config!$B$12))),"",E55/Config!$B$12-1)</f>
+        <f>IF(OR(E55="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E55/Config!$B$12-1))</f>
         <v>-0.0164566045061219</v>
       </c>
       <c r="G55" s="29">
@@ -2624,7 +2624,7 @@
         <v>149.242424242424</v>
       </c>
       <c r="F56" s="31">
-        <f>IF(OR(E56="",NOT(ISNUMBER(Config!$B$12))),"",E56/Config!$B$12-1)</f>
+        <f>IF(OR(E56="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E56/Config!$B$12-1))</f>
         <v>0.167049371718866</v>
       </c>
       <c r="G56" s="29">
@@ -2658,7 +2658,7 @@
         <v>186.991869918699</v>
       </c>
       <c r="F57" s="31">
-        <f>IF(OR(E57="",NOT(ISNUMBER(Config!$B$12))),"",E57/Config!$B$12-1)</f>
+        <f>IF(OR(E57="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E57/Config!$B$12-1))</f>
         <v>0.462243362856868</v>
       </c>
       <c r="G57" s="29">
@@ -2692,7 +2692,7 @@
         <v>145.806451612903</v>
       </c>
       <c r="F58" s="31">
-        <f>IF(OR(E58="",NOT(ISNUMBER(Config!$B$12))),"",E58/Config!$B$12-1)</f>
+        <f>IF(OR(E58="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E58/Config!$B$12-1))</f>
         <v>0.140180673231282</v>
       </c>
       <c r="G58" s="29">
@@ -2726,7 +2726,7 @@
         <v/>
       </c>
       <c r="F59" s="31">
-        <f>IF(OR(E59="",NOT(ISNUMBER(Config!$B$12))),"",E59/Config!$B$12-1)</f>
+        <f>IF(OR(E59="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E59/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G59" s="29">
@@ -2760,7 +2760,7 @@
         <v/>
       </c>
       <c r="F60" s="31">
-        <f>IF(OR(E60="",NOT(ISNUMBER(Config!$B$12))),"",E60/Config!$B$12-1)</f>
+        <f>IF(OR(E60="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E60/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G60" s="29">
@@ -2794,7 +2794,7 @@
         <v/>
       </c>
       <c r="F61" s="31">
-        <f>IF(OR(E61="",NOT(ISNUMBER(Config!$B$12))),"",E61/Config!$B$12-1)</f>
+        <f>IF(OR(E61="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E61/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G61" s="29">
@@ -2828,7 +2828,7 @@
         <v/>
       </c>
       <c r="F62" s="31">
-        <f>IF(OR(E62="",NOT(ISNUMBER(Config!$B$12))),"",E62/Config!$B$12-1)</f>
+        <f>IF(OR(E62="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E62/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G62" s="29">
@@ -2862,7 +2862,7 @@
         <v/>
       </c>
       <c r="F63" s="31">
-        <f>IF(OR(E63="",NOT(ISNUMBER(Config!$B$12))),"",E63/Config!$B$12-1)</f>
+        <f>IF(OR(E63="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E63/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G63" s="29">
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="F64" s="31">
-        <f>IF(OR(E64="",NOT(ISNUMBER(Config!$B$12))),"",E64/Config!$B$12-1)</f>
+        <f>IF(OR(E64="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E64/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G64" s="29">
@@ -2930,7 +2930,7 @@
         <v/>
       </c>
       <c r="F65" s="31">
-        <f>IF(OR(E65="",NOT(ISNUMBER(Config!$B$12))),"",E65/Config!$B$12-1)</f>
+        <f>IF(OR(E65="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E65/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G65" s="29">
@@ -2964,7 +2964,7 @@
         <v/>
       </c>
       <c r="F66" s="31">
-        <f>IF(OR(E66="",NOT(ISNUMBER(Config!$B$12))),"",E66/Config!$B$12-1)</f>
+        <f>IF(OR(E66="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E66/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G66" s="29">
@@ -2998,7 +2998,7 @@
         <v/>
       </c>
       <c r="F67" s="31">
-        <f>IF(OR(E67="",NOT(ISNUMBER(Config!$B$12))),"",E67/Config!$B$12-1)</f>
+        <f>IF(OR(E67="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E67/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G67" s="29">
@@ -3032,7 +3032,7 @@
         <v/>
       </c>
       <c r="F68" s="31">
-        <f>IF(OR(E68="",NOT(ISNUMBER(Config!$B$12))),"",E68/Config!$B$12-1)</f>
+        <f>IF(OR(E68="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E68/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G68" s="29">
@@ -3066,7 +3066,7 @@
         <v/>
       </c>
       <c r="F69" s="31">
-        <f>IF(OR(E69="",NOT(ISNUMBER(Config!$B$12))),"",E69/Config!$B$12-1)</f>
+        <f>IF(OR(E69="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E69/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G69" s="29">
@@ -3100,7 +3100,7 @@
         <v/>
       </c>
       <c r="F70" s="31">
-        <f>IF(OR(E70="",NOT(ISNUMBER(Config!$B$12))),"",E70/Config!$B$12-1)</f>
+        <f>IF(OR(E70="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E70/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G70" s="29">
@@ -3134,7 +3134,7 @@
         <v/>
       </c>
       <c r="F71" s="31">
-        <f>IF(OR(E71="",NOT(ISNUMBER(Config!$B$12))),"",E71/Config!$B$12-1)</f>
+        <f>IF(OR(E71="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E71/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G71" s="29">
@@ -3168,7 +3168,7 @@
         <v/>
       </c>
       <c r="F72" s="31">
-        <f>IF(OR(E72="",NOT(ISNUMBER(Config!$B$12))),"",E72/Config!$B$12-1)</f>
+        <f>IF(OR(E72="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E72/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G72" s="29">
@@ -3202,7 +3202,7 @@
         <v/>
       </c>
       <c r="F73" s="31">
-        <f>IF(OR(E73="",NOT(ISNUMBER(Config!$B$12))),"",E73/Config!$B$12-1)</f>
+        <f>IF(OR(E73="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E73/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G73" s="29">
@@ -3984,16 +3984,16 @@
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem mínima entre 0 % e a margem alvo, e impostos + margem abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B9),AND(B9&gt;=0,B9&lt;=N(B10),N(B8)+B9&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem alvo entre a margem mínima e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B10),B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B10),AND(B10&gt;=N(B9),B10&lt;1,N(B8)+B10&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Folga de 0 % para cima." type="custom">
-      <formula1>=AND(ISNUMBER(B11),B11&gt;=0)</formula1>
+      <formula1>=IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4136,7 +4136,7 @@
         <v>250</v>
       </c>
       <c r="I5" s="31">
-        <f>IF(OR(H5="",NOT(ISNUMBER(Config!$B$12))),"",H5/Config!$B$12-1)</f>
+        <f>IF(OR(H5="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H5/Config!$B$12-1))</f>
         <v>0.954955800341247</v>
       </c>
       <c r="J5" s="33" t="str">
@@ -4189,7 +4189,7 @@
         <v>85.7142857142857</v>
       </c>
       <c r="I6" s="31">
-        <f>IF(OR(H6="",NOT(ISNUMBER(Config!$B$12))),"",H6/Config!$B$12-1)</f>
+        <f>IF(OR(H6="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H6/Config!$B$12-1))</f>
         <v>-0.329729439883001</v>
       </c>
       <c r="J6" s="33" t="str">
@@ -4242,7 +4242,7 @@
         <v>172.222222222222</v>
       </c>
       <c r="I7" s="31">
-        <f>IF(OR(H7="",NOT(ISNUMBER(Config!$B$12))),"",H7/Config!$B$12-1)</f>
+        <f>IF(OR(H7="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H7/Config!$B$12-1))</f>
         <v>0.34674732912397</v>
       </c>
       <c r="J7" s="33" t="str">
@@ -4295,7 +4295,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="31">
-        <f>IF(OR(H8="",NOT(ISNUMBER(Config!$B$12))),"",H8/Config!$B$12-1)</f>
+        <f>IF(OR(H8="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H8/Config!$B$12-1))</f>
         <v>0.0556761321842736</v>
       </c>
       <c r="J8" s="33" t="str">
@@ -4348,7 +4348,7 @@
         <v>186.666666666667</v>
       </c>
       <c r="I9" s="31">
-        <f>IF(OR(H9="",NOT(ISNUMBER(Config!$B$12))),"",H9/Config!$B$12-1)</f>
+        <f>IF(OR(H9="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H9/Config!$B$12-1))</f>
         <v>0.459700330921465</v>
       </c>
       <c r="J9" s="33" t="str">
@@ -4401,7 +4401,7 @@
         <v>187.5</v>
       </c>
       <c r="I10" s="31">
-        <f>IF(OR(H10="",NOT(ISNUMBER(Config!$B$12))),"",H10/Config!$B$12-1)</f>
+        <f>IF(OR(H10="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H10/Config!$B$12-1))</f>
         <v>0.466216850255936</v>
       </c>
       <c r="J10" s="33" t="str">
@@ -4454,7 +4454,7 @@
         <v>183.333333333333</v>
       </c>
       <c r="I11" s="31">
-        <f>IF(OR(H11="",NOT(ISNUMBER(Config!$B$12))),"",H11/Config!$B$12-1)</f>
+        <f>IF(OR(H11="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H11/Config!$B$12-1))</f>
         <v>0.433634253583582</v>
       </c>
       <c r="J11" s="33" t="str">
@@ -4507,7 +4507,7 @@
         <v>118.75</v>
       </c>
       <c r="I12" s="31">
-        <f>IF(OR(H12="",NOT(ISNUMBER(Config!$B$12))),"",H12/Config!$B$12-1)</f>
+        <f>IF(OR(H12="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H12/Config!$B$12-1))</f>
         <v>-0.0713959948379075</v>
       </c>
       <c r="J12" s="33" t="str">
@@ -4560,7 +4560,7 @@
         <v>88.8888888888889</v>
       </c>
       <c r="I13" s="31">
-        <f>IF(OR(H13="",NOT(ISNUMBER(Config!$B$12))),"",H13/Config!$B$12-1)</f>
+        <f>IF(OR(H13="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H13/Config!$B$12-1))</f>
         <v>-0.304904604323112</v>
       </c>
       <c r="J13" s="33" t="str">
@@ -4613,7 +4613,7 @@
         <v>157.894736842105</v>
       </c>
       <c r="I14" s="31">
-        <f>IF(OR(H14="",NOT(ISNUMBER(Config!$B$12))),"",H14/Config!$B$12-1)</f>
+        <f>IF(OR(H14="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H14/Config!$B$12-1))</f>
         <v>0.234708926531314</v>
       </c>
       <c r="J14" s="33" t="str">
@@ -4666,7 +4666,7 @@
         <v>170</v>
       </c>
       <c r="I15" s="31">
-        <f>IF(OR(H15="",NOT(ISNUMBER(Config!$B$12))),"",H15/Config!$B$12-1)</f>
+        <f>IF(OR(H15="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H15/Config!$B$12-1))</f>
         <v>0.329369944232048</v>
       </c>
       <c r="J15" s="33" t="str">
@@ -4719,7 +4719,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="31">
-        <f>IF(OR(H16="",NOT(ISNUMBER(Config!$B$12))),"",H16/Config!$B$12-1)</f>
+        <f>IF(OR(H16="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H16/Config!$B$12-1))</f>
         <v>0.407568176245698</v>
       </c>
       <c r="J16" s="33" t="str">
@@ -4772,7 +4772,7 @@
         <v>163.636363636364</v>
       </c>
       <c r="I17" s="31">
-        <f>IF(OR(H17="",NOT(ISNUMBER(Config!$B$12))),"",H17/Config!$B$12-1)</f>
+        <f>IF(OR(H17="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H17/Config!$B$12-1))</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J17" s="33" t="str">
@@ -4825,7 +4825,7 @@
         <v>150</v>
       </c>
       <c r="I18" s="31">
-        <f>IF(OR(H18="",NOT(ISNUMBER(Config!$B$12))),"",H18/Config!$B$12-1)</f>
+        <f>IF(OR(H18="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H18/Config!$B$12-1))</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J18" s="33" t="str">
@@ -4878,7 +4878,7 @@
         <v>112.5</v>
       </c>
       <c r="I19" s="31">
-        <f>IF(OR(H19="",NOT(ISNUMBER(Config!$B$12))),"",H19/Config!$B$12-1)</f>
+        <f>IF(OR(H19="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H19/Config!$B$12-1))</f>
         <v>-0.120269889846439</v>
       </c>
       <c r="J19" s="33" t="str">
@@ -4931,7 +4931,7 @@
         <v>157.142857142857</v>
       </c>
       <c r="I20" s="31">
-        <f>IF(OR(H20="",NOT(ISNUMBER(Config!$B$12))),"",H20/Config!$B$12-1)</f>
+        <f>IF(OR(H20="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H20/Config!$B$12-1))</f>
         <v>0.228829360214498</v>
       </c>
       <c r="J20" s="33" t="str">
@@ -4984,7 +4984,7 @@
         <v>163.636363636364</v>
       </c>
       <c r="I21" s="31">
-        <f>IF(OR(H21="",NOT(ISNUMBER(Config!$B$12))),"",H21/Config!$B$12-1)</f>
+        <f>IF(OR(H21="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H21/Config!$B$12-1))</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J21" s="33" t="str">
@@ -5037,7 +5037,7 @@
         <v>146.666666666667</v>
       </c>
       <c r="I22" s="31">
-        <f>IF(OR(H22="",NOT(ISNUMBER(Config!$B$12))),"",H22/Config!$B$12-1)</f>
+        <f>IF(OR(H22="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H22/Config!$B$12-1))</f>
         <v>0.146907402866865</v>
       </c>
       <c r="J22" s="33" t="str">
@@ -5090,7 +5090,7 @@
         <v>111.111111111111</v>
       </c>
       <c r="I23" s="31">
-        <f>IF(OR(H23="",NOT(ISNUMBER(Config!$B$12))),"",H23/Config!$B$12-1)</f>
+        <f>IF(OR(H23="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H23/Config!$B$12-1))</f>
         <v>-0.13113075540389</v>
       </c>
       <c r="J23" s="33" t="str">
@@ -5143,7 +5143,7 @@
         <v>100</v>
       </c>
       <c r="I24" s="31">
-        <f>IF(OR(H24="",NOT(ISNUMBER(Config!$B$12))),"",H24/Config!$B$12-1)</f>
+        <f>IF(OR(H24="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H24/Config!$B$12-1))</f>
         <v>-0.218017679863501</v>
       </c>
       <c r="J24" s="33" t="str">
@@ -5196,7 +5196,7 @@
         <v>157.894736842105</v>
       </c>
       <c r="I25" s="31">
-        <f>IF(OR(H25="",NOT(ISNUMBER(Config!$B$12))),"",H25/Config!$B$12-1)</f>
+        <f>IF(OR(H25="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H25/Config!$B$12-1))</f>
         <v>0.234708926531314</v>
       </c>
       <c r="J25" s="33" t="str">
@@ -5249,7 +5249,7 @@
         <v>150</v>
       </c>
       <c r="I26" s="31">
-        <f>IF(OR(H26="",NOT(ISNUMBER(Config!$B$12))),"",H26/Config!$B$12-1)</f>
+        <f>IF(OR(H26="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H26/Config!$B$12-1))</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J26" s="33" t="str">
@@ -5302,7 +5302,7 @@
         <v>160</v>
       </c>
       <c r="I27" s="31">
-        <f>IF(OR(H27="",NOT(ISNUMBER(Config!$B$12))),"",H27/Config!$B$12-1)</f>
+        <f>IF(OR(H27="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H27/Config!$B$12-1))</f>
         <v>0.251171712218398</v>
       </c>
       <c r="J27" s="33" t="str">
@@ -5355,7 +5355,7 @@
         <v>190</v>
       </c>
       <c r="I28" s="31">
-        <f>IF(OR(H28="",NOT(ISNUMBER(Config!$B$12))),"",H28/Config!$B$12-1)</f>
+        <f>IF(OR(H28="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H28/Config!$B$12-1))</f>
         <v>0.485766408259348</v>
       </c>
       <c r="J28" s="33" t="str">
@@ -5408,7 +5408,7 @@
         <v>180.451127819549</v>
       </c>
       <c r="I29" s="31">
-        <f>IF(OR(H29="",NOT(ISNUMBER(Config!$B$12))),"",H29/Config!$B$12-1)</f>
+        <f>IF(OR(H29="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H29/Config!$B$12-1))</f>
         <v>0.411095916035788</v>
       </c>
       <c r="J29" s="33" t="str">
@@ -5461,7 +5461,7 @@
         <v>233.333333333333</v>
       </c>
       <c r="I30" s="31">
-        <f>IF(OR(H30="",NOT(ISNUMBER(Config!$B$12))),"",H30/Config!$B$12-1)</f>
+        <f>IF(OR(H30="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H30/Config!$B$12-1))</f>
         <v>0.824625413651831</v>
       </c>
       <c r="J30" s="33" t="str">
@@ -5514,7 +5514,7 @@
         <v>100</v>
       </c>
       <c r="I31" s="31">
-        <f>IF(OR(H31="",NOT(ISNUMBER(Config!$B$12))),"",H31/Config!$B$12-1)</f>
+        <f>IF(OR(H31="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H31/Config!$B$12-1))</f>
         <v>-0.218017679863501</v>
       </c>
       <c r="J31" s="33" t="str">
@@ -5567,7 +5567,7 @@
         <v>136.363636363636</v>
       </c>
       <c r="I32" s="31">
-        <f>IF(OR(H32="",NOT(ISNUMBER(Config!$B$12))),"",H32/Config!$B$12-1)</f>
+        <f>IF(OR(H32="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H32/Config!$B$12-1))</f>
         <v>0.0663395274588623</v>
       </c>
       <c r="J32" s="33" t="str">
@@ -5620,7 +5620,7 @@
         <v>190</v>
       </c>
       <c r="I33" s="31">
-        <f>IF(OR(H33="",NOT(ISNUMBER(Config!$B$12))),"",H33/Config!$B$12-1)</f>
+        <f>IF(OR(H33="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H33/Config!$B$12-1))</f>
         <v>0.485766408259348</v>
       </c>
       <c r="J33" s="33" t="str">
@@ -5673,7 +5673,7 @@
         <v>154.285714285714</v>
       </c>
       <c r="I34" s="31">
-        <f>IF(OR(H34="",NOT(ISNUMBER(Config!$B$12))),"",H34/Config!$B$12-1)</f>
+        <f>IF(OR(H34="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H34/Config!$B$12-1))</f>
         <v>0.206487008210598</v>
       </c>
       <c r="J34" s="33" t="str">
@@ -5726,7 +5726,7 @@
         <v>200</v>
       </c>
       <c r="I35" s="31">
-        <f>IF(OR(H35="",NOT(ISNUMBER(Config!$B$12))),"",H35/Config!$B$12-1)</f>
+        <f>IF(OR(H35="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H35/Config!$B$12-1))</f>
         <v>0.563964640272998</v>
       </c>
       <c r="J35" s="33" t="str">
@@ -5779,7 +5779,7 @@
         <v>163.636363636364</v>
       </c>
       <c r="I36" s="31">
-        <f>IF(OR(H36="",NOT(ISNUMBER(Config!$B$12))),"",H36/Config!$B$12-1)</f>
+        <f>IF(OR(H36="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H36/Config!$B$12-1))</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J36" s="33" t="str">
@@ -5832,7 +5832,7 @@
         <v>144.444444444444</v>
       </c>
       <c r="I37" s="31">
-        <f>IF(OR(H37="",NOT(ISNUMBER(Config!$B$12))),"",H37/Config!$B$12-1)</f>
+        <f>IF(OR(H37="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H37/Config!$B$12-1))</f>
         <v>0.129530017974943</v>
       </c>
       <c r="J37" s="33" t="str">
@@ -5885,7 +5885,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="I38" s="31">
-        <f>IF(OR(H38="",NOT(ISNUMBER(Config!$B$12))),"",H38/Config!$B$12-1)</f>
+        <f>IF(OR(H38="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H38/Config!$B$12-1))</f>
         <v>0.0426430935153319</v>
       </c>
       <c r="J38" s="33" t="str">
@@ -5938,7 +5938,7 @@
         <v>126.315789473684</v>
       </c>
       <c r="I39" s="31">
-        <f>IF(OR(H39="",NOT(ISNUMBER(Config!$B$12))),"",H39/Config!$B$12-1)</f>
+        <f>IF(OR(H39="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H39/Config!$B$12-1))</f>
         <v>-0.0122328587749487</v>
       </c>
       <c r="J39" s="33" t="str">
@@ -5991,7 +5991,7 @@
         <v>127.272727272727</v>
       </c>
       <c r="I40" s="31">
-        <f>IF(OR(H40="",NOT(ISNUMBER(Config!$B$12))),"",H40/Config!$B$12-1)</f>
+        <f>IF(OR(H40="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H40/Config!$B$12-1))</f>
         <v>-0.00474977437172863</v>
       </c>
       <c r="J40" s="33" t="str">
@@ -6044,7 +6044,7 @@
         <v>150</v>
       </c>
       <c r="I41" s="31">
-        <f>IF(OR(H41="",NOT(ISNUMBER(Config!$B$12))),"",H41/Config!$B$12-1)</f>
+        <f>IF(OR(H41="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H41/Config!$B$12-1))</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J41" s="33" t="str">
@@ -6097,7 +6097,7 @@
         <v>121.428571428571</v>
       </c>
       <c r="I42" s="31">
-        <f>IF(OR(H42="",NOT(ISNUMBER(Config!$B$12))),"",H42/Config!$B$12-1)</f>
+        <f>IF(OR(H42="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H42/Config!$B$12-1))</f>
         <v>-0.0504500398342512</v>
       </c>
       <c r="J42" s="33" t="str">
@@ -6126,7 +6126,7 @@
         <v/>
       </c>
       <c r="I43" s="31">
-        <f>IF(OR(H43="",NOT(ISNUMBER(Config!$B$12))),"",H43/Config!$B$12-1)</f>
+        <f>IF(OR(H43="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H43/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J43" s="33">
@@ -6155,7 +6155,7 @@
         <v/>
       </c>
       <c r="I44" s="31">
-        <f>IF(OR(H44="",NOT(ISNUMBER(Config!$B$12))),"",H44/Config!$B$12-1)</f>
+        <f>IF(OR(H44="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H44/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J44" s="33">
@@ -6184,7 +6184,7 @@
         <v/>
       </c>
       <c r="I45" s="31">
-        <f>IF(OR(H45="",NOT(ISNUMBER(Config!$B$12))),"",H45/Config!$B$12-1)</f>
+        <f>IF(OR(H45="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H45/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J45" s="33">
@@ -6213,7 +6213,7 @@
         <v/>
       </c>
       <c r="I46" s="31">
-        <f>IF(OR(H46="",NOT(ISNUMBER(Config!$B$12))),"",H46/Config!$B$12-1)</f>
+        <f>IF(OR(H46="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H46/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J46" s="33">
@@ -6242,7 +6242,7 @@
         <v/>
       </c>
       <c r="I47" s="31">
-        <f>IF(OR(H47="",NOT(ISNUMBER(Config!$B$12))),"",H47/Config!$B$12-1)</f>
+        <f>IF(OR(H47="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H47/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J47" s="33">
@@ -6271,7 +6271,7 @@
         <v/>
       </c>
       <c r="I48" s="31">
-        <f>IF(OR(H48="",NOT(ISNUMBER(Config!$B$12))),"",H48/Config!$B$12-1)</f>
+        <f>IF(OR(H48="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H48/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J48" s="33">
@@ -6300,7 +6300,7 @@
         <v/>
       </c>
       <c r="I49" s="31">
-        <f>IF(OR(H49="",NOT(ISNUMBER(Config!$B$12))),"",H49/Config!$B$12-1)</f>
+        <f>IF(OR(H49="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H49/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J49" s="33">
@@ -6329,7 +6329,7 @@
         <v/>
       </c>
       <c r="I50" s="31">
-        <f>IF(OR(H50="",NOT(ISNUMBER(Config!$B$12))),"",H50/Config!$B$12-1)</f>
+        <f>IF(OR(H50="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H50/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J50" s="33">
@@ -6358,7 +6358,7 @@
         <v/>
       </c>
       <c r="I51" s="31">
-        <f>IF(OR(H51="",NOT(ISNUMBER(Config!$B$12))),"",H51/Config!$B$12-1)</f>
+        <f>IF(OR(H51="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H51/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J51" s="33">
@@ -6387,7 +6387,7 @@
         <v/>
       </c>
       <c r="I52" s="31">
-        <f>IF(OR(H52="",NOT(ISNUMBER(Config!$B$12))),"",H52/Config!$B$12-1)</f>
+        <f>IF(OR(H52="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H52/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J52" s="33">
@@ -6416,7 +6416,7 @@
         <v/>
       </c>
       <c r="I53" s="31">
-        <f>IF(OR(H53="",NOT(ISNUMBER(Config!$B$12))),"",H53/Config!$B$12-1)</f>
+        <f>IF(OR(H53="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H53/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J53" s="33">
@@ -6445,7 +6445,7 @@
         <v/>
       </c>
       <c r="I54" s="31">
-        <f>IF(OR(H54="",NOT(ISNUMBER(Config!$B$12))),"",H54/Config!$B$12-1)</f>
+        <f>IF(OR(H54="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H54/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J54" s="33">
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="I55" s="31">
-        <f>IF(OR(H55="",NOT(ISNUMBER(Config!$B$12))),"",H55/Config!$B$12-1)</f>
+        <f>IF(OR(H55="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H55/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J55" s="33">
@@ -6503,7 +6503,7 @@
         <v/>
       </c>
       <c r="I56" s="31">
-        <f>IF(OR(H56="",NOT(ISNUMBER(Config!$B$12))),"",H56/Config!$B$12-1)</f>
+        <f>IF(OR(H56="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H56/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J56" s="33">
@@ -6532,7 +6532,7 @@
         <v/>
       </c>
       <c r="I57" s="31">
-        <f>IF(OR(H57="",NOT(ISNUMBER(Config!$B$12))),"",H57/Config!$B$12-1)</f>
+        <f>IF(OR(H57="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H57/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J57" s="33">
@@ -6561,7 +6561,7 @@
         <v/>
       </c>
       <c r="I58" s="31">
-        <f>IF(OR(H58="",NOT(ISNUMBER(Config!$B$12))),"",H58/Config!$B$12-1)</f>
+        <f>IF(OR(H58="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H58/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J58" s="33">
@@ -6590,7 +6590,7 @@
         <v/>
       </c>
       <c r="I59" s="31">
-        <f>IF(OR(H59="",NOT(ISNUMBER(Config!$B$12))),"",H59/Config!$B$12-1)</f>
+        <f>IF(OR(H59="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H59/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J59" s="33">
@@ -6619,7 +6619,7 @@
         <v/>
       </c>
       <c r="I60" s="31">
-        <f>IF(OR(H60="",NOT(ISNUMBER(Config!$B$12))),"",H60/Config!$B$12-1)</f>
+        <f>IF(OR(H60="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H60/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J60" s="33">
@@ -6648,7 +6648,7 @@
         <v/>
       </c>
       <c r="I61" s="31">
-        <f>IF(OR(H61="",NOT(ISNUMBER(Config!$B$12))),"",H61/Config!$B$12-1)</f>
+        <f>IF(OR(H61="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H61/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J61" s="33">
@@ -6677,7 +6677,7 @@
         <v/>
       </c>
       <c r="I62" s="31">
-        <f>IF(OR(H62="",NOT(ISNUMBER(Config!$B$12))),"",H62/Config!$B$12-1)</f>
+        <f>IF(OR(H62="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H62/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J62" s="33">
@@ -6706,7 +6706,7 @@
         <v/>
       </c>
       <c r="I63" s="31">
-        <f>IF(OR(H63="",NOT(ISNUMBER(Config!$B$12))),"",H63/Config!$B$12-1)</f>
+        <f>IF(OR(H63="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H63/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J63" s="33">
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="I64" s="31">
-        <f>IF(OR(H64="",NOT(ISNUMBER(Config!$B$12))),"",H64/Config!$B$12-1)</f>
+        <f>IF(OR(H64="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H64/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J64" s="33">
@@ -6764,7 +6764,7 @@
         <v/>
       </c>
       <c r="I65" s="31">
-        <f>IF(OR(H65="",NOT(ISNUMBER(Config!$B$12))),"",H65/Config!$B$12-1)</f>
+        <f>IF(OR(H65="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H65/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J65" s="33">
@@ -6793,7 +6793,7 @@
         <v/>
       </c>
       <c r="I66" s="31">
-        <f>IF(OR(H66="",NOT(ISNUMBER(Config!$B$12))),"",H66/Config!$B$12-1)</f>
+        <f>IF(OR(H66="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H66/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J66" s="33">
@@ -6822,7 +6822,7 @@
         <v/>
       </c>
       <c r="I67" s="31">
-        <f>IF(OR(H67="",NOT(ISNUMBER(Config!$B$12))),"",H67/Config!$B$12-1)</f>
+        <f>IF(OR(H67="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H67/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J67" s="33">
@@ -6851,7 +6851,7 @@
         <v/>
       </c>
       <c r="I68" s="31">
-        <f>IF(OR(H68="",NOT(ISNUMBER(Config!$B$12))),"",H68/Config!$B$12-1)</f>
+        <f>IF(OR(H68="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H68/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J68" s="33">
@@ -6880,7 +6880,7 @@
         <v/>
       </c>
       <c r="I69" s="31">
-        <f>IF(OR(H69="",NOT(ISNUMBER(Config!$B$12))),"",H69/Config!$B$12-1)</f>
+        <f>IF(OR(H69="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H69/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J69" s="33">
@@ -6909,7 +6909,7 @@
         <v/>
       </c>
       <c r="I70" s="31">
-        <f>IF(OR(H70="",NOT(ISNUMBER(Config!$B$12))),"",H70/Config!$B$12-1)</f>
+        <f>IF(OR(H70="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H70/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J70" s="33">
@@ -6938,7 +6938,7 @@
         <v/>
       </c>
       <c r="I71" s="31">
-        <f>IF(OR(H71="",NOT(ISNUMBER(Config!$B$12))),"",H71/Config!$B$12-1)</f>
+        <f>IF(OR(H71="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H71/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J71" s="33">
@@ -6967,7 +6967,7 @@
         <v/>
       </c>
       <c r="I72" s="31">
-        <f>IF(OR(H72="",NOT(ISNUMBER(Config!$B$12))),"",H72/Config!$B$12-1)</f>
+        <f>IF(OR(H72="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H72/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J72" s="33">
@@ -6996,7 +6996,7 @@
         <v/>
       </c>
       <c r="I73" s="31">
-        <f>IF(OR(H73="",NOT(ISNUMBER(Config!$B$12))),"",H73/Config!$B$12-1)</f>
+        <f>IF(OR(H73="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H73/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J73" s="33">
@@ -7025,7 +7025,7 @@
         <v/>
       </c>
       <c r="I74" s="31">
-        <f>IF(OR(H74="",NOT(ISNUMBER(Config!$B$12))),"",H74/Config!$B$12-1)</f>
+        <f>IF(OR(H74="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H74/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J74" s="33">
@@ -7054,7 +7054,7 @@
         <v/>
       </c>
       <c r="I75" s="31">
-        <f>IF(OR(H75="",NOT(ISNUMBER(Config!$B$12))),"",H75/Config!$B$12-1)</f>
+        <f>IF(OR(H75="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H75/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J75" s="33">
@@ -7083,7 +7083,7 @@
         <v/>
       </c>
       <c r="I76" s="31">
-        <f>IF(OR(H76="",NOT(ISNUMBER(Config!$B$12))),"",H76/Config!$B$12-1)</f>
+        <f>IF(OR(H76="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H76/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J76" s="33">
@@ -7112,7 +7112,7 @@
         <v/>
       </c>
       <c r="I77" s="31">
-        <f>IF(OR(H77="",NOT(ISNUMBER(Config!$B$12))),"",H77/Config!$B$12-1)</f>
+        <f>IF(OR(H77="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H77/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J77" s="33">
@@ -7141,7 +7141,7 @@
         <v/>
       </c>
       <c r="I78" s="31">
-        <f>IF(OR(H78="",NOT(ISNUMBER(Config!$B$12))),"",H78/Config!$B$12-1)</f>
+        <f>IF(OR(H78="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H78/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J78" s="33">
@@ -7170,7 +7170,7 @@
         <v/>
       </c>
       <c r="I79" s="31">
-        <f>IF(OR(H79="",NOT(ISNUMBER(Config!$B$12))),"",H79/Config!$B$12-1)</f>
+        <f>IF(OR(H79="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H79/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J79" s="33">
@@ -7199,7 +7199,7 @@
         <v/>
       </c>
       <c r="I80" s="31">
-        <f>IF(OR(H80="",NOT(ISNUMBER(Config!$B$12))),"",H80/Config!$B$12-1)</f>
+        <f>IF(OR(H80="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H80/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J80" s="33">
@@ -7228,7 +7228,7 @@
         <v/>
       </c>
       <c r="I81" s="31">
-        <f>IF(OR(H81="",NOT(ISNUMBER(Config!$B$12))),"",H81/Config!$B$12-1)</f>
+        <f>IF(OR(H81="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H81/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J81" s="33">
@@ -7257,7 +7257,7 @@
         <v/>
       </c>
       <c r="I82" s="31">
-        <f>IF(OR(H82="",NOT(ISNUMBER(Config!$B$12))),"",H82/Config!$B$12-1)</f>
+        <f>IF(OR(H82="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H82/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J82" s="33">
@@ -7286,7 +7286,7 @@
         <v/>
       </c>
       <c r="I83" s="31">
-        <f>IF(OR(H83="",NOT(ISNUMBER(Config!$B$12))),"",H83/Config!$B$12-1)</f>
+        <f>IF(OR(H83="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H83/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J83" s="33">
@@ -7315,7 +7315,7 @@
         <v/>
       </c>
       <c r="I84" s="31">
-        <f>IF(OR(H84="",NOT(ISNUMBER(Config!$B$12))),"",H84/Config!$B$12-1)</f>
+        <f>IF(OR(H84="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H84/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J84" s="33">
@@ -7344,7 +7344,7 @@
         <v/>
       </c>
       <c r="I85" s="31">
-        <f>IF(OR(H85="",NOT(ISNUMBER(Config!$B$12))),"",H85/Config!$B$12-1)</f>
+        <f>IF(OR(H85="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H85/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J85" s="33">
@@ -7373,7 +7373,7 @@
         <v/>
       </c>
       <c r="I86" s="31">
-        <f>IF(OR(H86="",NOT(ISNUMBER(Config!$B$12))),"",H86/Config!$B$12-1)</f>
+        <f>IF(OR(H86="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H86/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J86" s="33">
@@ -7402,7 +7402,7 @@
         <v/>
       </c>
       <c r="I87" s="31">
-        <f>IF(OR(H87="",NOT(ISNUMBER(Config!$B$12))),"",H87/Config!$B$12-1)</f>
+        <f>IF(OR(H87="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H87/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J87" s="33">
@@ -7431,7 +7431,7 @@
         <v/>
       </c>
       <c r="I88" s="31">
-        <f>IF(OR(H88="",NOT(ISNUMBER(Config!$B$12))),"",H88/Config!$B$12-1)</f>
+        <f>IF(OR(H88="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H88/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J88" s="33">
@@ -7460,7 +7460,7 @@
         <v/>
       </c>
       <c r="I89" s="31">
-        <f>IF(OR(H89="",NOT(ISNUMBER(Config!$B$12))),"",H89/Config!$B$12-1)</f>
+        <f>IF(OR(H89="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H89/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J89" s="33">
@@ -7489,7 +7489,7 @@
         <v/>
       </c>
       <c r="I90" s="31">
-        <f>IF(OR(H90="",NOT(ISNUMBER(Config!$B$12))),"",H90/Config!$B$12-1)</f>
+        <f>IF(OR(H90="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H90/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J90" s="33">
@@ -7518,7 +7518,7 @@
         <v/>
       </c>
       <c r="I91" s="31">
-        <f>IF(OR(H91="",NOT(ISNUMBER(Config!$B$12))),"",H91/Config!$B$12-1)</f>
+        <f>IF(OR(H91="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H91/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J91" s="33">
@@ -7547,7 +7547,7 @@
         <v/>
       </c>
       <c r="I92" s="31">
-        <f>IF(OR(H92="",NOT(ISNUMBER(Config!$B$12))),"",H92/Config!$B$12-1)</f>
+        <f>IF(OR(H92="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H92/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J92" s="33">
@@ -7576,7 +7576,7 @@
         <v/>
       </c>
       <c r="I93" s="31">
-        <f>IF(OR(H93="",NOT(ISNUMBER(Config!$B$12))),"",H93/Config!$B$12-1)</f>
+        <f>IF(OR(H93="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H93/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J93" s="33">
@@ -7605,7 +7605,7 @@
         <v/>
       </c>
       <c r="I94" s="31">
-        <f>IF(OR(H94="",NOT(ISNUMBER(Config!$B$12))),"",H94/Config!$B$12-1)</f>
+        <f>IF(OR(H94="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H94/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J94" s="33">
@@ -7634,7 +7634,7 @@
         <v/>
       </c>
       <c r="I95" s="31">
-        <f>IF(OR(H95="",NOT(ISNUMBER(Config!$B$12))),"",H95/Config!$B$12-1)</f>
+        <f>IF(OR(H95="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H95/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J95" s="33">
@@ -7663,7 +7663,7 @@
         <v/>
       </c>
       <c r="I96" s="31">
-        <f>IF(OR(H96="",NOT(ISNUMBER(Config!$B$12))),"",H96/Config!$B$12-1)</f>
+        <f>IF(OR(H96="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H96/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J96" s="33">
@@ -7692,7 +7692,7 @@
         <v/>
       </c>
       <c r="I97" s="31">
-        <f>IF(OR(H97="",NOT(ISNUMBER(Config!$B$12))),"",H97/Config!$B$12-1)</f>
+        <f>IF(OR(H97="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H97/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J97" s="33">
@@ -7721,7 +7721,7 @@
         <v/>
       </c>
       <c r="I98" s="31">
-        <f>IF(OR(H98="",NOT(ISNUMBER(Config!$B$12))),"",H98/Config!$B$12-1)</f>
+        <f>IF(OR(H98="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H98/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J98" s="33">
@@ -7750,7 +7750,7 @@
         <v/>
       </c>
       <c r="I99" s="31">
-        <f>IF(OR(H99="",NOT(ISNUMBER(Config!$B$12))),"",H99/Config!$B$12-1)</f>
+        <f>IF(OR(H99="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H99/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J99" s="33">
@@ -7779,7 +7779,7 @@
         <v/>
       </c>
       <c r="I100" s="31">
-        <f>IF(OR(H100="",NOT(ISNUMBER(Config!$B$12))),"",H100/Config!$B$12-1)</f>
+        <f>IF(OR(H100="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H100/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J100" s="33">
@@ -7808,7 +7808,7 @@
         <v/>
       </c>
       <c r="I101" s="31">
-        <f>IF(OR(H101="",NOT(ISNUMBER(Config!$B$12))),"",H101/Config!$B$12-1)</f>
+        <f>IF(OR(H101="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H101/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J101" s="33">
@@ -7837,7 +7837,7 @@
         <v/>
       </c>
       <c r="I102" s="31">
-        <f>IF(OR(H102="",NOT(ISNUMBER(Config!$B$12))),"",H102/Config!$B$12-1)</f>
+        <f>IF(OR(H102="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H102/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J102" s="33">
@@ -7866,7 +7866,7 @@
         <v/>
       </c>
       <c r="I103" s="31">
-        <f>IF(OR(H103="",NOT(ISNUMBER(Config!$B$12))),"",H103/Config!$B$12-1)</f>
+        <f>IF(OR(H103="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H103/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J103" s="33">
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
       <c r="I104" s="31">
-        <f>IF(OR(H104="",NOT(ISNUMBER(Config!$B$12))),"",H104/Config!$B$12-1)</f>
+        <f>IF(OR(H104="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H104/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J104" s="33">
@@ -7924,7 +7924,7 @@
         <v/>
       </c>
       <c r="I105" s="31">
-        <f>IF(OR(H105="",NOT(ISNUMBER(Config!$B$12))),"",H105/Config!$B$12-1)</f>
+        <f>IF(OR(H105="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H105/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J105" s="33">
@@ -7953,7 +7953,7 @@
         <v/>
       </c>
       <c r="I106" s="31">
-        <f>IF(OR(H106="",NOT(ISNUMBER(Config!$B$12))),"",H106/Config!$B$12-1)</f>
+        <f>IF(OR(H106="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H106/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J106" s="33">
@@ -7982,7 +7982,7 @@
         <v/>
       </c>
       <c r="I107" s="31">
-        <f>IF(OR(H107="",NOT(ISNUMBER(Config!$B$12))),"",H107/Config!$B$12-1)</f>
+        <f>IF(OR(H107="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H107/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J107" s="33">
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="I108" s="31">
-        <f>IF(OR(H108="",NOT(ISNUMBER(Config!$B$12))),"",H108/Config!$B$12-1)</f>
+        <f>IF(OR(H108="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H108/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J108" s="33">
@@ -8040,7 +8040,7 @@
         <v/>
       </c>
       <c r="I109" s="31">
-        <f>IF(OR(H109="",NOT(ISNUMBER(Config!$B$12))),"",H109/Config!$B$12-1)</f>
+        <f>IF(OR(H109="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H109/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J109" s="33">
@@ -8069,7 +8069,7 @@
         <v/>
       </c>
       <c r="I110" s="31">
-        <f>IF(OR(H110="",NOT(ISNUMBER(Config!$B$12))),"",H110/Config!$B$12-1)</f>
+        <f>IF(OR(H110="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H110/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J110" s="33">
@@ -8098,7 +8098,7 @@
         <v/>
       </c>
       <c r="I111" s="31">
-        <f>IF(OR(H111="",NOT(ISNUMBER(Config!$B$12))),"",H111/Config!$B$12-1)</f>
+        <f>IF(OR(H111="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H111/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J111" s="33">
@@ -8127,7 +8127,7 @@
         <v/>
       </c>
       <c r="I112" s="31">
-        <f>IF(OR(H112="",NOT(ISNUMBER(Config!$B$12))),"",H112/Config!$B$12-1)</f>
+        <f>IF(OR(H112="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H112/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J112" s="33">
@@ -8156,7 +8156,7 @@
         <v/>
       </c>
       <c r="I113" s="31">
-        <f>IF(OR(H113="",NOT(ISNUMBER(Config!$B$12))),"",H113/Config!$B$12-1)</f>
+        <f>IF(OR(H113="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H113/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J113" s="33">
@@ -8185,7 +8185,7 @@
         <v/>
       </c>
       <c r="I114" s="31">
-        <f>IF(OR(H114="",NOT(ISNUMBER(Config!$B$12))),"",H114/Config!$B$12-1)</f>
+        <f>IF(OR(H114="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H114/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J114" s="33">
@@ -8214,7 +8214,7 @@
         <v/>
       </c>
       <c r="I115" s="31">
-        <f>IF(OR(H115="",NOT(ISNUMBER(Config!$B$12))),"",H115/Config!$B$12-1)</f>
+        <f>IF(OR(H115="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H115/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J115" s="33">
@@ -8243,7 +8243,7 @@
         <v/>
       </c>
       <c r="I116" s="31">
-        <f>IF(OR(H116="",NOT(ISNUMBER(Config!$B$12))),"",H116/Config!$B$12-1)</f>
+        <f>IF(OR(H116="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H116/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J116" s="33">
@@ -8272,7 +8272,7 @@
         <v/>
       </c>
       <c r="I117" s="31">
-        <f>IF(OR(H117="",NOT(ISNUMBER(Config!$B$12))),"",H117/Config!$B$12-1)</f>
+        <f>IF(OR(H117="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H117/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J117" s="33">
@@ -8301,7 +8301,7 @@
         <v/>
       </c>
       <c r="I118" s="31">
-        <f>IF(OR(H118="",NOT(ISNUMBER(Config!$B$12))),"",H118/Config!$B$12-1)</f>
+        <f>IF(OR(H118="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H118/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J118" s="33">
@@ -8330,7 +8330,7 @@
         <v/>
       </c>
       <c r="I119" s="31">
-        <f>IF(OR(H119="",NOT(ISNUMBER(Config!$B$12))),"",H119/Config!$B$12-1)</f>
+        <f>IF(OR(H119="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H119/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J119" s="33">
@@ -8359,7 +8359,7 @@
         <v/>
       </c>
       <c r="I120" s="31">
-        <f>IF(OR(H120="",NOT(ISNUMBER(Config!$B$12))),"",H120/Config!$B$12-1)</f>
+        <f>IF(OR(H120="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H120/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J120" s="33">
@@ -8388,7 +8388,7 @@
         <v/>
       </c>
       <c r="I121" s="31">
-        <f>IF(OR(H121="",NOT(ISNUMBER(Config!$B$12))),"",H121/Config!$B$12-1)</f>
+        <f>IF(OR(H121="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H121/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J121" s="33">
@@ -8417,7 +8417,7 @@
         <v/>
       </c>
       <c r="I122" s="31">
-        <f>IF(OR(H122="",NOT(ISNUMBER(Config!$B$12))),"",H122/Config!$B$12-1)</f>
+        <f>IF(OR(H122="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H122/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J122" s="33">
@@ -8446,7 +8446,7 @@
         <v/>
       </c>
       <c r="I123" s="31">
-        <f>IF(OR(H123="",NOT(ISNUMBER(Config!$B$12))),"",H123/Config!$B$12-1)</f>
+        <f>IF(OR(H123="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H123/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J123" s="33">
@@ -8475,7 +8475,7 @@
         <v/>
       </c>
       <c r="I124" s="31">
-        <f>IF(OR(H124="",NOT(ISNUMBER(Config!$B$12))),"",H124/Config!$B$12-1)</f>
+        <f>IF(OR(H124="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H124/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J124" s="33">
@@ -8504,7 +8504,7 @@
         <v/>
       </c>
       <c r="I125" s="31">
-        <f>IF(OR(H125="",NOT(ISNUMBER(Config!$B$12))),"",H125/Config!$B$12-1)</f>
+        <f>IF(OR(H125="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H125/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J125" s="33">
@@ -8533,7 +8533,7 @@
         <v/>
       </c>
       <c r="I126" s="31">
-        <f>IF(OR(H126="",NOT(ISNUMBER(Config!$B$12))),"",H126/Config!$B$12-1)</f>
+        <f>IF(OR(H126="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H126/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J126" s="33">
@@ -8562,7 +8562,7 @@
         <v/>
       </c>
       <c r="I127" s="31">
-        <f>IF(OR(H127="",NOT(ISNUMBER(Config!$B$12))),"",H127/Config!$B$12-1)</f>
+        <f>IF(OR(H127="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H127/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J127" s="33">
@@ -8591,7 +8591,7 @@
         <v/>
       </c>
       <c r="I128" s="31">
-        <f>IF(OR(H128="",NOT(ISNUMBER(Config!$B$12))),"",H128/Config!$B$12-1)</f>
+        <f>IF(OR(H128="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H128/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J128" s="33">
@@ -8620,7 +8620,7 @@
         <v/>
       </c>
       <c r="I129" s="31">
-        <f>IF(OR(H129="",NOT(ISNUMBER(Config!$B$12))),"",H129/Config!$B$12-1)</f>
+        <f>IF(OR(H129="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H129/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J129" s="33">
@@ -8649,7 +8649,7 @@
         <v/>
       </c>
       <c r="I130" s="31">
-        <f>IF(OR(H130="",NOT(ISNUMBER(Config!$B$12))),"",H130/Config!$B$12-1)</f>
+        <f>IF(OR(H130="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H130/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J130" s="33">
@@ -8678,7 +8678,7 @@
         <v/>
       </c>
       <c r="I131" s="31">
-        <f>IF(OR(H131="",NOT(ISNUMBER(Config!$B$12))),"",H131/Config!$B$12-1)</f>
+        <f>IF(OR(H131="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H131/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J131" s="33">
@@ -8707,7 +8707,7 @@
         <v/>
       </c>
       <c r="I132" s="31">
-        <f>IF(OR(H132="",NOT(ISNUMBER(Config!$B$12))),"",H132/Config!$B$12-1)</f>
+        <f>IF(OR(H132="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H132/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J132" s="33">
@@ -8736,7 +8736,7 @@
         <v/>
       </c>
       <c r="I133" s="31">
-        <f>IF(OR(H133="",NOT(ISNUMBER(Config!$B$12))),"",H133/Config!$B$12-1)</f>
+        <f>IF(OR(H133="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H133/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J133" s="33">
@@ -8765,7 +8765,7 @@
         <v/>
       </c>
       <c r="I134" s="31">
-        <f>IF(OR(H134="",NOT(ISNUMBER(Config!$B$12))),"",H134/Config!$B$12-1)</f>
+        <f>IF(OR(H134="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H134/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J134" s="33">
@@ -8794,7 +8794,7 @@
         <v/>
       </c>
       <c r="I135" s="31">
-        <f>IF(OR(H135="",NOT(ISNUMBER(Config!$B$12))),"",H135/Config!$B$12-1)</f>
+        <f>IF(OR(H135="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H135/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J135" s="33">
@@ -8823,7 +8823,7 @@
         <v/>
       </c>
       <c r="I136" s="31">
-        <f>IF(OR(H136="",NOT(ISNUMBER(Config!$B$12))),"",H136/Config!$B$12-1)</f>
+        <f>IF(OR(H136="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H136/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J136" s="33">
@@ -8852,7 +8852,7 @@
         <v/>
       </c>
       <c r="I137" s="31">
-        <f>IF(OR(H137="",NOT(ISNUMBER(Config!$B$12))),"",H137/Config!$B$12-1)</f>
+        <f>IF(OR(H137="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H137/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J137" s="33">
@@ -8881,7 +8881,7 @@
         <v/>
       </c>
       <c r="I138" s="31">
-        <f>IF(OR(H138="",NOT(ISNUMBER(Config!$B$12))),"",H138/Config!$B$12-1)</f>
+        <f>IF(OR(H138="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H138/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J138" s="33">
@@ -8910,7 +8910,7 @@
         <v/>
       </c>
       <c r="I139" s="31">
-        <f>IF(OR(H139="",NOT(ISNUMBER(Config!$B$12))),"",H139/Config!$B$12-1)</f>
+        <f>IF(OR(H139="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H139/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J139" s="33">
@@ -8939,7 +8939,7 @@
         <v/>
       </c>
       <c r="I140" s="31">
-        <f>IF(OR(H140="",NOT(ISNUMBER(Config!$B$12))),"",H140/Config!$B$12-1)</f>
+        <f>IF(OR(H140="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H140/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J140" s="33">
@@ -8968,7 +8968,7 @@
         <v/>
       </c>
       <c r="I141" s="31">
-        <f>IF(OR(H141="",NOT(ISNUMBER(Config!$B$12))),"",H141/Config!$B$12-1)</f>
+        <f>IF(OR(H141="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H141/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J141" s="33">
@@ -8997,7 +8997,7 @@
         <v/>
       </c>
       <c r="I142" s="31">
-        <f>IF(OR(H142="",NOT(ISNUMBER(Config!$B$12))),"",H142/Config!$B$12-1)</f>
+        <f>IF(OR(H142="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H142/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J142" s="33">
@@ -9026,7 +9026,7 @@
         <v/>
       </c>
       <c r="I143" s="31">
-        <f>IF(OR(H143="",NOT(ISNUMBER(Config!$B$12))),"",H143/Config!$B$12-1)</f>
+        <f>IF(OR(H143="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H143/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J143" s="33">
@@ -9055,7 +9055,7 @@
         <v/>
       </c>
       <c r="I144" s="31">
-        <f>IF(OR(H144="",NOT(ISNUMBER(Config!$B$12))),"",H144/Config!$B$12-1)</f>
+        <f>IF(OR(H144="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H144/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J144" s="33">
@@ -9084,7 +9084,7 @@
         <v/>
       </c>
       <c r="I145" s="31">
-        <f>IF(OR(H145="",NOT(ISNUMBER(Config!$B$12))),"",H145/Config!$B$12-1)</f>
+        <f>IF(OR(H145="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H145/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J145" s="33">
@@ -9113,7 +9113,7 @@
         <v/>
       </c>
       <c r="I146" s="31">
-        <f>IF(OR(H146="",NOT(ISNUMBER(Config!$B$12))),"",H146/Config!$B$12-1)</f>
+        <f>IF(OR(H146="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H146/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J146" s="33">
@@ -9142,7 +9142,7 @@
         <v/>
       </c>
       <c r="I147" s="31">
-        <f>IF(OR(H147="",NOT(ISNUMBER(Config!$B$12))),"",H147/Config!$B$12-1)</f>
+        <f>IF(OR(H147="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H147/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J147" s="33">
@@ -9171,7 +9171,7 @@
         <v/>
       </c>
       <c r="I148" s="31">
-        <f>IF(OR(H148="",NOT(ISNUMBER(Config!$B$12))),"",H148/Config!$B$12-1)</f>
+        <f>IF(OR(H148="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H148/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J148" s="33">
@@ -9200,7 +9200,7 @@
         <v/>
       </c>
       <c r="I149" s="31">
-        <f>IF(OR(H149="",NOT(ISNUMBER(Config!$B$12))),"",H149/Config!$B$12-1)</f>
+        <f>IF(OR(H149="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H149/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J149" s="33">
@@ -9229,7 +9229,7 @@
         <v/>
       </c>
       <c r="I150" s="31">
-        <f>IF(OR(H150="",NOT(ISNUMBER(Config!$B$12))),"",H150/Config!$B$12-1)</f>
+        <f>IF(OR(H150="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H150/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J150" s="33">
@@ -9258,7 +9258,7 @@
         <v/>
       </c>
       <c r="I151" s="31">
-        <f>IF(OR(H151="",NOT(ISNUMBER(Config!$B$12))),"",H151/Config!$B$12-1)</f>
+        <f>IF(OR(H151="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H151/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J151" s="33">
@@ -9287,7 +9287,7 @@
         <v/>
       </c>
       <c r="I152" s="31">
-        <f>IF(OR(H152="",NOT(ISNUMBER(Config!$B$12))),"",H152/Config!$B$12-1)</f>
+        <f>IF(OR(H152="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H152/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J152" s="33">
@@ -9316,7 +9316,7 @@
         <v/>
       </c>
       <c r="I153" s="31">
-        <f>IF(OR(H153="",NOT(ISNUMBER(Config!$B$12))),"",H153/Config!$B$12-1)</f>
+        <f>IF(OR(H153="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H153/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J153" s="33">
@@ -9345,7 +9345,7 @@
         <v/>
       </c>
       <c r="I154" s="31">
-        <f>IF(OR(H154="",NOT(ISNUMBER(Config!$B$12))),"",H154/Config!$B$12-1)</f>
+        <f>IF(OR(H154="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H154/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J154" s="33">
@@ -9374,7 +9374,7 @@
         <v/>
       </c>
       <c r="I155" s="31">
-        <f>IF(OR(H155="",NOT(ISNUMBER(Config!$B$12))),"",H155/Config!$B$12-1)</f>
+        <f>IF(OR(H155="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H155/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J155" s="33">
@@ -9403,7 +9403,7 @@
         <v/>
       </c>
       <c r="I156" s="31">
-        <f>IF(OR(H156="",NOT(ISNUMBER(Config!$B$12))),"",H156/Config!$B$12-1)</f>
+        <f>IF(OR(H156="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H156/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J156" s="33">
@@ -9432,7 +9432,7 @@
         <v/>
       </c>
       <c r="I157" s="31">
-        <f>IF(OR(H157="",NOT(ISNUMBER(Config!$B$12))),"",H157/Config!$B$12-1)</f>
+        <f>IF(OR(H157="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H157/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J157" s="33">
@@ -9461,7 +9461,7 @@
         <v/>
       </c>
       <c r="I158" s="31">
-        <f>IF(OR(H158="",NOT(ISNUMBER(Config!$B$12))),"",H158/Config!$B$12-1)</f>
+        <f>IF(OR(H158="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H158/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J158" s="33">
@@ -9490,7 +9490,7 @@
         <v/>
       </c>
       <c r="I159" s="31">
-        <f>IF(OR(H159="",NOT(ISNUMBER(Config!$B$12))),"",H159/Config!$B$12-1)</f>
+        <f>IF(OR(H159="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H159/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J159" s="33">
@@ -9519,7 +9519,7 @@
         <v/>
       </c>
       <c r="I160" s="31">
-        <f>IF(OR(H160="",NOT(ISNUMBER(Config!$B$12))),"",H160/Config!$B$12-1)</f>
+        <f>IF(OR(H160="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H160/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J160" s="33">
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="I161" s="31">
-        <f>IF(OR(H161="",NOT(ISNUMBER(Config!$B$12))),"",H161/Config!$B$12-1)</f>
+        <f>IF(OR(H161="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H161/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J161" s="33">
@@ -9577,7 +9577,7 @@
         <v/>
       </c>
       <c r="I162" s="31">
-        <f>IF(OR(H162="",NOT(ISNUMBER(Config!$B$12))),"",H162/Config!$B$12-1)</f>
+        <f>IF(OR(H162="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H162/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J162" s="33">
@@ -9606,7 +9606,7 @@
         <v/>
       </c>
       <c r="I163" s="31">
-        <f>IF(OR(H163="",NOT(ISNUMBER(Config!$B$12))),"",H163/Config!$B$12-1)</f>
+        <f>IF(OR(H163="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H163/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J163" s="33">
@@ -9635,7 +9635,7 @@
         <v/>
       </c>
       <c r="I164" s="31">
-        <f>IF(OR(H164="",NOT(ISNUMBER(Config!$B$12))),"",H164/Config!$B$12-1)</f>
+        <f>IF(OR(H164="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H164/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J164" s="33">
@@ -9664,7 +9664,7 @@
         <v/>
       </c>
       <c r="I165" s="31">
-        <f>IF(OR(H165="",NOT(ISNUMBER(Config!$B$12))),"",H165/Config!$B$12-1)</f>
+        <f>IF(OR(H165="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H165/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J165" s="33">
@@ -9693,7 +9693,7 @@
         <v/>
       </c>
       <c r="I166" s="31">
-        <f>IF(OR(H166="",NOT(ISNUMBER(Config!$B$12))),"",H166/Config!$B$12-1)</f>
+        <f>IF(OR(H166="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H166/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J166" s="33">
@@ -9722,7 +9722,7 @@
         <v/>
       </c>
       <c r="I167" s="31">
-        <f>IF(OR(H167="",NOT(ISNUMBER(Config!$B$12))),"",H167/Config!$B$12-1)</f>
+        <f>IF(OR(H167="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H167/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J167" s="33">
@@ -9751,7 +9751,7 @@
         <v/>
       </c>
       <c r="I168" s="31">
-        <f>IF(OR(H168="",NOT(ISNUMBER(Config!$B$12))),"",H168/Config!$B$12-1)</f>
+        <f>IF(OR(H168="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H168/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J168" s="33">
@@ -9780,7 +9780,7 @@
         <v/>
       </c>
       <c r="I169" s="31">
-        <f>IF(OR(H169="",NOT(ISNUMBER(Config!$B$12))),"",H169/Config!$B$12-1)</f>
+        <f>IF(OR(H169="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H169/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J169" s="33">
@@ -9809,7 +9809,7 @@
         <v/>
       </c>
       <c r="I170" s="31">
-        <f>IF(OR(H170="",NOT(ISNUMBER(Config!$B$12))),"",H170/Config!$B$12-1)</f>
+        <f>IF(OR(H170="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H170/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J170" s="33">
@@ -9838,7 +9838,7 @@
         <v/>
       </c>
       <c r="I171" s="31">
-        <f>IF(OR(H171="",NOT(ISNUMBER(Config!$B$12))),"",H171/Config!$B$12-1)</f>
+        <f>IF(OR(H171="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H171/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J171" s="33">
@@ -9867,7 +9867,7 @@
         <v/>
       </c>
       <c r="I172" s="31">
-        <f>IF(OR(H172="",NOT(ISNUMBER(Config!$B$12))),"",H172/Config!$B$12-1)</f>
+        <f>IF(OR(H172="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H172/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J172" s="33">
@@ -9896,7 +9896,7 @@
         <v/>
       </c>
       <c r="I173" s="31">
-        <f>IF(OR(H173="",NOT(ISNUMBER(Config!$B$12))),"",H173/Config!$B$12-1)</f>
+        <f>IF(OR(H173="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H173/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J173" s="33">
@@ -9925,7 +9925,7 @@
         <v/>
       </c>
       <c r="I174" s="31">
-        <f>IF(OR(H174="",NOT(ISNUMBER(Config!$B$12))),"",H174/Config!$B$12-1)</f>
+        <f>IF(OR(H174="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H174/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J174" s="33">
@@ -9954,7 +9954,7 @@
         <v/>
       </c>
       <c r="I175" s="31">
-        <f>IF(OR(H175="",NOT(ISNUMBER(Config!$B$12))),"",H175/Config!$B$12-1)</f>
+        <f>IF(OR(H175="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H175/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J175" s="33">
@@ -9983,7 +9983,7 @@
         <v/>
       </c>
       <c r="I176" s="31">
-        <f>IF(OR(H176="",NOT(ISNUMBER(Config!$B$12))),"",H176/Config!$B$12-1)</f>
+        <f>IF(OR(H176="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H176/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J176" s="33">
@@ -10012,7 +10012,7 @@
         <v/>
       </c>
       <c r="I177" s="31">
-        <f>IF(OR(H177="",NOT(ISNUMBER(Config!$B$12))),"",H177/Config!$B$12-1)</f>
+        <f>IF(OR(H177="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H177/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J177" s="33">
@@ -10041,7 +10041,7 @@
         <v/>
       </c>
       <c r="I178" s="31">
-        <f>IF(OR(H178="",NOT(ISNUMBER(Config!$B$12))),"",H178/Config!$B$12-1)</f>
+        <f>IF(OR(H178="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H178/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J178" s="33">
@@ -10070,7 +10070,7 @@
         <v/>
       </c>
       <c r="I179" s="31">
-        <f>IF(OR(H179="",NOT(ISNUMBER(Config!$B$12))),"",H179/Config!$B$12-1)</f>
+        <f>IF(OR(H179="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H179/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J179" s="33">
@@ -10099,7 +10099,7 @@
         <v/>
       </c>
       <c r="I180" s="31">
-        <f>IF(OR(H180="",NOT(ISNUMBER(Config!$B$12))),"",H180/Config!$B$12-1)</f>
+        <f>IF(OR(H180="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H180/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J180" s="33">
@@ -10128,7 +10128,7 @@
         <v/>
       </c>
       <c r="I181" s="31">
-        <f>IF(OR(H181="",NOT(ISNUMBER(Config!$B$12))),"",H181/Config!$B$12-1)</f>
+        <f>IF(OR(H181="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H181/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J181" s="33">
@@ -10157,7 +10157,7 @@
         <v/>
       </c>
       <c r="I182" s="31">
-        <f>IF(OR(H182="",NOT(ISNUMBER(Config!$B$12))),"",H182/Config!$B$12-1)</f>
+        <f>IF(OR(H182="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H182/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J182" s="33">
@@ -10186,7 +10186,7 @@
         <v/>
       </c>
       <c r="I183" s="31">
-        <f>IF(OR(H183="",NOT(ISNUMBER(Config!$B$12))),"",H183/Config!$B$12-1)</f>
+        <f>IF(OR(H183="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H183/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J183" s="33">
@@ -10215,7 +10215,7 @@
         <v/>
       </c>
       <c r="I184" s="31">
-        <f>IF(OR(H184="",NOT(ISNUMBER(Config!$B$12))),"",H184/Config!$B$12-1)</f>
+        <f>IF(OR(H184="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H184/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J184" s="33">
@@ -10244,7 +10244,7 @@
         <v/>
       </c>
       <c r="I185" s="31">
-        <f>IF(OR(H185="",NOT(ISNUMBER(Config!$B$12))),"",H185/Config!$B$12-1)</f>
+        <f>IF(OR(H185="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H185/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J185" s="33">
@@ -10273,7 +10273,7 @@
         <v/>
       </c>
       <c r="I186" s="31">
-        <f>IF(OR(H186="",NOT(ISNUMBER(Config!$B$12))),"",H186/Config!$B$12-1)</f>
+        <f>IF(OR(H186="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H186/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J186" s="33">
@@ -10302,7 +10302,7 @@
         <v/>
       </c>
       <c r="I187" s="31">
-        <f>IF(OR(H187="",NOT(ISNUMBER(Config!$B$12))),"",H187/Config!$B$12-1)</f>
+        <f>IF(OR(H187="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H187/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J187" s="33">
@@ -10331,7 +10331,7 @@
         <v/>
       </c>
       <c r="I188" s="31">
-        <f>IF(OR(H188="",NOT(ISNUMBER(Config!$B$12))),"",H188/Config!$B$12-1)</f>
+        <f>IF(OR(H188="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H188/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J188" s="33">
@@ -10360,7 +10360,7 @@
         <v/>
       </c>
       <c r="I189" s="31">
-        <f>IF(OR(H189="",NOT(ISNUMBER(Config!$B$12))),"",H189/Config!$B$12-1)</f>
+        <f>IF(OR(H189="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H189/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J189" s="33">
@@ -10389,7 +10389,7 @@
         <v/>
       </c>
       <c r="I190" s="31">
-        <f>IF(OR(H190="",NOT(ISNUMBER(Config!$B$12))),"",H190/Config!$B$12-1)</f>
+        <f>IF(OR(H190="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H190/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J190" s="33">
@@ -10418,7 +10418,7 @@
         <v/>
       </c>
       <c r="I191" s="31">
-        <f>IF(OR(H191="",NOT(ISNUMBER(Config!$B$12))),"",H191/Config!$B$12-1)</f>
+        <f>IF(OR(H191="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H191/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J191" s="33">
@@ -10447,7 +10447,7 @@
         <v/>
       </c>
       <c r="I192" s="31">
-        <f>IF(OR(H192="",NOT(ISNUMBER(Config!$B$12))),"",H192/Config!$B$12-1)</f>
+        <f>IF(OR(H192="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H192/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J192" s="33">
@@ -10476,7 +10476,7 @@
         <v/>
       </c>
       <c r="I193" s="31">
-        <f>IF(OR(H193="",NOT(ISNUMBER(Config!$B$12))),"",H193/Config!$B$12-1)</f>
+        <f>IF(OR(H193="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H193/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J193" s="33">
@@ -10505,7 +10505,7 @@
         <v/>
       </c>
       <c r="I194" s="31">
-        <f>IF(OR(H194="",NOT(ISNUMBER(Config!$B$12))),"",H194/Config!$B$12-1)</f>
+        <f>IF(OR(H194="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H194/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J194" s="33">
@@ -10534,7 +10534,7 @@
         <v/>
       </c>
       <c r="I195" s="31">
-        <f>IF(OR(H195="",NOT(ISNUMBER(Config!$B$12))),"",H195/Config!$B$12-1)</f>
+        <f>IF(OR(H195="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H195/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J195" s="33">
@@ -10563,7 +10563,7 @@
         <v/>
       </c>
       <c r="I196" s="31">
-        <f>IF(OR(H196="",NOT(ISNUMBER(Config!$B$12))),"",H196/Config!$B$12-1)</f>
+        <f>IF(OR(H196="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H196/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J196" s="33">
@@ -10592,7 +10592,7 @@
         <v/>
       </c>
       <c r="I197" s="31">
-        <f>IF(OR(H197="",NOT(ISNUMBER(Config!$B$12))),"",H197/Config!$B$12-1)</f>
+        <f>IF(OR(H197="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H197/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J197" s="33">
@@ -10621,7 +10621,7 @@
         <v/>
       </c>
       <c r="I198" s="31">
-        <f>IF(OR(H198="",NOT(ISNUMBER(Config!$B$12))),"",H198/Config!$B$12-1)</f>
+        <f>IF(OR(H198="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H198/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J198" s="33">
@@ -10650,7 +10650,7 @@
         <v/>
       </c>
       <c r="I199" s="31">
-        <f>IF(OR(H199="",NOT(ISNUMBER(Config!$B$12))),"",H199/Config!$B$12-1)</f>
+        <f>IF(OR(H199="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H199/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J199" s="33">
@@ -10679,7 +10679,7 @@
         <v/>
       </c>
       <c r="I200" s="31">
-        <f>IF(OR(H200="",NOT(ISNUMBER(Config!$B$12))),"",H200/Config!$B$12-1)</f>
+        <f>IF(OR(H200="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H200/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J200" s="33">
@@ -10708,7 +10708,7 @@
         <v/>
       </c>
       <c r="I201" s="31">
-        <f>IF(OR(H201="",NOT(ISNUMBER(Config!$B$12))),"",H201/Config!$B$12-1)</f>
+        <f>IF(OR(H201="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H201/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J201" s="33">
@@ -10737,7 +10737,7 @@
         <v/>
       </c>
       <c r="I202" s="31">
-        <f>IF(OR(H202="",NOT(ISNUMBER(Config!$B$12))),"",H202/Config!$B$12-1)</f>
+        <f>IF(OR(H202="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H202/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J202" s="33">
@@ -10766,7 +10766,7 @@
         <v/>
       </c>
       <c r="I203" s="31">
-        <f>IF(OR(H203="",NOT(ISNUMBER(Config!$B$12))),"",H203/Config!$B$12-1)</f>
+        <f>IF(OR(H203="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H203/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J203" s="33">
@@ -10795,7 +10795,7 @@
         <v/>
       </c>
       <c r="I204" s="31">
-        <f>IF(OR(H204="",NOT(ISNUMBER(Config!$B$12))),"",H204/Config!$B$12-1)</f>
+        <f>IF(OR(H204="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H204/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J204" s="33">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -1089,12 +1089,12 @@
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo")))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&gt;0,COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&amp;" caso(s) com valor ou horas inválidos",COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo"))))</f>
         <v>10 de 38</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,SUM('Nossos casos'!$K$5:$K$204))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&gt;0,COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&amp;" caso(s) com valor ou horas inválidos",SUM('Nossos casos'!$K$5:$K$204)))</f>
         <v>11876.6896774193</v>
       </c>
       <c r="H5" s="12" t="n"/>
@@ -1181,11 +1181,11 @@
         </is>
       </c>
       <c r="F9" s="25">
-        <f>IF(OR(A9="",C9=""),"",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A9="",C9=""),"",IF(NOT(ISNUMBER(C9)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G9" s="25">
-        <f>IF(OR(A9="",D9=""),"",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A9="",D9=""),"",IF(NOT(ISNUMBER(D9)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H9" s="25">
@@ -1220,11 +1220,11 @@
         </is>
       </c>
       <c r="F10" s="25">
-        <f>IF(OR(A10="",C10=""),"",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A10="",C10=""),"",IF(NOT(ISNUMBER(C10)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G10" s="25">
-        <f>IF(OR(A10="",D10=""),"",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A10="",D10=""),"",IF(NOT(ISNUMBER(D10)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H10" s="25">
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="F11" s="25">
-        <f>IF(OR(A11="",C11=""),"",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A11="",C11=""),"",IF(NOT(ISNUMBER(C11)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12)))</f>
         <v>6394.0064516129</v>
       </c>
       <c r="G11" s="25">
-        <f>IF(OR(A11="",D11=""),"",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A11="",D11=""),"",IF(NOT(ISNUMBER(D11)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13)))</f>
         <v>16869.2936170213</v>
       </c>
       <c r="H11" s="25">
@@ -1298,11 +1298,11 @@
         </is>
       </c>
       <c r="F12" s="25">
-        <f>IF(OR(A12="",C12=""),"",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A12="",C12=""),"",IF(NOT(ISNUMBER(C12)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G12" s="25">
-        <f>IF(OR(A12="",D12=""),"",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A12="",D12=""),"",IF(NOT(ISNUMBER(D12)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H12" s="25">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="F13" s="25">
-        <f>IF(OR(A13="",C13=""),"",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A13="",C13=""),"",IF(NOT(ISNUMBER(C13)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G13" s="25">
-        <f>IF(OR(A13="",D13=""),"",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A13="",D13=""),"",IF(NOT(ISNUMBER(D13)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H13" s="25">
@@ -1376,11 +1376,11 @@
         </is>
       </c>
       <c r="F14" s="25">
-        <f>IF(OR(A14="",C14=""),"",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A14="",C14=""),"",IF(NOT(ISNUMBER(C14)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G14" s="25">
-        <f>IF(OR(A14="",D14=""),"",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A14="",D14=""),"",IF(NOT(ISNUMBER(D14)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H14" s="25">
@@ -1415,11 +1415,11 @@
         </is>
       </c>
       <c r="F15" s="25">
-        <f>IF(OR(A15="",C15=""),"",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A15="",C15=""),"",IF(NOT(ISNUMBER(C15)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G15" s="25">
-        <f>IF(OR(A15="",D15=""),"",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A15="",D15=""),"",IF(NOT(ISNUMBER(D15)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H15" s="25">
@@ -1454,11 +1454,11 @@
         </is>
       </c>
       <c r="F16" s="25">
-        <f>IF(OR(A16="",C16=""),"",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A16="",C16=""),"",IF(NOT(ISNUMBER(C16)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12)))</f>
         <v>4475.80451612903</v>
       </c>
       <c r="G16" s="25">
-        <f>IF(OR(A16="",D16=""),"",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A16="",D16=""),"",IF(NOT(ISNUMBER(D16)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13)))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H16" s="25">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="F17" s="25">
-        <f>IF(OR(A17="",C17=""),"",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A17="",C17=""),"",IF(NOT(ISNUMBER(C17)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G17" s="25">
-        <f>IF(OR(A17="",D17=""),"",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A17="",D17=""),"",IF(NOT(ISNUMBER(D17)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H17" s="25">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="F18" s="25">
-        <f>IF(OR(A18="",C18=""),"",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A18="",C18=""),"",IF(NOT(ISNUMBER(C18)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G18" s="25">
-        <f>IF(OR(A18="",D18=""),"",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A18="",D18=""),"",IF(NOT(ISNUMBER(D18)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H18" s="25">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="F19" s="25">
-        <f>IF(OR(A19="",C19=""),"",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A19="",C19=""),"",IF(NOT(ISNUMBER(C19)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G19" s="25">
-        <f>IF(OR(A19="",D19=""),"",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A19="",D19=""),"",IF(NOT(ISNUMBER(D19)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H19" s="25">
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="F20" s="25">
-        <f>IF(OR(A20="",C20=""),"",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A20="",C20=""),"",IF(NOT(ISNUMBER(C20)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G20" s="25">
-        <f>IF(OR(A20="",D20=""),"",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A20="",D20=""),"",IF(NOT(ISNUMBER(D20)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H20" s="25">
@@ -1649,11 +1649,11 @@
         </is>
       </c>
       <c r="F21" s="25">
-        <f>IF(OR(A21="",C21=""),"",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A21="",C21=""),"",IF(NOT(ISNUMBER(C21)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12)))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G21" s="25">
-        <f>IF(OR(A21="",D21=""),"",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A21="",D21=""),"",IF(NOT(ISNUMBER(D21)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13)))</f>
         <v>10121.5761702128</v>
       </c>
       <c r="H21" s="25">
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="F22" s="25">
-        <f>IF(OR(A22="",C22=""),"",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A22="",C22=""),"",IF(NOT(ISNUMBER(C22)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G22" s="25">
-        <f>IF(OR(A22="",D22=""),"",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A22="",D22=""),"",IF(NOT(ISNUMBER(D22)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H22" s="25">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="F23" s="25">
-        <f>IF(OR(A23="",C23=""),"",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A23="",C23=""),"",IF(NOT(ISNUMBER(C23)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G23" s="25">
-        <f>IF(OR(A23="",D23=""),"",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A23="",D23=""),"",IF(NOT(ISNUMBER(D23)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H23" s="25">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="F24" s="25">
-        <f>IF(OR(A24="",C24=""),"",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A24="",C24=""),"",IF(NOT(ISNUMBER(C24)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12)))</f>
         <v>511.520516129032</v>
       </c>
       <c r="G24" s="25">
-        <f>IF(OR(A24="",D24=""),"",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A24="",D24=""),"",IF(NOT(ISNUMBER(D24)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13)))</f>
         <v>2024.31523404255</v>
       </c>
       <c r="H24" s="25">
@@ -1805,11 +1805,11 @@
         </is>
       </c>
       <c r="F25" s="25">
-        <f>IF(OR(A25="",C25=""),"",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A25="",C25=""),"",IF(NOT(ISNUMBER(C25)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G25" s="25">
-        <f>IF(OR(A25="",D25=""),"",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A25="",D25=""),"",IF(NOT(ISNUMBER(D25)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H25" s="25">
@@ -1844,11 +1844,11 @@
         </is>
       </c>
       <c r="F26" s="25">
-        <f>IF(OR(A26="",C26=""),"",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A26="",C26=""),"",IF(NOT(ISNUMBER(C26)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12)))</f>
         <v>7672.80774193548</v>
       </c>
       <c r="G26" s="25">
-        <f>IF(OR(A26="",D26=""),"",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A26="",D26=""),"",IF(NOT(ISNUMBER(D26)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13)))</f>
         <v>20243.1523404255</v>
       </c>
       <c r="H26" s="25">
@@ -1883,11 +1883,11 @@
         </is>
       </c>
       <c r="F27" s="25">
-        <f>IF(OR(A27="",C27=""),"",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A27="",C27=""),"",IF(NOT(ISNUMBER(C27)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G27" s="25">
-        <f>IF(OR(A27="",D27=""),"",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A27="",D27=""),"",IF(NOT(ISNUMBER(D27)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H27" s="25">
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="F28" s="25">
-        <f>IF(OR(A28="",C28=""),"",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A28="",C28=""),"",IF(NOT(ISNUMBER(C28)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G28" s="25">
-        <f>IF(OR(A28="",D28=""),"",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A28="",D28=""),"",IF(NOT(ISNUMBER(D28)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H28" s="25">
@@ -1961,11 +1961,11 @@
         </is>
       </c>
       <c r="F29" s="25">
-        <f>IF(OR(A29="",C29=""),"",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A29="",C29=""),"",IF(NOT(ISNUMBER(C29)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G29" s="25">
-        <f>IF(OR(A29="",D29=""),"",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A29="",D29=""),"",IF(NOT(ISNUMBER(D29)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H29" s="25">
@@ -2000,11 +2000,11 @@
         </is>
       </c>
       <c r="F30" s="25">
-        <f>IF(OR(A30="",C30=""),"",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A30="",C30=""),"",IF(NOT(ISNUMBER(C30)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G30" s="25">
-        <f>IF(OR(A30="",D30=""),"",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A30="",D30=""),"",IF(NOT(ISNUMBER(D30)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H30" s="25">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="F31" s="25">
-        <f>IF(OR(A31="",C31=""),"",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A31="",C31=""),"",IF(NOT(ISNUMBER(C31)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12)))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G31" s="25">
-        <f>IF(OR(A31="",D31=""),"",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A31="",D31=""),"",IF(NOT(ISNUMBER(D31)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13)))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H31" s="25">
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="F32" s="25">
-        <f>IF(OR(A32="",C32=""),"",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A32="",C32=""),"",IF(NOT(ISNUMBER(C32)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G32" s="25">
-        <f>IF(OR(A32="",D32=""),"",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A32="",D32=""),"",IF(NOT(ISNUMBER(D32)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H32" s="25">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="F33" s="25">
-        <f>IF(OR(A33="",C33=""),"",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A33="",C33=""),"",IF(NOT(ISNUMBER(C33)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G33" s="25">
-        <f>IF(OR(A33="",D33=""),"",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A33="",D33=""),"",IF(NOT(ISNUMBER(D33)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H33" s="25">
@@ -2140,11 +2140,11 @@
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="24" t="n"/>
       <c r="F34" s="25">
-        <f>IF(OR(A34="",C34=""),"",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A34="",C34=""),"",IF(NOT(ISNUMBER(C34)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G34" s="25">
-        <f>IF(OR(A34="",D34=""),"",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A34="",D34=""),"",IF(NOT(ISNUMBER(D34)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H34" s="25">
@@ -2163,11 +2163,11 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="24" t="n"/>
       <c r="F35" s="25">
-        <f>IF(OR(A35="",C35=""),"",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A35="",C35=""),"",IF(NOT(ISNUMBER(C35)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G35" s="25">
-        <f>IF(OR(A35="",D35=""),"",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A35="",D35=""),"",IF(NOT(ISNUMBER(D35)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H35" s="25">
@@ -2186,11 +2186,11 @@
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="24" t="n"/>
       <c r="F36" s="25">
-        <f>IF(OR(A36="",C36=""),"",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A36="",C36=""),"",IF(NOT(ISNUMBER(C36)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G36" s="25">
-        <f>IF(OR(A36="",D36=""),"",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A36="",D36=""),"",IF(NOT(ISNUMBER(D36)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H36" s="25">
@@ -2209,11 +2209,11 @@
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="24" t="n"/>
       <c r="F37" s="25">
-        <f>IF(OR(A37="",C37=""),"",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A37="",C37=""),"",IF(NOT(ISNUMBER(C37)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G37" s="25">
-        <f>IF(OR(A37="",D37=""),"",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A37="",D37=""),"",IF(NOT(ISNUMBER(D37)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H37" s="25">
@@ -2232,11 +2232,11 @@
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="24" t="n"/>
       <c r="F38" s="25">
-        <f>IF(OR(A38="",C38=""),"",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A38="",C38=""),"",IF(NOT(ISNUMBER(C38)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G38" s="25">
-        <f>IF(OR(A38="",D38=""),"",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A38="",D38=""),"",IF(NOT(ISNUMBER(D38)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H38" s="25">
@@ -2255,11 +2255,11 @@
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="25">
-        <f>IF(OR(A39="",C39=""),"",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A39="",C39=""),"",IF(NOT(ISNUMBER(C39)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G39" s="25">
-        <f>IF(OR(A39="",D39=""),"",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A39="",D39=""),"",IF(NOT(ISNUMBER(D39)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H39" s="25">
@@ -2278,11 +2278,11 @@
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="24" t="n"/>
       <c r="F40" s="25">
-        <f>IF(OR(A40="",C40=""),"",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A40="",C40=""),"",IF(NOT(ISNUMBER(C40)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G40" s="25">
-        <f>IF(OR(A40="",D40=""),"",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A40="",D40=""),"",IF(NOT(ISNUMBER(D40)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H40" s="25">
@@ -2301,11 +2301,11 @@
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="24" t="n"/>
       <c r="F41" s="25">
-        <f>IF(OR(A41="",C41=""),"",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A41="",C41=""),"",IF(NOT(ISNUMBER(C41)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G41" s="25">
-        <f>IF(OR(A41="",D41=""),"",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A41="",D41=""),"",IF(NOT(ISNUMBER(D41)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H41" s="25">
@@ -2324,11 +2324,11 @@
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="25">
-        <f>IF(OR(A42="",C42=""),"",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A42="",C42=""),"",IF(NOT(ISNUMBER(C42)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G42" s="25">
-        <f>IF(OR(A42="",D42=""),"",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A42="",D42=""),"",IF(NOT(ISNUMBER(D42)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H42" s="25">
@@ -2347,11 +2347,11 @@
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="24" t="n"/>
       <c r="F43" s="25">
-        <f>IF(OR(A43="",C43=""),"",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A43="",C43=""),"",IF(NOT(ISNUMBER(C43)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G43" s="25">
-        <f>IF(OR(A43="",D43=""),"",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A43="",D43=""),"",IF(NOT(ISNUMBER(D43)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H43" s="25">
@@ -2370,11 +2370,11 @@
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="24" t="n"/>
       <c r="F44" s="25">
-        <f>IF(OR(A44="",C44=""),"",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A44="",C44=""),"",IF(NOT(ISNUMBER(C44)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G44" s="25">
-        <f>IF(OR(A44="",D44=""),"",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A44="",D44=""),"",IF(NOT(ISNUMBER(D44)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H44" s="25">
@@ -2393,11 +2393,11 @@
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="24" t="n"/>
       <c r="F45" s="25">
-        <f>IF(OR(A45="",C45=""),"",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A45="",C45=""),"",IF(NOT(ISNUMBER(C45)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G45" s="25">
-        <f>IF(OR(A45="",D45=""),"",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A45="",D45=""),"",IF(NOT(ISNUMBER(D45)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H45" s="25">
@@ -2416,11 +2416,11 @@
       <c r="D46" s="23" t="n"/>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="25">
-        <f>IF(OR(A46="",C46=""),"",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A46="",C46=""),"",IF(NOT(ISNUMBER(C46)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G46" s="25">
-        <f>IF(OR(A46="",D46=""),"",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A46="",D46=""),"",IF(NOT(ISNUMBER(D46)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H46" s="25">
@@ -2439,11 +2439,11 @@
       <c r="D47" s="23" t="n"/>
       <c r="E47" s="24" t="n"/>
       <c r="F47" s="25">
-        <f>IF(OR(A47="",C47=""),"",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A47="",C47=""),"",IF(NOT(ISNUMBER(C47)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G47" s="25">
-        <f>IF(OR(A47="",D47=""),"",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A47="",D47=""),"",IF(NOT(ISNUMBER(D47)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H47" s="25">
@@ -2462,11 +2462,11 @@
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="24" t="n"/>
       <c r="F48" s="25">
-        <f>IF(OR(A48="",C48=""),"",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12))</f>
+        <f>IF(OR(A48="",C48=""),"",IF(NOT(ISNUMBER(C48)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G48" s="25">
-        <f>IF(OR(A48="",D48=""),"",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13))</f>
+        <f>IF(OR(A48="",D48=""),"",IF(NOT(ISNUMBER(D48)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H48" s="25">
@@ -4132,19 +4132,19 @@
         <v>72</v>
       </c>
       <c r="H5" s="30">
-        <f>IF(OR(A5="",G5="",G5=0,F5=""),"",F5/G5)</f>
+        <f>IF(OR(A5="",G5="",F5=""),"",IF(OR(NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"valor ou horas inválidos",IF(G5=0,"",F5/G5)))</f>
         <v>250</v>
       </c>
       <c r="I5" s="31">
-        <f>IF(OR(H5="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H5/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H5)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H5/Config!$B$12-1))</f>
         <v>0.954955800341247</v>
       </c>
       <c r="J5" s="33" t="str">
-        <f>IF(H5="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H5&lt;Config!$B$12,"Abaixo do mínimo",IF(H5&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H5="","",IF(NOT(ISNUMBER(H5)),H5,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H5&lt;Config!$B$12,"Abaixo do mínimo",IF(H5&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K5" s="25">
-        <f>IF(OR(H5="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G5-F5))</f>
+        <f>IF(OR(NOT(ISNUMBER(H5)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G5-F5))</f>
         <v>0</v>
       </c>
       <c r="L5" s="41">
@@ -4185,19 +4185,19 @@
         <v>70</v>
       </c>
       <c r="H6" s="30">
-        <f>IF(OR(A6="",G6="",G6=0,F6=""),"",F6/G6)</f>
+        <f>IF(OR(A6="",G6="",F6=""),"",IF(OR(NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"valor ou horas inválidos",IF(G6=0,"",F6/G6)))</f>
         <v>85.7142857142857</v>
       </c>
       <c r="I6" s="31">
-        <f>IF(OR(H6="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H6/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H6)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H6/Config!$B$12-1))</f>
         <v>-0.329729439883001</v>
       </c>
       <c r="J6" s="33" t="str">
-        <f>IF(H6="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H6&lt;Config!$B$12,"Abaixo do mínimo",IF(H6&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H6="","",IF(NOT(ISNUMBER(H6)),H6,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H6&lt;Config!$B$12,"Abaixo do mínimo",IF(H6&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K6" s="25">
-        <f>IF(OR(H6="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G6-F6))</f>
+        <f>IF(OR(NOT(ISNUMBER(H6)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G6-F6))</f>
         <v>2951.60903225806</v>
       </c>
       <c r="L6" s="41">
@@ -4238,19 +4238,19 @@
         <v>90</v>
       </c>
       <c r="H7" s="30">
-        <f>IF(OR(A7="",G7="",G7=0,F7=""),"",F7/G7)</f>
+        <f>IF(OR(A7="",G7="",F7=""),"",IF(OR(NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"valor ou horas inválidos",IF(G7=0,"",F7/G7)))</f>
         <v>172.222222222222</v>
       </c>
       <c r="I7" s="31">
-        <f>IF(OR(H7="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H7/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H7)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H7/Config!$B$12-1))</f>
         <v>0.34674732912397</v>
       </c>
       <c r="J7" s="33" t="str">
-        <f>IF(H7="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H7&lt;Config!$B$12,"Abaixo do mínimo",IF(H7&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H7="","",IF(NOT(ISNUMBER(H7)),H7,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H7&lt;Config!$B$12,"Abaixo do mínimo",IF(H7&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K7" s="25">
-        <f>IF(OR(H7="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G7-F7))</f>
+        <f>IF(OR(NOT(ISNUMBER(H7)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G7-F7))</f>
         <v>0</v>
       </c>
       <c r="L7" s="41">
@@ -4291,19 +4291,19 @@
         <v>40</v>
       </c>
       <c r="H8" s="30">
-        <f>IF(OR(A8="",G8="",G8=0,F8=""),"",F8/G8)</f>
+        <f>IF(OR(A8="",G8="",F8=""),"",IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"valor ou horas inválidos",IF(G8=0,"",F8/G8)))</f>
         <v>135</v>
       </c>
       <c r="I8" s="31">
-        <f>IF(OR(H8="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H8/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H8)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H8/Config!$B$12-1))</f>
         <v>0.0556761321842736</v>
       </c>
       <c r="J8" s="33" t="str">
-        <f>IF(H8="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H8&lt;Config!$B$12,"Abaixo do mínimo",IF(H8&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H8="","",IF(NOT(ISNUMBER(H8)),H8,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H8&lt;Config!$B$12,"Abaixo do mínimo",IF(H8&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K8" s="25">
-        <f>IF(OR(H8="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G8-F8))</f>
+        <f>IF(OR(NOT(ISNUMBER(H8)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G8-F8))</f>
         <v>0</v>
       </c>
       <c r="L8" s="41">
@@ -4344,19 +4344,19 @@
         <v>45</v>
       </c>
       <c r="H9" s="30">
-        <f>IF(OR(A9="",G9="",G9=0,F9=""),"",F9/G9)</f>
+        <f>IF(OR(A9="",G9="",F9=""),"",IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"valor ou horas inválidos",IF(G9=0,"",F9/G9)))</f>
         <v>186.666666666667</v>
       </c>
       <c r="I9" s="31">
-        <f>IF(OR(H9="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H9/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H9)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H9/Config!$B$12-1))</f>
         <v>0.459700330921465</v>
       </c>
       <c r="J9" s="33" t="str">
-        <f>IF(H9="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H9&lt;Config!$B$12,"Abaixo do mínimo",IF(H9&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H9="","",IF(NOT(ISNUMBER(H9)),H9,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H9&lt;Config!$B$12,"Abaixo do mínimo",IF(H9&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K9" s="25">
-        <f>IF(OR(H9="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G9-F9))</f>
+        <f>IF(OR(NOT(ISNUMBER(H9)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G9-F9))</f>
         <v>0</v>
       </c>
       <c r="L9" s="41">
@@ -4397,19 +4397,19 @@
         <v>24</v>
       </c>
       <c r="H10" s="30">
-        <f>IF(OR(A10="",G10="",G10=0,F10=""),"",F10/G10)</f>
+        <f>IF(OR(A10="",G10="",F10=""),"",IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"valor ou horas inválidos",IF(G10=0,"",F10/G10)))</f>
         <v>187.5</v>
       </c>
       <c r="I10" s="31">
-        <f>IF(OR(H10="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H10/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H10)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H10/Config!$B$12-1))</f>
         <v>0.466216850255936</v>
       </c>
       <c r="J10" s="33" t="str">
-        <f>IF(H10="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H10&lt;Config!$B$12,"Abaixo do mínimo",IF(H10&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H10="","",IF(NOT(ISNUMBER(H10)),H10,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H10&lt;Config!$B$12,"Abaixo do mínimo",IF(H10&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K10" s="25">
-        <f>IF(OR(H10="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G10-F10))</f>
+        <f>IF(OR(NOT(ISNUMBER(H10)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G10-F10))</f>
         <v>0</v>
       </c>
       <c r="L10" s="41">
@@ -4450,19 +4450,19 @@
         <v>72</v>
       </c>
       <c r="H11" s="30">
-        <f>IF(OR(A11="",G11="",G11=0,F11=""),"",F11/G11)</f>
+        <f>IF(OR(A11="",G11="",F11=""),"",IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"valor ou horas inválidos",IF(G11=0,"",F11/G11)))</f>
         <v>183.333333333333</v>
       </c>
       <c r="I11" s="31">
-        <f>IF(OR(H11="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H11/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H11)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H11/Config!$B$12-1))</f>
         <v>0.433634253583582</v>
       </c>
       <c r="J11" s="33" t="str">
-        <f>IF(H11="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H11&lt;Config!$B$12,"Abaixo do mínimo",IF(H11&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H11="","",IF(NOT(ISNUMBER(H11)),H11,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H11&lt;Config!$B$12,"Abaixo do mínimo",IF(H11&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K11" s="25">
-        <f>IF(OR(H11="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G11-F11))</f>
+        <f>IF(OR(NOT(ISNUMBER(H11)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G11-F11))</f>
         <v>0</v>
       </c>
       <c r="L11" s="41">
@@ -4503,19 +4503,19 @@
         <v>80</v>
       </c>
       <c r="H12" s="30">
-        <f>IF(OR(A12="",G12="",G12=0,F12=""),"",F12/G12)</f>
+        <f>IF(OR(A12="",G12="",F12=""),"",IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"valor ou horas inválidos",IF(G12=0,"",F12/G12)))</f>
         <v>118.75</v>
       </c>
       <c r="I12" s="31">
-        <f>IF(OR(H12="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H12/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H12)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H12/Config!$B$12-1))</f>
         <v>-0.0713959948379075</v>
       </c>
       <c r="J12" s="33" t="str">
-        <f>IF(H12="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H12&lt;Config!$B$12,"Abaixo do mínimo",IF(H12&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H12="","",IF(NOT(ISNUMBER(H12)),H12,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H12&lt;Config!$B$12,"Abaixo do mínimo",IF(H12&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K12" s="25">
-        <f>IF(OR(H12="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G12-F12))</f>
+        <f>IF(OR(NOT(ISNUMBER(H12)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G12-F12))</f>
         <v>730.410322580643</v>
       </c>
       <c r="L12" s="41">
@@ -4556,19 +4556,19 @@
         <v>45</v>
       </c>
       <c r="H13" s="30">
-        <f>IF(OR(A13="",G13="",G13=0,F13=""),"",F13/G13)</f>
+        <f>IF(OR(A13="",G13="",F13=""),"",IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"valor ou horas inválidos",IF(G13=0,"",F13/G13)))</f>
         <v>88.8888888888889</v>
       </c>
       <c r="I13" s="31">
-        <f>IF(OR(H13="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H13/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H13)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H13/Config!$B$12-1))</f>
         <v>-0.304904604323112</v>
       </c>
       <c r="J13" s="33" t="str">
-        <f>IF(H13="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H13&lt;Config!$B$12,"Abaixo do mínimo",IF(H13&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H13="","",IF(NOT(ISNUMBER(H13)),H13,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H13&lt;Config!$B$12,"Abaixo do mínimo",IF(H13&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K13" s="25">
-        <f>IF(OR(H13="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G13-F13))</f>
+        <f>IF(OR(NOT(ISNUMBER(H13)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G13-F13))</f>
         <v>1754.60580645161</v>
       </c>
       <c r="L13" s="41">
@@ -4609,19 +4609,19 @@
         <v>95</v>
       </c>
       <c r="H14" s="30">
-        <f>IF(OR(A14="",G14="",G14=0,F14=""),"",F14/G14)</f>
+        <f>IF(OR(A14="",G14="",F14=""),"",IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"valor ou horas inválidos",IF(G14=0,"",F14/G14)))</f>
         <v>157.894736842105</v>
       </c>
       <c r="I14" s="31">
-        <f>IF(OR(H14="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H14/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H14)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H14/Config!$B$12-1))</f>
         <v>0.234708926531314</v>
       </c>
       <c r="J14" s="33" t="str">
-        <f>IF(H14="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H14&lt;Config!$B$12,"Abaixo do mínimo",IF(H14&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H14="","",IF(NOT(ISNUMBER(H14)),H14,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H14&lt;Config!$B$12,"Abaixo do mínimo",IF(H14&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K14" s="25">
-        <f>IF(OR(H14="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G14-F14))</f>
+        <f>IF(OR(NOT(ISNUMBER(H14)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G14-F14))</f>
         <v>0</v>
       </c>
       <c r="L14" s="41">
@@ -4662,19 +4662,19 @@
         <v>60</v>
       </c>
       <c r="H15" s="30">
-        <f>IF(OR(A15="",G15="",G15=0,F15=""),"",F15/G15)</f>
+        <f>IF(OR(A15="",G15="",F15=""),"",IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"valor ou horas inválidos",IF(G15=0,"",F15/G15)))</f>
         <v>170</v>
       </c>
       <c r="I15" s="31">
-        <f>IF(OR(H15="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H15/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H15)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H15/Config!$B$12-1))</f>
         <v>0.329369944232048</v>
       </c>
       <c r="J15" s="33" t="str">
-        <f>IF(H15="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H15&lt;Config!$B$12,"Abaixo do mínimo",IF(H15&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H15="","",IF(NOT(ISNUMBER(H15)),H15,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H15&lt;Config!$B$12,"Abaixo do mínimo",IF(H15&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K15" s="25">
-        <f>IF(OR(H15="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G15-F15))</f>
+        <f>IF(OR(NOT(ISNUMBER(H15)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G15-F15))</f>
         <v>0</v>
       </c>
       <c r="L15" s="41">
@@ -4715,19 +4715,19 @@
         <v>120</v>
       </c>
       <c r="H16" s="30">
-        <f>IF(OR(A16="",G16="",G16=0,F16=""),"",F16/G16)</f>
+        <f>IF(OR(A16="",G16="",F16=""),"",IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"valor ou horas inválidos",IF(G16=0,"",F16/G16)))</f>
         <v>180</v>
       </c>
       <c r="I16" s="31">
-        <f>IF(OR(H16="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H16/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H16)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H16/Config!$B$12-1))</f>
         <v>0.407568176245698</v>
       </c>
       <c r="J16" s="33" t="str">
-        <f>IF(H16="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H16&lt;Config!$B$12,"Abaixo do mínimo",IF(H16&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H16="","",IF(NOT(ISNUMBER(H16)),H16,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H16&lt;Config!$B$12,"Abaixo do mínimo",IF(H16&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K16" s="25">
-        <f>IF(OR(H16="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G16-F16))</f>
+        <f>IF(OR(NOT(ISNUMBER(H16)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G16-F16))</f>
         <v>0</v>
       </c>
       <c r="L16" s="41">
@@ -4768,19 +4768,19 @@
         <v>110</v>
       </c>
       <c r="H17" s="30">
-        <f>IF(OR(A17="",G17="",G17=0,F17=""),"",F17/G17)</f>
+        <f>IF(OR(A17="",G17="",F17=""),"",IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"valor ou horas inválidos",IF(G17=0,"",F17/G17)))</f>
         <v>163.636363636364</v>
       </c>
       <c r="I17" s="31">
-        <f>IF(OR(H17="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H17/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H17)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H17/Config!$B$12-1))</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J17" s="33" t="str">
-        <f>IF(H17="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H17&lt;Config!$B$12,"Abaixo do mínimo",IF(H17&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H17="","",IF(NOT(ISNUMBER(H17)),H17,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H17&lt;Config!$B$12,"Abaixo do mínimo",IF(H17&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K17" s="25">
-        <f>IF(OR(H17="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G17-F17))</f>
+        <f>IF(OR(NOT(ISNUMBER(H17)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G17-F17))</f>
         <v>0</v>
       </c>
       <c r="L17" s="41">
@@ -4821,19 +4821,19 @@
         <v>90</v>
       </c>
       <c r="H18" s="30">
-        <f>IF(OR(A18="",G18="",G18=0,F18=""),"",F18/G18)</f>
+        <f>IF(OR(A18="",G18="",F18=""),"",IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"valor ou horas inválidos",IF(G18=0,"",F18/G18)))</f>
         <v>150</v>
       </c>
       <c r="I18" s="31">
-        <f>IF(OR(H18="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H18/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H18)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H18/Config!$B$12-1))</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J18" s="33" t="str">
-        <f>IF(H18="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H18&lt;Config!$B$12,"Abaixo do mínimo",IF(H18&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H18="","",IF(NOT(ISNUMBER(H18)),H18,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H18&lt;Config!$B$12,"Abaixo do mínimo",IF(H18&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K18" s="25">
-        <f>IF(OR(H18="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G18-F18))</f>
+        <f>IF(OR(NOT(ISNUMBER(H18)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G18-F18))</f>
         <v>0</v>
       </c>
       <c r="L18" s="41">
@@ -4874,19 +4874,19 @@
         <v>80</v>
       </c>
       <c r="H19" s="30">
-        <f>IF(OR(A19="",G19="",G19=0,F19=""),"",F19/G19)</f>
+        <f>IF(OR(A19="",G19="",F19=""),"",IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"valor ou horas inválidos",IF(G19=0,"",F19/G19)))</f>
         <v>112.5</v>
       </c>
       <c r="I19" s="31">
-        <f>IF(OR(H19="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H19/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H19)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H19/Config!$B$12-1))</f>
         <v>-0.120269889846439</v>
       </c>
       <c r="J19" s="33" t="str">
-        <f>IF(H19="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H19&lt;Config!$B$12,"Abaixo do mínimo",IF(H19&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H19="","",IF(NOT(ISNUMBER(H19)),H19,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H19&lt;Config!$B$12,"Abaixo do mínimo",IF(H19&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K19" s="25">
-        <f>IF(OR(H19="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G19-F19))</f>
+        <f>IF(OR(NOT(ISNUMBER(H19)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G19-F19))</f>
         <v>1230.41032258064</v>
       </c>
       <c r="L19" s="41">
@@ -4927,19 +4927,19 @@
         <v>28</v>
       </c>
       <c r="H20" s="30">
-        <f>IF(OR(A20="",G20="",G20=0,F20=""),"",F20/G20)</f>
+        <f>IF(OR(A20="",G20="",F20=""),"",IF(OR(NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20))),"valor ou horas inválidos",IF(G20=0,"",F20/G20)))</f>
         <v>157.142857142857</v>
       </c>
       <c r="I20" s="31">
-        <f>IF(OR(H20="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H20/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H20)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H20/Config!$B$12-1))</f>
         <v>0.228829360214498</v>
       </c>
       <c r="J20" s="33" t="str">
-        <f>IF(H20="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H20&lt;Config!$B$12,"Abaixo do mínimo",IF(H20&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H20="","",IF(NOT(ISNUMBER(H20)),H20,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H20&lt;Config!$B$12,"Abaixo do mínimo",IF(H20&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K20" s="25">
-        <f>IF(OR(H20="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G20-F20))</f>
+        <f>IF(OR(NOT(ISNUMBER(H20)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G20-F20))</f>
         <v>0</v>
       </c>
       <c r="L20" s="41">
@@ -4980,19 +4980,19 @@
         <v>55</v>
       </c>
       <c r="H21" s="30">
-        <f>IF(OR(A21="",G21="",G21=0,F21=""),"",F21/G21)</f>
+        <f>IF(OR(A21="",G21="",F21=""),"",IF(OR(NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21))),"valor ou horas inválidos",IF(G21=0,"",F21/G21)))</f>
         <v>163.636363636364</v>
       </c>
       <c r="I21" s="31">
-        <f>IF(OR(H21="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H21/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H21)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H21/Config!$B$12-1))</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J21" s="33" t="str">
-        <f>IF(H21="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H21&lt;Config!$B$12,"Abaixo do mínimo",IF(H21&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H21="","",IF(NOT(ISNUMBER(H21)),H21,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H21&lt;Config!$B$12,"Abaixo do mínimo",IF(H21&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K21" s="25">
-        <f>IF(OR(H21="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G21-F21))</f>
+        <f>IF(OR(NOT(ISNUMBER(H21)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G21-F21))</f>
         <v>0</v>
       </c>
       <c r="L21" s="41">
@@ -5033,19 +5033,19 @@
         <v>45</v>
       </c>
       <c r="H22" s="30">
-        <f>IF(OR(A22="",G22="",G22=0,F22=""),"",F22/G22)</f>
+        <f>IF(OR(A22="",G22="",F22=""),"",IF(OR(NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22))),"valor ou horas inválidos",IF(G22=0,"",F22/G22)))</f>
         <v>146.666666666667</v>
       </c>
       <c r="I22" s="31">
-        <f>IF(OR(H22="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H22/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H22)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H22/Config!$B$12-1))</f>
         <v>0.146907402866865</v>
       </c>
       <c r="J22" s="33" t="str">
-        <f>IF(H22="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H22&lt;Config!$B$12,"Abaixo do mínimo",IF(H22&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H22="","",IF(NOT(ISNUMBER(H22)),H22,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H22&lt;Config!$B$12,"Abaixo do mínimo",IF(H22&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K22" s="25">
-        <f>IF(OR(H22="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G22-F22))</f>
+        <f>IF(OR(NOT(ISNUMBER(H22)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G22-F22))</f>
         <v>0</v>
       </c>
       <c r="L22" s="41">
@@ -5086,19 +5086,19 @@
         <v>90</v>
       </c>
       <c r="H23" s="30">
-        <f>IF(OR(A23="",G23="",G23=0,F23=""),"",F23/G23)</f>
+        <f>IF(OR(A23="",G23="",F23=""),"",IF(OR(NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23))),"valor ou horas inválidos",IF(G23=0,"",F23/G23)))</f>
         <v>111.111111111111</v>
       </c>
       <c r="I23" s="31">
-        <f>IF(OR(H23="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H23/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H23)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H23/Config!$B$12-1))</f>
         <v>-0.13113075540389</v>
       </c>
       <c r="J23" s="33" t="str">
-        <f>IF(H23="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H23&lt;Config!$B$12,"Abaixo do mínimo",IF(H23&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H23="","",IF(NOT(ISNUMBER(H23)),H23,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H23&lt;Config!$B$12,"Abaixo do mínimo",IF(H23&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K23" s="25">
-        <f>IF(OR(H23="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G23-F23))</f>
+        <f>IF(OR(NOT(ISNUMBER(H23)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G23-F23))</f>
         <v>1509.21161290322</v>
       </c>
       <c r="L23" s="41">
@@ -5139,19 +5139,19 @@
         <v>40</v>
       </c>
       <c r="H24" s="30">
-        <f>IF(OR(A24="",G24="",G24=0,F24=""),"",F24/G24)</f>
+        <f>IF(OR(A24="",G24="",F24=""),"",IF(OR(NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24))),"valor ou horas inválidos",IF(G24=0,"",F24/G24)))</f>
         <v>100</v>
       </c>
       <c r="I24" s="31">
-        <f>IF(OR(H24="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H24/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H24)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H24/Config!$B$12-1))</f>
         <v>-0.218017679863501</v>
       </c>
       <c r="J24" s="33" t="str">
-        <f>IF(H24="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H24&lt;Config!$B$12,"Abaixo do mínimo",IF(H24&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H24="","",IF(NOT(ISNUMBER(H24)),H24,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H24&lt;Config!$B$12,"Abaixo do mínimo",IF(H24&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K24" s="25">
-        <f>IF(OR(H24="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G24-F24))</f>
+        <f>IF(OR(NOT(ISNUMBER(H24)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G24-F24))</f>
         <v>1115.20516129032</v>
       </c>
       <c r="L24" s="41">
@@ -5192,19 +5192,19 @@
         <v>95</v>
       </c>
       <c r="H25" s="30">
-        <f>IF(OR(A25="",G25="",G25=0,F25=""),"",F25/G25)</f>
+        <f>IF(OR(A25="",G25="",F25=""),"",IF(OR(NOT(ISNUMBER(F25)),NOT(ISNUMBER(G25))),"valor ou horas inválidos",IF(G25=0,"",F25/G25)))</f>
         <v>157.894736842105</v>
       </c>
       <c r="I25" s="31">
-        <f>IF(OR(H25="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H25/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H25)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H25/Config!$B$12-1))</f>
         <v>0.234708926531314</v>
       </c>
       <c r="J25" s="33" t="str">
-        <f>IF(H25="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H25&lt;Config!$B$12,"Abaixo do mínimo",IF(H25&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H25="","",IF(NOT(ISNUMBER(H25)),H25,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H25&lt;Config!$B$12,"Abaixo do mínimo",IF(H25&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K25" s="25">
-        <f>IF(OR(H25="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G25-F25))</f>
+        <f>IF(OR(NOT(ISNUMBER(H25)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G25-F25))</f>
         <v>0</v>
       </c>
       <c r="L25" s="41">
@@ -5245,19 +5245,19 @@
         <v>60</v>
       </c>
       <c r="H26" s="30">
-        <f>IF(OR(A26="",G26="",G26=0,F26=""),"",F26/G26)</f>
+        <f>IF(OR(A26="",G26="",F26=""),"",IF(OR(NOT(ISNUMBER(F26)),NOT(ISNUMBER(G26))),"valor ou horas inválidos",IF(G26=0,"",F26/G26)))</f>
         <v>150</v>
       </c>
       <c r="I26" s="31">
-        <f>IF(OR(H26="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H26/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H26)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H26/Config!$B$12-1))</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J26" s="33" t="str">
-        <f>IF(H26="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H26&lt;Config!$B$12,"Abaixo do mínimo",IF(H26&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H26="","",IF(NOT(ISNUMBER(H26)),H26,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H26&lt;Config!$B$12,"Abaixo do mínimo",IF(H26&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K26" s="25">
-        <f>IF(OR(H26="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G26-F26))</f>
+        <f>IF(OR(NOT(ISNUMBER(H26)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G26-F26))</f>
         <v>0</v>
       </c>
       <c r="L26" s="41">
@@ -5298,19 +5298,19 @@
         <v>75</v>
       </c>
       <c r="H27" s="30">
-        <f>IF(OR(A27="",G27="",G27=0,F27=""),"",F27/G27)</f>
+        <f>IF(OR(A27="",G27="",F27=""),"",IF(OR(NOT(ISNUMBER(F27)),NOT(ISNUMBER(G27))),"valor ou horas inválidos",IF(G27=0,"",F27/G27)))</f>
         <v>160</v>
       </c>
       <c r="I27" s="31">
-        <f>IF(OR(H27="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H27/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H27)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H27/Config!$B$12-1))</f>
         <v>0.251171712218398</v>
       </c>
       <c r="J27" s="33" t="str">
-        <f>IF(H27="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H27&lt;Config!$B$12,"Abaixo do mínimo",IF(H27&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H27="","",IF(NOT(ISNUMBER(H27)),H27,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H27&lt;Config!$B$12,"Abaixo do mínimo",IF(H27&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K27" s="25">
-        <f>IF(OR(H27="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G27-F27))</f>
+        <f>IF(OR(NOT(ISNUMBER(H27)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G27-F27))</f>
         <v>0</v>
       </c>
       <c r="L27" s="41">
@@ -5351,19 +5351,19 @@
         <v>40</v>
       </c>
       <c r="H28" s="30">
-        <f>IF(OR(A28="",G28="",G28=0,F28=""),"",F28/G28)</f>
+        <f>IF(OR(A28="",G28="",F28=""),"",IF(OR(NOT(ISNUMBER(F28)),NOT(ISNUMBER(G28))),"valor ou horas inválidos",IF(G28=0,"",F28/G28)))</f>
         <v>190</v>
       </c>
       <c r="I28" s="31">
-        <f>IF(OR(H28="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H28/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H28)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H28/Config!$B$12-1))</f>
         <v>0.485766408259348</v>
       </c>
       <c r="J28" s="33" t="str">
-        <f>IF(H28="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H28&lt;Config!$B$12,"Abaixo do mínimo",IF(H28&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H28="","",IF(NOT(ISNUMBER(H28)),H28,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H28&lt;Config!$B$12,"Abaixo do mínimo",IF(H28&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K28" s="25">
-        <f>IF(OR(H28="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G28-F28))</f>
+        <f>IF(OR(NOT(ISNUMBER(H28)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G28-F28))</f>
         <v>0</v>
       </c>
       <c r="L28" s="41">
@@ -5404,19 +5404,19 @@
         <v>133</v>
       </c>
       <c r="H29" s="30">
-        <f>IF(OR(A29="",G29="",G29=0,F29=""),"",F29/G29)</f>
+        <f>IF(OR(A29="",G29="",F29=""),"",IF(OR(NOT(ISNUMBER(F29)),NOT(ISNUMBER(G29))),"valor ou horas inválidos",IF(G29=0,"",F29/G29)))</f>
         <v>180.451127819549</v>
       </c>
       <c r="I29" s="31">
-        <f>IF(OR(H29="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H29/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H29)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H29/Config!$B$12-1))</f>
         <v>0.411095916035788</v>
       </c>
       <c r="J29" s="33" t="str">
-        <f>IF(H29="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H29&lt;Config!$B$12,"Abaixo do mínimo",IF(H29&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H29="","",IF(NOT(ISNUMBER(H29)),H29,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H29&lt;Config!$B$12,"Abaixo do mínimo",IF(H29&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K29" s="25">
-        <f>IF(OR(H29="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G29-F29))</f>
+        <f>IF(OR(NOT(ISNUMBER(H29)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G29-F29))</f>
         <v>0</v>
       </c>
       <c r="L29" s="41">
@@ -5457,19 +5457,19 @@
         <v>30</v>
       </c>
       <c r="H30" s="30">
-        <f>IF(OR(A30="",G30="",G30=0,F30=""),"",F30/G30)</f>
+        <f>IF(OR(A30="",G30="",F30=""),"",IF(OR(NOT(ISNUMBER(F30)),NOT(ISNUMBER(G30))),"valor ou horas inválidos",IF(G30=0,"",F30/G30)))</f>
         <v>233.333333333333</v>
       </c>
       <c r="I30" s="31">
-        <f>IF(OR(H30="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H30/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H30)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H30/Config!$B$12-1))</f>
         <v>0.824625413651831</v>
       </c>
       <c r="J30" s="33" t="str">
-        <f>IF(H30="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H30&lt;Config!$B$12,"Abaixo do mínimo",IF(H30&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H30="","",IF(NOT(ISNUMBER(H30)),H30,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H30&lt;Config!$B$12,"Abaixo do mínimo",IF(H30&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K30" s="25">
-        <f>IF(OR(H30="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G30-F30))</f>
+        <f>IF(OR(NOT(ISNUMBER(H30)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G30-F30))</f>
         <v>0</v>
       </c>
       <c r="L30" s="41">
@@ -5510,19 +5510,19 @@
         <v>70</v>
       </c>
       <c r="H31" s="30">
-        <f>IF(OR(A31="",G31="",G31=0,F31=""),"",F31/G31)</f>
+        <f>IF(OR(A31="",G31="",F31=""),"",IF(OR(NOT(ISNUMBER(F31)),NOT(ISNUMBER(G31))),"valor ou horas inválidos",IF(G31=0,"",F31/G31)))</f>
         <v>100</v>
       </c>
       <c r="I31" s="31">
-        <f>IF(OR(H31="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H31/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H31)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H31/Config!$B$12-1))</f>
         <v>-0.218017679863501</v>
       </c>
       <c r="J31" s="33" t="str">
-        <f>IF(H31="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H31&lt;Config!$B$12,"Abaixo do mínimo",IF(H31&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H31="","",IF(NOT(ISNUMBER(H31)),H31,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H31&lt;Config!$B$12,"Abaixo do mínimo",IF(H31&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K31" s="25">
-        <f>IF(OR(H31="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G31-F31))</f>
+        <f>IF(OR(NOT(ISNUMBER(H31)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G31-F31))</f>
         <v>1951.60903225806</v>
       </c>
       <c r="L31" s="41">
@@ -5563,19 +5563,19 @@
         <v>55</v>
       </c>
       <c r="H32" s="30">
-        <f>IF(OR(A32="",G32="",G32=0,F32=""),"",F32/G32)</f>
+        <f>IF(OR(A32="",G32="",F32=""),"",IF(OR(NOT(ISNUMBER(F32)),NOT(ISNUMBER(G32))),"valor ou horas inválidos",IF(G32=0,"",F32/G32)))</f>
         <v>136.363636363636</v>
       </c>
       <c r="I32" s="31">
-        <f>IF(OR(H32="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H32/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H32)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H32/Config!$B$12-1))</f>
         <v>0.0663395274588623</v>
       </c>
       <c r="J32" s="33" t="str">
-        <f>IF(H32="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H32&lt;Config!$B$12,"Abaixo do mínimo",IF(H32&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H32="","",IF(NOT(ISNUMBER(H32)),H32,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H32&lt;Config!$B$12,"Abaixo do mínimo",IF(H32&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K32" s="25">
-        <f>IF(OR(H32="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G32-F32))</f>
+        <f>IF(OR(NOT(ISNUMBER(H32)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G32-F32))</f>
         <v>0</v>
       </c>
       <c r="L32" s="41">
@@ -5616,19 +5616,19 @@
         <v>40</v>
       </c>
       <c r="H33" s="30">
-        <f>IF(OR(A33="",G33="",G33=0,F33=""),"",F33/G33)</f>
+        <f>IF(OR(A33="",G33="",F33=""),"",IF(OR(NOT(ISNUMBER(F33)),NOT(ISNUMBER(G33))),"valor ou horas inválidos",IF(G33=0,"",F33/G33)))</f>
         <v>190</v>
       </c>
       <c r="I33" s="31">
-        <f>IF(OR(H33="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H33/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H33)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H33/Config!$B$12-1))</f>
         <v>0.485766408259348</v>
       </c>
       <c r="J33" s="33" t="str">
-        <f>IF(H33="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H33&lt;Config!$B$12,"Abaixo do mínimo",IF(H33&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H33="","",IF(NOT(ISNUMBER(H33)),H33,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H33&lt;Config!$B$12,"Abaixo do mínimo",IF(H33&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K33" s="25">
-        <f>IF(OR(H33="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G33-F33))</f>
+        <f>IF(OR(NOT(ISNUMBER(H33)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G33-F33))</f>
         <v>0</v>
       </c>
       <c r="L33" s="41">
@@ -5669,19 +5669,19 @@
         <v>35</v>
       </c>
       <c r="H34" s="30">
-        <f>IF(OR(A34="",G34="",G34=0,F34=""),"",F34/G34)</f>
+        <f>IF(OR(A34="",G34="",F34=""),"",IF(OR(NOT(ISNUMBER(F34)),NOT(ISNUMBER(G34))),"valor ou horas inválidos",IF(G34=0,"",F34/G34)))</f>
         <v>154.285714285714</v>
       </c>
       <c r="I34" s="31">
-        <f>IF(OR(H34="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H34/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H34)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H34/Config!$B$12-1))</f>
         <v>0.206487008210598</v>
       </c>
       <c r="J34" s="33" t="str">
-        <f>IF(H34="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H34&lt;Config!$B$12,"Abaixo do mínimo",IF(H34&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H34="","",IF(NOT(ISNUMBER(H34)),H34,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H34&lt;Config!$B$12,"Abaixo do mínimo",IF(H34&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K34" s="25">
-        <f>IF(OR(H34="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G34-F34))</f>
+        <f>IF(OR(NOT(ISNUMBER(H34)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G34-F34))</f>
         <v>0</v>
       </c>
       <c r="L34" s="41">
@@ -5722,19 +5722,19 @@
         <v>60</v>
       </c>
       <c r="H35" s="30">
-        <f>IF(OR(A35="",G35="",G35=0,F35=""),"",F35/G35)</f>
+        <f>IF(OR(A35="",G35="",F35=""),"",IF(OR(NOT(ISNUMBER(F35)),NOT(ISNUMBER(G35))),"valor ou horas inválidos",IF(G35=0,"",F35/G35)))</f>
         <v>200</v>
       </c>
       <c r="I35" s="31">
-        <f>IF(OR(H35="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H35/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H35)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H35/Config!$B$12-1))</f>
         <v>0.563964640272998</v>
       </c>
       <c r="J35" s="33" t="str">
-        <f>IF(H35="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H35&lt;Config!$B$12,"Abaixo do mínimo",IF(H35&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H35="","",IF(NOT(ISNUMBER(H35)),H35,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H35&lt;Config!$B$12,"Abaixo do mínimo",IF(H35&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Acima do alvo</v>
       </c>
       <c r="K35" s="25">
-        <f>IF(OR(H35="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G35-F35))</f>
+        <f>IF(OR(NOT(ISNUMBER(H35)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G35-F35))</f>
         <v>0</v>
       </c>
       <c r="L35" s="41">
@@ -5775,19 +5775,19 @@
         <v>110</v>
       </c>
       <c r="H36" s="30">
-        <f>IF(OR(A36="",G36="",G36=0,F36=""),"",F36/G36)</f>
+        <f>IF(OR(A36="",G36="",F36=""),"",IF(OR(NOT(ISNUMBER(F36)),NOT(ISNUMBER(G36))),"valor ou horas inválidos",IF(G36=0,"",F36/G36)))</f>
         <v>163.636363636364</v>
       </c>
       <c r="I36" s="31">
-        <f>IF(OR(H36="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H36/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H36)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H36/Config!$B$12-1))</f>
         <v>0.279607432950635</v>
       </c>
       <c r="J36" s="33" t="str">
-        <f>IF(H36="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H36&lt;Config!$B$12,"Abaixo do mínimo",IF(H36&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H36="","",IF(NOT(ISNUMBER(H36)),H36,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H36&lt;Config!$B$12,"Abaixo do mínimo",IF(H36&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K36" s="25">
-        <f>IF(OR(H36="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G36-F36))</f>
+        <f>IF(OR(NOT(ISNUMBER(H36)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G36-F36))</f>
         <v>0</v>
       </c>
       <c r="L36" s="41">
@@ -5828,19 +5828,19 @@
         <v>45</v>
       </c>
       <c r="H37" s="30">
-        <f>IF(OR(A37="",G37="",G37=0,F37=""),"",F37/G37)</f>
+        <f>IF(OR(A37="",G37="",F37=""),"",IF(OR(NOT(ISNUMBER(F37)),NOT(ISNUMBER(G37))),"valor ou horas inválidos",IF(G37=0,"",F37/G37)))</f>
         <v>144.444444444444</v>
       </c>
       <c r="I37" s="31">
-        <f>IF(OR(H37="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H37/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H37)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H37/Config!$B$12-1))</f>
         <v>0.129530017974943</v>
       </c>
       <c r="J37" s="33" t="str">
-        <f>IF(H37="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H37&lt;Config!$B$12,"Abaixo do mínimo",IF(H37&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H37="","",IF(NOT(ISNUMBER(H37)),H37,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H37&lt;Config!$B$12,"Abaixo do mínimo",IF(H37&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K37" s="25">
-        <f>IF(OR(H37="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G37-F37))</f>
+        <f>IF(OR(NOT(ISNUMBER(H37)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G37-F37))</f>
         <v>0</v>
       </c>
       <c r="L37" s="41">
@@ -5881,19 +5881,19 @@
         <v>45</v>
       </c>
       <c r="H38" s="30">
-        <f>IF(OR(A38="",G38="",G38=0,F38=""),"",F38/G38)</f>
+        <f>IF(OR(A38="",G38="",F38=""),"",IF(OR(NOT(ISNUMBER(F38)),NOT(ISNUMBER(G38))),"valor ou horas inválidos",IF(G38=0,"",F38/G38)))</f>
         <v>133.333333333333</v>
       </c>
       <c r="I38" s="31">
-        <f>IF(OR(H38="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H38/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H38)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H38/Config!$B$12-1))</f>
         <v>0.0426430935153319</v>
       </c>
       <c r="J38" s="33" t="str">
-        <f>IF(H38="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H38&lt;Config!$B$12,"Abaixo do mínimo",IF(H38&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H38="","",IF(NOT(ISNUMBER(H38)),H38,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H38&lt;Config!$B$12,"Abaixo do mínimo",IF(H38&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K38" s="25">
-        <f>IF(OR(H38="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G38-F38))</f>
+        <f>IF(OR(NOT(ISNUMBER(H38)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G38-F38))</f>
         <v>0</v>
       </c>
       <c r="L38" s="41">
@@ -5934,19 +5934,19 @@
         <v>95</v>
       </c>
       <c r="H39" s="30">
-        <f>IF(OR(A39="",G39="",G39=0,F39=""),"",F39/G39)</f>
+        <f>IF(OR(A39="",G39="",F39=""),"",IF(OR(NOT(ISNUMBER(F39)),NOT(ISNUMBER(G39))),"valor ou horas inválidos",IF(G39=0,"",F39/G39)))</f>
         <v>126.315789473684</v>
       </c>
       <c r="I39" s="31">
-        <f>IF(OR(H39="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H39/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H39)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H39/Config!$B$12-1))</f>
         <v>-0.0122328587749487</v>
       </c>
       <c r="J39" s="33" t="str">
-        <f>IF(H39="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H39&lt;Config!$B$12,"Abaixo do mínimo",IF(H39&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H39="","",IF(NOT(ISNUMBER(H39)),H39,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H39&lt;Config!$B$12,"Abaixo do mínimo",IF(H39&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K39" s="25">
-        <f>IF(OR(H39="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G39-F39))</f>
+        <f>IF(OR(NOT(ISNUMBER(H39)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G39-F39))</f>
         <v>148.612258064513</v>
       </c>
       <c r="L39" s="41">
@@ -5987,19 +5987,19 @@
         <v>55</v>
       </c>
       <c r="H40" s="30">
-        <f>IF(OR(A40="",G40="",G40=0,F40=""),"",F40/G40)</f>
+        <f>IF(OR(A40="",G40="",F40=""),"",IF(OR(NOT(ISNUMBER(F40)),NOT(ISNUMBER(G40))),"valor ou horas inválidos",IF(G40=0,"",F40/G40)))</f>
         <v>127.272727272727</v>
       </c>
       <c r="I40" s="31">
-        <f>IF(OR(H40="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H40/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H40)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H40/Config!$B$12-1))</f>
         <v>-0.00474977437172863</v>
       </c>
       <c r="J40" s="33" t="str">
-        <f>IF(H40="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H40&lt;Config!$B$12,"Abaixo do mínimo",IF(H40&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H40="","",IF(NOT(ISNUMBER(H40)),H40,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H40&lt;Config!$B$12,"Abaixo do mínimo",IF(H40&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K40" s="25">
-        <f>IF(OR(H40="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G40-F40))</f>
+        <f>IF(OR(NOT(ISNUMBER(H40)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G40-F40))</f>
         <v>33.4070967741918</v>
       </c>
       <c r="L40" s="41">
@@ -6040,19 +6040,19 @@
         <v>40</v>
       </c>
       <c r="H41" s="30">
-        <f>IF(OR(A41="",G41="",G41=0,F41=""),"",F41/G41)</f>
+        <f>IF(OR(A41="",G41="",F41=""),"",IF(OR(NOT(ISNUMBER(F41)),NOT(ISNUMBER(G41))),"valor ou horas inválidos",IF(G41=0,"",F41/G41)))</f>
         <v>150</v>
       </c>
       <c r="I41" s="31">
-        <f>IF(OR(H41="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H41/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H41)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H41/Config!$B$12-1))</f>
         <v>0.172973480204748</v>
       </c>
       <c r="J41" s="33" t="str">
-        <f>IF(H41="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H41&lt;Config!$B$12,"Abaixo do mínimo",IF(H41&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H41="","",IF(NOT(ISNUMBER(H41)),H41,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H41&lt;Config!$B$12,"Abaixo do mínimo",IF(H41&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Na faixa</v>
       </c>
       <c r="K41" s="25">
-        <f>IF(OR(H41="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G41-F41))</f>
+        <f>IF(OR(NOT(ISNUMBER(H41)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G41-F41))</f>
         <v>0</v>
       </c>
       <c r="L41" s="41">
@@ -6093,19 +6093,19 @@
         <v>70</v>
       </c>
       <c r="H42" s="30">
-        <f>IF(OR(A42="",G42="",G42=0,F42=""),"",F42/G42)</f>
+        <f>IF(OR(A42="",G42="",F42=""),"",IF(OR(NOT(ISNUMBER(F42)),NOT(ISNUMBER(G42))),"valor ou horas inválidos",IF(G42=0,"",F42/G42)))</f>
         <v>121.428571428571</v>
       </c>
       <c r="I42" s="31">
-        <f>IF(OR(H42="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H42/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H42)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H42/Config!$B$12-1))</f>
         <v>-0.0504500398342512</v>
       </c>
       <c r="J42" s="33" t="str">
-        <f>IF(H42="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H42&lt;Config!$B$12,"Abaixo do mínimo",IF(H42&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H42="","",IF(NOT(ISNUMBER(H42)),H42,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H42&lt;Config!$B$12,"Abaixo do mínimo",IF(H42&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v>Abaixo do mínimo</v>
       </c>
       <c r="K42" s="25">
-        <f>IF(OR(H42="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G42-F42))</f>
+        <f>IF(OR(NOT(ISNUMBER(H42)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G42-F42))</f>
         <v>451.609032258062</v>
       </c>
       <c r="L42" s="41">
@@ -6122,19 +6122,19 @@
       <c r="F43" s="40" t="n"/>
       <c r="G43" s="23" t="n"/>
       <c r="H43" s="30">
-        <f>IF(OR(A43="",G43="",G43=0,F43=""),"",F43/G43)</f>
+        <f>IF(OR(A43="",G43="",F43=""),"",IF(OR(NOT(ISNUMBER(F43)),NOT(ISNUMBER(G43))),"valor ou horas inválidos",IF(G43=0,"",F43/G43)))</f>
         <v/>
       </c>
       <c r="I43" s="31">
-        <f>IF(OR(H43="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H43/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H43)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H43/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J43" s="33">
-        <f>IF(H43="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H43&lt;Config!$B$12,"Abaixo do mínimo",IF(H43&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H43="","",IF(NOT(ISNUMBER(H43)),H43,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H43&lt;Config!$B$12,"Abaixo do mínimo",IF(H43&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K43" s="25">
-        <f>IF(OR(H43="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G43-F43))</f>
+        <f>IF(OR(NOT(ISNUMBER(H43)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G43-F43))</f>
         <v/>
       </c>
       <c r="L43" s="41">
@@ -6151,19 +6151,19 @@
       <c r="F44" s="40" t="n"/>
       <c r="G44" s="23" t="n"/>
       <c r="H44" s="30">
-        <f>IF(OR(A44="",G44="",G44=0,F44=""),"",F44/G44)</f>
+        <f>IF(OR(A44="",G44="",F44=""),"",IF(OR(NOT(ISNUMBER(F44)),NOT(ISNUMBER(G44))),"valor ou horas inválidos",IF(G44=0,"",F44/G44)))</f>
         <v/>
       </c>
       <c r="I44" s="31">
-        <f>IF(OR(H44="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H44/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H44)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H44/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J44" s="33">
-        <f>IF(H44="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H44&lt;Config!$B$12,"Abaixo do mínimo",IF(H44&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H44="","",IF(NOT(ISNUMBER(H44)),H44,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H44&lt;Config!$B$12,"Abaixo do mínimo",IF(H44&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K44" s="25">
-        <f>IF(OR(H44="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G44-F44))</f>
+        <f>IF(OR(NOT(ISNUMBER(H44)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G44-F44))</f>
         <v/>
       </c>
       <c r="L44" s="41">
@@ -6180,19 +6180,19 @@
       <c r="F45" s="40" t="n"/>
       <c r="G45" s="23" t="n"/>
       <c r="H45" s="30">
-        <f>IF(OR(A45="",G45="",G45=0,F45=""),"",F45/G45)</f>
+        <f>IF(OR(A45="",G45="",F45=""),"",IF(OR(NOT(ISNUMBER(F45)),NOT(ISNUMBER(G45))),"valor ou horas inválidos",IF(G45=0,"",F45/G45)))</f>
         <v/>
       </c>
       <c r="I45" s="31">
-        <f>IF(OR(H45="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H45/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H45)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H45/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J45" s="33">
-        <f>IF(H45="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H45&lt;Config!$B$12,"Abaixo do mínimo",IF(H45&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H45="","",IF(NOT(ISNUMBER(H45)),H45,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H45&lt;Config!$B$12,"Abaixo do mínimo",IF(H45&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K45" s="25">
-        <f>IF(OR(H45="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G45-F45))</f>
+        <f>IF(OR(NOT(ISNUMBER(H45)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G45-F45))</f>
         <v/>
       </c>
       <c r="L45" s="41">
@@ -6209,19 +6209,19 @@
       <c r="F46" s="40" t="n"/>
       <c r="G46" s="23" t="n"/>
       <c r="H46" s="30">
-        <f>IF(OR(A46="",G46="",G46=0,F46=""),"",F46/G46)</f>
+        <f>IF(OR(A46="",G46="",F46=""),"",IF(OR(NOT(ISNUMBER(F46)),NOT(ISNUMBER(G46))),"valor ou horas inválidos",IF(G46=0,"",F46/G46)))</f>
         <v/>
       </c>
       <c r="I46" s="31">
-        <f>IF(OR(H46="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H46/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H46)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H46/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J46" s="33">
-        <f>IF(H46="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H46&lt;Config!$B$12,"Abaixo do mínimo",IF(H46&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H46="","",IF(NOT(ISNUMBER(H46)),H46,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H46&lt;Config!$B$12,"Abaixo do mínimo",IF(H46&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K46" s="25">
-        <f>IF(OR(H46="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G46-F46))</f>
+        <f>IF(OR(NOT(ISNUMBER(H46)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G46-F46))</f>
         <v/>
       </c>
       <c r="L46" s="41">
@@ -6238,19 +6238,19 @@
       <c r="F47" s="40" t="n"/>
       <c r="G47" s="23" t="n"/>
       <c r="H47" s="30">
-        <f>IF(OR(A47="",G47="",G47=0,F47=""),"",F47/G47)</f>
+        <f>IF(OR(A47="",G47="",F47=""),"",IF(OR(NOT(ISNUMBER(F47)),NOT(ISNUMBER(G47))),"valor ou horas inválidos",IF(G47=0,"",F47/G47)))</f>
         <v/>
       </c>
       <c r="I47" s="31">
-        <f>IF(OR(H47="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H47/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H47)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H47/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J47" s="33">
-        <f>IF(H47="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H47&lt;Config!$B$12,"Abaixo do mínimo",IF(H47&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H47="","",IF(NOT(ISNUMBER(H47)),H47,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H47&lt;Config!$B$12,"Abaixo do mínimo",IF(H47&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K47" s="25">
-        <f>IF(OR(H47="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G47-F47))</f>
+        <f>IF(OR(NOT(ISNUMBER(H47)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G47-F47))</f>
         <v/>
       </c>
       <c r="L47" s="41">
@@ -6267,19 +6267,19 @@
       <c r="F48" s="40" t="n"/>
       <c r="G48" s="23" t="n"/>
       <c r="H48" s="30">
-        <f>IF(OR(A48="",G48="",G48=0,F48=""),"",F48/G48)</f>
+        <f>IF(OR(A48="",G48="",F48=""),"",IF(OR(NOT(ISNUMBER(F48)),NOT(ISNUMBER(G48))),"valor ou horas inválidos",IF(G48=0,"",F48/G48)))</f>
         <v/>
       </c>
       <c r="I48" s="31">
-        <f>IF(OR(H48="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H48/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H48)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H48/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J48" s="33">
-        <f>IF(H48="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H48&lt;Config!$B$12,"Abaixo do mínimo",IF(H48&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H48="","",IF(NOT(ISNUMBER(H48)),H48,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H48&lt;Config!$B$12,"Abaixo do mínimo",IF(H48&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K48" s="25">
-        <f>IF(OR(H48="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G48-F48))</f>
+        <f>IF(OR(NOT(ISNUMBER(H48)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G48-F48))</f>
         <v/>
       </c>
       <c r="L48" s="41">
@@ -6296,19 +6296,19 @@
       <c r="F49" s="40" t="n"/>
       <c r="G49" s="23" t="n"/>
       <c r="H49" s="30">
-        <f>IF(OR(A49="",G49="",G49=0,F49=""),"",F49/G49)</f>
+        <f>IF(OR(A49="",G49="",F49=""),"",IF(OR(NOT(ISNUMBER(F49)),NOT(ISNUMBER(G49))),"valor ou horas inválidos",IF(G49=0,"",F49/G49)))</f>
         <v/>
       </c>
       <c r="I49" s="31">
-        <f>IF(OR(H49="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H49/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H49)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H49/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J49" s="33">
-        <f>IF(H49="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H49&lt;Config!$B$12,"Abaixo do mínimo",IF(H49&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H49="","",IF(NOT(ISNUMBER(H49)),H49,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H49&lt;Config!$B$12,"Abaixo do mínimo",IF(H49&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K49" s="25">
-        <f>IF(OR(H49="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G49-F49))</f>
+        <f>IF(OR(NOT(ISNUMBER(H49)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G49-F49))</f>
         <v/>
       </c>
       <c r="L49" s="41">
@@ -6325,19 +6325,19 @@
       <c r="F50" s="40" t="n"/>
       <c r="G50" s="23" t="n"/>
       <c r="H50" s="30">
-        <f>IF(OR(A50="",G50="",G50=0,F50=""),"",F50/G50)</f>
+        <f>IF(OR(A50="",G50="",F50=""),"",IF(OR(NOT(ISNUMBER(F50)),NOT(ISNUMBER(G50))),"valor ou horas inválidos",IF(G50=0,"",F50/G50)))</f>
         <v/>
       </c>
       <c r="I50" s="31">
-        <f>IF(OR(H50="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H50/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H50)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H50/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J50" s="33">
-        <f>IF(H50="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H50&lt;Config!$B$12,"Abaixo do mínimo",IF(H50&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H50="","",IF(NOT(ISNUMBER(H50)),H50,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H50&lt;Config!$B$12,"Abaixo do mínimo",IF(H50&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K50" s="25">
-        <f>IF(OR(H50="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G50-F50))</f>
+        <f>IF(OR(NOT(ISNUMBER(H50)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G50-F50))</f>
         <v/>
       </c>
       <c r="L50" s="41">
@@ -6354,19 +6354,19 @@
       <c r="F51" s="40" t="n"/>
       <c r="G51" s="23" t="n"/>
       <c r="H51" s="30">
-        <f>IF(OR(A51="",G51="",G51=0,F51=""),"",F51/G51)</f>
+        <f>IF(OR(A51="",G51="",F51=""),"",IF(OR(NOT(ISNUMBER(F51)),NOT(ISNUMBER(G51))),"valor ou horas inválidos",IF(G51=0,"",F51/G51)))</f>
         <v/>
       </c>
       <c r="I51" s="31">
-        <f>IF(OR(H51="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H51/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H51)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H51/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J51" s="33">
-        <f>IF(H51="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H51&lt;Config!$B$12,"Abaixo do mínimo",IF(H51&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H51="","",IF(NOT(ISNUMBER(H51)),H51,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H51&lt;Config!$B$12,"Abaixo do mínimo",IF(H51&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K51" s="25">
-        <f>IF(OR(H51="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G51-F51))</f>
+        <f>IF(OR(NOT(ISNUMBER(H51)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G51-F51))</f>
         <v/>
       </c>
       <c r="L51" s="41">
@@ -6383,19 +6383,19 @@
       <c r="F52" s="40" t="n"/>
       <c r="G52" s="23" t="n"/>
       <c r="H52" s="30">
-        <f>IF(OR(A52="",G52="",G52=0,F52=""),"",F52/G52)</f>
+        <f>IF(OR(A52="",G52="",F52=""),"",IF(OR(NOT(ISNUMBER(F52)),NOT(ISNUMBER(G52))),"valor ou horas inválidos",IF(G52=0,"",F52/G52)))</f>
         <v/>
       </c>
       <c r="I52" s="31">
-        <f>IF(OR(H52="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H52/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H52)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H52/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J52" s="33">
-        <f>IF(H52="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H52&lt;Config!$B$12,"Abaixo do mínimo",IF(H52&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H52="","",IF(NOT(ISNUMBER(H52)),H52,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H52&lt;Config!$B$12,"Abaixo do mínimo",IF(H52&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K52" s="25">
-        <f>IF(OR(H52="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G52-F52))</f>
+        <f>IF(OR(NOT(ISNUMBER(H52)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G52-F52))</f>
         <v/>
       </c>
       <c r="L52" s="41">
@@ -6412,19 +6412,19 @@
       <c r="F53" s="40" t="n"/>
       <c r="G53" s="23" t="n"/>
       <c r="H53" s="30">
-        <f>IF(OR(A53="",G53="",G53=0,F53=""),"",F53/G53)</f>
+        <f>IF(OR(A53="",G53="",F53=""),"",IF(OR(NOT(ISNUMBER(F53)),NOT(ISNUMBER(G53))),"valor ou horas inválidos",IF(G53=0,"",F53/G53)))</f>
         <v/>
       </c>
       <c r="I53" s="31">
-        <f>IF(OR(H53="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H53/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H53)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H53/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J53" s="33">
-        <f>IF(H53="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H53&lt;Config!$B$12,"Abaixo do mínimo",IF(H53&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H53="","",IF(NOT(ISNUMBER(H53)),H53,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H53&lt;Config!$B$12,"Abaixo do mínimo",IF(H53&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K53" s="25">
-        <f>IF(OR(H53="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G53-F53))</f>
+        <f>IF(OR(NOT(ISNUMBER(H53)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G53-F53))</f>
         <v/>
       </c>
       <c r="L53" s="41">
@@ -6441,19 +6441,19 @@
       <c r="F54" s="40" t="n"/>
       <c r="G54" s="23" t="n"/>
       <c r="H54" s="30">
-        <f>IF(OR(A54="",G54="",G54=0,F54=""),"",F54/G54)</f>
+        <f>IF(OR(A54="",G54="",F54=""),"",IF(OR(NOT(ISNUMBER(F54)),NOT(ISNUMBER(G54))),"valor ou horas inválidos",IF(G54=0,"",F54/G54)))</f>
         <v/>
       </c>
       <c r="I54" s="31">
-        <f>IF(OR(H54="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H54/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H54)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H54/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J54" s="33">
-        <f>IF(H54="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H54&lt;Config!$B$12,"Abaixo do mínimo",IF(H54&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H54="","",IF(NOT(ISNUMBER(H54)),H54,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H54&lt;Config!$B$12,"Abaixo do mínimo",IF(H54&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K54" s="25">
-        <f>IF(OR(H54="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G54-F54))</f>
+        <f>IF(OR(NOT(ISNUMBER(H54)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G54-F54))</f>
         <v/>
       </c>
       <c r="L54" s="41">
@@ -6470,19 +6470,19 @@
       <c r="F55" s="40" t="n"/>
       <c r="G55" s="23" t="n"/>
       <c r="H55" s="30">
-        <f>IF(OR(A55="",G55="",G55=0,F55=""),"",F55/G55)</f>
+        <f>IF(OR(A55="",G55="",F55=""),"",IF(OR(NOT(ISNUMBER(F55)),NOT(ISNUMBER(G55))),"valor ou horas inválidos",IF(G55=0,"",F55/G55)))</f>
         <v/>
       </c>
       <c r="I55" s="31">
-        <f>IF(OR(H55="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H55/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H55)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H55/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J55" s="33">
-        <f>IF(H55="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H55&lt;Config!$B$12,"Abaixo do mínimo",IF(H55&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H55="","",IF(NOT(ISNUMBER(H55)),H55,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H55&lt;Config!$B$12,"Abaixo do mínimo",IF(H55&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K55" s="25">
-        <f>IF(OR(H55="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G55-F55))</f>
+        <f>IF(OR(NOT(ISNUMBER(H55)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G55-F55))</f>
         <v/>
       </c>
       <c r="L55" s="41">
@@ -6499,19 +6499,19 @@
       <c r="F56" s="40" t="n"/>
       <c r="G56" s="23" t="n"/>
       <c r="H56" s="30">
-        <f>IF(OR(A56="",G56="",G56=0,F56=""),"",F56/G56)</f>
+        <f>IF(OR(A56="",G56="",F56=""),"",IF(OR(NOT(ISNUMBER(F56)),NOT(ISNUMBER(G56))),"valor ou horas inválidos",IF(G56=0,"",F56/G56)))</f>
         <v/>
       </c>
       <c r="I56" s="31">
-        <f>IF(OR(H56="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H56/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H56)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H56/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J56" s="33">
-        <f>IF(H56="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H56&lt;Config!$B$12,"Abaixo do mínimo",IF(H56&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H56="","",IF(NOT(ISNUMBER(H56)),H56,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H56&lt;Config!$B$12,"Abaixo do mínimo",IF(H56&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K56" s="25">
-        <f>IF(OR(H56="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G56-F56))</f>
+        <f>IF(OR(NOT(ISNUMBER(H56)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G56-F56))</f>
         <v/>
       </c>
       <c r="L56" s="41">
@@ -6528,19 +6528,19 @@
       <c r="F57" s="40" t="n"/>
       <c r="G57" s="23" t="n"/>
       <c r="H57" s="30">
-        <f>IF(OR(A57="",G57="",G57=0,F57=""),"",F57/G57)</f>
+        <f>IF(OR(A57="",G57="",F57=""),"",IF(OR(NOT(ISNUMBER(F57)),NOT(ISNUMBER(G57))),"valor ou horas inválidos",IF(G57=0,"",F57/G57)))</f>
         <v/>
       </c>
       <c r="I57" s="31">
-        <f>IF(OR(H57="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H57/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H57)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H57/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J57" s="33">
-        <f>IF(H57="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H57&lt;Config!$B$12,"Abaixo do mínimo",IF(H57&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H57="","",IF(NOT(ISNUMBER(H57)),H57,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H57&lt;Config!$B$12,"Abaixo do mínimo",IF(H57&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K57" s="25">
-        <f>IF(OR(H57="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G57-F57))</f>
+        <f>IF(OR(NOT(ISNUMBER(H57)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G57-F57))</f>
         <v/>
       </c>
       <c r="L57" s="41">
@@ -6557,19 +6557,19 @@
       <c r="F58" s="40" t="n"/>
       <c r="G58" s="23" t="n"/>
       <c r="H58" s="30">
-        <f>IF(OR(A58="",G58="",G58=0,F58=""),"",F58/G58)</f>
+        <f>IF(OR(A58="",G58="",F58=""),"",IF(OR(NOT(ISNUMBER(F58)),NOT(ISNUMBER(G58))),"valor ou horas inválidos",IF(G58=0,"",F58/G58)))</f>
         <v/>
       </c>
       <c r="I58" s="31">
-        <f>IF(OR(H58="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H58/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H58)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H58/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J58" s="33">
-        <f>IF(H58="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H58&lt;Config!$B$12,"Abaixo do mínimo",IF(H58&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H58="","",IF(NOT(ISNUMBER(H58)),H58,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H58&lt;Config!$B$12,"Abaixo do mínimo",IF(H58&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K58" s="25">
-        <f>IF(OR(H58="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G58-F58))</f>
+        <f>IF(OR(NOT(ISNUMBER(H58)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G58-F58))</f>
         <v/>
       </c>
       <c r="L58" s="41">
@@ -6586,19 +6586,19 @@
       <c r="F59" s="40" t="n"/>
       <c r="G59" s="23" t="n"/>
       <c r="H59" s="30">
-        <f>IF(OR(A59="",G59="",G59=0,F59=""),"",F59/G59)</f>
+        <f>IF(OR(A59="",G59="",F59=""),"",IF(OR(NOT(ISNUMBER(F59)),NOT(ISNUMBER(G59))),"valor ou horas inválidos",IF(G59=0,"",F59/G59)))</f>
         <v/>
       </c>
       <c r="I59" s="31">
-        <f>IF(OR(H59="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H59/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H59)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H59/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J59" s="33">
-        <f>IF(H59="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H59&lt;Config!$B$12,"Abaixo do mínimo",IF(H59&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H59="","",IF(NOT(ISNUMBER(H59)),H59,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H59&lt;Config!$B$12,"Abaixo do mínimo",IF(H59&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K59" s="25">
-        <f>IF(OR(H59="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G59-F59))</f>
+        <f>IF(OR(NOT(ISNUMBER(H59)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G59-F59))</f>
         <v/>
       </c>
       <c r="L59" s="41">
@@ -6615,19 +6615,19 @@
       <c r="F60" s="40" t="n"/>
       <c r="G60" s="23" t="n"/>
       <c r="H60" s="30">
-        <f>IF(OR(A60="",G60="",G60=0,F60=""),"",F60/G60)</f>
+        <f>IF(OR(A60="",G60="",F60=""),"",IF(OR(NOT(ISNUMBER(F60)),NOT(ISNUMBER(G60))),"valor ou horas inválidos",IF(G60=0,"",F60/G60)))</f>
         <v/>
       </c>
       <c r="I60" s="31">
-        <f>IF(OR(H60="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H60/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H60)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H60/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J60" s="33">
-        <f>IF(H60="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H60&lt;Config!$B$12,"Abaixo do mínimo",IF(H60&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H60="","",IF(NOT(ISNUMBER(H60)),H60,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H60&lt;Config!$B$12,"Abaixo do mínimo",IF(H60&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K60" s="25">
-        <f>IF(OR(H60="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G60-F60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H60)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G60-F60))</f>
         <v/>
       </c>
       <c r="L60" s="41">
@@ -6644,19 +6644,19 @@
       <c r="F61" s="40" t="n"/>
       <c r="G61" s="23" t="n"/>
       <c r="H61" s="30">
-        <f>IF(OR(A61="",G61="",G61=0,F61=""),"",F61/G61)</f>
+        <f>IF(OR(A61="",G61="",F61=""),"",IF(OR(NOT(ISNUMBER(F61)),NOT(ISNUMBER(G61))),"valor ou horas inválidos",IF(G61=0,"",F61/G61)))</f>
         <v/>
       </c>
       <c r="I61" s="31">
-        <f>IF(OR(H61="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H61/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H61)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H61/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J61" s="33">
-        <f>IF(H61="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H61&lt;Config!$B$12,"Abaixo do mínimo",IF(H61&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H61="","",IF(NOT(ISNUMBER(H61)),H61,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H61&lt;Config!$B$12,"Abaixo do mínimo",IF(H61&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K61" s="25">
-        <f>IF(OR(H61="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G61-F61))</f>
+        <f>IF(OR(NOT(ISNUMBER(H61)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G61-F61))</f>
         <v/>
       </c>
       <c r="L61" s="41">
@@ -6673,19 +6673,19 @@
       <c r="F62" s="40" t="n"/>
       <c r="G62" s="23" t="n"/>
       <c r="H62" s="30">
-        <f>IF(OR(A62="",G62="",G62=0,F62=""),"",F62/G62)</f>
+        <f>IF(OR(A62="",G62="",F62=""),"",IF(OR(NOT(ISNUMBER(F62)),NOT(ISNUMBER(G62))),"valor ou horas inválidos",IF(G62=0,"",F62/G62)))</f>
         <v/>
       </c>
       <c r="I62" s="31">
-        <f>IF(OR(H62="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H62/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H62)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H62/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J62" s="33">
-        <f>IF(H62="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H62&lt;Config!$B$12,"Abaixo do mínimo",IF(H62&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H62="","",IF(NOT(ISNUMBER(H62)),H62,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H62&lt;Config!$B$12,"Abaixo do mínimo",IF(H62&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K62" s="25">
-        <f>IF(OR(H62="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G62-F62))</f>
+        <f>IF(OR(NOT(ISNUMBER(H62)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G62-F62))</f>
         <v/>
       </c>
       <c r="L62" s="41">
@@ -6702,19 +6702,19 @@
       <c r="F63" s="40" t="n"/>
       <c r="G63" s="23" t="n"/>
       <c r="H63" s="30">
-        <f>IF(OR(A63="",G63="",G63=0,F63=""),"",F63/G63)</f>
+        <f>IF(OR(A63="",G63="",F63=""),"",IF(OR(NOT(ISNUMBER(F63)),NOT(ISNUMBER(G63))),"valor ou horas inválidos",IF(G63=0,"",F63/G63)))</f>
         <v/>
       </c>
       <c r="I63" s="31">
-        <f>IF(OR(H63="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H63/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H63)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H63/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J63" s="33">
-        <f>IF(H63="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H63&lt;Config!$B$12,"Abaixo do mínimo",IF(H63&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H63="","",IF(NOT(ISNUMBER(H63)),H63,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H63&lt;Config!$B$12,"Abaixo do mínimo",IF(H63&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K63" s="25">
-        <f>IF(OR(H63="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G63-F63))</f>
+        <f>IF(OR(NOT(ISNUMBER(H63)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G63-F63))</f>
         <v/>
       </c>
       <c r="L63" s="41">
@@ -6731,19 +6731,19 @@
       <c r="F64" s="40" t="n"/>
       <c r="G64" s="23" t="n"/>
       <c r="H64" s="30">
-        <f>IF(OR(A64="",G64="",G64=0,F64=""),"",F64/G64)</f>
+        <f>IF(OR(A64="",G64="",F64=""),"",IF(OR(NOT(ISNUMBER(F64)),NOT(ISNUMBER(G64))),"valor ou horas inválidos",IF(G64=0,"",F64/G64)))</f>
         <v/>
       </c>
       <c r="I64" s="31">
-        <f>IF(OR(H64="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H64/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H64)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H64/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J64" s="33">
-        <f>IF(H64="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H64&lt;Config!$B$12,"Abaixo do mínimo",IF(H64&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H64="","",IF(NOT(ISNUMBER(H64)),H64,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H64&lt;Config!$B$12,"Abaixo do mínimo",IF(H64&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K64" s="25">
-        <f>IF(OR(H64="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G64-F64))</f>
+        <f>IF(OR(NOT(ISNUMBER(H64)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G64-F64))</f>
         <v/>
       </c>
       <c r="L64" s="41">
@@ -6760,19 +6760,19 @@
       <c r="F65" s="40" t="n"/>
       <c r="G65" s="23" t="n"/>
       <c r="H65" s="30">
-        <f>IF(OR(A65="",G65="",G65=0,F65=""),"",F65/G65)</f>
+        <f>IF(OR(A65="",G65="",F65=""),"",IF(OR(NOT(ISNUMBER(F65)),NOT(ISNUMBER(G65))),"valor ou horas inválidos",IF(G65=0,"",F65/G65)))</f>
         <v/>
       </c>
       <c r="I65" s="31">
-        <f>IF(OR(H65="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H65/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H65)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H65/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J65" s="33">
-        <f>IF(H65="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H65&lt;Config!$B$12,"Abaixo do mínimo",IF(H65&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H65="","",IF(NOT(ISNUMBER(H65)),H65,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H65&lt;Config!$B$12,"Abaixo do mínimo",IF(H65&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K65" s="25">
-        <f>IF(OR(H65="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G65-F65))</f>
+        <f>IF(OR(NOT(ISNUMBER(H65)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G65-F65))</f>
         <v/>
       </c>
       <c r="L65" s="41">
@@ -6789,19 +6789,19 @@
       <c r="F66" s="40" t="n"/>
       <c r="G66" s="23" t="n"/>
       <c r="H66" s="30">
-        <f>IF(OR(A66="",G66="",G66=0,F66=""),"",F66/G66)</f>
+        <f>IF(OR(A66="",G66="",F66=""),"",IF(OR(NOT(ISNUMBER(F66)),NOT(ISNUMBER(G66))),"valor ou horas inválidos",IF(G66=0,"",F66/G66)))</f>
         <v/>
       </c>
       <c r="I66" s="31">
-        <f>IF(OR(H66="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H66/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H66)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H66/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J66" s="33">
-        <f>IF(H66="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H66&lt;Config!$B$12,"Abaixo do mínimo",IF(H66&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H66="","",IF(NOT(ISNUMBER(H66)),H66,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H66&lt;Config!$B$12,"Abaixo do mínimo",IF(H66&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K66" s="25">
-        <f>IF(OR(H66="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G66-F66))</f>
+        <f>IF(OR(NOT(ISNUMBER(H66)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G66-F66))</f>
         <v/>
       </c>
       <c r="L66" s="41">
@@ -6818,19 +6818,19 @@
       <c r="F67" s="40" t="n"/>
       <c r="G67" s="23" t="n"/>
       <c r="H67" s="30">
-        <f>IF(OR(A67="",G67="",G67=0,F67=""),"",F67/G67)</f>
+        <f>IF(OR(A67="",G67="",F67=""),"",IF(OR(NOT(ISNUMBER(F67)),NOT(ISNUMBER(G67))),"valor ou horas inválidos",IF(G67=0,"",F67/G67)))</f>
         <v/>
       </c>
       <c r="I67" s="31">
-        <f>IF(OR(H67="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H67/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H67)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H67/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J67" s="33">
-        <f>IF(H67="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H67&lt;Config!$B$12,"Abaixo do mínimo",IF(H67&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H67="","",IF(NOT(ISNUMBER(H67)),H67,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H67&lt;Config!$B$12,"Abaixo do mínimo",IF(H67&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K67" s="25">
-        <f>IF(OR(H67="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G67-F67))</f>
+        <f>IF(OR(NOT(ISNUMBER(H67)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G67-F67))</f>
         <v/>
       </c>
       <c r="L67" s="41">
@@ -6847,19 +6847,19 @@
       <c r="F68" s="40" t="n"/>
       <c r="G68" s="23" t="n"/>
       <c r="H68" s="30">
-        <f>IF(OR(A68="",G68="",G68=0,F68=""),"",F68/G68)</f>
+        <f>IF(OR(A68="",G68="",F68=""),"",IF(OR(NOT(ISNUMBER(F68)),NOT(ISNUMBER(G68))),"valor ou horas inválidos",IF(G68=0,"",F68/G68)))</f>
         <v/>
       </c>
       <c r="I68" s="31">
-        <f>IF(OR(H68="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H68/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H68)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H68/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J68" s="33">
-        <f>IF(H68="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H68&lt;Config!$B$12,"Abaixo do mínimo",IF(H68&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H68="","",IF(NOT(ISNUMBER(H68)),H68,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H68&lt;Config!$B$12,"Abaixo do mínimo",IF(H68&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K68" s="25">
-        <f>IF(OR(H68="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G68-F68))</f>
+        <f>IF(OR(NOT(ISNUMBER(H68)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G68-F68))</f>
         <v/>
       </c>
       <c r="L68" s="41">
@@ -6876,19 +6876,19 @@
       <c r="F69" s="40" t="n"/>
       <c r="G69" s="23" t="n"/>
       <c r="H69" s="30">
-        <f>IF(OR(A69="",G69="",G69=0,F69=""),"",F69/G69)</f>
+        <f>IF(OR(A69="",G69="",F69=""),"",IF(OR(NOT(ISNUMBER(F69)),NOT(ISNUMBER(G69))),"valor ou horas inválidos",IF(G69=0,"",F69/G69)))</f>
         <v/>
       </c>
       <c r="I69" s="31">
-        <f>IF(OR(H69="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H69/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H69)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H69/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J69" s="33">
-        <f>IF(H69="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H69&lt;Config!$B$12,"Abaixo do mínimo",IF(H69&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H69="","",IF(NOT(ISNUMBER(H69)),H69,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H69&lt;Config!$B$12,"Abaixo do mínimo",IF(H69&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K69" s="25">
-        <f>IF(OR(H69="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G69-F69))</f>
+        <f>IF(OR(NOT(ISNUMBER(H69)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G69-F69))</f>
         <v/>
       </c>
       <c r="L69" s="41">
@@ -6905,19 +6905,19 @@
       <c r="F70" s="40" t="n"/>
       <c r="G70" s="23" t="n"/>
       <c r="H70" s="30">
-        <f>IF(OR(A70="",G70="",G70=0,F70=""),"",F70/G70)</f>
+        <f>IF(OR(A70="",G70="",F70=""),"",IF(OR(NOT(ISNUMBER(F70)),NOT(ISNUMBER(G70))),"valor ou horas inválidos",IF(G70=0,"",F70/G70)))</f>
         <v/>
       </c>
       <c r="I70" s="31">
-        <f>IF(OR(H70="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H70/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H70)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H70/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J70" s="33">
-        <f>IF(H70="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H70&lt;Config!$B$12,"Abaixo do mínimo",IF(H70&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H70="","",IF(NOT(ISNUMBER(H70)),H70,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H70&lt;Config!$B$12,"Abaixo do mínimo",IF(H70&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K70" s="25">
-        <f>IF(OR(H70="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G70-F70))</f>
+        <f>IF(OR(NOT(ISNUMBER(H70)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G70-F70))</f>
         <v/>
       </c>
       <c r="L70" s="41">
@@ -6934,19 +6934,19 @@
       <c r="F71" s="40" t="n"/>
       <c r="G71" s="23" t="n"/>
       <c r="H71" s="30">
-        <f>IF(OR(A71="",G71="",G71=0,F71=""),"",F71/G71)</f>
+        <f>IF(OR(A71="",G71="",F71=""),"",IF(OR(NOT(ISNUMBER(F71)),NOT(ISNUMBER(G71))),"valor ou horas inválidos",IF(G71=0,"",F71/G71)))</f>
         <v/>
       </c>
       <c r="I71" s="31">
-        <f>IF(OR(H71="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H71/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H71)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H71/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J71" s="33">
-        <f>IF(H71="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H71&lt;Config!$B$12,"Abaixo do mínimo",IF(H71&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H71="","",IF(NOT(ISNUMBER(H71)),H71,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H71&lt;Config!$B$12,"Abaixo do mínimo",IF(H71&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K71" s="25">
-        <f>IF(OR(H71="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G71-F71))</f>
+        <f>IF(OR(NOT(ISNUMBER(H71)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G71-F71))</f>
         <v/>
       </c>
       <c r="L71" s="41">
@@ -6963,19 +6963,19 @@
       <c r="F72" s="40" t="n"/>
       <c r="G72" s="23" t="n"/>
       <c r="H72" s="30">
-        <f>IF(OR(A72="",G72="",G72=0,F72=""),"",F72/G72)</f>
+        <f>IF(OR(A72="",G72="",F72=""),"",IF(OR(NOT(ISNUMBER(F72)),NOT(ISNUMBER(G72))),"valor ou horas inválidos",IF(G72=0,"",F72/G72)))</f>
         <v/>
       </c>
       <c r="I72" s="31">
-        <f>IF(OR(H72="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H72/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H72)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H72/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J72" s="33">
-        <f>IF(H72="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H72&lt;Config!$B$12,"Abaixo do mínimo",IF(H72&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H72="","",IF(NOT(ISNUMBER(H72)),H72,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H72&lt;Config!$B$12,"Abaixo do mínimo",IF(H72&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K72" s="25">
-        <f>IF(OR(H72="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G72-F72))</f>
+        <f>IF(OR(NOT(ISNUMBER(H72)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G72-F72))</f>
         <v/>
       </c>
       <c r="L72" s="41">
@@ -6992,19 +6992,19 @@
       <c r="F73" s="40" t="n"/>
       <c r="G73" s="23" t="n"/>
       <c r="H73" s="30">
-        <f>IF(OR(A73="",G73="",G73=0,F73=""),"",F73/G73)</f>
+        <f>IF(OR(A73="",G73="",F73=""),"",IF(OR(NOT(ISNUMBER(F73)),NOT(ISNUMBER(G73))),"valor ou horas inválidos",IF(G73=0,"",F73/G73)))</f>
         <v/>
       </c>
       <c r="I73" s="31">
-        <f>IF(OR(H73="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H73/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H73)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H73/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J73" s="33">
-        <f>IF(H73="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H73&lt;Config!$B$12,"Abaixo do mínimo",IF(H73&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H73="","",IF(NOT(ISNUMBER(H73)),H73,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H73&lt;Config!$B$12,"Abaixo do mínimo",IF(H73&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K73" s="25">
-        <f>IF(OR(H73="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G73-F73))</f>
+        <f>IF(OR(NOT(ISNUMBER(H73)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G73-F73))</f>
         <v/>
       </c>
       <c r="L73" s="41">
@@ -7021,19 +7021,19 @@
       <c r="F74" s="40" t="n"/>
       <c r="G74" s="23" t="n"/>
       <c r="H74" s="30">
-        <f>IF(OR(A74="",G74="",G74=0,F74=""),"",F74/G74)</f>
+        <f>IF(OR(A74="",G74="",F74=""),"",IF(OR(NOT(ISNUMBER(F74)),NOT(ISNUMBER(G74))),"valor ou horas inválidos",IF(G74=0,"",F74/G74)))</f>
         <v/>
       </c>
       <c r="I74" s="31">
-        <f>IF(OR(H74="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H74/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H74)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H74/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J74" s="33">
-        <f>IF(H74="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H74&lt;Config!$B$12,"Abaixo do mínimo",IF(H74&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H74="","",IF(NOT(ISNUMBER(H74)),H74,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H74&lt;Config!$B$12,"Abaixo do mínimo",IF(H74&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K74" s="25">
-        <f>IF(OR(H74="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G74-F74))</f>
+        <f>IF(OR(NOT(ISNUMBER(H74)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G74-F74))</f>
         <v/>
       </c>
       <c r="L74" s="41">
@@ -7050,19 +7050,19 @@
       <c r="F75" s="40" t="n"/>
       <c r="G75" s="23" t="n"/>
       <c r="H75" s="30">
-        <f>IF(OR(A75="",G75="",G75=0,F75=""),"",F75/G75)</f>
+        <f>IF(OR(A75="",G75="",F75=""),"",IF(OR(NOT(ISNUMBER(F75)),NOT(ISNUMBER(G75))),"valor ou horas inválidos",IF(G75=0,"",F75/G75)))</f>
         <v/>
       </c>
       <c r="I75" s="31">
-        <f>IF(OR(H75="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H75/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H75)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H75/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J75" s="33">
-        <f>IF(H75="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H75&lt;Config!$B$12,"Abaixo do mínimo",IF(H75&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H75="","",IF(NOT(ISNUMBER(H75)),H75,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H75&lt;Config!$B$12,"Abaixo do mínimo",IF(H75&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K75" s="25">
-        <f>IF(OR(H75="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G75-F75))</f>
+        <f>IF(OR(NOT(ISNUMBER(H75)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G75-F75))</f>
         <v/>
       </c>
       <c r="L75" s="41">
@@ -7079,19 +7079,19 @@
       <c r="F76" s="40" t="n"/>
       <c r="G76" s="23" t="n"/>
       <c r="H76" s="30">
-        <f>IF(OR(A76="",G76="",G76=0,F76=""),"",F76/G76)</f>
+        <f>IF(OR(A76="",G76="",F76=""),"",IF(OR(NOT(ISNUMBER(F76)),NOT(ISNUMBER(G76))),"valor ou horas inválidos",IF(G76=0,"",F76/G76)))</f>
         <v/>
       </c>
       <c r="I76" s="31">
-        <f>IF(OR(H76="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H76/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H76)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H76/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J76" s="33">
-        <f>IF(H76="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H76&lt;Config!$B$12,"Abaixo do mínimo",IF(H76&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H76="","",IF(NOT(ISNUMBER(H76)),H76,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H76&lt;Config!$B$12,"Abaixo do mínimo",IF(H76&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K76" s="25">
-        <f>IF(OR(H76="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G76-F76))</f>
+        <f>IF(OR(NOT(ISNUMBER(H76)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G76-F76))</f>
         <v/>
       </c>
       <c r="L76" s="41">
@@ -7108,19 +7108,19 @@
       <c r="F77" s="40" t="n"/>
       <c r="G77" s="23" t="n"/>
       <c r="H77" s="30">
-        <f>IF(OR(A77="",G77="",G77=0,F77=""),"",F77/G77)</f>
+        <f>IF(OR(A77="",G77="",F77=""),"",IF(OR(NOT(ISNUMBER(F77)),NOT(ISNUMBER(G77))),"valor ou horas inválidos",IF(G77=0,"",F77/G77)))</f>
         <v/>
       </c>
       <c r="I77" s="31">
-        <f>IF(OR(H77="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H77/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H77)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H77/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J77" s="33">
-        <f>IF(H77="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H77&lt;Config!$B$12,"Abaixo do mínimo",IF(H77&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H77="","",IF(NOT(ISNUMBER(H77)),H77,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H77&lt;Config!$B$12,"Abaixo do mínimo",IF(H77&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K77" s="25">
-        <f>IF(OR(H77="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G77-F77))</f>
+        <f>IF(OR(NOT(ISNUMBER(H77)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G77-F77))</f>
         <v/>
       </c>
       <c r="L77" s="41">
@@ -7137,19 +7137,19 @@
       <c r="F78" s="40" t="n"/>
       <c r="G78" s="23" t="n"/>
       <c r="H78" s="30">
-        <f>IF(OR(A78="",G78="",G78=0,F78=""),"",F78/G78)</f>
+        <f>IF(OR(A78="",G78="",F78=""),"",IF(OR(NOT(ISNUMBER(F78)),NOT(ISNUMBER(G78))),"valor ou horas inválidos",IF(G78=0,"",F78/G78)))</f>
         <v/>
       </c>
       <c r="I78" s="31">
-        <f>IF(OR(H78="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H78/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H78)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H78/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J78" s="33">
-        <f>IF(H78="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H78&lt;Config!$B$12,"Abaixo do mínimo",IF(H78&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H78="","",IF(NOT(ISNUMBER(H78)),H78,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H78&lt;Config!$B$12,"Abaixo do mínimo",IF(H78&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K78" s="25">
-        <f>IF(OR(H78="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G78-F78))</f>
+        <f>IF(OR(NOT(ISNUMBER(H78)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G78-F78))</f>
         <v/>
       </c>
       <c r="L78" s="41">
@@ -7166,19 +7166,19 @@
       <c r="F79" s="40" t="n"/>
       <c r="G79" s="23" t="n"/>
       <c r="H79" s="30">
-        <f>IF(OR(A79="",G79="",G79=0,F79=""),"",F79/G79)</f>
+        <f>IF(OR(A79="",G79="",F79=""),"",IF(OR(NOT(ISNUMBER(F79)),NOT(ISNUMBER(G79))),"valor ou horas inválidos",IF(G79=0,"",F79/G79)))</f>
         <v/>
       </c>
       <c r="I79" s="31">
-        <f>IF(OR(H79="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H79/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H79)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H79/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J79" s="33">
-        <f>IF(H79="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H79&lt;Config!$B$12,"Abaixo do mínimo",IF(H79&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H79="","",IF(NOT(ISNUMBER(H79)),H79,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H79&lt;Config!$B$12,"Abaixo do mínimo",IF(H79&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K79" s="25">
-        <f>IF(OR(H79="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G79-F79))</f>
+        <f>IF(OR(NOT(ISNUMBER(H79)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G79-F79))</f>
         <v/>
       </c>
       <c r="L79" s="41">
@@ -7195,19 +7195,19 @@
       <c r="F80" s="40" t="n"/>
       <c r="G80" s="23" t="n"/>
       <c r="H80" s="30">
-        <f>IF(OR(A80="",G80="",G80=0,F80=""),"",F80/G80)</f>
+        <f>IF(OR(A80="",G80="",F80=""),"",IF(OR(NOT(ISNUMBER(F80)),NOT(ISNUMBER(G80))),"valor ou horas inválidos",IF(G80=0,"",F80/G80)))</f>
         <v/>
       </c>
       <c r="I80" s="31">
-        <f>IF(OR(H80="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H80/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H80)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H80/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J80" s="33">
-        <f>IF(H80="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H80&lt;Config!$B$12,"Abaixo do mínimo",IF(H80&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H80="","",IF(NOT(ISNUMBER(H80)),H80,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H80&lt;Config!$B$12,"Abaixo do mínimo",IF(H80&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K80" s="25">
-        <f>IF(OR(H80="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G80-F80))</f>
+        <f>IF(OR(NOT(ISNUMBER(H80)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G80-F80))</f>
         <v/>
       </c>
       <c r="L80" s="41">
@@ -7224,19 +7224,19 @@
       <c r="F81" s="40" t="n"/>
       <c r="G81" s="23" t="n"/>
       <c r="H81" s="30">
-        <f>IF(OR(A81="",G81="",G81=0,F81=""),"",F81/G81)</f>
+        <f>IF(OR(A81="",G81="",F81=""),"",IF(OR(NOT(ISNUMBER(F81)),NOT(ISNUMBER(G81))),"valor ou horas inválidos",IF(G81=0,"",F81/G81)))</f>
         <v/>
       </c>
       <c r="I81" s="31">
-        <f>IF(OR(H81="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H81/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H81)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H81/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J81" s="33">
-        <f>IF(H81="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H81&lt;Config!$B$12,"Abaixo do mínimo",IF(H81&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H81="","",IF(NOT(ISNUMBER(H81)),H81,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H81&lt;Config!$B$12,"Abaixo do mínimo",IF(H81&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K81" s="25">
-        <f>IF(OR(H81="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G81-F81))</f>
+        <f>IF(OR(NOT(ISNUMBER(H81)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G81-F81))</f>
         <v/>
       </c>
       <c r="L81" s="41">
@@ -7253,19 +7253,19 @@
       <c r="F82" s="40" t="n"/>
       <c r="G82" s="23" t="n"/>
       <c r="H82" s="30">
-        <f>IF(OR(A82="",G82="",G82=0,F82=""),"",F82/G82)</f>
+        <f>IF(OR(A82="",G82="",F82=""),"",IF(OR(NOT(ISNUMBER(F82)),NOT(ISNUMBER(G82))),"valor ou horas inválidos",IF(G82=0,"",F82/G82)))</f>
         <v/>
       </c>
       <c r="I82" s="31">
-        <f>IF(OR(H82="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H82/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H82)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H82/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J82" s="33">
-        <f>IF(H82="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H82&lt;Config!$B$12,"Abaixo do mínimo",IF(H82&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H82="","",IF(NOT(ISNUMBER(H82)),H82,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H82&lt;Config!$B$12,"Abaixo do mínimo",IF(H82&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K82" s="25">
-        <f>IF(OR(H82="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G82-F82))</f>
+        <f>IF(OR(NOT(ISNUMBER(H82)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G82-F82))</f>
         <v/>
       </c>
       <c r="L82" s="41">
@@ -7282,19 +7282,19 @@
       <c r="F83" s="40" t="n"/>
       <c r="G83" s="23" t="n"/>
       <c r="H83" s="30">
-        <f>IF(OR(A83="",G83="",G83=0,F83=""),"",F83/G83)</f>
+        <f>IF(OR(A83="",G83="",F83=""),"",IF(OR(NOT(ISNUMBER(F83)),NOT(ISNUMBER(G83))),"valor ou horas inválidos",IF(G83=0,"",F83/G83)))</f>
         <v/>
       </c>
       <c r="I83" s="31">
-        <f>IF(OR(H83="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H83/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H83)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H83/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J83" s="33">
-        <f>IF(H83="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H83&lt;Config!$B$12,"Abaixo do mínimo",IF(H83&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H83="","",IF(NOT(ISNUMBER(H83)),H83,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H83&lt;Config!$B$12,"Abaixo do mínimo",IF(H83&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K83" s="25">
-        <f>IF(OR(H83="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G83-F83))</f>
+        <f>IF(OR(NOT(ISNUMBER(H83)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G83-F83))</f>
         <v/>
       </c>
       <c r="L83" s="41">
@@ -7311,19 +7311,19 @@
       <c r="F84" s="40" t="n"/>
       <c r="G84" s="23" t="n"/>
       <c r="H84" s="30">
-        <f>IF(OR(A84="",G84="",G84=0,F84=""),"",F84/G84)</f>
+        <f>IF(OR(A84="",G84="",F84=""),"",IF(OR(NOT(ISNUMBER(F84)),NOT(ISNUMBER(G84))),"valor ou horas inválidos",IF(G84=0,"",F84/G84)))</f>
         <v/>
       </c>
       <c r="I84" s="31">
-        <f>IF(OR(H84="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H84/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H84)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H84/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J84" s="33">
-        <f>IF(H84="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H84&lt;Config!$B$12,"Abaixo do mínimo",IF(H84&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H84="","",IF(NOT(ISNUMBER(H84)),H84,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H84&lt;Config!$B$12,"Abaixo do mínimo",IF(H84&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K84" s="25">
-        <f>IF(OR(H84="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G84-F84))</f>
+        <f>IF(OR(NOT(ISNUMBER(H84)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G84-F84))</f>
         <v/>
       </c>
       <c r="L84" s="41">
@@ -7340,19 +7340,19 @@
       <c r="F85" s="40" t="n"/>
       <c r="G85" s="23" t="n"/>
       <c r="H85" s="30">
-        <f>IF(OR(A85="",G85="",G85=0,F85=""),"",F85/G85)</f>
+        <f>IF(OR(A85="",G85="",F85=""),"",IF(OR(NOT(ISNUMBER(F85)),NOT(ISNUMBER(G85))),"valor ou horas inválidos",IF(G85=0,"",F85/G85)))</f>
         <v/>
       </c>
       <c r="I85" s="31">
-        <f>IF(OR(H85="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H85/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H85)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H85/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J85" s="33">
-        <f>IF(H85="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H85&lt;Config!$B$12,"Abaixo do mínimo",IF(H85&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H85="","",IF(NOT(ISNUMBER(H85)),H85,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H85&lt;Config!$B$12,"Abaixo do mínimo",IF(H85&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K85" s="25">
-        <f>IF(OR(H85="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G85-F85))</f>
+        <f>IF(OR(NOT(ISNUMBER(H85)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G85-F85))</f>
         <v/>
       </c>
       <c r="L85" s="41">
@@ -7369,19 +7369,19 @@
       <c r="F86" s="40" t="n"/>
       <c r="G86" s="23" t="n"/>
       <c r="H86" s="30">
-        <f>IF(OR(A86="",G86="",G86=0,F86=""),"",F86/G86)</f>
+        <f>IF(OR(A86="",G86="",F86=""),"",IF(OR(NOT(ISNUMBER(F86)),NOT(ISNUMBER(G86))),"valor ou horas inválidos",IF(G86=0,"",F86/G86)))</f>
         <v/>
       </c>
       <c r="I86" s="31">
-        <f>IF(OR(H86="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H86/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H86)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H86/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J86" s="33">
-        <f>IF(H86="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H86&lt;Config!$B$12,"Abaixo do mínimo",IF(H86&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H86="","",IF(NOT(ISNUMBER(H86)),H86,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H86&lt;Config!$B$12,"Abaixo do mínimo",IF(H86&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K86" s="25">
-        <f>IF(OR(H86="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G86-F86))</f>
+        <f>IF(OR(NOT(ISNUMBER(H86)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G86-F86))</f>
         <v/>
       </c>
       <c r="L86" s="41">
@@ -7398,19 +7398,19 @@
       <c r="F87" s="40" t="n"/>
       <c r="G87" s="23" t="n"/>
       <c r="H87" s="30">
-        <f>IF(OR(A87="",G87="",G87=0,F87=""),"",F87/G87)</f>
+        <f>IF(OR(A87="",G87="",F87=""),"",IF(OR(NOT(ISNUMBER(F87)),NOT(ISNUMBER(G87))),"valor ou horas inválidos",IF(G87=0,"",F87/G87)))</f>
         <v/>
       </c>
       <c r="I87" s="31">
-        <f>IF(OR(H87="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H87/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H87)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H87/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J87" s="33">
-        <f>IF(H87="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H87&lt;Config!$B$12,"Abaixo do mínimo",IF(H87&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H87="","",IF(NOT(ISNUMBER(H87)),H87,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H87&lt;Config!$B$12,"Abaixo do mínimo",IF(H87&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K87" s="25">
-        <f>IF(OR(H87="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G87-F87))</f>
+        <f>IF(OR(NOT(ISNUMBER(H87)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G87-F87))</f>
         <v/>
       </c>
       <c r="L87" s="41">
@@ -7427,19 +7427,19 @@
       <c r="F88" s="40" t="n"/>
       <c r="G88" s="23" t="n"/>
       <c r="H88" s="30">
-        <f>IF(OR(A88="",G88="",G88=0,F88=""),"",F88/G88)</f>
+        <f>IF(OR(A88="",G88="",F88=""),"",IF(OR(NOT(ISNUMBER(F88)),NOT(ISNUMBER(G88))),"valor ou horas inválidos",IF(G88=0,"",F88/G88)))</f>
         <v/>
       </c>
       <c r="I88" s="31">
-        <f>IF(OR(H88="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H88/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H88)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H88/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J88" s="33">
-        <f>IF(H88="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H88&lt;Config!$B$12,"Abaixo do mínimo",IF(H88&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H88="","",IF(NOT(ISNUMBER(H88)),H88,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H88&lt;Config!$B$12,"Abaixo do mínimo",IF(H88&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K88" s="25">
-        <f>IF(OR(H88="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G88-F88))</f>
+        <f>IF(OR(NOT(ISNUMBER(H88)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G88-F88))</f>
         <v/>
       </c>
       <c r="L88" s="41">
@@ -7456,19 +7456,19 @@
       <c r="F89" s="40" t="n"/>
       <c r="G89" s="23" t="n"/>
       <c r="H89" s="30">
-        <f>IF(OR(A89="",G89="",G89=0,F89=""),"",F89/G89)</f>
+        <f>IF(OR(A89="",G89="",F89=""),"",IF(OR(NOT(ISNUMBER(F89)),NOT(ISNUMBER(G89))),"valor ou horas inválidos",IF(G89=0,"",F89/G89)))</f>
         <v/>
       </c>
       <c r="I89" s="31">
-        <f>IF(OR(H89="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H89/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H89)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H89/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J89" s="33">
-        <f>IF(H89="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H89&lt;Config!$B$12,"Abaixo do mínimo",IF(H89&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H89="","",IF(NOT(ISNUMBER(H89)),H89,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H89&lt;Config!$B$12,"Abaixo do mínimo",IF(H89&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K89" s="25">
-        <f>IF(OR(H89="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G89-F89))</f>
+        <f>IF(OR(NOT(ISNUMBER(H89)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G89-F89))</f>
         <v/>
       </c>
       <c r="L89" s="41">
@@ -7485,19 +7485,19 @@
       <c r="F90" s="40" t="n"/>
       <c r="G90" s="23" t="n"/>
       <c r="H90" s="30">
-        <f>IF(OR(A90="",G90="",G90=0,F90=""),"",F90/G90)</f>
+        <f>IF(OR(A90="",G90="",F90=""),"",IF(OR(NOT(ISNUMBER(F90)),NOT(ISNUMBER(G90))),"valor ou horas inválidos",IF(G90=0,"",F90/G90)))</f>
         <v/>
       </c>
       <c r="I90" s="31">
-        <f>IF(OR(H90="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H90/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H90)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H90/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J90" s="33">
-        <f>IF(H90="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H90&lt;Config!$B$12,"Abaixo do mínimo",IF(H90&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H90="","",IF(NOT(ISNUMBER(H90)),H90,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H90&lt;Config!$B$12,"Abaixo do mínimo",IF(H90&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K90" s="25">
-        <f>IF(OR(H90="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G90-F90))</f>
+        <f>IF(OR(NOT(ISNUMBER(H90)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G90-F90))</f>
         <v/>
       </c>
       <c r="L90" s="41">
@@ -7514,19 +7514,19 @@
       <c r="F91" s="40" t="n"/>
       <c r="G91" s="23" t="n"/>
       <c r="H91" s="30">
-        <f>IF(OR(A91="",G91="",G91=0,F91=""),"",F91/G91)</f>
+        <f>IF(OR(A91="",G91="",F91=""),"",IF(OR(NOT(ISNUMBER(F91)),NOT(ISNUMBER(G91))),"valor ou horas inválidos",IF(G91=0,"",F91/G91)))</f>
         <v/>
       </c>
       <c r="I91" s="31">
-        <f>IF(OR(H91="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H91/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H91)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H91/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J91" s="33">
-        <f>IF(H91="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H91&lt;Config!$B$12,"Abaixo do mínimo",IF(H91&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H91="","",IF(NOT(ISNUMBER(H91)),H91,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H91&lt;Config!$B$12,"Abaixo do mínimo",IF(H91&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K91" s="25">
-        <f>IF(OR(H91="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G91-F91))</f>
+        <f>IF(OR(NOT(ISNUMBER(H91)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G91-F91))</f>
         <v/>
       </c>
       <c r="L91" s="41">
@@ -7543,19 +7543,19 @@
       <c r="F92" s="40" t="n"/>
       <c r="G92" s="23" t="n"/>
       <c r="H92" s="30">
-        <f>IF(OR(A92="",G92="",G92=0,F92=""),"",F92/G92)</f>
+        <f>IF(OR(A92="",G92="",F92=""),"",IF(OR(NOT(ISNUMBER(F92)),NOT(ISNUMBER(G92))),"valor ou horas inválidos",IF(G92=0,"",F92/G92)))</f>
         <v/>
       </c>
       <c r="I92" s="31">
-        <f>IF(OR(H92="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H92/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H92)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H92/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J92" s="33">
-        <f>IF(H92="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H92&lt;Config!$B$12,"Abaixo do mínimo",IF(H92&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H92="","",IF(NOT(ISNUMBER(H92)),H92,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H92&lt;Config!$B$12,"Abaixo do mínimo",IF(H92&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K92" s="25">
-        <f>IF(OR(H92="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G92-F92))</f>
+        <f>IF(OR(NOT(ISNUMBER(H92)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G92-F92))</f>
         <v/>
       </c>
       <c r="L92" s="41">
@@ -7572,19 +7572,19 @@
       <c r="F93" s="40" t="n"/>
       <c r="G93" s="23" t="n"/>
       <c r="H93" s="30">
-        <f>IF(OR(A93="",G93="",G93=0,F93=""),"",F93/G93)</f>
+        <f>IF(OR(A93="",G93="",F93=""),"",IF(OR(NOT(ISNUMBER(F93)),NOT(ISNUMBER(G93))),"valor ou horas inválidos",IF(G93=0,"",F93/G93)))</f>
         <v/>
       </c>
       <c r="I93" s="31">
-        <f>IF(OR(H93="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H93/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H93)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H93/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J93" s="33">
-        <f>IF(H93="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H93&lt;Config!$B$12,"Abaixo do mínimo",IF(H93&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H93="","",IF(NOT(ISNUMBER(H93)),H93,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H93&lt;Config!$B$12,"Abaixo do mínimo",IF(H93&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K93" s="25">
-        <f>IF(OR(H93="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G93-F93))</f>
+        <f>IF(OR(NOT(ISNUMBER(H93)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G93-F93))</f>
         <v/>
       </c>
       <c r="L93" s="41">
@@ -7601,19 +7601,19 @@
       <c r="F94" s="40" t="n"/>
       <c r="G94" s="23" t="n"/>
       <c r="H94" s="30">
-        <f>IF(OR(A94="",G94="",G94=0,F94=""),"",F94/G94)</f>
+        <f>IF(OR(A94="",G94="",F94=""),"",IF(OR(NOT(ISNUMBER(F94)),NOT(ISNUMBER(G94))),"valor ou horas inválidos",IF(G94=0,"",F94/G94)))</f>
         <v/>
       </c>
       <c r="I94" s="31">
-        <f>IF(OR(H94="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H94/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H94)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H94/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J94" s="33">
-        <f>IF(H94="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H94&lt;Config!$B$12,"Abaixo do mínimo",IF(H94&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H94="","",IF(NOT(ISNUMBER(H94)),H94,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H94&lt;Config!$B$12,"Abaixo do mínimo",IF(H94&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K94" s="25">
-        <f>IF(OR(H94="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G94-F94))</f>
+        <f>IF(OR(NOT(ISNUMBER(H94)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G94-F94))</f>
         <v/>
       </c>
       <c r="L94" s="41">
@@ -7630,19 +7630,19 @@
       <c r="F95" s="40" t="n"/>
       <c r="G95" s="23" t="n"/>
       <c r="H95" s="30">
-        <f>IF(OR(A95="",G95="",G95=0,F95=""),"",F95/G95)</f>
+        <f>IF(OR(A95="",G95="",F95=""),"",IF(OR(NOT(ISNUMBER(F95)),NOT(ISNUMBER(G95))),"valor ou horas inválidos",IF(G95=0,"",F95/G95)))</f>
         <v/>
       </c>
       <c r="I95" s="31">
-        <f>IF(OR(H95="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H95/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H95)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H95/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J95" s="33">
-        <f>IF(H95="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H95&lt;Config!$B$12,"Abaixo do mínimo",IF(H95&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H95="","",IF(NOT(ISNUMBER(H95)),H95,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H95&lt;Config!$B$12,"Abaixo do mínimo",IF(H95&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K95" s="25">
-        <f>IF(OR(H95="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G95-F95))</f>
+        <f>IF(OR(NOT(ISNUMBER(H95)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G95-F95))</f>
         <v/>
       </c>
       <c r="L95" s="41">
@@ -7659,19 +7659,19 @@
       <c r="F96" s="40" t="n"/>
       <c r="G96" s="23" t="n"/>
       <c r="H96" s="30">
-        <f>IF(OR(A96="",G96="",G96=0,F96=""),"",F96/G96)</f>
+        <f>IF(OR(A96="",G96="",F96=""),"",IF(OR(NOT(ISNUMBER(F96)),NOT(ISNUMBER(G96))),"valor ou horas inválidos",IF(G96=0,"",F96/G96)))</f>
         <v/>
       </c>
       <c r="I96" s="31">
-        <f>IF(OR(H96="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H96/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H96)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H96/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J96" s="33">
-        <f>IF(H96="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H96&lt;Config!$B$12,"Abaixo do mínimo",IF(H96&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H96="","",IF(NOT(ISNUMBER(H96)),H96,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H96&lt;Config!$B$12,"Abaixo do mínimo",IF(H96&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K96" s="25">
-        <f>IF(OR(H96="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G96-F96))</f>
+        <f>IF(OR(NOT(ISNUMBER(H96)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G96-F96))</f>
         <v/>
       </c>
       <c r="L96" s="41">
@@ -7688,19 +7688,19 @@
       <c r="F97" s="40" t="n"/>
       <c r="G97" s="23" t="n"/>
       <c r="H97" s="30">
-        <f>IF(OR(A97="",G97="",G97=0,F97=""),"",F97/G97)</f>
+        <f>IF(OR(A97="",G97="",F97=""),"",IF(OR(NOT(ISNUMBER(F97)),NOT(ISNUMBER(G97))),"valor ou horas inválidos",IF(G97=0,"",F97/G97)))</f>
         <v/>
       </c>
       <c r="I97" s="31">
-        <f>IF(OR(H97="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H97/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H97)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H97/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J97" s="33">
-        <f>IF(H97="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H97&lt;Config!$B$12,"Abaixo do mínimo",IF(H97&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H97="","",IF(NOT(ISNUMBER(H97)),H97,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H97&lt;Config!$B$12,"Abaixo do mínimo",IF(H97&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K97" s="25">
-        <f>IF(OR(H97="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G97-F97))</f>
+        <f>IF(OR(NOT(ISNUMBER(H97)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G97-F97))</f>
         <v/>
       </c>
       <c r="L97" s="41">
@@ -7717,19 +7717,19 @@
       <c r="F98" s="40" t="n"/>
       <c r="G98" s="23" t="n"/>
       <c r="H98" s="30">
-        <f>IF(OR(A98="",G98="",G98=0,F98=""),"",F98/G98)</f>
+        <f>IF(OR(A98="",G98="",F98=""),"",IF(OR(NOT(ISNUMBER(F98)),NOT(ISNUMBER(G98))),"valor ou horas inválidos",IF(G98=0,"",F98/G98)))</f>
         <v/>
       </c>
       <c r="I98" s="31">
-        <f>IF(OR(H98="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H98/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H98)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H98/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J98" s="33">
-        <f>IF(H98="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H98&lt;Config!$B$12,"Abaixo do mínimo",IF(H98&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H98="","",IF(NOT(ISNUMBER(H98)),H98,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H98&lt;Config!$B$12,"Abaixo do mínimo",IF(H98&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K98" s="25">
-        <f>IF(OR(H98="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G98-F98))</f>
+        <f>IF(OR(NOT(ISNUMBER(H98)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G98-F98))</f>
         <v/>
       </c>
       <c r="L98" s="41">
@@ -7746,19 +7746,19 @@
       <c r="F99" s="40" t="n"/>
       <c r="G99" s="23" t="n"/>
       <c r="H99" s="30">
-        <f>IF(OR(A99="",G99="",G99=0,F99=""),"",F99/G99)</f>
+        <f>IF(OR(A99="",G99="",F99=""),"",IF(OR(NOT(ISNUMBER(F99)),NOT(ISNUMBER(G99))),"valor ou horas inválidos",IF(G99=0,"",F99/G99)))</f>
         <v/>
       </c>
       <c r="I99" s="31">
-        <f>IF(OR(H99="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H99/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H99)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H99/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J99" s="33">
-        <f>IF(H99="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H99&lt;Config!$B$12,"Abaixo do mínimo",IF(H99&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H99="","",IF(NOT(ISNUMBER(H99)),H99,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H99&lt;Config!$B$12,"Abaixo do mínimo",IF(H99&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K99" s="25">
-        <f>IF(OR(H99="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G99-F99))</f>
+        <f>IF(OR(NOT(ISNUMBER(H99)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G99-F99))</f>
         <v/>
       </c>
       <c r="L99" s="41">
@@ -7775,19 +7775,19 @@
       <c r="F100" s="40" t="n"/>
       <c r="G100" s="23" t="n"/>
       <c r="H100" s="30">
-        <f>IF(OR(A100="",G100="",G100=0,F100=""),"",F100/G100)</f>
+        <f>IF(OR(A100="",G100="",F100=""),"",IF(OR(NOT(ISNUMBER(F100)),NOT(ISNUMBER(G100))),"valor ou horas inválidos",IF(G100=0,"",F100/G100)))</f>
         <v/>
       </c>
       <c r="I100" s="31">
-        <f>IF(OR(H100="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H100/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H100)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H100/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J100" s="33">
-        <f>IF(H100="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H100&lt;Config!$B$12,"Abaixo do mínimo",IF(H100&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H100="","",IF(NOT(ISNUMBER(H100)),H100,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H100&lt;Config!$B$12,"Abaixo do mínimo",IF(H100&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K100" s="25">
-        <f>IF(OR(H100="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G100-F100))</f>
+        <f>IF(OR(NOT(ISNUMBER(H100)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G100-F100))</f>
         <v/>
       </c>
       <c r="L100" s="41">
@@ -7804,19 +7804,19 @@
       <c r="F101" s="40" t="n"/>
       <c r="G101" s="23" t="n"/>
       <c r="H101" s="30">
-        <f>IF(OR(A101="",G101="",G101=0,F101=""),"",F101/G101)</f>
+        <f>IF(OR(A101="",G101="",F101=""),"",IF(OR(NOT(ISNUMBER(F101)),NOT(ISNUMBER(G101))),"valor ou horas inválidos",IF(G101=0,"",F101/G101)))</f>
         <v/>
       </c>
       <c r="I101" s="31">
-        <f>IF(OR(H101="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H101/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H101)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H101/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J101" s="33">
-        <f>IF(H101="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H101&lt;Config!$B$12,"Abaixo do mínimo",IF(H101&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H101="","",IF(NOT(ISNUMBER(H101)),H101,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H101&lt;Config!$B$12,"Abaixo do mínimo",IF(H101&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K101" s="25">
-        <f>IF(OR(H101="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G101-F101))</f>
+        <f>IF(OR(NOT(ISNUMBER(H101)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G101-F101))</f>
         <v/>
       </c>
       <c r="L101" s="41">
@@ -7833,19 +7833,19 @@
       <c r="F102" s="40" t="n"/>
       <c r="G102" s="23" t="n"/>
       <c r="H102" s="30">
-        <f>IF(OR(A102="",G102="",G102=0,F102=""),"",F102/G102)</f>
+        <f>IF(OR(A102="",G102="",F102=""),"",IF(OR(NOT(ISNUMBER(F102)),NOT(ISNUMBER(G102))),"valor ou horas inválidos",IF(G102=0,"",F102/G102)))</f>
         <v/>
       </c>
       <c r="I102" s="31">
-        <f>IF(OR(H102="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H102/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H102)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H102/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J102" s="33">
-        <f>IF(H102="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H102&lt;Config!$B$12,"Abaixo do mínimo",IF(H102&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H102="","",IF(NOT(ISNUMBER(H102)),H102,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H102&lt;Config!$B$12,"Abaixo do mínimo",IF(H102&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K102" s="25">
-        <f>IF(OR(H102="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G102-F102))</f>
+        <f>IF(OR(NOT(ISNUMBER(H102)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G102-F102))</f>
         <v/>
       </c>
       <c r="L102" s="41">
@@ -7862,19 +7862,19 @@
       <c r="F103" s="40" t="n"/>
       <c r="G103" s="23" t="n"/>
       <c r="H103" s="30">
-        <f>IF(OR(A103="",G103="",G103=0,F103=""),"",F103/G103)</f>
+        <f>IF(OR(A103="",G103="",F103=""),"",IF(OR(NOT(ISNUMBER(F103)),NOT(ISNUMBER(G103))),"valor ou horas inválidos",IF(G103=0,"",F103/G103)))</f>
         <v/>
       </c>
       <c r="I103" s="31">
-        <f>IF(OR(H103="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H103/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H103)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H103/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J103" s="33">
-        <f>IF(H103="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H103&lt;Config!$B$12,"Abaixo do mínimo",IF(H103&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H103="","",IF(NOT(ISNUMBER(H103)),H103,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H103&lt;Config!$B$12,"Abaixo do mínimo",IF(H103&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K103" s="25">
-        <f>IF(OR(H103="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G103-F103))</f>
+        <f>IF(OR(NOT(ISNUMBER(H103)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G103-F103))</f>
         <v/>
       </c>
       <c r="L103" s="41">
@@ -7891,19 +7891,19 @@
       <c r="F104" s="40" t="n"/>
       <c r="G104" s="23" t="n"/>
       <c r="H104" s="30">
-        <f>IF(OR(A104="",G104="",G104=0,F104=""),"",F104/G104)</f>
+        <f>IF(OR(A104="",G104="",F104=""),"",IF(OR(NOT(ISNUMBER(F104)),NOT(ISNUMBER(G104))),"valor ou horas inválidos",IF(G104=0,"",F104/G104)))</f>
         <v/>
       </c>
       <c r="I104" s="31">
-        <f>IF(OR(H104="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H104/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H104)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H104/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J104" s="33">
-        <f>IF(H104="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H104&lt;Config!$B$12,"Abaixo do mínimo",IF(H104&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H104="","",IF(NOT(ISNUMBER(H104)),H104,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H104&lt;Config!$B$12,"Abaixo do mínimo",IF(H104&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K104" s="25">
-        <f>IF(OR(H104="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G104-F104))</f>
+        <f>IF(OR(NOT(ISNUMBER(H104)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G104-F104))</f>
         <v/>
       </c>
       <c r="L104" s="41">
@@ -7920,19 +7920,19 @@
       <c r="F105" s="40" t="n"/>
       <c r="G105" s="23" t="n"/>
       <c r="H105" s="30">
-        <f>IF(OR(A105="",G105="",G105=0,F105=""),"",F105/G105)</f>
+        <f>IF(OR(A105="",G105="",F105=""),"",IF(OR(NOT(ISNUMBER(F105)),NOT(ISNUMBER(G105))),"valor ou horas inválidos",IF(G105=0,"",F105/G105)))</f>
         <v/>
       </c>
       <c r="I105" s="31">
-        <f>IF(OR(H105="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H105/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H105)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H105/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J105" s="33">
-        <f>IF(H105="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H105&lt;Config!$B$12,"Abaixo do mínimo",IF(H105&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H105="","",IF(NOT(ISNUMBER(H105)),H105,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H105&lt;Config!$B$12,"Abaixo do mínimo",IF(H105&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K105" s="25">
-        <f>IF(OR(H105="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G105-F105))</f>
+        <f>IF(OR(NOT(ISNUMBER(H105)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G105-F105))</f>
         <v/>
       </c>
       <c r="L105" s="41">
@@ -7949,19 +7949,19 @@
       <c r="F106" s="40" t="n"/>
       <c r="G106" s="23" t="n"/>
       <c r="H106" s="30">
-        <f>IF(OR(A106="",G106="",G106=0,F106=""),"",F106/G106)</f>
+        <f>IF(OR(A106="",G106="",F106=""),"",IF(OR(NOT(ISNUMBER(F106)),NOT(ISNUMBER(G106))),"valor ou horas inválidos",IF(G106=0,"",F106/G106)))</f>
         <v/>
       </c>
       <c r="I106" s="31">
-        <f>IF(OR(H106="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H106/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H106)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H106/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J106" s="33">
-        <f>IF(H106="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H106&lt;Config!$B$12,"Abaixo do mínimo",IF(H106&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H106="","",IF(NOT(ISNUMBER(H106)),H106,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H106&lt;Config!$B$12,"Abaixo do mínimo",IF(H106&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K106" s="25">
-        <f>IF(OR(H106="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G106-F106))</f>
+        <f>IF(OR(NOT(ISNUMBER(H106)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G106-F106))</f>
         <v/>
       </c>
       <c r="L106" s="41">
@@ -7978,19 +7978,19 @@
       <c r="F107" s="40" t="n"/>
       <c r="G107" s="23" t="n"/>
       <c r="H107" s="30">
-        <f>IF(OR(A107="",G107="",G107=0,F107=""),"",F107/G107)</f>
+        <f>IF(OR(A107="",G107="",F107=""),"",IF(OR(NOT(ISNUMBER(F107)),NOT(ISNUMBER(G107))),"valor ou horas inválidos",IF(G107=0,"",F107/G107)))</f>
         <v/>
       </c>
       <c r="I107" s="31">
-        <f>IF(OR(H107="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H107/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H107)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H107/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J107" s="33">
-        <f>IF(H107="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H107&lt;Config!$B$12,"Abaixo do mínimo",IF(H107&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H107="","",IF(NOT(ISNUMBER(H107)),H107,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H107&lt;Config!$B$12,"Abaixo do mínimo",IF(H107&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K107" s="25">
-        <f>IF(OR(H107="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G107-F107))</f>
+        <f>IF(OR(NOT(ISNUMBER(H107)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G107-F107))</f>
         <v/>
       </c>
       <c r="L107" s="41">
@@ -8007,19 +8007,19 @@
       <c r="F108" s="40" t="n"/>
       <c r="G108" s="23" t="n"/>
       <c r="H108" s="30">
-        <f>IF(OR(A108="",G108="",G108=0,F108=""),"",F108/G108)</f>
+        <f>IF(OR(A108="",G108="",F108=""),"",IF(OR(NOT(ISNUMBER(F108)),NOT(ISNUMBER(G108))),"valor ou horas inválidos",IF(G108=0,"",F108/G108)))</f>
         <v/>
       </c>
       <c r="I108" s="31">
-        <f>IF(OR(H108="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H108/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H108)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H108/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J108" s="33">
-        <f>IF(H108="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H108&lt;Config!$B$12,"Abaixo do mínimo",IF(H108&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H108="","",IF(NOT(ISNUMBER(H108)),H108,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H108&lt;Config!$B$12,"Abaixo do mínimo",IF(H108&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K108" s="25">
-        <f>IF(OR(H108="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G108-F108))</f>
+        <f>IF(OR(NOT(ISNUMBER(H108)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G108-F108))</f>
         <v/>
       </c>
       <c r="L108" s="41">
@@ -8036,19 +8036,19 @@
       <c r="F109" s="40" t="n"/>
       <c r="G109" s="23" t="n"/>
       <c r="H109" s="30">
-        <f>IF(OR(A109="",G109="",G109=0,F109=""),"",F109/G109)</f>
+        <f>IF(OR(A109="",G109="",F109=""),"",IF(OR(NOT(ISNUMBER(F109)),NOT(ISNUMBER(G109))),"valor ou horas inválidos",IF(G109=0,"",F109/G109)))</f>
         <v/>
       </c>
       <c r="I109" s="31">
-        <f>IF(OR(H109="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H109/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H109)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H109/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J109" s="33">
-        <f>IF(H109="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H109&lt;Config!$B$12,"Abaixo do mínimo",IF(H109&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H109="","",IF(NOT(ISNUMBER(H109)),H109,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H109&lt;Config!$B$12,"Abaixo do mínimo",IF(H109&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K109" s="25">
-        <f>IF(OR(H109="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G109-F109))</f>
+        <f>IF(OR(NOT(ISNUMBER(H109)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G109-F109))</f>
         <v/>
       </c>
       <c r="L109" s="41">
@@ -8065,19 +8065,19 @@
       <c r="F110" s="40" t="n"/>
       <c r="G110" s="23" t="n"/>
       <c r="H110" s="30">
-        <f>IF(OR(A110="",G110="",G110=0,F110=""),"",F110/G110)</f>
+        <f>IF(OR(A110="",G110="",F110=""),"",IF(OR(NOT(ISNUMBER(F110)),NOT(ISNUMBER(G110))),"valor ou horas inválidos",IF(G110=0,"",F110/G110)))</f>
         <v/>
       </c>
       <c r="I110" s="31">
-        <f>IF(OR(H110="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H110/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H110)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H110/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J110" s="33">
-        <f>IF(H110="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H110&lt;Config!$B$12,"Abaixo do mínimo",IF(H110&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H110="","",IF(NOT(ISNUMBER(H110)),H110,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H110&lt;Config!$B$12,"Abaixo do mínimo",IF(H110&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K110" s="25">
-        <f>IF(OR(H110="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G110-F110))</f>
+        <f>IF(OR(NOT(ISNUMBER(H110)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G110-F110))</f>
         <v/>
       </c>
       <c r="L110" s="41">
@@ -8094,19 +8094,19 @@
       <c r="F111" s="40" t="n"/>
       <c r="G111" s="23" t="n"/>
       <c r="H111" s="30">
-        <f>IF(OR(A111="",G111="",G111=0,F111=""),"",F111/G111)</f>
+        <f>IF(OR(A111="",G111="",F111=""),"",IF(OR(NOT(ISNUMBER(F111)),NOT(ISNUMBER(G111))),"valor ou horas inválidos",IF(G111=0,"",F111/G111)))</f>
         <v/>
       </c>
       <c r="I111" s="31">
-        <f>IF(OR(H111="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H111/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H111)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H111/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J111" s="33">
-        <f>IF(H111="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H111&lt;Config!$B$12,"Abaixo do mínimo",IF(H111&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H111="","",IF(NOT(ISNUMBER(H111)),H111,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H111&lt;Config!$B$12,"Abaixo do mínimo",IF(H111&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K111" s="25">
-        <f>IF(OR(H111="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G111-F111))</f>
+        <f>IF(OR(NOT(ISNUMBER(H111)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G111-F111))</f>
         <v/>
       </c>
       <c r="L111" s="41">
@@ -8123,19 +8123,19 @@
       <c r="F112" s="40" t="n"/>
       <c r="G112" s="23" t="n"/>
       <c r="H112" s="30">
-        <f>IF(OR(A112="",G112="",G112=0,F112=""),"",F112/G112)</f>
+        <f>IF(OR(A112="",G112="",F112=""),"",IF(OR(NOT(ISNUMBER(F112)),NOT(ISNUMBER(G112))),"valor ou horas inválidos",IF(G112=0,"",F112/G112)))</f>
         <v/>
       </c>
       <c r="I112" s="31">
-        <f>IF(OR(H112="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H112/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H112)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H112/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J112" s="33">
-        <f>IF(H112="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H112&lt;Config!$B$12,"Abaixo do mínimo",IF(H112&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H112="","",IF(NOT(ISNUMBER(H112)),H112,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H112&lt;Config!$B$12,"Abaixo do mínimo",IF(H112&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K112" s="25">
-        <f>IF(OR(H112="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G112-F112))</f>
+        <f>IF(OR(NOT(ISNUMBER(H112)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G112-F112))</f>
         <v/>
       </c>
       <c r="L112" s="41">
@@ -8152,19 +8152,19 @@
       <c r="F113" s="40" t="n"/>
       <c r="G113" s="23" t="n"/>
       <c r="H113" s="30">
-        <f>IF(OR(A113="",G113="",G113=0,F113=""),"",F113/G113)</f>
+        <f>IF(OR(A113="",G113="",F113=""),"",IF(OR(NOT(ISNUMBER(F113)),NOT(ISNUMBER(G113))),"valor ou horas inválidos",IF(G113=0,"",F113/G113)))</f>
         <v/>
       </c>
       <c r="I113" s="31">
-        <f>IF(OR(H113="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H113/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H113)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H113/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J113" s="33">
-        <f>IF(H113="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H113&lt;Config!$B$12,"Abaixo do mínimo",IF(H113&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H113="","",IF(NOT(ISNUMBER(H113)),H113,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H113&lt;Config!$B$12,"Abaixo do mínimo",IF(H113&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K113" s="25">
-        <f>IF(OR(H113="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G113-F113))</f>
+        <f>IF(OR(NOT(ISNUMBER(H113)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G113-F113))</f>
         <v/>
       </c>
       <c r="L113" s="41">
@@ -8181,19 +8181,19 @@
       <c r="F114" s="40" t="n"/>
       <c r="G114" s="23" t="n"/>
       <c r="H114" s="30">
-        <f>IF(OR(A114="",G114="",G114=0,F114=""),"",F114/G114)</f>
+        <f>IF(OR(A114="",G114="",F114=""),"",IF(OR(NOT(ISNUMBER(F114)),NOT(ISNUMBER(G114))),"valor ou horas inválidos",IF(G114=0,"",F114/G114)))</f>
         <v/>
       </c>
       <c r="I114" s="31">
-        <f>IF(OR(H114="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H114/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H114)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H114/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J114" s="33">
-        <f>IF(H114="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H114&lt;Config!$B$12,"Abaixo do mínimo",IF(H114&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H114="","",IF(NOT(ISNUMBER(H114)),H114,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H114&lt;Config!$B$12,"Abaixo do mínimo",IF(H114&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K114" s="25">
-        <f>IF(OR(H114="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G114-F114))</f>
+        <f>IF(OR(NOT(ISNUMBER(H114)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G114-F114))</f>
         <v/>
       </c>
       <c r="L114" s="41">
@@ -8210,19 +8210,19 @@
       <c r="F115" s="40" t="n"/>
       <c r="G115" s="23" t="n"/>
       <c r="H115" s="30">
-        <f>IF(OR(A115="",G115="",G115=0,F115=""),"",F115/G115)</f>
+        <f>IF(OR(A115="",G115="",F115=""),"",IF(OR(NOT(ISNUMBER(F115)),NOT(ISNUMBER(G115))),"valor ou horas inválidos",IF(G115=0,"",F115/G115)))</f>
         <v/>
       </c>
       <c r="I115" s="31">
-        <f>IF(OR(H115="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H115/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H115)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H115/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J115" s="33">
-        <f>IF(H115="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H115&lt;Config!$B$12,"Abaixo do mínimo",IF(H115&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H115="","",IF(NOT(ISNUMBER(H115)),H115,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H115&lt;Config!$B$12,"Abaixo do mínimo",IF(H115&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K115" s="25">
-        <f>IF(OR(H115="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G115-F115))</f>
+        <f>IF(OR(NOT(ISNUMBER(H115)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G115-F115))</f>
         <v/>
       </c>
       <c r="L115" s="41">
@@ -8239,19 +8239,19 @@
       <c r="F116" s="40" t="n"/>
       <c r="G116" s="23" t="n"/>
       <c r="H116" s="30">
-        <f>IF(OR(A116="",G116="",G116=0,F116=""),"",F116/G116)</f>
+        <f>IF(OR(A116="",G116="",F116=""),"",IF(OR(NOT(ISNUMBER(F116)),NOT(ISNUMBER(G116))),"valor ou horas inválidos",IF(G116=0,"",F116/G116)))</f>
         <v/>
       </c>
       <c r="I116" s="31">
-        <f>IF(OR(H116="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H116/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H116)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H116/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J116" s="33">
-        <f>IF(H116="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H116&lt;Config!$B$12,"Abaixo do mínimo",IF(H116&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H116="","",IF(NOT(ISNUMBER(H116)),H116,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H116&lt;Config!$B$12,"Abaixo do mínimo",IF(H116&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K116" s="25">
-        <f>IF(OR(H116="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G116-F116))</f>
+        <f>IF(OR(NOT(ISNUMBER(H116)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G116-F116))</f>
         <v/>
       </c>
       <c r="L116" s="41">
@@ -8268,19 +8268,19 @@
       <c r="F117" s="40" t="n"/>
       <c r="G117" s="23" t="n"/>
       <c r="H117" s="30">
-        <f>IF(OR(A117="",G117="",G117=0,F117=""),"",F117/G117)</f>
+        <f>IF(OR(A117="",G117="",F117=""),"",IF(OR(NOT(ISNUMBER(F117)),NOT(ISNUMBER(G117))),"valor ou horas inválidos",IF(G117=0,"",F117/G117)))</f>
         <v/>
       </c>
       <c r="I117" s="31">
-        <f>IF(OR(H117="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H117/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H117)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H117/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J117" s="33">
-        <f>IF(H117="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H117&lt;Config!$B$12,"Abaixo do mínimo",IF(H117&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H117="","",IF(NOT(ISNUMBER(H117)),H117,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H117&lt;Config!$B$12,"Abaixo do mínimo",IF(H117&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K117" s="25">
-        <f>IF(OR(H117="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G117-F117))</f>
+        <f>IF(OR(NOT(ISNUMBER(H117)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G117-F117))</f>
         <v/>
       </c>
       <c r="L117" s="41">
@@ -8297,19 +8297,19 @@
       <c r="F118" s="40" t="n"/>
       <c r="G118" s="23" t="n"/>
       <c r="H118" s="30">
-        <f>IF(OR(A118="",G118="",G118=0,F118=""),"",F118/G118)</f>
+        <f>IF(OR(A118="",G118="",F118=""),"",IF(OR(NOT(ISNUMBER(F118)),NOT(ISNUMBER(G118))),"valor ou horas inválidos",IF(G118=0,"",F118/G118)))</f>
         <v/>
       </c>
       <c r="I118" s="31">
-        <f>IF(OR(H118="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H118/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H118)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H118/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J118" s="33">
-        <f>IF(H118="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H118&lt;Config!$B$12,"Abaixo do mínimo",IF(H118&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H118="","",IF(NOT(ISNUMBER(H118)),H118,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H118&lt;Config!$B$12,"Abaixo do mínimo",IF(H118&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K118" s="25">
-        <f>IF(OR(H118="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G118-F118))</f>
+        <f>IF(OR(NOT(ISNUMBER(H118)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G118-F118))</f>
         <v/>
       </c>
       <c r="L118" s="41">
@@ -8326,19 +8326,19 @@
       <c r="F119" s="40" t="n"/>
       <c r="G119" s="23" t="n"/>
       <c r="H119" s="30">
-        <f>IF(OR(A119="",G119="",G119=0,F119=""),"",F119/G119)</f>
+        <f>IF(OR(A119="",G119="",F119=""),"",IF(OR(NOT(ISNUMBER(F119)),NOT(ISNUMBER(G119))),"valor ou horas inválidos",IF(G119=0,"",F119/G119)))</f>
         <v/>
       </c>
       <c r="I119" s="31">
-        <f>IF(OR(H119="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H119/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H119)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H119/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J119" s="33">
-        <f>IF(H119="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H119&lt;Config!$B$12,"Abaixo do mínimo",IF(H119&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H119="","",IF(NOT(ISNUMBER(H119)),H119,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H119&lt;Config!$B$12,"Abaixo do mínimo",IF(H119&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K119" s="25">
-        <f>IF(OR(H119="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G119-F119))</f>
+        <f>IF(OR(NOT(ISNUMBER(H119)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G119-F119))</f>
         <v/>
       </c>
       <c r="L119" s="41">
@@ -8355,19 +8355,19 @@
       <c r="F120" s="40" t="n"/>
       <c r="G120" s="23" t="n"/>
       <c r="H120" s="30">
-        <f>IF(OR(A120="",G120="",G120=0,F120=""),"",F120/G120)</f>
+        <f>IF(OR(A120="",G120="",F120=""),"",IF(OR(NOT(ISNUMBER(F120)),NOT(ISNUMBER(G120))),"valor ou horas inválidos",IF(G120=0,"",F120/G120)))</f>
         <v/>
       </c>
       <c r="I120" s="31">
-        <f>IF(OR(H120="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H120/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H120)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H120/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J120" s="33">
-        <f>IF(H120="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H120&lt;Config!$B$12,"Abaixo do mínimo",IF(H120&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H120="","",IF(NOT(ISNUMBER(H120)),H120,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H120&lt;Config!$B$12,"Abaixo do mínimo",IF(H120&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K120" s="25">
-        <f>IF(OR(H120="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G120-F120))</f>
+        <f>IF(OR(NOT(ISNUMBER(H120)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G120-F120))</f>
         <v/>
       </c>
       <c r="L120" s="41">
@@ -8384,19 +8384,19 @@
       <c r="F121" s="40" t="n"/>
       <c r="G121" s="23" t="n"/>
       <c r="H121" s="30">
-        <f>IF(OR(A121="",G121="",G121=0,F121=""),"",F121/G121)</f>
+        <f>IF(OR(A121="",G121="",F121=""),"",IF(OR(NOT(ISNUMBER(F121)),NOT(ISNUMBER(G121))),"valor ou horas inválidos",IF(G121=0,"",F121/G121)))</f>
         <v/>
       </c>
       <c r="I121" s="31">
-        <f>IF(OR(H121="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H121/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H121)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H121/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J121" s="33">
-        <f>IF(H121="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H121&lt;Config!$B$12,"Abaixo do mínimo",IF(H121&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H121="","",IF(NOT(ISNUMBER(H121)),H121,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H121&lt;Config!$B$12,"Abaixo do mínimo",IF(H121&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K121" s="25">
-        <f>IF(OR(H121="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G121-F121))</f>
+        <f>IF(OR(NOT(ISNUMBER(H121)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G121-F121))</f>
         <v/>
       </c>
       <c r="L121" s="41">
@@ -8413,19 +8413,19 @@
       <c r="F122" s="40" t="n"/>
       <c r="G122" s="23" t="n"/>
       <c r="H122" s="30">
-        <f>IF(OR(A122="",G122="",G122=0,F122=""),"",F122/G122)</f>
+        <f>IF(OR(A122="",G122="",F122=""),"",IF(OR(NOT(ISNUMBER(F122)),NOT(ISNUMBER(G122))),"valor ou horas inválidos",IF(G122=0,"",F122/G122)))</f>
         <v/>
       </c>
       <c r="I122" s="31">
-        <f>IF(OR(H122="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H122/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H122)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H122/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J122" s="33">
-        <f>IF(H122="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H122&lt;Config!$B$12,"Abaixo do mínimo",IF(H122&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H122="","",IF(NOT(ISNUMBER(H122)),H122,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H122&lt;Config!$B$12,"Abaixo do mínimo",IF(H122&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K122" s="25">
-        <f>IF(OR(H122="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G122-F122))</f>
+        <f>IF(OR(NOT(ISNUMBER(H122)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G122-F122))</f>
         <v/>
       </c>
       <c r="L122" s="41">
@@ -8442,19 +8442,19 @@
       <c r="F123" s="40" t="n"/>
       <c r="G123" s="23" t="n"/>
       <c r="H123" s="30">
-        <f>IF(OR(A123="",G123="",G123=0,F123=""),"",F123/G123)</f>
+        <f>IF(OR(A123="",G123="",F123=""),"",IF(OR(NOT(ISNUMBER(F123)),NOT(ISNUMBER(G123))),"valor ou horas inválidos",IF(G123=0,"",F123/G123)))</f>
         <v/>
       </c>
       <c r="I123" s="31">
-        <f>IF(OR(H123="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H123/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H123)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H123/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J123" s="33">
-        <f>IF(H123="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H123&lt;Config!$B$12,"Abaixo do mínimo",IF(H123&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H123="","",IF(NOT(ISNUMBER(H123)),H123,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H123&lt;Config!$B$12,"Abaixo do mínimo",IF(H123&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K123" s="25">
-        <f>IF(OR(H123="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G123-F123))</f>
+        <f>IF(OR(NOT(ISNUMBER(H123)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G123-F123))</f>
         <v/>
       </c>
       <c r="L123" s="41">
@@ -8471,19 +8471,19 @@
       <c r="F124" s="40" t="n"/>
       <c r="G124" s="23" t="n"/>
       <c r="H124" s="30">
-        <f>IF(OR(A124="",G124="",G124=0,F124=""),"",F124/G124)</f>
+        <f>IF(OR(A124="",G124="",F124=""),"",IF(OR(NOT(ISNUMBER(F124)),NOT(ISNUMBER(G124))),"valor ou horas inválidos",IF(G124=0,"",F124/G124)))</f>
         <v/>
       </c>
       <c r="I124" s="31">
-        <f>IF(OR(H124="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H124/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H124)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H124/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J124" s="33">
-        <f>IF(H124="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H124&lt;Config!$B$12,"Abaixo do mínimo",IF(H124&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H124="","",IF(NOT(ISNUMBER(H124)),H124,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H124&lt;Config!$B$12,"Abaixo do mínimo",IF(H124&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K124" s="25">
-        <f>IF(OR(H124="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G124-F124))</f>
+        <f>IF(OR(NOT(ISNUMBER(H124)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G124-F124))</f>
         <v/>
       </c>
       <c r="L124" s="41">
@@ -8500,19 +8500,19 @@
       <c r="F125" s="40" t="n"/>
       <c r="G125" s="23" t="n"/>
       <c r="H125" s="30">
-        <f>IF(OR(A125="",G125="",G125=0,F125=""),"",F125/G125)</f>
+        <f>IF(OR(A125="",G125="",F125=""),"",IF(OR(NOT(ISNUMBER(F125)),NOT(ISNUMBER(G125))),"valor ou horas inválidos",IF(G125=0,"",F125/G125)))</f>
         <v/>
       </c>
       <c r="I125" s="31">
-        <f>IF(OR(H125="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H125/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H125)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H125/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J125" s="33">
-        <f>IF(H125="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H125&lt;Config!$B$12,"Abaixo do mínimo",IF(H125&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H125="","",IF(NOT(ISNUMBER(H125)),H125,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H125&lt;Config!$B$12,"Abaixo do mínimo",IF(H125&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K125" s="25">
-        <f>IF(OR(H125="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G125-F125))</f>
+        <f>IF(OR(NOT(ISNUMBER(H125)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G125-F125))</f>
         <v/>
       </c>
       <c r="L125" s="41">
@@ -8529,19 +8529,19 @@
       <c r="F126" s="40" t="n"/>
       <c r="G126" s="23" t="n"/>
       <c r="H126" s="30">
-        <f>IF(OR(A126="",G126="",G126=0,F126=""),"",F126/G126)</f>
+        <f>IF(OR(A126="",G126="",F126=""),"",IF(OR(NOT(ISNUMBER(F126)),NOT(ISNUMBER(G126))),"valor ou horas inválidos",IF(G126=0,"",F126/G126)))</f>
         <v/>
       </c>
       <c r="I126" s="31">
-        <f>IF(OR(H126="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H126/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H126)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H126/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J126" s="33">
-        <f>IF(H126="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H126&lt;Config!$B$12,"Abaixo do mínimo",IF(H126&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H126="","",IF(NOT(ISNUMBER(H126)),H126,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H126&lt;Config!$B$12,"Abaixo do mínimo",IF(H126&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K126" s="25">
-        <f>IF(OR(H126="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G126-F126))</f>
+        <f>IF(OR(NOT(ISNUMBER(H126)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G126-F126))</f>
         <v/>
       </c>
       <c r="L126" s="41">
@@ -8558,19 +8558,19 @@
       <c r="F127" s="40" t="n"/>
       <c r="G127" s="23" t="n"/>
       <c r="H127" s="30">
-        <f>IF(OR(A127="",G127="",G127=0,F127=""),"",F127/G127)</f>
+        <f>IF(OR(A127="",G127="",F127=""),"",IF(OR(NOT(ISNUMBER(F127)),NOT(ISNUMBER(G127))),"valor ou horas inválidos",IF(G127=0,"",F127/G127)))</f>
         <v/>
       </c>
       <c r="I127" s="31">
-        <f>IF(OR(H127="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H127/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H127)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H127/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J127" s="33">
-        <f>IF(H127="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H127&lt;Config!$B$12,"Abaixo do mínimo",IF(H127&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H127="","",IF(NOT(ISNUMBER(H127)),H127,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H127&lt;Config!$B$12,"Abaixo do mínimo",IF(H127&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K127" s="25">
-        <f>IF(OR(H127="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G127-F127))</f>
+        <f>IF(OR(NOT(ISNUMBER(H127)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G127-F127))</f>
         <v/>
       </c>
       <c r="L127" s="41">
@@ -8587,19 +8587,19 @@
       <c r="F128" s="40" t="n"/>
       <c r="G128" s="23" t="n"/>
       <c r="H128" s="30">
-        <f>IF(OR(A128="",G128="",G128=0,F128=""),"",F128/G128)</f>
+        <f>IF(OR(A128="",G128="",F128=""),"",IF(OR(NOT(ISNUMBER(F128)),NOT(ISNUMBER(G128))),"valor ou horas inválidos",IF(G128=0,"",F128/G128)))</f>
         <v/>
       </c>
       <c r="I128" s="31">
-        <f>IF(OR(H128="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H128/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H128)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H128/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J128" s="33">
-        <f>IF(H128="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H128&lt;Config!$B$12,"Abaixo do mínimo",IF(H128&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H128="","",IF(NOT(ISNUMBER(H128)),H128,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H128&lt;Config!$B$12,"Abaixo do mínimo",IF(H128&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K128" s="25">
-        <f>IF(OR(H128="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G128-F128))</f>
+        <f>IF(OR(NOT(ISNUMBER(H128)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G128-F128))</f>
         <v/>
       </c>
       <c r="L128" s="41">
@@ -8616,19 +8616,19 @@
       <c r="F129" s="40" t="n"/>
       <c r="G129" s="23" t="n"/>
       <c r="H129" s="30">
-        <f>IF(OR(A129="",G129="",G129=0,F129=""),"",F129/G129)</f>
+        <f>IF(OR(A129="",G129="",F129=""),"",IF(OR(NOT(ISNUMBER(F129)),NOT(ISNUMBER(G129))),"valor ou horas inválidos",IF(G129=0,"",F129/G129)))</f>
         <v/>
       </c>
       <c r="I129" s="31">
-        <f>IF(OR(H129="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H129/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H129)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H129/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J129" s="33">
-        <f>IF(H129="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H129&lt;Config!$B$12,"Abaixo do mínimo",IF(H129&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H129="","",IF(NOT(ISNUMBER(H129)),H129,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H129&lt;Config!$B$12,"Abaixo do mínimo",IF(H129&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K129" s="25">
-        <f>IF(OR(H129="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G129-F129))</f>
+        <f>IF(OR(NOT(ISNUMBER(H129)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G129-F129))</f>
         <v/>
       </c>
       <c r="L129" s="41">
@@ -8645,19 +8645,19 @@
       <c r="F130" s="40" t="n"/>
       <c r="G130" s="23" t="n"/>
       <c r="H130" s="30">
-        <f>IF(OR(A130="",G130="",G130=0,F130=""),"",F130/G130)</f>
+        <f>IF(OR(A130="",G130="",F130=""),"",IF(OR(NOT(ISNUMBER(F130)),NOT(ISNUMBER(G130))),"valor ou horas inválidos",IF(G130=0,"",F130/G130)))</f>
         <v/>
       </c>
       <c r="I130" s="31">
-        <f>IF(OR(H130="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H130/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H130)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H130/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J130" s="33">
-        <f>IF(H130="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H130&lt;Config!$B$12,"Abaixo do mínimo",IF(H130&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H130="","",IF(NOT(ISNUMBER(H130)),H130,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H130&lt;Config!$B$12,"Abaixo do mínimo",IF(H130&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K130" s="25">
-        <f>IF(OR(H130="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G130-F130))</f>
+        <f>IF(OR(NOT(ISNUMBER(H130)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G130-F130))</f>
         <v/>
       </c>
       <c r="L130" s="41">
@@ -8674,19 +8674,19 @@
       <c r="F131" s="40" t="n"/>
       <c r="G131" s="23" t="n"/>
       <c r="H131" s="30">
-        <f>IF(OR(A131="",G131="",G131=0,F131=""),"",F131/G131)</f>
+        <f>IF(OR(A131="",G131="",F131=""),"",IF(OR(NOT(ISNUMBER(F131)),NOT(ISNUMBER(G131))),"valor ou horas inválidos",IF(G131=0,"",F131/G131)))</f>
         <v/>
       </c>
       <c r="I131" s="31">
-        <f>IF(OR(H131="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H131/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H131)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H131/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J131" s="33">
-        <f>IF(H131="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H131&lt;Config!$B$12,"Abaixo do mínimo",IF(H131&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H131="","",IF(NOT(ISNUMBER(H131)),H131,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H131&lt;Config!$B$12,"Abaixo do mínimo",IF(H131&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K131" s="25">
-        <f>IF(OR(H131="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G131-F131))</f>
+        <f>IF(OR(NOT(ISNUMBER(H131)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G131-F131))</f>
         <v/>
       </c>
       <c r="L131" s="41">
@@ -8703,19 +8703,19 @@
       <c r="F132" s="40" t="n"/>
       <c r="G132" s="23" t="n"/>
       <c r="H132" s="30">
-        <f>IF(OR(A132="",G132="",G132=0,F132=""),"",F132/G132)</f>
+        <f>IF(OR(A132="",G132="",F132=""),"",IF(OR(NOT(ISNUMBER(F132)),NOT(ISNUMBER(G132))),"valor ou horas inválidos",IF(G132=0,"",F132/G132)))</f>
         <v/>
       </c>
       <c r="I132" s="31">
-        <f>IF(OR(H132="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H132/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H132)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H132/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J132" s="33">
-        <f>IF(H132="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H132&lt;Config!$B$12,"Abaixo do mínimo",IF(H132&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H132="","",IF(NOT(ISNUMBER(H132)),H132,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H132&lt;Config!$B$12,"Abaixo do mínimo",IF(H132&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K132" s="25">
-        <f>IF(OR(H132="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G132-F132))</f>
+        <f>IF(OR(NOT(ISNUMBER(H132)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G132-F132))</f>
         <v/>
       </c>
       <c r="L132" s="41">
@@ -8732,19 +8732,19 @@
       <c r="F133" s="40" t="n"/>
       <c r="G133" s="23" t="n"/>
       <c r="H133" s="30">
-        <f>IF(OR(A133="",G133="",G133=0,F133=""),"",F133/G133)</f>
+        <f>IF(OR(A133="",G133="",F133=""),"",IF(OR(NOT(ISNUMBER(F133)),NOT(ISNUMBER(G133))),"valor ou horas inválidos",IF(G133=0,"",F133/G133)))</f>
         <v/>
       </c>
       <c r="I133" s="31">
-        <f>IF(OR(H133="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H133/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H133)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H133/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J133" s="33">
-        <f>IF(H133="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H133&lt;Config!$B$12,"Abaixo do mínimo",IF(H133&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H133="","",IF(NOT(ISNUMBER(H133)),H133,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H133&lt;Config!$B$12,"Abaixo do mínimo",IF(H133&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K133" s="25">
-        <f>IF(OR(H133="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G133-F133))</f>
+        <f>IF(OR(NOT(ISNUMBER(H133)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G133-F133))</f>
         <v/>
       </c>
       <c r="L133" s="41">
@@ -8761,19 +8761,19 @@
       <c r="F134" s="40" t="n"/>
       <c r="G134" s="23" t="n"/>
       <c r="H134" s="30">
-        <f>IF(OR(A134="",G134="",G134=0,F134=""),"",F134/G134)</f>
+        <f>IF(OR(A134="",G134="",F134=""),"",IF(OR(NOT(ISNUMBER(F134)),NOT(ISNUMBER(G134))),"valor ou horas inválidos",IF(G134=0,"",F134/G134)))</f>
         <v/>
       </c>
       <c r="I134" s="31">
-        <f>IF(OR(H134="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H134/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H134)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H134/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J134" s="33">
-        <f>IF(H134="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H134&lt;Config!$B$12,"Abaixo do mínimo",IF(H134&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H134="","",IF(NOT(ISNUMBER(H134)),H134,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H134&lt;Config!$B$12,"Abaixo do mínimo",IF(H134&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K134" s="25">
-        <f>IF(OR(H134="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G134-F134))</f>
+        <f>IF(OR(NOT(ISNUMBER(H134)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G134-F134))</f>
         <v/>
       </c>
       <c r="L134" s="41">
@@ -8790,19 +8790,19 @@
       <c r="F135" s="40" t="n"/>
       <c r="G135" s="23" t="n"/>
       <c r="H135" s="30">
-        <f>IF(OR(A135="",G135="",G135=0,F135=""),"",F135/G135)</f>
+        <f>IF(OR(A135="",G135="",F135=""),"",IF(OR(NOT(ISNUMBER(F135)),NOT(ISNUMBER(G135))),"valor ou horas inválidos",IF(G135=0,"",F135/G135)))</f>
         <v/>
       </c>
       <c r="I135" s="31">
-        <f>IF(OR(H135="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H135/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H135)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H135/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J135" s="33">
-        <f>IF(H135="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H135&lt;Config!$B$12,"Abaixo do mínimo",IF(H135&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H135="","",IF(NOT(ISNUMBER(H135)),H135,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H135&lt;Config!$B$12,"Abaixo do mínimo",IF(H135&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K135" s="25">
-        <f>IF(OR(H135="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G135-F135))</f>
+        <f>IF(OR(NOT(ISNUMBER(H135)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G135-F135))</f>
         <v/>
       </c>
       <c r="L135" s="41">
@@ -8819,19 +8819,19 @@
       <c r="F136" s="40" t="n"/>
       <c r="G136" s="23" t="n"/>
       <c r="H136" s="30">
-        <f>IF(OR(A136="",G136="",G136=0,F136=""),"",F136/G136)</f>
+        <f>IF(OR(A136="",G136="",F136=""),"",IF(OR(NOT(ISNUMBER(F136)),NOT(ISNUMBER(G136))),"valor ou horas inválidos",IF(G136=0,"",F136/G136)))</f>
         <v/>
       </c>
       <c r="I136" s="31">
-        <f>IF(OR(H136="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H136/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H136)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H136/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J136" s="33">
-        <f>IF(H136="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H136&lt;Config!$B$12,"Abaixo do mínimo",IF(H136&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H136="","",IF(NOT(ISNUMBER(H136)),H136,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H136&lt;Config!$B$12,"Abaixo do mínimo",IF(H136&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K136" s="25">
-        <f>IF(OR(H136="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G136-F136))</f>
+        <f>IF(OR(NOT(ISNUMBER(H136)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G136-F136))</f>
         <v/>
       </c>
       <c r="L136" s="41">
@@ -8848,19 +8848,19 @@
       <c r="F137" s="40" t="n"/>
       <c r="G137" s="23" t="n"/>
       <c r="H137" s="30">
-        <f>IF(OR(A137="",G137="",G137=0,F137=""),"",F137/G137)</f>
+        <f>IF(OR(A137="",G137="",F137=""),"",IF(OR(NOT(ISNUMBER(F137)),NOT(ISNUMBER(G137))),"valor ou horas inválidos",IF(G137=0,"",F137/G137)))</f>
         <v/>
       </c>
       <c r="I137" s="31">
-        <f>IF(OR(H137="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H137/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H137)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H137/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J137" s="33">
-        <f>IF(H137="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H137&lt;Config!$B$12,"Abaixo do mínimo",IF(H137&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H137="","",IF(NOT(ISNUMBER(H137)),H137,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H137&lt;Config!$B$12,"Abaixo do mínimo",IF(H137&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K137" s="25">
-        <f>IF(OR(H137="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G137-F137))</f>
+        <f>IF(OR(NOT(ISNUMBER(H137)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G137-F137))</f>
         <v/>
       </c>
       <c r="L137" s="41">
@@ -8877,19 +8877,19 @@
       <c r="F138" s="40" t="n"/>
       <c r="G138" s="23" t="n"/>
       <c r="H138" s="30">
-        <f>IF(OR(A138="",G138="",G138=0,F138=""),"",F138/G138)</f>
+        <f>IF(OR(A138="",G138="",F138=""),"",IF(OR(NOT(ISNUMBER(F138)),NOT(ISNUMBER(G138))),"valor ou horas inválidos",IF(G138=0,"",F138/G138)))</f>
         <v/>
       </c>
       <c r="I138" s="31">
-        <f>IF(OR(H138="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H138/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H138)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H138/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J138" s="33">
-        <f>IF(H138="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H138&lt;Config!$B$12,"Abaixo do mínimo",IF(H138&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H138="","",IF(NOT(ISNUMBER(H138)),H138,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H138&lt;Config!$B$12,"Abaixo do mínimo",IF(H138&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K138" s="25">
-        <f>IF(OR(H138="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G138-F138))</f>
+        <f>IF(OR(NOT(ISNUMBER(H138)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G138-F138))</f>
         <v/>
       </c>
       <c r="L138" s="41">
@@ -8906,19 +8906,19 @@
       <c r="F139" s="40" t="n"/>
       <c r="G139" s="23" t="n"/>
       <c r="H139" s="30">
-        <f>IF(OR(A139="",G139="",G139=0,F139=""),"",F139/G139)</f>
+        <f>IF(OR(A139="",G139="",F139=""),"",IF(OR(NOT(ISNUMBER(F139)),NOT(ISNUMBER(G139))),"valor ou horas inválidos",IF(G139=0,"",F139/G139)))</f>
         <v/>
       </c>
       <c r="I139" s="31">
-        <f>IF(OR(H139="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H139/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H139)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H139/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J139" s="33">
-        <f>IF(H139="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H139&lt;Config!$B$12,"Abaixo do mínimo",IF(H139&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H139="","",IF(NOT(ISNUMBER(H139)),H139,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H139&lt;Config!$B$12,"Abaixo do mínimo",IF(H139&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K139" s="25">
-        <f>IF(OR(H139="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G139-F139))</f>
+        <f>IF(OR(NOT(ISNUMBER(H139)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G139-F139))</f>
         <v/>
       </c>
       <c r="L139" s="41">
@@ -8935,19 +8935,19 @@
       <c r="F140" s="40" t="n"/>
       <c r="G140" s="23" t="n"/>
       <c r="H140" s="30">
-        <f>IF(OR(A140="",G140="",G140=0,F140=""),"",F140/G140)</f>
+        <f>IF(OR(A140="",G140="",F140=""),"",IF(OR(NOT(ISNUMBER(F140)),NOT(ISNUMBER(G140))),"valor ou horas inválidos",IF(G140=0,"",F140/G140)))</f>
         <v/>
       </c>
       <c r="I140" s="31">
-        <f>IF(OR(H140="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H140/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H140)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H140/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J140" s="33">
-        <f>IF(H140="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H140&lt;Config!$B$12,"Abaixo do mínimo",IF(H140&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H140="","",IF(NOT(ISNUMBER(H140)),H140,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H140&lt;Config!$B$12,"Abaixo do mínimo",IF(H140&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K140" s="25">
-        <f>IF(OR(H140="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G140-F140))</f>
+        <f>IF(OR(NOT(ISNUMBER(H140)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G140-F140))</f>
         <v/>
       </c>
       <c r="L140" s="41">
@@ -8964,19 +8964,19 @@
       <c r="F141" s="40" t="n"/>
       <c r="G141" s="23" t="n"/>
       <c r="H141" s="30">
-        <f>IF(OR(A141="",G141="",G141=0,F141=""),"",F141/G141)</f>
+        <f>IF(OR(A141="",G141="",F141=""),"",IF(OR(NOT(ISNUMBER(F141)),NOT(ISNUMBER(G141))),"valor ou horas inválidos",IF(G141=0,"",F141/G141)))</f>
         <v/>
       </c>
       <c r="I141" s="31">
-        <f>IF(OR(H141="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H141/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H141)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H141/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J141" s="33">
-        <f>IF(H141="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H141&lt;Config!$B$12,"Abaixo do mínimo",IF(H141&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H141="","",IF(NOT(ISNUMBER(H141)),H141,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H141&lt;Config!$B$12,"Abaixo do mínimo",IF(H141&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K141" s="25">
-        <f>IF(OR(H141="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G141-F141))</f>
+        <f>IF(OR(NOT(ISNUMBER(H141)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G141-F141))</f>
         <v/>
       </c>
       <c r="L141" s="41">
@@ -8993,19 +8993,19 @@
       <c r="F142" s="40" t="n"/>
       <c r="G142" s="23" t="n"/>
       <c r="H142" s="30">
-        <f>IF(OR(A142="",G142="",G142=0,F142=""),"",F142/G142)</f>
+        <f>IF(OR(A142="",G142="",F142=""),"",IF(OR(NOT(ISNUMBER(F142)),NOT(ISNUMBER(G142))),"valor ou horas inválidos",IF(G142=0,"",F142/G142)))</f>
         <v/>
       </c>
       <c r="I142" s="31">
-        <f>IF(OR(H142="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H142/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H142)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H142/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J142" s="33">
-        <f>IF(H142="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H142&lt;Config!$B$12,"Abaixo do mínimo",IF(H142&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H142="","",IF(NOT(ISNUMBER(H142)),H142,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H142&lt;Config!$B$12,"Abaixo do mínimo",IF(H142&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K142" s="25">
-        <f>IF(OR(H142="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G142-F142))</f>
+        <f>IF(OR(NOT(ISNUMBER(H142)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G142-F142))</f>
         <v/>
       </c>
       <c r="L142" s="41">
@@ -9022,19 +9022,19 @@
       <c r="F143" s="40" t="n"/>
       <c r="G143" s="23" t="n"/>
       <c r="H143" s="30">
-        <f>IF(OR(A143="",G143="",G143=0,F143=""),"",F143/G143)</f>
+        <f>IF(OR(A143="",G143="",F143=""),"",IF(OR(NOT(ISNUMBER(F143)),NOT(ISNUMBER(G143))),"valor ou horas inválidos",IF(G143=0,"",F143/G143)))</f>
         <v/>
       </c>
       <c r="I143" s="31">
-        <f>IF(OR(H143="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H143/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H143)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H143/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J143" s="33">
-        <f>IF(H143="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H143&lt;Config!$B$12,"Abaixo do mínimo",IF(H143&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H143="","",IF(NOT(ISNUMBER(H143)),H143,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H143&lt;Config!$B$12,"Abaixo do mínimo",IF(H143&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K143" s="25">
-        <f>IF(OR(H143="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G143-F143))</f>
+        <f>IF(OR(NOT(ISNUMBER(H143)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G143-F143))</f>
         <v/>
       </c>
       <c r="L143" s="41">
@@ -9051,19 +9051,19 @@
       <c r="F144" s="40" t="n"/>
       <c r="G144" s="23" t="n"/>
       <c r="H144" s="30">
-        <f>IF(OR(A144="",G144="",G144=0,F144=""),"",F144/G144)</f>
+        <f>IF(OR(A144="",G144="",F144=""),"",IF(OR(NOT(ISNUMBER(F144)),NOT(ISNUMBER(G144))),"valor ou horas inválidos",IF(G144=0,"",F144/G144)))</f>
         <v/>
       </c>
       <c r="I144" s="31">
-        <f>IF(OR(H144="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H144/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H144)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H144/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J144" s="33">
-        <f>IF(H144="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H144&lt;Config!$B$12,"Abaixo do mínimo",IF(H144&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H144="","",IF(NOT(ISNUMBER(H144)),H144,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H144&lt;Config!$B$12,"Abaixo do mínimo",IF(H144&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K144" s="25">
-        <f>IF(OR(H144="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G144-F144))</f>
+        <f>IF(OR(NOT(ISNUMBER(H144)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G144-F144))</f>
         <v/>
       </c>
       <c r="L144" s="41">
@@ -9080,19 +9080,19 @@
       <c r="F145" s="40" t="n"/>
       <c r="G145" s="23" t="n"/>
       <c r="H145" s="30">
-        <f>IF(OR(A145="",G145="",G145=0,F145=""),"",F145/G145)</f>
+        <f>IF(OR(A145="",G145="",F145=""),"",IF(OR(NOT(ISNUMBER(F145)),NOT(ISNUMBER(G145))),"valor ou horas inválidos",IF(G145=0,"",F145/G145)))</f>
         <v/>
       </c>
       <c r="I145" s="31">
-        <f>IF(OR(H145="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H145/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H145)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H145/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J145" s="33">
-        <f>IF(H145="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H145&lt;Config!$B$12,"Abaixo do mínimo",IF(H145&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H145="","",IF(NOT(ISNUMBER(H145)),H145,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H145&lt;Config!$B$12,"Abaixo do mínimo",IF(H145&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K145" s="25">
-        <f>IF(OR(H145="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G145-F145))</f>
+        <f>IF(OR(NOT(ISNUMBER(H145)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G145-F145))</f>
         <v/>
       </c>
       <c r="L145" s="41">
@@ -9109,19 +9109,19 @@
       <c r="F146" s="40" t="n"/>
       <c r="G146" s="23" t="n"/>
       <c r="H146" s="30">
-        <f>IF(OR(A146="",G146="",G146=0,F146=""),"",F146/G146)</f>
+        <f>IF(OR(A146="",G146="",F146=""),"",IF(OR(NOT(ISNUMBER(F146)),NOT(ISNUMBER(G146))),"valor ou horas inválidos",IF(G146=0,"",F146/G146)))</f>
         <v/>
       </c>
       <c r="I146" s="31">
-        <f>IF(OR(H146="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H146/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H146)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H146/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J146" s="33">
-        <f>IF(H146="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H146&lt;Config!$B$12,"Abaixo do mínimo",IF(H146&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H146="","",IF(NOT(ISNUMBER(H146)),H146,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H146&lt;Config!$B$12,"Abaixo do mínimo",IF(H146&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K146" s="25">
-        <f>IF(OR(H146="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G146-F146))</f>
+        <f>IF(OR(NOT(ISNUMBER(H146)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G146-F146))</f>
         <v/>
       </c>
       <c r="L146" s="41">
@@ -9138,19 +9138,19 @@
       <c r="F147" s="40" t="n"/>
       <c r="G147" s="23" t="n"/>
       <c r="H147" s="30">
-        <f>IF(OR(A147="",G147="",G147=0,F147=""),"",F147/G147)</f>
+        <f>IF(OR(A147="",G147="",F147=""),"",IF(OR(NOT(ISNUMBER(F147)),NOT(ISNUMBER(G147))),"valor ou horas inválidos",IF(G147=0,"",F147/G147)))</f>
         <v/>
       </c>
       <c r="I147" s="31">
-        <f>IF(OR(H147="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H147/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H147)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H147/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J147" s="33">
-        <f>IF(H147="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H147&lt;Config!$B$12,"Abaixo do mínimo",IF(H147&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H147="","",IF(NOT(ISNUMBER(H147)),H147,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H147&lt;Config!$B$12,"Abaixo do mínimo",IF(H147&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K147" s="25">
-        <f>IF(OR(H147="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G147-F147))</f>
+        <f>IF(OR(NOT(ISNUMBER(H147)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G147-F147))</f>
         <v/>
       </c>
       <c r="L147" s="41">
@@ -9167,19 +9167,19 @@
       <c r="F148" s="40" t="n"/>
       <c r="G148" s="23" t="n"/>
       <c r="H148" s="30">
-        <f>IF(OR(A148="",G148="",G148=0,F148=""),"",F148/G148)</f>
+        <f>IF(OR(A148="",G148="",F148=""),"",IF(OR(NOT(ISNUMBER(F148)),NOT(ISNUMBER(G148))),"valor ou horas inválidos",IF(G148=0,"",F148/G148)))</f>
         <v/>
       </c>
       <c r="I148" s="31">
-        <f>IF(OR(H148="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H148/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H148)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H148/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J148" s="33">
-        <f>IF(H148="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H148&lt;Config!$B$12,"Abaixo do mínimo",IF(H148&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H148="","",IF(NOT(ISNUMBER(H148)),H148,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H148&lt;Config!$B$12,"Abaixo do mínimo",IF(H148&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K148" s="25">
-        <f>IF(OR(H148="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G148-F148))</f>
+        <f>IF(OR(NOT(ISNUMBER(H148)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G148-F148))</f>
         <v/>
       </c>
       <c r="L148" s="41">
@@ -9196,19 +9196,19 @@
       <c r="F149" s="40" t="n"/>
       <c r="G149" s="23" t="n"/>
       <c r="H149" s="30">
-        <f>IF(OR(A149="",G149="",G149=0,F149=""),"",F149/G149)</f>
+        <f>IF(OR(A149="",G149="",F149=""),"",IF(OR(NOT(ISNUMBER(F149)),NOT(ISNUMBER(G149))),"valor ou horas inválidos",IF(G149=0,"",F149/G149)))</f>
         <v/>
       </c>
       <c r="I149" s="31">
-        <f>IF(OR(H149="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H149/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H149)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H149/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J149" s="33">
-        <f>IF(H149="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H149&lt;Config!$B$12,"Abaixo do mínimo",IF(H149&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H149="","",IF(NOT(ISNUMBER(H149)),H149,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H149&lt;Config!$B$12,"Abaixo do mínimo",IF(H149&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K149" s="25">
-        <f>IF(OR(H149="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G149-F149))</f>
+        <f>IF(OR(NOT(ISNUMBER(H149)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G149-F149))</f>
         <v/>
       </c>
       <c r="L149" s="41">
@@ -9225,19 +9225,19 @@
       <c r="F150" s="40" t="n"/>
       <c r="G150" s="23" t="n"/>
       <c r="H150" s="30">
-        <f>IF(OR(A150="",G150="",G150=0,F150=""),"",F150/G150)</f>
+        <f>IF(OR(A150="",G150="",F150=""),"",IF(OR(NOT(ISNUMBER(F150)),NOT(ISNUMBER(G150))),"valor ou horas inválidos",IF(G150=0,"",F150/G150)))</f>
         <v/>
       </c>
       <c r="I150" s="31">
-        <f>IF(OR(H150="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H150/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H150)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H150/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J150" s="33">
-        <f>IF(H150="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H150&lt;Config!$B$12,"Abaixo do mínimo",IF(H150&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H150="","",IF(NOT(ISNUMBER(H150)),H150,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H150&lt;Config!$B$12,"Abaixo do mínimo",IF(H150&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K150" s="25">
-        <f>IF(OR(H150="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G150-F150))</f>
+        <f>IF(OR(NOT(ISNUMBER(H150)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G150-F150))</f>
         <v/>
       </c>
       <c r="L150" s="41">
@@ -9254,19 +9254,19 @@
       <c r="F151" s="40" t="n"/>
       <c r="G151" s="23" t="n"/>
       <c r="H151" s="30">
-        <f>IF(OR(A151="",G151="",G151=0,F151=""),"",F151/G151)</f>
+        <f>IF(OR(A151="",G151="",F151=""),"",IF(OR(NOT(ISNUMBER(F151)),NOT(ISNUMBER(G151))),"valor ou horas inválidos",IF(G151=0,"",F151/G151)))</f>
         <v/>
       </c>
       <c r="I151" s="31">
-        <f>IF(OR(H151="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H151/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H151)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H151/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J151" s="33">
-        <f>IF(H151="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H151&lt;Config!$B$12,"Abaixo do mínimo",IF(H151&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H151="","",IF(NOT(ISNUMBER(H151)),H151,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H151&lt;Config!$B$12,"Abaixo do mínimo",IF(H151&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K151" s="25">
-        <f>IF(OR(H151="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G151-F151))</f>
+        <f>IF(OR(NOT(ISNUMBER(H151)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G151-F151))</f>
         <v/>
       </c>
       <c r="L151" s="41">
@@ -9283,19 +9283,19 @@
       <c r="F152" s="40" t="n"/>
       <c r="G152" s="23" t="n"/>
       <c r="H152" s="30">
-        <f>IF(OR(A152="",G152="",G152=0,F152=""),"",F152/G152)</f>
+        <f>IF(OR(A152="",G152="",F152=""),"",IF(OR(NOT(ISNUMBER(F152)),NOT(ISNUMBER(G152))),"valor ou horas inválidos",IF(G152=0,"",F152/G152)))</f>
         <v/>
       </c>
       <c r="I152" s="31">
-        <f>IF(OR(H152="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H152/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H152)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H152/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J152" s="33">
-        <f>IF(H152="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H152&lt;Config!$B$12,"Abaixo do mínimo",IF(H152&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H152="","",IF(NOT(ISNUMBER(H152)),H152,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H152&lt;Config!$B$12,"Abaixo do mínimo",IF(H152&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K152" s="25">
-        <f>IF(OR(H152="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G152-F152))</f>
+        <f>IF(OR(NOT(ISNUMBER(H152)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G152-F152))</f>
         <v/>
       </c>
       <c r="L152" s="41">
@@ -9312,19 +9312,19 @@
       <c r="F153" s="40" t="n"/>
       <c r="G153" s="23" t="n"/>
       <c r="H153" s="30">
-        <f>IF(OR(A153="",G153="",G153=0,F153=""),"",F153/G153)</f>
+        <f>IF(OR(A153="",G153="",F153=""),"",IF(OR(NOT(ISNUMBER(F153)),NOT(ISNUMBER(G153))),"valor ou horas inválidos",IF(G153=0,"",F153/G153)))</f>
         <v/>
       </c>
       <c r="I153" s="31">
-        <f>IF(OR(H153="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H153/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H153)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H153/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J153" s="33">
-        <f>IF(H153="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H153&lt;Config!$B$12,"Abaixo do mínimo",IF(H153&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H153="","",IF(NOT(ISNUMBER(H153)),H153,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H153&lt;Config!$B$12,"Abaixo do mínimo",IF(H153&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K153" s="25">
-        <f>IF(OR(H153="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G153-F153))</f>
+        <f>IF(OR(NOT(ISNUMBER(H153)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G153-F153))</f>
         <v/>
       </c>
       <c r="L153" s="41">
@@ -9341,19 +9341,19 @@
       <c r="F154" s="40" t="n"/>
       <c r="G154" s="23" t="n"/>
       <c r="H154" s="30">
-        <f>IF(OR(A154="",G154="",G154=0,F154=""),"",F154/G154)</f>
+        <f>IF(OR(A154="",G154="",F154=""),"",IF(OR(NOT(ISNUMBER(F154)),NOT(ISNUMBER(G154))),"valor ou horas inválidos",IF(G154=0,"",F154/G154)))</f>
         <v/>
       </c>
       <c r="I154" s="31">
-        <f>IF(OR(H154="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H154/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H154)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H154/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J154" s="33">
-        <f>IF(H154="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H154&lt;Config!$B$12,"Abaixo do mínimo",IF(H154&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H154="","",IF(NOT(ISNUMBER(H154)),H154,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H154&lt;Config!$B$12,"Abaixo do mínimo",IF(H154&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K154" s="25">
-        <f>IF(OR(H154="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G154-F154))</f>
+        <f>IF(OR(NOT(ISNUMBER(H154)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G154-F154))</f>
         <v/>
       </c>
       <c r="L154" s="41">
@@ -9370,19 +9370,19 @@
       <c r="F155" s="40" t="n"/>
       <c r="G155" s="23" t="n"/>
       <c r="H155" s="30">
-        <f>IF(OR(A155="",G155="",G155=0,F155=""),"",F155/G155)</f>
+        <f>IF(OR(A155="",G155="",F155=""),"",IF(OR(NOT(ISNUMBER(F155)),NOT(ISNUMBER(G155))),"valor ou horas inválidos",IF(G155=0,"",F155/G155)))</f>
         <v/>
       </c>
       <c r="I155" s="31">
-        <f>IF(OR(H155="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H155/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H155)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H155/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J155" s="33">
-        <f>IF(H155="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H155&lt;Config!$B$12,"Abaixo do mínimo",IF(H155&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H155="","",IF(NOT(ISNUMBER(H155)),H155,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H155&lt;Config!$B$12,"Abaixo do mínimo",IF(H155&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K155" s="25">
-        <f>IF(OR(H155="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G155-F155))</f>
+        <f>IF(OR(NOT(ISNUMBER(H155)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G155-F155))</f>
         <v/>
       </c>
       <c r="L155" s="41">
@@ -9399,19 +9399,19 @@
       <c r="F156" s="40" t="n"/>
       <c r="G156" s="23" t="n"/>
       <c r="H156" s="30">
-        <f>IF(OR(A156="",G156="",G156=0,F156=""),"",F156/G156)</f>
+        <f>IF(OR(A156="",G156="",F156=""),"",IF(OR(NOT(ISNUMBER(F156)),NOT(ISNUMBER(G156))),"valor ou horas inválidos",IF(G156=0,"",F156/G156)))</f>
         <v/>
       </c>
       <c r="I156" s="31">
-        <f>IF(OR(H156="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H156/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H156)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H156/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J156" s="33">
-        <f>IF(H156="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H156&lt;Config!$B$12,"Abaixo do mínimo",IF(H156&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H156="","",IF(NOT(ISNUMBER(H156)),H156,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H156&lt;Config!$B$12,"Abaixo do mínimo",IF(H156&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K156" s="25">
-        <f>IF(OR(H156="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G156-F156))</f>
+        <f>IF(OR(NOT(ISNUMBER(H156)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G156-F156))</f>
         <v/>
       </c>
       <c r="L156" s="41">
@@ -9428,19 +9428,19 @@
       <c r="F157" s="40" t="n"/>
       <c r="G157" s="23" t="n"/>
       <c r="H157" s="30">
-        <f>IF(OR(A157="",G157="",G157=0,F157=""),"",F157/G157)</f>
+        <f>IF(OR(A157="",G157="",F157=""),"",IF(OR(NOT(ISNUMBER(F157)),NOT(ISNUMBER(G157))),"valor ou horas inválidos",IF(G157=0,"",F157/G157)))</f>
         <v/>
       </c>
       <c r="I157" s="31">
-        <f>IF(OR(H157="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H157/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H157)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H157/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J157" s="33">
-        <f>IF(H157="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H157&lt;Config!$B$12,"Abaixo do mínimo",IF(H157&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H157="","",IF(NOT(ISNUMBER(H157)),H157,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H157&lt;Config!$B$12,"Abaixo do mínimo",IF(H157&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K157" s="25">
-        <f>IF(OR(H157="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G157-F157))</f>
+        <f>IF(OR(NOT(ISNUMBER(H157)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G157-F157))</f>
         <v/>
       </c>
       <c r="L157" s="41">
@@ -9457,19 +9457,19 @@
       <c r="F158" s="40" t="n"/>
       <c r="G158" s="23" t="n"/>
       <c r="H158" s="30">
-        <f>IF(OR(A158="",G158="",G158=0,F158=""),"",F158/G158)</f>
+        <f>IF(OR(A158="",G158="",F158=""),"",IF(OR(NOT(ISNUMBER(F158)),NOT(ISNUMBER(G158))),"valor ou horas inválidos",IF(G158=0,"",F158/G158)))</f>
         <v/>
       </c>
       <c r="I158" s="31">
-        <f>IF(OR(H158="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H158/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H158)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H158/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J158" s="33">
-        <f>IF(H158="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H158&lt;Config!$B$12,"Abaixo do mínimo",IF(H158&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H158="","",IF(NOT(ISNUMBER(H158)),H158,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H158&lt;Config!$B$12,"Abaixo do mínimo",IF(H158&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K158" s="25">
-        <f>IF(OR(H158="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G158-F158))</f>
+        <f>IF(OR(NOT(ISNUMBER(H158)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G158-F158))</f>
         <v/>
       </c>
       <c r="L158" s="41">
@@ -9486,19 +9486,19 @@
       <c r="F159" s="40" t="n"/>
       <c r="G159" s="23" t="n"/>
       <c r="H159" s="30">
-        <f>IF(OR(A159="",G159="",G159=0,F159=""),"",F159/G159)</f>
+        <f>IF(OR(A159="",G159="",F159=""),"",IF(OR(NOT(ISNUMBER(F159)),NOT(ISNUMBER(G159))),"valor ou horas inválidos",IF(G159=0,"",F159/G159)))</f>
         <v/>
       </c>
       <c r="I159" s="31">
-        <f>IF(OR(H159="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H159/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H159)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H159/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J159" s="33">
-        <f>IF(H159="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H159&lt;Config!$B$12,"Abaixo do mínimo",IF(H159&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H159="","",IF(NOT(ISNUMBER(H159)),H159,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H159&lt;Config!$B$12,"Abaixo do mínimo",IF(H159&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K159" s="25">
-        <f>IF(OR(H159="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G159-F159))</f>
+        <f>IF(OR(NOT(ISNUMBER(H159)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G159-F159))</f>
         <v/>
       </c>
       <c r="L159" s="41">
@@ -9515,19 +9515,19 @@
       <c r="F160" s="40" t="n"/>
       <c r="G160" s="23" t="n"/>
       <c r="H160" s="30">
-        <f>IF(OR(A160="",G160="",G160=0,F160=""),"",F160/G160)</f>
+        <f>IF(OR(A160="",G160="",F160=""),"",IF(OR(NOT(ISNUMBER(F160)),NOT(ISNUMBER(G160))),"valor ou horas inválidos",IF(G160=0,"",F160/G160)))</f>
         <v/>
       </c>
       <c r="I160" s="31">
-        <f>IF(OR(H160="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H160/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H160)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H160/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J160" s="33">
-        <f>IF(H160="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H160&lt;Config!$B$12,"Abaixo do mínimo",IF(H160&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H160="","",IF(NOT(ISNUMBER(H160)),H160,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H160&lt;Config!$B$12,"Abaixo do mínimo",IF(H160&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K160" s="25">
-        <f>IF(OR(H160="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G160-F160))</f>
+        <f>IF(OR(NOT(ISNUMBER(H160)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G160-F160))</f>
         <v/>
       </c>
       <c r="L160" s="41">
@@ -9544,19 +9544,19 @@
       <c r="F161" s="40" t="n"/>
       <c r="G161" s="23" t="n"/>
       <c r="H161" s="30">
-        <f>IF(OR(A161="",G161="",G161=0,F161=""),"",F161/G161)</f>
+        <f>IF(OR(A161="",G161="",F161=""),"",IF(OR(NOT(ISNUMBER(F161)),NOT(ISNUMBER(G161))),"valor ou horas inválidos",IF(G161=0,"",F161/G161)))</f>
         <v/>
       </c>
       <c r="I161" s="31">
-        <f>IF(OR(H161="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H161/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H161)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H161/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J161" s="33">
-        <f>IF(H161="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H161&lt;Config!$B$12,"Abaixo do mínimo",IF(H161&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H161="","",IF(NOT(ISNUMBER(H161)),H161,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H161&lt;Config!$B$12,"Abaixo do mínimo",IF(H161&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K161" s="25">
-        <f>IF(OR(H161="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G161-F161))</f>
+        <f>IF(OR(NOT(ISNUMBER(H161)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G161-F161))</f>
         <v/>
       </c>
       <c r="L161" s="41">
@@ -9573,19 +9573,19 @@
       <c r="F162" s="40" t="n"/>
       <c r="G162" s="23" t="n"/>
       <c r="H162" s="30">
-        <f>IF(OR(A162="",G162="",G162=0,F162=""),"",F162/G162)</f>
+        <f>IF(OR(A162="",G162="",F162=""),"",IF(OR(NOT(ISNUMBER(F162)),NOT(ISNUMBER(G162))),"valor ou horas inválidos",IF(G162=0,"",F162/G162)))</f>
         <v/>
       </c>
       <c r="I162" s="31">
-        <f>IF(OR(H162="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H162/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H162)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H162/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J162" s="33">
-        <f>IF(H162="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H162&lt;Config!$B$12,"Abaixo do mínimo",IF(H162&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H162="","",IF(NOT(ISNUMBER(H162)),H162,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H162&lt;Config!$B$12,"Abaixo do mínimo",IF(H162&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K162" s="25">
-        <f>IF(OR(H162="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G162-F162))</f>
+        <f>IF(OR(NOT(ISNUMBER(H162)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G162-F162))</f>
         <v/>
       </c>
       <c r="L162" s="41">
@@ -9602,19 +9602,19 @@
       <c r="F163" s="40" t="n"/>
       <c r="G163" s="23" t="n"/>
       <c r="H163" s="30">
-        <f>IF(OR(A163="",G163="",G163=0,F163=""),"",F163/G163)</f>
+        <f>IF(OR(A163="",G163="",F163=""),"",IF(OR(NOT(ISNUMBER(F163)),NOT(ISNUMBER(G163))),"valor ou horas inválidos",IF(G163=0,"",F163/G163)))</f>
         <v/>
       </c>
       <c r="I163" s="31">
-        <f>IF(OR(H163="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H163/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H163)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H163/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J163" s="33">
-        <f>IF(H163="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H163&lt;Config!$B$12,"Abaixo do mínimo",IF(H163&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H163="","",IF(NOT(ISNUMBER(H163)),H163,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H163&lt;Config!$B$12,"Abaixo do mínimo",IF(H163&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K163" s="25">
-        <f>IF(OR(H163="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G163-F163))</f>
+        <f>IF(OR(NOT(ISNUMBER(H163)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G163-F163))</f>
         <v/>
       </c>
       <c r="L163" s="41">
@@ -9631,19 +9631,19 @@
       <c r="F164" s="40" t="n"/>
       <c r="G164" s="23" t="n"/>
       <c r="H164" s="30">
-        <f>IF(OR(A164="",G164="",G164=0,F164=""),"",F164/G164)</f>
+        <f>IF(OR(A164="",G164="",F164=""),"",IF(OR(NOT(ISNUMBER(F164)),NOT(ISNUMBER(G164))),"valor ou horas inválidos",IF(G164=0,"",F164/G164)))</f>
         <v/>
       </c>
       <c r="I164" s="31">
-        <f>IF(OR(H164="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H164/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H164)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H164/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J164" s="33">
-        <f>IF(H164="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H164&lt;Config!$B$12,"Abaixo do mínimo",IF(H164&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H164="","",IF(NOT(ISNUMBER(H164)),H164,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H164&lt;Config!$B$12,"Abaixo do mínimo",IF(H164&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K164" s="25">
-        <f>IF(OR(H164="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G164-F164))</f>
+        <f>IF(OR(NOT(ISNUMBER(H164)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G164-F164))</f>
         <v/>
       </c>
       <c r="L164" s="41">
@@ -9660,19 +9660,19 @@
       <c r="F165" s="40" t="n"/>
       <c r="G165" s="23" t="n"/>
       <c r="H165" s="30">
-        <f>IF(OR(A165="",G165="",G165=0,F165=""),"",F165/G165)</f>
+        <f>IF(OR(A165="",G165="",F165=""),"",IF(OR(NOT(ISNUMBER(F165)),NOT(ISNUMBER(G165))),"valor ou horas inválidos",IF(G165=0,"",F165/G165)))</f>
         <v/>
       </c>
       <c r="I165" s="31">
-        <f>IF(OR(H165="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H165/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H165)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H165/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J165" s="33">
-        <f>IF(H165="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H165&lt;Config!$B$12,"Abaixo do mínimo",IF(H165&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H165="","",IF(NOT(ISNUMBER(H165)),H165,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H165&lt;Config!$B$12,"Abaixo do mínimo",IF(H165&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K165" s="25">
-        <f>IF(OR(H165="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G165-F165))</f>
+        <f>IF(OR(NOT(ISNUMBER(H165)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G165-F165))</f>
         <v/>
       </c>
       <c r="L165" s="41">
@@ -9689,19 +9689,19 @@
       <c r="F166" s="40" t="n"/>
       <c r="G166" s="23" t="n"/>
       <c r="H166" s="30">
-        <f>IF(OR(A166="",G166="",G166=0,F166=""),"",F166/G166)</f>
+        <f>IF(OR(A166="",G166="",F166=""),"",IF(OR(NOT(ISNUMBER(F166)),NOT(ISNUMBER(G166))),"valor ou horas inválidos",IF(G166=0,"",F166/G166)))</f>
         <v/>
       </c>
       <c r="I166" s="31">
-        <f>IF(OR(H166="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H166/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H166)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H166/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J166" s="33">
-        <f>IF(H166="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H166&lt;Config!$B$12,"Abaixo do mínimo",IF(H166&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H166="","",IF(NOT(ISNUMBER(H166)),H166,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H166&lt;Config!$B$12,"Abaixo do mínimo",IF(H166&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K166" s="25">
-        <f>IF(OR(H166="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G166-F166))</f>
+        <f>IF(OR(NOT(ISNUMBER(H166)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G166-F166))</f>
         <v/>
       </c>
       <c r="L166" s="41">
@@ -9718,19 +9718,19 @@
       <c r="F167" s="40" t="n"/>
       <c r="G167" s="23" t="n"/>
       <c r="H167" s="30">
-        <f>IF(OR(A167="",G167="",G167=0,F167=""),"",F167/G167)</f>
+        <f>IF(OR(A167="",G167="",F167=""),"",IF(OR(NOT(ISNUMBER(F167)),NOT(ISNUMBER(G167))),"valor ou horas inválidos",IF(G167=0,"",F167/G167)))</f>
         <v/>
       </c>
       <c r="I167" s="31">
-        <f>IF(OR(H167="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H167/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H167)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H167/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J167" s="33">
-        <f>IF(H167="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H167&lt;Config!$B$12,"Abaixo do mínimo",IF(H167&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H167="","",IF(NOT(ISNUMBER(H167)),H167,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H167&lt;Config!$B$12,"Abaixo do mínimo",IF(H167&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K167" s="25">
-        <f>IF(OR(H167="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G167-F167))</f>
+        <f>IF(OR(NOT(ISNUMBER(H167)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G167-F167))</f>
         <v/>
       </c>
       <c r="L167" s="41">
@@ -9747,19 +9747,19 @@
       <c r="F168" s="40" t="n"/>
       <c r="G168" s="23" t="n"/>
       <c r="H168" s="30">
-        <f>IF(OR(A168="",G168="",G168=0,F168=""),"",F168/G168)</f>
+        <f>IF(OR(A168="",G168="",F168=""),"",IF(OR(NOT(ISNUMBER(F168)),NOT(ISNUMBER(G168))),"valor ou horas inválidos",IF(G168=0,"",F168/G168)))</f>
         <v/>
       </c>
       <c r="I168" s="31">
-        <f>IF(OR(H168="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H168/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H168)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H168/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J168" s="33">
-        <f>IF(H168="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H168&lt;Config!$B$12,"Abaixo do mínimo",IF(H168&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H168="","",IF(NOT(ISNUMBER(H168)),H168,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H168&lt;Config!$B$12,"Abaixo do mínimo",IF(H168&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K168" s="25">
-        <f>IF(OR(H168="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G168-F168))</f>
+        <f>IF(OR(NOT(ISNUMBER(H168)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G168-F168))</f>
         <v/>
       </c>
       <c r="L168" s="41">
@@ -9776,19 +9776,19 @@
       <c r="F169" s="40" t="n"/>
       <c r="G169" s="23" t="n"/>
       <c r="H169" s="30">
-        <f>IF(OR(A169="",G169="",G169=0,F169=""),"",F169/G169)</f>
+        <f>IF(OR(A169="",G169="",F169=""),"",IF(OR(NOT(ISNUMBER(F169)),NOT(ISNUMBER(G169))),"valor ou horas inválidos",IF(G169=0,"",F169/G169)))</f>
         <v/>
       </c>
       <c r="I169" s="31">
-        <f>IF(OR(H169="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H169/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H169)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H169/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J169" s="33">
-        <f>IF(H169="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H169&lt;Config!$B$12,"Abaixo do mínimo",IF(H169&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H169="","",IF(NOT(ISNUMBER(H169)),H169,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H169&lt;Config!$B$12,"Abaixo do mínimo",IF(H169&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K169" s="25">
-        <f>IF(OR(H169="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G169-F169))</f>
+        <f>IF(OR(NOT(ISNUMBER(H169)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G169-F169))</f>
         <v/>
       </c>
       <c r="L169" s="41">
@@ -9805,19 +9805,19 @@
       <c r="F170" s="40" t="n"/>
       <c r="G170" s="23" t="n"/>
       <c r="H170" s="30">
-        <f>IF(OR(A170="",G170="",G170=0,F170=""),"",F170/G170)</f>
+        <f>IF(OR(A170="",G170="",F170=""),"",IF(OR(NOT(ISNUMBER(F170)),NOT(ISNUMBER(G170))),"valor ou horas inválidos",IF(G170=0,"",F170/G170)))</f>
         <v/>
       </c>
       <c r="I170" s="31">
-        <f>IF(OR(H170="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H170/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H170)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H170/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J170" s="33">
-        <f>IF(H170="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H170&lt;Config!$B$12,"Abaixo do mínimo",IF(H170&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H170="","",IF(NOT(ISNUMBER(H170)),H170,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H170&lt;Config!$B$12,"Abaixo do mínimo",IF(H170&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K170" s="25">
-        <f>IF(OR(H170="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G170-F170))</f>
+        <f>IF(OR(NOT(ISNUMBER(H170)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G170-F170))</f>
         <v/>
       </c>
       <c r="L170" s="41">
@@ -9834,19 +9834,19 @@
       <c r="F171" s="40" t="n"/>
       <c r="G171" s="23" t="n"/>
       <c r="H171" s="30">
-        <f>IF(OR(A171="",G171="",G171=0,F171=""),"",F171/G171)</f>
+        <f>IF(OR(A171="",G171="",F171=""),"",IF(OR(NOT(ISNUMBER(F171)),NOT(ISNUMBER(G171))),"valor ou horas inválidos",IF(G171=0,"",F171/G171)))</f>
         <v/>
       </c>
       <c r="I171" s="31">
-        <f>IF(OR(H171="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H171/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H171)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H171/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J171" s="33">
-        <f>IF(H171="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H171&lt;Config!$B$12,"Abaixo do mínimo",IF(H171&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H171="","",IF(NOT(ISNUMBER(H171)),H171,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H171&lt;Config!$B$12,"Abaixo do mínimo",IF(H171&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K171" s="25">
-        <f>IF(OR(H171="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G171-F171))</f>
+        <f>IF(OR(NOT(ISNUMBER(H171)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G171-F171))</f>
         <v/>
       </c>
       <c r="L171" s="41">
@@ -9863,19 +9863,19 @@
       <c r="F172" s="40" t="n"/>
       <c r="G172" s="23" t="n"/>
       <c r="H172" s="30">
-        <f>IF(OR(A172="",G172="",G172=0,F172=""),"",F172/G172)</f>
+        <f>IF(OR(A172="",G172="",F172=""),"",IF(OR(NOT(ISNUMBER(F172)),NOT(ISNUMBER(G172))),"valor ou horas inválidos",IF(G172=0,"",F172/G172)))</f>
         <v/>
       </c>
       <c r="I172" s="31">
-        <f>IF(OR(H172="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H172/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H172)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H172/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J172" s="33">
-        <f>IF(H172="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H172&lt;Config!$B$12,"Abaixo do mínimo",IF(H172&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H172="","",IF(NOT(ISNUMBER(H172)),H172,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H172&lt;Config!$B$12,"Abaixo do mínimo",IF(H172&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K172" s="25">
-        <f>IF(OR(H172="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G172-F172))</f>
+        <f>IF(OR(NOT(ISNUMBER(H172)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G172-F172))</f>
         <v/>
       </c>
       <c r="L172" s="41">
@@ -9892,19 +9892,19 @@
       <c r="F173" s="40" t="n"/>
       <c r="G173" s="23" t="n"/>
       <c r="H173" s="30">
-        <f>IF(OR(A173="",G173="",G173=0,F173=""),"",F173/G173)</f>
+        <f>IF(OR(A173="",G173="",F173=""),"",IF(OR(NOT(ISNUMBER(F173)),NOT(ISNUMBER(G173))),"valor ou horas inválidos",IF(G173=0,"",F173/G173)))</f>
         <v/>
       </c>
       <c r="I173" s="31">
-        <f>IF(OR(H173="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H173/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H173)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H173/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J173" s="33">
-        <f>IF(H173="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H173&lt;Config!$B$12,"Abaixo do mínimo",IF(H173&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H173="","",IF(NOT(ISNUMBER(H173)),H173,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H173&lt;Config!$B$12,"Abaixo do mínimo",IF(H173&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K173" s="25">
-        <f>IF(OR(H173="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G173-F173))</f>
+        <f>IF(OR(NOT(ISNUMBER(H173)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G173-F173))</f>
         <v/>
       </c>
       <c r="L173" s="41">
@@ -9921,19 +9921,19 @@
       <c r="F174" s="40" t="n"/>
       <c r="G174" s="23" t="n"/>
       <c r="H174" s="30">
-        <f>IF(OR(A174="",G174="",G174=0,F174=""),"",F174/G174)</f>
+        <f>IF(OR(A174="",G174="",F174=""),"",IF(OR(NOT(ISNUMBER(F174)),NOT(ISNUMBER(G174))),"valor ou horas inválidos",IF(G174=0,"",F174/G174)))</f>
         <v/>
       </c>
       <c r="I174" s="31">
-        <f>IF(OR(H174="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H174/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H174)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H174/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J174" s="33">
-        <f>IF(H174="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H174&lt;Config!$B$12,"Abaixo do mínimo",IF(H174&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H174="","",IF(NOT(ISNUMBER(H174)),H174,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H174&lt;Config!$B$12,"Abaixo do mínimo",IF(H174&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K174" s="25">
-        <f>IF(OR(H174="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G174-F174))</f>
+        <f>IF(OR(NOT(ISNUMBER(H174)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G174-F174))</f>
         <v/>
       </c>
       <c r="L174" s="41">
@@ -9950,19 +9950,19 @@
       <c r="F175" s="40" t="n"/>
       <c r="G175" s="23" t="n"/>
       <c r="H175" s="30">
-        <f>IF(OR(A175="",G175="",G175=0,F175=""),"",F175/G175)</f>
+        <f>IF(OR(A175="",G175="",F175=""),"",IF(OR(NOT(ISNUMBER(F175)),NOT(ISNUMBER(G175))),"valor ou horas inválidos",IF(G175=0,"",F175/G175)))</f>
         <v/>
       </c>
       <c r="I175" s="31">
-        <f>IF(OR(H175="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H175/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H175)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H175/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J175" s="33">
-        <f>IF(H175="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H175&lt;Config!$B$12,"Abaixo do mínimo",IF(H175&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H175="","",IF(NOT(ISNUMBER(H175)),H175,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H175&lt;Config!$B$12,"Abaixo do mínimo",IF(H175&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K175" s="25">
-        <f>IF(OR(H175="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G175-F175))</f>
+        <f>IF(OR(NOT(ISNUMBER(H175)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G175-F175))</f>
         <v/>
       </c>
       <c r="L175" s="41">
@@ -9979,19 +9979,19 @@
       <c r="F176" s="40" t="n"/>
       <c r="G176" s="23" t="n"/>
       <c r="H176" s="30">
-        <f>IF(OR(A176="",G176="",G176=0,F176=""),"",F176/G176)</f>
+        <f>IF(OR(A176="",G176="",F176=""),"",IF(OR(NOT(ISNUMBER(F176)),NOT(ISNUMBER(G176))),"valor ou horas inválidos",IF(G176=0,"",F176/G176)))</f>
         <v/>
       </c>
       <c r="I176" s="31">
-        <f>IF(OR(H176="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H176/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H176)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H176/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J176" s="33">
-        <f>IF(H176="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H176&lt;Config!$B$12,"Abaixo do mínimo",IF(H176&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H176="","",IF(NOT(ISNUMBER(H176)),H176,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H176&lt;Config!$B$12,"Abaixo do mínimo",IF(H176&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K176" s="25">
-        <f>IF(OR(H176="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G176-F176))</f>
+        <f>IF(OR(NOT(ISNUMBER(H176)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G176-F176))</f>
         <v/>
       </c>
       <c r="L176" s="41">
@@ -10008,19 +10008,19 @@
       <c r="F177" s="40" t="n"/>
       <c r="G177" s="23" t="n"/>
       <c r="H177" s="30">
-        <f>IF(OR(A177="",G177="",G177=0,F177=""),"",F177/G177)</f>
+        <f>IF(OR(A177="",G177="",F177=""),"",IF(OR(NOT(ISNUMBER(F177)),NOT(ISNUMBER(G177))),"valor ou horas inválidos",IF(G177=0,"",F177/G177)))</f>
         <v/>
       </c>
       <c r="I177" s="31">
-        <f>IF(OR(H177="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H177/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H177)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H177/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J177" s="33">
-        <f>IF(H177="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H177&lt;Config!$B$12,"Abaixo do mínimo",IF(H177&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H177="","",IF(NOT(ISNUMBER(H177)),H177,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H177&lt;Config!$B$12,"Abaixo do mínimo",IF(H177&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K177" s="25">
-        <f>IF(OR(H177="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G177-F177))</f>
+        <f>IF(OR(NOT(ISNUMBER(H177)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G177-F177))</f>
         <v/>
       </c>
       <c r="L177" s="41">
@@ -10037,19 +10037,19 @@
       <c r="F178" s="40" t="n"/>
       <c r="G178" s="23" t="n"/>
       <c r="H178" s="30">
-        <f>IF(OR(A178="",G178="",G178=0,F178=""),"",F178/G178)</f>
+        <f>IF(OR(A178="",G178="",F178=""),"",IF(OR(NOT(ISNUMBER(F178)),NOT(ISNUMBER(G178))),"valor ou horas inválidos",IF(G178=0,"",F178/G178)))</f>
         <v/>
       </c>
       <c r="I178" s="31">
-        <f>IF(OR(H178="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H178/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H178)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H178/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J178" s="33">
-        <f>IF(H178="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H178&lt;Config!$B$12,"Abaixo do mínimo",IF(H178&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H178="","",IF(NOT(ISNUMBER(H178)),H178,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H178&lt;Config!$B$12,"Abaixo do mínimo",IF(H178&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K178" s="25">
-        <f>IF(OR(H178="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G178-F178))</f>
+        <f>IF(OR(NOT(ISNUMBER(H178)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G178-F178))</f>
         <v/>
       </c>
       <c r="L178" s="41">
@@ -10066,19 +10066,19 @@
       <c r="F179" s="40" t="n"/>
       <c r="G179" s="23" t="n"/>
       <c r="H179" s="30">
-        <f>IF(OR(A179="",G179="",G179=0,F179=""),"",F179/G179)</f>
+        <f>IF(OR(A179="",G179="",F179=""),"",IF(OR(NOT(ISNUMBER(F179)),NOT(ISNUMBER(G179))),"valor ou horas inválidos",IF(G179=0,"",F179/G179)))</f>
         <v/>
       </c>
       <c r="I179" s="31">
-        <f>IF(OR(H179="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H179/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H179)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H179/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J179" s="33">
-        <f>IF(H179="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H179&lt;Config!$B$12,"Abaixo do mínimo",IF(H179&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H179="","",IF(NOT(ISNUMBER(H179)),H179,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H179&lt;Config!$B$12,"Abaixo do mínimo",IF(H179&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K179" s="25">
-        <f>IF(OR(H179="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G179-F179))</f>
+        <f>IF(OR(NOT(ISNUMBER(H179)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G179-F179))</f>
         <v/>
       </c>
       <c r="L179" s="41">
@@ -10095,19 +10095,19 @@
       <c r="F180" s="40" t="n"/>
       <c r="G180" s="23" t="n"/>
       <c r="H180" s="30">
-        <f>IF(OR(A180="",G180="",G180=0,F180=""),"",F180/G180)</f>
+        <f>IF(OR(A180="",G180="",F180=""),"",IF(OR(NOT(ISNUMBER(F180)),NOT(ISNUMBER(G180))),"valor ou horas inválidos",IF(G180=0,"",F180/G180)))</f>
         <v/>
       </c>
       <c r="I180" s="31">
-        <f>IF(OR(H180="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H180/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H180)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H180/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J180" s="33">
-        <f>IF(H180="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H180&lt;Config!$B$12,"Abaixo do mínimo",IF(H180&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H180="","",IF(NOT(ISNUMBER(H180)),H180,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H180&lt;Config!$B$12,"Abaixo do mínimo",IF(H180&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K180" s="25">
-        <f>IF(OR(H180="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G180-F180))</f>
+        <f>IF(OR(NOT(ISNUMBER(H180)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G180-F180))</f>
         <v/>
       </c>
       <c r="L180" s="41">
@@ -10124,19 +10124,19 @@
       <c r="F181" s="40" t="n"/>
       <c r="G181" s="23" t="n"/>
       <c r="H181" s="30">
-        <f>IF(OR(A181="",G181="",G181=0,F181=""),"",F181/G181)</f>
+        <f>IF(OR(A181="",G181="",F181=""),"",IF(OR(NOT(ISNUMBER(F181)),NOT(ISNUMBER(G181))),"valor ou horas inválidos",IF(G181=0,"",F181/G181)))</f>
         <v/>
       </c>
       <c r="I181" s="31">
-        <f>IF(OR(H181="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H181/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H181)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H181/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J181" s="33">
-        <f>IF(H181="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H181&lt;Config!$B$12,"Abaixo do mínimo",IF(H181&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H181="","",IF(NOT(ISNUMBER(H181)),H181,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H181&lt;Config!$B$12,"Abaixo do mínimo",IF(H181&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K181" s="25">
-        <f>IF(OR(H181="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G181-F181))</f>
+        <f>IF(OR(NOT(ISNUMBER(H181)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G181-F181))</f>
         <v/>
       </c>
       <c r="L181" s="41">
@@ -10153,19 +10153,19 @@
       <c r="F182" s="40" t="n"/>
       <c r="G182" s="23" t="n"/>
       <c r="H182" s="30">
-        <f>IF(OR(A182="",G182="",G182=0,F182=""),"",F182/G182)</f>
+        <f>IF(OR(A182="",G182="",F182=""),"",IF(OR(NOT(ISNUMBER(F182)),NOT(ISNUMBER(G182))),"valor ou horas inválidos",IF(G182=0,"",F182/G182)))</f>
         <v/>
       </c>
       <c r="I182" s="31">
-        <f>IF(OR(H182="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H182/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H182)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H182/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J182" s="33">
-        <f>IF(H182="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H182&lt;Config!$B$12,"Abaixo do mínimo",IF(H182&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H182="","",IF(NOT(ISNUMBER(H182)),H182,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H182&lt;Config!$B$12,"Abaixo do mínimo",IF(H182&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K182" s="25">
-        <f>IF(OR(H182="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G182-F182))</f>
+        <f>IF(OR(NOT(ISNUMBER(H182)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G182-F182))</f>
         <v/>
       </c>
       <c r="L182" s="41">
@@ -10182,19 +10182,19 @@
       <c r="F183" s="40" t="n"/>
       <c r="G183" s="23" t="n"/>
       <c r="H183" s="30">
-        <f>IF(OR(A183="",G183="",G183=0,F183=""),"",F183/G183)</f>
+        <f>IF(OR(A183="",G183="",F183=""),"",IF(OR(NOT(ISNUMBER(F183)),NOT(ISNUMBER(G183))),"valor ou horas inválidos",IF(G183=0,"",F183/G183)))</f>
         <v/>
       </c>
       <c r="I183" s="31">
-        <f>IF(OR(H183="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H183/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H183)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H183/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J183" s="33">
-        <f>IF(H183="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H183&lt;Config!$B$12,"Abaixo do mínimo",IF(H183&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H183="","",IF(NOT(ISNUMBER(H183)),H183,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H183&lt;Config!$B$12,"Abaixo do mínimo",IF(H183&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K183" s="25">
-        <f>IF(OR(H183="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G183-F183))</f>
+        <f>IF(OR(NOT(ISNUMBER(H183)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G183-F183))</f>
         <v/>
       </c>
       <c r="L183" s="41">
@@ -10211,19 +10211,19 @@
       <c r="F184" s="40" t="n"/>
       <c r="G184" s="23" t="n"/>
       <c r="H184" s="30">
-        <f>IF(OR(A184="",G184="",G184=0,F184=""),"",F184/G184)</f>
+        <f>IF(OR(A184="",G184="",F184=""),"",IF(OR(NOT(ISNUMBER(F184)),NOT(ISNUMBER(G184))),"valor ou horas inválidos",IF(G184=0,"",F184/G184)))</f>
         <v/>
       </c>
       <c r="I184" s="31">
-        <f>IF(OR(H184="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H184/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H184)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H184/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J184" s="33">
-        <f>IF(H184="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H184&lt;Config!$B$12,"Abaixo do mínimo",IF(H184&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H184="","",IF(NOT(ISNUMBER(H184)),H184,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H184&lt;Config!$B$12,"Abaixo do mínimo",IF(H184&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K184" s="25">
-        <f>IF(OR(H184="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G184-F184))</f>
+        <f>IF(OR(NOT(ISNUMBER(H184)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G184-F184))</f>
         <v/>
       </c>
       <c r="L184" s="41">
@@ -10240,19 +10240,19 @@
       <c r="F185" s="40" t="n"/>
       <c r="G185" s="23" t="n"/>
       <c r="H185" s="30">
-        <f>IF(OR(A185="",G185="",G185=0,F185=""),"",F185/G185)</f>
+        <f>IF(OR(A185="",G185="",F185=""),"",IF(OR(NOT(ISNUMBER(F185)),NOT(ISNUMBER(G185))),"valor ou horas inválidos",IF(G185=0,"",F185/G185)))</f>
         <v/>
       </c>
       <c r="I185" s="31">
-        <f>IF(OR(H185="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H185/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H185)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H185/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J185" s="33">
-        <f>IF(H185="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H185&lt;Config!$B$12,"Abaixo do mínimo",IF(H185&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H185="","",IF(NOT(ISNUMBER(H185)),H185,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H185&lt;Config!$B$12,"Abaixo do mínimo",IF(H185&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K185" s="25">
-        <f>IF(OR(H185="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G185-F185))</f>
+        <f>IF(OR(NOT(ISNUMBER(H185)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G185-F185))</f>
         <v/>
       </c>
       <c r="L185" s="41">
@@ -10269,19 +10269,19 @@
       <c r="F186" s="40" t="n"/>
       <c r="G186" s="23" t="n"/>
       <c r="H186" s="30">
-        <f>IF(OR(A186="",G186="",G186=0,F186=""),"",F186/G186)</f>
+        <f>IF(OR(A186="",G186="",F186=""),"",IF(OR(NOT(ISNUMBER(F186)),NOT(ISNUMBER(G186))),"valor ou horas inválidos",IF(G186=0,"",F186/G186)))</f>
         <v/>
       </c>
       <c r="I186" s="31">
-        <f>IF(OR(H186="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H186/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H186)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H186/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J186" s="33">
-        <f>IF(H186="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H186&lt;Config!$B$12,"Abaixo do mínimo",IF(H186&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H186="","",IF(NOT(ISNUMBER(H186)),H186,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H186&lt;Config!$B$12,"Abaixo do mínimo",IF(H186&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K186" s="25">
-        <f>IF(OR(H186="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G186-F186))</f>
+        <f>IF(OR(NOT(ISNUMBER(H186)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G186-F186))</f>
         <v/>
       </c>
       <c r="L186" s="41">
@@ -10298,19 +10298,19 @@
       <c r="F187" s="40" t="n"/>
       <c r="G187" s="23" t="n"/>
       <c r="H187" s="30">
-        <f>IF(OR(A187="",G187="",G187=0,F187=""),"",F187/G187)</f>
+        <f>IF(OR(A187="",G187="",F187=""),"",IF(OR(NOT(ISNUMBER(F187)),NOT(ISNUMBER(G187))),"valor ou horas inválidos",IF(G187=0,"",F187/G187)))</f>
         <v/>
       </c>
       <c r="I187" s="31">
-        <f>IF(OR(H187="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H187/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H187)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H187/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J187" s="33">
-        <f>IF(H187="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H187&lt;Config!$B$12,"Abaixo do mínimo",IF(H187&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H187="","",IF(NOT(ISNUMBER(H187)),H187,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H187&lt;Config!$B$12,"Abaixo do mínimo",IF(H187&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K187" s="25">
-        <f>IF(OR(H187="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G187-F187))</f>
+        <f>IF(OR(NOT(ISNUMBER(H187)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G187-F187))</f>
         <v/>
       </c>
       <c r="L187" s="41">
@@ -10327,19 +10327,19 @@
       <c r="F188" s="40" t="n"/>
       <c r="G188" s="23" t="n"/>
       <c r="H188" s="30">
-        <f>IF(OR(A188="",G188="",G188=0,F188=""),"",F188/G188)</f>
+        <f>IF(OR(A188="",G188="",F188=""),"",IF(OR(NOT(ISNUMBER(F188)),NOT(ISNUMBER(G188))),"valor ou horas inválidos",IF(G188=0,"",F188/G188)))</f>
         <v/>
       </c>
       <c r="I188" s="31">
-        <f>IF(OR(H188="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H188/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H188)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H188/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J188" s="33">
-        <f>IF(H188="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H188&lt;Config!$B$12,"Abaixo do mínimo",IF(H188&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H188="","",IF(NOT(ISNUMBER(H188)),H188,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H188&lt;Config!$B$12,"Abaixo do mínimo",IF(H188&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K188" s="25">
-        <f>IF(OR(H188="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G188-F188))</f>
+        <f>IF(OR(NOT(ISNUMBER(H188)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G188-F188))</f>
         <v/>
       </c>
       <c r="L188" s="41">
@@ -10356,19 +10356,19 @@
       <c r="F189" s="40" t="n"/>
       <c r="G189" s="23" t="n"/>
       <c r="H189" s="30">
-        <f>IF(OR(A189="",G189="",G189=0,F189=""),"",F189/G189)</f>
+        <f>IF(OR(A189="",G189="",F189=""),"",IF(OR(NOT(ISNUMBER(F189)),NOT(ISNUMBER(G189))),"valor ou horas inválidos",IF(G189=0,"",F189/G189)))</f>
         <v/>
       </c>
       <c r="I189" s="31">
-        <f>IF(OR(H189="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H189/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H189)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H189/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J189" s="33">
-        <f>IF(H189="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H189&lt;Config!$B$12,"Abaixo do mínimo",IF(H189&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H189="","",IF(NOT(ISNUMBER(H189)),H189,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H189&lt;Config!$B$12,"Abaixo do mínimo",IF(H189&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K189" s="25">
-        <f>IF(OR(H189="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G189-F189))</f>
+        <f>IF(OR(NOT(ISNUMBER(H189)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G189-F189))</f>
         <v/>
       </c>
       <c r="L189" s="41">
@@ -10385,19 +10385,19 @@
       <c r="F190" s="40" t="n"/>
       <c r="G190" s="23" t="n"/>
       <c r="H190" s="30">
-        <f>IF(OR(A190="",G190="",G190=0,F190=""),"",F190/G190)</f>
+        <f>IF(OR(A190="",G190="",F190=""),"",IF(OR(NOT(ISNUMBER(F190)),NOT(ISNUMBER(G190))),"valor ou horas inválidos",IF(G190=0,"",F190/G190)))</f>
         <v/>
       </c>
       <c r="I190" s="31">
-        <f>IF(OR(H190="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H190/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H190)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H190/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J190" s="33">
-        <f>IF(H190="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H190&lt;Config!$B$12,"Abaixo do mínimo",IF(H190&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H190="","",IF(NOT(ISNUMBER(H190)),H190,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H190&lt;Config!$B$12,"Abaixo do mínimo",IF(H190&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K190" s="25">
-        <f>IF(OR(H190="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G190-F190))</f>
+        <f>IF(OR(NOT(ISNUMBER(H190)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G190-F190))</f>
         <v/>
       </c>
       <c r="L190" s="41">
@@ -10414,19 +10414,19 @@
       <c r="F191" s="40" t="n"/>
       <c r="G191" s="23" t="n"/>
       <c r="H191" s="30">
-        <f>IF(OR(A191="",G191="",G191=0,F191=""),"",F191/G191)</f>
+        <f>IF(OR(A191="",G191="",F191=""),"",IF(OR(NOT(ISNUMBER(F191)),NOT(ISNUMBER(G191))),"valor ou horas inválidos",IF(G191=0,"",F191/G191)))</f>
         <v/>
       </c>
       <c r="I191" s="31">
-        <f>IF(OR(H191="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H191/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H191)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H191/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J191" s="33">
-        <f>IF(H191="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H191&lt;Config!$B$12,"Abaixo do mínimo",IF(H191&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H191="","",IF(NOT(ISNUMBER(H191)),H191,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H191&lt;Config!$B$12,"Abaixo do mínimo",IF(H191&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K191" s="25">
-        <f>IF(OR(H191="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G191-F191))</f>
+        <f>IF(OR(NOT(ISNUMBER(H191)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G191-F191))</f>
         <v/>
       </c>
       <c r="L191" s="41">
@@ -10443,19 +10443,19 @@
       <c r="F192" s="40" t="n"/>
       <c r="G192" s="23" t="n"/>
       <c r="H192" s="30">
-        <f>IF(OR(A192="",G192="",G192=0,F192=""),"",F192/G192)</f>
+        <f>IF(OR(A192="",G192="",F192=""),"",IF(OR(NOT(ISNUMBER(F192)),NOT(ISNUMBER(G192))),"valor ou horas inválidos",IF(G192=0,"",F192/G192)))</f>
         <v/>
       </c>
       <c r="I192" s="31">
-        <f>IF(OR(H192="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H192/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H192)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H192/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J192" s="33">
-        <f>IF(H192="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H192&lt;Config!$B$12,"Abaixo do mínimo",IF(H192&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H192="","",IF(NOT(ISNUMBER(H192)),H192,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H192&lt;Config!$B$12,"Abaixo do mínimo",IF(H192&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K192" s="25">
-        <f>IF(OR(H192="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G192-F192))</f>
+        <f>IF(OR(NOT(ISNUMBER(H192)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G192-F192))</f>
         <v/>
       </c>
       <c r="L192" s="41">
@@ -10472,19 +10472,19 @@
       <c r="F193" s="40" t="n"/>
       <c r="G193" s="23" t="n"/>
       <c r="H193" s="30">
-        <f>IF(OR(A193="",G193="",G193=0,F193=""),"",F193/G193)</f>
+        <f>IF(OR(A193="",G193="",F193=""),"",IF(OR(NOT(ISNUMBER(F193)),NOT(ISNUMBER(G193))),"valor ou horas inválidos",IF(G193=0,"",F193/G193)))</f>
         <v/>
       </c>
       <c r="I193" s="31">
-        <f>IF(OR(H193="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H193/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H193)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H193/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J193" s="33">
-        <f>IF(H193="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H193&lt;Config!$B$12,"Abaixo do mínimo",IF(H193&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H193="","",IF(NOT(ISNUMBER(H193)),H193,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H193&lt;Config!$B$12,"Abaixo do mínimo",IF(H193&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K193" s="25">
-        <f>IF(OR(H193="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G193-F193))</f>
+        <f>IF(OR(NOT(ISNUMBER(H193)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G193-F193))</f>
         <v/>
       </c>
       <c r="L193" s="41">
@@ -10501,19 +10501,19 @@
       <c r="F194" s="40" t="n"/>
       <c r="G194" s="23" t="n"/>
       <c r="H194" s="30">
-        <f>IF(OR(A194="",G194="",G194=0,F194=""),"",F194/G194)</f>
+        <f>IF(OR(A194="",G194="",F194=""),"",IF(OR(NOT(ISNUMBER(F194)),NOT(ISNUMBER(G194))),"valor ou horas inválidos",IF(G194=0,"",F194/G194)))</f>
         <v/>
       </c>
       <c r="I194" s="31">
-        <f>IF(OR(H194="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H194/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H194)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H194/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J194" s="33">
-        <f>IF(H194="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H194&lt;Config!$B$12,"Abaixo do mínimo",IF(H194&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H194="","",IF(NOT(ISNUMBER(H194)),H194,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H194&lt;Config!$B$12,"Abaixo do mínimo",IF(H194&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K194" s="25">
-        <f>IF(OR(H194="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G194-F194))</f>
+        <f>IF(OR(NOT(ISNUMBER(H194)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G194-F194))</f>
         <v/>
       </c>
       <c r="L194" s="41">
@@ -10530,19 +10530,19 @@
       <c r="F195" s="40" t="n"/>
       <c r="G195" s="23" t="n"/>
       <c r="H195" s="30">
-        <f>IF(OR(A195="",G195="",G195=0,F195=""),"",F195/G195)</f>
+        <f>IF(OR(A195="",G195="",F195=""),"",IF(OR(NOT(ISNUMBER(F195)),NOT(ISNUMBER(G195))),"valor ou horas inválidos",IF(G195=0,"",F195/G195)))</f>
         <v/>
       </c>
       <c r="I195" s="31">
-        <f>IF(OR(H195="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H195/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H195)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H195/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J195" s="33">
-        <f>IF(H195="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H195&lt;Config!$B$12,"Abaixo do mínimo",IF(H195&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H195="","",IF(NOT(ISNUMBER(H195)),H195,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H195&lt;Config!$B$12,"Abaixo do mínimo",IF(H195&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K195" s="25">
-        <f>IF(OR(H195="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G195-F195))</f>
+        <f>IF(OR(NOT(ISNUMBER(H195)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G195-F195))</f>
         <v/>
       </c>
       <c r="L195" s="41">
@@ -10559,19 +10559,19 @@
       <c r="F196" s="40" t="n"/>
       <c r="G196" s="23" t="n"/>
       <c r="H196" s="30">
-        <f>IF(OR(A196="",G196="",G196=0,F196=""),"",F196/G196)</f>
+        <f>IF(OR(A196="",G196="",F196=""),"",IF(OR(NOT(ISNUMBER(F196)),NOT(ISNUMBER(G196))),"valor ou horas inválidos",IF(G196=0,"",F196/G196)))</f>
         <v/>
       </c>
       <c r="I196" s="31">
-        <f>IF(OR(H196="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H196/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H196)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H196/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J196" s="33">
-        <f>IF(H196="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H196&lt;Config!$B$12,"Abaixo do mínimo",IF(H196&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H196="","",IF(NOT(ISNUMBER(H196)),H196,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H196&lt;Config!$B$12,"Abaixo do mínimo",IF(H196&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K196" s="25">
-        <f>IF(OR(H196="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G196-F196))</f>
+        <f>IF(OR(NOT(ISNUMBER(H196)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G196-F196))</f>
         <v/>
       </c>
       <c r="L196" s="41">
@@ -10588,19 +10588,19 @@
       <c r="F197" s="40" t="n"/>
       <c r="G197" s="23" t="n"/>
       <c r="H197" s="30">
-        <f>IF(OR(A197="",G197="",G197=0,F197=""),"",F197/G197)</f>
+        <f>IF(OR(A197="",G197="",F197=""),"",IF(OR(NOT(ISNUMBER(F197)),NOT(ISNUMBER(G197))),"valor ou horas inválidos",IF(G197=0,"",F197/G197)))</f>
         <v/>
       </c>
       <c r="I197" s="31">
-        <f>IF(OR(H197="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H197/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H197)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H197/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J197" s="33">
-        <f>IF(H197="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H197&lt;Config!$B$12,"Abaixo do mínimo",IF(H197&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H197="","",IF(NOT(ISNUMBER(H197)),H197,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H197&lt;Config!$B$12,"Abaixo do mínimo",IF(H197&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K197" s="25">
-        <f>IF(OR(H197="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G197-F197))</f>
+        <f>IF(OR(NOT(ISNUMBER(H197)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G197-F197))</f>
         <v/>
       </c>
       <c r="L197" s="41">
@@ -10617,19 +10617,19 @@
       <c r="F198" s="40" t="n"/>
       <c r="G198" s="23" t="n"/>
       <c r="H198" s="30">
-        <f>IF(OR(A198="",G198="",G198=0,F198=""),"",F198/G198)</f>
+        <f>IF(OR(A198="",G198="",F198=""),"",IF(OR(NOT(ISNUMBER(F198)),NOT(ISNUMBER(G198))),"valor ou horas inválidos",IF(G198=0,"",F198/G198)))</f>
         <v/>
       </c>
       <c r="I198" s="31">
-        <f>IF(OR(H198="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H198/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H198)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H198/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J198" s="33">
-        <f>IF(H198="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H198&lt;Config!$B$12,"Abaixo do mínimo",IF(H198&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H198="","",IF(NOT(ISNUMBER(H198)),H198,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H198&lt;Config!$B$12,"Abaixo do mínimo",IF(H198&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K198" s="25">
-        <f>IF(OR(H198="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G198-F198))</f>
+        <f>IF(OR(NOT(ISNUMBER(H198)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G198-F198))</f>
         <v/>
       </c>
       <c r="L198" s="41">
@@ -10646,19 +10646,19 @@
       <c r="F199" s="40" t="n"/>
       <c r="G199" s="23" t="n"/>
       <c r="H199" s="30">
-        <f>IF(OR(A199="",G199="",G199=0,F199=""),"",F199/G199)</f>
+        <f>IF(OR(A199="",G199="",F199=""),"",IF(OR(NOT(ISNUMBER(F199)),NOT(ISNUMBER(G199))),"valor ou horas inválidos",IF(G199=0,"",F199/G199)))</f>
         <v/>
       </c>
       <c r="I199" s="31">
-        <f>IF(OR(H199="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H199/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H199)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H199/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J199" s="33">
-        <f>IF(H199="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H199&lt;Config!$B$12,"Abaixo do mínimo",IF(H199&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H199="","",IF(NOT(ISNUMBER(H199)),H199,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H199&lt;Config!$B$12,"Abaixo do mínimo",IF(H199&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K199" s="25">
-        <f>IF(OR(H199="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G199-F199))</f>
+        <f>IF(OR(NOT(ISNUMBER(H199)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G199-F199))</f>
         <v/>
       </c>
       <c r="L199" s="41">
@@ -10675,19 +10675,19 @@
       <c r="F200" s="40" t="n"/>
       <c r="G200" s="23" t="n"/>
       <c r="H200" s="30">
-        <f>IF(OR(A200="",G200="",G200=0,F200=""),"",F200/G200)</f>
+        <f>IF(OR(A200="",G200="",F200=""),"",IF(OR(NOT(ISNUMBER(F200)),NOT(ISNUMBER(G200))),"valor ou horas inválidos",IF(G200=0,"",F200/G200)))</f>
         <v/>
       </c>
       <c r="I200" s="31">
-        <f>IF(OR(H200="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H200/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H200)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H200/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J200" s="33">
-        <f>IF(H200="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H200&lt;Config!$B$12,"Abaixo do mínimo",IF(H200&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H200="","",IF(NOT(ISNUMBER(H200)),H200,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H200&lt;Config!$B$12,"Abaixo do mínimo",IF(H200&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K200" s="25">
-        <f>IF(OR(H200="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G200-F200))</f>
+        <f>IF(OR(NOT(ISNUMBER(H200)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G200-F200))</f>
         <v/>
       </c>
       <c r="L200" s="41">
@@ -10704,19 +10704,19 @@
       <c r="F201" s="40" t="n"/>
       <c r="G201" s="23" t="n"/>
       <c r="H201" s="30">
-        <f>IF(OR(A201="",G201="",G201=0,F201=""),"",F201/G201)</f>
+        <f>IF(OR(A201="",G201="",F201=""),"",IF(OR(NOT(ISNUMBER(F201)),NOT(ISNUMBER(G201))),"valor ou horas inválidos",IF(G201=0,"",F201/G201)))</f>
         <v/>
       </c>
       <c r="I201" s="31">
-        <f>IF(OR(H201="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H201/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H201)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H201/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J201" s="33">
-        <f>IF(H201="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H201&lt;Config!$B$12,"Abaixo do mínimo",IF(H201&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H201="","",IF(NOT(ISNUMBER(H201)),H201,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H201&lt;Config!$B$12,"Abaixo do mínimo",IF(H201&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K201" s="25">
-        <f>IF(OR(H201="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G201-F201))</f>
+        <f>IF(OR(NOT(ISNUMBER(H201)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G201-F201))</f>
         <v/>
       </c>
       <c r="L201" s="41">
@@ -10733,19 +10733,19 @@
       <c r="F202" s="40" t="n"/>
       <c r="G202" s="23" t="n"/>
       <c r="H202" s="30">
-        <f>IF(OR(A202="",G202="",G202=0,F202=""),"",F202/G202)</f>
+        <f>IF(OR(A202="",G202="",F202=""),"",IF(OR(NOT(ISNUMBER(F202)),NOT(ISNUMBER(G202))),"valor ou horas inválidos",IF(G202=0,"",F202/G202)))</f>
         <v/>
       </c>
       <c r="I202" s="31">
-        <f>IF(OR(H202="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H202/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H202)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H202/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J202" s="33">
-        <f>IF(H202="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H202&lt;Config!$B$12,"Abaixo do mínimo",IF(H202&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H202="","",IF(NOT(ISNUMBER(H202)),H202,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H202&lt;Config!$B$12,"Abaixo do mínimo",IF(H202&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K202" s="25">
-        <f>IF(OR(H202="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G202-F202))</f>
+        <f>IF(OR(NOT(ISNUMBER(H202)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G202-F202))</f>
         <v/>
       </c>
       <c r="L202" s="41">
@@ -10762,19 +10762,19 @@
       <c r="F203" s="40" t="n"/>
       <c r="G203" s="23" t="n"/>
       <c r="H203" s="30">
-        <f>IF(OR(A203="",G203="",G203=0,F203=""),"",F203/G203)</f>
+        <f>IF(OR(A203="",G203="",F203=""),"",IF(OR(NOT(ISNUMBER(F203)),NOT(ISNUMBER(G203))),"valor ou horas inválidos",IF(G203=0,"",F203/G203)))</f>
         <v/>
       </c>
       <c r="I203" s="31">
-        <f>IF(OR(H203="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H203/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H203)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H203/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J203" s="33">
-        <f>IF(H203="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H203&lt;Config!$B$12,"Abaixo do mínimo",IF(H203&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H203="","",IF(NOT(ISNUMBER(H203)),H203,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H203&lt;Config!$B$12,"Abaixo do mínimo",IF(H203&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K203" s="25">
-        <f>IF(OR(H203="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G203-F203))</f>
+        <f>IF(OR(NOT(ISNUMBER(H203)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G203-F203))</f>
         <v/>
       </c>
       <c r="L203" s="41">
@@ -10791,19 +10791,19 @@
       <c r="F204" s="40" t="n"/>
       <c r="G204" s="23" t="n"/>
       <c r="H204" s="30">
-        <f>IF(OR(A204="",G204="",G204=0,F204=""),"",F204/G204)</f>
+        <f>IF(OR(A204="",G204="",F204=""),"",IF(OR(NOT(ISNUMBER(F204)),NOT(ISNUMBER(G204))),"valor ou horas inválidos",IF(G204=0,"",F204/G204)))</f>
         <v/>
       </c>
       <c r="I204" s="31">
-        <f>IF(OR(H204="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H204/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(H204)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",H204/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="J204" s="33">
-        <f>IF(H204="","",IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H204&lt;Config!$B$12,"Abaixo do mínimo",IF(H204&lt;Config!$B$13,"Na faixa","Acima do alvo")))))</f>
+        <f>IF(H204="","",IF(NOT(ISNUMBER(H204)),H204,IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(NOT(ISNUMBER(Config!$B$13)),Config!$B$13,IF(H204&lt;Config!$B$12,"Abaixo do mínimo",IF(H204&lt;Config!$B$13,"Na faixa","Acima do alvo"))))))</f>
         <v/>
       </c>
       <c r="K204" s="25">
-        <f>IF(OR(H204="",NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G204-F204))</f>
+        <f>IF(OR(NOT(ISNUMBER(H204)),NOT(ISNUMBER(Config!$B$12))),"",MAX(0,Config!$B$12*G204-F204))</f>
         <v/>
       </c>
       <c r="L204" s="41">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -1089,17 +1089,17 @@
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17" t="str">
-        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&gt;0,COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&amp;" caso(s) com valor ou horas inválidos",COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo"))))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(SUMPRODUCT(((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,SUMPRODUCT(((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&amp;" caso(s) incompletos (nº, área, valor ou horas)",COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")&amp;" de "&amp;(COUNTIF('Nossos casos'!$J$5:$J$204,"Abaixo do mínimo")+COUNTIF('Nossos casos'!$J$5:$J$204,"Na faixa")+COUNTIF('Nossos casos'!$J$5:$J$204,"Acima do alvo"))))</f>
         <v>10 de 38</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
-        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&gt;0,COUNTIF('Nossos casos'!$H$5:$H$204,"valor ou horas inválidos")&amp;" caso(s) com valor ou horas inválidos",SUM('Nossos casos'!$K$5:$K$204)))</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$12)),Config!$B$12,IF(SUMPRODUCT(((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,SUMPRODUCT(((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&amp;" caso(s) incompletos (nº, área, valor ou horas)",SUM('Nossos casos'!$K$5:$K$204)))</f>
         <v>11876.6896774193</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="19">
-        <f>IFERROR(SUM('Nossos casos'!$F$5:$F$204)/SUM('Nossos casos'!$G$5:$G$204),0)</f>
+        <f>IF(SUMPRODUCT(((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,SUMPRODUCT(((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&amp;" caso(s) incompletos (nº, área, valor ou horas)",IFERROR(SUM('Nossos casos'!$F$5:$F$204)/SUM('Nossos casos'!$G$5:$G$204),""))</f>
         <v>153.314696485623</v>
       </c>
       <c r="J5" s="14" t="n"/>
@@ -1181,11 +1181,11 @@
         </is>
       </c>
       <c r="F9" s="25">
-        <f>IF(OR(A9="",C9=""),"",IF(NOT(ISNUMBER(C9)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A9="",C9=""),"",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G9" s="25">
-        <f>IF(OR(A9="",D9=""),"",IF(NOT(ISNUMBER(D9)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A9="",D9=""),"",IF(NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H9" s="25">
@@ -1220,11 +1220,11 @@
         </is>
       </c>
       <c r="F10" s="25">
-        <f>IF(OR(A10="",C10=""),"",IF(NOT(ISNUMBER(C10)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A10="",C10=""),"",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G10" s="25">
-        <f>IF(OR(A10="",D10=""),"",IF(NOT(ISNUMBER(D10)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A10="",D10=""),"",IF(NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H10" s="25">
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="F11" s="25">
-        <f>IF(OR(A11="",C11=""),"",IF(NOT(ISNUMBER(C11)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A11="",C11=""),"",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12)))</f>
         <v>6394.0064516129</v>
       </c>
       <c r="G11" s="25">
-        <f>IF(OR(A11="",D11=""),"",IF(NOT(ISNUMBER(D11)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A11="",D11=""),"",IF(NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13)))</f>
         <v>16869.2936170213</v>
       </c>
       <c r="H11" s="25">
@@ -1298,11 +1298,11 @@
         </is>
       </c>
       <c r="F12" s="25">
-        <f>IF(OR(A12="",C12=""),"",IF(NOT(ISNUMBER(C12)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A12="",C12=""),"",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G12" s="25">
-        <f>IF(OR(A12="",D12=""),"",IF(NOT(ISNUMBER(D12)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A12="",D12=""),"",IF(NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H12" s="25">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="F13" s="25">
-        <f>IF(OR(A13="",C13=""),"",IF(NOT(ISNUMBER(C13)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A13="",C13=""),"",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G13" s="25">
-        <f>IF(OR(A13="",D13=""),"",IF(NOT(ISNUMBER(D13)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A13="",D13=""),"",IF(NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H13" s="25">
@@ -1376,11 +1376,11 @@
         </is>
       </c>
       <c r="F14" s="25">
-        <f>IF(OR(A14="",C14=""),"",IF(NOT(ISNUMBER(C14)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A14="",C14=""),"",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G14" s="25">
-        <f>IF(OR(A14="",D14=""),"",IF(NOT(ISNUMBER(D14)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A14="",D14=""),"",IF(NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H14" s="25">
@@ -1415,11 +1415,11 @@
         </is>
       </c>
       <c r="F15" s="25">
-        <f>IF(OR(A15="",C15=""),"",IF(NOT(ISNUMBER(C15)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A15="",C15=""),"",IF(NOT(IF(ISNUMBER(C15),C15&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G15" s="25">
-        <f>IF(OR(A15="",D15=""),"",IF(NOT(ISNUMBER(D15)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A15="",D15=""),"",IF(NOT(IF(ISNUMBER(D15),D15&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H15" s="25">
@@ -1454,11 +1454,11 @@
         </is>
       </c>
       <c r="F16" s="25">
-        <f>IF(OR(A16="",C16=""),"",IF(NOT(ISNUMBER(C16)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A16="",C16=""),"",IF(NOT(IF(ISNUMBER(C16),C16&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12)))</f>
         <v>4475.80451612903</v>
       </c>
       <c r="G16" s="25">
-        <f>IF(OR(A16="",D16=""),"",IF(NOT(ISNUMBER(D16)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A16="",D16=""),"",IF(NOT(IF(ISNUMBER(D16),D16&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13)))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H16" s="25">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="F17" s="25">
-        <f>IF(OR(A17="",C17=""),"",IF(NOT(ISNUMBER(C17)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A17="",C17=""),"",IF(NOT(IF(ISNUMBER(C17),C17&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G17" s="25">
-        <f>IF(OR(A17="",D17=""),"",IF(NOT(ISNUMBER(D17)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A17="",D17=""),"",IF(NOT(IF(ISNUMBER(D17),D17&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H17" s="25">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="F18" s="25">
-        <f>IF(OR(A18="",C18=""),"",IF(NOT(ISNUMBER(C18)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A18="",C18=""),"",IF(NOT(IF(ISNUMBER(C18),C18&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G18" s="25">
-        <f>IF(OR(A18="",D18=""),"",IF(NOT(ISNUMBER(D18)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A18="",D18=""),"",IF(NOT(IF(ISNUMBER(D18),D18&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H18" s="25">
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="F19" s="25">
-        <f>IF(OR(A19="",C19=""),"",IF(NOT(ISNUMBER(C19)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A19="",C19=""),"",IF(NOT(IF(ISNUMBER(C19),C19&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G19" s="25">
-        <f>IF(OR(A19="",D19=""),"",IF(NOT(ISNUMBER(D19)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A19="",D19=""),"",IF(NOT(IF(ISNUMBER(D19),D19&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H19" s="25">
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="F20" s="25">
-        <f>IF(OR(A20="",C20=""),"",IF(NOT(ISNUMBER(C20)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A20="",C20=""),"",IF(NOT(IF(ISNUMBER(C20),C20&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G20" s="25">
-        <f>IF(OR(A20="",D20=""),"",IF(NOT(ISNUMBER(D20)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A20="",D20=""),"",IF(NOT(IF(ISNUMBER(D20),D20&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H20" s="25">
@@ -1649,11 +1649,11 @@
         </is>
       </c>
       <c r="F21" s="25">
-        <f>IF(OR(A21="",C21=""),"",IF(NOT(ISNUMBER(C21)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A21="",C21=""),"",IF(NOT(IF(ISNUMBER(C21),C21&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12)))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G21" s="25">
-        <f>IF(OR(A21="",D21=""),"",IF(NOT(ISNUMBER(D21)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A21="",D21=""),"",IF(NOT(IF(ISNUMBER(D21),D21&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13)))</f>
         <v>10121.5761702128</v>
       </c>
       <c r="H21" s="25">
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="F22" s="25">
-        <f>IF(OR(A22="",C22=""),"",IF(NOT(ISNUMBER(C22)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A22="",C22=""),"",IF(NOT(IF(ISNUMBER(C22),C22&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G22" s="25">
-        <f>IF(OR(A22="",D22=""),"",IF(NOT(ISNUMBER(D22)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A22="",D22=""),"",IF(NOT(IF(ISNUMBER(D22),D22&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H22" s="25">
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="F23" s="25">
-        <f>IF(OR(A23="",C23=""),"",IF(NOT(ISNUMBER(C23)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A23="",C23=""),"",IF(NOT(IF(ISNUMBER(C23),C23&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G23" s="25">
-        <f>IF(OR(A23="",D23=""),"",IF(NOT(ISNUMBER(D23)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A23="",D23=""),"",IF(NOT(IF(ISNUMBER(D23),D23&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H23" s="25">
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="F24" s="25">
-        <f>IF(OR(A24="",C24=""),"",IF(NOT(ISNUMBER(C24)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A24="",C24=""),"",IF(NOT(IF(ISNUMBER(C24),C24&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12)))</f>
         <v>511.520516129032</v>
       </c>
       <c r="G24" s="25">
-        <f>IF(OR(A24="",D24=""),"",IF(NOT(ISNUMBER(D24)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A24="",D24=""),"",IF(NOT(IF(ISNUMBER(D24),D24&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13)))</f>
         <v>2024.31523404255</v>
       </c>
       <c r="H24" s="25">
@@ -1805,11 +1805,11 @@
         </is>
       </c>
       <c r="F25" s="25">
-        <f>IF(OR(A25="",C25=""),"",IF(NOT(ISNUMBER(C25)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A25="",C25=""),"",IF(NOT(IF(ISNUMBER(C25),C25&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G25" s="25">
-        <f>IF(OR(A25="",D25=""),"",IF(NOT(ISNUMBER(D25)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A25="",D25=""),"",IF(NOT(IF(ISNUMBER(D25),D25&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H25" s="25">
@@ -1844,11 +1844,11 @@
         </is>
       </c>
       <c r="F26" s="25">
-        <f>IF(OR(A26="",C26=""),"",IF(NOT(ISNUMBER(C26)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A26="",C26=""),"",IF(NOT(IF(ISNUMBER(C26),C26&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12)))</f>
         <v>7672.80774193548</v>
       </c>
       <c r="G26" s="25">
-        <f>IF(OR(A26="",D26=""),"",IF(NOT(ISNUMBER(D26)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A26="",D26=""),"",IF(NOT(IF(ISNUMBER(D26),D26&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13)))</f>
         <v>20243.1523404255</v>
       </c>
       <c r="H26" s="25">
@@ -1883,11 +1883,11 @@
         </is>
       </c>
       <c r="F27" s="25">
-        <f>IF(OR(A27="",C27=""),"",IF(NOT(ISNUMBER(C27)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A27="",C27=""),"",IF(NOT(IF(ISNUMBER(C27),C27&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G27" s="25">
-        <f>IF(OR(A27="",D27=""),"",IF(NOT(ISNUMBER(D27)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A27="",D27=""),"",IF(NOT(IF(ISNUMBER(D27),D27&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H27" s="25">
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="F28" s="25">
-        <f>IF(OR(A28="",C28=""),"",IF(NOT(ISNUMBER(C28)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A28="",C28=""),"",IF(NOT(IF(ISNUMBER(C28),C28&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G28" s="25">
-        <f>IF(OR(A28="",D28=""),"",IF(NOT(ISNUMBER(D28)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A28="",D28=""),"",IF(NOT(IF(ISNUMBER(D28),D28&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H28" s="25">
@@ -1961,11 +1961,11 @@
         </is>
       </c>
       <c r="F29" s="25">
-        <f>IF(OR(A29="",C29=""),"",IF(NOT(ISNUMBER(C29)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A29="",C29=""),"",IF(NOT(IF(ISNUMBER(C29),C29&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12)))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G29" s="25">
-        <f>IF(OR(A29="",D29=""),"",IF(NOT(ISNUMBER(D29)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A29="",D29=""),"",IF(NOT(IF(ISNUMBER(D29),D29&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13)))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H29" s="25">
@@ -2000,11 +2000,11 @@
         </is>
       </c>
       <c r="F30" s="25">
-        <f>IF(OR(A30="",C30=""),"",IF(NOT(ISNUMBER(C30)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A30="",C30=""),"",IF(NOT(IF(ISNUMBER(C30),C30&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12)))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G30" s="25">
-        <f>IF(OR(A30="",D30=""),"",IF(NOT(ISNUMBER(D30)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A30="",D30=""),"",IF(NOT(IF(ISNUMBER(D30),D30&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13)))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H30" s="25">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="F31" s="25">
-        <f>IF(OR(A31="",C31=""),"",IF(NOT(ISNUMBER(C31)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A31="",C31=""),"",IF(NOT(IF(ISNUMBER(C31),C31&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12)))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G31" s="25">
-        <f>IF(OR(A31="",D31=""),"",IF(NOT(ISNUMBER(D31)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A31="",D31=""),"",IF(NOT(IF(ISNUMBER(D31),D31&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13)))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H31" s="25">
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="F32" s="25">
-        <f>IF(OR(A32="",C32=""),"",IF(NOT(ISNUMBER(C32)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A32="",C32=""),"",IF(NOT(IF(ISNUMBER(C32),C32&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12)))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G32" s="25">
-        <f>IF(OR(A32="",D32=""),"",IF(NOT(ISNUMBER(D32)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A32="",D32=""),"",IF(NOT(IF(ISNUMBER(D32),D32&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13)))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H32" s="25">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="F33" s="25">
-        <f>IF(OR(A33="",C33=""),"",IF(NOT(ISNUMBER(C33)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A33="",C33=""),"",IF(NOT(IF(ISNUMBER(C33),C33&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12)))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G33" s="25">
-        <f>IF(OR(A33="",D33=""),"",IF(NOT(ISNUMBER(D33)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A33="",D33=""),"",IF(NOT(IF(ISNUMBER(D33),D33&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13)))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H33" s="25">
@@ -2140,11 +2140,11 @@
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="24" t="n"/>
       <c r="F34" s="25">
-        <f>IF(OR(A34="",C34=""),"",IF(NOT(ISNUMBER(C34)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A34="",C34=""),"",IF(NOT(IF(ISNUMBER(C34),C34&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G34" s="25">
-        <f>IF(OR(A34="",D34=""),"",IF(NOT(ISNUMBER(D34)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A34="",D34=""),"",IF(NOT(IF(ISNUMBER(D34),D34&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H34" s="25">
@@ -2163,11 +2163,11 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="24" t="n"/>
       <c r="F35" s="25">
-        <f>IF(OR(A35="",C35=""),"",IF(NOT(ISNUMBER(C35)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A35="",C35=""),"",IF(NOT(IF(ISNUMBER(C35),C35&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G35" s="25">
-        <f>IF(OR(A35="",D35=""),"",IF(NOT(ISNUMBER(D35)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A35="",D35=""),"",IF(NOT(IF(ISNUMBER(D35),D35&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H35" s="25">
@@ -2186,11 +2186,11 @@
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="24" t="n"/>
       <c r="F36" s="25">
-        <f>IF(OR(A36="",C36=""),"",IF(NOT(ISNUMBER(C36)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A36="",C36=""),"",IF(NOT(IF(ISNUMBER(C36),C36&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G36" s="25">
-        <f>IF(OR(A36="",D36=""),"",IF(NOT(ISNUMBER(D36)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A36="",D36=""),"",IF(NOT(IF(ISNUMBER(D36),D36&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H36" s="25">
@@ -2209,11 +2209,11 @@
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="24" t="n"/>
       <c r="F37" s="25">
-        <f>IF(OR(A37="",C37=""),"",IF(NOT(ISNUMBER(C37)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A37="",C37=""),"",IF(NOT(IF(ISNUMBER(C37),C37&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G37" s="25">
-        <f>IF(OR(A37="",D37=""),"",IF(NOT(ISNUMBER(D37)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A37="",D37=""),"",IF(NOT(IF(ISNUMBER(D37),D37&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H37" s="25">
@@ -2232,11 +2232,11 @@
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="24" t="n"/>
       <c r="F38" s="25">
-        <f>IF(OR(A38="",C38=""),"",IF(NOT(ISNUMBER(C38)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A38="",C38=""),"",IF(NOT(IF(ISNUMBER(C38),C38&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G38" s="25">
-        <f>IF(OR(A38="",D38=""),"",IF(NOT(ISNUMBER(D38)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A38="",D38=""),"",IF(NOT(IF(ISNUMBER(D38),D38&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H38" s="25">
@@ -2255,11 +2255,11 @@
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="25">
-        <f>IF(OR(A39="",C39=""),"",IF(NOT(ISNUMBER(C39)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A39="",C39=""),"",IF(NOT(IF(ISNUMBER(C39),C39&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G39" s="25">
-        <f>IF(OR(A39="",D39=""),"",IF(NOT(ISNUMBER(D39)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A39="",D39=""),"",IF(NOT(IF(ISNUMBER(D39),D39&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H39" s="25">
@@ -2278,11 +2278,11 @@
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="24" t="n"/>
       <c r="F40" s="25">
-        <f>IF(OR(A40="",C40=""),"",IF(NOT(ISNUMBER(C40)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A40="",C40=""),"",IF(NOT(IF(ISNUMBER(C40),C40&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G40" s="25">
-        <f>IF(OR(A40="",D40=""),"",IF(NOT(ISNUMBER(D40)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A40="",D40=""),"",IF(NOT(IF(ISNUMBER(D40),D40&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H40" s="25">
@@ -2301,11 +2301,11 @@
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="24" t="n"/>
       <c r="F41" s="25">
-        <f>IF(OR(A41="",C41=""),"",IF(NOT(ISNUMBER(C41)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A41="",C41=""),"",IF(NOT(IF(ISNUMBER(C41),C41&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G41" s="25">
-        <f>IF(OR(A41="",D41=""),"",IF(NOT(ISNUMBER(D41)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A41="",D41=""),"",IF(NOT(IF(ISNUMBER(D41),D41&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H41" s="25">
@@ -2324,11 +2324,11 @@
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="25">
-        <f>IF(OR(A42="",C42=""),"",IF(NOT(ISNUMBER(C42)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A42="",C42=""),"",IF(NOT(IF(ISNUMBER(C42),C42&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G42" s="25">
-        <f>IF(OR(A42="",D42=""),"",IF(NOT(ISNUMBER(D42)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A42="",D42=""),"",IF(NOT(IF(ISNUMBER(D42),D42&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H42" s="25">
@@ -2347,11 +2347,11 @@
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="24" t="n"/>
       <c r="F43" s="25">
-        <f>IF(OR(A43="",C43=""),"",IF(NOT(ISNUMBER(C43)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A43="",C43=""),"",IF(NOT(IF(ISNUMBER(C43),C43&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G43" s="25">
-        <f>IF(OR(A43="",D43=""),"",IF(NOT(ISNUMBER(D43)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A43="",D43=""),"",IF(NOT(IF(ISNUMBER(D43),D43&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H43" s="25">
@@ -2370,11 +2370,11 @@
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="24" t="n"/>
       <c r="F44" s="25">
-        <f>IF(OR(A44="",C44=""),"",IF(NOT(ISNUMBER(C44)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A44="",C44=""),"",IF(NOT(IF(ISNUMBER(C44),C44&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G44" s="25">
-        <f>IF(OR(A44="",D44=""),"",IF(NOT(ISNUMBER(D44)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A44="",D44=""),"",IF(NOT(IF(ISNUMBER(D44),D44&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H44" s="25">
@@ -2393,11 +2393,11 @@
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="24" t="n"/>
       <c r="F45" s="25">
-        <f>IF(OR(A45="",C45=""),"",IF(NOT(ISNUMBER(C45)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A45="",C45=""),"",IF(NOT(IF(ISNUMBER(C45),C45&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G45" s="25">
-        <f>IF(OR(A45="",D45=""),"",IF(NOT(ISNUMBER(D45)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A45="",D45=""),"",IF(NOT(IF(ISNUMBER(D45),D45&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H45" s="25">
@@ -2416,11 +2416,11 @@
       <c r="D46" s="23" t="n"/>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="25">
-        <f>IF(OR(A46="",C46=""),"",IF(NOT(ISNUMBER(C46)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A46="",C46=""),"",IF(NOT(IF(ISNUMBER(C46),C46&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G46" s="25">
-        <f>IF(OR(A46="",D46=""),"",IF(NOT(ISNUMBER(D46)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A46="",D46=""),"",IF(NOT(IF(ISNUMBER(D46),D46&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H46" s="25">
@@ -2439,11 +2439,11 @@
       <c r="D47" s="23" t="n"/>
       <c r="E47" s="24" t="n"/>
       <c r="F47" s="25">
-        <f>IF(OR(A47="",C47=""),"",IF(NOT(ISNUMBER(C47)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A47="",C47=""),"",IF(NOT(IF(ISNUMBER(C47),C47&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G47" s="25">
-        <f>IF(OR(A47="",D47=""),"",IF(NOT(ISNUMBER(D47)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A47="",D47=""),"",IF(NOT(IF(ISNUMBER(D47),D47&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H47" s="25">
@@ -2462,11 +2462,11 @@
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="24" t="n"/>
       <c r="F48" s="25">
-        <f>IF(OR(A48="",C48=""),"",IF(NOT(ISNUMBER(C48)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A48="",C48=""),"",IF(NOT(IF(ISNUMBER(C48),C48&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12)))</f>
         <v/>
       </c>
       <c r="G48" s="25">
-        <f>IF(OR(A48="",D48=""),"",IF(NOT(ISNUMBER(D48)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A48="",D48=""),"",IF(NOT(IF(ISNUMBER(D48),D48&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13)))</f>
         <v/>
       </c>
       <c r="H48" s="25">
@@ -2544,27 +2544,27 @@
         <v>8</v>
       </c>
       <c r="C54" s="25">
-        <f>IF(Config!$E$16="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
+        <f>IF(Config!$E$16="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$16)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$16)))</f>
         <v>101500</v>
       </c>
       <c r="D54" s="29">
-        <f>IF(Config!$E$16="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
+        <f>IF(OR(Config!$E$16="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$16)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
         <v>632</v>
       </c>
       <c r="E54" s="30">
-        <f>IF(OR(Config!$E$16="",D54=0),"",C54/D54)</f>
+        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(C54)),NOT(ISNUMBER(D54)),N(D54)=0),"",C54/D54)</f>
         <v>160.601265822785</v>
       </c>
       <c r="F54" s="31">
-        <f>IF(OR(E54="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E54/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E54)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E54/Config!$B$12-1))</f>
         <v>0.255873504649599</v>
       </c>
       <c r="G54" s="29">
-        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$16,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$16)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$16,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>1</v>
       </c>
       <c r="H54" s="25">
-        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
+        <f>IF(OR(Config!$E$16="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$16)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$16))</f>
         <v>1509.21161290322</v>
       </c>
     </row>
@@ -2578,27 +2578,27 @@
         <v>12</v>
       </c>
       <c r="C55" s="25">
-        <f>IF(Config!$E$17="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
+        <f>IF(Config!$E$17="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$17)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$17)))</f>
         <v>105400</v>
       </c>
       <c r="D55" s="29">
-        <f>IF(Config!$E$17="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
+        <f>IF(OR(Config!$E$17="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$17)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
         <v>838</v>
       </c>
       <c r="E55" s="30">
-        <f>IF(OR(Config!$E$17="",D55=0),"",C55/D55)</f>
+        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(C55)),NOT(ISNUMBER(D55)),N(D55)=0),"",C55/D55)</f>
         <v>125.775656324582</v>
       </c>
       <c r="F55" s="31">
-        <f>IF(OR(E55="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E55/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E55)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E55/Config!$B$12-1))</f>
         <v>-0.0164566045061219</v>
       </c>
       <c r="G55" s="29">
-        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$17,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$17)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$17,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>7</v>
       </c>
       <c r="H55" s="25">
-        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
+        <f>IF(OR(Config!$E$17="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$17)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$17))</f>
         <v>9218.8658064516</v>
       </c>
     </row>
@@ -2612,27 +2612,27 @@
         <v>7</v>
       </c>
       <c r="C56" s="25">
-        <f>IF(Config!$E$18="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
+        <f>IF(Config!$E$18="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$18)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$18)))</f>
         <v>39400</v>
       </c>
       <c r="D56" s="29">
-        <f>IF(Config!$E$18="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
+        <f>IF(OR(Config!$E$18="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$18)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
         <v>264</v>
       </c>
       <c r="E56" s="30">
-        <f>IF(OR(Config!$E$18="",D56=0),"",C56/D56)</f>
+        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(C56)),NOT(ISNUMBER(D56)),N(D56)=0),"",C56/D56)</f>
         <v>149.242424242424</v>
       </c>
       <c r="F56" s="31">
-        <f>IF(OR(E56="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E56/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E56)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E56/Config!$B$12-1))</f>
         <v>0.167049371718866</v>
       </c>
       <c r="G56" s="29">
-        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$18,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$18)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$18,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>1</v>
       </c>
       <c r="H56" s="25">
-        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
+        <f>IF(OR(Config!$E$18="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$18)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$18))</f>
         <v>1115.20516129032</v>
       </c>
     </row>
@@ -2646,27 +2646,27 @@
         <v>8</v>
       </c>
       <c r="C57" s="25">
-        <f>IF(Config!$E$19="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
+        <f>IF(Config!$E$19="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$19)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$19)))</f>
         <v>115000</v>
       </c>
       <c r="D57" s="29">
-        <f>IF(Config!$E$19="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
+        <f>IF(OR(Config!$E$19="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$19)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
         <v>615</v>
       </c>
       <c r="E57" s="30">
-        <f>IF(OR(Config!$E$19="",D57=0),"",C57/D57)</f>
+        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(C57)),NOT(ISNUMBER(D57)),N(D57)=0),"",C57/D57)</f>
         <v>186.991869918699</v>
       </c>
       <c r="F57" s="31">
-        <f>IF(OR(E57="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E57/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E57)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E57/Config!$B$12-1))</f>
         <v>0.462243362856868</v>
       </c>
       <c r="G57" s="29">
-        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$19,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$19)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$19,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>0</v>
       </c>
       <c r="H57" s="25">
-        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
+        <f>IF(OR(Config!$E$19="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$19)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$19))</f>
         <v>0</v>
       </c>
     </row>
@@ -2680,27 +2680,27 @@
         <v>3</v>
       </c>
       <c r="C58" s="25">
-        <f>IF(Config!$E$20="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
+        <f>IF(Config!$E$20="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$20)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$20)))</f>
         <v>22600</v>
       </c>
       <c r="D58" s="29">
-        <f>IF(Config!$E$20="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
+        <f>IF(OR(Config!$E$20="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$20)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
         <v>155</v>
       </c>
       <c r="E58" s="30">
-        <f>IF(OR(Config!$E$20="",D58=0),"",C58/D58)</f>
+        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(C58)),NOT(ISNUMBER(D58)),N(D58)=0),"",C58/D58)</f>
         <v>145.806451612903</v>
       </c>
       <c r="F58" s="31">
-        <f>IF(OR(E58="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E58/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E58)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E58/Config!$B$12-1))</f>
         <v>0.140180673231282</v>
       </c>
       <c r="G58" s="29">
-        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$20,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$20)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$20,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v>1</v>
       </c>
       <c r="H58" s="25">
-        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
+        <f>IF(OR(Config!$E$20="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$20)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$20))</f>
         <v>33.4070967741918</v>
       </c>
     </row>
@@ -2714,27 +2714,27 @@
         <v/>
       </c>
       <c r="C59" s="25">
-        <f>IF(Config!$E$21="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
+        <f>IF(Config!$E$21="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$21)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$21)))</f>
         <v/>
       </c>
       <c r="D59" s="29">
-        <f>IF(Config!$E$21="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
+        <f>IF(OR(Config!$E$21="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$21)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
         <v/>
       </c>
       <c r="E59" s="30">
-        <f>IF(OR(Config!$E$21="",D59=0),"",C59/D59)</f>
+        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(C59)),NOT(ISNUMBER(D59)),N(D59)=0),"",C59/D59)</f>
         <v/>
       </c>
       <c r="F59" s="31">
-        <f>IF(OR(E59="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E59/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E59)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E59/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G59" s="29">
-        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$21,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$21)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$21,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H59" s="25">
-        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
+        <f>IF(OR(Config!$E$21="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$21)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$21))</f>
         <v/>
       </c>
     </row>
@@ -2748,27 +2748,27 @@
         <v/>
       </c>
       <c r="C60" s="25">
-        <f>IF(Config!$E$22="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
+        <f>IF(Config!$E$22="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$22)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$22)))</f>
         <v/>
       </c>
       <c r="D60" s="29">
-        <f>IF(Config!$E$22="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
+        <f>IF(OR(Config!$E$22="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$22)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
         <v/>
       </c>
       <c r="E60" s="30">
-        <f>IF(OR(Config!$E$22="",D60=0),"",C60/D60)</f>
+        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(C60)),NOT(ISNUMBER(D60)),N(D60)=0),"",C60/D60)</f>
         <v/>
       </c>
       <c r="F60" s="31">
-        <f>IF(OR(E60="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E60/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E60)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E60/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G60" s="29">
-        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$22,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$22)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$22,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H60" s="25">
-        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
+        <f>IF(OR(Config!$E$22="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$22)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$22))</f>
         <v/>
       </c>
     </row>
@@ -2782,27 +2782,27 @@
         <v/>
       </c>
       <c r="C61" s="25">
-        <f>IF(Config!$E$23="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
+        <f>IF(Config!$E$23="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$23)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$23)))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF(Config!$E$23="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
+        <f>IF(OR(Config!$E$23="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$23)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
         <v/>
       </c>
       <c r="E61" s="30">
-        <f>IF(OR(Config!$E$23="",D61=0),"",C61/D61)</f>
+        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(C61)),NOT(ISNUMBER(D61)),N(D61)=0),"",C61/D61)</f>
         <v/>
       </c>
       <c r="F61" s="31">
-        <f>IF(OR(E61="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E61/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E61)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E61/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G61" s="29">
-        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$23,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$23)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$23,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H61" s="25">
-        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
+        <f>IF(OR(Config!$E$23="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$23)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$23))</f>
         <v/>
       </c>
     </row>
@@ -2816,27 +2816,27 @@
         <v/>
       </c>
       <c r="C62" s="25">
-        <f>IF(Config!$E$24="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
+        <f>IF(Config!$E$24="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$24)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$24)))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF(Config!$E$24="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
+        <f>IF(OR(Config!$E$24="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$24)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
         <v/>
       </c>
       <c r="E62" s="30">
-        <f>IF(OR(Config!$E$24="",D62=0),"",C62/D62)</f>
+        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(C62)),NOT(ISNUMBER(D62)),N(D62)=0),"",C62/D62)</f>
         <v/>
       </c>
       <c r="F62" s="31">
-        <f>IF(OR(E62="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E62/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E62)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E62/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G62" s="29">
-        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$24,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$24)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$24,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H62" s="25">
-        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
+        <f>IF(OR(Config!$E$24="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$24)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$24))</f>
         <v/>
       </c>
     </row>
@@ -2850,27 +2850,27 @@
         <v/>
       </c>
       <c r="C63" s="25">
-        <f>IF(Config!$E$25="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
+        <f>IF(Config!$E$25="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$25)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$25)))</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF(Config!$E$25="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
+        <f>IF(OR(Config!$E$25="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$25)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
         <v/>
       </c>
       <c r="E63" s="30">
-        <f>IF(OR(Config!$E$25="",D63=0),"",C63/D63)</f>
+        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(C63)),NOT(ISNUMBER(D63)),N(D63)=0),"",C63/D63)</f>
         <v/>
       </c>
       <c r="F63" s="31">
-        <f>IF(OR(E63="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E63/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E63)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E63/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G63" s="29">
-        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$25,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$25)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$25,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H63" s="25">
-        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
+        <f>IF(OR(Config!$E$25="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$25)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$25))</f>
         <v/>
       </c>
     </row>
@@ -2884,27 +2884,27 @@
         <v/>
       </c>
       <c r="C64" s="25">
-        <f>IF(Config!$E$26="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
+        <f>IF(Config!$E$26="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$26)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$26)))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF(Config!$E$26="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
+        <f>IF(OR(Config!$E$26="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$26)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
         <v/>
       </c>
       <c r="E64" s="30">
-        <f>IF(OR(Config!$E$26="",D64=0),"",C64/D64)</f>
+        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(C64)),NOT(ISNUMBER(D64)),N(D64)=0),"",C64/D64)</f>
         <v/>
       </c>
       <c r="F64" s="31">
-        <f>IF(OR(E64="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E64/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E64)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E64/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G64" s="29">
-        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$26,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$26)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$26,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H64" s="25">
-        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
+        <f>IF(OR(Config!$E$26="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$26)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$26))</f>
         <v/>
       </c>
     </row>
@@ -2918,27 +2918,27 @@
         <v/>
       </c>
       <c r="C65" s="25">
-        <f>IF(Config!$E$27="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
+        <f>IF(Config!$E$27="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$27)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$27)))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF(Config!$E$27="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
+        <f>IF(OR(Config!$E$27="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$27)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
         <v/>
       </c>
       <c r="E65" s="30">
-        <f>IF(OR(Config!$E$27="",D65=0),"",C65/D65)</f>
+        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(C65)),NOT(ISNUMBER(D65)),N(D65)=0),"",C65/D65)</f>
         <v/>
       </c>
       <c r="F65" s="31">
-        <f>IF(OR(E65="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E65/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E65)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E65/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G65" s="29">
-        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$27,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$27)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$27,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H65" s="25">
-        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
+        <f>IF(OR(Config!$E$27="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$27)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$27))</f>
         <v/>
       </c>
     </row>
@@ -2952,27 +2952,27 @@
         <v/>
       </c>
       <c r="C66" s="25">
-        <f>IF(Config!$E$28="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
+        <f>IF(Config!$E$28="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$28)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$28)))</f>
         <v/>
       </c>
       <c r="D66" s="29">
-        <f>IF(Config!$E$28="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
+        <f>IF(OR(Config!$E$28="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$28)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
         <v/>
       </c>
       <c r="E66" s="30">
-        <f>IF(OR(Config!$E$28="",D66=0),"",C66/D66)</f>
+        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(C66)),NOT(ISNUMBER(D66)),N(D66)=0),"",C66/D66)</f>
         <v/>
       </c>
       <c r="F66" s="31">
-        <f>IF(OR(E66="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E66/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E66)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E66/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G66" s="29">
-        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$28,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$28)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$28,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H66" s="25">
-        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
+        <f>IF(OR(Config!$E$28="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$28)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$28))</f>
         <v/>
       </c>
     </row>
@@ -2986,27 +2986,27 @@
         <v/>
       </c>
       <c r="C67" s="25">
-        <f>IF(Config!$E$29="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
+        <f>IF(Config!$E$29="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$29)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$29)))</f>
         <v/>
       </c>
       <c r="D67" s="29">
-        <f>IF(Config!$E$29="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
+        <f>IF(OR(Config!$E$29="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$29)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
         <v/>
       </c>
       <c r="E67" s="30">
-        <f>IF(OR(Config!$E$29="",D67=0),"",C67/D67)</f>
+        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(C67)),NOT(ISNUMBER(D67)),N(D67)=0),"",C67/D67)</f>
         <v/>
       </c>
       <c r="F67" s="31">
-        <f>IF(OR(E67="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E67/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E67)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E67/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G67" s="29">
-        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$29,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$29)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$29,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H67" s="25">
-        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
+        <f>IF(OR(Config!$E$29="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$29)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$29))</f>
         <v/>
       </c>
     </row>
@@ -3020,27 +3020,27 @@
         <v/>
       </c>
       <c r="C68" s="25">
-        <f>IF(Config!$E$30="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
+        <f>IF(Config!$E$30="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$30)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$30)))</f>
         <v/>
       </c>
       <c r="D68" s="29">
-        <f>IF(Config!$E$30="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
+        <f>IF(OR(Config!$E$30="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$30)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
         <v/>
       </c>
       <c r="E68" s="30">
-        <f>IF(OR(Config!$E$30="",D68=0),"",C68/D68)</f>
+        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(C68)),NOT(ISNUMBER(D68)),N(D68)=0),"",C68/D68)</f>
         <v/>
       </c>
       <c r="F68" s="31">
-        <f>IF(OR(E68="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E68/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E68)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E68/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G68" s="29">
-        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$30,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$30)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$30,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H68" s="25">
-        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
+        <f>IF(OR(Config!$E$30="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$30)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$30))</f>
         <v/>
       </c>
     </row>
@@ -3054,27 +3054,27 @@
         <v/>
       </c>
       <c r="C69" s="25">
-        <f>IF(Config!$E$31="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
+        <f>IF(Config!$E$31="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$31)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$31)))</f>
         <v/>
       </c>
       <c r="D69" s="29">
-        <f>IF(Config!$E$31="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
+        <f>IF(OR(Config!$E$31="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$31)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
         <v/>
       </c>
       <c r="E69" s="30">
-        <f>IF(OR(Config!$E$31="",D69=0),"",C69/D69)</f>
+        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(C69)),NOT(ISNUMBER(D69)),N(D69)=0),"",C69/D69)</f>
         <v/>
       </c>
       <c r="F69" s="31">
-        <f>IF(OR(E69="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E69/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E69)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E69/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G69" s="29">
-        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$31,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$31)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$31,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H69" s="25">
-        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
+        <f>IF(OR(Config!$E$31="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$31)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$31))</f>
         <v/>
       </c>
     </row>
@@ -3088,27 +3088,27 @@
         <v/>
       </c>
       <c r="C70" s="25">
-        <f>IF(Config!$E$32="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
+        <f>IF(Config!$E$32="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$32)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$32)))</f>
         <v/>
       </c>
       <c r="D70" s="29">
-        <f>IF(Config!$E$32="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
+        <f>IF(OR(Config!$E$32="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$32)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
         <v/>
       </c>
       <c r="E70" s="30">
-        <f>IF(OR(Config!$E$32="",D70=0),"",C70/D70)</f>
+        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(C70)),NOT(ISNUMBER(D70)),N(D70)=0),"",C70/D70)</f>
         <v/>
       </c>
       <c r="F70" s="31">
-        <f>IF(OR(E70="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E70/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E70)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E70/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G70" s="29">
-        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$32,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$32)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$32,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H70" s="25">
-        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
+        <f>IF(OR(Config!$E$32="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$32)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$32))</f>
         <v/>
       </c>
     </row>
@@ -3122,27 +3122,27 @@
         <v/>
       </c>
       <c r="C71" s="25">
-        <f>IF(Config!$E$33="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
+        <f>IF(Config!$E$33="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$33)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$33)))</f>
         <v/>
       </c>
       <c r="D71" s="29">
-        <f>IF(Config!$E$33="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
+        <f>IF(OR(Config!$E$33="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$33)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
         <v/>
       </c>
       <c r="E71" s="30">
-        <f>IF(OR(Config!$E$33="",D71=0),"",C71/D71)</f>
+        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(C71)),NOT(ISNUMBER(D71)),N(D71)=0),"",C71/D71)</f>
         <v/>
       </c>
       <c r="F71" s="31">
-        <f>IF(OR(E71="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E71/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E71)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E71/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G71" s="29">
-        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$33,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$33)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$33,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H71" s="25">
-        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
+        <f>IF(OR(Config!$E$33="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$33)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$33))</f>
         <v/>
       </c>
     </row>
@@ -3156,27 +3156,27 @@
         <v/>
       </c>
       <c r="C72" s="25">
-        <f>IF(Config!$E$34="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
+        <f>IF(Config!$E$34="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$34)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$34)))</f>
         <v/>
       </c>
       <c r="D72" s="29">
-        <f>IF(Config!$E$34="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
+        <f>IF(OR(Config!$E$34="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$34)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
         <v/>
       </c>
       <c r="E72" s="30">
-        <f>IF(OR(Config!$E$34="",D72=0),"",C72/D72)</f>
+        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(C72)),NOT(ISNUMBER(D72)),N(D72)=0),"",C72/D72)</f>
         <v/>
       </c>
       <c r="F72" s="31">
-        <f>IF(OR(E72="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E72/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E72)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E72/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G72" s="29">
-        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$34,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$34)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$34,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H72" s="25">
-        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
+        <f>IF(OR(Config!$E$34="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$34)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$34))</f>
         <v/>
       </c>
     </row>
@@ -3190,27 +3190,27 @@
         <v/>
       </c>
       <c r="C73" s="25">
-        <f>IF(Config!$E$35="","",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
+        <f>IF(Config!$E$35="","",IF(SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$35)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0,"caso incompleto",SUMIFS('Nossos casos'!$F$5:$F$204,'Nossos casos'!$C$5:$C$204,Config!$E$35)))</f>
         <v/>
       </c>
       <c r="D73" s="29">
-        <f>IF(Config!$E$35="","",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
+        <f>IF(OR(Config!$E$35="",SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$35)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$G$5:$G$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
         <v/>
       </c>
       <c r="E73" s="30">
-        <f>IF(OR(Config!$E$35="",D73=0),"",C73/D73)</f>
+        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(C73)),NOT(ISNUMBER(D73)),N(D73)=0),"",C73/D73)</f>
         <v/>
       </c>
       <c r="F73" s="31">
-        <f>IF(OR(E73="",NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E73/Config!$B$12-1))</f>
+        <f>IF(OR(NOT(ISNUMBER(E73)),NOT(ISNUMBER(Config!$B$12))),"",IF(Config!$B$12=0,"sem base (mínimo zero)",E73/Config!$B$12-1))</f>
         <v/>
       </c>
       <c r="G73" s="29">
-        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(Config!$B$12))),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$35,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
+        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$35)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",COUNTIFS('Nossos casos'!$C$5:$C$204,Config!$E$35,'Nossos casos'!$J$5:$J$204,"Abaixo do mínimo"))</f>
         <v/>
       </c>
       <c r="H73" s="25">
-        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(Config!$B$12))),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
+        <f>IF(OR(Config!$E$35="",NOT(ISNUMBER(Config!$B$12)),SUMPRODUCT(('Nossos casos'!$C$5:$C$204=Config!$E$35)*((('Nossos casos'!$A$5:$A$204&lt;&gt;"")+('Nossos casos'!$C$5:$C$204&lt;&gt;"")+('Nossos casos'!$F$5:$F$204&lt;&gt;"")+('Nossos casos'!$G$5:$G$204&lt;&gt;"")&gt;0)*((('Nossos casos'!$A$5:$A$204="")+(ISNUMBER(MATCH('Nossos casos'!$C$5:$C$204,Config!$E$16:$E$35,0))=FALSE)+(ISNUMBER('Nossos casos'!$F$5:$F$204)=FALSE)+ISNUMBER('Nossos casos'!$F$5:$F$204)*('Nossos casos'!$F$5:$F$204&lt;0)+(ISNUMBER('Nossos casos'!$G$5:$G$204)=FALSE)+ISNUMBER('Nossos casos'!$G$5:$G$204)*('Nossos casos'!$G$5:$G$204&lt;0))&gt;0)))&gt;0),"",SUMIFS('Nossos casos'!$K$5:$K$204,'Nossos casos'!$C$5:$C$204,Config!$E$35))</f>
         <v/>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
         <v>72</v>
       </c>
       <c r="H5" s="30">
-        <f>IF(OR(A5="",G5="",F5=""),"",IF(OR(NOT(ISNUMBER(F5)),NOT(ISNUMBER(G5))),"valor ou horas inválidos",IF(G5=0,"",F5/G5)))</f>
+        <f>IF(OR(A5="",G5="",F5=""),"",IF(OR(NOT(IF(ISNUMBER(F5),F5&gt;=0,FALSE)),NOT(IF(ISNUMBER(G5),G5&gt;=0,FALSE))),"valor ou horas inválidos",IF(G5=0,"",F5/G5)))</f>
         <v>250</v>
       </c>
       <c r="I5" s="31">
@@ -4185,7 +4185,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="30">
-        <f>IF(OR(A6="",G6="",F6=""),"",IF(OR(NOT(ISNUMBER(F6)),NOT(ISNUMBER(G6))),"valor ou horas inválidos",IF(G6=0,"",F6/G6)))</f>
+        <f>IF(OR(A6="",G6="",F6=""),"",IF(OR(NOT(IF(ISNUMBER(F6),F6&gt;=0,FALSE)),NOT(IF(ISNUMBER(G6),G6&gt;=0,FALSE))),"valor ou horas inválidos",IF(G6=0,"",F6/G6)))</f>
         <v>85.7142857142857</v>
       </c>
       <c r="I6" s="31">
@@ -4238,7 +4238,7 @@
         <v>90</v>
       </c>
       <c r="H7" s="30">
-        <f>IF(OR(A7="",G7="",F7=""),"",IF(OR(NOT(ISNUMBER(F7)),NOT(ISNUMBER(G7))),"valor ou horas inválidos",IF(G7=0,"",F7/G7)))</f>
+        <f>IF(OR(A7="",G7="",F7=""),"",IF(OR(NOT(IF(ISNUMBER(F7),F7&gt;=0,FALSE)),NOT(IF(ISNUMBER(G7),G7&gt;=0,FALSE))),"valor ou horas inválidos",IF(G7=0,"",F7/G7)))</f>
         <v>172.222222222222</v>
       </c>
       <c r="I7" s="31">
@@ -4291,7 +4291,7 @@
         <v>40</v>
       </c>
       <c r="H8" s="30">
-        <f>IF(OR(A8="",G8="",F8=""),"",IF(OR(NOT(ISNUMBER(F8)),NOT(ISNUMBER(G8))),"valor ou horas inválidos",IF(G8=0,"",F8/G8)))</f>
+        <f>IF(OR(A8="",G8="",F8=""),"",IF(OR(NOT(IF(ISNUMBER(F8),F8&gt;=0,FALSE)),NOT(IF(ISNUMBER(G8),G8&gt;=0,FALSE))),"valor ou horas inválidos",IF(G8=0,"",F8/G8)))</f>
         <v>135</v>
       </c>
       <c r="I8" s="31">
@@ -4344,7 +4344,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="30">
-        <f>IF(OR(A9="",G9="",F9=""),"",IF(OR(NOT(ISNUMBER(F9)),NOT(ISNUMBER(G9))),"valor ou horas inválidos",IF(G9=0,"",F9/G9)))</f>
+        <f>IF(OR(A9="",G9="",F9=""),"",IF(OR(NOT(IF(ISNUMBER(F9),F9&gt;=0,FALSE)),NOT(IF(ISNUMBER(G9),G9&gt;=0,FALSE))),"valor ou horas inválidos",IF(G9=0,"",F9/G9)))</f>
         <v>186.666666666667</v>
       </c>
       <c r="I9" s="31">
@@ -4397,7 +4397,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="30">
-        <f>IF(OR(A10="",G10="",F10=""),"",IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(G10))),"valor ou horas inválidos",IF(G10=0,"",F10/G10)))</f>
+        <f>IF(OR(A10="",G10="",F10=""),"",IF(OR(NOT(IF(ISNUMBER(F10),F10&gt;=0,FALSE)),NOT(IF(ISNUMBER(G10),G10&gt;=0,FALSE))),"valor ou horas inválidos",IF(G10=0,"",F10/G10)))</f>
         <v>187.5</v>
       </c>
       <c r="I10" s="31">
@@ -4450,7 +4450,7 @@
         <v>72</v>
       </c>
       <c r="H11" s="30">
-        <f>IF(OR(A11="",G11="",F11=""),"",IF(OR(NOT(ISNUMBER(F11)),NOT(ISNUMBER(G11))),"valor ou horas inválidos",IF(G11=0,"",F11/G11)))</f>
+        <f>IF(OR(A11="",G11="",F11=""),"",IF(OR(NOT(IF(ISNUMBER(F11),F11&gt;=0,FALSE)),NOT(IF(ISNUMBER(G11),G11&gt;=0,FALSE))),"valor ou horas inválidos",IF(G11=0,"",F11/G11)))</f>
         <v>183.333333333333</v>
       </c>
       <c r="I11" s="31">
@@ -4503,7 +4503,7 @@
         <v>80</v>
       </c>
       <c r="H12" s="30">
-        <f>IF(OR(A12="",G12="",F12=""),"",IF(OR(NOT(ISNUMBER(F12)),NOT(ISNUMBER(G12))),"valor ou horas inválidos",IF(G12=0,"",F12/G12)))</f>
+        <f>IF(OR(A12="",G12="",F12=""),"",IF(OR(NOT(IF(ISNUMBER(F12),F12&gt;=0,FALSE)),NOT(IF(ISNUMBER(G12),G12&gt;=0,FALSE))),"valor ou horas inválidos",IF(G12=0,"",F12/G12)))</f>
         <v>118.75</v>
       </c>
       <c r="I12" s="31">
@@ -4556,7 +4556,7 @@
         <v>45</v>
       </c>
       <c r="H13" s="30">
-        <f>IF(OR(A13="",G13="",F13=""),"",IF(OR(NOT(ISNUMBER(F13)),NOT(ISNUMBER(G13))),"valor ou horas inválidos",IF(G13=0,"",F13/G13)))</f>
+        <f>IF(OR(A13="",G13="",F13=""),"",IF(OR(NOT(IF(ISNUMBER(F13),F13&gt;=0,FALSE)),NOT(IF(ISNUMBER(G13),G13&gt;=0,FALSE))),"valor ou horas inválidos",IF(G13=0,"",F13/G13)))</f>
         <v>88.8888888888889</v>
       </c>
       <c r="I13" s="31">
@@ -4609,7 +4609,7 @@
         <v>95</v>
       </c>
       <c r="H14" s="30">
-        <f>IF(OR(A14="",G14="",F14=""),"",IF(OR(NOT(ISNUMBER(F14)),NOT(ISNUMBER(G14))),"valor ou horas inválidos",IF(G14=0,"",F14/G14)))</f>
+        <f>IF(OR(A14="",G14="",F14=""),"",IF(OR(NOT(IF(ISNUMBER(F14),F14&gt;=0,FALSE)),NOT(IF(ISNUMBER(G14),G14&gt;=0,FALSE))),"valor ou horas inválidos",IF(G14=0,"",F14/G14)))</f>
         <v>157.894736842105</v>
       </c>
       <c r="I14" s="31">
@@ -4662,7 +4662,7 @@
         <v>60</v>
       </c>
       <c r="H15" s="30">
-        <f>IF(OR(A15="",G15="",F15=""),"",IF(OR(NOT(ISNUMBER(F15)),NOT(ISNUMBER(G15))),"valor ou horas inválidos",IF(G15=0,"",F15/G15)))</f>
+        <f>IF(OR(A15="",G15="",F15=""),"",IF(OR(NOT(IF(ISNUMBER(F15),F15&gt;=0,FALSE)),NOT(IF(ISNUMBER(G15),G15&gt;=0,FALSE))),"valor ou horas inválidos",IF(G15=0,"",F15/G15)))</f>
         <v>170</v>
       </c>
       <c r="I15" s="31">
@@ -4715,7 +4715,7 @@
         <v>120</v>
       </c>
       <c r="H16" s="30">
-        <f>IF(OR(A16="",G16="",F16=""),"",IF(OR(NOT(ISNUMBER(F16)),NOT(ISNUMBER(G16))),"valor ou horas inválidos",IF(G16=0,"",F16/G16)))</f>
+        <f>IF(OR(A16="",G16="",F16=""),"",IF(OR(NOT(IF(ISNUMBER(F16),F16&gt;=0,FALSE)),NOT(IF(ISNUMBER(G16),G16&gt;=0,FALSE))),"valor ou horas inválidos",IF(G16=0,"",F16/G16)))</f>
         <v>180</v>
       </c>
       <c r="I16" s="31">
@@ -4768,7 +4768,7 @@
         <v>110</v>
       </c>
       <c r="H17" s="30">
-        <f>IF(OR(A17="",G17="",F17=""),"",IF(OR(NOT(ISNUMBER(F17)),NOT(ISNUMBER(G17))),"valor ou horas inválidos",IF(G17=0,"",F17/G17)))</f>
+        <f>IF(OR(A17="",G17="",F17=""),"",IF(OR(NOT(IF(ISNUMBER(F17),F17&gt;=0,FALSE)),NOT(IF(ISNUMBER(G17),G17&gt;=0,FALSE))),"valor ou horas inválidos",IF(G17=0,"",F17/G17)))</f>
         <v>163.636363636364</v>
       </c>
       <c r="I17" s="31">
@@ -4821,7 +4821,7 @@
         <v>90</v>
       </c>
       <c r="H18" s="30">
-        <f>IF(OR(A18="",G18="",F18=""),"",IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER(G18))),"valor ou horas inválidos",IF(G18=0,"",F18/G18)))</f>
+        <f>IF(OR(A18="",G18="",F18=""),"",IF(OR(NOT(IF(ISNUMBER(F18),F18&gt;=0,FALSE)),NOT(IF(ISNUMBER(G18),G18&gt;=0,FALSE))),"valor ou horas inválidos",IF(G18=0,"",F18/G18)))</f>
         <v>150</v>
       </c>
       <c r="I18" s="31">
@@ -4874,7 +4874,7 @@
         <v>80</v>
       </c>
       <c r="H19" s="30">
-        <f>IF(OR(A19="",G19="",F19=""),"",IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"valor ou horas inválidos",IF(G19=0,"",F19/G19)))</f>
+        <f>IF(OR(A19="",G19="",F19=""),"",IF(OR(NOT(IF(ISNUMBER(F19),F19&gt;=0,FALSE)),NOT(IF(ISNUMBER(G19),G19&gt;=0,FALSE))),"valor ou horas inválidos",IF(G19=0,"",F19/G19)))</f>
         <v>112.5</v>
       </c>
       <c r="I19" s="31">
@@ -4927,7 +4927,7 @@
         <v>28</v>
       </c>
       <c r="H20" s="30">
-        <f>IF(OR(A20="",G20="",F20=""),"",IF(OR(NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20))),"valor ou horas inválidos",IF(G20=0,"",F20/G20)))</f>
+        <f>IF(OR(A20="",G20="",F20=""),"",IF(OR(NOT(IF(ISNUMBER(F20),F20&gt;=0,FALSE)),NOT(IF(ISNUMBER(G20),G20&gt;=0,FALSE))),"valor ou horas inválidos",IF(G20=0,"",F20/G20)))</f>
         <v>157.142857142857</v>
       </c>
       <c r="I20" s="31">
@@ -4980,7 +4980,7 @@
         <v>55</v>
       </c>
       <c r="H21" s="30">
-        <f>IF(OR(A21="",G21="",F21=""),"",IF(OR(NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21))),"valor ou horas inválidos",IF(G21=0,"",F21/G21)))</f>
+        <f>IF(OR(A21="",G21="",F21=""),"",IF(OR(NOT(IF(ISNUMBER(F21),F21&gt;=0,FALSE)),NOT(IF(ISNUMBER(G21),G21&gt;=0,FALSE))),"valor ou horas inválidos",IF(G21=0,"",F21/G21)))</f>
         <v>163.636363636364</v>
       </c>
       <c r="I21" s="31">
@@ -5033,7 +5033,7 @@
         <v>45</v>
       </c>
       <c r="H22" s="30">
-        <f>IF(OR(A22="",G22="",F22=""),"",IF(OR(NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22))),"valor ou horas inválidos",IF(G22=0,"",F22/G22)))</f>
+        <f>IF(OR(A22="",G22="",F22=""),"",IF(OR(NOT(IF(ISNUMBER(F22),F22&gt;=0,FALSE)),NOT(IF(ISNUMBER(G22),G22&gt;=0,FALSE))),"valor ou horas inválidos",IF(G22=0,"",F22/G22)))</f>
         <v>146.666666666667</v>
       </c>
       <c r="I22" s="31">
@@ -5086,7 +5086,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="30">
-        <f>IF(OR(A23="",G23="",F23=""),"",IF(OR(NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23))),"valor ou horas inválidos",IF(G23=0,"",F23/G23)))</f>
+        <f>IF(OR(A23="",G23="",F23=""),"",IF(OR(NOT(IF(ISNUMBER(F23),F23&gt;=0,FALSE)),NOT(IF(ISNUMBER(G23),G23&gt;=0,FALSE))),"valor ou horas inválidos",IF(G23=0,"",F23/G23)))</f>
         <v>111.111111111111</v>
       </c>
       <c r="I23" s="31">
@@ -5139,7 +5139,7 @@
         <v>40</v>
       </c>
       <c r="H24" s="30">
-        <f>IF(OR(A24="",G24="",F24=""),"",IF(OR(NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24))),"valor ou horas inválidos",IF(G24=0,"",F24/G24)))</f>
+        <f>IF(OR(A24="",G24="",F24=""),"",IF(OR(NOT(IF(ISNUMBER(F24),F24&gt;=0,FALSE)),NOT(IF(ISNUMBER(G24),G24&gt;=0,FALSE))),"valor ou horas inválidos",IF(G24=0,"",F24/G24)))</f>
         <v>100</v>
       </c>
       <c r="I24" s="31">
@@ -5192,7 +5192,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="30">
-        <f>IF(OR(A25="",G25="",F25=""),"",IF(OR(NOT(ISNUMBER(F25)),NOT(ISNUMBER(G25))),"valor ou horas inválidos",IF(G25=0,"",F25/G25)))</f>
+        <f>IF(OR(A25="",G25="",F25=""),"",IF(OR(NOT(IF(ISNUMBER(F25),F25&gt;=0,FALSE)),NOT(IF(ISNUMBER(G25),G25&gt;=0,FALSE))),"valor ou horas inválidos",IF(G25=0,"",F25/G25)))</f>
         <v>157.894736842105</v>
       </c>
       <c r="I25" s="31">
@@ -5245,7 +5245,7 @@
         <v>60</v>
       </c>
       <c r="H26" s="30">
-        <f>IF(OR(A26="",G26="",F26=""),"",IF(OR(NOT(ISNUMBER(F26)),NOT(ISNUMBER(G26))),"valor ou horas inválidos",IF(G26=0,"",F26/G26)))</f>
+        <f>IF(OR(A26="",G26="",F26=""),"",IF(OR(NOT(IF(ISNUMBER(F26),F26&gt;=0,FALSE)),NOT(IF(ISNUMBER(G26),G26&gt;=0,FALSE))),"valor ou horas inválidos",IF(G26=0,"",F26/G26)))</f>
         <v>150</v>
       </c>
       <c r="I26" s="31">
@@ -5298,7 +5298,7 @@
         <v>75</v>
       </c>
       <c r="H27" s="30">
-        <f>IF(OR(A27="",G27="",F27=""),"",IF(OR(NOT(ISNUMBER(F27)),NOT(ISNUMBER(G27))),"valor ou horas inválidos",IF(G27=0,"",F27/G27)))</f>
+        <f>IF(OR(A27="",G27="",F27=""),"",IF(OR(NOT(IF(ISNUMBER(F27),F27&gt;=0,FALSE)),NOT(IF(ISNUMBER(G27),G27&gt;=0,FALSE))),"valor ou horas inválidos",IF(G27=0,"",F27/G27)))</f>
         <v>160</v>
       </c>
       <c r="I27" s="31">
@@ -5351,7 +5351,7 @@
         <v>40</v>
       </c>
       <c r="H28" s="30">
-        <f>IF(OR(A28="",G28="",F28=""),"",IF(OR(NOT(ISNUMBER(F28)),NOT(ISNUMBER(G28))),"valor ou horas inválidos",IF(G28=0,"",F28/G28)))</f>
+        <f>IF(OR(A28="",G28="",F28=""),"",IF(OR(NOT(IF(ISNUMBER(F28),F28&gt;=0,FALSE)),NOT(IF(ISNUMBER(G28),G28&gt;=0,FALSE))),"valor ou horas inválidos",IF(G28=0,"",F28/G28)))</f>
         <v>190</v>
       </c>
       <c r="I28" s="31">
@@ -5404,7 +5404,7 @@
         <v>133</v>
       </c>
       <c r="H29" s="30">
-        <f>IF(OR(A29="",G29="",F29=""),"",IF(OR(NOT(ISNUMBER(F29)),NOT(ISNUMBER(G29))),"valor ou horas inválidos",IF(G29=0,"",F29/G29)))</f>
+        <f>IF(OR(A29="",G29="",F29=""),"",IF(OR(NOT(IF(ISNUMBER(F29),F29&gt;=0,FALSE)),NOT(IF(ISNUMBER(G29),G29&gt;=0,FALSE))),"valor ou horas inválidos",IF(G29=0,"",F29/G29)))</f>
         <v>180.451127819549</v>
       </c>
       <c r="I29" s="31">
@@ -5457,7 +5457,7 @@
         <v>30</v>
       </c>
       <c r="H30" s="30">
-        <f>IF(OR(A30="",G30="",F30=""),"",IF(OR(NOT(ISNUMBER(F30)),NOT(ISNUMBER(G30))),"valor ou horas inválidos",IF(G30=0,"",F30/G30)))</f>
+        <f>IF(OR(A30="",G30="",F30=""),"",IF(OR(NOT(IF(ISNUMBER(F30),F30&gt;=0,FALSE)),NOT(IF(ISNUMBER(G30),G30&gt;=0,FALSE))),"valor ou horas inválidos",IF(G30=0,"",F30/G30)))</f>
         <v>233.333333333333</v>
       </c>
       <c r="I30" s="31">
@@ -5510,7 +5510,7 @@
         <v>70</v>
       </c>
       <c r="H31" s="30">
-        <f>IF(OR(A31="",G31="",F31=""),"",IF(OR(NOT(ISNUMBER(F31)),NOT(ISNUMBER(G31))),"valor ou horas inválidos",IF(G31=0,"",F31/G31)))</f>
+        <f>IF(OR(A31="",G31="",F31=""),"",IF(OR(NOT(IF(ISNUMBER(F31),F31&gt;=0,FALSE)),NOT(IF(ISNUMBER(G31),G31&gt;=0,FALSE))),"valor ou horas inválidos",IF(G31=0,"",F31/G31)))</f>
         <v>100</v>
       </c>
       <c r="I31" s="31">
@@ -5563,7 +5563,7 @@
         <v>55</v>
       </c>
       <c r="H32" s="30">
-        <f>IF(OR(A32="",G32="",F32=""),"",IF(OR(NOT(ISNUMBER(F32)),NOT(ISNUMBER(G32))),"valor ou horas inválidos",IF(G32=0,"",F32/G32)))</f>
+        <f>IF(OR(A32="",G32="",F32=""),"",IF(OR(NOT(IF(ISNUMBER(F32),F32&gt;=0,FALSE)),NOT(IF(ISNUMBER(G32),G32&gt;=0,FALSE))),"valor ou horas inválidos",IF(G32=0,"",F32/G32)))</f>
         <v>136.363636363636</v>
       </c>
       <c r="I32" s="31">
@@ -5616,7 +5616,7 @@
         <v>40</v>
       </c>
       <c r="H33" s="30">
-        <f>IF(OR(A33="",G33="",F33=""),"",IF(OR(NOT(ISNUMBER(F33)),NOT(ISNUMBER(G33))),"valor ou horas inválidos",IF(G33=0,"",F33/G33)))</f>
+        <f>IF(OR(A33="",G33="",F33=""),"",IF(OR(NOT(IF(ISNUMBER(F33),F33&gt;=0,FALSE)),NOT(IF(ISNUMBER(G33),G33&gt;=0,FALSE))),"valor ou horas inválidos",IF(G33=0,"",F33/G33)))</f>
         <v>190</v>
       </c>
       <c r="I33" s="31">
@@ -5669,7 +5669,7 @@
         <v>35</v>
       </c>
       <c r="H34" s="30">
-        <f>IF(OR(A34="",G34="",F34=""),"",IF(OR(NOT(ISNUMBER(F34)),NOT(ISNUMBER(G34))),"valor ou horas inválidos",IF(G34=0,"",F34/G34)))</f>
+        <f>IF(OR(A34="",G34="",F34=""),"",IF(OR(NOT(IF(ISNUMBER(F34),F34&gt;=0,FALSE)),NOT(IF(ISNUMBER(G34),G34&gt;=0,FALSE))),"valor ou horas inválidos",IF(G34=0,"",F34/G34)))</f>
         <v>154.285714285714</v>
       </c>
       <c r="I34" s="31">
@@ -5722,7 +5722,7 @@
         <v>60</v>
       </c>
       <c r="H35" s="30">
-        <f>IF(OR(A35="",G35="",F35=""),"",IF(OR(NOT(ISNUMBER(F35)),NOT(ISNUMBER(G35))),"valor ou horas inválidos",IF(G35=0,"",F35/G35)))</f>
+        <f>IF(OR(A35="",G35="",F35=""),"",IF(OR(NOT(IF(ISNUMBER(F35),F35&gt;=0,FALSE)),NOT(IF(ISNUMBER(G35),G35&gt;=0,FALSE))),"valor ou horas inválidos",IF(G35=0,"",F35/G35)))</f>
         <v>200</v>
       </c>
       <c r="I35" s="31">
@@ -5775,7 +5775,7 @@
         <v>110</v>
       </c>
       <c r="H36" s="30">
-        <f>IF(OR(A36="",G36="",F36=""),"",IF(OR(NOT(ISNUMBER(F36)),NOT(ISNUMBER(G36))),"valor ou horas inválidos",IF(G36=0,"",F36/G36)))</f>
+        <f>IF(OR(A36="",G36="",F36=""),"",IF(OR(NOT(IF(ISNUMBER(F36),F36&gt;=0,FALSE)),NOT(IF(ISNUMBER(G36),G36&gt;=0,FALSE))),"valor ou horas inválidos",IF(G36=0,"",F36/G36)))</f>
         <v>163.636363636364</v>
       </c>
       <c r="I36" s="31">
@@ -5828,7 +5828,7 @@
         <v>45</v>
       </c>
       <c r="H37" s="30">
-        <f>IF(OR(A37="",G37="",F37=""),"",IF(OR(NOT(ISNUMBER(F37)),NOT(ISNUMBER(G37))),"valor ou horas inválidos",IF(G37=0,"",F37/G37)))</f>
+        <f>IF(OR(A37="",G37="",F37=""),"",IF(OR(NOT(IF(ISNUMBER(F37),F37&gt;=0,FALSE)),NOT(IF(ISNUMBER(G37),G37&gt;=0,FALSE))),"valor ou horas inválidos",IF(G37=0,"",F37/G37)))</f>
         <v>144.444444444444</v>
       </c>
       <c r="I37" s="31">
@@ -5881,7 +5881,7 @@
         <v>45</v>
       </c>
       <c r="H38" s="30">
-        <f>IF(OR(A38="",G38="",F38=""),"",IF(OR(NOT(ISNUMBER(F38)),NOT(ISNUMBER(G38))),"valor ou horas inválidos",IF(G38=0,"",F38/G38)))</f>
+        <f>IF(OR(A38="",G38="",F38=""),"",IF(OR(NOT(IF(ISNUMBER(F38),F38&gt;=0,FALSE)),NOT(IF(ISNUMBER(G38),G38&gt;=0,FALSE))),"valor ou horas inválidos",IF(G38=0,"",F38/G38)))</f>
         <v>133.333333333333</v>
       </c>
       <c r="I38" s="31">
@@ -5934,7 +5934,7 @@
         <v>95</v>
       </c>
       <c r="H39" s="30">
-        <f>IF(OR(A39="",G39="",F39=""),"",IF(OR(NOT(ISNUMBER(F39)),NOT(ISNUMBER(G39))),"valor ou horas inválidos",IF(G39=0,"",F39/G39)))</f>
+        <f>IF(OR(A39="",G39="",F39=""),"",IF(OR(NOT(IF(ISNUMBER(F39),F39&gt;=0,FALSE)),NOT(IF(ISNUMBER(G39),G39&gt;=0,FALSE))),"valor ou horas inválidos",IF(G39=0,"",F39/G39)))</f>
         <v>126.315789473684</v>
       </c>
       <c r="I39" s="31">
@@ -5987,7 +5987,7 @@
         <v>55</v>
       </c>
       <c r="H40" s="30">
-        <f>IF(OR(A40="",G40="",F40=""),"",IF(OR(NOT(ISNUMBER(F40)),NOT(ISNUMBER(G40))),"valor ou horas inválidos",IF(G40=0,"",F40/G40)))</f>
+        <f>IF(OR(A40="",G40="",F40=""),"",IF(OR(NOT(IF(ISNUMBER(F40),F40&gt;=0,FALSE)),NOT(IF(ISNUMBER(G40),G40&gt;=0,FALSE))),"valor ou horas inválidos",IF(G40=0,"",F40/G40)))</f>
         <v>127.272727272727</v>
       </c>
       <c r="I40" s="31">
@@ -6040,7 +6040,7 @@
         <v>40</v>
       </c>
       <c r="H41" s="30">
-        <f>IF(OR(A41="",G41="",F41=""),"",IF(OR(NOT(ISNUMBER(F41)),NOT(ISNUMBER(G41))),"valor ou horas inválidos",IF(G41=0,"",F41/G41)))</f>
+        <f>IF(OR(A41="",G41="",F41=""),"",IF(OR(NOT(IF(ISNUMBER(F41),F41&gt;=0,FALSE)),NOT(IF(ISNUMBER(G41),G41&gt;=0,FALSE))),"valor ou horas inválidos",IF(G41=0,"",F41/G41)))</f>
         <v>150</v>
       </c>
       <c r="I41" s="31">
@@ -6093,7 +6093,7 @@
         <v>70</v>
       </c>
       <c r="H42" s="30">
-        <f>IF(OR(A42="",G42="",F42=""),"",IF(OR(NOT(ISNUMBER(F42)),NOT(ISNUMBER(G42))),"valor ou horas inválidos",IF(G42=0,"",F42/G42)))</f>
+        <f>IF(OR(A42="",G42="",F42=""),"",IF(OR(NOT(IF(ISNUMBER(F42),F42&gt;=0,FALSE)),NOT(IF(ISNUMBER(G42),G42&gt;=0,FALSE))),"valor ou horas inválidos",IF(G42=0,"",F42/G42)))</f>
         <v>121.428571428571</v>
       </c>
       <c r="I42" s="31">
@@ -6122,7 +6122,7 @@
       <c r="F43" s="40" t="n"/>
       <c r="G43" s="23" t="n"/>
       <c r="H43" s="30">
-        <f>IF(OR(A43="",G43="",F43=""),"",IF(OR(NOT(ISNUMBER(F43)),NOT(ISNUMBER(G43))),"valor ou horas inválidos",IF(G43=0,"",F43/G43)))</f>
+        <f>IF(OR(A43="",G43="",F43=""),"",IF(OR(NOT(IF(ISNUMBER(F43),F43&gt;=0,FALSE)),NOT(IF(ISNUMBER(G43),G43&gt;=0,FALSE))),"valor ou horas inválidos",IF(G43=0,"",F43/G43)))</f>
         <v/>
       </c>
       <c r="I43" s="31">
@@ -6151,7 +6151,7 @@
       <c r="F44" s="40" t="n"/>
       <c r="G44" s="23" t="n"/>
       <c r="H44" s="30">
-        <f>IF(OR(A44="",G44="",F44=""),"",IF(OR(NOT(ISNUMBER(F44)),NOT(ISNUMBER(G44))),"valor ou horas inválidos",IF(G44=0,"",F44/G44)))</f>
+        <f>IF(OR(A44="",G44="",F44=""),"",IF(OR(NOT(IF(ISNUMBER(F44),F44&gt;=0,FALSE)),NOT(IF(ISNUMBER(G44),G44&gt;=0,FALSE))),"valor ou horas inválidos",IF(G44=0,"",F44/G44)))</f>
         <v/>
       </c>
       <c r="I44" s="31">
@@ -6180,7 +6180,7 @@
       <c r="F45" s="40" t="n"/>
       <c r="G45" s="23" t="n"/>
       <c r="H45" s="30">
-        <f>IF(OR(A45="",G45="",F45=""),"",IF(OR(NOT(ISNUMBER(F45)),NOT(ISNUMBER(G45))),"valor ou horas inválidos",IF(G45=0,"",F45/G45)))</f>
+        <f>IF(OR(A45="",G45="",F45=""),"",IF(OR(NOT(IF(ISNUMBER(F45),F45&gt;=0,FALSE)),NOT(IF(ISNUMBER(G45),G45&gt;=0,FALSE))),"valor ou horas inválidos",IF(G45=0,"",F45/G45)))</f>
         <v/>
       </c>
       <c r="I45" s="31">
@@ -6209,7 +6209,7 @@
       <c r="F46" s="40" t="n"/>
       <c r="G46" s="23" t="n"/>
       <c r="H46" s="30">
-        <f>IF(OR(A46="",G46="",F46=""),"",IF(OR(NOT(ISNUMBER(F46)),NOT(ISNUMBER(G46))),"valor ou horas inválidos",IF(G46=0,"",F46/G46)))</f>
+        <f>IF(OR(A46="",G46="",F46=""),"",IF(OR(NOT(IF(ISNUMBER(F46),F46&gt;=0,FALSE)),NOT(IF(ISNUMBER(G46),G46&gt;=0,FALSE))),"valor ou horas inválidos",IF(G46=0,"",F46/G46)))</f>
         <v/>
       </c>
       <c r="I46" s="31">
@@ -6238,7 +6238,7 @@
       <c r="F47" s="40" t="n"/>
       <c r="G47" s="23" t="n"/>
       <c r="H47" s="30">
-        <f>IF(OR(A47="",G47="",F47=""),"",IF(OR(NOT(ISNUMBER(F47)),NOT(ISNUMBER(G47))),"valor ou horas inválidos",IF(G47=0,"",F47/G47)))</f>
+        <f>IF(OR(A47="",G47="",F47=""),"",IF(OR(NOT(IF(ISNUMBER(F47),F47&gt;=0,FALSE)),NOT(IF(ISNUMBER(G47),G47&gt;=0,FALSE))),"valor ou horas inválidos",IF(G47=0,"",F47/G47)))</f>
         <v/>
       </c>
       <c r="I47" s="31">
@@ -6267,7 +6267,7 @@
       <c r="F48" s="40" t="n"/>
       <c r="G48" s="23" t="n"/>
       <c r="H48" s="30">
-        <f>IF(OR(A48="",G48="",F48=""),"",IF(OR(NOT(ISNUMBER(F48)),NOT(ISNUMBER(G48))),"valor ou horas inválidos",IF(G48=0,"",F48/G48)))</f>
+        <f>IF(OR(A48="",G48="",F48=""),"",IF(OR(NOT(IF(ISNUMBER(F48),F48&gt;=0,FALSE)),NOT(IF(ISNUMBER(G48),G48&gt;=0,FALSE))),"valor ou horas inválidos",IF(G48=0,"",F48/G48)))</f>
         <v/>
       </c>
       <c r="I48" s="31">
@@ -6296,7 +6296,7 @@
       <c r="F49" s="40" t="n"/>
       <c r="G49" s="23" t="n"/>
       <c r="H49" s="30">
-        <f>IF(OR(A49="",G49="",F49=""),"",IF(OR(NOT(ISNUMBER(F49)),NOT(ISNUMBER(G49))),"valor ou horas inválidos",IF(G49=0,"",F49/G49)))</f>
+        <f>IF(OR(A49="",G49="",F49=""),"",IF(OR(NOT(IF(ISNUMBER(F49),F49&gt;=0,FALSE)),NOT(IF(ISNUMBER(G49),G49&gt;=0,FALSE))),"valor ou horas inválidos",IF(G49=0,"",F49/G49)))</f>
         <v/>
       </c>
       <c r="I49" s="31">
@@ -6325,7 +6325,7 @@
       <c r="F50" s="40" t="n"/>
       <c r="G50" s="23" t="n"/>
       <c r="H50" s="30">
-        <f>IF(OR(A50="",G50="",F50=""),"",IF(OR(NOT(ISNUMBER(F50)),NOT(ISNUMBER(G50))),"valor ou horas inválidos",IF(G50=0,"",F50/G50)))</f>
+        <f>IF(OR(A50="",G50="",F50=""),"",IF(OR(NOT(IF(ISNUMBER(F50),F50&gt;=0,FALSE)),NOT(IF(ISNUMBER(G50),G50&gt;=0,FALSE))),"valor ou horas inválidos",IF(G50=0,"",F50/G50)))</f>
         <v/>
       </c>
       <c r="I50" s="31">
@@ -6354,7 +6354,7 @@
       <c r="F51" s="40" t="n"/>
       <c r="G51" s="23" t="n"/>
       <c r="H51" s="30">
-        <f>IF(OR(A51="",G51="",F51=""),"",IF(OR(NOT(ISNUMBER(F51)),NOT(ISNUMBER(G51))),"valor ou horas inválidos",IF(G51=0,"",F51/G51)))</f>
+        <f>IF(OR(A51="",G51="",F51=""),"",IF(OR(NOT(IF(ISNUMBER(F51),F51&gt;=0,FALSE)),NOT(IF(ISNUMBER(G51),G51&gt;=0,FALSE))),"valor ou horas inválidos",IF(G51=0,"",F51/G51)))</f>
         <v/>
       </c>
       <c r="I51" s="31">
@@ -6383,7 +6383,7 @@
       <c r="F52" s="40" t="n"/>
       <c r="G52" s="23" t="n"/>
       <c r="H52" s="30">
-        <f>IF(OR(A52="",G52="",F52=""),"",IF(OR(NOT(ISNUMBER(F52)),NOT(ISNUMBER(G52))),"valor ou horas inválidos",IF(G52=0,"",F52/G52)))</f>
+        <f>IF(OR(A52="",G52="",F52=""),"",IF(OR(NOT(IF(ISNUMBER(F52),F52&gt;=0,FALSE)),NOT(IF(ISNUMBER(G52),G52&gt;=0,FALSE))),"valor ou horas inválidos",IF(G52=0,"",F52/G52)))</f>
         <v/>
       </c>
       <c r="I52" s="31">
@@ -6412,7 +6412,7 @@
       <c r="F53" s="40" t="n"/>
       <c r="G53" s="23" t="n"/>
       <c r="H53" s="30">
-        <f>IF(OR(A53="",G53="",F53=""),"",IF(OR(NOT(ISNUMBER(F53)),NOT(ISNUMBER(G53))),"valor ou horas inválidos",IF(G53=0,"",F53/G53)))</f>
+        <f>IF(OR(A53="",G53="",F53=""),"",IF(OR(NOT(IF(ISNUMBER(F53),F53&gt;=0,FALSE)),NOT(IF(ISNUMBER(G53),G53&gt;=0,FALSE))),"valor ou horas inválidos",IF(G53=0,"",F53/G53)))</f>
         <v/>
       </c>
       <c r="I53" s="31">
@@ -6441,7 +6441,7 @@
       <c r="F54" s="40" t="n"/>
       <c r="G54" s="23" t="n"/>
       <c r="H54" s="30">
-        <f>IF(OR(A54="",G54="",F54=""),"",IF(OR(NOT(ISNUMBER(F54)),NOT(ISNUMBER(G54))),"valor ou horas inválidos",IF(G54=0,"",F54/G54)))</f>
+        <f>IF(OR(A54="",G54="",F54=""),"",IF(OR(NOT(IF(ISNUMBER(F54),F54&gt;=0,FALSE)),NOT(IF(ISNUMBER(G54),G54&gt;=0,FALSE))),"valor ou horas inválidos",IF(G54=0,"",F54/G54)))</f>
         <v/>
       </c>
       <c r="I54" s="31">
@@ -6470,7 +6470,7 @@
       <c r="F55" s="40" t="n"/>
       <c r="G55" s="23" t="n"/>
       <c r="H55" s="30">
-        <f>IF(OR(A55="",G55="",F55=""),"",IF(OR(NOT(ISNUMBER(F55)),NOT(ISNUMBER(G55))),"valor ou horas inválidos",IF(G55=0,"",F55/G55)))</f>
+        <f>IF(OR(A55="",G55="",F55=""),"",IF(OR(NOT(IF(ISNUMBER(F55),F55&gt;=0,FALSE)),NOT(IF(ISNUMBER(G55),G55&gt;=0,FALSE))),"valor ou horas inválidos",IF(G55=0,"",F55/G55)))</f>
         <v/>
       </c>
       <c r="I55" s="31">
@@ -6499,7 +6499,7 @@
       <c r="F56" s="40" t="n"/>
       <c r="G56" s="23" t="n"/>
       <c r="H56" s="30">
-        <f>IF(OR(A56="",G56="",F56=""),"",IF(OR(NOT(ISNUMBER(F56)),NOT(ISNUMBER(G56))),"valor ou horas inválidos",IF(G56=0,"",F56/G56)))</f>
+        <f>IF(OR(A56="",G56="",F56=""),"",IF(OR(NOT(IF(ISNUMBER(F56),F56&gt;=0,FALSE)),NOT(IF(ISNUMBER(G56),G56&gt;=0,FALSE))),"valor ou horas inválidos",IF(G56=0,"",F56/G56)))</f>
         <v/>
       </c>
       <c r="I56" s="31">
@@ -6528,7 +6528,7 @@
       <c r="F57" s="40" t="n"/>
       <c r="G57" s="23" t="n"/>
       <c r="H57" s="30">
-        <f>IF(OR(A57="",G57="",F57=""),"",IF(OR(NOT(ISNUMBER(F57)),NOT(ISNUMBER(G57))),"valor ou horas inválidos",IF(G57=0,"",F57/G57)))</f>
+        <f>IF(OR(A57="",G57="",F57=""),"",IF(OR(NOT(IF(ISNUMBER(F57),F57&gt;=0,FALSE)),NOT(IF(ISNUMBER(G57),G57&gt;=0,FALSE))),"valor ou horas inválidos",IF(G57=0,"",F57/G57)))</f>
         <v/>
       </c>
       <c r="I57" s="31">
@@ -6557,7 +6557,7 @@
       <c r="F58" s="40" t="n"/>
       <c r="G58" s="23" t="n"/>
       <c r="H58" s="30">
-        <f>IF(OR(A58="",G58="",F58=""),"",IF(OR(NOT(ISNUMBER(F58)),NOT(ISNUMBER(G58))),"valor ou horas inválidos",IF(G58=0,"",F58/G58)))</f>
+        <f>IF(OR(A58="",G58="",F58=""),"",IF(OR(NOT(IF(ISNUMBER(F58),F58&gt;=0,FALSE)),NOT(IF(ISNUMBER(G58),G58&gt;=0,FALSE))),"valor ou horas inválidos",IF(G58=0,"",F58/G58)))</f>
         <v/>
       </c>
       <c r="I58" s="31">
@@ -6586,7 +6586,7 @@
       <c r="F59" s="40" t="n"/>
       <c r="G59" s="23" t="n"/>
       <c r="H59" s="30">
-        <f>IF(OR(A59="",G59="",F59=""),"",IF(OR(NOT(ISNUMBER(F59)),NOT(ISNUMBER(G59))),"valor ou horas inválidos",IF(G59=0,"",F59/G59)))</f>
+        <f>IF(OR(A59="",G59="",F59=""),"",IF(OR(NOT(IF(ISNUMBER(F59),F59&gt;=0,FALSE)),NOT(IF(ISNUMBER(G59),G59&gt;=0,FALSE))),"valor ou horas inválidos",IF(G59=0,"",F59/G59)))</f>
         <v/>
       </c>
       <c r="I59" s="31">
@@ -6615,7 +6615,7 @@
       <c r="F60" s="40" t="n"/>
       <c r="G60" s="23" t="n"/>
       <c r="H60" s="30">
-        <f>IF(OR(A60="",G60="",F60=""),"",IF(OR(NOT(ISNUMBER(F60)),NOT(ISNUMBER(G60))),"valor ou horas inválidos",IF(G60=0,"",F60/G60)))</f>
+        <f>IF(OR(A60="",G60="",F60=""),"",IF(OR(NOT(IF(ISNUMBER(F60),F60&gt;=0,FALSE)),NOT(IF(ISNUMBER(G60),G60&gt;=0,FALSE))),"valor ou horas inválidos",IF(G60=0,"",F60/G60)))</f>
         <v/>
       </c>
       <c r="I60" s="31">
@@ -6644,7 +6644,7 @@
       <c r="F61" s="40" t="n"/>
       <c r="G61" s="23" t="n"/>
       <c r="H61" s="30">
-        <f>IF(OR(A61="",G61="",F61=""),"",IF(OR(NOT(ISNUMBER(F61)),NOT(ISNUMBER(G61))),"valor ou horas inválidos",IF(G61=0,"",F61/G61)))</f>
+        <f>IF(OR(A61="",G61="",F61=""),"",IF(OR(NOT(IF(ISNUMBER(F61),F61&gt;=0,FALSE)),NOT(IF(ISNUMBER(G61),G61&gt;=0,FALSE))),"valor ou horas inválidos",IF(G61=0,"",F61/G61)))</f>
         <v/>
       </c>
       <c r="I61" s="31">
@@ -6673,7 +6673,7 @@
       <c r="F62" s="40" t="n"/>
       <c r="G62" s="23" t="n"/>
       <c r="H62" s="30">
-        <f>IF(OR(A62="",G62="",F62=""),"",IF(OR(NOT(ISNUMBER(F62)),NOT(ISNUMBER(G62))),"valor ou horas inválidos",IF(G62=0,"",F62/G62)))</f>
+        <f>IF(OR(A62="",G62="",F62=""),"",IF(OR(NOT(IF(ISNUMBER(F62),F62&gt;=0,FALSE)),NOT(IF(ISNUMBER(G62),G62&gt;=0,FALSE))),"valor ou horas inválidos",IF(G62=0,"",F62/G62)))</f>
         <v/>
       </c>
       <c r="I62" s="31">
@@ -6702,7 +6702,7 @@
       <c r="F63" s="40" t="n"/>
       <c r="G63" s="23" t="n"/>
       <c r="H63" s="30">
-        <f>IF(OR(A63="",G63="",F63=""),"",IF(OR(NOT(ISNUMBER(F63)),NOT(ISNUMBER(G63))),"valor ou horas inválidos",IF(G63=0,"",F63/G63)))</f>
+        <f>IF(OR(A63="",G63="",F63=""),"",IF(OR(NOT(IF(ISNUMBER(F63),F63&gt;=0,FALSE)),NOT(IF(ISNUMBER(G63),G63&gt;=0,FALSE))),"valor ou horas inválidos",IF(G63=0,"",F63/G63)))</f>
         <v/>
       </c>
       <c r="I63" s="31">
@@ -6731,7 +6731,7 @@
       <c r="F64" s="40" t="n"/>
       <c r="G64" s="23" t="n"/>
       <c r="H64" s="30">
-        <f>IF(OR(A64="",G64="",F64=""),"",IF(OR(NOT(ISNUMBER(F64)),NOT(ISNUMBER(G64))),"valor ou horas inválidos",IF(G64=0,"",F64/G64)))</f>
+        <f>IF(OR(A64="",G64="",F64=""),"",IF(OR(NOT(IF(ISNUMBER(F64),F64&gt;=0,FALSE)),NOT(IF(ISNUMBER(G64),G64&gt;=0,FALSE))),"valor ou horas inválidos",IF(G64=0,"",F64/G64)))</f>
         <v/>
       </c>
       <c r="I64" s="31">
@@ -6760,7 +6760,7 @@
       <c r="F65" s="40" t="n"/>
       <c r="G65" s="23" t="n"/>
       <c r="H65" s="30">
-        <f>IF(OR(A65="",G65="",F65=""),"",IF(OR(NOT(ISNUMBER(F65)),NOT(ISNUMBER(G65))),"valor ou horas inválidos",IF(G65=0,"",F65/G65)))</f>
+        <f>IF(OR(A65="",G65="",F65=""),"",IF(OR(NOT(IF(ISNUMBER(F65),F65&gt;=0,FALSE)),NOT(IF(ISNUMBER(G65),G65&gt;=0,FALSE))),"valor ou horas inválidos",IF(G65=0,"",F65/G65)))</f>
         <v/>
       </c>
       <c r="I65" s="31">
@@ -6789,7 +6789,7 @@
       <c r="F66" s="40" t="n"/>
       <c r="G66" s="23" t="n"/>
       <c r="H66" s="30">
-        <f>IF(OR(A66="",G66="",F66=""),"",IF(OR(NOT(ISNUMBER(F66)),NOT(ISNUMBER(G66))),"valor ou horas inválidos",IF(G66=0,"",F66/G66)))</f>
+        <f>IF(OR(A66="",G66="",F66=""),"",IF(OR(NOT(IF(ISNUMBER(F66),F66&gt;=0,FALSE)),NOT(IF(ISNUMBER(G66),G66&gt;=0,FALSE))),"valor ou horas inválidos",IF(G66=0,"",F66/G66)))</f>
         <v/>
       </c>
       <c r="I66" s="31">
@@ -6818,7 +6818,7 @@
       <c r="F67" s="40" t="n"/>
       <c r="G67" s="23" t="n"/>
       <c r="H67" s="30">
-        <f>IF(OR(A67="",G67="",F67=""),"",IF(OR(NOT(ISNUMBER(F67)),NOT(ISNUMBER(G67))),"valor ou horas inválidos",IF(G67=0,"",F67/G67)))</f>
+        <f>IF(OR(A67="",G67="",F67=""),"",IF(OR(NOT(IF(ISNUMBER(F67),F67&gt;=0,FALSE)),NOT(IF(ISNUMBER(G67),G67&gt;=0,FALSE))),"valor ou horas inválidos",IF(G67=0,"",F67/G67)))</f>
         <v/>
       </c>
       <c r="I67" s="31">
@@ -6847,7 +6847,7 @@
       <c r="F68" s="40" t="n"/>
       <c r="G68" s="23" t="n"/>
       <c r="H68" s="30">
-        <f>IF(OR(A68="",G68="",F68=""),"",IF(OR(NOT(ISNUMBER(F68)),NOT(ISNUMBER(G68))),"valor ou horas inválidos",IF(G68=0,"",F68/G68)))</f>
+        <f>IF(OR(A68="",G68="",F68=""),"",IF(OR(NOT(IF(ISNUMBER(F68),F68&gt;=0,FALSE)),NOT(IF(ISNUMBER(G68),G68&gt;=0,FALSE))),"valor ou horas inválidos",IF(G68=0,"",F68/G68)))</f>
         <v/>
       </c>
       <c r="I68" s="31">
@@ -6876,7 +6876,7 @@
       <c r="F69" s="40" t="n"/>
       <c r="G69" s="23" t="n"/>
       <c r="H69" s="30">
-        <f>IF(OR(A69="",G69="",F69=""),"",IF(OR(NOT(ISNUMBER(F69)),NOT(ISNUMBER(G69))),"valor ou horas inválidos",IF(G69=0,"",F69/G69)))</f>
+        <f>IF(OR(A69="",G69="",F69=""),"",IF(OR(NOT(IF(ISNUMBER(F69),F69&gt;=0,FALSE)),NOT(IF(ISNUMBER(G69),G69&gt;=0,FALSE))),"valor ou horas inválidos",IF(G69=0,"",F69/G69)))</f>
         <v/>
       </c>
       <c r="I69" s="31">
@@ -6905,7 +6905,7 @@
       <c r="F70" s="40" t="n"/>
       <c r="G70" s="23" t="n"/>
       <c r="H70" s="30">
-        <f>IF(OR(A70="",G70="",F70=""),"",IF(OR(NOT(ISNUMBER(F70)),NOT(ISNUMBER(G70))),"valor ou horas inválidos",IF(G70=0,"",F70/G70)))</f>
+        <f>IF(OR(A70="",G70="",F70=""),"",IF(OR(NOT(IF(ISNUMBER(F70),F70&gt;=0,FALSE)),NOT(IF(ISNUMBER(G70),G70&gt;=0,FALSE))),"valor ou horas inválidos",IF(G70=0,"",F70/G70)))</f>
         <v/>
       </c>
       <c r="I70" s="31">
@@ -6934,7 +6934,7 @@
       <c r="F71" s="40" t="n"/>
       <c r="G71" s="23" t="n"/>
       <c r="H71" s="30">
-        <f>IF(OR(A71="",G71="",F71=""),"",IF(OR(NOT(ISNUMBER(F71)),NOT(ISNUMBER(G71))),"valor ou horas inválidos",IF(G71=0,"",F71/G71)))</f>
+        <f>IF(OR(A71="",G71="",F71=""),"",IF(OR(NOT(IF(ISNUMBER(F71),F71&gt;=0,FALSE)),NOT(IF(ISNUMBER(G71),G71&gt;=0,FALSE))),"valor ou horas inválidos",IF(G71=0,"",F71/G71)))</f>
         <v/>
       </c>
       <c r="I71" s="31">
@@ -6963,7 +6963,7 @@
       <c r="F72" s="40" t="n"/>
       <c r="G72" s="23" t="n"/>
       <c r="H72" s="30">
-        <f>IF(OR(A72="",G72="",F72=""),"",IF(OR(NOT(ISNUMBER(F72)),NOT(ISNUMBER(G72))),"valor ou horas inválidos",IF(G72=0,"",F72/G72)))</f>
+        <f>IF(OR(A72="",G72="",F72=""),"",IF(OR(NOT(IF(ISNUMBER(F72),F72&gt;=0,FALSE)),NOT(IF(ISNUMBER(G72),G72&gt;=0,FALSE))),"valor ou horas inválidos",IF(G72=0,"",F72/G72)))</f>
         <v/>
       </c>
       <c r="I72" s="31">
@@ -6992,7 +6992,7 @@
       <c r="F73" s="40" t="n"/>
       <c r="G73" s="23" t="n"/>
       <c r="H73" s="30">
-        <f>IF(OR(A73="",G73="",F73=""),"",IF(OR(NOT(ISNUMBER(F73)),NOT(ISNUMBER(G73))),"valor ou horas inválidos",IF(G73=0,"",F73/G73)))</f>
+        <f>IF(OR(A73="",G73="",F73=""),"",IF(OR(NOT(IF(ISNUMBER(F73),F73&gt;=0,FALSE)),NOT(IF(ISNUMBER(G73),G73&gt;=0,FALSE))),"valor ou horas inválidos",IF(G73=0,"",F73/G73)))</f>
         <v/>
       </c>
       <c r="I73" s="31">
@@ -7021,7 +7021,7 @@
       <c r="F74" s="40" t="n"/>
       <c r="G74" s="23" t="n"/>
       <c r="H74" s="30">
-        <f>IF(OR(A74="",G74="",F74=""),"",IF(OR(NOT(ISNUMBER(F74)),NOT(ISNUMBER(G74))),"valor ou horas inválidos",IF(G74=0,"",F74/G74)))</f>
+        <f>IF(OR(A74="",G74="",F74=""),"",IF(OR(NOT(IF(ISNUMBER(F74),F74&gt;=0,FALSE)),NOT(IF(ISNUMBER(G74),G74&gt;=0,FALSE))),"valor ou horas inválidos",IF(G74=0,"",F74/G74)))</f>
         <v/>
       </c>
       <c r="I74" s="31">
@@ -7050,7 +7050,7 @@
       <c r="F75" s="40" t="n"/>
       <c r="G75" s="23" t="n"/>
       <c r="H75" s="30">
-        <f>IF(OR(A75="",G75="",F75=""),"",IF(OR(NOT(ISNUMBER(F75)),NOT(ISNUMBER(G75))),"valor ou horas inválidos",IF(G75=0,"",F75/G75)))</f>
+        <f>IF(OR(A75="",G75="",F75=""),"",IF(OR(NOT(IF(ISNUMBER(F75),F75&gt;=0,FALSE)),NOT(IF(ISNUMBER(G75),G75&gt;=0,FALSE))),"valor ou horas inválidos",IF(G75=0,"",F75/G75)))</f>
         <v/>
       </c>
       <c r="I75" s="31">
@@ -7079,7 +7079,7 @@
       <c r="F76" s="40" t="n"/>
       <c r="G76" s="23" t="n"/>
       <c r="H76" s="30">
-        <f>IF(OR(A76="",G76="",F76=""),"",IF(OR(NOT(ISNUMBER(F76)),NOT(ISNUMBER(G76))),"valor ou horas inválidos",IF(G76=0,"",F76/G76)))</f>
+        <f>IF(OR(A76="",G76="",F76=""),"",IF(OR(NOT(IF(ISNUMBER(F76),F76&gt;=0,FALSE)),NOT(IF(ISNUMBER(G76),G76&gt;=0,FALSE))),"valor ou horas inválidos",IF(G76=0,"",F76/G76)))</f>
         <v/>
       </c>
       <c r="I76" s="31">
@@ -7108,7 +7108,7 @@
       <c r="F77" s="40" t="n"/>
       <c r="G77" s="23" t="n"/>
       <c r="H77" s="30">
-        <f>IF(OR(A77="",G77="",F77=""),"",IF(OR(NOT(ISNUMBER(F77)),NOT(ISNUMBER(G77))),"valor ou horas inválidos",IF(G77=0,"",F77/G77)))</f>
+        <f>IF(OR(A77="",G77="",F77=""),"",IF(OR(NOT(IF(ISNUMBER(F77),F77&gt;=0,FALSE)),NOT(IF(ISNUMBER(G77),G77&gt;=0,FALSE))),"valor ou horas inválidos",IF(G77=0,"",F77/G77)))</f>
         <v/>
       </c>
       <c r="I77" s="31">
@@ -7137,7 +7137,7 @@
       <c r="F78" s="40" t="n"/>
       <c r="G78" s="23" t="n"/>
       <c r="H78" s="30">
-        <f>IF(OR(A78="",G78="",F78=""),"",IF(OR(NOT(ISNUMBER(F78)),NOT(ISNUMBER(G78))),"valor ou horas inválidos",IF(G78=0,"",F78/G78)))</f>
+        <f>IF(OR(A78="",G78="",F78=""),"",IF(OR(NOT(IF(ISNUMBER(F78),F78&gt;=0,FALSE)),NOT(IF(ISNUMBER(G78),G78&gt;=0,FALSE))),"valor ou horas inválidos",IF(G78=0,"",F78/G78)))</f>
         <v/>
       </c>
       <c r="I78" s="31">
@@ -7166,7 +7166,7 @@
       <c r="F79" s="40" t="n"/>
       <c r="G79" s="23" t="n"/>
       <c r="H79" s="30">
-        <f>IF(OR(A79="",G79="",F79=""),"",IF(OR(NOT(ISNUMBER(F79)),NOT(ISNUMBER(G79))),"valor ou horas inválidos",IF(G79=0,"",F79/G79)))</f>
+        <f>IF(OR(A79="",G79="",F79=""),"",IF(OR(NOT(IF(ISNUMBER(F79),F79&gt;=0,FALSE)),NOT(IF(ISNUMBER(G79),G79&gt;=0,FALSE))),"valor ou horas inválidos",IF(G79=0,"",F79/G79)))</f>
         <v/>
       </c>
       <c r="I79" s="31">
@@ -7195,7 +7195,7 @@
       <c r="F80" s="40" t="n"/>
       <c r="G80" s="23" t="n"/>
       <c r="H80" s="30">
-        <f>IF(OR(A80="",G80="",F80=""),"",IF(OR(NOT(ISNUMBER(F80)),NOT(ISNUMBER(G80))),"valor ou horas inválidos",IF(G80=0,"",F80/G80)))</f>
+        <f>IF(OR(A80="",G80="",F80=""),"",IF(OR(NOT(IF(ISNUMBER(F80),F80&gt;=0,FALSE)),NOT(IF(ISNUMBER(G80),G80&gt;=0,FALSE))),"valor ou horas inválidos",IF(G80=0,"",F80/G80)))</f>
         <v/>
       </c>
       <c r="I80" s="31">
@@ -7224,7 +7224,7 @@
       <c r="F81" s="40" t="n"/>
       <c r="G81" s="23" t="n"/>
       <c r="H81" s="30">
-        <f>IF(OR(A81="",G81="",F81=""),"",IF(OR(NOT(ISNUMBER(F81)),NOT(ISNUMBER(G81))),"valor ou horas inválidos",IF(G81=0,"",F81/G81)))</f>
+        <f>IF(OR(A81="",G81="",F81=""),"",IF(OR(NOT(IF(ISNUMBER(F81),F81&gt;=0,FALSE)),NOT(IF(ISNUMBER(G81),G81&gt;=0,FALSE))),"valor ou horas inválidos",IF(G81=0,"",F81/G81)))</f>
         <v/>
       </c>
       <c r="I81" s="31">
@@ -7253,7 +7253,7 @@
       <c r="F82" s="40" t="n"/>
       <c r="G82" s="23" t="n"/>
       <c r="H82" s="30">
-        <f>IF(OR(A82="",G82="",F82=""),"",IF(OR(NOT(ISNUMBER(F82)),NOT(ISNUMBER(G82))),"valor ou horas inválidos",IF(G82=0,"",F82/G82)))</f>
+        <f>IF(OR(A82="",G82="",F82=""),"",IF(OR(NOT(IF(ISNUMBER(F82),F82&gt;=0,FALSE)),NOT(IF(ISNUMBER(G82),G82&gt;=0,FALSE))),"valor ou horas inválidos",IF(G82=0,"",F82/G82)))</f>
         <v/>
       </c>
       <c r="I82" s="31">
@@ -7282,7 +7282,7 @@
       <c r="F83" s="40" t="n"/>
       <c r="G83" s="23" t="n"/>
       <c r="H83" s="30">
-        <f>IF(OR(A83="",G83="",F83=""),"",IF(OR(NOT(ISNUMBER(F83)),NOT(ISNUMBER(G83))),"valor ou horas inválidos",IF(G83=0,"",F83/G83)))</f>
+        <f>IF(OR(A83="",G83="",F83=""),"",IF(OR(NOT(IF(ISNUMBER(F83),F83&gt;=0,FALSE)),NOT(IF(ISNUMBER(G83),G83&gt;=0,FALSE))),"valor ou horas inválidos",IF(G83=0,"",F83/G83)))</f>
         <v/>
       </c>
       <c r="I83" s="31">
@@ -7311,7 +7311,7 @@
       <c r="F84" s="40" t="n"/>
       <c r="G84" s="23" t="n"/>
       <c r="H84" s="30">
-        <f>IF(OR(A84="",G84="",F84=""),"",IF(OR(NOT(ISNUMBER(F84)),NOT(ISNUMBER(G84))),"valor ou horas inválidos",IF(G84=0,"",F84/G84)))</f>
+        <f>IF(OR(A84="",G84="",F84=""),"",IF(OR(NOT(IF(ISNUMBER(F84),F84&gt;=0,FALSE)),NOT(IF(ISNUMBER(G84),G84&gt;=0,FALSE))),"valor ou horas inválidos",IF(G84=0,"",F84/G84)))</f>
         <v/>
       </c>
       <c r="I84" s="31">
@@ -7340,7 +7340,7 @@
       <c r="F85" s="40" t="n"/>
       <c r="G85" s="23" t="n"/>
       <c r="H85" s="30">
-        <f>IF(OR(A85="",G85="",F85=""),"",IF(OR(NOT(ISNUMBER(F85)),NOT(ISNUMBER(G85))),"valor ou horas inválidos",IF(G85=0,"",F85/G85)))</f>
+        <f>IF(OR(A85="",G85="",F85=""),"",IF(OR(NOT(IF(ISNUMBER(F85),F85&gt;=0,FALSE)),NOT(IF(ISNUMBER(G85),G85&gt;=0,FALSE))),"valor ou horas inválidos",IF(G85=0,"",F85/G85)))</f>
         <v/>
       </c>
       <c r="I85" s="31">
@@ -7369,7 +7369,7 @@
       <c r="F86" s="40" t="n"/>
       <c r="G86" s="23" t="n"/>
       <c r="H86" s="30">
-        <f>IF(OR(A86="",G86="",F86=""),"",IF(OR(NOT(ISNUMBER(F86)),NOT(ISNUMBER(G86))),"valor ou horas inválidos",IF(G86=0,"",F86/G86)))</f>
+        <f>IF(OR(A86="",G86="",F86=""),"",IF(OR(NOT(IF(ISNUMBER(F86),F86&gt;=0,FALSE)),NOT(IF(ISNUMBER(G86),G86&gt;=0,FALSE))),"valor ou horas inválidos",IF(G86=0,"",F86/G86)))</f>
         <v/>
       </c>
       <c r="I86" s="31">
@@ -7398,7 +7398,7 @@
       <c r="F87" s="40" t="n"/>
       <c r="G87" s="23" t="n"/>
       <c r="H87" s="30">
-        <f>IF(OR(A87="",G87="",F87=""),"",IF(OR(NOT(ISNUMBER(F87)),NOT(ISNUMBER(G87))),"valor ou horas inválidos",IF(G87=0,"",F87/G87)))</f>
+        <f>IF(OR(A87="",G87="",F87=""),"",IF(OR(NOT(IF(ISNUMBER(F87),F87&gt;=0,FALSE)),NOT(IF(ISNUMBER(G87),G87&gt;=0,FALSE))),"valor ou horas inválidos",IF(G87=0,"",F87/G87)))</f>
         <v/>
       </c>
       <c r="I87" s="31">
@@ -7427,7 +7427,7 @@
       <c r="F88" s="40" t="n"/>
       <c r="G88" s="23" t="n"/>
       <c r="H88" s="30">
-        <f>IF(OR(A88="",G88="",F88=""),"",IF(OR(NOT(ISNUMBER(F88)),NOT(ISNUMBER(G88))),"valor ou horas inválidos",IF(G88=0,"",F88/G88)))</f>
+        <f>IF(OR(A88="",G88="",F88=""),"",IF(OR(NOT(IF(ISNUMBER(F88),F88&gt;=0,FALSE)),NOT(IF(ISNUMBER(G88),G88&gt;=0,FALSE))),"valor ou horas inválidos",IF(G88=0,"",F88/G88)))</f>
         <v/>
       </c>
       <c r="I88" s="31">
@@ -7456,7 +7456,7 @@
       <c r="F89" s="40" t="n"/>
       <c r="G89" s="23" t="n"/>
       <c r="H89" s="30">
-        <f>IF(OR(A89="",G89="",F89=""),"",IF(OR(NOT(ISNUMBER(F89)),NOT(ISNUMBER(G89))),"valor ou horas inválidos",IF(G89=0,"",F89/G89)))</f>
+        <f>IF(OR(A89="",G89="",F89=""),"",IF(OR(NOT(IF(ISNUMBER(F89),F89&gt;=0,FALSE)),NOT(IF(ISNUMBER(G89),G89&gt;=0,FALSE))),"valor ou horas inválidos",IF(G89=0,"",F89/G89)))</f>
         <v/>
       </c>
       <c r="I89" s="31">
@@ -7485,7 +7485,7 @@
       <c r="F90" s="40" t="n"/>
       <c r="G90" s="23" t="n"/>
       <c r="H90" s="30">
-        <f>IF(OR(A90="",G90="",F90=""),"",IF(OR(NOT(ISNUMBER(F90)),NOT(ISNUMBER(G90))),"valor ou horas inválidos",IF(G90=0,"",F90/G90)))</f>
+        <f>IF(OR(A90="",G90="",F90=""),"",IF(OR(NOT(IF(ISNUMBER(F90),F90&gt;=0,FALSE)),NOT(IF(ISNUMBER(G90),G90&gt;=0,FALSE))),"valor ou horas inválidos",IF(G90=0,"",F90/G90)))</f>
         <v/>
       </c>
       <c r="I90" s="31">
@@ -7514,7 +7514,7 @@
       <c r="F91" s="40" t="n"/>
       <c r="G91" s="23" t="n"/>
       <c r="H91" s="30">
-        <f>IF(OR(A91="",G91="",F91=""),"",IF(OR(NOT(ISNUMBER(F91)),NOT(ISNUMBER(G91))),"valor ou horas inválidos",IF(G91=0,"",F91/G91)))</f>
+        <f>IF(OR(A91="",G91="",F91=""),"",IF(OR(NOT(IF(ISNUMBER(F91),F91&gt;=0,FALSE)),NOT(IF(ISNUMBER(G91),G91&gt;=0,FALSE))),"valor ou horas inválidos",IF(G91=0,"",F91/G91)))</f>
         <v/>
       </c>
       <c r="I91" s="31">
@@ -7543,7 +7543,7 @@
       <c r="F92" s="40" t="n"/>
       <c r="G92" s="23" t="n"/>
       <c r="H92" s="30">
-        <f>IF(OR(A92="",G92="",F92=""),"",IF(OR(NOT(ISNUMBER(F92)),NOT(ISNUMBER(G92))),"valor ou horas inválidos",IF(G92=0,"",F92/G92)))</f>
+        <f>IF(OR(A92="",G92="",F92=""),"",IF(OR(NOT(IF(ISNUMBER(F92),F92&gt;=0,FALSE)),NOT(IF(ISNUMBER(G92),G92&gt;=0,FALSE))),"valor ou horas inválidos",IF(G92=0,"",F92/G92)))</f>
         <v/>
       </c>
       <c r="I92" s="31">
@@ -7572,7 +7572,7 @@
       <c r="F93" s="40" t="n"/>
       <c r="G93" s="23" t="n"/>
       <c r="H93" s="30">
-        <f>IF(OR(A93="",G93="",F93=""),"",IF(OR(NOT(ISNUMBER(F93)),NOT(ISNUMBER(G93))),"valor ou horas inválidos",IF(G93=0,"",F93/G93)))</f>
+        <f>IF(OR(A93="",G93="",F93=""),"",IF(OR(NOT(IF(ISNUMBER(F93),F93&gt;=0,FALSE)),NOT(IF(ISNUMBER(G93),G93&gt;=0,FALSE))),"valor ou horas inválidos",IF(G93=0,"",F93/G93)))</f>
         <v/>
       </c>
       <c r="I93" s="31">
@@ -7601,7 +7601,7 @@
       <c r="F94" s="40" t="n"/>
       <c r="G94" s="23" t="n"/>
       <c r="H94" s="30">
-        <f>IF(OR(A94="",G94="",F94=""),"",IF(OR(NOT(ISNUMBER(F94)),NOT(ISNUMBER(G94))),"valor ou horas inválidos",IF(G94=0,"",F94/G94)))</f>
+        <f>IF(OR(A94="",G94="",F94=""),"",IF(OR(NOT(IF(ISNUMBER(F94),F94&gt;=0,FALSE)),NOT(IF(ISNUMBER(G94),G94&gt;=0,FALSE))),"valor ou horas inválidos",IF(G94=0,"",F94/G94)))</f>
         <v/>
       </c>
       <c r="I94" s="31">
@@ -7630,7 +7630,7 @@
       <c r="F95" s="40" t="n"/>
       <c r="G95" s="23" t="n"/>
       <c r="H95" s="30">
-        <f>IF(OR(A95="",G95="",F95=""),"",IF(OR(NOT(ISNUMBER(F95)),NOT(ISNUMBER(G95))),"valor ou horas inválidos",IF(G95=0,"",F95/G95)))</f>
+        <f>IF(OR(A95="",G95="",F95=""),"",IF(OR(NOT(IF(ISNUMBER(F95),F95&gt;=0,FALSE)),NOT(IF(ISNUMBER(G95),G95&gt;=0,FALSE))),"valor ou horas inválidos",IF(G95=0,"",F95/G95)))</f>
         <v/>
       </c>
       <c r="I95" s="31">
@@ -7659,7 +7659,7 @@
       <c r="F96" s="40" t="n"/>
       <c r="G96" s="23" t="n"/>
       <c r="H96" s="30">
-        <f>IF(OR(A96="",G96="",F96=""),"",IF(OR(NOT(ISNUMBER(F96)),NOT(ISNUMBER(G96))),"valor ou horas inválidos",IF(G96=0,"",F96/G96)))</f>
+        <f>IF(OR(A96="",G96="",F96=""),"",IF(OR(NOT(IF(ISNUMBER(F96),F96&gt;=0,FALSE)),NOT(IF(ISNUMBER(G96),G96&gt;=0,FALSE))),"valor ou horas inválidos",IF(G96=0,"",F96/G96)))</f>
         <v/>
       </c>
       <c r="I96" s="31">
@@ -7688,7 +7688,7 @@
       <c r="F97" s="40" t="n"/>
       <c r="G97" s="23" t="n"/>
       <c r="H97" s="30">
-        <f>IF(OR(A97="",G97="",F97=""),"",IF(OR(NOT(ISNUMBER(F97)),NOT(ISNUMBER(G97))),"valor ou horas inválidos",IF(G97=0,"",F97/G97)))</f>
+        <f>IF(OR(A97="",G97="",F97=""),"",IF(OR(NOT(IF(ISNUMBER(F97),F97&gt;=0,FALSE)),NOT(IF(ISNUMBER(G97),G97&gt;=0,FALSE))),"valor ou horas inválidos",IF(G97=0,"",F97/G97)))</f>
         <v/>
       </c>
       <c r="I97" s="31">
@@ -7717,7 +7717,7 @@
       <c r="F98" s="40" t="n"/>
       <c r="G98" s="23" t="n"/>
       <c r="H98" s="30">
-        <f>IF(OR(A98="",G98="",F98=""),"",IF(OR(NOT(ISNUMBER(F98)),NOT(ISNUMBER(G98))),"valor ou horas inválidos",IF(G98=0,"",F98/G98)))</f>
+        <f>IF(OR(A98="",G98="",F98=""),"",IF(OR(NOT(IF(ISNUMBER(F98),F98&gt;=0,FALSE)),NOT(IF(ISNUMBER(G98),G98&gt;=0,FALSE))),"valor ou horas inválidos",IF(G98=0,"",F98/G98)))</f>
         <v/>
       </c>
       <c r="I98" s="31">
@@ -7746,7 +7746,7 @@
       <c r="F99" s="40" t="n"/>
       <c r="G99" s="23" t="n"/>
       <c r="H99" s="30">
-        <f>IF(OR(A99="",G99="",F99=""),"",IF(OR(NOT(ISNUMBER(F99)),NOT(ISNUMBER(G99))),"valor ou horas inválidos",IF(G99=0,"",F99/G99)))</f>
+        <f>IF(OR(A99="",G99="",F99=""),"",IF(OR(NOT(IF(ISNUMBER(F99),F99&gt;=0,FALSE)),NOT(IF(ISNUMBER(G99),G99&gt;=0,FALSE))),"valor ou horas inválidos",IF(G99=0,"",F99/G99)))</f>
         <v/>
       </c>
       <c r="I99" s="31">
@@ -7775,7 +7775,7 @@
       <c r="F100" s="40" t="n"/>
       <c r="G100" s="23" t="n"/>
       <c r="H100" s="30">
-        <f>IF(OR(A100="",G100="",F100=""),"",IF(OR(NOT(ISNUMBER(F100)),NOT(ISNUMBER(G100))),"valor ou horas inválidos",IF(G100=0,"",F100/G100)))</f>
+        <f>IF(OR(A100="",G100="",F100=""),"",IF(OR(NOT(IF(ISNUMBER(F100),F100&gt;=0,FALSE)),NOT(IF(ISNUMBER(G100),G100&gt;=0,FALSE))),"valor ou horas inválidos",IF(G100=0,"",F100/G100)))</f>
         <v/>
       </c>
       <c r="I100" s="31">
@@ -7804,7 +7804,7 @@
       <c r="F101" s="40" t="n"/>
       <c r="G101" s="23" t="n"/>
       <c r="H101" s="30">
-        <f>IF(OR(A101="",G101="",F101=""),"",IF(OR(NOT(ISNUMBER(F101)),NOT(ISNUMBER(G101))),"valor ou horas inválidos",IF(G101=0,"",F101/G101)))</f>
+        <f>IF(OR(A101="",G101="",F101=""),"",IF(OR(NOT(IF(ISNUMBER(F101),F101&gt;=0,FALSE)),NOT(IF(ISNUMBER(G101),G101&gt;=0,FALSE))),"valor ou horas inválidos",IF(G101=0,"",F101/G101)))</f>
         <v/>
       </c>
       <c r="I101" s="31">
@@ -7833,7 +7833,7 @@
       <c r="F102" s="40" t="n"/>
       <c r="G102" s="23" t="n"/>
       <c r="H102" s="30">
-        <f>IF(OR(A102="",G102="",F102=""),"",IF(OR(NOT(ISNUMBER(F102)),NOT(ISNUMBER(G102))),"valor ou horas inválidos",IF(G102=0,"",F102/G102)))</f>
+        <f>IF(OR(A102="",G102="",F102=""),"",IF(OR(NOT(IF(ISNUMBER(F102),F102&gt;=0,FALSE)),NOT(IF(ISNUMBER(G102),G102&gt;=0,FALSE))),"valor ou horas inválidos",IF(G102=0,"",F102/G102)))</f>
         <v/>
       </c>
       <c r="I102" s="31">
@@ -7862,7 +7862,7 @@
       <c r="F103" s="40" t="n"/>
       <c r="G103" s="23" t="n"/>
       <c r="H103" s="30">
-        <f>IF(OR(A103="",G103="",F103=""),"",IF(OR(NOT(ISNUMBER(F103)),NOT(ISNUMBER(G103))),"valor ou horas inválidos",IF(G103=0,"",F103/G103)))</f>
+        <f>IF(OR(A103="",G103="",F103=""),"",IF(OR(NOT(IF(ISNUMBER(F103),F103&gt;=0,FALSE)),NOT(IF(ISNUMBER(G103),G103&gt;=0,FALSE))),"valor ou horas inválidos",IF(G103=0,"",F103/G103)))</f>
         <v/>
       </c>
       <c r="I103" s="31">
@@ -7891,7 +7891,7 @@
       <c r="F104" s="40" t="n"/>
       <c r="G104" s="23" t="n"/>
       <c r="H104" s="30">
-        <f>IF(OR(A104="",G104="",F104=""),"",IF(OR(NOT(ISNUMBER(F104)),NOT(ISNUMBER(G104))),"valor ou horas inválidos",IF(G104=0,"",F104/G104)))</f>
+        <f>IF(OR(A104="",G104="",F104=""),"",IF(OR(NOT(IF(ISNUMBER(F104),F104&gt;=0,FALSE)),NOT(IF(ISNUMBER(G104),G104&gt;=0,FALSE))),"valor ou horas inválidos",IF(G104=0,"",F104/G104)))</f>
         <v/>
       </c>
       <c r="I104" s="31">
@@ -7920,7 +7920,7 @@
       <c r="F105" s="40" t="n"/>
       <c r="G105" s="23" t="n"/>
       <c r="H105" s="30">
-        <f>IF(OR(A105="",G105="",F105=""),"",IF(OR(NOT(ISNUMBER(F105)),NOT(ISNUMBER(G105))),"valor ou horas inválidos",IF(G105=0,"",F105/G105)))</f>
+        <f>IF(OR(A105="",G105="",F105=""),"",IF(OR(NOT(IF(ISNUMBER(F105),F105&gt;=0,FALSE)),NOT(IF(ISNUMBER(G105),G105&gt;=0,FALSE))),"valor ou horas inválidos",IF(G105=0,"",F105/G105)))</f>
         <v/>
       </c>
       <c r="I105" s="31">
@@ -7949,7 +7949,7 @@
       <c r="F106" s="40" t="n"/>
       <c r="G106" s="23" t="n"/>
       <c r="H106" s="30">
-        <f>IF(OR(A106="",G106="",F106=""),"",IF(OR(NOT(ISNUMBER(F106)),NOT(ISNUMBER(G106))),"valor ou horas inválidos",IF(G106=0,"",F106/G106)))</f>
+        <f>IF(OR(A106="",G106="",F106=""),"",IF(OR(NOT(IF(ISNUMBER(F106),F106&gt;=0,FALSE)),NOT(IF(ISNUMBER(G106),G106&gt;=0,FALSE))),"valor ou horas inválidos",IF(G106=0,"",F106/G106)))</f>
         <v/>
       </c>
       <c r="I106" s="31">
@@ -7978,7 +7978,7 @@
       <c r="F107" s="40" t="n"/>
       <c r="G107" s="23" t="n"/>
       <c r="H107" s="30">
-        <f>IF(OR(A107="",G107="",F107=""),"",IF(OR(NOT(ISNUMBER(F107)),NOT(ISNUMBER(G107))),"valor ou horas inválidos",IF(G107=0,"",F107/G107)))</f>
+        <f>IF(OR(A107="",G107="",F107=""),"",IF(OR(NOT(IF(ISNUMBER(F107),F107&gt;=0,FALSE)),NOT(IF(ISNUMBER(G107),G107&gt;=0,FALSE))),"valor ou horas inválidos",IF(G107=0,"",F107/G107)))</f>
         <v/>
       </c>
       <c r="I107" s="31">
@@ -8007,7 +8007,7 @@
       <c r="F108" s="40" t="n"/>
       <c r="G108" s="23" t="n"/>
       <c r="H108" s="30">
-        <f>IF(OR(A108="",G108="",F108=""),"",IF(OR(NOT(ISNUMBER(F108)),NOT(ISNUMBER(G108))),"valor ou horas inválidos",IF(G108=0,"",F108/G108)))</f>
+        <f>IF(OR(A108="",G108="",F108=""),"",IF(OR(NOT(IF(ISNUMBER(F108),F108&gt;=0,FALSE)),NOT(IF(ISNUMBER(G108),G108&gt;=0,FALSE))),"valor ou horas inválidos",IF(G108=0,"",F108/G108)))</f>
         <v/>
       </c>
       <c r="I108" s="31">
@@ -8036,7 +8036,7 @@
       <c r="F109" s="40" t="n"/>
       <c r="G109" s="23" t="n"/>
       <c r="H109" s="30">
-        <f>IF(OR(A109="",G109="",F109=""),"",IF(OR(NOT(ISNUMBER(F109)),NOT(ISNUMBER(G109))),"valor ou horas inválidos",IF(G109=0,"",F109/G109)))</f>
+        <f>IF(OR(A109="",G109="",F109=""),"",IF(OR(NOT(IF(ISNUMBER(F109),F109&gt;=0,FALSE)),NOT(IF(ISNUMBER(G109),G109&gt;=0,FALSE))),"valor ou horas inválidos",IF(G109=0,"",F109/G109)))</f>
         <v/>
       </c>
       <c r="I109" s="31">
@@ -8065,7 +8065,7 @@
       <c r="F110" s="40" t="n"/>
       <c r="G110" s="23" t="n"/>
       <c r="H110" s="30">
-        <f>IF(OR(A110="",G110="",F110=""),"",IF(OR(NOT(ISNUMBER(F110)),NOT(ISNUMBER(G110))),"valor ou horas inválidos",IF(G110=0,"",F110/G110)))</f>
+        <f>IF(OR(A110="",G110="",F110=""),"",IF(OR(NOT(IF(ISNUMBER(F110),F110&gt;=0,FALSE)),NOT(IF(ISNUMBER(G110),G110&gt;=0,FALSE))),"valor ou horas inválidos",IF(G110=0,"",F110/G110)))</f>
         <v/>
       </c>
       <c r="I110" s="31">
@@ -8094,7 +8094,7 @@
       <c r="F111" s="40" t="n"/>
       <c r="G111" s="23" t="n"/>
       <c r="H111" s="30">
-        <f>IF(OR(A111="",G111="",F111=""),"",IF(OR(NOT(ISNUMBER(F111)),NOT(ISNUMBER(G111))),"valor ou horas inválidos",IF(G111=0,"",F111/G111)))</f>
+        <f>IF(OR(A111="",G111="",F111=""),"",IF(OR(NOT(IF(ISNUMBER(F111),F111&gt;=0,FALSE)),NOT(IF(ISNUMBER(G111),G111&gt;=0,FALSE))),"valor ou horas inválidos",IF(G111=0,"",F111/G111)))</f>
         <v/>
       </c>
       <c r="I111" s="31">
@@ -8123,7 +8123,7 @@
       <c r="F112" s="40" t="n"/>
       <c r="G112" s="23" t="n"/>
       <c r="H112" s="30">
-        <f>IF(OR(A112="",G112="",F112=""),"",IF(OR(NOT(ISNUMBER(F112)),NOT(ISNUMBER(G112))),"valor ou horas inválidos",IF(G112=0,"",F112/G112)))</f>
+        <f>IF(OR(A112="",G112="",F112=""),"",IF(OR(NOT(IF(ISNUMBER(F112),F112&gt;=0,FALSE)),NOT(IF(ISNUMBER(G112),G112&gt;=0,FALSE))),"valor ou horas inválidos",IF(G112=0,"",F112/G112)))</f>
         <v/>
       </c>
       <c r="I112" s="31">
@@ -8152,7 +8152,7 @@
       <c r="F113" s="40" t="n"/>
       <c r="G113" s="23" t="n"/>
       <c r="H113" s="30">
-        <f>IF(OR(A113="",G113="",F113=""),"",IF(OR(NOT(ISNUMBER(F113)),NOT(ISNUMBER(G113))),"valor ou horas inválidos",IF(G113=0,"",F113/G113)))</f>
+        <f>IF(OR(A113="",G113="",F113=""),"",IF(OR(NOT(IF(ISNUMBER(F113),F113&gt;=0,FALSE)),NOT(IF(ISNUMBER(G113),G113&gt;=0,FALSE))),"valor ou horas inválidos",IF(G113=0,"",F113/G113)))</f>
         <v/>
       </c>
       <c r="I113" s="31">
@@ -8181,7 +8181,7 @@
       <c r="F114" s="40" t="n"/>
       <c r="G114" s="23" t="n"/>
       <c r="H114" s="30">
-        <f>IF(OR(A114="",G114="",F114=""),"",IF(OR(NOT(ISNUMBER(F114)),NOT(ISNUMBER(G114))),"valor ou horas inválidos",IF(G114=0,"",F114/G114)))</f>
+        <f>IF(OR(A114="",G114="",F114=""),"",IF(OR(NOT(IF(ISNUMBER(F114),F114&gt;=0,FALSE)),NOT(IF(ISNUMBER(G114),G114&gt;=0,FALSE))),"valor ou horas inválidos",IF(G114=0,"",F114/G114)))</f>
         <v/>
       </c>
       <c r="I114" s="31">
@@ -8210,7 +8210,7 @@
       <c r="F115" s="40" t="n"/>
       <c r="G115" s="23" t="n"/>
       <c r="H115" s="30">
-        <f>IF(OR(A115="",G115="",F115=""),"",IF(OR(NOT(ISNUMBER(F115)),NOT(ISNUMBER(G115))),"valor ou horas inválidos",IF(G115=0,"",F115/G115)))</f>
+        <f>IF(OR(A115="",G115="",F115=""),"",IF(OR(NOT(IF(ISNUMBER(F115),F115&gt;=0,FALSE)),NOT(IF(ISNUMBER(G115),G115&gt;=0,FALSE))),"valor ou horas inválidos",IF(G115=0,"",F115/G115)))</f>
         <v/>
       </c>
       <c r="I115" s="31">
@@ -8239,7 +8239,7 @@
       <c r="F116" s="40" t="n"/>
       <c r="G116" s="23" t="n"/>
       <c r="H116" s="30">
-        <f>IF(OR(A116="",G116="",F116=""),"",IF(OR(NOT(ISNUMBER(F116)),NOT(ISNUMBER(G116))),"valor ou horas inválidos",IF(G116=0,"",F116/G116)))</f>
+        <f>IF(OR(A116="",G116="",F116=""),"",IF(OR(NOT(IF(ISNUMBER(F116),F116&gt;=0,FALSE)),NOT(IF(ISNUMBER(G116),G116&gt;=0,FALSE))),"valor ou horas inválidos",IF(G116=0,"",F116/G116)))</f>
         <v/>
       </c>
       <c r="I116" s="31">
@@ -8268,7 +8268,7 @@
       <c r="F117" s="40" t="n"/>
       <c r="G117" s="23" t="n"/>
       <c r="H117" s="30">
-        <f>IF(OR(A117="",G117="",F117=""),"",IF(OR(NOT(ISNUMBER(F117)),NOT(ISNUMBER(G117))),"valor ou horas inválidos",IF(G117=0,"",F117/G117)))</f>
+        <f>IF(OR(A117="",G117="",F117=""),"",IF(OR(NOT(IF(ISNUMBER(F117),F117&gt;=0,FALSE)),NOT(IF(ISNUMBER(G117),G117&gt;=0,FALSE))),"valor ou horas inválidos",IF(G117=0,"",F117/G117)))</f>
         <v/>
       </c>
       <c r="I117" s="31">
@@ -8297,7 +8297,7 @@
       <c r="F118" s="40" t="n"/>
       <c r="G118" s="23" t="n"/>
       <c r="H118" s="30">
-        <f>IF(OR(A118="",G118="",F118=""),"",IF(OR(NOT(ISNUMBER(F118)),NOT(ISNUMBER(G118))),"valor ou horas inválidos",IF(G118=0,"",F118/G118)))</f>
+        <f>IF(OR(A118="",G118="",F118=""),"",IF(OR(NOT(IF(ISNUMBER(F118),F118&gt;=0,FALSE)),NOT(IF(ISNUMBER(G118),G118&gt;=0,FALSE))),"valor ou horas inválidos",IF(G118=0,"",F118/G118)))</f>
         <v/>
       </c>
       <c r="I118" s="31">
@@ -8326,7 +8326,7 @@
       <c r="F119" s="40" t="n"/>
       <c r="G119" s="23" t="n"/>
       <c r="H119" s="30">
-        <f>IF(OR(A119="",G119="",F119=""),"",IF(OR(NOT(ISNUMBER(F119)),NOT(ISNUMBER(G119))),"valor ou horas inválidos",IF(G119=0,"",F119/G119)))</f>
+        <f>IF(OR(A119="",G119="",F119=""),"",IF(OR(NOT(IF(ISNUMBER(F119),F119&gt;=0,FALSE)),NOT(IF(ISNUMBER(G119),G119&gt;=0,FALSE))),"valor ou horas inválidos",IF(G119=0,"",F119/G119)))</f>
         <v/>
       </c>
       <c r="I119" s="31">
@@ -8355,7 +8355,7 @@
       <c r="F120" s="40" t="n"/>
       <c r="G120" s="23" t="n"/>
       <c r="H120" s="30">
-        <f>IF(OR(A120="",G120="",F120=""),"",IF(OR(NOT(ISNUMBER(F120)),NOT(ISNUMBER(G120))),"valor ou horas inválidos",IF(G120=0,"",F120/G120)))</f>
+        <f>IF(OR(A120="",G120="",F120=""),"",IF(OR(NOT(IF(ISNUMBER(F120),F120&gt;=0,FALSE)),NOT(IF(ISNUMBER(G120),G120&gt;=0,FALSE))),"valor ou horas inválidos",IF(G120=0,"",F120/G120)))</f>
         <v/>
       </c>
       <c r="I120" s="31">
@@ -8384,7 +8384,7 @@
       <c r="F121" s="40" t="n"/>
       <c r="G121" s="23" t="n"/>
       <c r="H121" s="30">
-        <f>IF(OR(A121="",G121="",F121=""),"",IF(OR(NOT(ISNUMBER(F121)),NOT(ISNUMBER(G121))),"valor ou horas inválidos",IF(G121=0,"",F121/G121)))</f>
+        <f>IF(OR(A121="",G121="",F121=""),"",IF(OR(NOT(IF(ISNUMBER(F121),F121&gt;=0,FALSE)),NOT(IF(ISNUMBER(G121),G121&gt;=0,FALSE))),"valor ou horas inválidos",IF(G121=0,"",F121/G121)))</f>
         <v/>
       </c>
       <c r="I121" s="31">
@@ -8413,7 +8413,7 @@
       <c r="F122" s="40" t="n"/>
       <c r="G122" s="23" t="n"/>
       <c r="H122" s="30">
-        <f>IF(OR(A122="",G122="",F122=""),"",IF(OR(NOT(ISNUMBER(F122)),NOT(ISNUMBER(G122))),"valor ou horas inválidos",IF(G122=0,"",F122/G122)))</f>
+        <f>IF(OR(A122="",G122="",F122=""),"",IF(OR(NOT(IF(ISNUMBER(F122),F122&gt;=0,FALSE)),NOT(IF(ISNUMBER(G122),G122&gt;=0,FALSE))),"valor ou horas inválidos",IF(G122=0,"",F122/G122)))</f>
         <v/>
       </c>
       <c r="I122" s="31">
@@ -8442,7 +8442,7 @@
       <c r="F123" s="40" t="n"/>
       <c r="G123" s="23" t="n"/>
       <c r="H123" s="30">
-        <f>IF(OR(A123="",G123="",F123=""),"",IF(OR(NOT(ISNUMBER(F123)),NOT(ISNUMBER(G123))),"valor ou horas inválidos",IF(G123=0,"",F123/G123)))</f>
+        <f>IF(OR(A123="",G123="",F123=""),"",IF(OR(NOT(IF(ISNUMBER(F123),F123&gt;=0,FALSE)),NOT(IF(ISNUMBER(G123),G123&gt;=0,FALSE))),"valor ou horas inválidos",IF(G123=0,"",F123/G123)))</f>
         <v/>
       </c>
       <c r="I123" s="31">
@@ -8471,7 +8471,7 @@
       <c r="F124" s="40" t="n"/>
       <c r="G124" s="23" t="n"/>
       <c r="H124" s="30">
-        <f>IF(OR(A124="",G124="",F124=""),"",IF(OR(NOT(ISNUMBER(F124)),NOT(ISNUMBER(G124))),"valor ou horas inválidos",IF(G124=0,"",F124/G124)))</f>
+        <f>IF(OR(A124="",G124="",F124=""),"",IF(OR(NOT(IF(ISNUMBER(F124),F124&gt;=0,FALSE)),NOT(IF(ISNUMBER(G124),G124&gt;=0,FALSE))),"valor ou horas inválidos",IF(G124=0,"",F124/G124)))</f>
         <v/>
       </c>
       <c r="I124" s="31">
@@ -8500,7 +8500,7 @@
       <c r="F125" s="40" t="n"/>
       <c r="G125" s="23" t="n"/>
       <c r="H125" s="30">
-        <f>IF(OR(A125="",G125="",F125=""),"",IF(OR(NOT(ISNUMBER(F125)),NOT(ISNUMBER(G125))),"valor ou horas inválidos",IF(G125=0,"",F125/G125)))</f>
+        <f>IF(OR(A125="",G125="",F125=""),"",IF(OR(NOT(IF(ISNUMBER(F125),F125&gt;=0,FALSE)),NOT(IF(ISNUMBER(G125),G125&gt;=0,FALSE))),"valor ou horas inválidos",IF(G125=0,"",F125/G125)))</f>
         <v/>
       </c>
       <c r="I125" s="31">
@@ -8529,7 +8529,7 @@
       <c r="F126" s="40" t="n"/>
       <c r="G126" s="23" t="n"/>
       <c r="H126" s="30">
-        <f>IF(OR(A126="",G126="",F126=""),"",IF(OR(NOT(ISNUMBER(F126)),NOT(ISNUMBER(G126))),"valor ou horas inválidos",IF(G126=0,"",F126/G126)))</f>
+        <f>IF(OR(A126="",G126="",F126=""),"",IF(OR(NOT(IF(ISNUMBER(F126),F126&gt;=0,FALSE)),NOT(IF(ISNUMBER(G126),G126&gt;=0,FALSE))),"valor ou horas inválidos",IF(G126=0,"",F126/G126)))</f>
         <v/>
       </c>
       <c r="I126" s="31">
@@ -8558,7 +8558,7 @@
       <c r="F127" s="40" t="n"/>
       <c r="G127" s="23" t="n"/>
       <c r="H127" s="30">
-        <f>IF(OR(A127="",G127="",F127=""),"",IF(OR(NOT(ISNUMBER(F127)),NOT(ISNUMBER(G127))),"valor ou horas inválidos",IF(G127=0,"",F127/G127)))</f>
+        <f>IF(OR(A127="",G127="",F127=""),"",IF(OR(NOT(IF(ISNUMBER(F127),F127&gt;=0,FALSE)),NOT(IF(ISNUMBER(G127),G127&gt;=0,FALSE))),"valor ou horas inválidos",IF(G127=0,"",F127/G127)))</f>
         <v/>
       </c>
       <c r="I127" s="31">
@@ -8587,7 +8587,7 @@
       <c r="F128" s="40" t="n"/>
       <c r="G128" s="23" t="n"/>
       <c r="H128" s="30">
-        <f>IF(OR(A128="",G128="",F128=""),"",IF(OR(NOT(ISNUMBER(F128)),NOT(ISNUMBER(G128))),"valor ou horas inválidos",IF(G128=0,"",F128/G128)))</f>
+        <f>IF(OR(A128="",G128="",F128=""),"",IF(OR(NOT(IF(ISNUMBER(F128),F128&gt;=0,FALSE)),NOT(IF(ISNUMBER(G128),G128&gt;=0,FALSE))),"valor ou horas inválidos",IF(G128=0,"",F128/G128)))</f>
         <v/>
       </c>
       <c r="I128" s="31">
@@ -8616,7 +8616,7 @@
       <c r="F129" s="40" t="n"/>
       <c r="G129" s="23" t="n"/>
       <c r="H129" s="30">
-        <f>IF(OR(A129="",G129="",F129=""),"",IF(OR(NOT(ISNUMBER(F129)),NOT(ISNUMBER(G129))),"valor ou horas inválidos",IF(G129=0,"",F129/G129)))</f>
+        <f>IF(OR(A129="",G129="",F129=""),"",IF(OR(NOT(IF(ISNUMBER(F129),F129&gt;=0,FALSE)),NOT(IF(ISNUMBER(G129),G129&gt;=0,FALSE))),"valor ou horas inválidos",IF(G129=0,"",F129/G129)))</f>
         <v/>
       </c>
       <c r="I129" s="31">
@@ -8645,7 +8645,7 @@
       <c r="F130" s="40" t="n"/>
       <c r="G130" s="23" t="n"/>
       <c r="H130" s="30">
-        <f>IF(OR(A130="",G130="",F130=""),"",IF(OR(NOT(ISNUMBER(F130)),NOT(ISNUMBER(G130))),"valor ou horas inválidos",IF(G130=0,"",F130/G130)))</f>
+        <f>IF(OR(A130="",G130="",F130=""),"",IF(OR(NOT(IF(ISNUMBER(F130),F130&gt;=0,FALSE)),NOT(IF(ISNUMBER(G130),G130&gt;=0,FALSE))),"valor ou horas inválidos",IF(G130=0,"",F130/G130)))</f>
         <v/>
       </c>
       <c r="I130" s="31">
@@ -8674,7 +8674,7 @@
       <c r="F131" s="40" t="n"/>
       <c r="G131" s="23" t="n"/>
       <c r="H131" s="30">
-        <f>IF(OR(A131="",G131="",F131=""),"",IF(OR(NOT(ISNUMBER(F131)),NOT(ISNUMBER(G131))),"valor ou horas inválidos",IF(G131=0,"",F131/G131)))</f>
+        <f>IF(OR(A131="",G131="",F131=""),"",IF(OR(NOT(IF(ISNUMBER(F131),F131&gt;=0,FALSE)),NOT(IF(ISNUMBER(G131),G131&gt;=0,FALSE))),"valor ou horas inválidos",IF(G131=0,"",F131/G131)))</f>
         <v/>
       </c>
       <c r="I131" s="31">
@@ -8703,7 +8703,7 @@
       <c r="F132" s="40" t="n"/>
       <c r="G132" s="23" t="n"/>
       <c r="H132" s="30">
-        <f>IF(OR(A132="",G132="",F132=""),"",IF(OR(NOT(ISNUMBER(F132)),NOT(ISNUMBER(G132))),"valor ou horas inválidos",IF(G132=0,"",F132/G132)))</f>
+        <f>IF(OR(A132="",G132="",F132=""),"",IF(OR(NOT(IF(ISNUMBER(F132),F132&gt;=0,FALSE)),NOT(IF(ISNUMBER(G132),G132&gt;=0,FALSE))),"valor ou horas inválidos",IF(G132=0,"",F132/G132)))</f>
         <v/>
       </c>
       <c r="I132" s="31">
@@ -8732,7 +8732,7 @@
       <c r="F133" s="40" t="n"/>
       <c r="G133" s="23" t="n"/>
       <c r="H133" s="30">
-        <f>IF(OR(A133="",G133="",F133=""),"",IF(OR(NOT(ISNUMBER(F133)),NOT(ISNUMBER(G133))),"valor ou horas inválidos",IF(G133=0,"",F133/G133)))</f>
+        <f>IF(OR(A133="",G133="",F133=""),"",IF(OR(NOT(IF(ISNUMBER(F133),F133&gt;=0,FALSE)),NOT(IF(ISNUMBER(G133),G133&gt;=0,FALSE))),"valor ou horas inválidos",IF(G133=0,"",F133/G133)))</f>
         <v/>
       </c>
       <c r="I133" s="31">
@@ -8761,7 +8761,7 @@
       <c r="F134" s="40" t="n"/>
       <c r="G134" s="23" t="n"/>
       <c r="H134" s="30">
-        <f>IF(OR(A134="",G134="",F134=""),"",IF(OR(NOT(ISNUMBER(F134)),NOT(ISNUMBER(G134))),"valor ou horas inválidos",IF(G134=0,"",F134/G134)))</f>
+        <f>IF(OR(A134="",G134="",F134=""),"",IF(OR(NOT(IF(ISNUMBER(F134),F134&gt;=0,FALSE)),NOT(IF(ISNUMBER(G134),G134&gt;=0,FALSE))),"valor ou horas inválidos",IF(G134=0,"",F134/G134)))</f>
         <v/>
       </c>
       <c r="I134" s="31">
@@ -8790,7 +8790,7 @@
       <c r="F135" s="40" t="n"/>
       <c r="G135" s="23" t="n"/>
       <c r="H135" s="30">
-        <f>IF(OR(A135="",G135="",F135=""),"",IF(OR(NOT(ISNUMBER(F135)),NOT(ISNUMBER(G135))),"valor ou horas inválidos",IF(G135=0,"",F135/G135)))</f>
+        <f>IF(OR(A135="",G135="",F135=""),"",IF(OR(NOT(IF(ISNUMBER(F135),F135&gt;=0,FALSE)),NOT(IF(ISNUMBER(G135),G135&gt;=0,FALSE))),"valor ou horas inválidos",IF(G135=0,"",F135/G135)))</f>
         <v/>
       </c>
       <c r="I135" s="31">
@@ -8819,7 +8819,7 @@
       <c r="F136" s="40" t="n"/>
       <c r="G136" s="23" t="n"/>
       <c r="H136" s="30">
-        <f>IF(OR(A136="",G136="",F136=""),"",IF(OR(NOT(ISNUMBER(F136)),NOT(ISNUMBER(G136))),"valor ou horas inválidos",IF(G136=0,"",F136/G136)))</f>
+        <f>IF(OR(A136="",G136="",F136=""),"",IF(OR(NOT(IF(ISNUMBER(F136),F136&gt;=0,FALSE)),NOT(IF(ISNUMBER(G136),G136&gt;=0,FALSE))),"valor ou horas inválidos",IF(G136=0,"",F136/G136)))</f>
         <v/>
       </c>
       <c r="I136" s="31">
@@ -8848,7 +8848,7 @@
       <c r="F137" s="40" t="n"/>
       <c r="G137" s="23" t="n"/>
       <c r="H137" s="30">
-        <f>IF(OR(A137="",G137="",F137=""),"",IF(OR(NOT(ISNUMBER(F137)),NOT(ISNUMBER(G137))),"valor ou horas inválidos",IF(G137=0,"",F137/G137)))</f>
+        <f>IF(OR(A137="",G137="",F137=""),"",IF(OR(NOT(IF(ISNUMBER(F137),F137&gt;=0,FALSE)),NOT(IF(ISNUMBER(G137),G137&gt;=0,FALSE))),"valor ou horas inválidos",IF(G137=0,"",F137/G137)))</f>
         <v/>
       </c>
       <c r="I137" s="31">
@@ -8877,7 +8877,7 @@
       <c r="F138" s="40" t="n"/>
       <c r="G138" s="23" t="n"/>
       <c r="H138" s="30">
-        <f>IF(OR(A138="",G138="",F138=""),"",IF(OR(NOT(ISNUMBER(F138)),NOT(ISNUMBER(G138))),"valor ou horas inválidos",IF(G138=0,"",F138/G138)))</f>
+        <f>IF(OR(A138="",G138="",F138=""),"",IF(OR(NOT(IF(ISNUMBER(F138),F138&gt;=0,FALSE)),NOT(IF(ISNUMBER(G138),G138&gt;=0,FALSE))),"valor ou horas inválidos",IF(G138=0,"",F138/G138)))</f>
         <v/>
       </c>
       <c r="I138" s="31">
@@ -8906,7 +8906,7 @@
       <c r="F139" s="40" t="n"/>
       <c r="G139" s="23" t="n"/>
       <c r="H139" s="30">
-        <f>IF(OR(A139="",G139="",F139=""),"",IF(OR(NOT(ISNUMBER(F139)),NOT(ISNUMBER(G139))),"valor ou horas inválidos",IF(G139=0,"",F139/G139)))</f>
+        <f>IF(OR(A139="",G139="",F139=""),"",IF(OR(NOT(IF(ISNUMBER(F139),F139&gt;=0,FALSE)),NOT(IF(ISNUMBER(G139),G139&gt;=0,FALSE))),"valor ou horas inválidos",IF(G139=0,"",F139/G139)))</f>
         <v/>
       </c>
       <c r="I139" s="31">
@@ -8935,7 +8935,7 @@
       <c r="F140" s="40" t="n"/>
       <c r="G140" s="23" t="n"/>
       <c r="H140" s="30">
-        <f>IF(OR(A140="",G140="",F140=""),"",IF(OR(NOT(ISNUMBER(F140)),NOT(ISNUMBER(G140))),"valor ou horas inválidos",IF(G140=0,"",F140/G140)))</f>
+        <f>IF(OR(A140="",G140="",F140=""),"",IF(OR(NOT(IF(ISNUMBER(F140),F140&gt;=0,FALSE)),NOT(IF(ISNUMBER(G140),G140&gt;=0,FALSE))),"valor ou horas inválidos",IF(G140=0,"",F140/G140)))</f>
         <v/>
       </c>
       <c r="I140" s="31">
@@ -8964,7 +8964,7 @@
       <c r="F141" s="40" t="n"/>
       <c r="G141" s="23" t="n"/>
       <c r="H141" s="30">
-        <f>IF(OR(A141="",G141="",F141=""),"",IF(OR(NOT(ISNUMBER(F141)),NOT(ISNUMBER(G141))),"valor ou horas inválidos",IF(G141=0,"",F141/G141)))</f>
+        <f>IF(OR(A141="",G141="",F141=""),"",IF(OR(NOT(IF(ISNUMBER(F141),F141&gt;=0,FALSE)),NOT(IF(ISNUMBER(G141),G141&gt;=0,FALSE))),"valor ou horas inválidos",IF(G141=0,"",F141/G141)))</f>
         <v/>
       </c>
       <c r="I141" s="31">
@@ -8993,7 +8993,7 @@
       <c r="F142" s="40" t="n"/>
       <c r="G142" s="23" t="n"/>
       <c r="H142" s="30">
-        <f>IF(OR(A142="",G142="",F142=""),"",IF(OR(NOT(ISNUMBER(F142)),NOT(ISNUMBER(G142))),"valor ou horas inválidos",IF(G142=0,"",F142/G142)))</f>
+        <f>IF(OR(A142="",G142="",F142=""),"",IF(OR(NOT(IF(ISNUMBER(F142),F142&gt;=0,FALSE)),NOT(IF(ISNUMBER(G142),G142&gt;=0,FALSE))),"valor ou horas inválidos",IF(G142=0,"",F142/G142)))</f>
         <v/>
       </c>
       <c r="I142" s="31">
@@ -9022,7 +9022,7 @@
       <c r="F143" s="40" t="n"/>
       <c r="G143" s="23" t="n"/>
       <c r="H143" s="30">
-        <f>IF(OR(A143="",G143="",F143=""),"",IF(OR(NOT(ISNUMBER(F143)),NOT(ISNUMBER(G143))),"valor ou horas inválidos",IF(G143=0,"",F143/G143)))</f>
+        <f>IF(OR(A143="",G143="",F143=""),"",IF(OR(NOT(IF(ISNUMBER(F143),F143&gt;=0,FALSE)),NOT(IF(ISNUMBER(G143),G143&gt;=0,FALSE))),"valor ou horas inválidos",IF(G143=0,"",F143/G143)))</f>
         <v/>
       </c>
       <c r="I143" s="31">
@@ -9051,7 +9051,7 @@
       <c r="F144" s="40" t="n"/>
       <c r="G144" s="23" t="n"/>
       <c r="H144" s="30">
-        <f>IF(OR(A144="",G144="",F144=""),"",IF(OR(NOT(ISNUMBER(F144)),NOT(ISNUMBER(G144))),"valor ou horas inválidos",IF(G144=0,"",F144/G144)))</f>
+        <f>IF(OR(A144="",G144="",F144=""),"",IF(OR(NOT(IF(ISNUMBER(F144),F144&gt;=0,FALSE)),NOT(IF(ISNUMBER(G144),G144&gt;=0,FALSE))),"valor ou horas inválidos",IF(G144=0,"",F144/G144)))</f>
         <v/>
       </c>
       <c r="I144" s="31">
@@ -9080,7 +9080,7 @@
       <c r="F145" s="40" t="n"/>
       <c r="G145" s="23" t="n"/>
       <c r="H145" s="30">
-        <f>IF(OR(A145="",G145="",F145=""),"",IF(OR(NOT(ISNUMBER(F145)),NOT(ISNUMBER(G145))),"valor ou horas inválidos",IF(G145=0,"",F145/G145)))</f>
+        <f>IF(OR(A145="",G145="",F145=""),"",IF(OR(NOT(IF(ISNUMBER(F145),F145&gt;=0,FALSE)),NOT(IF(ISNUMBER(G145),G145&gt;=0,FALSE))),"valor ou horas inválidos",IF(G145=0,"",F145/G145)))</f>
         <v/>
       </c>
       <c r="I145" s="31">
@@ -9109,7 +9109,7 @@
       <c r="F146" s="40" t="n"/>
       <c r="G146" s="23" t="n"/>
       <c r="H146" s="30">
-        <f>IF(OR(A146="",G146="",F146=""),"",IF(OR(NOT(ISNUMBER(F146)),NOT(ISNUMBER(G146))),"valor ou horas inválidos",IF(G146=0,"",F146/G146)))</f>
+        <f>IF(OR(A146="",G146="",F146=""),"",IF(OR(NOT(IF(ISNUMBER(F146),F146&gt;=0,FALSE)),NOT(IF(ISNUMBER(G146),G146&gt;=0,FALSE))),"valor ou horas inválidos",IF(G146=0,"",F146/G146)))</f>
         <v/>
       </c>
       <c r="I146" s="31">
@@ -9138,7 +9138,7 @@
       <c r="F147" s="40" t="n"/>
       <c r="G147" s="23" t="n"/>
       <c r="H147" s="30">
-        <f>IF(OR(A147="",G147="",F147=""),"",IF(OR(NOT(ISNUMBER(F147)),NOT(ISNUMBER(G147))),"valor ou horas inválidos",IF(G147=0,"",F147/G147)))</f>
+        <f>IF(OR(A147="",G147="",F147=""),"",IF(OR(NOT(IF(ISNUMBER(F147),F147&gt;=0,FALSE)),NOT(IF(ISNUMBER(G147),G147&gt;=0,FALSE))),"valor ou horas inválidos",IF(G147=0,"",F147/G147)))</f>
         <v/>
       </c>
       <c r="I147" s="31">
@@ -9167,7 +9167,7 @@
       <c r="F148" s="40" t="n"/>
       <c r="G148" s="23" t="n"/>
       <c r="H148" s="30">
-        <f>IF(OR(A148="",G148="",F148=""),"",IF(OR(NOT(ISNUMBER(F148)),NOT(ISNUMBER(G148))),"valor ou horas inválidos",IF(G148=0,"",F148/G148)))</f>
+        <f>IF(OR(A148="",G148="",F148=""),"",IF(OR(NOT(IF(ISNUMBER(F148),F148&gt;=0,FALSE)),NOT(IF(ISNUMBER(G148),G148&gt;=0,FALSE))),"valor ou horas inválidos",IF(G148=0,"",F148/G148)))</f>
         <v/>
       </c>
       <c r="I148" s="31">
@@ -9196,7 +9196,7 @@
       <c r="F149" s="40" t="n"/>
       <c r="G149" s="23" t="n"/>
       <c r="H149" s="30">
-        <f>IF(OR(A149="",G149="",F149=""),"",IF(OR(NOT(ISNUMBER(F149)),NOT(ISNUMBER(G149))),"valor ou horas inválidos",IF(G149=0,"",F149/G149)))</f>
+        <f>IF(OR(A149="",G149="",F149=""),"",IF(OR(NOT(IF(ISNUMBER(F149),F149&gt;=0,FALSE)),NOT(IF(ISNUMBER(G149),G149&gt;=0,FALSE))),"valor ou horas inválidos",IF(G149=0,"",F149/G149)))</f>
         <v/>
       </c>
       <c r="I149" s="31">
@@ -9225,7 +9225,7 @@
       <c r="F150" s="40" t="n"/>
       <c r="G150" s="23" t="n"/>
       <c r="H150" s="30">
-        <f>IF(OR(A150="",G150="",F150=""),"",IF(OR(NOT(ISNUMBER(F150)),NOT(ISNUMBER(G150))),"valor ou horas inválidos",IF(G150=0,"",F150/G150)))</f>
+        <f>IF(OR(A150="",G150="",F150=""),"",IF(OR(NOT(IF(ISNUMBER(F150),F150&gt;=0,FALSE)),NOT(IF(ISNUMBER(G150),G150&gt;=0,FALSE))),"valor ou horas inválidos",IF(G150=0,"",F150/G150)))</f>
         <v/>
       </c>
       <c r="I150" s="31">
@@ -9254,7 +9254,7 @@
       <c r="F151" s="40" t="n"/>
       <c r="G151" s="23" t="n"/>
       <c r="H151" s="30">
-        <f>IF(OR(A151="",G151="",F151=""),"",IF(OR(NOT(ISNUMBER(F151)),NOT(ISNUMBER(G151))),"valor ou horas inválidos",IF(G151=0,"",F151/G151)))</f>
+        <f>IF(OR(A151="",G151="",F151=""),"",IF(OR(NOT(IF(ISNUMBER(F151),F151&gt;=0,FALSE)),NOT(IF(ISNUMBER(G151),G151&gt;=0,FALSE))),"valor ou horas inválidos",IF(G151=0,"",F151/G151)))</f>
         <v/>
       </c>
       <c r="I151" s="31">
@@ -9283,7 +9283,7 @@
       <c r="F152" s="40" t="n"/>
       <c r="G152" s="23" t="n"/>
       <c r="H152" s="30">
-        <f>IF(OR(A152="",G152="",F152=""),"",IF(OR(NOT(ISNUMBER(F152)),NOT(ISNUMBER(G152))),"valor ou horas inválidos",IF(G152=0,"",F152/G152)))</f>
+        <f>IF(OR(A152="",G152="",F152=""),"",IF(OR(NOT(IF(ISNUMBER(F152),F152&gt;=0,FALSE)),NOT(IF(ISNUMBER(G152),G152&gt;=0,FALSE))),"valor ou horas inválidos",IF(G152=0,"",F152/G152)))</f>
         <v/>
       </c>
       <c r="I152" s="31">
@@ -9312,7 +9312,7 @@
       <c r="F153" s="40" t="n"/>
       <c r="G153" s="23" t="n"/>
       <c r="H153" s="30">
-        <f>IF(OR(A153="",G153="",F153=""),"",IF(OR(NOT(ISNUMBER(F153)),NOT(ISNUMBER(G153))),"valor ou horas inválidos",IF(G153=0,"",F153/G153)))</f>
+        <f>IF(OR(A153="",G153="",F153=""),"",IF(OR(NOT(IF(ISNUMBER(F153),F153&gt;=0,FALSE)),NOT(IF(ISNUMBER(G153),G153&gt;=0,FALSE))),"valor ou horas inválidos",IF(G153=0,"",F153/G153)))</f>
         <v/>
       </c>
       <c r="I153" s="31">
@@ -9341,7 +9341,7 @@
       <c r="F154" s="40" t="n"/>
       <c r="G154" s="23" t="n"/>
       <c r="H154" s="30">
-        <f>IF(OR(A154="",G154="",F154=""),"",IF(OR(NOT(ISNUMBER(F154)),NOT(ISNUMBER(G154))),"valor ou horas inválidos",IF(G154=0,"",F154/G154)))</f>
+        <f>IF(OR(A154="",G154="",F154=""),"",IF(OR(NOT(IF(ISNUMBER(F154),F154&gt;=0,FALSE)),NOT(IF(ISNUMBER(G154),G154&gt;=0,FALSE))),"valor ou horas inválidos",IF(G154=0,"",F154/G154)))</f>
         <v/>
       </c>
       <c r="I154" s="31">
@@ -9370,7 +9370,7 @@
       <c r="F155" s="40" t="n"/>
       <c r="G155" s="23" t="n"/>
       <c r="H155" s="30">
-        <f>IF(OR(A155="",G155="",F155=""),"",IF(OR(NOT(ISNUMBER(F155)),NOT(ISNUMBER(G155))),"valor ou horas inválidos",IF(G155=0,"",F155/G155)))</f>
+        <f>IF(OR(A155="",G155="",F155=""),"",IF(OR(NOT(IF(ISNUMBER(F155),F155&gt;=0,FALSE)),NOT(IF(ISNUMBER(G155),G155&gt;=0,FALSE))),"valor ou horas inválidos",IF(G155=0,"",F155/G155)))</f>
         <v/>
       </c>
       <c r="I155" s="31">
@@ -9399,7 +9399,7 @@
       <c r="F156" s="40" t="n"/>
       <c r="G156" s="23" t="n"/>
       <c r="H156" s="30">
-        <f>IF(OR(A156="",G156="",F156=""),"",IF(OR(NOT(ISNUMBER(F156)),NOT(ISNUMBER(G156))),"valor ou horas inválidos",IF(G156=0,"",F156/G156)))</f>
+        <f>IF(OR(A156="",G156="",F156=""),"",IF(OR(NOT(IF(ISNUMBER(F156),F156&gt;=0,FALSE)),NOT(IF(ISNUMBER(G156),G156&gt;=0,FALSE))),"valor ou horas inválidos",IF(G156=0,"",F156/G156)))</f>
         <v/>
       </c>
       <c r="I156" s="31">
@@ -9428,7 +9428,7 @@
       <c r="F157" s="40" t="n"/>
       <c r="G157" s="23" t="n"/>
       <c r="H157" s="30">
-        <f>IF(OR(A157="",G157="",F157=""),"",IF(OR(NOT(ISNUMBER(F157)),NOT(ISNUMBER(G157))),"valor ou horas inválidos",IF(G157=0,"",F157/G157)))</f>
+        <f>IF(OR(A157="",G157="",F157=""),"",IF(OR(NOT(IF(ISNUMBER(F157),F157&gt;=0,FALSE)),NOT(IF(ISNUMBER(G157),G157&gt;=0,FALSE))),"valor ou horas inválidos",IF(G157=0,"",F157/G157)))</f>
         <v/>
       </c>
       <c r="I157" s="31">
@@ -9457,7 +9457,7 @@
       <c r="F158" s="40" t="n"/>
       <c r="G158" s="23" t="n"/>
       <c r="H158" s="30">
-        <f>IF(OR(A158="",G158="",F158=""),"",IF(OR(NOT(ISNUMBER(F158)),NOT(ISNUMBER(G158))),"valor ou horas inválidos",IF(G158=0,"",F158/G158)))</f>
+        <f>IF(OR(A158="",G158="",F158=""),"",IF(OR(NOT(IF(ISNUMBER(F158),F158&gt;=0,FALSE)),NOT(IF(ISNUMBER(G158),G158&gt;=0,FALSE))),"valor ou horas inválidos",IF(G158=0,"",F158/G158)))</f>
         <v/>
       </c>
       <c r="I158" s="31">
@@ -9486,7 +9486,7 @@
       <c r="F159" s="40" t="n"/>
       <c r="G159" s="23" t="n"/>
       <c r="H159" s="30">
-        <f>IF(OR(A159="",G159="",F159=""),"",IF(OR(NOT(ISNUMBER(F159)),NOT(ISNUMBER(G159))),"valor ou horas inválidos",IF(G159=0,"",F159/G159)))</f>
+        <f>IF(OR(A159="",G159="",F159=""),"",IF(OR(NOT(IF(ISNUMBER(F159),F159&gt;=0,FALSE)),NOT(IF(ISNUMBER(G159),G159&gt;=0,FALSE))),"valor ou horas inválidos",IF(G159=0,"",F159/G159)))</f>
         <v/>
       </c>
       <c r="I159" s="31">
@@ -9515,7 +9515,7 @@
       <c r="F160" s="40" t="n"/>
       <c r="G160" s="23" t="n"/>
       <c r="H160" s="30">
-        <f>IF(OR(A160="",G160="",F160=""),"",IF(OR(NOT(ISNUMBER(F160)),NOT(ISNUMBER(G160))),"valor ou horas inválidos",IF(G160=0,"",F160/G160)))</f>
+        <f>IF(OR(A160="",G160="",F160=""),"",IF(OR(NOT(IF(ISNUMBER(F160),F160&gt;=0,FALSE)),NOT(IF(ISNUMBER(G160),G160&gt;=0,FALSE))),"valor ou horas inválidos",IF(G160=0,"",F160/G160)))</f>
         <v/>
       </c>
       <c r="I160" s="31">
@@ -9544,7 +9544,7 @@
       <c r="F161" s="40" t="n"/>
       <c r="G161" s="23" t="n"/>
       <c r="H161" s="30">
-        <f>IF(OR(A161="",G161="",F161=""),"",IF(OR(NOT(ISNUMBER(F161)),NOT(ISNUMBER(G161))),"valor ou horas inválidos",IF(G161=0,"",F161/G161)))</f>
+        <f>IF(OR(A161="",G161="",F161=""),"",IF(OR(NOT(IF(ISNUMBER(F161),F161&gt;=0,FALSE)),NOT(IF(ISNUMBER(G161),G161&gt;=0,FALSE))),"valor ou horas inválidos",IF(G161=0,"",F161/G161)))</f>
         <v/>
       </c>
       <c r="I161" s="31">
@@ -9573,7 +9573,7 @@
       <c r="F162" s="40" t="n"/>
       <c r="G162" s="23" t="n"/>
       <c r="H162" s="30">
-        <f>IF(OR(A162="",G162="",F162=""),"",IF(OR(NOT(ISNUMBER(F162)),NOT(ISNUMBER(G162))),"valor ou horas inválidos",IF(G162=0,"",F162/G162)))</f>
+        <f>IF(OR(A162="",G162="",F162=""),"",IF(OR(NOT(IF(ISNUMBER(F162),F162&gt;=0,FALSE)),NOT(IF(ISNUMBER(G162),G162&gt;=0,FALSE))),"valor ou horas inválidos",IF(G162=0,"",F162/G162)))</f>
         <v/>
       </c>
       <c r="I162" s="31">
@@ -9602,7 +9602,7 @@
       <c r="F163" s="40" t="n"/>
       <c r="G163" s="23" t="n"/>
       <c r="H163" s="30">
-        <f>IF(OR(A163="",G163="",F163=""),"",IF(OR(NOT(ISNUMBER(F163)),NOT(ISNUMBER(G163))),"valor ou horas inválidos",IF(G163=0,"",F163/G163)))</f>
+        <f>IF(OR(A163="",G163="",F163=""),"",IF(OR(NOT(IF(ISNUMBER(F163),F163&gt;=0,FALSE)),NOT(IF(ISNUMBER(G163),G163&gt;=0,FALSE))),"valor ou horas inválidos",IF(G163=0,"",F163/G163)))</f>
         <v/>
       </c>
       <c r="I163" s="31">
@@ -9631,7 +9631,7 @@
       <c r="F164" s="40" t="n"/>
       <c r="G164" s="23" t="n"/>
       <c r="H164" s="30">
-        <f>IF(OR(A164="",G164="",F164=""),"",IF(OR(NOT(ISNUMBER(F164)),NOT(ISNUMBER(G164))),"valor ou horas inválidos",IF(G164=0,"",F164/G164)))</f>
+        <f>IF(OR(A164="",G164="",F164=""),"",IF(OR(NOT(IF(ISNUMBER(F164),F164&gt;=0,FALSE)),NOT(IF(ISNUMBER(G164),G164&gt;=0,FALSE))),"valor ou horas inválidos",IF(G164=0,"",F164/G164)))</f>
         <v/>
       </c>
       <c r="I164" s="31">
@@ -9660,7 +9660,7 @@
       <c r="F165" s="40" t="n"/>
       <c r="G165" s="23" t="n"/>
       <c r="H165" s="30">
-        <f>IF(OR(A165="",G165="",F165=""),"",IF(OR(NOT(ISNUMBER(F165)),NOT(ISNUMBER(G165))),"valor ou horas inválidos",IF(G165=0,"",F165/G165)))</f>
+        <f>IF(OR(A165="",G165="",F165=""),"",IF(OR(NOT(IF(ISNUMBER(F165),F165&gt;=0,FALSE)),NOT(IF(ISNUMBER(G165),G165&gt;=0,FALSE))),"valor ou horas inválidos",IF(G165=0,"",F165/G165)))</f>
         <v/>
       </c>
       <c r="I165" s="31">
@@ -9689,7 +9689,7 @@
       <c r="F166" s="40" t="n"/>
       <c r="G166" s="23" t="n"/>
       <c r="H166" s="30">
-        <f>IF(OR(A166="",G166="",F166=""),"",IF(OR(NOT(ISNUMBER(F166)),NOT(ISNUMBER(G166))),"valor ou horas inválidos",IF(G166=0,"",F166/G166)))</f>
+        <f>IF(OR(A166="",G166="",F166=""),"",IF(OR(NOT(IF(ISNUMBER(F166),F166&gt;=0,FALSE)),NOT(IF(ISNUMBER(G166),G166&gt;=0,FALSE))),"valor ou horas inválidos",IF(G166=0,"",F166/G166)))</f>
         <v/>
       </c>
       <c r="I166" s="31">
@@ -9718,7 +9718,7 @@
       <c r="F167" s="40" t="n"/>
       <c r="G167" s="23" t="n"/>
       <c r="H167" s="30">
-        <f>IF(OR(A167="",G167="",F167=""),"",IF(OR(NOT(ISNUMBER(F167)),NOT(ISNUMBER(G167))),"valor ou horas inválidos",IF(G167=0,"",F167/G167)))</f>
+        <f>IF(OR(A167="",G167="",F167=""),"",IF(OR(NOT(IF(ISNUMBER(F167),F167&gt;=0,FALSE)),NOT(IF(ISNUMBER(G167),G167&gt;=0,FALSE))),"valor ou horas inválidos",IF(G167=0,"",F167/G167)))</f>
         <v/>
       </c>
       <c r="I167" s="31">
@@ -9747,7 +9747,7 @@
       <c r="F168" s="40" t="n"/>
       <c r="G168" s="23" t="n"/>
       <c r="H168" s="30">
-        <f>IF(OR(A168="",G168="",F168=""),"",IF(OR(NOT(ISNUMBER(F168)),NOT(ISNUMBER(G168))),"valor ou horas inválidos",IF(G168=0,"",F168/G168)))</f>
+        <f>IF(OR(A168="",G168="",F168=""),"",IF(OR(NOT(IF(ISNUMBER(F168),F168&gt;=0,FALSE)),NOT(IF(ISNUMBER(G168),G168&gt;=0,FALSE))),"valor ou horas inválidos",IF(G168=0,"",F168/G168)))</f>
         <v/>
       </c>
       <c r="I168" s="31">
@@ -9776,7 +9776,7 @@
       <c r="F169" s="40" t="n"/>
       <c r="G169" s="23" t="n"/>
       <c r="H169" s="30">
-        <f>IF(OR(A169="",G169="",F169=""),"",IF(OR(NOT(ISNUMBER(F169)),NOT(ISNUMBER(G169))),"valor ou horas inválidos",IF(G169=0,"",F169/G169)))</f>
+        <f>IF(OR(A169="",G169="",F169=""),"",IF(OR(NOT(IF(ISNUMBER(F169),F169&gt;=0,FALSE)),NOT(IF(ISNUMBER(G169),G169&gt;=0,FALSE))),"valor ou horas inválidos",IF(G169=0,"",F169/G169)))</f>
         <v/>
       </c>
       <c r="I169" s="31">
@@ -9805,7 +9805,7 @@
       <c r="F170" s="40" t="n"/>
       <c r="G170" s="23" t="n"/>
       <c r="H170" s="30">
-        <f>IF(OR(A170="",G170="",F170=""),"",IF(OR(NOT(ISNUMBER(F170)),NOT(ISNUMBER(G170))),"valor ou horas inválidos",IF(G170=0,"",F170/G170)))</f>
+        <f>IF(OR(A170="",G170="",F170=""),"",IF(OR(NOT(IF(ISNUMBER(F170),F170&gt;=0,FALSE)),NOT(IF(ISNUMBER(G170),G170&gt;=0,FALSE))),"valor ou horas inválidos",IF(G170=0,"",F170/G170)))</f>
         <v/>
       </c>
       <c r="I170" s="31">
@@ -9834,7 +9834,7 @@
       <c r="F171" s="40" t="n"/>
       <c r="G171" s="23" t="n"/>
       <c r="H171" s="30">
-        <f>IF(OR(A171="",G171="",F171=""),"",IF(OR(NOT(ISNUMBER(F171)),NOT(ISNUMBER(G171))),"valor ou horas inválidos",IF(G171=0,"",F171/G171)))</f>
+        <f>IF(OR(A171="",G171="",F171=""),"",IF(OR(NOT(IF(ISNUMBER(F171),F171&gt;=0,FALSE)),NOT(IF(ISNUMBER(G171),G171&gt;=0,FALSE))),"valor ou horas inválidos",IF(G171=0,"",F171/G171)))</f>
         <v/>
       </c>
       <c r="I171" s="31">
@@ -9863,7 +9863,7 @@
       <c r="F172" s="40" t="n"/>
       <c r="G172" s="23" t="n"/>
       <c r="H172" s="30">
-        <f>IF(OR(A172="",G172="",F172=""),"",IF(OR(NOT(ISNUMBER(F172)),NOT(ISNUMBER(G172))),"valor ou horas inválidos",IF(G172=0,"",F172/G172)))</f>
+        <f>IF(OR(A172="",G172="",F172=""),"",IF(OR(NOT(IF(ISNUMBER(F172),F172&gt;=0,FALSE)),NOT(IF(ISNUMBER(G172),G172&gt;=0,FALSE))),"valor ou horas inválidos",IF(G172=0,"",F172/G172)))</f>
         <v/>
       </c>
       <c r="I172" s="31">
@@ -9892,7 +9892,7 @@
       <c r="F173" s="40" t="n"/>
       <c r="G173" s="23" t="n"/>
       <c r="H173" s="30">
-        <f>IF(OR(A173="",G173="",F173=""),"",IF(OR(NOT(ISNUMBER(F173)),NOT(ISNUMBER(G173))),"valor ou horas inválidos",IF(G173=0,"",F173/G173)))</f>
+        <f>IF(OR(A173="",G173="",F173=""),"",IF(OR(NOT(IF(ISNUMBER(F173),F173&gt;=0,FALSE)),NOT(IF(ISNUMBER(G173),G173&gt;=0,FALSE))),"valor ou horas inválidos",IF(G173=0,"",F173/G173)))</f>
         <v/>
       </c>
       <c r="I173" s="31">
@@ -9921,7 +9921,7 @@
       <c r="F174" s="40" t="n"/>
       <c r="G174" s="23" t="n"/>
       <c r="H174" s="30">
-        <f>IF(OR(A174="",G174="",F174=""),"",IF(OR(NOT(ISNUMBER(F174)),NOT(ISNUMBER(G174))),"valor ou horas inválidos",IF(G174=0,"",F174/G174)))</f>
+        <f>IF(OR(A174="",G174="",F174=""),"",IF(OR(NOT(IF(ISNUMBER(F174),F174&gt;=0,FALSE)),NOT(IF(ISNUMBER(G174),G174&gt;=0,FALSE))),"valor ou horas inválidos",IF(G174=0,"",F174/G174)))</f>
         <v/>
       </c>
       <c r="I174" s="31">
@@ -9950,7 +9950,7 @@
       <c r="F175" s="40" t="n"/>
       <c r="G175" s="23" t="n"/>
       <c r="H175" s="30">
-        <f>IF(OR(A175="",G175="",F175=""),"",IF(OR(NOT(ISNUMBER(F175)),NOT(ISNUMBER(G175))),"valor ou horas inválidos",IF(G175=0,"",F175/G175)))</f>
+        <f>IF(OR(A175="",G175="",F175=""),"",IF(OR(NOT(IF(ISNUMBER(F175),F175&gt;=0,FALSE)),NOT(IF(ISNUMBER(G175),G175&gt;=0,FALSE))),"valor ou horas inválidos",IF(G175=0,"",F175/G175)))</f>
         <v/>
       </c>
       <c r="I175" s="31">
@@ -9979,7 +9979,7 @@
       <c r="F176" s="40" t="n"/>
       <c r="G176" s="23" t="n"/>
       <c r="H176" s="30">
-        <f>IF(OR(A176="",G176="",F176=""),"",IF(OR(NOT(ISNUMBER(F176)),NOT(ISNUMBER(G176))),"valor ou horas inválidos",IF(G176=0,"",F176/G176)))</f>
+        <f>IF(OR(A176="",G176="",F176=""),"",IF(OR(NOT(IF(ISNUMBER(F176),F176&gt;=0,FALSE)),NOT(IF(ISNUMBER(G176),G176&gt;=0,FALSE))),"valor ou horas inválidos",IF(G176=0,"",F176/G176)))</f>
         <v/>
       </c>
       <c r="I176" s="31">
@@ -10008,7 +10008,7 @@
       <c r="F177" s="40" t="n"/>
       <c r="G177" s="23" t="n"/>
       <c r="H177" s="30">
-        <f>IF(OR(A177="",G177="",F177=""),"",IF(OR(NOT(ISNUMBER(F177)),NOT(ISNUMBER(G177))),"valor ou horas inválidos",IF(G177=0,"",F177/G177)))</f>
+        <f>IF(OR(A177="",G177="",F177=""),"",IF(OR(NOT(IF(ISNUMBER(F177),F177&gt;=0,FALSE)),NOT(IF(ISNUMBER(G177),G177&gt;=0,FALSE))),"valor ou horas inválidos",IF(G177=0,"",F177/G177)))</f>
         <v/>
       </c>
       <c r="I177" s="31">
@@ -10037,7 +10037,7 @@
       <c r="F178" s="40" t="n"/>
       <c r="G178" s="23" t="n"/>
       <c r="H178" s="30">
-        <f>IF(OR(A178="",G178="",F178=""),"",IF(OR(NOT(ISNUMBER(F178)),NOT(ISNUMBER(G178))),"valor ou horas inválidos",IF(G178=0,"",F178/G178)))</f>
+        <f>IF(OR(A178="",G178="",F178=""),"",IF(OR(NOT(IF(ISNUMBER(F178),F178&gt;=0,FALSE)),NOT(IF(ISNUMBER(G178),G178&gt;=0,FALSE))),"valor ou horas inválidos",IF(G178=0,"",F178/G178)))</f>
         <v/>
       </c>
       <c r="I178" s="31">
@@ -10066,7 +10066,7 @@
       <c r="F179" s="40" t="n"/>
       <c r="G179" s="23" t="n"/>
       <c r="H179" s="30">
-        <f>IF(OR(A179="",G179="",F179=""),"",IF(OR(NOT(ISNUMBER(F179)),NOT(ISNUMBER(G179))),"valor ou horas inválidos",IF(G179=0,"",F179/G179)))</f>
+        <f>IF(OR(A179="",G179="",F179=""),"",IF(OR(NOT(IF(ISNUMBER(F179),F179&gt;=0,FALSE)),NOT(IF(ISNUMBER(G179),G179&gt;=0,FALSE))),"valor ou horas inválidos",IF(G179=0,"",F179/G179)))</f>
         <v/>
       </c>
       <c r="I179" s="31">
@@ -10095,7 +10095,7 @@
       <c r="F180" s="40" t="n"/>
       <c r="G180" s="23" t="n"/>
       <c r="H180" s="30">
-        <f>IF(OR(A180="",G180="",F180=""),"",IF(OR(NOT(ISNUMBER(F180)),NOT(ISNUMBER(G180))),"valor ou horas inválidos",IF(G180=0,"",F180/G180)))</f>
+        <f>IF(OR(A180="",G180="",F180=""),"",IF(OR(NOT(IF(ISNUMBER(F180),F180&gt;=0,FALSE)),NOT(IF(ISNUMBER(G180),G180&gt;=0,FALSE))),"valor ou horas inválidos",IF(G180=0,"",F180/G180)))</f>
         <v/>
       </c>
       <c r="I180" s="31">
@@ -10124,7 +10124,7 @@
       <c r="F181" s="40" t="n"/>
       <c r="G181" s="23" t="n"/>
       <c r="H181" s="30">
-        <f>IF(OR(A181="",G181="",F181=""),"",IF(OR(NOT(ISNUMBER(F181)),NOT(ISNUMBER(G181))),"valor ou horas inválidos",IF(G181=0,"",F181/G181)))</f>
+        <f>IF(OR(A181="",G181="",F181=""),"",IF(OR(NOT(IF(ISNUMBER(F181),F181&gt;=0,FALSE)),NOT(IF(ISNUMBER(G181),G181&gt;=0,FALSE))),"valor ou horas inválidos",IF(G181=0,"",F181/G181)))</f>
         <v/>
       </c>
       <c r="I181" s="31">
@@ -10153,7 +10153,7 @@
       <c r="F182" s="40" t="n"/>
       <c r="G182" s="23" t="n"/>
       <c r="H182" s="30">
-        <f>IF(OR(A182="",G182="",F182=""),"",IF(OR(NOT(ISNUMBER(F182)),NOT(ISNUMBER(G182))),"valor ou horas inválidos",IF(G182=0,"",F182/G182)))</f>
+        <f>IF(OR(A182="",G182="",F182=""),"",IF(OR(NOT(IF(ISNUMBER(F182),F182&gt;=0,FALSE)),NOT(IF(ISNUMBER(G182),G182&gt;=0,FALSE))),"valor ou horas inválidos",IF(G182=0,"",F182/G182)))</f>
         <v/>
       </c>
       <c r="I182" s="31">
@@ -10182,7 +10182,7 @@
       <c r="F183" s="40" t="n"/>
       <c r="G183" s="23" t="n"/>
       <c r="H183" s="30">
-        <f>IF(OR(A183="",G183="",F183=""),"",IF(OR(NOT(ISNUMBER(F183)),NOT(ISNUMBER(G183))),"valor ou horas inválidos",IF(G183=0,"",F183/G183)))</f>
+        <f>IF(OR(A183="",G183="",F183=""),"",IF(OR(NOT(IF(ISNUMBER(F183),F183&gt;=0,FALSE)),NOT(IF(ISNUMBER(G183),G183&gt;=0,FALSE))),"valor ou horas inválidos",IF(G183=0,"",F183/G183)))</f>
         <v/>
       </c>
       <c r="I183" s="31">
@@ -10211,7 +10211,7 @@
       <c r="F184" s="40" t="n"/>
       <c r="G184" s="23" t="n"/>
       <c r="H184" s="30">
-        <f>IF(OR(A184="",G184="",F184=""),"",IF(OR(NOT(ISNUMBER(F184)),NOT(ISNUMBER(G184))),"valor ou horas inválidos",IF(G184=0,"",F184/G184)))</f>
+        <f>IF(OR(A184="",G184="",F184=""),"",IF(OR(NOT(IF(ISNUMBER(F184),F184&gt;=0,FALSE)),NOT(IF(ISNUMBER(G184),G184&gt;=0,FALSE))),"valor ou horas inválidos",IF(G184=0,"",F184/G184)))</f>
         <v/>
       </c>
       <c r="I184" s="31">
@@ -10240,7 +10240,7 @@
       <c r="F185" s="40" t="n"/>
       <c r="G185" s="23" t="n"/>
       <c r="H185" s="30">
-        <f>IF(OR(A185="",G185="",F185=""),"",IF(OR(NOT(ISNUMBER(F185)),NOT(ISNUMBER(G185))),"valor ou horas inválidos",IF(G185=0,"",F185/G185)))</f>
+        <f>IF(OR(A185="",G185="",F185=""),"",IF(OR(NOT(IF(ISNUMBER(F185),F185&gt;=0,FALSE)),NOT(IF(ISNUMBER(G185),G185&gt;=0,FALSE))),"valor ou horas inválidos",IF(G185=0,"",F185/G185)))</f>
         <v/>
       </c>
       <c r="I185" s="31">
@@ -10269,7 +10269,7 @@
       <c r="F186" s="40" t="n"/>
       <c r="G186" s="23" t="n"/>
       <c r="H186" s="30">
-        <f>IF(OR(A186="",G186="",F186=""),"",IF(OR(NOT(ISNUMBER(F186)),NOT(ISNUMBER(G186))),"valor ou horas inválidos",IF(G186=0,"",F186/G186)))</f>
+        <f>IF(OR(A186="",G186="",F186=""),"",IF(OR(NOT(IF(ISNUMBER(F186),F186&gt;=0,FALSE)),NOT(IF(ISNUMBER(G186),G186&gt;=0,FALSE))),"valor ou horas inválidos",IF(G186=0,"",F186/G186)))</f>
         <v/>
       </c>
       <c r="I186" s="31">
@@ -10298,7 +10298,7 @@
       <c r="F187" s="40" t="n"/>
       <c r="G187" s="23" t="n"/>
       <c r="H187" s="30">
-        <f>IF(OR(A187="",G187="",F187=""),"",IF(OR(NOT(ISNUMBER(F187)),NOT(ISNUMBER(G187))),"valor ou horas inválidos",IF(G187=0,"",F187/G187)))</f>
+        <f>IF(OR(A187="",G187="",F187=""),"",IF(OR(NOT(IF(ISNUMBER(F187),F187&gt;=0,FALSE)),NOT(IF(ISNUMBER(G187),G187&gt;=0,FALSE))),"valor ou horas inválidos",IF(G187=0,"",F187/G187)))</f>
         <v/>
       </c>
       <c r="I187" s="31">
@@ -10327,7 +10327,7 @@
       <c r="F188" s="40" t="n"/>
       <c r="G188" s="23" t="n"/>
       <c r="H188" s="30">
-        <f>IF(OR(A188="",G188="",F188=""),"",IF(OR(NOT(ISNUMBER(F188)),NOT(ISNUMBER(G188))),"valor ou horas inválidos",IF(G188=0,"",F188/G188)))</f>
+        <f>IF(OR(A188="",G188="",F188=""),"",IF(OR(NOT(IF(ISNUMBER(F188),F188&gt;=0,FALSE)),NOT(IF(ISNUMBER(G188),G188&gt;=0,FALSE))),"valor ou horas inválidos",IF(G188=0,"",F188/G188)))</f>
         <v/>
       </c>
       <c r="I188" s="31">
@@ -10356,7 +10356,7 @@
       <c r="F189" s="40" t="n"/>
       <c r="G189" s="23" t="n"/>
       <c r="H189" s="30">
-        <f>IF(OR(A189="",G189="",F189=""),"",IF(OR(NOT(ISNUMBER(F189)),NOT(ISNUMBER(G189))),"valor ou horas inválidos",IF(G189=0,"",F189/G189)))</f>
+        <f>IF(OR(A189="",G189="",F189=""),"",IF(OR(NOT(IF(ISNUMBER(F189),F189&gt;=0,FALSE)),NOT(IF(ISNUMBER(G189),G189&gt;=0,FALSE))),"valor ou horas inválidos",IF(G189=0,"",F189/G189)))</f>
         <v/>
       </c>
       <c r="I189" s="31">
@@ -10385,7 +10385,7 @@
       <c r="F190" s="40" t="n"/>
       <c r="G190" s="23" t="n"/>
       <c r="H190" s="30">
-        <f>IF(OR(A190="",G190="",F190=""),"",IF(OR(NOT(ISNUMBER(F190)),NOT(ISNUMBER(G190))),"valor ou horas inválidos",IF(G190=0,"",F190/G190)))</f>
+        <f>IF(OR(A190="",G190="",F190=""),"",IF(OR(NOT(IF(ISNUMBER(F190),F190&gt;=0,FALSE)),NOT(IF(ISNUMBER(G190),G190&gt;=0,FALSE))),"valor ou horas inválidos",IF(G190=0,"",F190/G190)))</f>
         <v/>
       </c>
       <c r="I190" s="31">
@@ -10414,7 +10414,7 @@
       <c r="F191" s="40" t="n"/>
       <c r="G191" s="23" t="n"/>
       <c r="H191" s="30">
-        <f>IF(OR(A191="",G191="",F191=""),"",IF(OR(NOT(ISNUMBER(F191)),NOT(ISNUMBER(G191))),"valor ou horas inválidos",IF(G191=0,"",F191/G191)))</f>
+        <f>IF(OR(A191="",G191="",F191=""),"",IF(OR(NOT(IF(ISNUMBER(F191),F191&gt;=0,FALSE)),NOT(IF(ISNUMBER(G191),G191&gt;=0,FALSE))),"valor ou horas inválidos",IF(G191=0,"",F191/G191)))</f>
         <v/>
       </c>
       <c r="I191" s="31">
@@ -10443,7 +10443,7 @@
       <c r="F192" s="40" t="n"/>
       <c r="G192" s="23" t="n"/>
       <c r="H192" s="30">
-        <f>IF(OR(A192="",G192="",F192=""),"",IF(OR(NOT(ISNUMBER(F192)),NOT(ISNUMBER(G192))),"valor ou horas inválidos",IF(G192=0,"",F192/G192)))</f>
+        <f>IF(OR(A192="",G192="",F192=""),"",IF(OR(NOT(IF(ISNUMBER(F192),F192&gt;=0,FALSE)),NOT(IF(ISNUMBER(G192),G192&gt;=0,FALSE))),"valor ou horas inválidos",IF(G192=0,"",F192/G192)))</f>
         <v/>
       </c>
       <c r="I192" s="31">
@@ -10472,7 +10472,7 @@
       <c r="F193" s="40" t="n"/>
       <c r="G193" s="23" t="n"/>
       <c r="H193" s="30">
-        <f>IF(OR(A193="",G193="",F193=""),"",IF(OR(NOT(ISNUMBER(F193)),NOT(ISNUMBER(G193))),"valor ou horas inválidos",IF(G193=0,"",F193/G193)))</f>
+        <f>IF(OR(A193="",G193="",F193=""),"",IF(OR(NOT(IF(ISNUMBER(F193),F193&gt;=0,FALSE)),NOT(IF(ISNUMBER(G193),G193&gt;=0,FALSE))),"valor ou horas inválidos",IF(G193=0,"",F193/G193)))</f>
         <v/>
       </c>
       <c r="I193" s="31">
@@ -10501,7 +10501,7 @@
       <c r="F194" s="40" t="n"/>
       <c r="G194" s="23" t="n"/>
       <c r="H194" s="30">
-        <f>IF(OR(A194="",G194="",F194=""),"",IF(OR(NOT(ISNUMBER(F194)),NOT(ISNUMBER(G194))),"valor ou horas inválidos",IF(G194=0,"",F194/G194)))</f>
+        <f>IF(OR(A194="",G194="",F194=""),"",IF(OR(NOT(IF(ISNUMBER(F194),F194&gt;=0,FALSE)),NOT(IF(ISNUMBER(G194),G194&gt;=0,FALSE))),"valor ou horas inválidos",IF(G194=0,"",F194/G194)))</f>
         <v/>
       </c>
       <c r="I194" s="31">
@@ -10530,7 +10530,7 @@
       <c r="F195" s="40" t="n"/>
       <c r="G195" s="23" t="n"/>
       <c r="H195" s="30">
-        <f>IF(OR(A195="",G195="",F195=""),"",IF(OR(NOT(ISNUMBER(F195)),NOT(ISNUMBER(G195))),"valor ou horas inválidos",IF(G195=0,"",F195/G195)))</f>
+        <f>IF(OR(A195="",G195="",F195=""),"",IF(OR(NOT(IF(ISNUMBER(F195),F195&gt;=0,FALSE)),NOT(IF(ISNUMBER(G195),G195&gt;=0,FALSE))),"valor ou horas inválidos",IF(G195=0,"",F195/G195)))</f>
         <v/>
       </c>
       <c r="I195" s="31">
@@ -10559,7 +10559,7 @@
       <c r="F196" s="40" t="n"/>
       <c r="G196" s="23" t="n"/>
       <c r="H196" s="30">
-        <f>IF(OR(A196="",G196="",F196=""),"",IF(OR(NOT(ISNUMBER(F196)),NOT(ISNUMBER(G196))),"valor ou horas inválidos",IF(G196=0,"",F196/G196)))</f>
+        <f>IF(OR(A196="",G196="",F196=""),"",IF(OR(NOT(IF(ISNUMBER(F196),F196&gt;=0,FALSE)),NOT(IF(ISNUMBER(G196),G196&gt;=0,FALSE))),"valor ou horas inválidos",IF(G196=0,"",F196/G196)))</f>
         <v/>
       </c>
       <c r="I196" s="31">
@@ -10588,7 +10588,7 @@
       <c r="F197" s="40" t="n"/>
       <c r="G197" s="23" t="n"/>
       <c r="H197" s="30">
-        <f>IF(OR(A197="",G197="",F197=""),"",IF(OR(NOT(ISNUMBER(F197)),NOT(ISNUMBER(G197))),"valor ou horas inválidos",IF(G197=0,"",F197/G197)))</f>
+        <f>IF(OR(A197="",G197="",F197=""),"",IF(OR(NOT(IF(ISNUMBER(F197),F197&gt;=0,FALSE)),NOT(IF(ISNUMBER(G197),G197&gt;=0,FALSE))),"valor ou horas inválidos",IF(G197=0,"",F197/G197)))</f>
         <v/>
       </c>
       <c r="I197" s="31">
@@ -10617,7 +10617,7 @@
       <c r="F198" s="40" t="n"/>
       <c r="G198" s="23" t="n"/>
       <c r="H198" s="30">
-        <f>IF(OR(A198="",G198="",F198=""),"",IF(OR(NOT(ISNUMBER(F198)),NOT(ISNUMBER(G198))),"valor ou horas inválidos",IF(G198=0,"",F198/G198)))</f>
+        <f>IF(OR(A198="",G198="",F198=""),"",IF(OR(NOT(IF(ISNUMBER(F198),F198&gt;=0,FALSE)),NOT(IF(ISNUMBER(G198),G198&gt;=0,FALSE))),"valor ou horas inválidos",IF(G198=0,"",F198/G198)))</f>
         <v/>
       </c>
       <c r="I198" s="31">
@@ -10646,7 +10646,7 @@
       <c r="F199" s="40" t="n"/>
       <c r="G199" s="23" t="n"/>
       <c r="H199" s="30">
-        <f>IF(OR(A199="",G199="",F199=""),"",IF(OR(NOT(ISNUMBER(F199)),NOT(ISNUMBER(G199))),"valor ou horas inválidos",IF(G199=0,"",F199/G199)))</f>
+        <f>IF(OR(A199="",G199="",F199=""),"",IF(OR(NOT(IF(ISNUMBER(F199),F199&gt;=0,FALSE)),NOT(IF(ISNUMBER(G199),G199&gt;=0,FALSE))),"valor ou horas inválidos",IF(G199=0,"",F199/G199)))</f>
         <v/>
       </c>
       <c r="I199" s="31">
@@ -10675,7 +10675,7 @@
       <c r="F200" s="40" t="n"/>
       <c r="G200" s="23" t="n"/>
       <c r="H200" s="30">
-        <f>IF(OR(A200="",G200="",F200=""),"",IF(OR(NOT(ISNUMBER(F200)),NOT(ISNUMBER(G200))),"valor ou horas inválidos",IF(G200=0,"",F200/G200)))</f>
+        <f>IF(OR(A200="",G200="",F200=""),"",IF(OR(NOT(IF(ISNUMBER(F200),F200&gt;=0,FALSE)),NOT(IF(ISNUMBER(G200),G200&gt;=0,FALSE))),"valor ou horas inválidos",IF(G200=0,"",F200/G200)))</f>
         <v/>
       </c>
       <c r="I200" s="31">
@@ -10704,7 +10704,7 @@
       <c r="F201" s="40" t="n"/>
       <c r="G201" s="23" t="n"/>
       <c r="H201" s="30">
-        <f>IF(OR(A201="",G201="",F201=""),"",IF(OR(NOT(ISNUMBER(F201)),NOT(ISNUMBER(G201))),"valor ou horas inválidos",IF(G201=0,"",F201/G201)))</f>
+        <f>IF(OR(A201="",G201="",F201=""),"",IF(OR(NOT(IF(ISNUMBER(F201),F201&gt;=0,FALSE)),NOT(IF(ISNUMBER(G201),G201&gt;=0,FALSE))),"valor ou horas inválidos",IF(G201=0,"",F201/G201)))</f>
         <v/>
       </c>
       <c r="I201" s="31">
@@ -10733,7 +10733,7 @@
       <c r="F202" s="40" t="n"/>
       <c r="G202" s="23" t="n"/>
       <c r="H202" s="30">
-        <f>IF(OR(A202="",G202="",F202=""),"",IF(OR(NOT(ISNUMBER(F202)),NOT(ISNUMBER(G202))),"valor ou horas inválidos",IF(G202=0,"",F202/G202)))</f>
+        <f>IF(OR(A202="",G202="",F202=""),"",IF(OR(NOT(IF(ISNUMBER(F202),F202&gt;=0,FALSE)),NOT(IF(ISNUMBER(G202),G202&gt;=0,FALSE))),"valor ou horas inválidos",IF(G202=0,"",F202/G202)))</f>
         <v/>
       </c>
       <c r="I202" s="31">
@@ -10762,7 +10762,7 @@
       <c r="F203" s="40" t="n"/>
       <c r="G203" s="23" t="n"/>
       <c r="H203" s="30">
-        <f>IF(OR(A203="",G203="",F203=""),"",IF(OR(NOT(ISNUMBER(F203)),NOT(ISNUMBER(G203))),"valor ou horas inválidos",IF(G203=0,"",F203/G203)))</f>
+        <f>IF(OR(A203="",G203="",F203=""),"",IF(OR(NOT(IF(ISNUMBER(F203),F203&gt;=0,FALSE)),NOT(IF(ISNUMBER(G203),G203&gt;=0,FALSE))),"valor ou horas inválidos",IF(G203=0,"",F203/G203)))</f>
         <v/>
       </c>
       <c r="I203" s="31">
@@ -10791,7 +10791,7 @@
       <c r="F204" s="40" t="n"/>
       <c r="G204" s="23" t="n"/>
       <c r="H204" s="30">
-        <f>IF(OR(A204="",G204="",F204=""),"",IF(OR(NOT(ISNUMBER(F204)),NOT(ISNUMBER(G204))),"valor ou horas inválidos",IF(G204=0,"",F204/G204)))</f>
+        <f>IF(OR(A204="",G204="",F204=""),"",IF(OR(NOT(IF(ISNUMBER(F204),F204&gt;=0,FALSE)),NOT(IF(ISNUMBER(G204),G204&gt;=0,FALSE))),"valor ou horas inválidos",IF(G204=0,"",F204/G204)))</f>
         <v/>
       </c>
       <c r="I204" s="31">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/08-tabela-de-referencia.xlsx
@@ -1181,11 +1181,11 @@
         </is>
       </c>
       <c r="F9" s="25">
-        <f>IF(OR(A9="",C9=""),"",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A9="",C9=""),"",IF(NOT(IF(ISNUMBER(C9),C9&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C9),ISNUMBER(D9),C9&gt;D9),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C9*Config!$B$12,Config!$B$12))))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G9" s="25">
-        <f>IF(OR(A9="",D9=""),"",IF(NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A9="",D9=""),"",IF(NOT(IF(ISNUMBER(D9),D9&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C9),ISNUMBER(D9),C9&gt;D9),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D9*Config!$B$13,Config!$B$13))))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H9" s="25">
@@ -1193,7 +1193,7 @@
         <v>866.591938229238</v>
       </c>
       <c r="I9" s="26" t="str">
-        <f>IF(A9="","",IF(E9="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E9="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E9="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A9="","",IF(AND(ISNUMBER(C9),ISNUMBER(D9),C9&gt;D9),"Corrija a faixa de horas: o de é maior que o até",IF(E9="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E9="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E9="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1220,11 +1220,11 @@
         </is>
       </c>
       <c r="F10" s="25">
-        <f>IF(OR(A10="",C10=""),"",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A10="",C10=""),"",IF(NOT(IF(ISNUMBER(C10),C10&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C10),ISNUMBER(D10),C10&gt;D10),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C10*Config!$B$12,Config!$B$12))))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G10" s="25">
-        <f>IF(OR(A10="",D10=""),"",IF(NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A10="",D10=""),"",IF(NOT(IF(ISNUMBER(D10),D10&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C10),ISNUMBER(D10),C10&gt;D10),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D10*Config!$B$13,Config!$B$13))))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H10" s="25">
@@ -1232,7 +1232,7 @@
         <v>1648.83740837337</v>
       </c>
       <c r="I10" s="26" t="str">
-        <f>IF(A10="","",IF(E10="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E10="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E10="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A10="","",IF(AND(ISNUMBER(C10),ISNUMBER(D10),C10&gt;D10),"Corrija a faixa de horas: o de é maior que o até",IF(E10="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E10="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E10="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="F11" s="25">
-        <f>IF(OR(A11="",C11=""),"",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A11="",C11=""),"",IF(NOT(IF(ISNUMBER(C11),C11&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C11),ISNUMBER(D11),C11&gt;D11),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C11*Config!$B$12,Config!$B$12))))</f>
         <v>6394.0064516129</v>
       </c>
       <c r="G11" s="25">
-        <f>IF(OR(A11="",D11=""),"",IF(NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A11="",D11=""),"",IF(NOT(IF(ISNUMBER(D11),D11&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C11),ISNUMBER(D11),C11&gt;D11),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D11*Config!$B$13,Config!$B$13))))</f>
         <v>16869.2936170213</v>
       </c>
       <c r="H11" s="25">
@@ -1271,7 +1271,7 @@
         <v>11631.6500343171</v>
       </c>
       <c r="I11" s="26" t="str">
-        <f>IF(A11="","",IF(E11="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E11="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E11="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A11="","",IF(AND(ISNUMBER(C11),ISNUMBER(D11),C11&gt;D11),"Corrija a faixa de horas: o de é maior que o até",IF(E11="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E11="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E11="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
@@ -1298,11 +1298,11 @@
         </is>
       </c>
       <c r="F12" s="25">
-        <f>IF(OR(A12="",C12=""),"",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A12="",C12=""),"",IF(NOT(IF(ISNUMBER(C12),C12&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C12),ISNUMBER(D12),C12&gt;D12),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C12*Config!$B$12,Config!$B$12))))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G12" s="25">
-        <f>IF(OR(A12="",D12=""),"",IF(NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A12="",D12=""),"",IF(NOT(IF(ISNUMBER(D12),D12&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C12),ISNUMBER(D12),C12&gt;D12),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D12*Config!$B$13,Config!$B$13))))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H12" s="25">
@@ -1310,7 +1310,7 @@
         <v>3911.22735072066</v>
       </c>
       <c r="I12" s="26" t="str">
-        <f>IF(A12="","",IF(E12="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E12="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E12="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A12="","",IF(AND(ISNUMBER(C12),ISNUMBER(D12),C12&gt;D12),"Corrija a faixa de horas: o de é maior que o até",IF(E12="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E12="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E12="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="F13" s="25">
-        <f>IF(OR(A13="",C13=""),"",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A13="",C13=""),"",IF(NOT(IF(ISNUMBER(C13),C13&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C13),ISNUMBER(D13),C13&gt;D13),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C13*Config!$B$12,Config!$B$12))))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G13" s="25">
-        <f>IF(OR(A13="",D13=""),"",IF(NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A13="",D13=""),"",IF(NOT(IF(ISNUMBER(D13),D13&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C13),ISNUMBER(D13),C13&gt;D13),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D13*Config!$B$13,Config!$B$13))))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H13" s="25">
@@ -1349,7 +1349,7 @@
         <v>2620.18221825669</v>
       </c>
       <c r="I13" s="26" t="str">
-        <f>IF(A13="","",IF(E13="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E13="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E13="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A13="","",IF(AND(ISNUMBER(C13),ISNUMBER(D13),C13&gt;D13),"Corrija a faixa de horas: o de é maior que o até",IF(E13="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E13="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E13="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
@@ -1376,11 +1376,11 @@
         </is>
       </c>
       <c r="F14" s="25">
-        <f>IF(OR(A14="",C14=""),"",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A14="",C14=""),"",IF(NOT(IF(ISNUMBER(C14),C14&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C14),ISNUMBER(D14),C14&gt;D14),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C14*Config!$B$12,Config!$B$12))))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G14" s="25">
-        <f>IF(OR(A14="",D14=""),"",IF(NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A14="",D14=""),"",IF(NOT(IF(ISNUMBER(D14),D14&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C14),ISNUMBER(D14),C14&gt;D14),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D14*Config!$B$13,Config!$B$13))))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H14" s="25">
@@ -1388,7 +1388,7 @@
         <v>866.591938229238</v>
       </c>
       <c r="I14" s="26" t="str">
-        <f>IF(A14="","",IF(E14="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E14="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E14="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A14="","",IF(AND(ISNUMBER(C14),ISNUMBER(D14),C14&gt;D14),"Corrija a faixa de horas: o de é maior que o até",IF(E14="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E14="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E14="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1415,11 +1415,11 @@
         </is>
       </c>
       <c r="F15" s="25">
-        <f>IF(OR(A15="",C15=""),"",IF(NOT(IF(ISNUMBER(C15),C15&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A15="",C15=""),"",IF(NOT(IF(ISNUMBER(C15),C15&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C15),ISNUMBER(D15),C15&gt;D15),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C15*Config!$B$12,Config!$B$12))))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G15" s="25">
-        <f>IF(OR(A15="",D15=""),"",IF(NOT(IF(ISNUMBER(D15),D15&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A15="",D15=""),"",IF(NOT(IF(ISNUMBER(D15),D15&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C15),ISNUMBER(D15),C15&gt;D15),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D15*Config!$B$13,Config!$B$13))))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H15" s="25">
@@ -1427,7 +1427,7 @@
         <v>1648.83740837337</v>
       </c>
       <c r="I15" s="26" t="str">
-        <f>IF(A15="","",IF(E15="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E15="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E15="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A15="","",IF(AND(ISNUMBER(C15),ISNUMBER(D15),C15&gt;D15),"Corrija a faixa de horas: o de é maior que o até",IF(E15="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E15="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E15="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1454,11 +1454,11 @@
         </is>
       </c>
       <c r="F16" s="25">
-        <f>IF(OR(A16="",C16=""),"",IF(NOT(IF(ISNUMBER(C16),C16&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A16="",C16=""),"",IF(NOT(IF(ISNUMBER(C16),C16&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C16),ISNUMBER(D16),C16&gt;D16),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C16*Config!$B$12,Config!$B$12))))</f>
         <v>4475.80451612903</v>
       </c>
       <c r="G16" s="25">
-        <f>IF(OR(A16="",D16=""),"",IF(NOT(IF(ISNUMBER(D16),D16&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A16="",D16=""),"",IF(NOT(IF(ISNUMBER(D16),D16&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C16),ISNUMBER(D16),C16&gt;D16),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D16*Config!$B$13,Config!$B$13))))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H16" s="25">
@@ -1466,7 +1466,7 @@
         <v>8142.15502402196</v>
       </c>
       <c r="I16" s="26" t="str">
-        <f>IF(A16="","",IF(E16="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E16="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E16="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A16="","",IF(AND(ISNUMBER(C16),ISNUMBER(D16),C16&gt;D16),"Corrija a faixa de horas: o de é maior que o até",IF(E16="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E16="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E16="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Percentual que, na chance esperada, fique dentro da faixa</v>
       </c>
     </row>
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="F17" s="25">
-        <f>IF(OR(A17="",C17=""),"",IF(NOT(IF(ISNUMBER(C17),C17&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A17="",C17=""),"",IF(NOT(IF(ISNUMBER(C17),C17&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C17),ISNUMBER(D17),C17&gt;D17),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C17*Config!$B$12,Config!$B$12))))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G17" s="25">
-        <f>IF(OR(A17="",D17=""),"",IF(NOT(IF(ISNUMBER(D17),D17&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A17="",D17=""),"",IF(NOT(IF(ISNUMBER(D17),D17&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C17),ISNUMBER(D17),C17&gt;D17),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D17*Config!$B$13,Config!$B$13))))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H17" s="25">
@@ -1505,7 +1505,7 @@
         <v>3911.22735072066</v>
       </c>
       <c r="I17" s="26" t="str">
-        <f>IF(A17="","",IF(E17="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E17="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E17="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A17="","",IF(AND(ISNUMBER(C17),ISNUMBER(D17),C17&gt;D17),"Corrija a faixa de horas: o de é maior que o até",IF(E17="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E17="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E17="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="F18" s="25">
-        <f>IF(OR(A18="",C18=""),"",IF(NOT(IF(ISNUMBER(C18),C18&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A18="",C18=""),"",IF(NOT(IF(ISNUMBER(C18),C18&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C18),ISNUMBER(D18),C18&gt;D18),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C18*Config!$B$12,Config!$B$12))))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G18" s="25">
-        <f>IF(OR(A18="",D18=""),"",IF(NOT(IF(ISNUMBER(D18),D18&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A18="",D18=""),"",IF(NOT(IF(ISNUMBER(D18),D18&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C18),ISNUMBER(D18),C18&gt;D18),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D18*Config!$B$13,Config!$B$13))))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H18" s="25">
@@ -1544,7 +1544,7 @@
         <v>2620.18221825669</v>
       </c>
       <c r="I18" s="26" t="str">
-        <f>IF(A18="","",IF(E18="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E18="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E18="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A18="","",IF(AND(ISNUMBER(C18),ISNUMBER(D18),C18&gt;D18),"Corrija a faixa de horas: o de é maior que o até",IF(E18="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E18="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E18="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
@@ -1571,11 +1571,11 @@
         </is>
       </c>
       <c r="F19" s="25">
-        <f>IF(OR(A19="",C19=""),"",IF(NOT(IF(ISNUMBER(C19),C19&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A19="",C19=""),"",IF(NOT(IF(ISNUMBER(C19),C19&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C19),ISNUMBER(D19),C19&gt;D19),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C19*Config!$B$12,Config!$B$12))))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G19" s="25">
-        <f>IF(OR(A19="",D19=""),"",IF(NOT(IF(ISNUMBER(D19),D19&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A19="",D19=""),"",IF(NOT(IF(ISNUMBER(D19),D19&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C19),ISNUMBER(D19),C19&gt;D19),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D19*Config!$B$13,Config!$B$13))))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H19" s="25">
@@ -1583,7 +1583,7 @@
         <v>866.591938229238</v>
       </c>
       <c r="I19" s="26" t="str">
-        <f>IF(A19="","",IF(E19="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E19="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E19="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A19="","",IF(AND(ISNUMBER(C19),ISNUMBER(D19),C19&gt;D19),"Corrija a faixa de horas: o de é maior que o até",IF(E19="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E19="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E19="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="F20" s="25">
-        <f>IF(OR(A20="",C20=""),"",IF(NOT(IF(ISNUMBER(C20),C20&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A20="",C20=""),"",IF(NOT(IF(ISNUMBER(C20),C20&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C20),ISNUMBER(D20),C20&gt;D20),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C20*Config!$B$12,Config!$B$12))))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G20" s="25">
-        <f>IF(OR(A20="",D20=""),"",IF(NOT(IF(ISNUMBER(D20),D20&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A20="",D20=""),"",IF(NOT(IF(ISNUMBER(D20),D20&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C20),ISNUMBER(D20),C20&gt;D20),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D20*Config!$B$13,Config!$B$13))))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H20" s="25">
@@ -1622,7 +1622,7 @@
         <v>1648.83740837337</v>
       </c>
       <c r="I20" s="26" t="str">
-        <f>IF(A20="","",IF(E20="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E20="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E20="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A20="","",IF(AND(ISNUMBER(C20),ISNUMBER(D20),C20&gt;D20),"Corrija a faixa de horas: o de é maior que o até",IF(E20="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E20="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E20="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1649,11 +1649,11 @@
         </is>
       </c>
       <c r="F21" s="25">
-        <f>IF(OR(A21="",C21=""),"",IF(NOT(IF(ISNUMBER(C21),C21&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A21="",C21=""),"",IF(NOT(IF(ISNUMBER(C21),C21&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C21),ISNUMBER(D21),C21&gt;D21),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C21*Config!$B$12,Config!$B$12))))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G21" s="25">
-        <f>IF(OR(A21="",D21=""),"",IF(NOT(IF(ISNUMBER(D21),D21&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A21="",D21=""),"",IF(NOT(IF(ISNUMBER(D21),D21&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C21),ISNUMBER(D21),C21&gt;D21),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D21*Config!$B$13,Config!$B$13))))</f>
         <v>10121.5761702128</v>
       </c>
       <c r="H21" s="25">
@@ -1661,7 +1661,7 @@
         <v>6978.99002059025</v>
       </c>
       <c r="I21" s="26" t="str">
-        <f>IF(A21="","",IF(E21="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E21="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E21="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A21="","",IF(AND(ISNUMBER(C21),ISNUMBER(D21),C21&gt;D21),"Corrija a faixa de horas: o de é maior que o até",IF(E21="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E21="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E21="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Percentual que, na chance esperada, fique dentro da faixa</v>
       </c>
     </row>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="F22" s="25">
-        <f>IF(OR(A22="",C22=""),"",IF(NOT(IF(ISNUMBER(C22),C22&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A22="",C22=""),"",IF(NOT(IF(ISNUMBER(C22),C22&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C22),ISNUMBER(D22),C22&gt;D22),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C22*Config!$B$12,Config!$B$12))))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G22" s="25">
-        <f>IF(OR(A22="",D22=""),"",IF(NOT(IF(ISNUMBER(D22),D22&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A22="",D22=""),"",IF(NOT(IF(ISNUMBER(D22),D22&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C22),ISNUMBER(D22),C22&gt;D22),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D22*Config!$B$13,Config!$B$13))))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H22" s="25">
@@ -1700,7 +1700,7 @@
         <v>3911.22735072066</v>
       </c>
       <c r="I22" s="26" t="str">
-        <f>IF(A22="","",IF(E22="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E22="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E22="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A22="","",IF(AND(ISNUMBER(C22),ISNUMBER(D22),C22&gt;D22),"Corrija a faixa de horas: o de é maior que o até",IF(E22="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E22="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E22="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="F23" s="25">
-        <f>IF(OR(A23="",C23=""),"",IF(NOT(IF(ISNUMBER(C23),C23&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A23="",C23=""),"",IF(NOT(IF(ISNUMBER(C23),C23&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C23),ISNUMBER(D23),C23&gt;D23),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C23*Config!$B$12,Config!$B$12))))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G23" s="25">
-        <f>IF(OR(A23="",D23=""),"",IF(NOT(IF(ISNUMBER(D23),D23&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A23="",D23=""),"",IF(NOT(IF(ISNUMBER(D23),D23&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C23),ISNUMBER(D23),C23&gt;D23),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D23*Config!$B$13,Config!$B$13))))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H23" s="25">
@@ -1739,7 +1739,7 @@
         <v>2620.18221825669</v>
       </c>
       <c r="I23" s="26" t="str">
-        <f>IF(A23="","",IF(E23="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E23="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E23="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A23="","",IF(AND(ISNUMBER(C23),ISNUMBER(D23),C23&gt;D23),"Corrija a faixa de horas: o de é maior que o até",IF(E23="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E23="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E23="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="F24" s="25">
-        <f>IF(OR(A24="",C24=""),"",IF(NOT(IF(ISNUMBER(C24),C24&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A24="",C24=""),"",IF(NOT(IF(ISNUMBER(C24),C24&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C24),ISNUMBER(D24),C24&gt;D24),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C24*Config!$B$12,Config!$B$12))))</f>
         <v>511.520516129032</v>
       </c>
       <c r="G24" s="25">
-        <f>IF(OR(A24="",D24=""),"",IF(NOT(IF(ISNUMBER(D24),D24&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A24="",D24=""),"",IF(NOT(IF(ISNUMBER(D24),D24&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C24),ISNUMBER(D24),C24&gt;D24),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D24*Config!$B$13,Config!$B$13))))</f>
         <v>2024.31523404255</v>
       </c>
       <c r="H24" s="25">
@@ -1778,7 +1778,7 @@
         <v>1267.91787508579</v>
       </c>
       <c r="I24" s="26" t="str">
-        <f>IF(A24="","",IF(E24="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E24="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E24="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A24="","",IF(AND(ISNUMBER(C24),ISNUMBER(D24),C24&gt;D24),"Corrija a faixa de horas: o de é maior que o até",IF(E24="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E24="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E24="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Cobre a hora entre a mínima e a alvo; a faixa é o total esperado</v>
       </c>
     </row>
@@ -1805,11 +1805,11 @@
         </is>
       </c>
       <c r="F25" s="25">
-        <f>IF(OR(A25="",C25=""),"",IF(NOT(IF(ISNUMBER(C25),C25&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A25="",C25=""),"",IF(NOT(IF(ISNUMBER(C25),C25&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C25),ISNUMBER(D25),C25&gt;D25),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C25*Config!$B$12,Config!$B$12))))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G25" s="25">
-        <f>IF(OR(A25="",D25=""),"",IF(NOT(IF(ISNUMBER(D25),D25&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A25="",D25=""),"",IF(NOT(IF(ISNUMBER(D25),D25&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C25),ISNUMBER(D25),C25&gt;D25),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D25*Config!$B$13,Config!$B$13))))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H25" s="25">
@@ -1817,7 +1817,7 @@
         <v>1648.83740837337</v>
       </c>
       <c r="I25" s="26" t="str">
-        <f>IF(A25="","",IF(E25="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E25="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E25="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A25="","",IF(AND(ISNUMBER(C25),ISNUMBER(D25),C25&gt;D25),"Corrija a faixa de horas: o de é maior que o até",IF(E25="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E25="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E25="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1844,11 +1844,11 @@
         </is>
       </c>
       <c r="F26" s="25">
-        <f>IF(OR(A26="",C26=""),"",IF(NOT(IF(ISNUMBER(C26),C26&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A26="",C26=""),"",IF(NOT(IF(ISNUMBER(C26),C26&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C26),ISNUMBER(D26),C26&gt;D26),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C26*Config!$B$12,Config!$B$12))))</f>
         <v>7672.80774193548</v>
       </c>
       <c r="G26" s="25">
-        <f>IF(OR(A26="",D26=""),"",IF(NOT(IF(ISNUMBER(D26),D26&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A26="",D26=""),"",IF(NOT(IF(ISNUMBER(D26),D26&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C26),ISNUMBER(D26),C26&gt;D26),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D26*Config!$B$13,Config!$B$13))))</f>
         <v>20243.1523404255</v>
       </c>
       <c r="H26" s="25">
@@ -1856,7 +1856,7 @@
         <v>13957.9800411805</v>
       </c>
       <c r="I26" s="26" t="str">
-        <f>IF(A26="","",IF(E26="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E26="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E26="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A26="","",IF(AND(ISNUMBER(C26),ISNUMBER(D26),C26&gt;D26),"Corrija a faixa de horas: o de é maior que o até",IF(E26="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E26="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E26="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Cobre a hora entre a mínima e a alvo; a faixa é o total esperado</v>
       </c>
     </row>
@@ -1883,11 +1883,11 @@
         </is>
       </c>
       <c r="F27" s="25">
-        <f>IF(OR(A27="",C27=""),"",IF(NOT(IF(ISNUMBER(C27),C27&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A27="",C27=""),"",IF(NOT(IF(ISNUMBER(C27),C27&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C27),ISNUMBER(D27),C27&gt;D27),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C27*Config!$B$12,Config!$B$12))))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G27" s="25">
-        <f>IF(OR(A27="",D27=""),"",IF(NOT(IF(ISNUMBER(D27),D27&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A27="",D27=""),"",IF(NOT(IF(ISNUMBER(D27),D27&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C27),ISNUMBER(D27),C27&gt;D27),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D27*Config!$B$13,Config!$B$13))))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H27" s="25">
@@ -1895,7 +1895,7 @@
         <v>3911.22735072066</v>
       </c>
       <c r="I27" s="26" t="str">
-        <f>IF(A27="","",IF(E27="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E27="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E27="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A27="","",IF(AND(ISNUMBER(C27),ISNUMBER(D27),C27&gt;D27),"Corrija a faixa de horas: o de é maior que o até",IF(E27="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E27="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E27="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="F28" s="25">
-        <f>IF(OR(A28="",C28=""),"",IF(NOT(IF(ISNUMBER(C28),C28&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A28="",C28=""),"",IF(NOT(IF(ISNUMBER(C28),C28&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C28),ISNUMBER(D28),C28&gt;D28),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C28*Config!$B$12,Config!$B$12))))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G28" s="25">
-        <f>IF(OR(A28="",D28=""),"",IF(NOT(IF(ISNUMBER(D28),D28&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A28="",D28=""),"",IF(NOT(IF(ISNUMBER(D28),D28&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C28),ISNUMBER(D28),C28&gt;D28),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D28*Config!$B$13,Config!$B$13))))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H28" s="25">
@@ -1934,7 +1934,7 @@
         <v>2620.18221825669</v>
       </c>
       <c r="I28" s="26" t="str">
-        <f>IF(A28="","",IF(E28="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E28="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E28="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A28="","",IF(AND(ISNUMBER(C28),ISNUMBER(D28),C28&gt;D28),"Corrija a faixa de horas: o de é maior que o até",IF(E28="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E28="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E28="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
@@ -1961,11 +1961,11 @@
         </is>
       </c>
       <c r="F29" s="25">
-        <f>IF(OR(A29="",C29=""),"",IF(NOT(IF(ISNUMBER(C29),C29&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A29="",C29=""),"",IF(NOT(IF(ISNUMBER(C29),C29&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C29),ISNUMBER(D29),C29&gt;D29),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C29*Config!$B$12,Config!$B$12))))</f>
         <v>383.640387096774</v>
       </c>
       <c r="G29" s="25">
-        <f>IF(OR(A29="",D29=""),"",IF(NOT(IF(ISNUMBER(D29),D29&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A29="",D29=""),"",IF(NOT(IF(ISNUMBER(D29),D29&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C29),ISNUMBER(D29),C29&gt;D29),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D29*Config!$B$13,Config!$B$13))))</f>
         <v>1349.5434893617</v>
       </c>
       <c r="H29" s="25">
@@ -1973,7 +1973,7 @@
         <v>866.591938229238</v>
       </c>
       <c r="I29" s="26" t="str">
-        <f>IF(A29="","",IF(E29="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E29="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E29="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A29="","",IF(AND(ISNUMBER(C29),ISNUMBER(D29),C29&gt;D29),"Corrija a faixa de horas: o de é maior que o até",IF(E29="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E29="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E29="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -2000,11 +2000,11 @@
         </is>
       </c>
       <c r="F30" s="25">
-        <f>IF(OR(A30="",C30=""),"",IF(NOT(IF(ISNUMBER(C30),C30&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A30="",C30=""),"",IF(NOT(IF(ISNUMBER(C30),C30&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C30),ISNUMBER(D30),C30&gt;D30),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C30*Config!$B$12,Config!$B$12))))</f>
         <v>767.280774193548</v>
       </c>
       <c r="G30" s="25">
-        <f>IF(OR(A30="",D30=""),"",IF(NOT(IF(ISNUMBER(D30),D30&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A30="",D30=""),"",IF(NOT(IF(ISNUMBER(D30),D30&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C30),ISNUMBER(D30),C30&gt;D30),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D30*Config!$B$13,Config!$B$13))))</f>
         <v>2530.39404255319</v>
       </c>
       <c r="H30" s="25">
@@ -2012,7 +2012,7 @@
         <v>1648.83740837337</v>
       </c>
       <c r="I30" s="26" t="str">
-        <f>IF(A30="","",IF(E30="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E30="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E30="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A30="","",IF(AND(ISNUMBER(C30),ISNUMBER(D30),C30&gt;D30),"Corrija a faixa de horas: o de é maior que o até",IF(E30="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E30="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E30="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="F31" s="25">
-        <f>IF(OR(A31="",C31=""),"",IF(NOT(IF(ISNUMBER(C31),C31&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A31="",C31=""),"",IF(NOT(IF(ISNUMBER(C31),C31&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C31),ISNUMBER(D31),C31&gt;D31),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C31*Config!$B$12,Config!$B$12))))</f>
         <v>3836.40387096774</v>
       </c>
       <c r="G31" s="25">
-        <f>IF(OR(A31="",D31=""),"",IF(NOT(IF(ISNUMBER(D31),D31&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A31="",D31=""),"",IF(NOT(IF(ISNUMBER(D31),D31&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C31),ISNUMBER(D31),C31&gt;D31),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D31*Config!$B$13,Config!$B$13))))</f>
         <v>11808.5055319149</v>
       </c>
       <c r="H31" s="25">
@@ -2051,7 +2051,7 @@
         <v>7822.45470144132</v>
       </c>
       <c r="I31" s="26" t="str">
-        <f>IF(A31="","",IF(E31="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E31="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E31="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A31="","",IF(AND(ISNUMBER(C31),ISNUMBER(D31),C31&gt;D31),"Corrija a faixa de horas: o de é maior que o até",IF(E31="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E31="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E31="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="F32" s="25">
-        <f>IF(OR(A32="",C32=""),"",IF(NOT(IF(ISNUMBER(C32),C32&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A32="",C32=""),"",IF(NOT(IF(ISNUMBER(C32),C32&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C32),ISNUMBER(D32),C32&gt;D32),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C32*Config!$B$12,Config!$B$12))))</f>
         <v>1918.20193548387</v>
       </c>
       <c r="G32" s="25">
-        <f>IF(OR(A32="",D32=""),"",IF(NOT(IF(ISNUMBER(D32),D32&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A32="",D32=""),"",IF(NOT(IF(ISNUMBER(D32),D32&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C32),ISNUMBER(D32),C32&gt;D32),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D32*Config!$B$13,Config!$B$13))))</f>
         <v>5904.25276595745</v>
       </c>
       <c r="H32" s="25">
@@ -2090,7 +2090,7 @@
         <v>3911.22735072066</v>
       </c>
       <c r="I32" s="26" t="str">
-        <f>IF(A32="","",IF(E32="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E32="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E32="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A32="","",IF(AND(ISNUMBER(C32),ISNUMBER(D32),C32&gt;D32),"Corrija a faixa de horas: o de é maior que o até",IF(E32="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E32="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E32="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Caso simples perto do mínimo; complexo perto do máximo</v>
       </c>
     </row>
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="F33" s="25">
-        <f>IF(OR(A33="",C33=""),"",IF(NOT(IF(ISNUMBER(C33),C33&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A33="",C33=""),"",IF(NOT(IF(ISNUMBER(C33),C33&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C33),ISNUMBER(D33),C33&gt;D33),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C33*Config!$B$12,Config!$B$12))))</f>
         <v>1023.04103225806</v>
       </c>
       <c r="G33" s="25">
-        <f>IF(OR(A33="",D33=""),"",IF(NOT(IF(ISNUMBER(D33),D33&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A33="",D33=""),"",IF(NOT(IF(ISNUMBER(D33),D33&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C33),ISNUMBER(D33),C33&gt;D33),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D33*Config!$B$13,Config!$B$13))))</f>
         <v>4217.32340425532</v>
       </c>
       <c r="H33" s="25">
@@ -2129,7 +2129,7 @@
         <v>2620.18221825669</v>
       </c>
       <c r="I33" s="26" t="str">
-        <f>IF(A33="","",IF(E33="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E33="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E33="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A33="","",IF(AND(ISNUMBER(C33),ISNUMBER(D33),C33&gt;D33),"Corrija a faixa de horas: o de é maior que o até",IF(E33="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E33="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E33="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v>Entrada perto do mínimo; o êxito leva ao máximo</v>
       </c>
     </row>
@@ -2140,11 +2140,11 @@
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="24" t="n"/>
       <c r="F34" s="25">
-        <f>IF(OR(A34="",C34=""),"",IF(NOT(IF(ISNUMBER(C34),C34&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A34="",C34=""),"",IF(NOT(IF(ISNUMBER(C34),C34&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C34),ISNUMBER(D34),C34&gt;D34),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C34*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G34" s="25">
-        <f>IF(OR(A34="",D34=""),"",IF(NOT(IF(ISNUMBER(D34),D34&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A34="",D34=""),"",IF(NOT(IF(ISNUMBER(D34),D34&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C34),ISNUMBER(D34),C34&gt;D34),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D34*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H34" s="25">
@@ -2152,7 +2152,7 @@
         <v/>
       </c>
       <c r="I34" s="26">
-        <f>IF(A34="","",IF(E34="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E34="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E34="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A34="","",IF(AND(ISNUMBER(C34),ISNUMBER(D34),C34&gt;D34),"Corrija a faixa de horas: o de é maior que o até",IF(E34="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E34="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E34="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2163,11 +2163,11 @@
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="24" t="n"/>
       <c r="F35" s="25">
-        <f>IF(OR(A35="",C35=""),"",IF(NOT(IF(ISNUMBER(C35),C35&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A35="",C35=""),"",IF(NOT(IF(ISNUMBER(C35),C35&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C35),ISNUMBER(D35),C35&gt;D35),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C35*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G35" s="25">
-        <f>IF(OR(A35="",D35=""),"",IF(NOT(IF(ISNUMBER(D35),D35&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A35="",D35=""),"",IF(NOT(IF(ISNUMBER(D35),D35&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C35),ISNUMBER(D35),C35&gt;D35),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D35*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H35" s="25">
@@ -2175,7 +2175,7 @@
         <v/>
       </c>
       <c r="I35" s="26">
-        <f>IF(A35="","",IF(E35="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E35="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E35="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A35="","",IF(AND(ISNUMBER(C35),ISNUMBER(D35),C35&gt;D35),"Corrija a faixa de horas: o de é maior que o até",IF(E35="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E35="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E35="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2186,11 +2186,11 @@
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="24" t="n"/>
       <c r="F36" s="25">
-        <f>IF(OR(A36="",C36=""),"",IF(NOT(IF(ISNUMBER(C36),C36&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A36="",C36=""),"",IF(NOT(IF(ISNUMBER(C36),C36&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C36),ISNUMBER(D36),C36&gt;D36),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C36*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G36" s="25">
-        <f>IF(OR(A36="",D36=""),"",IF(NOT(IF(ISNUMBER(D36),D36&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A36="",D36=""),"",IF(NOT(IF(ISNUMBER(D36),D36&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C36),ISNUMBER(D36),C36&gt;D36),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D36*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H36" s="25">
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="I36" s="26">
-        <f>IF(A36="","",IF(E36="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E36="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E36="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A36="","",IF(AND(ISNUMBER(C36),ISNUMBER(D36),C36&gt;D36),"Corrija a faixa de horas: o de é maior que o até",IF(E36="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E36="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E36="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2209,11 +2209,11 @@
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="24" t="n"/>
       <c r="F37" s="25">
-        <f>IF(OR(A37="",C37=""),"",IF(NOT(IF(ISNUMBER(C37),C37&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A37="",C37=""),"",IF(NOT(IF(ISNUMBER(C37),C37&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C37),ISNUMBER(D37),C37&gt;D37),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C37*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G37" s="25">
-        <f>IF(OR(A37="",D37=""),"",IF(NOT(IF(ISNUMBER(D37),D37&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A37="",D37=""),"",IF(NOT(IF(ISNUMBER(D37),D37&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C37),ISNUMBER(D37),C37&gt;D37),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D37*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H37" s="25">
@@ -2221,7 +2221,7 @@
         <v/>
       </c>
       <c r="I37" s="26">
-        <f>IF(A37="","",IF(E37="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E37="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E37="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A37="","",IF(AND(ISNUMBER(C37),ISNUMBER(D37),C37&gt;D37),"Corrija a faixa de horas: o de é maior que o até",IF(E37="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E37="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E37="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2232,11 +2232,11 @@
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="24" t="n"/>
       <c r="F38" s="25">
-        <f>IF(OR(A38="",C38=""),"",IF(NOT(IF(ISNUMBER(C38),C38&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A38="",C38=""),"",IF(NOT(IF(ISNUMBER(C38),C38&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C38),ISNUMBER(D38),C38&gt;D38),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C38*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G38" s="25">
-        <f>IF(OR(A38="",D38=""),"",IF(NOT(IF(ISNUMBER(D38),D38&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A38="",D38=""),"",IF(NOT(IF(ISNUMBER(D38),D38&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C38),ISNUMBER(D38),C38&gt;D38),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D38*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H38" s="25">
@@ -2244,7 +2244,7 @@
         <v/>
       </c>
       <c r="I38" s="26">
-        <f>IF(A38="","",IF(E38="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E38="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E38="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A38="","",IF(AND(ISNUMBER(C38),ISNUMBER(D38),C38&gt;D38),"Corrija a faixa de horas: o de é maior que o até",IF(E38="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E38="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E38="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2255,11 +2255,11 @@
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="25">
-        <f>IF(OR(A39="",C39=""),"",IF(NOT(IF(ISNUMBER(C39),C39&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A39="",C39=""),"",IF(NOT(IF(ISNUMBER(C39),C39&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C39),ISNUMBER(D39),C39&gt;D39),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C39*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G39" s="25">
-        <f>IF(OR(A39="",D39=""),"",IF(NOT(IF(ISNUMBER(D39),D39&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A39="",D39=""),"",IF(NOT(IF(ISNUMBER(D39),D39&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C39),ISNUMBER(D39),C39&gt;D39),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D39*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H39" s="25">
@@ -2267,7 +2267,7 @@
         <v/>
       </c>
       <c r="I39" s="26">
-        <f>IF(A39="","",IF(E39="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E39="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E39="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A39="","",IF(AND(ISNUMBER(C39),ISNUMBER(D39),C39&gt;D39),"Corrija a faixa de horas: o de é maior que o até",IF(E39="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E39="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E39="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2278,11 +2278,11 @@
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="24" t="n"/>
       <c r="F40" s="25">
-        <f>IF(OR(A40="",C40=""),"",IF(NOT(IF(ISNUMBER(C40),C40&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A40="",C40=""),"",IF(NOT(IF(ISNUMBER(C40),C40&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C40),ISNUMBER(D40),C40&gt;D40),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C40*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G40" s="25">
-        <f>IF(OR(A40="",D40=""),"",IF(NOT(IF(ISNUMBER(D40),D40&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A40="",D40=""),"",IF(NOT(IF(ISNUMBER(D40),D40&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C40),ISNUMBER(D40),C40&gt;D40),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D40*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H40" s="25">
@@ -2290,7 +2290,7 @@
         <v/>
       </c>
       <c r="I40" s="26">
-        <f>IF(A40="","",IF(E40="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E40="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E40="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A40="","",IF(AND(ISNUMBER(C40),ISNUMBER(D40),C40&gt;D40),"Corrija a faixa de horas: o de é maior que o até",IF(E40="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E40="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E40="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2301,11 +2301,11 @@
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="24" t="n"/>
       <c r="F41" s="25">
-        <f>IF(OR(A41="",C41=""),"",IF(NOT(IF(ISNUMBER(C41),C41&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A41="",C41=""),"",IF(NOT(IF(ISNUMBER(C41),C41&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C41),ISNUMBER(D41),C41&gt;D41),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C41*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G41" s="25">
-        <f>IF(OR(A41="",D41=""),"",IF(NOT(IF(ISNUMBER(D41),D41&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A41="",D41=""),"",IF(NOT(IF(ISNUMBER(D41),D41&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C41),ISNUMBER(D41),C41&gt;D41),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D41*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H41" s="25">
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="I41" s="26">
-        <f>IF(A41="","",IF(E41="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E41="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E41="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A41="","",IF(AND(ISNUMBER(C41),ISNUMBER(D41),C41&gt;D41),"Corrija a faixa de horas: o de é maior que o até",IF(E41="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E41="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E41="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2324,11 +2324,11 @@
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="25">
-        <f>IF(OR(A42="",C42=""),"",IF(NOT(IF(ISNUMBER(C42),C42&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A42="",C42=""),"",IF(NOT(IF(ISNUMBER(C42),C42&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C42),ISNUMBER(D42),C42&gt;D42),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C42*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G42" s="25">
-        <f>IF(OR(A42="",D42=""),"",IF(NOT(IF(ISNUMBER(D42),D42&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A42="",D42=""),"",IF(NOT(IF(ISNUMBER(D42),D42&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C42),ISNUMBER(D42),C42&gt;D42),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D42*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H42" s="25">
@@ -2336,7 +2336,7 @@
         <v/>
       </c>
       <c r="I42" s="26">
-        <f>IF(A42="","",IF(E42="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E42="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E42="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A42="","",IF(AND(ISNUMBER(C42),ISNUMBER(D42),C42&gt;D42),"Corrija a faixa de horas: o de é maior que o até",IF(E42="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E42="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E42="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2347,11 +2347,11 @@
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="24" t="n"/>
       <c r="F43" s="25">
-        <f>IF(OR(A43="",C43=""),"",IF(NOT(IF(ISNUMBER(C43),C43&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A43="",C43=""),"",IF(NOT(IF(ISNUMBER(C43),C43&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C43),ISNUMBER(D43),C43&gt;D43),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C43*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G43" s="25">
-        <f>IF(OR(A43="",D43=""),"",IF(NOT(IF(ISNUMBER(D43),D43&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A43="",D43=""),"",IF(NOT(IF(ISNUMBER(D43),D43&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C43),ISNUMBER(D43),C43&gt;D43),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D43*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H43" s="25">
@@ -2359,7 +2359,7 @@
         <v/>
       </c>
       <c r="I43" s="26">
-        <f>IF(A43="","",IF(E43="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E43="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E43="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A43="","",IF(AND(ISNUMBER(C43),ISNUMBER(D43),C43&gt;D43),"Corrija a faixa de horas: o de é maior que o até",IF(E43="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E43="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E43="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2370,11 +2370,11 @@
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="24" t="n"/>
       <c r="F44" s="25">
-        <f>IF(OR(A44="",C44=""),"",IF(NOT(IF(ISNUMBER(C44),C44&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A44="",C44=""),"",IF(NOT(IF(ISNUMBER(C44),C44&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C44),ISNUMBER(D44),C44&gt;D44),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C44*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G44" s="25">
-        <f>IF(OR(A44="",D44=""),"",IF(NOT(IF(ISNUMBER(D44),D44&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A44="",D44=""),"",IF(NOT(IF(ISNUMBER(D44),D44&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C44),ISNUMBER(D44),C44&gt;D44),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D44*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H44" s="25">
@@ -2382,7 +2382,7 @@
         <v/>
       </c>
       <c r="I44" s="26">
-        <f>IF(A44="","",IF(E44="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E44="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E44="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A44="","",IF(AND(ISNUMBER(C44),ISNUMBER(D44),C44&gt;D44),"Corrija a faixa de horas: o de é maior que o até",IF(E44="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E44="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E44="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2393,11 +2393,11 @@
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="24" t="n"/>
       <c r="F45" s="25">
-        <f>IF(OR(A45="",C45=""),"",IF(NOT(IF(ISNUMBER(C45),C45&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A45="",C45=""),"",IF(NOT(IF(ISNUMBER(C45),C45&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C45),ISNUMBER(D45),C45&gt;D45),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C45*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G45" s="25">
-        <f>IF(OR(A45="",D45=""),"",IF(NOT(IF(ISNUMBER(D45),D45&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A45="",D45=""),"",IF(NOT(IF(ISNUMBER(D45),D45&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C45),ISNUMBER(D45),C45&gt;D45),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D45*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H45" s="25">
@@ -2405,7 +2405,7 @@
         <v/>
       </c>
       <c r="I45" s="26">
-        <f>IF(A45="","",IF(E45="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E45="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E45="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A45="","",IF(AND(ISNUMBER(C45),ISNUMBER(D45),C45&gt;D45),"Corrija a faixa de horas: o de é maior que o até",IF(E45="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E45="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E45="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2416,11 +2416,11 @@
       <c r="D46" s="23" t="n"/>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="25">
-        <f>IF(OR(A46="",C46=""),"",IF(NOT(IF(ISNUMBER(C46),C46&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A46="",C46=""),"",IF(NOT(IF(ISNUMBER(C46),C46&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C46),ISNUMBER(D46),C46&gt;D46),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C46*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G46" s="25">
-        <f>IF(OR(A46="",D46=""),"",IF(NOT(IF(ISNUMBER(D46),D46&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A46="",D46=""),"",IF(NOT(IF(ISNUMBER(D46),D46&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C46),ISNUMBER(D46),C46&gt;D46),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D46*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H46" s="25">
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="I46" s="26">
-        <f>IF(A46="","",IF(E46="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E46="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E46="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A46="","",IF(AND(ISNUMBER(C46),ISNUMBER(D46),C46&gt;D46),"Corrija a faixa de horas: o de é maior que o até",IF(E46="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E46="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E46="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2439,11 +2439,11 @@
       <c r="D47" s="23" t="n"/>
       <c r="E47" s="24" t="n"/>
       <c r="F47" s="25">
-        <f>IF(OR(A47="",C47=""),"",IF(NOT(IF(ISNUMBER(C47),C47&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A47="",C47=""),"",IF(NOT(IF(ISNUMBER(C47),C47&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C47),ISNUMBER(D47),C47&gt;D47),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C47*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G47" s="25">
-        <f>IF(OR(A47="",D47=""),"",IF(NOT(IF(ISNUMBER(D47),D47&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A47="",D47=""),"",IF(NOT(IF(ISNUMBER(D47),D47&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C47),ISNUMBER(D47),C47&gt;D47),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D47*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H47" s="25">
@@ -2451,7 +2451,7 @@
         <v/>
       </c>
       <c r="I47" s="26">
-        <f>IF(A47="","",IF(E47="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E47="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E47="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A47="","",IF(AND(ISNUMBER(C47),ISNUMBER(D47),C47&gt;D47),"Corrija a faixa de horas: o de é maior que o até",IF(E47="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E47="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E47="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -2462,11 +2462,11 @@
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="24" t="n"/>
       <c r="F48" s="25">
-        <f>IF(OR(A48="",C48=""),"",IF(NOT(IF(ISNUMBER(C48),C48&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12)))</f>
+        <f>IF(OR(A48="",C48=""),"",IF(NOT(IF(ISNUMBER(C48),C48&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C48),ISNUMBER(D48),C48&gt;D48),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$12),C48*Config!$B$12,Config!$B$12))))</f>
         <v/>
       </c>
       <c r="G48" s="25">
-        <f>IF(OR(A48="",D48=""),"",IF(NOT(IF(ISNUMBER(D48),D48&gt;=0,FALSE)),"horas inválidas",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13)))</f>
+        <f>IF(OR(A48="",D48=""),"",IF(NOT(IF(ISNUMBER(D48),D48&gt;=0,FALSE)),"horas inválidas",IF(AND(ISNUMBER(C48),ISNUMBER(D48),C48&gt;D48),"faixa invertida (de &gt; até)",IF(ISNUMBER(Config!$B$13),D48*Config!$B$13,Config!$B$13))))</f>
         <v/>
       </c>
       <c r="H48" s="25">
@@ -2474,7 +2474,7 @@
         <v/>
       </c>
       <c r="I48" s="26">
-        <f>IF(A48="","",IF(E48="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E48="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E48="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo"))))</f>
+        <f>IF(A48="","",IF(AND(ISNUMBER(C48),ISNUMBER(D48),C48&gt;D48),"Corrija a faixa de horas: o de é maior que o até",IF(E48="Hora","Cobre a hora entre a mínima e a alvo; a faixa é o total esperado",IF(E48="Êxito","Percentual que, na chance esperada, fique dentro da faixa",IF(E48="Misto","Entrada perto do mínimo; o êxito leva ao máximo","Caso simples perto do mínimo; complexo perto do máximo")))))</f>
         <v/>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="B12" s="39">
-        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1,B11&gt;=0),FALSE),B7*(1+B11)/(1-B8-B9),"margens inválidas (Config)"))</f>
+        <f>IF(NOT(IF(ISNUMBER(B7),B7&gt;=0,FALSE)),"falta o custo-hora",IF(IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1,B11&gt;=0),FALSE),B7*(1+B11)/(1-B8-B9),"margens inválidas (Config)"))</f>
         <v>127.880129032258</v>
       </c>
       <c r="C12" s="27" t="inlineStr">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="B13" s="39">
-        <f>IF(NOT(ISNUMBER(B7)),"falta o custo-hora",IF(IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1,B11&gt;=0),FALSE),B7*(1+B11)/(1-B8-B10),"margens inválidas (Config)"))</f>
+        <f>IF(NOT(IF(ISNUMBER(B7),B7&gt;=0,FALSE)),"falta o custo-hora",IF(IF(AND(ISNUMBER(B8),ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),AND(B8&gt;=0,B8&lt;1,B9&gt;=0,B9&lt;=B10,B10&lt;1,B8+B10&lt;1,B11&gt;=0),FALSE),B7*(1+B11)/(1-B8-B10),"margens inválidas (Config)"))</f>
         <v>168.692936170213</v>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem alvo abaixo de 100 %." type="custom">
       <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B10)&lt;1),FALSE)</formula1>
     </dataValidation>
@@ -3994,6 +3994,9 @@
     </dataValidation>
     <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Folga de 0 % para cima." type="custom">
       <formula1>=IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Custo-hora" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
